--- a/BRISAS/EXPENSAS/2026/JULIO/BRISAS-JULIO.xlsx
+++ b/BRISAS/EXPENSAS/2026/JULIO/BRISAS-JULIO.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="24334"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\USUARIOS\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistemax\Desktop\rc-consorcio2025\BRISAS\EXPENSAS\2026\JULIO\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C60F9E6-A38F-4F64-9B9B-70A05046600E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4746F670-34C2-4D77-9BAF-46222AFAC20F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" tabRatio="850" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="850" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RESUMEN" sheetId="1" r:id="rId1"/>
@@ -22,11 +22,16 @@
     <definedName name="_xlnm.Print_Area" localSheetId="0">RESUMEN!$A$1:$E$208</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
+  <extLst>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="738" uniqueCount="471">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="756" uniqueCount="473">
   <si>
     <t>Dpto.</t>
   </si>
@@ -1455,6 +1460,12 @@
   </si>
   <si>
     <t>Transfririo $727.479 el 13/07</t>
+  </si>
+  <si>
+    <t>Lote 70 transirio $1.000.000 el 30/07</t>
+  </si>
+  <si>
+    <t>Lote 109 transfirio $741.000 el 30/07</t>
   </si>
 </sst>
 </file>
@@ -2319,7 +2330,7 @@
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="430">
+  <cellXfs count="434">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
@@ -2796,6 +2807,18 @@
     <xf numFmtId="0" fontId="0" fillId="8" borderId="16" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="17" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="17" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="17" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -3119,9 +3142,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema de Office">
   <a:themeElements>
-    <a:clrScheme name="Office 2007 - 2010">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -3159,9 +3182,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -3194,9 +3217,26 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -3229,9 +3269,26 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -3406,49 +3463,49 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:O208"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="37.5546875" customWidth="1"/>
-    <col min="2" max="2" width="24.5546875" customWidth="1"/>
-    <col min="3" max="3" width="15.88671875" hidden="1" customWidth="1"/>
-    <col min="4" max="4" width="21.44140625" customWidth="1"/>
-    <col min="5" max="5" width="16.88671875" customWidth="1"/>
-    <col min="6" max="6" width="16.44140625" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="15.44140625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="37.5703125" customWidth="1"/>
+    <col min="2" max="2" width="24.5703125" customWidth="1"/>
+    <col min="3" max="3" width="15.85546875" hidden="1" customWidth="1"/>
+    <col min="4" max="4" width="21.42578125" customWidth="1"/>
+    <col min="5" max="5" width="16.85546875" customWidth="1"/>
+    <col min="6" max="6" width="16.42578125" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="15.42578125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.140625" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="18" customWidth="1"/>
-    <col min="12" max="12" width="18.44140625" customWidth="1"/>
+    <col min="12" max="12" width="18.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="381"/>
-      <c r="B1" s="376" t="s">
+    <row r="1" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="385"/>
+      <c r="B1" s="380" t="s">
         <v>155</v>
       </c>
-      <c r="C1" s="377"/>
-      <c r="D1" s="377"/>
-      <c r="E1" s="378"/>
-    </row>
-    <row r="2" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="382"/>
-      <c r="B2" s="376" t="s">
+      <c r="C1" s="381"/>
+      <c r="D1" s="381"/>
+      <c r="E1" s="382"/>
+    </row>
+    <row r="2" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="386"/>
+      <c r="B2" s="380" t="s">
         <v>157</v>
       </c>
-      <c r="C2" s="377"/>
-      <c r="D2" s="377"/>
-      <c r="E2" s="378"/>
-    </row>
-    <row r="3" spans="1:5" ht="32.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="382"/>
-      <c r="B3" s="373" t="s">
+      <c r="C2" s="381"/>
+      <c r="D2" s="381"/>
+      <c r="E2" s="382"/>
+    </row>
+    <row r="3" spans="1:5" ht="32.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="386"/>
+      <c r="B3" s="377" t="s">
         <v>153</v>
       </c>
-      <c r="C3" s="374"/>
-      <c r="D3" s="374"/>
-      <c r="E3" s="375"/>
-    </row>
-    <row r="4" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="382"/>
+      <c r="C3" s="378"/>
+      <c r="D3" s="378"/>
+      <c r="E3" s="379"/>
+    </row>
+    <row r="4" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="386"/>
       <c r="B4" s="43" t="s">
         <v>154</v>
       </c>
@@ -3456,8 +3513,8 @@
       <c r="D4" s="42"/>
       <c r="E4" s="42"/>
     </row>
-    <row r="5" spans="1:5" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="382"/>
+    <row r="5" spans="1:5" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="386"/>
       <c r="B5" s="46" t="s">
         <v>338</v>
       </c>
@@ -3465,8 +3522,8 @@
       <c r="D5" s="44"/>
       <c r="E5" s="45"/>
     </row>
-    <row r="6" spans="1:5" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="382"/>
+    <row r="6" spans="1:5" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="386"/>
       <c r="B6" s="47" t="s">
         <v>282</v>
       </c>
@@ -3474,8 +3531,8 @@
       <c r="D6" s="44"/>
       <c r="E6" s="45"/>
     </row>
-    <row r="7" spans="1:5" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="382"/>
+    <row r="7" spans="1:5" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="386"/>
       <c r="B7" s="47" t="s">
         <v>281</v>
       </c>
@@ -3483,111 +3540,111 @@
       <c r="D7" s="44"/>
       <c r="E7" s="45"/>
     </row>
-    <row r="8" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="383"/>
-      <c r="B8" s="379" t="s">
+    <row r="8" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="387"/>
+      <c r="B8" s="383" t="s">
         <v>156</v>
       </c>
-      <c r="C8" s="379"/>
-      <c r="D8" s="379"/>
-      <c r="E8" s="380"/>
-    </row>
-    <row r="9" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C8" s="383"/>
+      <c r="D8" s="383"/>
+      <c r="E8" s="384"/>
+    </row>
+    <row r="9" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="30"/>
       <c r="B9" s="30"/>
       <c r="C9" s="30"/>
       <c r="D9" s="30"/>
       <c r="E9" s="30"/>
     </row>
-    <row r="10" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="358" t="s">
+    <row r="10" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="362" t="s">
         <v>343</v>
       </c>
-      <c r="B10" s="359"/>
-      <c r="C10" s="359"/>
-      <c r="D10" s="359"/>
-      <c r="E10" s="360"/>
-    </row>
-    <row r="11" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="361"/>
-      <c r="B11" s="362"/>
-      <c r="C11" s="362"/>
-      <c r="D11" s="362"/>
-      <c r="E11" s="363"/>
-    </row>
-    <row r="12" spans="1:5" ht="14.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="364"/>
-      <c r="B12" s="365"/>
-      <c r="C12" s="365"/>
-      <c r="D12" s="365"/>
-      <c r="E12" s="366"/>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B10" s="363"/>
+      <c r="C10" s="363"/>
+      <c r="D10" s="363"/>
+      <c r="E10" s="364"/>
+    </row>
+    <row r="11" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="365"/>
+      <c r="B11" s="366"/>
+      <c r="C11" s="366"/>
+      <c r="D11" s="366"/>
+      <c r="E11" s="367"/>
+    </row>
+    <row r="12" spans="1:5" ht="14.45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="368"/>
+      <c r="B12" s="369"/>
+      <c r="C12" s="369"/>
+      <c r="D12" s="369"/>
+      <c r="E12" s="370"/>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" s="30"/>
       <c r="B13" s="30"/>
       <c r="C13" s="30"/>
       <c r="D13" s="30"/>
       <c r="E13" s="30"/>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" s="30"/>
       <c r="B14" s="30"/>
       <c r="C14" s="30"/>
       <c r="D14" s="30"/>
       <c r="E14" s="30"/>
     </row>
-    <row r="15" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="367" t="s">
+    <row r="15" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="371" t="s">
         <v>240</v>
       </c>
-      <c r="B15" s="367"/>
-      <c r="C15" s="367"/>
-      <c r="D15" s="367"/>
-      <c r="E15" s="367"/>
-    </row>
-    <row r="16" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="367"/>
-      <c r="B16" s="367"/>
-      <c r="C16" s="367"/>
-      <c r="D16" s="367"/>
-      <c r="E16" s="367"/>
-    </row>
-    <row r="17" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="367"/>
-      <c r="B17" s="367"/>
-      <c r="C17" s="367"/>
-      <c r="D17" s="367"/>
-      <c r="E17" s="367"/>
-    </row>
-    <row r="18" spans="1:8" ht="243" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="367"/>
-      <c r="B18" s="367"/>
-      <c r="C18" s="367"/>
-      <c r="D18" s="367"/>
-      <c r="E18" s="367"/>
-    </row>
-    <row r="19" spans="1:8" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B15" s="371"/>
+      <c r="C15" s="371"/>
+      <c r="D15" s="371"/>
+      <c r="E15" s="371"/>
+    </row>
+    <row r="16" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="371"/>
+      <c r="B16" s="371"/>
+      <c r="C16" s="371"/>
+      <c r="D16" s="371"/>
+      <c r="E16" s="371"/>
+    </row>
+    <row r="17" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="371"/>
+      <c r="B17" s="371"/>
+      <c r="C17" s="371"/>
+      <c r="D17" s="371"/>
+      <c r="E17" s="371"/>
+    </row>
+    <row r="18" spans="1:8" ht="243" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="371"/>
+      <c r="B18" s="371"/>
+      <c r="C18" s="371"/>
+      <c r="D18" s="371"/>
+      <c r="E18" s="371"/>
+    </row>
+    <row r="19" spans="1:8" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A19" s="30"/>
       <c r="B19" s="30"/>
       <c r="C19" s="30"/>
       <c r="D19" s="30"/>
       <c r="E19" s="30"/>
     </row>
-    <row r="20" spans="1:8" ht="14.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:8" ht="14.45" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="89"/>
       <c r="B20" s="30"/>
       <c r="C20" s="30"/>
       <c r="D20" s="30"/>
       <c r="E20" s="30"/>
     </row>
-    <row r="21" spans="1:8" ht="15" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:8" ht="15" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A21" s="30"/>
       <c r="B21" s="30"/>
       <c r="C21" s="30"/>
       <c r="D21" s="30"/>
       <c r="E21" s="30"/>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" s="90" t="s">
         <v>5</v>
       </c>
@@ -3598,7 +3655,7 @@
       <c r="F22" s="30"/>
       <c r="G22" s="30"/>
     </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" s="8" t="s">
         <v>18</v>
       </c>
@@ -3609,7 +3666,7 @@
       <c r="F23" s="30"/>
       <c r="G23" s="30"/>
     </row>
-    <row r="24" spans="1:8" ht="36.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:8" ht="36.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="187" t="s">
         <v>339</v>
       </c>
@@ -3624,11 +3681,11 @@
       <c r="F24" s="30"/>
       <c r="G24" s="254"/>
     </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A25" s="369" t="s">
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A25" s="373" t="s">
         <v>340</v>
       </c>
-      <c r="B25" s="370"/>
+      <c r="B25" s="374"/>
       <c r="C25" s="22"/>
       <c r="D25" s="271">
         <v>-739800.57</v>
@@ -3637,11 +3694,11 @@
       <c r="F25" s="30"/>
       <c r="G25" s="255"/>
     </row>
-    <row r="26" spans="1:8" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="371" t="s">
+    <row r="26" spans="1:8" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="375" t="s">
         <v>341</v>
       </c>
-      <c r="B26" s="372"/>
+      <c r="B26" s="376"/>
       <c r="C26" s="22"/>
       <c r="D26" s="271">
         <v>0.69</v>
@@ -3650,7 +3707,7 @@
       <c r="F26" s="255"/>
       <c r="G26" s="255"/>
     </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A27" s="95" t="s">
         <v>19</v>
       </c>
@@ -3665,11 +3722,11 @@
       <c r="G27" s="255"/>
       <c r="H27" s="71"/>
     </row>
-    <row r="28" spans="1:8" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="348" t="s">
+    <row r="28" spans="1:8" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="352" t="s">
         <v>364</v>
       </c>
-      <c r="B28" s="349"/>
+      <c r="B28" s="353"/>
       <c r="C28" s="22"/>
       <c r="D28" s="253">
         <v>1520000</v>
@@ -3683,7 +3740,7 @@
         <v>2104581</v>
       </c>
     </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29" s="95" t="s">
         <v>19</v>
       </c>
@@ -3697,7 +3754,7 @@
       <c r="F29" s="30"/>
       <c r="G29" s="255"/>
     </row>
-    <row r="30" spans="1:8" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:8" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A30" s="96" t="s">
         <v>167</v>
       </c>
@@ -3711,7 +3768,7 @@
       <c r="F30" s="255"/>
       <c r="G30" s="30"/>
     </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A31" s="8" t="s">
         <v>173</v>
       </c>
@@ -3722,7 +3779,7 @@
       <c r="F31" s="30"/>
       <c r="G31" s="30"/>
     </row>
-    <row r="32" spans="1:8" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:8" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="22" t="s">
         <v>344</v>
       </c>
@@ -3737,7 +3794,7 @@
       <c r="F32" s="256"/>
       <c r="G32" s="257"/>
     </row>
-    <row r="33" spans="1:9" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:9" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="98" t="s">
         <v>345</v>
       </c>
@@ -3754,7 +3811,7 @@
       <c r="F33" s="256"/>
       <c r="G33" s="257"/>
     </row>
-    <row r="34" spans="1:9" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:9" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="98" t="str">
         <f>A33</f>
         <v>Sindicatos mes de JUNIO</v>
@@ -3773,7 +3830,7 @@
       <c r="F34" s="256"/>
       <c r="G34" s="257"/>
     </row>
-    <row r="35" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="98" t="str">
         <f>A34</f>
         <v>Sindicatos mes de JUNIO</v>
@@ -3793,7 +3850,7 @@
       <c r="G35" s="30"/>
       <c r="H35" s="33"/>
     </row>
-    <row r="36" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A36" s="96" t="s">
         <v>147</v>
       </c>
@@ -3807,7 +3864,7 @@
       <c r="F36" s="30"/>
       <c r="G36" s="30"/>
     </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A37" s="8" t="s">
         <v>166</v>
       </c>
@@ -3818,11 +3875,11 @@
       <c r="F37" s="30"/>
       <c r="G37" s="30"/>
     </row>
-    <row r="38" spans="1:9" ht="32.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A38" s="348" t="s">
+    <row r="38" spans="1:9" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="352" t="s">
         <v>268</v>
       </c>
-      <c r="B38" s="349"/>
+      <c r="B38" s="353"/>
       <c r="C38" s="22"/>
       <c r="D38" s="198">
         <v>148964</v>
@@ -3833,11 +3890,11 @@
       <c r="F38" s="30"/>
       <c r="G38" s="30"/>
     </row>
-    <row r="39" spans="1:9" ht="32.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A39" s="348" t="s">
+    <row r="39" spans="1:9" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A39" s="352" t="s">
         <v>269</v>
       </c>
-      <c r="B39" s="349"/>
+      <c r="B39" s="353"/>
       <c r="C39" s="22"/>
       <c r="D39" s="198">
         <v>7453</v>
@@ -3848,11 +3905,11 @@
       <c r="F39" s="30"/>
       <c r="G39" s="30"/>
     </row>
-    <row r="40" spans="1:9" ht="32.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A40" s="348" t="s">
+    <row r="40" spans="1:9" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A40" s="352" t="s">
         <v>269</v>
       </c>
-      <c r="B40" s="349"/>
+      <c r="B40" s="353"/>
       <c r="C40" s="22"/>
       <c r="D40" s="198">
         <v>7453</v>
@@ -3863,11 +3920,11 @@
       <c r="F40" s="30"/>
       <c r="G40" s="30"/>
     </row>
-    <row r="41" spans="1:9" ht="32.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A41" s="348" t="s">
+    <row r="41" spans="1:9" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A41" s="352" t="s">
         <v>308</v>
       </c>
-      <c r="B41" s="349"/>
+      <c r="B41" s="353"/>
       <c r="C41" s="22"/>
       <c r="D41" s="198">
         <v>23573.47</v>
@@ -3878,7 +3935,7 @@
       <c r="F41" s="30"/>
       <c r="G41" s="30"/>
     </row>
-    <row r="42" spans="1:9" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:9" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A42" s="96" t="s">
         <v>148</v>
       </c>
@@ -3892,7 +3949,7 @@
       <c r="F42" s="30"/>
       <c r="G42" s="30"/>
     </row>
-    <row r="43" spans="1:9" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:9" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A43" s="64" t="s">
         <v>174</v>
       </c>
@@ -3903,11 +3960,11 @@
       <c r="F43" s="30"/>
       <c r="G43" s="30"/>
     </row>
-    <row r="44" spans="1:9" ht="42.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A44" s="348" t="s">
+    <row r="44" spans="1:9" ht="42.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A44" s="352" t="s">
         <v>395</v>
       </c>
-      <c r="B44" s="368"/>
+      <c r="B44" s="372"/>
       <c r="C44" s="101"/>
       <c r="D44" s="198">
         <v>47492852.960000001</v>
@@ -3922,11 +3979,11 @@
       <c r="G44" s="258"/>
       <c r="I44" s="37"/>
     </row>
-    <row r="45" spans="1:9" ht="41.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A45" s="348" t="s">
+    <row r="45" spans="1:9" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A45" s="352" t="s">
         <v>352</v>
       </c>
-      <c r="B45" s="368"/>
+      <c r="B45" s="372"/>
       <c r="C45" s="101"/>
       <c r="D45" s="198">
         <v>5892398.1600000001</v>
@@ -3937,7 +3994,7 @@
       <c r="F45" s="258"/>
       <c r="G45" s="30"/>
     </row>
-    <row r="46" spans="1:9" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:9" ht="17.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="96" t="s">
         <v>175</v>
       </c>
@@ -3951,7 +4008,7 @@
       <c r="F46" s="30"/>
       <c r="G46" s="30"/>
     </row>
-    <row r="47" spans="1:9" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:9" ht="17.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="64" t="s">
         <v>176</v>
       </c>
@@ -3964,11 +4021,11 @@
       <c r="F47" s="30"/>
       <c r="G47" s="30"/>
     </row>
-    <row r="48" spans="1:9" ht="40.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A48" s="348" t="s">
+    <row r="48" spans="1:9" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A48" s="352" t="s">
         <v>400</v>
       </c>
-      <c r="B48" s="368"/>
+      <c r="B48" s="372"/>
       <c r="C48" s="101"/>
       <c r="D48" s="198">
         <v>1472058.6</v>
@@ -3979,11 +4036,11 @@
       <c r="F48" s="30"/>
       <c r="G48" s="30"/>
     </row>
-    <row r="49" spans="1:8" ht="51.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A49" s="348" t="s">
+    <row r="49" spans="1:8" ht="51.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A49" s="352" t="s">
         <v>418</v>
       </c>
-      <c r="B49" s="368"/>
+      <c r="B49" s="372"/>
       <c r="C49" s="101"/>
       <c r="D49" s="198">
         <v>909920</v>
@@ -3994,11 +4051,11 @@
       <c r="F49" s="30"/>
       <c r="G49" s="30"/>
     </row>
-    <row r="50" spans="1:8" ht="51.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A50" s="348" t="s">
+    <row r="50" spans="1:8" ht="51.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A50" s="352" t="s">
         <v>399</v>
       </c>
-      <c r="B50" s="368"/>
+      <c r="B50" s="372"/>
       <c r="C50" s="101"/>
       <c r="D50" s="198">
         <v>25613.279999999999</v>
@@ -4009,11 +4066,11 @@
       <c r="F50" s="30"/>
       <c r="G50" s="30"/>
     </row>
-    <row r="51" spans="1:8" ht="51.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A51" s="348" t="s">
+    <row r="51" spans="1:8" ht="51.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A51" s="352" t="s">
         <v>409</v>
       </c>
-      <c r="B51" s="368"/>
+      <c r="B51" s="372"/>
       <c r="C51" s="101"/>
       <c r="D51" s="198">
         <v>97574.399999999994</v>
@@ -4024,11 +4081,11 @@
       <c r="F51" s="30"/>
       <c r="G51" s="30"/>
     </row>
-    <row r="52" spans="1:8" ht="37.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A52" s="348" t="s">
+    <row r="52" spans="1:8" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A52" s="352" t="s">
         <v>376</v>
       </c>
-      <c r="B52" s="349"/>
+      <c r="B52" s="353"/>
       <c r="C52" s="102"/>
       <c r="D52" s="198">
         <v>6300000</v>
@@ -4039,11 +4096,11 @@
       <c r="F52" s="30"/>
       <c r="G52" s="30"/>
     </row>
-    <row r="53" spans="1:8" ht="39" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A53" s="348" t="s">
+    <row r="53" spans="1:8" ht="39" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A53" s="352" t="s">
         <v>346</v>
       </c>
-      <c r="B53" s="349"/>
+      <c r="B53" s="353"/>
       <c r="C53" s="102"/>
       <c r="D53" s="198">
         <v>228690</v>
@@ -4054,11 +4111,11 @@
       <c r="F53" s="30"/>
       <c r="G53" s="30"/>
     </row>
-    <row r="54" spans="1:8" ht="60" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A54" s="348" t="s">
+    <row r="54" spans="1:8" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A54" s="352" t="s">
         <v>416</v>
       </c>
-      <c r="B54" s="349"/>
+      <c r="B54" s="353"/>
       <c r="C54" s="102"/>
       <c r="D54" s="198">
         <v>0</v>
@@ -4067,11 +4124,11 @@
       <c r="F54" s="30"/>
       <c r="G54" s="30"/>
     </row>
-    <row r="55" spans="1:8" ht="73.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A55" s="348" t="s">
+    <row r="55" spans="1:8" ht="73.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A55" s="352" t="s">
         <v>411</v>
       </c>
-      <c r="B55" s="349"/>
+      <c r="B55" s="353"/>
       <c r="C55" s="102"/>
       <c r="D55" s="198">
         <v>1899700</v>
@@ -4082,11 +4139,11 @@
       <c r="F55" s="30"/>
       <c r="G55" s="30"/>
     </row>
-    <row r="56" spans="1:8" ht="44.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A56" s="348" t="s">
+    <row r="56" spans="1:8" ht="44.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A56" s="352" t="s">
         <v>410</v>
       </c>
-      <c r="B56" s="349"/>
+      <c r="B56" s="353"/>
       <c r="C56" s="102"/>
       <c r="D56" s="198">
         <v>943800</v>
@@ -4097,11 +4154,11 @@
       <c r="F56" s="30"/>
       <c r="G56" s="30"/>
     </row>
-    <row r="57" spans="1:8" ht="37.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A57" s="348" t="s">
+    <row r="57" spans="1:8" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A57" s="352" t="s">
         <v>361</v>
       </c>
-      <c r="B57" s="349"/>
+      <c r="B57" s="353"/>
       <c r="C57" s="102"/>
       <c r="D57" s="198">
         <v>820380</v>
@@ -4112,11 +4169,11 @@
       <c r="F57" s="30"/>
       <c r="G57" s="30"/>
     </row>
-    <row r="58" spans="1:8" ht="37.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A58" s="348" t="s">
+    <row r="58" spans="1:8" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A58" s="352" t="s">
         <v>355</v>
       </c>
-      <c r="B58" s="349"/>
+      <c r="B58" s="353"/>
       <c r="C58" s="102"/>
       <c r="D58" s="198">
         <v>110000</v>
@@ -4127,11 +4184,11 @@
       <c r="F58" s="30"/>
       <c r="G58" s="30"/>
     </row>
-    <row r="59" spans="1:8" ht="37.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A59" s="348" t="s">
+    <row r="59" spans="1:8" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A59" s="352" t="s">
         <v>377</v>
       </c>
-      <c r="B59" s="349"/>
+      <c r="B59" s="353"/>
       <c r="C59" s="102"/>
       <c r="D59" s="198">
         <v>110000</v>
@@ -4142,11 +4199,11 @@
       <c r="F59" s="30"/>
       <c r="G59" s="30"/>
     </row>
-    <row r="60" spans="1:8" ht="37.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A60" s="348" t="s">
+    <row r="60" spans="1:8" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A60" s="352" t="s">
         <v>396</v>
       </c>
-      <c r="B60" s="349"/>
+      <c r="B60" s="353"/>
       <c r="C60" s="102"/>
       <c r="D60" s="198">
         <v>220000</v>
@@ -4157,11 +4214,11 @@
       <c r="F60" s="30"/>
       <c r="G60" s="30"/>
     </row>
-    <row r="61" spans="1:8" ht="37.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A61" s="348" t="s">
+    <row r="61" spans="1:8" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A61" s="352" t="s">
         <v>342</v>
       </c>
-      <c r="B61" s="349"/>
+      <c r="B61" s="353"/>
       <c r="C61" s="102"/>
       <c r="D61" s="198">
         <v>1300000</v>
@@ -4172,11 +4229,11 @@
       <c r="F61" s="30"/>
       <c r="G61" s="30"/>
     </row>
-    <row r="62" spans="1:8" ht="51" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A62" s="348" t="s">
+    <row r="62" spans="1:8" ht="51" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A62" s="352" t="s">
         <v>378</v>
       </c>
-      <c r="B62" s="349"/>
+      <c r="B62" s="353"/>
       <c r="C62" s="22"/>
       <c r="D62" s="198">
         <v>2459883</v>
@@ -4188,7 +4245,7 @@
       <c r="G62" s="259"/>
       <c r="H62" s="86"/>
     </row>
-    <row r="63" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A63" s="96" t="s">
         <v>177</v>
       </c>
@@ -4202,7 +4259,7 @@
       <c r="F63" s="30"/>
       <c r="G63" s="30"/>
     </row>
-    <row r="64" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A64" s="8" t="s">
         <v>178</v>
       </c>
@@ -4213,11 +4270,11 @@
       <c r="F64" s="30"/>
       <c r="G64" s="30"/>
     </row>
-    <row r="65" spans="1:7" ht="63.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A65" s="348" t="s">
+    <row r="65" spans="1:7" ht="63.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A65" s="352" t="s">
         <v>383</v>
       </c>
-      <c r="B65" s="349"/>
+      <c r="B65" s="353"/>
       <c r="C65" s="22"/>
       <c r="D65" s="276">
         <v>1500000</v>
@@ -4228,12 +4285,12 @@
       <c r="F65" s="30"/>
       <c r="G65" s="30"/>
     </row>
-    <row r="66" spans="1:7" ht="63.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A66" s="348" t="s">
+    <row r="66" spans="1:7" ht="63.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A66" s="352" t="s">
         <v>392</v>
       </c>
-      <c r="B66" s="368"/>
-      <c r="C66" s="349"/>
+      <c r="B66" s="372"/>
+      <c r="C66" s="353"/>
       <c r="D66" s="276">
         <v>750000</v>
       </c>
@@ -4243,11 +4300,11 @@
       <c r="F66" s="30"/>
       <c r="G66" s="30"/>
     </row>
-    <row r="67" spans="1:7" ht="51.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A67" s="348" t="s">
+    <row r="67" spans="1:7" ht="51.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A67" s="352" t="s">
         <v>408</v>
       </c>
-      <c r="B67" s="349"/>
+      <c r="B67" s="353"/>
       <c r="C67" s="22"/>
       <c r="D67" s="276">
         <v>3600000</v>
@@ -4258,11 +4315,11 @@
       <c r="F67" s="30"/>
       <c r="G67" s="30"/>
     </row>
-    <row r="68" spans="1:7" ht="55.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A68" s="348" t="s">
+    <row r="68" spans="1:7" ht="55.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A68" s="352" t="s">
         <v>386</v>
       </c>
-      <c r="B68" s="349"/>
+      <c r="B68" s="353"/>
       <c r="C68" s="98"/>
       <c r="D68" s="276">
         <v>904475</v>
@@ -4273,11 +4330,11 @@
       <c r="F68" s="259"/>
       <c r="G68" s="30"/>
     </row>
-    <row r="69" spans="1:7" ht="52.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A69" s="348" t="s">
+    <row r="69" spans="1:7" ht="52.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A69" s="352" t="s">
         <v>390</v>
       </c>
-      <c r="B69" s="349"/>
+      <c r="B69" s="353"/>
       <c r="C69" s="98"/>
       <c r="D69" s="276">
         <v>188854.26</v>
@@ -4288,11 +4345,11 @@
       <c r="F69" s="259"/>
       <c r="G69" s="30"/>
     </row>
-    <row r="70" spans="1:7" ht="52.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A70" s="348" t="s">
+    <row r="70" spans="1:7" ht="52.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A70" s="352" t="s">
         <v>407</v>
       </c>
-      <c r="B70" s="349"/>
+      <c r="B70" s="353"/>
       <c r="C70" s="98"/>
       <c r="D70" s="276">
         <v>41000</v>
@@ -4303,11 +4360,11 @@
       <c r="F70" s="259"/>
       <c r="G70" s="30"/>
     </row>
-    <row r="71" spans="1:7" ht="52.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A71" s="348" t="s">
+    <row r="71" spans="1:7" ht="52.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A71" s="352" t="s">
         <v>419</v>
       </c>
-      <c r="B71" s="349"/>
+      <c r="B71" s="353"/>
       <c r="C71" s="98"/>
       <c r="D71" s="276">
         <v>600000</v>
@@ -4318,11 +4375,11 @@
       <c r="F71" s="259"/>
       <c r="G71" s="30"/>
     </row>
-    <row r="72" spans="1:7" ht="52.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A72" s="348" t="s">
+    <row r="72" spans="1:7" ht="52.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A72" s="352" t="s">
         <v>421</v>
       </c>
-      <c r="B72" s="349"/>
+      <c r="B72" s="353"/>
       <c r="C72" s="98"/>
       <c r="D72" s="276">
         <v>312000</v>
@@ -4333,11 +4390,11 @@
       <c r="F72" s="259"/>
       <c r="G72" s="30"/>
     </row>
-    <row r="73" spans="1:7" ht="52.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A73" s="348" t="s">
+    <row r="73" spans="1:7" ht="52.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A73" s="352" t="s">
         <v>422</v>
       </c>
-      <c r="B73" s="349"/>
+      <c r="B73" s="353"/>
       <c r="C73" s="98"/>
       <c r="D73" s="276">
         <v>160000</v>
@@ -4348,11 +4405,11 @@
       <c r="F73" s="259"/>
       <c r="G73" s="30"/>
     </row>
-    <row r="74" spans="1:7" ht="50.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A74" s="348" t="s">
+    <row r="74" spans="1:7" ht="50.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A74" s="352" t="s">
         <v>356</v>
       </c>
-      <c r="B74" s="349"/>
+      <c r="B74" s="353"/>
       <c r="C74" s="98"/>
       <c r="D74" s="276">
         <v>324000</v>
@@ -4363,7 +4420,7 @@
       <c r="F74" s="259"/>
       <c r="G74" s="30"/>
     </row>
-    <row r="75" spans="1:7" ht="31.35" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:7" ht="31.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A75" s="231" t="s">
         <v>349</v>
       </c>
@@ -4378,7 +4435,7 @@
       <c r="F75" s="30"/>
       <c r="G75" s="30"/>
     </row>
-    <row r="76" spans="1:7" ht="31.35" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:7" ht="31.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A76" s="231" t="s">
         <v>366</v>
       </c>
@@ -4393,11 +4450,11 @@
       <c r="F76" s="30"/>
       <c r="G76" s="30"/>
     </row>
-    <row r="77" spans="1:7" ht="43.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A77" s="348" t="s">
+    <row r="77" spans="1:7" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A77" s="352" t="s">
         <v>350</v>
       </c>
-      <c r="B77" s="349"/>
+      <c r="B77" s="353"/>
       <c r="C77" s="98"/>
       <c r="D77" s="276">
         <v>21660</v>
@@ -4408,11 +4465,11 @@
       <c r="F77" s="30"/>
       <c r="G77" s="30"/>
     </row>
-    <row r="78" spans="1:7" ht="42" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A78" s="348" t="s">
+    <row r="78" spans="1:7" ht="42" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A78" s="352" t="s">
         <v>351</v>
       </c>
-      <c r="B78" s="349"/>
+      <c r="B78" s="353"/>
       <c r="C78" s="98"/>
       <c r="D78" s="276">
         <v>11610</v>
@@ -4423,11 +4480,11 @@
       <c r="F78" s="259"/>
       <c r="G78" s="30"/>
     </row>
-    <row r="79" spans="1:7" ht="40.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A79" s="348" t="s">
+    <row r="79" spans="1:7" ht="40.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A79" s="352" t="s">
         <v>426</v>
       </c>
-      <c r="B79" s="349"/>
+      <c r="B79" s="353"/>
       <c r="C79" s="98"/>
       <c r="D79" s="276">
         <v>165848.65</v>
@@ -4438,11 +4495,11 @@
       <c r="F79" s="259"/>
       <c r="G79" s="30"/>
     </row>
-    <row r="80" spans="1:7" ht="40.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A80" s="348" t="s">
+    <row r="80" spans="1:7" ht="40.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A80" s="352" t="s">
         <v>385</v>
       </c>
-      <c r="B80" s="349"/>
+      <c r="B80" s="353"/>
       <c r="C80" s="98"/>
       <c r="D80" s="276">
         <v>1839200</v>
@@ -4453,11 +4510,11 @@
       <c r="F80" s="259"/>
       <c r="G80" s="30"/>
     </row>
-    <row r="81" spans="1:7" ht="40.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A81" s="348" t="s">
+    <row r="81" spans="1:7" ht="40.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A81" s="352" t="s">
         <v>389</v>
       </c>
-      <c r="B81" s="349"/>
+      <c r="B81" s="353"/>
       <c r="C81" s="98"/>
       <c r="D81" s="276">
         <v>1778700</v>
@@ -4468,11 +4525,11 @@
       <c r="F81" s="259"/>
       <c r="G81" s="30"/>
     </row>
-    <row r="82" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A82" s="348" t="s">
+    <row r="82" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A82" s="352" t="s">
         <v>415</v>
       </c>
-      <c r="B82" s="349"/>
+      <c r="B82" s="353"/>
       <c r="C82" s="98"/>
       <c r="D82" s="276">
         <v>175329</v>
@@ -4483,11 +4540,11 @@
       <c r="F82" s="30"/>
       <c r="G82" s="30"/>
     </row>
-    <row r="83" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A83" s="348" t="s">
+    <row r="83" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A83" s="352" t="s">
         <v>401</v>
       </c>
-      <c r="B83" s="349"/>
+      <c r="B83" s="353"/>
       <c r="C83" s="98"/>
       <c r="D83" s="276">
         <v>253193.5</v>
@@ -4498,11 +4555,11 @@
       <c r="F83" s="30"/>
       <c r="G83" s="30"/>
     </row>
-    <row r="84" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A84" s="348" t="s">
+    <row r="84" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A84" s="352" t="s">
         <v>387</v>
       </c>
-      <c r="B84" s="349"/>
+      <c r="B84" s="353"/>
       <c r="C84" s="98"/>
       <c r="D84" s="276">
         <v>57542.45</v>
@@ -4513,11 +4570,11 @@
       <c r="F84" s="30"/>
       <c r="G84" s="30"/>
     </row>
-    <row r="85" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A85" s="348" t="s">
+    <row r="85" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A85" s="352" t="s">
         <v>381</v>
       </c>
-      <c r="B85" s="349"/>
+      <c r="B85" s="353"/>
       <c r="C85" s="98"/>
       <c r="D85" s="276">
         <v>27888.333999999999</v>
@@ -4528,11 +4585,11 @@
       <c r="F85" s="30"/>
       <c r="G85" s="30"/>
     </row>
-    <row r="86" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A86" s="348" t="s">
+    <row r="86" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A86" s="352" t="s">
         <v>368</v>
       </c>
-      <c r="B86" s="349"/>
+      <c r="B86" s="353"/>
       <c r="C86" s="98"/>
       <c r="D86" s="276">
         <v>18600</v>
@@ -4543,11 +4600,11 @@
       <c r="F86" s="30"/>
       <c r="G86" s="30"/>
     </row>
-    <row r="87" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A87" s="348" t="s">
+    <row r="87" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A87" s="352" t="s">
         <v>379</v>
       </c>
-      <c r="B87" s="349"/>
+      <c r="B87" s="353"/>
       <c r="C87" s="98"/>
       <c r="D87" s="276">
         <v>1154830.69</v>
@@ -4558,11 +4615,11 @@
       <c r="F87" s="30"/>
       <c r="G87" s="30"/>
     </row>
-    <row r="88" spans="1:7" ht="68.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A88" s="348" t="s">
+    <row r="88" spans="1:7" ht="68.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A88" s="352" t="s">
         <v>412</v>
       </c>
-      <c r="B88" s="349"/>
+      <c r="B88" s="353"/>
       <c r="C88" s="98"/>
       <c r="D88" s="276">
         <v>1250000</v>
@@ -4573,11 +4630,11 @@
       <c r="F88" s="30"/>
       <c r="G88" s="30"/>
     </row>
-    <row r="89" spans="1:7" ht="66" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A89" s="348" t="s">
+    <row r="89" spans="1:7" ht="66" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A89" s="352" t="s">
         <v>413</v>
       </c>
-      <c r="B89" s="349"/>
+      <c r="B89" s="353"/>
       <c r="C89" s="98"/>
       <c r="D89" s="276">
         <v>1250000</v>
@@ -4588,11 +4645,11 @@
       <c r="F89" s="30"/>
       <c r="G89" s="30"/>
     </row>
-    <row r="90" spans="1:7" ht="66" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A90" s="348" t="s">
+    <row r="90" spans="1:7" ht="66" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A90" s="352" t="s">
         <v>424</v>
       </c>
-      <c r="B90" s="349"/>
+      <c r="B90" s="353"/>
       <c r="C90" s="98"/>
       <c r="D90" s="276">
         <v>1125000</v>
@@ -4603,11 +4660,11 @@
       <c r="F90" s="30"/>
       <c r="G90" s="30"/>
     </row>
-    <row r="91" spans="1:7" ht="70.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A91" s="348" t="s">
+    <row r="91" spans="1:7" ht="70.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A91" s="352" t="s">
         <v>414</v>
       </c>
-      <c r="B91" s="349"/>
+      <c r="B91" s="353"/>
       <c r="C91" s="98"/>
       <c r="D91" s="276">
         <v>750000</v>
@@ -4618,11 +4675,11 @@
       <c r="F91" s="30"/>
       <c r="G91" s="30"/>
     </row>
-    <row r="92" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A92" s="348" t="s">
+    <row r="92" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A92" s="352" t="s">
         <v>329</v>
       </c>
-      <c r="B92" s="349"/>
+      <c r="B92" s="353"/>
       <c r="C92" s="98"/>
       <c r="D92" s="276">
         <v>350000</v>
@@ -4633,7 +4690,7 @@
       <c r="F92" s="30"/>
       <c r="G92" s="30"/>
     </row>
-    <row r="93" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A93" s="104" t="s">
         <v>179</v>
       </c>
@@ -4647,7 +4704,7 @@
       <c r="F93" s="30"/>
       <c r="G93" s="30"/>
     </row>
-    <row r="94" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A94" s="8" t="s">
         <v>12</v>
       </c>
@@ -4658,11 +4715,11 @@
       <c r="F94" s="30"/>
       <c r="G94" s="30"/>
     </row>
-    <row r="95" spans="1:7" ht="23.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A95" s="348" t="s">
+    <row r="95" spans="1:7" ht="23.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A95" s="352" t="s">
         <v>430</v>
       </c>
-      <c r="B95" s="349"/>
+      <c r="B95" s="353"/>
       <c r="C95" s="22"/>
       <c r="D95" s="260">
         <v>0</v>
@@ -4671,7 +4728,7 @@
       <c r="F95" s="30"/>
       <c r="G95" s="30"/>
     </row>
-    <row r="96" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A96" s="96" t="s">
         <v>149</v>
       </c>
@@ -4685,7 +4742,7 @@
       <c r="F96" s="30"/>
       <c r="G96" s="30"/>
     </row>
-    <row r="97" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A97" s="8" t="s">
         <v>7</v>
       </c>
@@ -4696,7 +4753,7 @@
       <c r="F97" s="30"/>
       <c r="G97" s="30"/>
     </row>
-    <row r="98" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A98" s="22" t="s">
         <v>22</v>
       </c>
@@ -4710,7 +4767,7 @@
       <c r="F98" s="30"/>
       <c r="G98" s="30"/>
     </row>
-    <row r="99" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A99" s="22" t="s">
         <v>23</v>
       </c>
@@ -4723,7 +4780,7 @@
       <c r="F99" s="30"/>
       <c r="G99" s="30"/>
     </row>
-    <row r="100" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A100" s="105" t="s">
         <v>150</v>
       </c>
@@ -4737,7 +4794,7 @@
       <c r="F100" s="30"/>
       <c r="G100" s="30"/>
     </row>
-    <row r="101" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A101" s="22"/>
       <c r="B101" s="22"/>
       <c r="C101" s="22"/>
@@ -4746,7 +4803,7 @@
       <c r="F101" s="30"/>
       <c r="G101" s="30"/>
     </row>
-    <row r="102" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A102" s="22"/>
       <c r="B102" s="22"/>
       <c r="C102" s="22"/>
@@ -4755,7 +4812,7 @@
       <c r="F102" s="258"/>
       <c r="G102" s="261"/>
     </row>
-    <row r="103" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A103" s="106" t="s">
         <v>8</v>
       </c>
@@ -4769,7 +4826,7 @@
       <c r="F103" s="262"/>
       <c r="G103" s="30"/>
     </row>
-    <row r="104" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A104" s="30"/>
       <c r="B104" s="30"/>
       <c r="C104" s="30"/>
@@ -4778,7 +4835,7 @@
       <c r="F104" s="30"/>
       <c r="G104" s="30"/>
     </row>
-    <row r="105" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A105" s="30"/>
       <c r="B105" s="30"/>
       <c r="C105" s="30"/>
@@ -4787,7 +4844,7 @@
       <c r="F105" s="30"/>
       <c r="G105" s="30"/>
     </row>
-    <row r="106" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A106" s="108" t="s">
         <v>9</v>
       </c>
@@ -4798,11 +4855,11 @@
       <c r="F106" s="30"/>
       <c r="G106" s="30"/>
     </row>
-    <row r="107" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A107" s="348" t="s">
+    <row r="107" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A107" s="352" t="s">
         <v>406</v>
       </c>
-      <c r="B107" s="349"/>
+      <c r="B107" s="353"/>
       <c r="C107" s="22"/>
       <c r="D107" s="198">
         <v>262370.37</v>
@@ -4813,11 +4870,11 @@
       <c r="F107" s="30"/>
       <c r="G107" s="30"/>
     </row>
-    <row r="108" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A108" s="348" t="s">
+    <row r="108" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A108" s="352" t="s">
         <v>332</v>
       </c>
-      <c r="B108" s="349"/>
+      <c r="B108" s="353"/>
       <c r="C108" s="22"/>
       <c r="D108" s="198">
         <v>55287.19</v>
@@ -4828,11 +4885,11 @@
       <c r="F108" s="30"/>
       <c r="G108" s="30"/>
     </row>
-    <row r="109" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A109" s="348" t="s">
+    <row r="109" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A109" s="352" t="s">
         <v>333</v>
       </c>
-      <c r="B109" s="349"/>
+      <c r="B109" s="353"/>
       <c r="C109" s="22"/>
       <c r="D109" s="198">
         <v>55287.19</v>
@@ -4844,11 +4901,11 @@
       <c r="F109" s="30"/>
       <c r="G109" s="30"/>
     </row>
-    <row r="110" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A110" s="348" t="s">
+    <row r="110" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A110" s="352" t="s">
         <v>334</v>
       </c>
-      <c r="B110" s="349"/>
+      <c r="B110" s="353"/>
       <c r="C110" s="22"/>
       <c r="D110" s="198">
         <v>55486.59</v>
@@ -4860,11 +4917,11 @@
       <c r="F110" s="30"/>
       <c r="G110" s="30"/>
     </row>
-    <row r="111" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A111" s="350" t="s">
+    <row r="111" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A111" s="354" t="s">
         <v>369</v>
       </c>
-      <c r="B111" s="351"/>
+      <c r="B111" s="355"/>
       <c r="C111" s="22"/>
       <c r="D111" s="198">
         <v>1213387.58</v>
@@ -4875,11 +4932,11 @@
       <c r="F111" s="30"/>
       <c r="G111" s="30"/>
     </row>
-    <row r="112" spans="1:7" ht="54.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A112" s="350" t="s">
+    <row r="112" spans="1:7" ht="54.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A112" s="354" t="s">
         <v>370</v>
       </c>
-      <c r="B112" s="351"/>
+      <c r="B112" s="355"/>
       <c r="C112" s="22"/>
       <c r="D112" s="198">
         <v>433890.06</v>
@@ -4890,11 +4947,11 @@
       <c r="F112" s="30"/>
       <c r="G112" s="30"/>
     </row>
-    <row r="113" spans="1:7" ht="52.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A113" s="350" t="s">
+    <row r="113" spans="1:7" ht="52.15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A113" s="354" t="s">
         <v>371</v>
       </c>
-      <c r="B113" s="351"/>
+      <c r="B113" s="355"/>
       <c r="C113" s="22"/>
       <c r="D113" s="198">
         <v>118075.67</v>
@@ -4905,11 +4962,11 @@
       <c r="F113" s="30"/>
       <c r="G113" s="30"/>
     </row>
-    <row r="114" spans="1:7" ht="52.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A114" s="350" t="s">
+    <row r="114" spans="1:7" ht="52.15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A114" s="354" t="s">
         <v>372</v>
       </c>
-      <c r="B114" s="351"/>
+      <c r="B114" s="355"/>
       <c r="C114" s="22"/>
       <c r="D114" s="198">
         <v>87899.24</v>
@@ -4923,11 +4980,11 @@
       </c>
       <c r="G114" s="30"/>
     </row>
-    <row r="115" spans="1:7" ht="38.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A115" s="350" t="s">
+    <row r="115" spans="1:7" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A115" s="354" t="s">
         <v>189</v>
       </c>
-      <c r="B115" s="351"/>
+      <c r="B115" s="355"/>
       <c r="C115" s="22"/>
       <c r="D115" s="198">
         <v>115627.44</v>
@@ -4939,11 +4996,11 @@
       <c r="F115" s="30"/>
       <c r="G115" s="30"/>
     </row>
-    <row r="116" spans="1:7" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A116" s="350" t="s">
+    <row r="116" spans="1:7" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A116" s="354" t="s">
         <v>300</v>
       </c>
-      <c r="B116" s="351"/>
+      <c r="B116" s="355"/>
       <c r="C116" s="22"/>
       <c r="D116" s="198">
         <v>6911.2</v>
@@ -4956,7 +5013,7 @@
         <v>319</v>
       </c>
     </row>
-    <row r="117" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A117" s="108" t="s">
         <v>4</v>
       </c>
@@ -4970,7 +5027,7 @@
       <c r="F117" s="30"/>
       <c r="G117" s="30"/>
     </row>
-    <row r="118" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="118" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A118" s="30"/>
       <c r="B118" s="30"/>
       <c r="C118" s="30"/>
@@ -4979,7 +5036,7 @@
       <c r="F118" s="30"/>
       <c r="G118" s="30"/>
     </row>
-    <row r="119" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A119" s="109" t="s">
         <v>21</v>
       </c>
@@ -4990,11 +5047,11 @@
       <c r="F119" s="30"/>
       <c r="G119" s="30"/>
     </row>
-    <row r="120" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A120" s="350" t="s">
+    <row r="120" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A120" s="354" t="s">
         <v>363</v>
       </c>
-      <c r="B120" s="351"/>
+      <c r="B120" s="355"/>
       <c r="C120" s="22"/>
       <c r="D120" s="263">
         <v>17995434.600000001</v>
@@ -5005,11 +5062,11 @@
       <c r="F120" s="30"/>
       <c r="G120" s="30"/>
     </row>
-    <row r="121" spans="1:7" ht="51.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A121" s="348" t="s">
+    <row r="121" spans="1:7" ht="51.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A121" s="352" t="s">
         <v>374</v>
       </c>
-      <c r="B121" s="349"/>
+      <c r="B121" s="353"/>
       <c r="C121" s="22"/>
       <c r="D121" s="263">
         <v>1443530</v>
@@ -5020,11 +5077,11 @@
       <c r="F121" s="30"/>
       <c r="G121" s="30"/>
     </row>
-    <row r="122" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A122" s="348" t="s">
+    <row r="122" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A122" s="352" t="s">
         <v>404</v>
       </c>
-      <c r="B122" s="349"/>
+      <c r="B122" s="353"/>
       <c r="C122" s="22"/>
       <c r="D122" s="263">
         <v>8064666.6699999999</v>
@@ -5035,11 +5092,11 @@
       <c r="F122" s="30"/>
       <c r="G122" s="30"/>
     </row>
-    <row r="123" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A123" s="348" t="s">
+    <row r="123" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A123" s="352" t="s">
         <v>417</v>
       </c>
-      <c r="B123" s="349"/>
+      <c r="B123" s="353"/>
       <c r="C123" s="22"/>
       <c r="D123" s="263">
         <v>1071600</v>
@@ -5050,11 +5107,11 @@
       <c r="F123" s="30"/>
       <c r="G123" s="30"/>
     </row>
-    <row r="124" spans="1:7" ht="43.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A124" s="348" t="s">
+    <row r="124" spans="1:7" ht="43.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A124" s="352" t="s">
         <v>398</v>
       </c>
-      <c r="B124" s="349"/>
+      <c r="B124" s="353"/>
       <c r="C124" s="98"/>
       <c r="D124" s="263">
         <v>1071600</v>
@@ -5065,7 +5122,7 @@
       <c r="F124" s="30"/>
       <c r="G124" s="30"/>
     </row>
-    <row r="125" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="125" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A125" s="112" t="s">
         <v>4</v>
       </c>
@@ -5079,7 +5136,7 @@
       <c r="F125" s="30"/>
       <c r="G125" s="30"/>
     </row>
-    <row r="126" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A126" s="30"/>
       <c r="B126" s="30"/>
       <c r="C126" s="30"/>
@@ -5088,7 +5145,7 @@
       <c r="F126" s="30"/>
       <c r="G126" s="30"/>
     </row>
-    <row r="127" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="127" spans="1:7" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A127" s="30"/>
       <c r="B127" s="30"/>
       <c r="C127" s="30"/>
@@ -5097,7 +5154,7 @@
       <c r="F127" s="30"/>
       <c r="G127" s="30"/>
     </row>
-    <row r="128" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="128" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A128" s="30"/>
       <c r="B128" s="30"/>
       <c r="C128" s="30"/>
@@ -5106,7 +5163,7 @@
       <c r="F128" s="30"/>
       <c r="G128" s="30"/>
     </row>
-    <row r="129" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="129" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A129" s="112" t="s">
         <v>13</v>
       </c>
@@ -5120,7 +5177,7 @@
       <c r="F129" s="30"/>
       <c r="G129" s="30"/>
     </row>
-    <row r="130" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="130" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A130" s="30"/>
       <c r="B130" s="30"/>
       <c r="C130" s="30"/>
@@ -5129,7 +5186,7 @@
       <c r="F130" s="30"/>
       <c r="G130" s="30"/>
     </row>
-    <row r="131" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A131" s="118" t="s">
         <v>187</v>
       </c>
@@ -5140,11 +5197,11 @@
       <c r="F131" s="30"/>
       <c r="G131" s="30"/>
     </row>
-    <row r="132" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A132" s="353" t="s">
+    <row r="132" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A132" s="357" t="s">
         <v>402</v>
       </c>
-      <c r="B132" s="353"/>
+      <c r="B132" s="357"/>
       <c r="C132" s="22"/>
       <c r="D132" s="198">
         <f>2104581-1520000</f>
@@ -5157,11 +5214,11 @@
       <c r="F132" s="258"/>
       <c r="G132" s="258"/>
     </row>
-    <row r="133" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A133" s="348" t="s">
+    <row r="133" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A133" s="352" t="s">
         <v>358</v>
       </c>
-      <c r="B133" s="349"/>
+      <c r="B133" s="353"/>
       <c r="C133" s="22"/>
       <c r="D133" s="198">
         <v>97321.42</v>
@@ -5173,11 +5230,11 @@
       <c r="F133" s="30"/>
       <c r="G133" s="30"/>
     </row>
-    <row r="134" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A134" s="348" t="s">
+    <row r="134" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A134" s="352" t="s">
         <v>359</v>
       </c>
-      <c r="B134" s="349"/>
+      <c r="B134" s="353"/>
       <c r="C134" s="22"/>
       <c r="D134" s="198">
         <v>97321.41</v>
@@ -5189,16 +5246,16 @@
       <c r="F134" s="30"/>
       <c r="G134" s="30"/>
     </row>
-    <row r="135" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A135" s="348"/>
-      <c r="B135" s="349"/>
+    <row r="135" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A135" s="352"/>
+      <c r="B135" s="353"/>
       <c r="C135" s="98"/>
       <c r="D135" s="198"/>
       <c r="E135" s="26"/>
       <c r="F135" s="30"/>
       <c r="G135" s="264"/>
     </row>
-    <row r="136" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A136" s="205" t="s">
         <v>4</v>
       </c>
@@ -5210,28 +5267,28 @@
         <v>779223.83000000007</v>
       </c>
     </row>
-    <row r="137" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A137" s="30"/>
       <c r="B137" s="30"/>
       <c r="C137" s="30"/>
       <c r="D137" s="30"/>
       <c r="E137" s="30"/>
     </row>
-    <row r="138" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A138" s="30"/>
       <c r="B138" s="30"/>
       <c r="C138" s="30"/>
       <c r="D138" s="30"/>
       <c r="E138" s="30"/>
     </row>
-    <row r="139" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="139" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A139" s="30"/>
       <c r="B139" s="30"/>
       <c r="C139" s="30"/>
       <c r="D139" s="30"/>
       <c r="E139" s="30"/>
     </row>
-    <row r="140" spans="1:7" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="140" spans="1:7" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A140" s="208" t="s">
         <v>188</v>
       </c>
@@ -5243,21 +5300,21 @@
         <v>779223.83000000007</v>
       </c>
     </row>
-    <row r="141" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A141" s="30"/>
       <c r="B141" s="30"/>
       <c r="C141" s="30"/>
       <c r="D141" s="30"/>
       <c r="E141" s="30"/>
     </row>
-    <row r="142" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="142" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A142" s="30"/>
       <c r="B142" s="30"/>
       <c r="C142" s="30"/>
       <c r="D142" s="30"/>
       <c r="E142" s="30"/>
     </row>
-    <row r="143" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="143" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A143" s="212" t="s">
         <v>180</v>
       </c>
@@ -5269,7 +5326,7 @@
       <c r="D143" s="30"/>
       <c r="E143" s="30"/>
     </row>
-    <row r="144" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="144" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A144" s="212" t="s">
         <v>21</v>
       </c>
@@ -5281,7 +5338,7 @@
       <c r="D144" s="30"/>
       <c r="E144" s="30"/>
     </row>
-    <row r="145" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="145" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A145" s="214" t="s">
         <v>151</v>
       </c>
@@ -5293,7 +5350,7 @@
       <c r="D145" s="30"/>
       <c r="E145" s="30"/>
     </row>
-    <row r="146" spans="1:5" ht="34.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="146" spans="1:5" ht="34.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A146" s="216" t="s">
         <v>227</v>
       </c>
@@ -5305,7 +5362,7 @@
       <c r="D146" s="30"/>
       <c r="E146" s="30"/>
     </row>
-    <row r="147" spans="1:5" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="147" spans="1:5" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A147" s="277" t="s">
         <v>441</v>
       </c>
@@ -5317,24 +5374,24 @@
       <c r="D147" s="30"/>
       <c r="E147" s="30"/>
     </row>
-    <row r="148" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C148" s="30"/>
       <c r="D148" s="30"/>
       <c r="E148" s="30"/>
     </row>
-    <row r="149" spans="1:5" ht="54.75" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="149" spans="1:5" ht="54.75" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C149" s="30"/>
       <c r="D149" s="30"/>
       <c r="E149" s="30"/>
     </row>
-    <row r="150" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A150" s="130" t="s">
         <v>234</v>
       </c>
       <c r="B150" s="121"/>
       <c r="C150" s="5"/>
     </row>
-    <row r="151" spans="1:5" s="148" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:5" s="148" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A151" s="145" t="s">
         <v>230</v>
       </c>
@@ -5344,7 +5401,7 @@
       <c r="C151" s="147"/>
       <c r="E151" s="149"/>
     </row>
-    <row r="152" spans="1:5" s="148" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:5" s="148" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A152" s="150" t="s">
         <v>231</v>
       </c>
@@ -5354,7 +5411,7 @@
       </c>
       <c r="C152" s="152"/>
     </row>
-    <row r="153" spans="1:5" s="148" customFormat="1" ht="36.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:5" s="148" customFormat="1" ht="36.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A153" s="7" t="s">
         <v>239</v>
       </c>
@@ -5365,7 +5422,7 @@
       <c r="C153" s="152"/>
       <c r="D153" s="149"/>
     </row>
-    <row r="154" spans="1:5" s="148" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:5" s="148" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A154" s="7" t="s">
         <v>432</v>
       </c>
@@ -5375,7 +5432,7 @@
       <c r="C154" s="152"/>
       <c r="D154" s="149"/>
     </row>
-    <row r="155" spans="1:5" s="148" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:5" s="148" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A155" s="7" t="s">
         <v>436</v>
       </c>
@@ -5386,7 +5443,7 @@
       <c r="C155" s="152"/>
       <c r="D155" s="149"/>
     </row>
-    <row r="156" spans="1:5" s="148" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:5" s="148" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A156" s="7" t="s">
         <v>436</v>
       </c>
@@ -5396,7 +5453,7 @@
       <c r="C156" s="152"/>
       <c r="D156" s="149"/>
     </row>
-    <row r="157" spans="1:5" s="148" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:5" s="148" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A157" s="7" t="s">
         <v>437</v>
       </c>
@@ -5406,7 +5463,7 @@
       <c r="C157" s="152"/>
       <c r="D157" s="149"/>
     </row>
-    <row r="158" spans="1:5" s="148" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:5" s="148" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A158" s="7" t="s">
         <v>336</v>
       </c>
@@ -5416,7 +5473,7 @@
       <c r="C158" s="152"/>
       <c r="D158" s="149"/>
     </row>
-    <row r="159" spans="1:5" s="148" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:5" s="148" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A159" s="133" t="s">
         <v>294</v>
       </c>
@@ -5427,7 +5484,7 @@
       <c r="C159" s="152"/>
       <c r="D159" s="149"/>
     </row>
-    <row r="160" spans="1:5" s="148" customFormat="1" ht="28.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:5" s="148" customFormat="1" ht="28.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A160" s="7" t="s">
         <v>325</v>
       </c>
@@ -5438,7 +5495,7 @@
       <c r="C160" s="152"/>
       <c r="D160" s="149"/>
     </row>
-    <row r="161" spans="1:7" s="148" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:7" s="148" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A161" s="32" t="s">
         <v>186</v>
       </c>
@@ -5449,7 +5506,7 @@
       <c r="C161" s="152"/>
       <c r="F161" s="155"/>
     </row>
-    <row r="162" spans="1:7" s="148" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:7" s="148" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A162" s="7" t="s">
         <v>152</v>
       </c>
@@ -5460,7 +5517,7 @@
       <c r="C162" s="152"/>
       <c r="D162" s="155"/>
     </row>
-    <row r="163" spans="1:7" s="148" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:7" s="148" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A163" s="7" t="s">
         <v>14</v>
       </c>
@@ -5473,7 +5530,7 @@
       <c r="E163" s="156"/>
       <c r="F163" s="228"/>
     </row>
-    <row r="164" spans="1:7" s="148" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:7" s="148" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A164" s="7" t="s">
         <v>257</v>
       </c>
@@ -5485,7 +5542,7 @@
       <c r="E164" s="156"/>
       <c r="F164" s="228"/>
     </row>
-    <row r="165" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A165" s="131" t="s">
         <v>4</v>
       </c>
@@ -5498,7 +5555,7 @@
       <c r="E165" s="37"/>
       <c r="F165" s="37"/>
     </row>
-    <row r="166" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A166" s="132"/>
       <c r="B166" s="11"/>
       <c r="C166" s="6"/>
@@ -5506,7 +5563,7 @@
       <c r="E166" s="34"/>
       <c r="F166" s="74"/>
     </row>
-    <row r="167" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="167" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A167" s="132"/>
       <c r="B167" s="11"/>
       <c r="C167" s="6"/>
@@ -5514,17 +5571,17 @@
       <c r="E167" s="34"/>
       <c r="F167" s="74"/>
     </row>
-    <row r="168" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A168" s="356" t="s">
+    <row r="168" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A168" s="360" t="s">
         <v>326</v>
       </c>
-      <c r="B168" s="357"/>
+      <c r="B168" s="361"/>
       <c r="C168" s="6"/>
       <c r="D168" s="13"/>
       <c r="E168" s="34"/>
       <c r="F168" s="74"/>
     </row>
-    <row r="169" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A169" s="126" t="s">
         <v>293</v>
       </c>
@@ -5536,7 +5593,7 @@
       <c r="E169" s="34"/>
       <c r="F169" s="74"/>
     </row>
-    <row r="170" spans="1:7" ht="66.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:7" ht="66.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A170" s="232" t="s">
         <v>327</v>
       </c>
@@ -5549,7 +5606,7 @@
       <c r="E170" s="34"/>
       <c r="F170" s="74"/>
     </row>
-    <row r="171" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="171" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A171" s="126"/>
       <c r="B171" s="127"/>
       <c r="C171" s="6"/>
@@ -5557,7 +5614,7 @@
       <c r="E171" s="34"/>
       <c r="F171" s="74"/>
     </row>
-    <row r="172" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="172" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A172" s="233" t="s">
         <v>4</v>
       </c>
@@ -5570,7 +5627,7 @@
       <c r="E172" s="34"/>
       <c r="F172" s="74"/>
     </row>
-    <row r="173" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A173" s="132"/>
       <c r="B173" s="11"/>
       <c r="C173" s="6"/>
@@ -5578,7 +5635,7 @@
       <c r="E173" s="34"/>
       <c r="F173" s="74"/>
     </row>
-    <row r="174" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="174" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A174" s="132"/>
       <c r="B174" s="11"/>
       <c r="C174" s="6"/>
@@ -5586,18 +5643,18 @@
       <c r="E174" s="34"/>
       <c r="F174" s="74"/>
     </row>
-    <row r="175" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A175" s="354" t="s">
+    <row r="175" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A175" s="358" t="s">
         <v>292</v>
       </c>
-      <c r="B175" s="355"/>
+      <c r="B175" s="359"/>
       <c r="C175" s="6"/>
       <c r="D175" s="13"/>
       <c r="E175" s="34"/>
       <c r="F175" s="74"/>
       <c r="G175" s="229"/>
     </row>
-    <row r="176" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A176" s="126" t="s">
         <v>293</v>
       </c>
@@ -5609,7 +5666,7 @@
       <c r="E176" s="34"/>
       <c r="F176" s="74"/>
     </row>
-    <row r="177" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A177" s="126" t="s">
         <v>294</v>
       </c>
@@ -5621,7 +5678,7 @@
       <c r="E177" s="34"/>
       <c r="F177" s="74"/>
     </row>
-    <row r="178" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="178" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A178" s="126" t="s">
         <v>440</v>
       </c>
@@ -5633,7 +5690,7 @@
       <c r="E178" s="34"/>
       <c r="F178" s="74"/>
     </row>
-    <row r="179" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="179" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A179" s="128" t="s">
         <v>4</v>
       </c>
@@ -5646,7 +5703,7 @@
       <c r="E179" s="34"/>
       <c r="F179" s="74"/>
     </row>
-    <row r="180" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="180" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A180" s="124"/>
       <c r="B180" s="125"/>
       <c r="C180" s="6"/>
@@ -5654,7 +5711,7 @@
       <c r="E180" s="34"/>
       <c r="F180" s="74"/>
     </row>
-    <row r="181" spans="1:7" ht="42.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="181" spans="1:7" ht="42.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A181" s="140" t="s">
         <v>330</v>
       </c>
@@ -5668,14 +5725,14 @@
       <c r="F181" s="74"/>
       <c r="G181" s="35"/>
     </row>
-    <row r="182" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B182" s="11"/>
       <c r="C182" s="6"/>
       <c r="D182" s="13"/>
       <c r="E182" s="34"/>
       <c r="F182" s="74"/>
     </row>
-    <row r="183" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A183" s="69" t="s">
         <v>233</v>
       </c>
@@ -5685,7 +5742,7 @@
       <c r="E183" s="34"/>
       <c r="F183" s="35"/>
     </row>
-    <row r="184" spans="1:7" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:7" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A184" s="88" t="s">
         <v>293</v>
       </c>
@@ -5697,7 +5754,7 @@
       <c r="E184" s="34"/>
       <c r="F184" s="35"/>
     </row>
-    <row r="185" spans="1:7" ht="54" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:7" ht="54" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A185" s="88" t="s">
         <v>362</v>
       </c>
@@ -5708,7 +5765,7 @@
       <c r="E185" s="34"/>
       <c r="F185" s="35"/>
     </row>
-    <row r="186" spans="1:7" ht="54" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:7" ht="54" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A186" s="272" t="s">
         <v>373</v>
       </c>
@@ -5719,7 +5776,7 @@
       <c r="E186" s="34"/>
       <c r="F186" s="35"/>
     </row>
-    <row r="187" spans="1:7" ht="54" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:7" ht="54" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A187" s="88" t="s">
         <v>429</v>
       </c>
@@ -5730,7 +5787,7 @@
       <c r="E187" s="34"/>
       <c r="F187" s="35"/>
     </row>
-    <row r="188" spans="1:7" ht="54" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:7" ht="54" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A188" s="88" t="s">
         <v>428</v>
       </c>
@@ -5742,7 +5799,7 @@
       <c r="E188" s="34"/>
       <c r="F188" s="35"/>
     </row>
-    <row r="189" spans="1:7" ht="54" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:7" ht="54" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A189" s="88" t="s">
         <v>431</v>
       </c>
@@ -5754,7 +5811,7 @@
       <c r="E189" s="34"/>
       <c r="F189" s="35"/>
     </row>
-    <row r="190" spans="1:7" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:7" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A190" s="88" t="s">
         <v>309</v>
       </c>
@@ -5764,7 +5821,7 @@
       <c r="E190" s="34"/>
       <c r="F190" s="35"/>
     </row>
-    <row r="191" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A191" s="69" t="s">
         <v>4</v>
       </c>
@@ -5777,14 +5834,14 @@
       <c r="E191" s="34"/>
       <c r="F191" s="35"/>
     </row>
-    <row r="192" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="192" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B192" s="11"/>
       <c r="C192" s="6"/>
       <c r="D192" s="13"/>
       <c r="E192" s="34"/>
       <c r="F192" s="35"/>
     </row>
-    <row r="193" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A193" s="122" t="s">
         <v>228</v>
       </c>
@@ -5803,7 +5860,7 @@
       <c r="N193" s="33"/>
       <c r="O193" s="33"/>
     </row>
-    <row r="194" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A194" s="67" t="s">
         <v>434</v>
       </c>
@@ -5824,7 +5881,7 @@
       <c r="N194" s="33"/>
       <c r="O194" s="33"/>
     </row>
-    <row r="195" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A195" s="67" t="s">
         <v>435</v>
       </c>
@@ -5845,7 +5902,7 @@
       <c r="N195" s="33"/>
       <c r="O195" s="33"/>
     </row>
-    <row r="196" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A196" s="67" t="s">
         <v>435</v>
       </c>
@@ -5867,7 +5924,7 @@
       <c r="N196" s="33"/>
       <c r="O196" s="33"/>
     </row>
-    <row r="197" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A197" s="67" t="s">
         <v>438</v>
       </c>
@@ -5889,7 +5946,7 @@
       <c r="N197" s="33"/>
       <c r="O197" s="33"/>
     </row>
-    <row r="198" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="198" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A198" s="67" t="s">
         <v>335</v>
       </c>
@@ -5910,7 +5967,7 @@
       <c r="N198" s="33"/>
       <c r="O198" s="33"/>
     </row>
-    <row r="199" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="199" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A199" s="123" t="s">
         <v>439</v>
       </c>
@@ -5931,7 +5988,7 @@
       <c r="N199" s="33"/>
       <c r="O199" s="33"/>
     </row>
-    <row r="200" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="200" spans="1:15" x14ac:dyDescent="0.25">
       <c r="B200" s="11"/>
       <c r="C200" s="6"/>
       <c r="D200" s="73"/>
@@ -5947,43 +6004,43 @@
       <c r="N200" s="33"/>
       <c r="O200" s="33"/>
     </row>
-    <row r="201" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:15" x14ac:dyDescent="0.25">
       <c r="B201" s="11"/>
       <c r="C201" s="6"/>
       <c r="D201" s="13"/>
       <c r="E201" s="34"/>
       <c r="F201" s="35"/>
     </row>
-    <row r="202" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="202" spans="1:15" x14ac:dyDescent="0.25">
       <c r="B202" s="11"/>
       <c r="C202" s="6"/>
       <c r="D202" s="13"/>
       <c r="E202" s="34"/>
       <c r="F202" s="35"/>
     </row>
-    <row r="203" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A203" s="352" t="s">
+    <row r="203" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A203" s="356" t="s">
         <v>17</v>
       </c>
-      <c r="B203" s="352"/>
-      <c r="C203" s="352"/>
-    </row>
-    <row r="204" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A204" s="352"/>
-      <c r="B204" s="352"/>
-      <c r="C204" s="352"/>
-    </row>
-    <row r="205" spans="1:15" ht="42" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B203" s="356"/>
+      <c r="C203" s="356"/>
+    </row>
+    <row r="204" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A204" s="356"/>
+      <c r="B204" s="356"/>
+      <c r="C204" s="356"/>
+    </row>
+    <row r="205" spans="1:15" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A205" s="63"/>
       <c r="B205" s="39"/>
       <c r="C205" s="62"/>
     </row>
-    <row r="206" spans="1:15" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="206" spans="1:15" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A206" s="63"/>
       <c r="B206" s="39"/>
       <c r="C206" s="62"/>
     </row>
-    <row r="207" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="207" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A207" s="14" t="s">
         <v>4</v>
       </c>
@@ -5993,7 +6050,7 @@
       </c>
       <c r="C207" s="15"/>
     </row>
-    <row r="208" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="208" spans="1:15" x14ac:dyDescent="0.25">
       <c r="M208" s="3"/>
     </row>
   </sheetData>
@@ -6088,56 +6145,56 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:Y167"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="4.44140625" hidden="1" customWidth="1"/>
-    <col min="2" max="2" width="4.44140625" customWidth="1"/>
-    <col min="3" max="3" width="25.5546875" customWidth="1"/>
-    <col min="4" max="4" width="8.109375" customWidth="1"/>
-    <col min="5" max="5" width="14.109375" customWidth="1"/>
-    <col min="6" max="6" width="12.44140625" customWidth="1"/>
-    <col min="7" max="7" width="11.5546875" customWidth="1"/>
-    <col min="8" max="8" width="9.5546875" customWidth="1"/>
-    <col min="9" max="9" width="13.44140625" customWidth="1"/>
+    <col min="1" max="1" width="4.42578125" hidden="1" customWidth="1"/>
+    <col min="2" max="2" width="4.42578125" customWidth="1"/>
+    <col min="3" max="3" width="25.5703125" customWidth="1"/>
+    <col min="4" max="4" width="8.140625" customWidth="1"/>
+    <col min="5" max="5" width="14.140625" customWidth="1"/>
+    <col min="6" max="6" width="12.42578125" customWidth="1"/>
+    <col min="7" max="7" width="11.5703125" customWidth="1"/>
+    <col min="8" max="8" width="9.5703125" customWidth="1"/>
+    <col min="9" max="9" width="13.42578125" customWidth="1"/>
     <col min="10" max="10" width="6" hidden="1" customWidth="1"/>
-    <col min="11" max="11" width="14.5546875" customWidth="1"/>
-    <col min="12" max="12" width="14.44140625" customWidth="1"/>
+    <col min="11" max="11" width="14.5703125" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" customWidth="1"/>
     <col min="13" max="13" width="19" customWidth="1"/>
-    <col min="14" max="15" width="13.88671875" customWidth="1"/>
-    <col min="16" max="16" width="14.5546875" customWidth="1"/>
+    <col min="14" max="15" width="13.85546875" customWidth="1"/>
+    <col min="16" max="16" width="14.5703125" customWidth="1"/>
     <col min="17" max="17" width="10" customWidth="1"/>
-    <col min="18" max="18" width="23.44140625" customWidth="1"/>
-    <col min="19" max="19" width="7.109375" hidden="1" customWidth="1"/>
-    <col min="20" max="20" width="10.44140625" customWidth="1"/>
+    <col min="18" max="18" width="23.42578125" customWidth="1"/>
+    <col min="19" max="19" width="7.140625" hidden="1" customWidth="1"/>
+    <col min="20" max="20" width="10.42578125" customWidth="1"/>
     <col min="21" max="21" width="13" bestFit="1" customWidth="1"/>
     <col min="24" max="24" width="16" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="11.88671875" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="11.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" ht="203.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:24" ht="203.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="2"/>
       <c r="B1" s="2"/>
-      <c r="C1" s="397" t="s">
+      <c r="C1" s="401" t="s">
         <v>442</v>
       </c>
-      <c r="D1" s="398"/>
-      <c r="E1" s="398"/>
-      <c r="F1" s="398"/>
-      <c r="G1" s="398"/>
-      <c r="H1" s="398"/>
-      <c r="I1" s="398"/>
-      <c r="J1" s="398"/>
-      <c r="K1" s="398"/>
-      <c r="L1" s="398"/>
+      <c r="D1" s="402"/>
+      <c r="E1" s="402"/>
+      <c r="F1" s="402"/>
+      <c r="G1" s="402"/>
+      <c r="H1" s="402"/>
+      <c r="I1" s="402"/>
+      <c r="J1" s="402"/>
+      <c r="K1" s="402"/>
+      <c r="L1" s="402"/>
       <c r="M1" s="142"/>
-      <c r="N1" s="399" t="s">
+      <c r="N1" s="403" t="s">
         <v>310</v>
       </c>
-      <c r="O1" s="399"/>
-      <c r="P1" s="394">
+      <c r="O1" s="403"/>
+      <c r="P1" s="398">
         <v>30000000</v>
       </c>
-      <c r="Q1" s="394"/>
+      <c r="Q1" s="398"/>
       <c r="R1" s="164"/>
       <c r="S1" s="4"/>
       <c r="T1" s="2"/>
@@ -6148,38 +6205,38 @@
         <v>80675963.920000002</v>
       </c>
     </row>
-    <row r="2" spans="1:24" ht="34.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:24" ht="34.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="2"/>
       <c r="B2" s="2"/>
-      <c r="C2" s="396" t="s">
+      <c r="C2" s="400" t="s">
         <v>226</v>
       </c>
-      <c r="D2" s="396"/>
-      <c r="E2" s="396"/>
+      <c r="D2" s="400"/>
+      <c r="E2" s="400"/>
       <c r="F2" s="142"/>
-      <c r="G2" s="391">
+      <c r="G2" s="395">
         <f>X2</f>
         <v>27518571.293111999</v>
       </c>
-      <c r="H2" s="391"/>
+      <c r="H2" s="395"/>
       <c r="I2" s="142" t="s">
         <v>274</v>
       </c>
       <c r="J2" s="142"/>
-      <c r="K2" s="391">
+      <c r="K2" s="395">
         <f>W1</f>
         <v>80675963.920000002</v>
       </c>
-      <c r="L2" s="391"/>
+      <c r="L2" s="395"/>
       <c r="M2" s="224"/>
       <c r="N2" s="225" t="s">
         <v>260</v>
       </c>
       <c r="O2" s="224"/>
-      <c r="P2" s="395">
-        <v>0</v>
-      </c>
-      <c r="Q2" s="395"/>
+      <c r="P2" s="399">
+        <v>0</v>
+      </c>
+      <c r="Q2" s="399"/>
       <c r="R2" s="165"/>
       <c r="T2" s="2"/>
       <c r="U2" t="s">
@@ -6190,115 +6247,115 @@
         <v>27518571.293111999</v>
       </c>
     </row>
-    <row r="3" spans="1:24" ht="91.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="404" t="str">
+    <row r="3" spans="1:24" ht="91.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="408" t="str">
         <f>"ATENCIÓN: Si usted abona antes del " &amp; TEXT(RESUMEN!A10,"dd/mm/yyyy") &amp; ", deberá abonar el importe indicado en la columna de color naranja. En caso de abonar con posterioridad a dicha fecha, deberá abonar el monto indicado en la columna de color celeste."</f>
         <v>ATENCIÓN: Si usted abona antes del Primer Vencimiento:  17/07, deberá abonar el importe indicado en la columna de color naranja. En caso de abonar con posterioridad a dicha fecha, deberá abonar el monto indicado en la columna de color celeste.</v>
       </c>
-      <c r="B3" s="405"/>
-      <c r="C3" s="405"/>
-      <c r="D3" s="405"/>
-      <c r="E3" s="405"/>
-      <c r="F3" s="405"/>
-      <c r="G3" s="405"/>
-      <c r="H3" s="405"/>
-      <c r="I3" s="405"/>
-      <c r="J3" s="405"/>
-      <c r="K3" s="405"/>
-      <c r="L3" s="405"/>
-      <c r="M3" s="405"/>
-      <c r="N3" s="405"/>
-      <c r="O3" s="405"/>
-      <c r="P3" s="405"/>
-      <c r="Q3" s="405"/>
-      <c r="R3" s="405"/>
-      <c r="S3" s="405"/>
-      <c r="T3" s="406"/>
+      <c r="B3" s="409"/>
+      <c r="C3" s="409"/>
+      <c r="D3" s="409"/>
+      <c r="E3" s="409"/>
+      <c r="F3" s="409"/>
+      <c r="G3" s="409"/>
+      <c r="H3" s="409"/>
+      <c r="I3" s="409"/>
+      <c r="J3" s="409"/>
+      <c r="K3" s="409"/>
+      <c r="L3" s="409"/>
+      <c r="M3" s="409"/>
+      <c r="N3" s="409"/>
+      <c r="O3" s="409"/>
+      <c r="P3" s="409"/>
+      <c r="Q3" s="409"/>
+      <c r="R3" s="409"/>
+      <c r="S3" s="409"/>
+      <c r="T3" s="410"/>
       <c r="X3" s="37"/>
     </row>
-    <row r="4" spans="1:24" ht="43.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="407" t="s">
-        <v>0</v>
-      </c>
-      <c r="B4" s="409" t="s">
+    <row r="4" spans="1:24" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="411" t="s">
+        <v>0</v>
+      </c>
+      <c r="B4" s="413" t="s">
         <v>1</v>
       </c>
-      <c r="C4" s="409" t="s">
+      <c r="C4" s="413" t="s">
         <v>2</v>
       </c>
-      <c r="D4" s="409" t="s">
+      <c r="D4" s="413" t="s">
         <v>6</v>
       </c>
-      <c r="E4" s="392" t="s">
+      <c r="E4" s="396" t="s">
         <v>181</v>
       </c>
-      <c r="F4" s="409" t="s">
+      <c r="F4" s="413" t="s">
         <v>3</v>
       </c>
-      <c r="G4" s="411" t="s">
+      <c r="G4" s="415" t="s">
         <v>16</v>
       </c>
-      <c r="H4" s="392" t="s">
+      <c r="H4" s="396" t="s">
         <v>232</v>
       </c>
-      <c r="I4" s="392" t="s">
+      <c r="I4" s="396" t="s">
         <v>15</v>
       </c>
-      <c r="J4" s="392"/>
-      <c r="K4" s="392" t="s">
+      <c r="J4" s="396"/>
+      <c r="K4" s="396" t="s">
         <v>182</v>
       </c>
-      <c r="L4" s="392" t="s">
+      <c r="L4" s="396" t="s">
         <v>146</v>
       </c>
-      <c r="M4" s="392" t="s">
+      <c r="M4" s="396" t="s">
         <v>184</v>
       </c>
-      <c r="N4" s="392" t="s">
+      <c r="N4" s="396" t="s">
         <v>183</v>
       </c>
-      <c r="O4" s="392" t="s">
+      <c r="O4" s="396" t="s">
         <v>320</v>
       </c>
-      <c r="P4" s="400" t="s">
+      <c r="P4" s="404" t="s">
         <v>318</v>
       </c>
-      <c r="Q4" s="401"/>
-      <c r="R4" s="400" t="s">
+      <c r="Q4" s="405"/>
+      <c r="R4" s="404" t="s">
         <v>313</v>
       </c>
-      <c r="S4" s="401"/>
-      <c r="T4" s="392" t="s">
+      <c r="S4" s="405"/>
+      <c r="T4" s="396" t="s">
         <v>258</v>
       </c>
       <c r="U4" s="13"/>
     </row>
-    <row r="5" spans="1:24" ht="25.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="408"/>
-      <c r="B5" s="410"/>
-      <c r="C5" s="410"/>
-      <c r="D5" s="410"/>
-      <c r="E5" s="393"/>
-      <c r="F5" s="410"/>
-      <c r="G5" s="412"/>
-      <c r="H5" s="393"/>
-      <c r="I5" s="393"/>
-      <c r="J5" s="393"/>
-      <c r="K5" s="393"/>
-      <c r="L5" s="393"/>
-      <c r="M5" s="393"/>
-      <c r="N5" s="393"/>
-      <c r="O5" s="393"/>
-      <c r="P5" s="402" t="str">
+    <row r="5" spans="1:24" ht="25.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="412"/>
+      <c r="B5" s="414"/>
+      <c r="C5" s="414"/>
+      <c r="D5" s="414"/>
+      <c r="E5" s="397"/>
+      <c r="F5" s="414"/>
+      <c r="G5" s="416"/>
+      <c r="H5" s="397"/>
+      <c r="I5" s="397"/>
+      <c r="J5" s="397"/>
+      <c r="K5" s="397"/>
+      <c r="L5" s="397"/>
+      <c r="M5" s="397"/>
+      <c r="N5" s="397"/>
+      <c r="O5" s="397"/>
+      <c r="P5" s="406" t="str">
         <f>RESUMEN!A10</f>
         <v>Primer Vencimiento:  17/07</v>
       </c>
-      <c r="Q5" s="403"/>
-      <c r="R5" s="402"/>
-      <c r="S5" s="403"/>
-      <c r="T5" s="393"/>
-    </row>
-    <row r="6" spans="1:24" ht="26.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="Q5" s="407"/>
+      <c r="R5" s="406"/>
+      <c r="S5" s="407"/>
+      <c r="T5" s="397"/>
+    </row>
+    <row r="6" spans="1:24" ht="26.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="184"/>
       <c r="B6" s="279">
         <v>1</v>
@@ -6349,11 +6406,11 @@
       <c r="O6" s="185">
         <v>0</v>
       </c>
-      <c r="P6" s="413">
+      <c r="P6" s="417">
         <f t="shared" ref="P6:P37" si="2">ROUND(SUM(G6:O6),0) + S6</f>
         <v>759748.01</v>
       </c>
-      <c r="Q6" s="414"/>
+      <c r="Q6" s="418"/>
       <c r="R6" s="226">
         <f t="shared" ref="R6:R37" si="3">ROUND(P6+P6*3.033%,0) + S6</f>
         <v>782791.01</v>
@@ -6370,7 +6427,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="7" spans="1:24" ht="24.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:24" ht="24.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="16"/>
       <c r="B7" s="309">
         <f>B6+1</f>
@@ -6419,11 +6476,11 @@
       <c r="O7" s="185">
         <v>0</v>
       </c>
-      <c r="P7" s="415">
+      <c r="P7" s="419">
         <f t="shared" si="2"/>
         <v>2811752.02</v>
       </c>
-      <c r="Q7" s="416"/>
+      <c r="Q7" s="420"/>
       <c r="R7" s="226">
         <f t="shared" si="3"/>
         <v>2897032.02</v>
@@ -6437,7 +6494,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="8" spans="1:24" ht="24.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:24" ht="24.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="16"/>
       <c r="B8" s="278">
         <f t="shared" ref="B8:B37" si="9">B7+1</f>
@@ -6488,11 +6545,11 @@
       <c r="O8" s="185">
         <v>0</v>
       </c>
-      <c r="P8" s="384">
+      <c r="P8" s="388">
         <f t="shared" si="2"/>
         <v>737383.03</v>
       </c>
-      <c r="Q8" s="384"/>
+      <c r="Q8" s="388"/>
       <c r="R8" s="226">
         <f t="shared" si="3"/>
         <v>759748.03</v>
@@ -6509,7 +6566,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="9" spans="1:24" ht="24.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:24" ht="24.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="16"/>
       <c r="B9" s="278">
         <f t="shared" si="9"/>
@@ -6560,11 +6617,11 @@
       <c r="O9" s="185">
         <v>0</v>
       </c>
-      <c r="P9" s="384">
+      <c r="P9" s="388">
         <f t="shared" si="2"/>
         <v>1583813.04</v>
       </c>
-      <c r="Q9" s="384"/>
+      <c r="Q9" s="388"/>
       <c r="R9" s="226">
         <f t="shared" si="3"/>
         <v>1631850.04</v>
@@ -6582,7 +6639,7 @@
         <v>303</v>
       </c>
     </row>
-    <row r="10" spans="1:24" ht="24.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:24" ht="24.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="16"/>
       <c r="B10" s="278">
         <f t="shared" si="9"/>
@@ -6634,11 +6691,11 @@
       <c r="O10" s="185">
         <v>0</v>
       </c>
-      <c r="P10" s="384">
+      <c r="P10" s="388">
         <f t="shared" si="2"/>
         <v>767816.05</v>
       </c>
-      <c r="Q10" s="384"/>
+      <c r="Q10" s="388"/>
       <c r="R10" s="226">
         <f t="shared" si="3"/>
         <v>791104.05</v>
@@ -6653,7 +6710,7 @@
       </c>
       <c r="U10" s="124"/>
     </row>
-    <row r="11" spans="1:24" ht="24.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:24" ht="24.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="16"/>
       <c r="B11" s="278">
         <f t="shared" si="9"/>
@@ -6704,11 +6761,11 @@
       <c r="O11" s="185">
         <v>0</v>
       </c>
-      <c r="P11" s="384">
+      <c r="P11" s="388">
         <f t="shared" si="2"/>
         <v>728882.06</v>
       </c>
-      <c r="Q11" s="384"/>
+      <c r="Q11" s="388"/>
       <c r="R11" s="226">
         <f t="shared" si="3"/>
         <v>750989.06</v>
@@ -6725,7 +6782,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="12" spans="1:24" ht="24.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:24" ht="24.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="162"/>
       <c r="B12" s="347">
         <f t="shared" si="9"/>
@@ -6776,11 +6833,11 @@
       <c r="O12" s="185">
         <v>0</v>
       </c>
-      <c r="P12" s="384">
+      <c r="P12" s="388">
         <f t="shared" si="2"/>
         <v>734400.07</v>
       </c>
-      <c r="Q12" s="384"/>
+      <c r="Q12" s="388"/>
       <c r="R12" s="226">
         <f t="shared" si="3"/>
         <v>756674.07</v>
@@ -6797,7 +6854,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="13" spans="1:24" ht="24.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:24" ht="24.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="162"/>
       <c r="B13" s="347">
         <f t="shared" si="9"/>
@@ -6848,11 +6905,11 @@
       <c r="O13" s="185">
         <v>0</v>
       </c>
-      <c r="P13" s="384">
+      <c r="P13" s="388">
         <f t="shared" si="2"/>
         <v>745234.08</v>
       </c>
-      <c r="Q13" s="384"/>
+      <c r="Q13" s="388"/>
       <c r="R13" s="226">
         <f t="shared" si="3"/>
         <v>767837.08</v>
@@ -6869,7 +6926,7 @@
         <v>278</v>
       </c>
     </row>
-    <row r="14" spans="1:24" ht="24.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:24" ht="24.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="16"/>
       <c r="B14" s="278">
         <f t="shared" si="9"/>
@@ -6920,11 +6977,11 @@
       <c r="O14" s="185">
         <v>0</v>
       </c>
-      <c r="P14" s="384">
+      <c r="P14" s="388">
         <f t="shared" si="2"/>
         <v>258666.09</v>
       </c>
-      <c r="Q14" s="384"/>
+      <c r="Q14" s="388"/>
       <c r="R14" s="226">
         <f t="shared" si="3"/>
         <v>266511.09000000003</v>
@@ -6938,7 +6995,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="15" spans="1:24" ht="24.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:24" ht="24.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="158"/>
       <c r="B15" s="278">
         <f t="shared" si="9"/>
@@ -6990,11 +7047,11 @@
       <c r="O15" s="185">
         <v>0</v>
       </c>
-      <c r="P15" s="384">
+      <c r="P15" s="388">
         <f t="shared" si="2"/>
         <v>767816.1</v>
       </c>
-      <c r="Q15" s="384"/>
+      <c r="Q15" s="388"/>
       <c r="R15" s="226">
         <f t="shared" si="3"/>
         <v>791104.1</v>
@@ -7011,7 +7068,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="16" spans="1:24" ht="24.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:24" ht="24.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="16"/>
       <c r="B16" s="278">
         <f t="shared" si="9"/>
@@ -7062,11 +7119,11 @@
       <c r="O16" s="185">
         <v>0</v>
       </c>
-      <c r="P16" s="384">
+      <c r="P16" s="388">
         <f t="shared" si="2"/>
         <v>745213.11</v>
       </c>
-      <c r="Q16" s="384"/>
+      <c r="Q16" s="388"/>
       <c r="R16" s="226">
         <f t="shared" si="3"/>
         <v>767815.11</v>
@@ -7083,7 +7140,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="17" spans="1:22" ht="24.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:22" ht="24.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="16"/>
       <c r="B17" s="278">
         <f t="shared" si="9"/>
@@ -7134,11 +7191,11 @@
       <c r="O17" s="185">
         <v>0</v>
       </c>
-      <c r="P17" s="384">
+      <c r="P17" s="388">
         <f t="shared" si="2"/>
         <v>5164685.12</v>
       </c>
-      <c r="Q17" s="384"/>
+      <c r="Q17" s="388"/>
       <c r="R17" s="226">
         <f t="shared" si="3"/>
         <v>5321330.12</v>
@@ -7155,7 +7212,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="18" spans="1:22" ht="24.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:22" ht="24.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="218"/>
       <c r="B18" s="278">
         <f t="shared" si="9"/>
@@ -7207,11 +7264,11 @@
       <c r="O18" s="185">
         <v>0</v>
       </c>
-      <c r="P18" s="384">
+      <c r="P18" s="388">
         <f t="shared" si="2"/>
         <v>759748.13</v>
       </c>
-      <c r="Q18" s="384"/>
+      <c r="Q18" s="388"/>
       <c r="R18" s="226">
         <f t="shared" si="3"/>
         <v>782791.13</v>
@@ -7225,7 +7282,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="19" spans="1:22" ht="24.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:22" ht="24.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="16"/>
       <c r="B19" s="278">
         <f t="shared" si="9"/>
@@ -7277,11 +7334,11 @@
       <c r="O19" s="185">
         <v>0</v>
       </c>
-      <c r="P19" s="384">
+      <c r="P19" s="388">
         <f t="shared" si="2"/>
         <v>767816.14</v>
       </c>
-      <c r="Q19" s="384"/>
+      <c r="Q19" s="388"/>
       <c r="R19" s="226">
         <f t="shared" si="3"/>
         <v>791104.14</v>
@@ -7298,7 +7355,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="20" spans="1:22" ht="24.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:22" ht="24.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="16"/>
       <c r="B20" s="278">
         <f t="shared" si="9"/>
@@ -7350,11 +7407,11 @@
       <c r="O20" s="185">
         <v>0</v>
       </c>
-      <c r="P20" s="384">
+      <c r="P20" s="388">
         <f t="shared" si="2"/>
         <v>743613.15</v>
       </c>
-      <c r="Q20" s="384"/>
+      <c r="Q20" s="388"/>
       <c r="R20" s="226">
         <f t="shared" si="3"/>
         <v>766167.15</v>
@@ -7371,7 +7428,7 @@
         <v>290</v>
       </c>
     </row>
-    <row r="21" spans="1:22" ht="24.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:22" ht="24.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="16"/>
       <c r="B21" s="278">
         <f t="shared" si="9"/>
@@ -7423,11 +7480,11 @@
       <c r="O21" s="185">
         <v>0</v>
       </c>
-      <c r="P21" s="384">
+      <c r="P21" s="388">
         <f t="shared" si="2"/>
         <v>759748.16</v>
       </c>
-      <c r="Q21" s="384"/>
+      <c r="Q21" s="388"/>
       <c r="R21" s="226">
         <f t="shared" si="3"/>
         <v>782791.16</v>
@@ -7441,7 +7498,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="22" spans="1:22" ht="24.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:22" ht="24.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="246"/>
       <c r="B22" s="278">
         <f t="shared" si="9"/>
@@ -7493,11 +7550,11 @@
       <c r="O22" s="185">
         <v>0</v>
       </c>
-      <c r="P22" s="384">
+      <c r="P22" s="388">
         <f t="shared" si="2"/>
         <v>-130051.83</v>
       </c>
-      <c r="Q22" s="384"/>
+      <c r="Q22" s="388"/>
       <c r="R22" s="226">
         <f t="shared" si="3"/>
         <v>-133995.82999999999</v>
@@ -7514,7 +7571,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="23" spans="1:22" ht="24.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:22" ht="24.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="16"/>
       <c r="B23" s="278">
         <f t="shared" si="9"/>
@@ -7566,11 +7623,11 @@
       <c r="O23" s="185">
         <v>0</v>
       </c>
-      <c r="P23" s="384">
+      <c r="P23" s="388">
         <f t="shared" si="2"/>
         <v>759748.18</v>
       </c>
-      <c r="Q23" s="384"/>
+      <c r="Q23" s="388"/>
       <c r="R23" s="226">
         <f t="shared" si="3"/>
         <v>782791.18</v>
@@ -7587,7 +7644,7 @@
         <v>296</v>
       </c>
     </row>
-    <row r="24" spans="1:22" ht="24.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:22" ht="24.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="16"/>
       <c r="B24" s="278">
         <f t="shared" si="9"/>
@@ -7638,11 +7695,11 @@
       <c r="O24" s="185">
         <v>0</v>
       </c>
-      <c r="P24" s="384">
+      <c r="P24" s="388">
         <f t="shared" si="2"/>
         <v>745213.19</v>
       </c>
-      <c r="Q24" s="384"/>
+      <c r="Q24" s="388"/>
       <c r="R24" s="226">
         <f t="shared" si="3"/>
         <v>767816.19</v>
@@ -7656,7 +7713,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="25" spans="1:22" ht="24.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:22" ht="24.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="16"/>
       <c r="B25" s="278">
         <f t="shared" si="9"/>
@@ -7708,11 +7765,11 @@
       <c r="O25" s="185">
         <v>0</v>
       </c>
-      <c r="P25" s="384">
+      <c r="P25" s="388">
         <f t="shared" si="2"/>
         <v>767816.2</v>
       </c>
-      <c r="Q25" s="384"/>
+      <c r="Q25" s="388"/>
       <c r="R25" s="226">
         <f t="shared" si="3"/>
         <v>791104.2</v>
@@ -7726,7 +7783,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="26" spans="1:22" ht="24.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:22" ht="24.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="16"/>
       <c r="B26" s="278">
         <f t="shared" si="9"/>
@@ -7777,11 +7834,11 @@
       <c r="O26" s="185">
         <v>0</v>
       </c>
-      <c r="P26" s="384">
+      <c r="P26" s="388">
         <f t="shared" si="2"/>
         <v>744527.21</v>
       </c>
-      <c r="Q26" s="384"/>
+      <c r="Q26" s="388"/>
       <c r="R26" s="226">
         <f t="shared" si="3"/>
         <v>767109.21</v>
@@ -7801,7 +7858,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="27" spans="1:22" ht="24.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:22" ht="24.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="16"/>
       <c r="B27" s="278">
         <f t="shared" si="9"/>
@@ -7852,11 +7909,11 @@
       <c r="O27" s="185">
         <v>0</v>
       </c>
-      <c r="P27" s="384">
+      <c r="P27" s="388">
         <f t="shared" si="2"/>
         <v>745213.22</v>
       </c>
-      <c r="Q27" s="384"/>
+      <c r="Q27" s="388"/>
       <c r="R27" s="226">
         <f t="shared" si="3"/>
         <v>767816.22</v>
@@ -7873,7 +7930,7 @@
         <v>286</v>
       </c>
     </row>
-    <row r="28" spans="1:22" ht="24.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:22" ht="24.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="160"/>
       <c r="B28" s="278">
         <f t="shared" si="9"/>
@@ -7924,11 +7981,11 @@
       <c r="O28" s="185">
         <v>0</v>
       </c>
-      <c r="P28" s="384">
+      <c r="P28" s="388">
         <f t="shared" si="2"/>
         <v>743432.23</v>
       </c>
-      <c r="Q28" s="384"/>
+      <c r="Q28" s="388"/>
       <c r="R28" s="226">
         <f t="shared" si="3"/>
         <v>765981.23</v>
@@ -7945,7 +8002,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="29" spans="1:22" ht="24.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:22" ht="24.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="16"/>
       <c r="B29" s="278">
         <f t="shared" si="9"/>
@@ -7996,11 +8053,11 @@
       <c r="O29" s="185">
         <v>0</v>
       </c>
-      <c r="P29" s="384">
+      <c r="P29" s="388">
         <f t="shared" si="2"/>
         <v>745213.24</v>
       </c>
-      <c r="Q29" s="384"/>
+      <c r="Q29" s="388"/>
       <c r="R29" s="226">
         <f t="shared" si="3"/>
         <v>767816.24</v>
@@ -8017,7 +8074,7 @@
         <v>315</v>
       </c>
     </row>
-    <row r="30" spans="1:22" ht="24.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:22" ht="24.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="16"/>
       <c r="B30" s="278">
         <f t="shared" si="9"/>
@@ -8069,11 +8126,11 @@
       <c r="O30" s="185">
         <v>0</v>
       </c>
-      <c r="P30" s="384">
+      <c r="P30" s="388">
         <f t="shared" si="2"/>
         <v>775884.25</v>
       </c>
-      <c r="Q30" s="384"/>
+      <c r="Q30" s="388"/>
       <c r="R30" s="226">
         <f t="shared" si="3"/>
         <v>799417.25</v>
@@ -8090,7 +8147,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="31" spans="1:22" ht="24.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:22" ht="24.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="159"/>
       <c r="B31" s="278">
         <f t="shared" si="9"/>
@@ -8141,11 +8198,11 @@
       <c r="O31" s="185">
         <v>0</v>
       </c>
-      <c r="P31" s="384">
+      <c r="P31" s="388">
         <f t="shared" si="2"/>
         <v>752351.26</v>
       </c>
-      <c r="Q31" s="384"/>
+      <c r="Q31" s="388"/>
       <c r="R31" s="226">
         <f t="shared" si="3"/>
         <v>775170.26</v>
@@ -8162,7 +8219,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="32" spans="1:22" ht="24.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:22" ht="24.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="16"/>
       <c r="B32" s="278">
         <f t="shared" si="9"/>
@@ -8214,11 +8271,11 @@
       <c r="O32" s="185">
         <v>0</v>
       </c>
-      <c r="P32" s="384">
+      <c r="P32" s="388">
         <f t="shared" si="2"/>
         <v>775884.27</v>
       </c>
-      <c r="Q32" s="384"/>
+      <c r="Q32" s="388"/>
       <c r="R32" s="226">
         <f t="shared" si="3"/>
         <v>799417.27</v>
@@ -8232,7 +8289,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="33" spans="1:21" ht="24.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:21" ht="24.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="220"/>
       <c r="B33" s="278">
         <f t="shared" si="9"/>
@@ -8283,11 +8340,11 @@
       <c r="O33" s="185">
         <v>0</v>
       </c>
-      <c r="P33" s="384">
+      <c r="P33" s="388">
         <f t="shared" si="2"/>
         <v>734245.28</v>
       </c>
-      <c r="Q33" s="384"/>
+      <c r="Q33" s="388"/>
       <c r="R33" s="226">
         <f t="shared" si="3"/>
         <v>756515.28</v>
@@ -8304,7 +8361,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="34" spans="1:21" ht="24.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:21" ht="24.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="16"/>
       <c r="B34" s="278">
         <f t="shared" si="9"/>
@@ -8355,11 +8412,11 @@
       <c r="O34" s="185">
         <v>0</v>
       </c>
-      <c r="P34" s="384">
+      <c r="P34" s="388">
         <f t="shared" si="2"/>
         <v>753065.29</v>
       </c>
-      <c r="Q34" s="384"/>
+      <c r="Q34" s="388"/>
       <c r="R34" s="226">
         <f t="shared" si="3"/>
         <v>775906.29</v>
@@ -8376,7 +8433,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="35" spans="1:21" ht="24.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:21" ht="24.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="16"/>
       <c r="B35" s="278">
         <f t="shared" si="9"/>
@@ -8427,11 +8484,11 @@
       <c r="O35" s="185">
         <v>0</v>
       </c>
-      <c r="P35" s="384">
+      <c r="P35" s="388">
         <f t="shared" si="2"/>
         <v>729553.3</v>
       </c>
-      <c r="Q35" s="384"/>
+      <c r="Q35" s="388"/>
       <c r="R35" s="226">
         <f t="shared" si="3"/>
         <v>751681.3</v>
@@ -8448,7 +8505,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="36" spans="1:21" ht="24.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:21" ht="24.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="217"/>
       <c r="B36" s="278">
         <f t="shared" si="9"/>
@@ -8497,11 +8554,11 @@
       <c r="O36" s="185">
         <v>0</v>
       </c>
-      <c r="P36" s="384">
+      <c r="P36" s="388">
         <f t="shared" si="2"/>
         <v>1602327.31</v>
       </c>
-      <c r="Q36" s="384"/>
+      <c r="Q36" s="388"/>
       <c r="R36" s="226">
         <f t="shared" si="3"/>
         <v>1650926.31</v>
@@ -8518,7 +8575,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="37" spans="1:21" ht="24.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:21" ht="24.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="159"/>
       <c r="B37" s="338">
         <f t="shared" si="9"/>
@@ -8570,11 +8627,11 @@
       <c r="O37" s="185">
         <v>0</v>
       </c>
-      <c r="P37" s="384">
+      <c r="P37" s="388">
         <f t="shared" si="2"/>
         <v>615483.31999999995</v>
       </c>
-      <c r="Q37" s="384"/>
+      <c r="Q37" s="388"/>
       <c r="R37" s="226">
         <f t="shared" si="3"/>
         <v>634151.31999999995</v>
@@ -8588,7 +8645,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="38" spans="1:21" ht="24.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:21" ht="24.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="16"/>
       <c r="B38" s="278">
         <v>33</v>
@@ -8639,11 +8696,11 @@
       <c r="O38" s="185">
         <v>0</v>
       </c>
-      <c r="P38" s="384">
+      <c r="P38" s="388">
         <f t="shared" ref="P38:P69" si="13">ROUND(SUM(G38:O38),0) + S38</f>
         <v>751681.33</v>
       </c>
-      <c r="Q38" s="384"/>
+      <c r="Q38" s="388"/>
       <c r="R38" s="226">
         <f t="shared" ref="R38:R69" si="14">ROUND(P38+P38*3.033%,0) + S38</f>
         <v>774480.33</v>
@@ -8657,7 +8714,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="39" spans="1:21" ht="24.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:21" ht="24.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="218"/>
       <c r="B39" s="278">
         <v>34</v>
@@ -8708,11 +8765,11 @@
         <f>2239*100</f>
         <v>223900</v>
       </c>
-      <c r="P39" s="384">
+      <c r="P39" s="388">
         <f t="shared" si="13"/>
         <v>1645944.34</v>
       </c>
-      <c r="Q39" s="384"/>
+      <c r="Q39" s="388"/>
       <c r="R39" s="226">
         <f t="shared" si="14"/>
         <v>1695866.34</v>
@@ -8729,7 +8786,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="40" spans="1:21" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:21" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="16">
         <v>1</v>
       </c>
@@ -8782,11 +8839,11 @@
       <c r="O40" s="185">
         <v>0</v>
       </c>
-      <c r="P40" s="384">
+      <c r="P40" s="388">
         <f t="shared" si="13"/>
         <v>759748.35</v>
       </c>
-      <c r="Q40" s="384"/>
+      <c r="Q40" s="388"/>
       <c r="R40" s="226">
         <f t="shared" si="14"/>
         <v>782792.35</v>
@@ -8803,7 +8860,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="41" spans="1:21" ht="24.9" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:21" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="217">
         <v>2</v>
       </c>
@@ -8855,11 +8912,11 @@
       <c r="O41" s="185">
         <v>0</v>
       </c>
-      <c r="P41" s="384">
+      <c r="P41" s="388">
         <f t="shared" si="13"/>
         <v>720831.36</v>
       </c>
-      <c r="Q41" s="384"/>
+      <c r="Q41" s="388"/>
       <c r="R41" s="226">
         <f t="shared" si="14"/>
         <v>742694.36</v>
@@ -8874,7 +8931,7 @@
       </c>
       <c r="U41" s="13"/>
     </row>
-    <row r="42" spans="1:21" ht="24.9" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:21" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="16">
         <v>3</v>
       </c>
@@ -8926,11 +8983,11 @@
       <c r="O42" s="185">
         <v>0</v>
       </c>
-      <c r="P42" s="384">
+      <c r="P42" s="388">
         <f t="shared" si="13"/>
         <v>1478803.37</v>
       </c>
-      <c r="Q42" s="384"/>
+      <c r="Q42" s="388"/>
       <c r="R42" s="226">
         <f t="shared" si="14"/>
         <v>1523655.37</v>
@@ -8945,7 +9002,7 @@
       </c>
       <c r="U42" s="13"/>
     </row>
-    <row r="43" spans="1:21" ht="24.9" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:21" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="162">
         <v>4</v>
       </c>
@@ -8997,11 +9054,11 @@
       <c r="O43" s="185">
         <v>0</v>
       </c>
-      <c r="P43" s="384">
+      <c r="P43" s="388">
         <f t="shared" si="13"/>
         <v>774319.38</v>
       </c>
-      <c r="Q43" s="384"/>
+      <c r="Q43" s="388"/>
       <c r="R43" s="226">
         <f t="shared" si="14"/>
         <v>797804.38</v>
@@ -9018,7 +9075,7 @@
         <v>237</v>
       </c>
     </row>
-    <row r="44" spans="1:21" ht="24.9" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:21" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="16">
         <v>5</v>
       </c>
@@ -9070,11 +9127,11 @@
       <c r="O44" s="185">
         <v>0</v>
       </c>
-      <c r="P44" s="384">
+      <c r="P44" s="388">
         <f t="shared" si="13"/>
         <v>751362.39</v>
       </c>
-      <c r="Q44" s="384"/>
+      <c r="Q44" s="388"/>
       <c r="R44" s="226">
         <f t="shared" si="14"/>
         <v>774151.39</v>
@@ -9091,7 +9148,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="45" spans="1:21" ht="24.9" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:21" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="16">
         <v>6</v>
       </c>
@@ -9143,11 +9200,11 @@
       <c r="O45" s="185">
         <v>0</v>
       </c>
-      <c r="P45" s="384">
+      <c r="P45" s="388">
         <f t="shared" si="13"/>
         <v>751681.4</v>
       </c>
-      <c r="Q45" s="384"/>
+      <c r="Q45" s="388"/>
       <c r="R45" s="226">
         <f t="shared" si="14"/>
         <v>774480.4</v>
@@ -9161,7 +9218,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="46" spans="1:21" ht="24.9" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:21" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="16">
         <v>7</v>
       </c>
@@ -9213,11 +9270,11 @@
       <c r="O46" s="185">
         <v>0</v>
       </c>
-      <c r="P46" s="384">
+      <c r="P46" s="388">
         <f t="shared" si="13"/>
         <v>729553.41</v>
       </c>
-      <c r="Q46" s="384"/>
+      <c r="Q46" s="388"/>
       <c r="R46" s="226">
         <f t="shared" si="14"/>
         <v>751681.41</v>
@@ -9234,7 +9291,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="47" spans="1:21" ht="24.9" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:21" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="162">
         <v>8</v>
       </c>
@@ -9287,11 +9344,11 @@
       <c r="O47" s="185">
         <v>0</v>
       </c>
-      <c r="P47" s="384">
+      <c r="P47" s="388">
         <f t="shared" si="13"/>
         <v>751681.42</v>
       </c>
-      <c r="Q47" s="384"/>
+      <c r="Q47" s="388"/>
       <c r="R47" s="226">
         <f t="shared" si="14"/>
         <v>774480.42</v>
@@ -9308,7 +9365,7 @@
         <v>279</v>
       </c>
     </row>
-    <row r="48" spans="1:21" ht="24.9" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:21" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="16">
         <v>1</v>
       </c>
@@ -9361,11 +9418,11 @@
       <c r="O48" s="185">
         <v>0</v>
       </c>
-      <c r="P48" s="384">
+      <c r="P48" s="388">
         <f t="shared" si="13"/>
         <v>679072.43</v>
       </c>
-      <c r="Q48" s="384"/>
+      <c r="Q48" s="388"/>
       <c r="R48" s="226">
         <f t="shared" si="14"/>
         <v>699669.43</v>
@@ -9379,7 +9436,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="49" spans="1:21" ht="24.9" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:21" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="16">
         <v>1</v>
       </c>
@@ -9431,11 +9488,11 @@
       <c r="O49" s="185">
         <v>0</v>
       </c>
-      <c r="P49" s="384">
+      <c r="P49" s="388">
         <f t="shared" si="13"/>
         <v>173549.44</v>
       </c>
-      <c r="Q49" s="384"/>
+      <c r="Q49" s="388"/>
       <c r="R49" s="226">
         <f t="shared" si="14"/>
         <v>178813.44</v>
@@ -9452,7 +9509,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="50" spans="1:21" ht="24.9" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:21" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="16">
         <v>2</v>
       </c>
@@ -9505,11 +9562,11 @@
       <c r="O50" s="185">
         <v>0</v>
       </c>
-      <c r="P50" s="384">
+      <c r="P50" s="388">
         <f t="shared" si="13"/>
         <v>1644388.45</v>
       </c>
-      <c r="Q50" s="384"/>
+      <c r="Q50" s="388"/>
       <c r="R50" s="226">
         <f t="shared" si="14"/>
         <v>1694263.45</v>
@@ -9523,7 +9580,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="51" spans="1:21" ht="24.9" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:21" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="16">
         <v>2</v>
       </c>
@@ -9575,11 +9632,11 @@
       <c r="O51" s="185">
         <v>0</v>
       </c>
-      <c r="P51" s="384">
+      <c r="P51" s="388">
         <f t="shared" si="13"/>
         <v>1451354.46</v>
       </c>
-      <c r="Q51" s="384"/>
+      <c r="Q51" s="388"/>
       <c r="R51" s="226">
         <f t="shared" si="14"/>
         <v>1495374.46</v>
@@ -9596,7 +9653,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="52" spans="1:21" ht="24.9" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:21" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="16">
         <v>3</v>
       </c>
@@ -9646,11 +9703,11 @@
       <c r="O52" s="185">
         <v>0</v>
       </c>
-      <c r="P52" s="384">
+      <c r="P52" s="388">
         <f t="shared" si="13"/>
         <v>2325372.4700000002</v>
       </c>
-      <c r="Q52" s="384"/>
+      <c r="Q52" s="388"/>
       <c r="R52" s="226">
         <f t="shared" si="14"/>
         <v>2395901.4700000002</v>
@@ -9667,7 +9724,7 @@
         <v>304</v>
       </c>
     </row>
-    <row r="53" spans="1:21" ht="24.9" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:21" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="16">
         <v>3</v>
       </c>
@@ -9721,11 +9778,11 @@
       <c r="O53" s="185">
         <v>0</v>
       </c>
-      <c r="P53" s="384">
+      <c r="P53" s="388">
         <f t="shared" si="13"/>
         <v>1187332.48</v>
       </c>
-      <c r="Q53" s="384"/>
+      <c r="Q53" s="388"/>
       <c r="R53" s="226">
         <f t="shared" si="14"/>
         <v>1223344.48</v>
@@ -9740,7 +9797,7 @@
       </c>
       <c r="U53" s="12"/>
     </row>
-    <row r="54" spans="1:21" ht="24.9" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:21" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="16">
         <v>4</v>
       </c>
@@ -9793,11 +9850,11 @@
       <c r="O54" s="185">
         <v>0</v>
       </c>
-      <c r="P54" s="384">
+      <c r="P54" s="388">
         <f t="shared" si="13"/>
         <v>751681.49</v>
       </c>
-      <c r="Q54" s="384"/>
+      <c r="Q54" s="388"/>
       <c r="R54" s="226">
         <f t="shared" si="14"/>
         <v>774480.49</v>
@@ -9814,7 +9871,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="55" spans="1:21" ht="24.9" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:21" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="16">
         <v>4</v>
       </c>
@@ -9866,11 +9923,11 @@
       <c r="O55" s="185">
         <v>0</v>
       </c>
-      <c r="P55" s="384">
+      <c r="P55" s="388">
         <f t="shared" si="13"/>
         <v>729553.5</v>
       </c>
-      <c r="Q55" s="384"/>
+      <c r="Q55" s="388"/>
       <c r="R55" s="226">
         <f t="shared" si="14"/>
         <v>751681.5</v>
@@ -9887,7 +9944,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="56" spans="1:21" ht="24.9" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:21" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="16">
         <v>5</v>
       </c>
@@ -9939,11 +9996,11 @@
       <c r="O56" s="185">
         <v>0</v>
       </c>
-      <c r="P56" s="384">
+      <c r="P56" s="388">
         <f t="shared" si="13"/>
         <v>751681.51</v>
       </c>
-      <c r="Q56" s="384"/>
+      <c r="Q56" s="388"/>
       <c r="R56" s="226">
         <f t="shared" si="14"/>
         <v>774480.51</v>
@@ -9960,7 +10017,7 @@
         <v>249</v>
       </c>
     </row>
-    <row r="57" spans="1:21" ht="24.9" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:21" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="16">
         <v>5</v>
       </c>
@@ -10013,11 +10070,11 @@
       <c r="O57" s="185">
         <v>0</v>
       </c>
-      <c r="P57" s="384">
+      <c r="P57" s="388">
         <f t="shared" si="13"/>
         <v>759748.52</v>
       </c>
-      <c r="Q57" s="384"/>
+      <c r="Q57" s="388"/>
       <c r="R57" s="226">
         <f t="shared" si="14"/>
         <v>782792.52</v>
@@ -10034,7 +10091,7 @@
         <v>324</v>
       </c>
     </row>
-    <row r="58" spans="1:21" ht="24.9" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:21" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="159">
         <v>6</v>
       </c>
@@ -10084,11 +10141,11 @@
       <c r="O58" s="185">
         <v>0</v>
       </c>
-      <c r="P58" s="384">
+      <c r="P58" s="388">
         <f t="shared" si="13"/>
         <v>3874923.53</v>
       </c>
-      <c r="Q58" s="384"/>
+      <c r="Q58" s="388"/>
       <c r="R58" s="226">
         <f t="shared" si="14"/>
         <v>3992450.53</v>
@@ -10102,7 +10159,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="59" spans="1:21" ht="24.9" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:21" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" s="16">
         <v>6</v>
       </c>
@@ -10154,11 +10211,11 @@
       <c r="O59" s="185">
         <v>0</v>
       </c>
-      <c r="P59" s="384">
+      <c r="P59" s="388">
         <f t="shared" si="13"/>
         <v>728882.54</v>
       </c>
-      <c r="Q59" s="384"/>
+      <c r="Q59" s="388"/>
       <c r="R59" s="226">
         <f t="shared" si="14"/>
         <v>750990.54</v>
@@ -10175,7 +10232,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="60" spans="1:21" ht="24.9" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:21" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" s="16">
         <v>7</v>
       </c>
@@ -10227,11 +10284,11 @@
       <c r="O60" s="185">
         <v>0</v>
       </c>
-      <c r="P60" s="384">
+      <c r="P60" s="388">
         <f t="shared" si="13"/>
         <v>729553.55</v>
       </c>
-      <c r="Q60" s="384"/>
+      <c r="Q60" s="388"/>
       <c r="R60" s="226">
         <f t="shared" si="14"/>
         <v>751681.55</v>
@@ -10248,7 +10305,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="61" spans="1:21" ht="24.9" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:21" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" s="16">
         <v>7</v>
       </c>
@@ -10301,11 +10358,11 @@
       <c r="O61" s="185">
         <v>0</v>
       </c>
-      <c r="P61" s="384">
+      <c r="P61" s="388">
         <f t="shared" si="13"/>
         <v>751681.56</v>
       </c>
-      <c r="Q61" s="384"/>
+      <c r="Q61" s="388"/>
       <c r="R61" s="226">
         <f t="shared" si="14"/>
         <v>774480.56</v>
@@ -10322,7 +10379,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="62" spans="1:21" ht="24.9" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:21" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="16">
         <v>8</v>
       </c>
@@ -10375,11 +10432,11 @@
       <c r="O62" s="185">
         <v>0</v>
       </c>
-      <c r="P62" s="384">
+      <c r="P62" s="388">
         <f t="shared" si="13"/>
         <v>751681.57</v>
       </c>
-      <c r="Q62" s="384"/>
+      <c r="Q62" s="388"/>
       <c r="R62" s="226">
         <f t="shared" si="14"/>
         <v>774480.57</v>
@@ -10393,7 +10450,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="63" spans="1:21" ht="24.9" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:21" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63" s="16">
         <v>8</v>
       </c>
@@ -10445,11 +10502,11 @@
       <c r="O63" s="185">
         <v>0</v>
       </c>
-      <c r="P63" s="384">
+      <c r="P63" s="388">
         <f t="shared" si="13"/>
         <v>729553.58</v>
       </c>
-      <c r="Q63" s="384"/>
+      <c r="Q63" s="388"/>
       <c r="R63" s="226">
         <f t="shared" si="14"/>
         <v>751681.58</v>
@@ -10463,7 +10520,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="64" spans="1:21" ht="24.9" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:21" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64" s="162">
         <v>9</v>
       </c>
@@ -10515,11 +10572,11 @@
       <c r="O64" s="185">
         <v>0</v>
       </c>
-      <c r="P64" s="384">
+      <c r="P64" s="388">
         <f t="shared" si="13"/>
         <v>718821.59</v>
       </c>
-      <c r="Q64" s="384"/>
+      <c r="Q64" s="388"/>
       <c r="R64" s="226">
         <f t="shared" si="14"/>
         <v>740623.59</v>
@@ -10536,7 +10593,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="65" spans="1:21" ht="24.9" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:21" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65" s="248">
         <v>9</v>
       </c>
@@ -10588,11 +10645,11 @@
       <c r="O65" s="185">
         <v>0</v>
       </c>
-      <c r="P65" s="384">
+      <c r="P65" s="388">
         <f t="shared" si="13"/>
         <v>751551.6</v>
       </c>
-      <c r="Q65" s="384"/>
+      <c r="Q65" s="388"/>
       <c r="R65" s="226">
         <f t="shared" si="14"/>
         <v>774346.6</v>
@@ -10609,7 +10666,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="66" spans="1:21" ht="24.9" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:21" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66" s="162">
         <v>10</v>
       </c>
@@ -10661,11 +10718,11 @@
       <c r="O66" s="185">
         <v>0</v>
       </c>
-      <c r="P66" s="384">
+      <c r="P66" s="388">
         <f t="shared" si="13"/>
         <v>751043.61</v>
       </c>
-      <c r="Q66" s="384"/>
+      <c r="Q66" s="388"/>
       <c r="R66" s="226">
         <f t="shared" si="14"/>
         <v>773823.61</v>
@@ -10682,7 +10739,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="67" spans="1:21" ht="24.9" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:21" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A67" s="16">
         <v>10</v>
       </c>
@@ -10735,11 +10792,11 @@
       <c r="O67" s="185">
         <v>0</v>
       </c>
-      <c r="P67" s="384">
+      <c r="P67" s="388">
         <f t="shared" si="13"/>
         <v>785565.62</v>
       </c>
-      <c r="Q67" s="384"/>
+      <c r="Q67" s="388"/>
       <c r="R67" s="226">
         <f t="shared" si="14"/>
         <v>809392.62</v>
@@ -10753,7 +10810,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="68" spans="1:21" ht="24.9" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:21" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A68" s="16">
         <v>11</v>
       </c>
@@ -10806,11 +10863,11 @@
       <c r="O68" s="185">
         <v>0</v>
       </c>
-      <c r="P68" s="384">
+      <c r="P68" s="388">
         <f t="shared" si="13"/>
         <v>751681.63</v>
       </c>
-      <c r="Q68" s="384"/>
+      <c r="Q68" s="388"/>
       <c r="R68" s="226">
         <f t="shared" si="14"/>
         <v>774480.63</v>
@@ -10827,7 +10884,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="69" spans="1:21" ht="24.9" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:21" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A69" s="16">
         <v>11</v>
       </c>
@@ -10880,11 +10937,11 @@
       <c r="O69" s="185">
         <v>0</v>
       </c>
-      <c r="P69" s="384">
+      <c r="P69" s="388">
         <f t="shared" si="13"/>
         <v>751681.64</v>
       </c>
-      <c r="Q69" s="384"/>
+      <c r="Q69" s="388"/>
       <c r="R69" s="226">
         <f t="shared" si="14"/>
         <v>774480.64</v>
@@ -10901,7 +10958,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="70" spans="1:21" ht="24.9" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:21" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70" s="16">
         <v>12</v>
       </c>
@@ -10954,11 +11011,11 @@
       <c r="O70" s="185">
         <v>0</v>
       </c>
-      <c r="P70" s="384">
+      <c r="P70" s="388">
         <f t="shared" ref="P70:P101" si="21">ROUND(SUM(G70:O70),0) + S70</f>
         <v>751681.65</v>
       </c>
-      <c r="Q70" s="384"/>
+      <c r="Q70" s="388"/>
       <c r="R70" s="226">
         <f t="shared" ref="R70:R101" si="22">ROUND(P70+P70*3.033%,0) + S70</f>
         <v>774480.65</v>
@@ -10972,7 +11029,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="71" spans="1:21" ht="24.9" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:21" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A71" s="16">
         <v>12</v>
       </c>
@@ -11025,11 +11082,11 @@
       <c r="O71" s="185">
         <v>0</v>
       </c>
-      <c r="P71" s="384">
+      <c r="P71" s="388">
         <f t="shared" si="21"/>
         <v>751681.66</v>
       </c>
-      <c r="Q71" s="384"/>
+      <c r="Q71" s="388"/>
       <c r="R71" s="226">
         <f t="shared" si="22"/>
         <v>774480.66</v>
@@ -11046,7 +11103,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="72" spans="1:21" ht="24.9" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:21" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A72" s="217">
         <v>1</v>
       </c>
@@ -11098,11 +11155,11 @@
       <c r="O72" s="185">
         <v>0</v>
       </c>
-      <c r="P72" s="384">
+      <c r="P72" s="388">
         <f t="shared" si="21"/>
         <v>752172.67</v>
       </c>
-      <c r="Q72" s="384"/>
+      <c r="Q72" s="388"/>
       <c r="R72" s="226">
         <f t="shared" si="22"/>
         <v>774986.67</v>
@@ -11119,7 +11176,7 @@
         <v>267</v>
       </c>
     </row>
-    <row r="73" spans="1:21" ht="24.9" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:21" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A73" s="162"/>
       <c r="B73" s="278">
         <f>B72+1</f>
@@ -11169,11 +11226,11 @@
       <c r="O73" s="185">
         <v>0</v>
       </c>
-      <c r="P73" s="384">
+      <c r="P73" s="388">
         <f t="shared" si="21"/>
         <v>3673073.68</v>
       </c>
-      <c r="Q73" s="384"/>
+      <c r="Q73" s="388"/>
       <c r="R73" s="226">
         <f t="shared" si="22"/>
         <v>3784478.68</v>
@@ -11187,7 +11244,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="74" spans="1:21" ht="24.9" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:21" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A74" s="162"/>
       <c r="B74" s="278">
         <f t="shared" ref="B74:B137" si="28">B73+1</f>
@@ -11238,11 +11295,11 @@
       <c r="O74" s="185">
         <v>0</v>
       </c>
-      <c r="P74" s="384">
+      <c r="P74" s="388">
         <f t="shared" si="21"/>
         <v>658475.68999999994</v>
       </c>
-      <c r="Q74" s="384"/>
+      <c r="Q74" s="388"/>
       <c r="R74" s="226">
         <f t="shared" si="22"/>
         <v>678447.69</v>
@@ -11259,13 +11316,13 @@
         <v>210</v>
       </c>
     </row>
-    <row r="75" spans="1:21" ht="24.9" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:21" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A75" s="162"/>
-      <c r="B75" s="278">
+      <c r="B75" s="347">
         <f t="shared" si="28"/>
         <v>70</v>
       </c>
-      <c r="C75" s="278" t="s">
+      <c r="C75" s="347" t="s">
         <v>88</v>
       </c>
       <c r="D75" s="281">
@@ -11310,11 +11367,11 @@
       <c r="O75" s="185">
         <v>0</v>
       </c>
-      <c r="P75" s="384">
+      <c r="P75" s="388">
         <f t="shared" si="21"/>
         <v>1985816.7</v>
       </c>
-      <c r="Q75" s="384"/>
+      <c r="Q75" s="388"/>
       <c r="R75" s="226">
         <f t="shared" si="22"/>
         <v>2046047.7</v>
@@ -11331,7 +11388,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="76" spans="1:21" ht="24.9" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:21" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A76" s="162"/>
       <c r="B76" s="278">
         <f t="shared" si="28"/>
@@ -11383,11 +11440,11 @@
       <c r="O76" s="185">
         <v>0</v>
       </c>
-      <c r="P76" s="384">
+      <c r="P76" s="388">
         <f t="shared" si="21"/>
         <v>735149.71</v>
       </c>
-      <c r="Q76" s="384"/>
+      <c r="Q76" s="388"/>
       <c r="R76" s="226">
         <f t="shared" si="22"/>
         <v>757447.71</v>
@@ -11404,7 +11461,7 @@
         <v>307</v>
       </c>
     </row>
-    <row r="77" spans="1:21" ht="24.9" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:21" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A77" s="242"/>
       <c r="B77" s="278">
         <f t="shared" si="28"/>
@@ -11455,11 +11512,11 @@
       <c r="O77" s="185">
         <v>0</v>
       </c>
-      <c r="P77" s="384">
+      <c r="P77" s="388">
         <f t="shared" si="21"/>
         <v>711343.72</v>
       </c>
-      <c r="Q77" s="384"/>
+      <c r="Q77" s="388"/>
       <c r="R77" s="226">
         <f t="shared" si="22"/>
         <v>732919.72</v>
@@ -11476,7 +11533,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="78" spans="1:21" ht="24.9" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:21" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A78" s="221"/>
       <c r="B78" s="309">
         <f t="shared" si="28"/>
@@ -11527,11 +11584,11 @@
       <c r="O78" s="185">
         <v>0</v>
       </c>
-      <c r="P78" s="384">
+      <c r="P78" s="388">
         <f t="shared" si="21"/>
         <v>709719.73</v>
       </c>
-      <c r="Q78" s="384"/>
+      <c r="Q78" s="388"/>
       <c r="R78" s="226">
         <f t="shared" si="22"/>
         <v>731246.73</v>
@@ -11545,7 +11602,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="79" spans="1:21" ht="24.9" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:21" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A79" s="16"/>
       <c r="B79" s="278">
         <f t="shared" si="28"/>
@@ -11597,11 +11654,11 @@
       <c r="O79" s="185">
         <v>0</v>
       </c>
-      <c r="P79" s="384">
+      <c r="P79" s="388">
         <f t="shared" si="21"/>
         <v>743613.74</v>
       </c>
-      <c r="Q79" s="384"/>
+      <c r="Q79" s="388"/>
       <c r="R79" s="226">
         <f t="shared" si="22"/>
         <v>766168.74</v>
@@ -11615,7 +11672,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="80" spans="1:21" ht="24.9" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:21" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A80" s="16"/>
       <c r="B80" s="278">
         <f t="shared" si="28"/>
@@ -11667,11 +11724,11 @@
       <c r="O80" s="185">
         <v>0</v>
       </c>
-      <c r="P80" s="384">
+      <c r="P80" s="388">
         <f t="shared" si="21"/>
         <v>719410.75</v>
       </c>
-      <c r="Q80" s="384"/>
+      <c r="Q80" s="388"/>
       <c r="R80" s="226">
         <f t="shared" si="22"/>
         <v>741230.75</v>
@@ -11688,7 +11745,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="81" spans="1:25" ht="24.9" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:25" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81" s="16"/>
       <c r="B81" s="278">
         <f t="shared" si="28"/>
@@ -11740,11 +11797,11 @@
       <c r="O81" s="185">
         <v>0</v>
       </c>
-      <c r="P81" s="384">
+      <c r="P81" s="388">
         <f t="shared" si="21"/>
         <v>751681.76</v>
       </c>
-      <c r="Q81" s="384"/>
+      <c r="Q81" s="388"/>
       <c r="R81" s="226">
         <f t="shared" si="22"/>
         <v>774480.76</v>
@@ -11758,7 +11815,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="82" spans="1:25" ht="24.9" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:25" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A82" s="265"/>
       <c r="B82" s="278">
         <f t="shared" si="28"/>
@@ -11809,11 +11866,11 @@
       <c r="O82" s="185">
         <v>0</v>
       </c>
-      <c r="P82" s="384">
+      <c r="P82" s="388">
         <f t="shared" si="21"/>
         <v>880647.77</v>
       </c>
-      <c r="Q82" s="384"/>
+      <c r="Q82" s="388"/>
       <c r="R82" s="226">
         <f t="shared" si="22"/>
         <v>907358.77</v>
@@ -11830,7 +11887,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="83" spans="1:25" ht="24.9" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:25" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A83" s="161"/>
       <c r="B83" s="300">
         <f t="shared" si="28"/>
@@ -11881,11 +11938,11 @@
       <c r="O83" s="185">
         <v>0</v>
       </c>
-      <c r="P83" s="384">
+      <c r="P83" s="388">
         <f t="shared" si="21"/>
         <v>753049.78</v>
       </c>
-      <c r="Q83" s="384"/>
+      <c r="Q83" s="388"/>
       <c r="R83" s="226">
         <f t="shared" si="22"/>
         <v>775890.78</v>
@@ -11902,7 +11959,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="84" spans="1:25" ht="24.9" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:25" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A84" s="16"/>
       <c r="B84" s="278">
         <f t="shared" si="28"/>
@@ -11954,11 +12011,11 @@
       <c r="O84" s="185">
         <v>0</v>
       </c>
-      <c r="P84" s="384">
+      <c r="P84" s="388">
         <f t="shared" si="21"/>
         <v>1527078.79</v>
       </c>
-      <c r="Q84" s="384"/>
+      <c r="Q84" s="388"/>
       <c r="R84" s="226">
         <f t="shared" si="22"/>
         <v>1573395.79</v>
@@ -11978,7 +12035,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="85" spans="1:25" ht="24.9" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:25" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A85" s="220"/>
       <c r="B85" s="278">
         <f t="shared" si="28"/>
@@ -12030,11 +12087,11 @@
       <c r="O85" s="185">
         <v>0</v>
       </c>
-      <c r="P85" s="384">
+      <c r="P85" s="388">
         <f t="shared" si="21"/>
         <v>751681.8</v>
       </c>
-      <c r="Q85" s="384"/>
+      <c r="Q85" s="388"/>
       <c r="R85" s="226">
         <f t="shared" si="22"/>
         <v>774480.8</v>
@@ -12051,7 +12108,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="86" spans="1:25" ht="24.9" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:25" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A86" s="16"/>
       <c r="B86" s="278">
         <f t="shared" si="28"/>
@@ -12103,11 +12160,11 @@
       <c r="O86" s="185">
         <v>0</v>
       </c>
-      <c r="P86" s="384">
+      <c r="P86" s="388">
         <f t="shared" si="21"/>
         <v>751681.81</v>
       </c>
-      <c r="Q86" s="384"/>
+      <c r="Q86" s="388"/>
       <c r="R86" s="226">
         <f t="shared" si="22"/>
         <v>774480.81</v>
@@ -12124,7 +12181,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="87" spans="1:25" ht="24.9" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:25" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A87" s="16"/>
       <c r="B87" s="278">
         <f t="shared" si="28"/>
@@ -12175,11 +12232,11 @@
       <c r="O87" s="185">
         <v>0</v>
       </c>
-      <c r="P87" s="384">
+      <c r="P87" s="388">
         <f t="shared" si="21"/>
         <v>708198.82</v>
       </c>
-      <c r="Q87" s="384"/>
+      <c r="Q87" s="388"/>
       <c r="R87" s="226">
         <f t="shared" si="22"/>
         <v>729678.82</v>
@@ -12197,7 +12254,7 @@
       </c>
       <c r="W87" s="16"/>
     </row>
-    <row r="88" spans="1:25" ht="24.9" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:25" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A88" s="16"/>
       <c r="B88" s="278">
         <f t="shared" si="28"/>
@@ -12248,11 +12305,11 @@
       <c r="O88" s="185">
         <v>0</v>
       </c>
-      <c r="P88" s="384">
+      <c r="P88" s="388">
         <f t="shared" si="21"/>
         <v>753043.83</v>
       </c>
-      <c r="Q88" s="384"/>
+      <c r="Q88" s="388"/>
       <c r="R88" s="226">
         <f t="shared" si="22"/>
         <v>775884.83</v>
@@ -12266,7 +12323,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="89" spans="1:25" ht="24.9" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:25" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A89" s="16"/>
       <c r="B89" s="278">
         <f t="shared" si="28"/>
@@ -12317,11 +12374,11 @@
       <c r="O89" s="185">
         <v>0</v>
       </c>
-      <c r="P89" s="384">
+      <c r="P89" s="388">
         <f t="shared" si="21"/>
         <v>753043.84</v>
       </c>
-      <c r="Q89" s="384"/>
+      <c r="Q89" s="388"/>
       <c r="R89" s="226">
         <f t="shared" si="22"/>
         <v>775884.84</v>
@@ -12335,7 +12392,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="90" spans="1:25" ht="24.9" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:25" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A90" s="16"/>
       <c r="B90" s="278">
         <f t="shared" si="28"/>
@@ -12387,11 +12444,11 @@
       <c r="O90" s="185">
         <v>0</v>
       </c>
-      <c r="P90" s="384">
+      <c r="P90" s="388">
         <f t="shared" si="21"/>
         <v>775884.85</v>
       </c>
-      <c r="Q90" s="384"/>
+      <c r="Q90" s="388"/>
       <c r="R90" s="226">
         <f t="shared" si="22"/>
         <v>799417.85</v>
@@ -12408,7 +12465,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="91" spans="1:25" ht="24.9" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:25" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A91" s="162"/>
       <c r="B91" s="347">
         <f t="shared" si="28"/>
@@ -12461,11 +12518,11 @@
       <c r="O91" s="185">
         <v>0</v>
       </c>
-      <c r="P91" s="384">
+      <c r="P91" s="388">
         <f t="shared" si="21"/>
         <v>932748.86</v>
       </c>
-      <c r="Q91" s="384"/>
+      <c r="Q91" s="388"/>
       <c r="R91" s="226">
         <f t="shared" si="22"/>
         <v>961039.86</v>
@@ -12482,7 +12539,7 @@
         <v>322</v>
       </c>
     </row>
-    <row r="92" spans="1:25" ht="24.9" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:25" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A92" s="16"/>
       <c r="B92" s="278">
         <f t="shared" si="28"/>
@@ -12534,11 +12591,11 @@
       <c r="O92" s="185">
         <v>0</v>
       </c>
-      <c r="P92" s="384">
+      <c r="P92" s="388">
         <f t="shared" si="21"/>
         <v>775884.87</v>
       </c>
-      <c r="Q92" s="384"/>
+      <c r="Q92" s="388"/>
       <c r="R92" s="226">
         <f t="shared" si="22"/>
         <v>799417.87</v>
@@ -12552,7 +12609,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="93" spans="1:25" ht="24.9" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:25" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A93" s="347"/>
       <c r="B93" s="347">
         <f t="shared" si="28"/>
@@ -12603,11 +12660,11 @@
       <c r="O93" s="185">
         <v>0</v>
       </c>
-      <c r="P93" s="384">
+      <c r="P93" s="388">
         <f t="shared" si="21"/>
         <v>771769.88</v>
       </c>
-      <c r="Q93" s="384"/>
+      <c r="Q93" s="388"/>
       <c r="R93" s="226">
         <f t="shared" si="22"/>
         <v>795178.88</v>
@@ -12621,7 +12678,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="94" spans="1:25" ht="24.9" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:25" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A94" s="16"/>
       <c r="B94" s="278">
         <f t="shared" si="28"/>
@@ -12670,11 +12727,11 @@
       <c r="O94" s="185">
         <v>0</v>
       </c>
-      <c r="P94" s="384">
+      <c r="P94" s="388">
         <f t="shared" si="21"/>
         <v>1575720.89</v>
       </c>
-      <c r="Q94" s="384"/>
+      <c r="Q94" s="388"/>
       <c r="R94" s="226">
         <f t="shared" si="22"/>
         <v>1623513.89</v>
@@ -12691,7 +12748,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="95" spans="1:25" ht="24.9" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:25" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A95" s="218"/>
       <c r="B95" s="299">
         <f t="shared" si="28"/>
@@ -12740,11 +12797,11 @@
       <c r="O95" s="185">
         <v>0</v>
       </c>
-      <c r="P95" s="384">
+      <c r="P95" s="388">
         <f t="shared" si="21"/>
         <v>2131597.9</v>
       </c>
-      <c r="Q95" s="384"/>
+      <c r="Q95" s="388"/>
       <c r="R95" s="226">
         <f t="shared" si="22"/>
         <v>2196249.9</v>
@@ -12761,7 +12818,7 @@
         <v>246</v>
       </c>
     </row>
-    <row r="96" spans="1:25" ht="24.9" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:25" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A96" s="16"/>
       <c r="B96" s="278">
         <f t="shared" si="28"/>
@@ -12813,11 +12870,11 @@
       <c r="O96" s="185">
         <v>0</v>
       </c>
-      <c r="P96" s="384">
+      <c r="P96" s="388">
         <f t="shared" si="21"/>
         <v>775884.91</v>
       </c>
-      <c r="Q96" s="384"/>
+      <c r="Q96" s="388"/>
       <c r="R96" s="226">
         <f t="shared" si="22"/>
         <v>799417.91</v>
@@ -12834,7 +12891,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="97" spans="1:22" ht="24.9" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:22" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A97" s="16"/>
       <c r="B97" s="278">
         <f t="shared" si="28"/>
@@ -12886,11 +12943,11 @@
       <c r="O97" s="185">
         <v>0</v>
       </c>
-      <c r="P97" s="384">
+      <c r="P97" s="388">
         <f t="shared" si="21"/>
         <v>775884.92</v>
       </c>
-      <c r="Q97" s="384"/>
+      <c r="Q97" s="388"/>
       <c r="R97" s="226">
         <f t="shared" si="22"/>
         <v>799418.92</v>
@@ -12907,7 +12964,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="98" spans="1:22" ht="24.9" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:22" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A98" s="16"/>
       <c r="B98" s="288">
         <f t="shared" si="28"/>
@@ -12956,11 +13013,11 @@
       <c r="O98" s="185">
         <v>0</v>
       </c>
-      <c r="P98" s="384">
+      <c r="P98" s="388">
         <f t="shared" si="21"/>
         <v>1524620.93</v>
       </c>
-      <c r="Q98" s="384"/>
+      <c r="Q98" s="388"/>
       <c r="R98" s="226">
         <f t="shared" si="22"/>
         <v>1570863.93</v>
@@ -12977,7 +13034,7 @@
         <v>305</v>
       </c>
     </row>
-    <row r="99" spans="1:22" ht="24.9" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:22" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A99" s="16"/>
       <c r="B99" s="278">
         <f t="shared" si="28"/>
@@ -13029,11 +13086,11 @@
       <c r="O99" s="185">
         <v>0</v>
       </c>
-      <c r="P99" s="384">
+      <c r="P99" s="388">
         <f t="shared" si="21"/>
         <v>775884.94</v>
       </c>
-      <c r="Q99" s="384"/>
+      <c r="Q99" s="388"/>
       <c r="R99" s="226">
         <f t="shared" si="22"/>
         <v>799418.94</v>
@@ -13050,7 +13107,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="100" spans="1:22" ht="24.9" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:22" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A100" s="16"/>
       <c r="B100" s="278">
         <f t="shared" si="28"/>
@@ -13101,11 +13158,11 @@
       <c r="O100" s="185">
         <v>0</v>
       </c>
-      <c r="P100" s="384">
+      <c r="P100" s="388">
         <f t="shared" si="21"/>
         <v>5395597.9500000002</v>
       </c>
-      <c r="Q100" s="384"/>
+      <c r="Q100" s="388"/>
       <c r="R100" s="226">
         <f t="shared" si="22"/>
         <v>5559246.9500000002</v>
@@ -13119,7 +13176,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="101" spans="1:22" ht="24.9" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:22" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A101" s="161"/>
       <c r="B101" s="278">
         <f t="shared" si="28"/>
@@ -13170,11 +13227,11 @@
       <c r="O101" s="185">
         <v>0</v>
       </c>
-      <c r="P101" s="384">
+      <c r="P101" s="388">
         <f t="shared" si="21"/>
         <v>725928.95999999996</v>
       </c>
-      <c r="Q101" s="384"/>
+      <c r="Q101" s="388"/>
       <c r="R101" s="226">
         <f t="shared" si="22"/>
         <v>747946.96</v>
@@ -13191,7 +13248,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="102" spans="1:22" ht="24.9" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:22" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A102" s="157"/>
       <c r="B102" s="278">
         <f t="shared" si="28"/>
@@ -13242,11 +13299,11 @@
       <c r="O102" s="185">
         <v>0</v>
       </c>
-      <c r="P102" s="384">
+      <c r="P102" s="388">
         <f t="shared" ref="P102:P133" si="30">ROUND(SUM(G102:O102),0) + S102</f>
         <v>752947.97</v>
       </c>
-      <c r="Q102" s="384"/>
+      <c r="Q102" s="388"/>
       <c r="R102" s="226">
         <f t="shared" ref="R102:R133" si="31">ROUND(P102+P102*3.033%,0) + S102</f>
         <v>775785.97</v>
@@ -13263,7 +13320,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="103" spans="1:22" ht="24.9" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:22" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A103" s="16"/>
       <c r="B103" s="278">
         <f t="shared" si="28"/>
@@ -13315,11 +13372,11 @@
       <c r="O103" s="185">
         <v>0</v>
       </c>
-      <c r="P103" s="384">
+      <c r="P103" s="388">
         <f t="shared" si="30"/>
         <v>775884.98</v>
       </c>
-      <c r="Q103" s="384"/>
+      <c r="Q103" s="388"/>
       <c r="R103" s="226">
         <f t="shared" si="31"/>
         <v>799418.98</v>
@@ -13333,7 +13390,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="104" spans="1:22" ht="24.9" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:22" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A104" s="16"/>
       <c r="B104" s="278">
         <f t="shared" si="28"/>
@@ -13385,11 +13442,11 @@
       <c r="O104" s="185">
         <v>0</v>
       </c>
-      <c r="P104" s="384">
+      <c r="P104" s="388">
         <f t="shared" si="30"/>
         <v>775884.99</v>
       </c>
-      <c r="Q104" s="384"/>
+      <c r="Q104" s="388"/>
       <c r="R104" s="226">
         <f t="shared" si="31"/>
         <v>799418.99</v>
@@ -13406,7 +13463,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="105" spans="1:22" ht="24.9" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:22" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A105" s="16"/>
       <c r="B105" s="278">
         <f t="shared" si="28"/>
@@ -13458,11 +13515,11 @@
       <c r="O105" s="185">
         <v>0</v>
       </c>
-      <c r="P105" s="384">
+      <c r="P105" s="388">
         <f t="shared" si="30"/>
         <v>775885</v>
       </c>
-      <c r="Q105" s="384"/>
+      <c r="Q105" s="388"/>
       <c r="R105" s="226">
         <f t="shared" si="31"/>
         <v>799419</v>
@@ -13476,7 +13533,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="106" spans="1:22" ht="24.9" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:22" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A106" s="157"/>
       <c r="B106" s="278">
         <f t="shared" si="28"/>
@@ -13528,11 +13585,11 @@
       <c r="O106" s="185">
         <v>0</v>
       </c>
-      <c r="P106" s="384">
+      <c r="P106" s="388">
         <f t="shared" si="30"/>
         <v>775885.01</v>
       </c>
-      <c r="Q106" s="384"/>
+      <c r="Q106" s="388"/>
       <c r="R106" s="226">
         <f t="shared" si="31"/>
         <v>799419.01</v>
@@ -13546,7 +13603,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="107" spans="1:22" ht="24.9" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:22" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A107" s="218"/>
       <c r="B107" s="347">
         <f t="shared" si="28"/>
@@ -13597,11 +13654,11 @@
       <c r="O107" s="185">
         <v>0</v>
       </c>
-      <c r="P107" s="384">
+      <c r="P107" s="388">
         <f t="shared" si="30"/>
         <v>768658.02</v>
       </c>
-      <c r="Q107" s="384"/>
+      <c r="Q107" s="388"/>
       <c r="R107" s="226">
         <f t="shared" si="31"/>
         <v>791972.02</v>
@@ -13618,7 +13675,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="108" spans="1:22" ht="24.9" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:22" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A108" s="16"/>
       <c r="B108" s="278">
         <f t="shared" si="28"/>
@@ -13667,11 +13724,11 @@
       <c r="O108" s="185">
         <v>0</v>
       </c>
-      <c r="P108" s="384">
+      <c r="P108" s="388">
         <f t="shared" si="30"/>
         <v>2375239.0299999998</v>
       </c>
-      <c r="Q108" s="384"/>
+      <c r="Q108" s="388"/>
       <c r="R108" s="226">
         <f t="shared" si="31"/>
         <v>2447281.0299999998</v>
@@ -13685,7 +13742,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="109" spans="1:22" ht="24.9" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:22" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A109" s="218"/>
       <c r="B109" s="278">
         <f t="shared" si="28"/>
@@ -13734,11 +13791,11 @@
       <c r="O109" s="185">
         <v>0</v>
       </c>
-      <c r="P109" s="384">
+      <c r="P109" s="388">
         <f t="shared" si="30"/>
         <v>1535993.04</v>
       </c>
-      <c r="Q109" s="384"/>
+      <c r="Q109" s="388"/>
       <c r="R109" s="226">
         <f t="shared" si="31"/>
         <v>1582581.04</v>
@@ -13755,7 +13812,7 @@
         <v>337</v>
       </c>
     </row>
-    <row r="110" spans="1:22" ht="24.9" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:22" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A110" s="218"/>
       <c r="B110" s="347">
         <f t="shared" si="28"/>
@@ -13807,11 +13864,11 @@
       <c r="O110" s="185">
         <v>0</v>
       </c>
-      <c r="P110" s="384">
+      <c r="P110" s="388">
         <f t="shared" si="30"/>
         <v>727479.05</v>
       </c>
-      <c r="Q110" s="384"/>
+      <c r="Q110" s="388"/>
       <c r="R110" s="226">
         <f t="shared" si="31"/>
         <v>749544.05</v>
@@ -13829,7 +13886,7 @@
       </c>
       <c r="V110" s="33"/>
     </row>
-    <row r="111" spans="1:22" ht="24.9" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:22" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A111" s="219"/>
       <c r="B111" s="278">
         <f t="shared" si="28"/>
@@ -13879,11 +13936,11 @@
       <c r="O111" s="185">
         <v>0</v>
       </c>
-      <c r="P111" s="384">
+      <c r="P111" s="388">
         <f t="shared" si="30"/>
         <v>2375272.06</v>
       </c>
-      <c r="Q111" s="384"/>
+      <c r="Q111" s="388"/>
       <c r="R111" s="226">
         <f t="shared" si="31"/>
         <v>2447315.06</v>
@@ -13900,7 +13957,7 @@
         <v>316</v>
       </c>
     </row>
-    <row r="112" spans="1:22" ht="24.9" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:22" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A112" s="16"/>
       <c r="B112" s="278">
         <f t="shared" si="28"/>
@@ -13952,11 +14009,11 @@
       <c r="O112" s="185">
         <v>0</v>
       </c>
-      <c r="P112" s="384">
+      <c r="P112" s="388">
         <f t="shared" si="30"/>
         <v>743614.07</v>
       </c>
-      <c r="Q112" s="384"/>
+      <c r="Q112" s="388"/>
       <c r="R112" s="226">
         <f t="shared" si="31"/>
         <v>766169.07</v>
@@ -13973,7 +14030,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="113" spans="1:25" ht="24.9" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:25" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A113" s="16"/>
       <c r="B113" s="278">
         <f t="shared" si="28"/>
@@ -14024,11 +14081,11 @@
       <c r="O113" s="185">
         <v>0</v>
       </c>
-      <c r="P113" s="384">
+      <c r="P113" s="388">
         <f t="shared" si="30"/>
         <v>721059.08</v>
       </c>
-      <c r="Q113" s="384"/>
+      <c r="Q113" s="388"/>
       <c r="R113" s="226">
         <f t="shared" si="31"/>
         <v>742930.08</v>
@@ -14042,13 +14099,13 @@
         <v>108</v>
       </c>
     </row>
-    <row r="114" spans="1:25" ht="24.9" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:25" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A114" s="247"/>
-      <c r="B114" s="278">
+      <c r="B114" s="347">
         <f t="shared" si="28"/>
         <v>109</v>
       </c>
-      <c r="C114" s="278" t="s">
+      <c r="C114" s="347" t="s">
         <v>118</v>
       </c>
       <c r="D114" s="281">
@@ -14093,11 +14150,11 @@
       <c r="O114" s="185">
         <v>0</v>
       </c>
-      <c r="P114" s="384">
+      <c r="P114" s="388">
         <f t="shared" si="30"/>
         <v>1437332.09</v>
       </c>
-      <c r="Q114" s="384"/>
+      <c r="Q114" s="388"/>
       <c r="R114" s="226">
         <f t="shared" si="31"/>
         <v>1480927.09</v>
@@ -14114,7 +14171,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="115" spans="1:25" ht="24.9" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:25" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A115" s="218"/>
       <c r="B115" s="278">
         <f t="shared" si="28"/>
@@ -14165,11 +14222,11 @@
       <c r="O115" s="185">
         <v>0</v>
       </c>
-      <c r="P115" s="384">
+      <c r="P115" s="388">
         <f t="shared" si="30"/>
         <v>756957.1</v>
       </c>
-      <c r="Q115" s="384"/>
+      <c r="Q115" s="388"/>
       <c r="R115" s="226">
         <f t="shared" si="31"/>
         <v>779917.1</v>
@@ -14187,7 +14244,7 @@
       </c>
       <c r="Y115" s="38"/>
     </row>
-    <row r="116" spans="1:25" ht="24.9" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:25" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A116" s="16"/>
       <c r="B116" s="278">
         <f t="shared" si="28"/>
@@ -14239,11 +14296,11 @@
       <c r="O116" s="185">
         <v>0</v>
       </c>
-      <c r="P116" s="384">
+      <c r="P116" s="388">
         <f t="shared" si="30"/>
         <v>751682.11</v>
       </c>
-      <c r="Q116" s="384"/>
+      <c r="Q116" s="388"/>
       <c r="R116" s="226">
         <f t="shared" si="31"/>
         <v>774482.11</v>
@@ -14257,7 +14314,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="117" spans="1:25" ht="24.9" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:25" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A117" s="243"/>
       <c r="B117" s="278">
         <f t="shared" si="28"/>
@@ -14308,11 +14365,11 @@
       <c r="O117" s="185">
         <v>0</v>
       </c>
-      <c r="P117" s="384">
+      <c r="P117" s="388">
         <f t="shared" si="30"/>
         <v>751046.12</v>
       </c>
-      <c r="Q117" s="384"/>
+      <c r="Q117" s="388"/>
       <c r="R117" s="226">
         <f t="shared" si="31"/>
         <v>773826.12</v>
@@ -14329,7 +14386,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="118" spans="1:25" ht="24.9" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:25" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A118" s="16"/>
       <c r="B118" s="278">
         <f t="shared" si="28"/>
@@ -14380,11 +14437,11 @@
       <c r="O118" s="185">
         <v>0</v>
       </c>
-      <c r="P118" s="384">
+      <c r="P118" s="388">
         <f t="shared" si="30"/>
         <v>745234.13</v>
       </c>
-      <c r="Q118" s="384"/>
+      <c r="Q118" s="388"/>
       <c r="R118" s="226">
         <f t="shared" si="31"/>
         <v>767838.13</v>
@@ -14398,7 +14455,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="119" spans="1:25" ht="24.9" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:25" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A119" s="16"/>
       <c r="B119" s="278">
         <f t="shared" si="28"/>
@@ -14451,11 +14508,11 @@
         <f>2239*100</f>
         <v>223900</v>
       </c>
-      <c r="P119" s="384">
+      <c r="P119" s="388">
         <f t="shared" si="30"/>
         <v>975582.14</v>
       </c>
-      <c r="Q119" s="384"/>
+      <c r="Q119" s="388"/>
       <c r="R119" s="226">
         <f t="shared" si="31"/>
         <v>1005173.14</v>
@@ -14469,7 +14526,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="120" spans="1:25" ht="24.9" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:25" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A120" s="16"/>
       <c r="B120" s="278">
         <f t="shared" si="28"/>
@@ -14521,11 +14578,11 @@
       <c r="O120" s="185">
         <v>0</v>
       </c>
-      <c r="P120" s="384">
+      <c r="P120" s="388">
         <f t="shared" si="30"/>
         <v>904966.15</v>
       </c>
-      <c r="Q120" s="384"/>
+      <c r="Q120" s="388"/>
       <c r="R120" s="226">
         <f t="shared" si="31"/>
         <v>932415.15</v>
@@ -14542,7 +14599,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="121" spans="1:25" ht="24.9" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:25" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A121" s="16"/>
       <c r="B121" s="278">
         <f t="shared" si="28"/>
@@ -14593,11 +14650,11 @@
       <c r="O121" s="185">
         <v>0</v>
       </c>
-      <c r="P121" s="384">
+      <c r="P121" s="388">
         <f t="shared" si="30"/>
         <v>831345.16</v>
       </c>
-      <c r="Q121" s="384"/>
+      <c r="Q121" s="388"/>
       <c r="R121" s="226">
         <f t="shared" si="31"/>
         <v>856561.16</v>
@@ -14611,7 +14668,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="122" spans="1:25" ht="24.9" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:25" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A122" s="16"/>
       <c r="B122" s="278">
         <f t="shared" si="28"/>
@@ -14663,11 +14720,11 @@
       <c r="O122" s="185">
         <v>0</v>
       </c>
-      <c r="P122" s="384">
+      <c r="P122" s="388">
         <f t="shared" si="30"/>
         <v>880763.17</v>
       </c>
-      <c r="Q122" s="384"/>
+      <c r="Q122" s="388"/>
       <c r="R122" s="226">
         <f t="shared" si="31"/>
         <v>907478.17</v>
@@ -14684,7 +14741,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="123" spans="1:25" ht="24.9" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:25" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A123" s="243"/>
       <c r="B123" s="347">
         <f t="shared" si="28"/>
@@ -14736,11 +14793,11 @@
       <c r="O123" s="185">
         <v>0</v>
       </c>
-      <c r="P123" s="384">
+      <c r="P123" s="388">
         <f t="shared" si="30"/>
         <v>855741.18</v>
       </c>
-      <c r="Q123" s="384"/>
+      <c r="Q123" s="388"/>
       <c r="R123" s="226">
         <f t="shared" si="31"/>
         <v>881697.18</v>
@@ -14757,7 +14814,7 @@
         <v>298</v>
       </c>
     </row>
-    <row r="124" spans="1:25" ht="24.9" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:25" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A124" s="162"/>
       <c r="B124" s="324">
         <f t="shared" si="28"/>
@@ -14808,11 +14865,11 @@
       <c r="O124" s="185">
         <v>0</v>
       </c>
-      <c r="P124" s="384">
+      <c r="P124" s="388">
         <f t="shared" si="30"/>
         <v>824124.19</v>
       </c>
-      <c r="Q124" s="384"/>
+      <c r="Q124" s="388"/>
       <c r="R124" s="226">
         <f t="shared" si="31"/>
         <v>849121.19</v>
@@ -14829,7 +14886,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="125" spans="1:25" ht="24.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:25" ht="24.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A125" s="16"/>
       <c r="B125" s="278">
         <f t="shared" si="28"/>
@@ -14881,11 +14938,11 @@
       <c r="O125" s="185">
         <v>0</v>
       </c>
-      <c r="P125" s="384">
+      <c r="P125" s="388">
         <f t="shared" si="30"/>
         <v>759749.2</v>
       </c>
-      <c r="Q125" s="384"/>
+      <c r="Q125" s="388"/>
       <c r="R125" s="226">
         <f t="shared" si="31"/>
         <v>782793.2</v>
@@ -14902,7 +14959,7 @@
         <v>299</v>
       </c>
     </row>
-    <row r="126" spans="1:25" ht="24.9" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:25" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A126" s="16"/>
       <c r="B126" s="278">
         <f t="shared" si="28"/>
@@ -14954,11 +15011,11 @@
       <c r="O126" s="185">
         <v>0</v>
       </c>
-      <c r="P126" s="384">
+      <c r="P126" s="388">
         <f t="shared" si="30"/>
         <v>759749.21</v>
       </c>
-      <c r="Q126" s="384"/>
+      <c r="Q126" s="388"/>
       <c r="R126" s="226">
         <f t="shared" si="31"/>
         <v>782793.21</v>
@@ -14975,7 +15032,7 @@
         <v>299</v>
       </c>
     </row>
-    <row r="127" spans="1:25" ht="24.9" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:25" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A127" s="16"/>
       <c r="B127" s="278">
         <f t="shared" si="28"/>
@@ -15027,11 +15084,11 @@
       <c r="O127" s="185">
         <v>0</v>
       </c>
-      <c r="P127" s="384">
+      <c r="P127" s="388">
         <f t="shared" si="30"/>
         <v>759749.22</v>
       </c>
-      <c r="Q127" s="384"/>
+      <c r="Q127" s="388"/>
       <c r="R127" s="226">
         <f t="shared" si="31"/>
         <v>782793.22</v>
@@ -15045,7 +15102,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="128" spans="1:25" ht="24.9" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:25" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A128" s="16"/>
       <c r="B128" s="278">
         <f t="shared" si="28"/>
@@ -15097,11 +15154,11 @@
       <c r="O128" s="185">
         <v>0</v>
       </c>
-      <c r="P128" s="384">
+      <c r="P128" s="388">
         <f t="shared" si="30"/>
         <v>759749.23</v>
       </c>
-      <c r="Q128" s="384"/>
+      <c r="Q128" s="388"/>
       <c r="R128" s="226">
         <f t="shared" si="31"/>
         <v>782793.23</v>
@@ -15118,7 +15175,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="129" spans="1:21" ht="24.9" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:21" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A129" s="16"/>
       <c r="B129" s="278">
         <f t="shared" si="28"/>
@@ -15169,11 +15226,11 @@
       <c r="O129" s="185">
         <v>0</v>
       </c>
-      <c r="P129" s="384">
+      <c r="P129" s="388">
         <f t="shared" si="30"/>
         <v>737383.24</v>
       </c>
-      <c r="Q129" s="384"/>
+      <c r="Q129" s="388"/>
       <c r="R129" s="226">
         <f t="shared" si="31"/>
         <v>759749.24</v>
@@ -15187,7 +15244,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="130" spans="1:21" ht="24.9" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:21" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A130" s="16"/>
       <c r="B130" s="278">
         <f t="shared" si="28"/>
@@ -15239,11 +15296,11 @@
       <c r="O130" s="185">
         <v>0</v>
       </c>
-      <c r="P130" s="384">
+      <c r="P130" s="388">
         <f t="shared" si="30"/>
         <v>759749.25</v>
       </c>
-      <c r="Q130" s="384"/>
+      <c r="Q130" s="388"/>
       <c r="R130" s="226">
         <f t="shared" si="31"/>
         <v>782793.25</v>
@@ -15260,7 +15317,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="131" spans="1:21" ht="24.9" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:21" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A131" s="16"/>
       <c r="B131" s="278">
         <f t="shared" si="28"/>
@@ -15312,11 +15369,11 @@
       <c r="O131" s="185">
         <v>0</v>
       </c>
-      <c r="P131" s="384">
+      <c r="P131" s="388">
         <f t="shared" si="30"/>
         <v>759749.26</v>
       </c>
-      <c r="Q131" s="384"/>
+      <c r="Q131" s="388"/>
       <c r="R131" s="226">
         <f t="shared" si="31"/>
         <v>782793.26</v>
@@ -15330,7 +15387,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="132" spans="1:21" ht="24.9" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:21" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A132" s="16"/>
       <c r="B132" s="278">
         <f t="shared" si="28"/>
@@ -15382,11 +15439,11 @@
       <c r="O132" s="185">
         <v>0</v>
       </c>
-      <c r="P132" s="384">
+      <c r="P132" s="388">
         <f t="shared" si="30"/>
         <v>840425.27</v>
       </c>
-      <c r="Q132" s="384"/>
+      <c r="Q132" s="388"/>
       <c r="R132" s="226">
         <f t="shared" si="31"/>
         <v>865916.27</v>
@@ -15403,7 +15460,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="133" spans="1:21" ht="24.9" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:21" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A133" s="16"/>
       <c r="B133" s="278">
         <f t="shared" si="28"/>
@@ -15455,11 +15512,11 @@
       <c r="O133" s="185">
         <v>0</v>
       </c>
-      <c r="P133" s="384">
+      <c r="P133" s="388">
         <f t="shared" si="30"/>
         <v>880763.28</v>
       </c>
-      <c r="Q133" s="384"/>
+      <c r="Q133" s="388"/>
       <c r="R133" s="226">
         <f t="shared" si="31"/>
         <v>907478.28</v>
@@ -15473,7 +15530,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="134" spans="1:21" ht="24.9" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:21" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A134" s="16"/>
       <c r="B134" s="278">
         <f>B133+1</f>
@@ -15525,11 +15582,11 @@
       <c r="O134" s="185">
         <v>0</v>
       </c>
-      <c r="P134" s="384">
+      <c r="P134" s="388">
         <f t="shared" ref="P134:P144" si="37">ROUND(SUM(G134:O134),0) + S134</f>
         <v>880763.29</v>
       </c>
-      <c r="Q134" s="384"/>
+      <c r="Q134" s="388"/>
       <c r="R134" s="226">
         <f t="shared" ref="R134:R144" si="38">ROUND(P134+P134*3.033%,0) + S134</f>
         <v>907478.29</v>
@@ -15546,7 +15603,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="135" spans="1:21" ht="24.9" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:21" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A135" s="248"/>
       <c r="B135" s="347">
         <f t="shared" si="28"/>
@@ -15597,11 +15654,11 @@
       <c r="O135" s="185">
         <v>0</v>
       </c>
-      <c r="P135" s="384">
+      <c r="P135" s="388">
         <f t="shared" si="37"/>
         <v>846837.3</v>
       </c>
-      <c r="Q135" s="384"/>
+      <c r="Q135" s="388"/>
       <c r="R135" s="226">
         <f t="shared" si="38"/>
         <v>872523.3</v>
@@ -15618,7 +15675,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="136" spans="1:21" ht="24.9" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:21" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A136" s="16"/>
       <c r="B136" s="278">
         <f t="shared" si="28"/>
@@ -15670,11 +15727,11 @@
       <c r="O136" s="185">
         <v>0</v>
       </c>
-      <c r="P136" s="384">
+      <c r="P136" s="388">
         <f t="shared" si="37"/>
         <v>880763.31</v>
       </c>
-      <c r="Q136" s="384"/>
+      <c r="Q136" s="388"/>
       <c r="R136" s="226">
         <f t="shared" si="38"/>
         <v>907478.31</v>
@@ -15691,7 +15748,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="137" spans="1:21" ht="24.9" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:21" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A137" s="16"/>
       <c r="B137" s="278">
         <f t="shared" si="28"/>
@@ -15743,11 +15800,11 @@
       <c r="O137" s="185">
         <v>0</v>
       </c>
-      <c r="P137" s="384">
+      <c r="P137" s="388">
         <f t="shared" si="37"/>
         <v>872696.31999999995</v>
       </c>
-      <c r="Q137" s="384"/>
+      <c r="Q137" s="388"/>
       <c r="R137" s="226">
         <f t="shared" si="38"/>
         <v>899166.32</v>
@@ -15764,7 +15821,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="138" spans="1:21" ht="24.9" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:21" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A138" s="16"/>
       <c r="B138" s="278">
         <f t="shared" ref="B138:B146" si="44">B137+1</f>
@@ -15816,11 +15873,11 @@
       <c r="O138" s="185">
         <v>0</v>
       </c>
-      <c r="P138" s="384">
+      <c r="P138" s="388">
         <f t="shared" si="37"/>
         <v>904966.33</v>
       </c>
-      <c r="Q138" s="384"/>
+      <c r="Q138" s="388"/>
       <c r="R138" s="226">
         <f t="shared" si="38"/>
         <v>932415.33</v>
@@ -15837,7 +15894,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="139" spans="1:21" ht="24.9" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:21" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A139" s="16"/>
       <c r="B139" s="278">
         <f t="shared" si="44"/>
@@ -15888,11 +15945,11 @@
       <c r="O139" s="185">
         <v>0</v>
       </c>
-      <c r="P139" s="384">
+      <c r="P139" s="388">
         <f t="shared" si="37"/>
         <v>792216.34</v>
       </c>
-      <c r="Q139" s="384"/>
+      <c r="Q139" s="388"/>
       <c r="R139" s="226">
         <f t="shared" si="38"/>
         <v>816245.34</v>
@@ -15909,7 +15966,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="140" spans="1:21" ht="24.9" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:21" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A140" s="16"/>
       <c r="B140" s="278">
         <f t="shared" si="44"/>
@@ -15960,11 +16017,11 @@
       <c r="O140" s="185">
         <v>0</v>
       </c>
-      <c r="P140" s="384">
+      <c r="P140" s="388">
         <f t="shared" si="37"/>
         <v>854858.35</v>
       </c>
-      <c r="Q140" s="384"/>
+      <c r="Q140" s="388"/>
       <c r="R140" s="226">
         <f t="shared" si="38"/>
         <v>880787.35</v>
@@ -15981,7 +16038,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="141" spans="1:21" ht="24.9" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:21" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A141" s="16"/>
       <c r="B141" s="278">
         <f t="shared" si="44"/>
@@ -16033,11 +16090,11 @@
       <c r="O141" s="185">
         <v>0</v>
       </c>
-      <c r="P141" s="384">
+      <c r="P141" s="388">
         <f t="shared" si="37"/>
         <v>888831.36</v>
       </c>
-      <c r="Q141" s="384"/>
+      <c r="Q141" s="388"/>
       <c r="R141" s="226">
         <f t="shared" si="38"/>
         <v>915791.35999999999</v>
@@ -16054,7 +16111,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="142" spans="1:21" ht="24.9" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:21" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A142" s="16"/>
       <c r="B142" s="278">
         <f t="shared" si="44"/>
@@ -16106,11 +16163,11 @@
       <c r="O142" s="185">
         <v>0</v>
       </c>
-      <c r="P142" s="384">
+      <c r="P142" s="388">
         <f t="shared" si="37"/>
         <v>824290.37</v>
       </c>
-      <c r="Q142" s="384"/>
+      <c r="Q142" s="388"/>
       <c r="R142" s="226">
         <f t="shared" si="38"/>
         <v>849292.37</v>
@@ -16124,7 +16181,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="143" spans="1:21" ht="24.9" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:21" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A143" s="16"/>
       <c r="B143" s="278">
         <f t="shared" si="44"/>
@@ -16175,11 +16232,11 @@
       <c r="O143" s="185">
         <v>0</v>
       </c>
-      <c r="P143" s="384">
+      <c r="P143" s="388">
         <f t="shared" si="37"/>
         <v>886155.38</v>
       </c>
-      <c r="Q143" s="384"/>
+      <c r="Q143" s="388"/>
       <c r="R143" s="226">
         <f t="shared" si="38"/>
         <v>913033.38</v>
@@ -16196,7 +16253,7 @@
         <v>280</v>
       </c>
     </row>
-    <row r="144" spans="1:21" ht="24.9" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:21" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A144" s="16"/>
       <c r="B144" s="278">
         <f t="shared" si="44"/>
@@ -16247,11 +16304,11 @@
       <c r="O144" s="185">
         <v>0</v>
       </c>
-      <c r="P144" s="384">
+      <c r="P144" s="388">
         <f t="shared" si="37"/>
         <v>1273198.3899999999</v>
       </c>
-      <c r="Q144" s="384"/>
+      <c r="Q144" s="388"/>
       <c r="R144" s="226">
         <f t="shared" si="38"/>
         <v>1311815.3899999999</v>
@@ -16268,7 +16325,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="145" spans="1:22" ht="24.9" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:22" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A145" s="16"/>
       <c r="B145" s="278">
         <f t="shared" si="44"/>
@@ -16297,8 +16354,8 @@
       <c r="O145" s="185">
         <v>0</v>
       </c>
-      <c r="P145" s="384"/>
-      <c r="Q145" s="384"/>
+      <c r="P145" s="388"/>
+      <c r="Q145" s="388"/>
       <c r="R145" s="227"/>
       <c r="S145" s="13">
         <f t="shared" si="39"/>
@@ -16309,7 +16366,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="146" spans="1:22" ht="24.9" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:22" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A146" s="16"/>
       <c r="B146" s="278">
         <f t="shared" si="44"/>
@@ -16338,8 +16395,8 @@
       <c r="O146" s="185">
         <v>0</v>
       </c>
-      <c r="P146" s="384"/>
-      <c r="Q146" s="384"/>
+      <c r="P146" s="388"/>
+      <c r="Q146" s="388"/>
       <c r="R146" s="227"/>
       <c r="S146" s="13">
         <f t="shared" si="39"/>
@@ -16350,7 +16407,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="147" spans="1:22" ht="24.9" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:22" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A147" s="16"/>
       <c r="B147" s="278"/>
       <c r="C147" s="278"/>
@@ -16372,8 +16429,8 @@
       <c r="O147" s="185">
         <v>0</v>
       </c>
-      <c r="P147" s="384"/>
-      <c r="Q147" s="384"/>
+      <c r="P147" s="388"/>
+      <c r="Q147" s="388"/>
       <c r="R147" s="227"/>
       <c r="S147" s="13">
         <f t="shared" si="39"/>
@@ -16384,7 +16441,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="148" spans="1:22" ht="24.9" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:22" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A148" s="16"/>
       <c r="B148" s="278"/>
       <c r="C148" s="278"/>
@@ -16406,8 +16463,8 @@
       <c r="O148" s="185">
         <v>0</v>
       </c>
-      <c r="P148" s="384"/>
-      <c r="Q148" s="384"/>
+      <c r="P148" s="388"/>
+      <c r="Q148" s="388"/>
       <c r="R148" s="227"/>
       <c r="S148" s="13">
         <f t="shared" si="39"/>
@@ -16418,7 +16475,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="149" spans="1:22" ht="24.9" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:22" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A149" s="16"/>
       <c r="B149" s="278">
         <v>146</v>
@@ -16469,11 +16526,11 @@
       <c r="O149" s="185">
         <v>0</v>
       </c>
-      <c r="P149" s="384">
+      <c r="P149" s="388">
         <f t="shared" ref="P149:P158" si="47">ROUND(SUM(G149:O149),0) + S149</f>
         <v>695209.46</v>
       </c>
-      <c r="Q149" s="384"/>
+      <c r="Q149" s="388"/>
       <c r="R149" s="226">
         <f t="shared" ref="R149:R158" si="48">ROUND(P149+P149*3.033%,0) + S149</f>
         <v>716296.46</v>
@@ -16487,7 +16544,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="150" spans="1:22" ht="24.9" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:22" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A150" s="16"/>
       <c r="B150" s="278">
         <v>155</v>
@@ -16536,11 +16593,11 @@
       <c r="O150" s="185">
         <v>0</v>
       </c>
-      <c r="P150" s="384">
+      <c r="P150" s="388">
         <f t="shared" si="47"/>
         <v>1139411.55</v>
       </c>
-      <c r="Q150" s="384"/>
+      <c r="Q150" s="388"/>
       <c r="R150" s="226">
         <f t="shared" si="48"/>
         <v>1173971.55</v>
@@ -16557,7 +16614,7 @@
         <v>297</v>
       </c>
     </row>
-    <row r="151" spans="1:22" ht="24.9" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:22" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A151" s="16"/>
       <c r="B151" s="278">
         <v>158</v>
@@ -16608,11 +16665,11 @@
       <c r="O151" s="185">
         <v>0</v>
       </c>
-      <c r="P151" s="384">
+      <c r="P151" s="388">
         <f t="shared" si="47"/>
         <v>759749.58</v>
       </c>
-      <c r="Q151" s="384"/>
+      <c r="Q151" s="388"/>
       <c r="R151" s="226">
         <f t="shared" si="48"/>
         <v>782794.58</v>
@@ -16626,7 +16683,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="152" spans="1:22" ht="24.9" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:22" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A152" s="16"/>
       <c r="B152" s="278">
         <v>159</v>
@@ -16677,11 +16734,11 @@
       <c r="O152" s="185">
         <v>0</v>
       </c>
-      <c r="P152" s="384">
+      <c r="P152" s="388">
         <f t="shared" si="47"/>
         <v>759749.59</v>
       </c>
-      <c r="Q152" s="384"/>
+      <c r="Q152" s="388"/>
       <c r="R152" s="226">
         <f t="shared" si="48"/>
         <v>782794.59</v>
@@ -16695,7 +16752,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="153" spans="1:22" ht="24.9" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:22" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A153" s="16"/>
       <c r="B153" s="278">
         <v>163</v>
@@ -16746,11 +16803,11 @@
       <c r="O153" s="185">
         <v>0</v>
       </c>
-      <c r="P153" s="384">
+      <c r="P153" s="388">
         <f t="shared" si="47"/>
         <v>759749.63</v>
       </c>
-      <c r="Q153" s="384"/>
+      <c r="Q153" s="388"/>
       <c r="R153" s="226">
         <f t="shared" si="48"/>
         <v>782794.63</v>
@@ -16764,7 +16821,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="154" spans="1:22" ht="24.9" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:22" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A154" s="16"/>
       <c r="B154" s="278">
         <v>168</v>
@@ -16815,11 +16872,11 @@
       <c r="O154" s="185">
         <v>0</v>
       </c>
-      <c r="P154" s="384">
+      <c r="P154" s="388">
         <f t="shared" si="47"/>
         <v>743614.68</v>
       </c>
-      <c r="Q154" s="384"/>
+      <c r="Q154" s="388"/>
       <c r="R154" s="226">
         <f t="shared" si="48"/>
         <v>766170.68</v>
@@ -16833,7 +16890,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="155" spans="1:22" ht="24.9" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:22" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A155" s="16"/>
       <c r="B155" s="278">
         <v>173</v>
@@ -16883,11 +16940,11 @@
       <c r="O155" s="185">
         <v>0</v>
       </c>
-      <c r="P155" s="384">
+      <c r="P155" s="388">
         <f t="shared" si="47"/>
         <v>737403.73</v>
       </c>
-      <c r="Q155" s="384"/>
+      <c r="Q155" s="388"/>
       <c r="R155" s="226">
         <f t="shared" si="48"/>
         <v>759770.73</v>
@@ -16904,7 +16961,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="156" spans="1:22" ht="24.9" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:22" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A156" s="16"/>
       <c r="B156" s="278">
         <v>175</v>
@@ -16954,11 +17011,11 @@
       <c r="O156" s="185">
         <v>0</v>
       </c>
-      <c r="P156" s="384">
+      <c r="P156" s="388">
         <f t="shared" si="47"/>
         <v>737403.75</v>
       </c>
-      <c r="Q156" s="384"/>
+      <c r="Q156" s="388"/>
       <c r="R156" s="226">
         <f t="shared" si="48"/>
         <v>759770.75</v>
@@ -16975,7 +17032,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="157" spans="1:22" ht="24.9" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:22" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A157" s="16"/>
       <c r="B157" s="278">
         <v>176</v>
@@ -17026,11 +17083,11 @@
       <c r="O157" s="185">
         <v>0</v>
       </c>
-      <c r="P157" s="384">
+      <c r="P157" s="388">
         <f t="shared" si="47"/>
         <v>759749.76</v>
       </c>
-      <c r="Q157" s="384"/>
+      <c r="Q157" s="388"/>
       <c r="R157" s="226">
         <f t="shared" si="48"/>
         <v>782794.76</v>
@@ -17044,7 +17101,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="158" spans="1:22" ht="24.9" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:22" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A158" s="16"/>
       <c r="B158" s="278">
         <v>204</v>
@@ -17094,11 +17151,11 @@
       <c r="O158" s="185">
         <v>0</v>
       </c>
-      <c r="P158" s="384">
+      <c r="P158" s="388">
         <f t="shared" si="47"/>
         <v>760106.04</v>
       </c>
-      <c r="Q158" s="384"/>
+      <c r="Q158" s="388"/>
       <c r="R158" s="226">
         <f t="shared" si="48"/>
         <v>783162.04</v>
@@ -17115,7 +17172,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="159" spans="1:22" ht="24.9" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:22" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A159" s="17"/>
       <c r="B159" s="278"/>
       <c r="C159" s="278"/>
@@ -17131,13 +17188,13 @@
       <c r="M159" s="20"/>
       <c r="N159" s="20"/>
       <c r="O159" s="66"/>
-      <c r="P159" s="389"/>
-      <c r="Q159" s="389"/>
+      <c r="P159" s="393"/>
+      <c r="Q159" s="393"/>
       <c r="R159" s="163"/>
       <c r="S159" s="13"/>
       <c r="T159" s="1"/>
     </row>
-    <row r="160" spans="1:22" ht="24.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="160" spans="1:22" ht="24.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A160" s="17"/>
       <c r="B160" s="168"/>
       <c r="C160" s="168"/>
@@ -17153,13 +17210,13 @@
       <c r="M160" s="174"/>
       <c r="N160" s="174"/>
       <c r="O160" s="223"/>
-      <c r="P160" s="390"/>
-      <c r="Q160" s="390"/>
+      <c r="P160" s="394"/>
+      <c r="Q160" s="394"/>
       <c r="R160" s="166"/>
       <c r="S160" s="13"/>
       <c r="T160" s="175"/>
     </row>
-    <row r="161" spans="1:20" ht="24.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="161" spans="1:20" ht="24.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A161" s="21"/>
       <c r="B161" s="176"/>
       <c r="C161" s="176"/>
@@ -17208,147 +17265,147 @@
         <f t="shared" si="51"/>
         <v>447800</v>
       </c>
-      <c r="P161" s="387">
+      <c r="P161" s="391">
         <f>SUM(P6:P160)</f>
         <v>146695229.06999999</v>
       </c>
-      <c r="Q161" s="388"/>
+      <c r="Q161" s="392"/>
       <c r="R161" s="167">
         <f>SUM(R6:R160)</f>
         <v>151144610.07000002</v>
       </c>
-      <c r="S161" s="387"/>
-      <c r="T161" s="388"/>
-    </row>
-    <row r="162" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B162" s="385" t="s">
+      <c r="S161" s="391"/>
+      <c r="T161" s="392"/>
+    </row>
+    <row r="162" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B162" s="389" t="s">
         <v>314</v>
       </c>
-      <c r="C162" s="385"/>
-      <c r="D162" s="385"/>
-      <c r="E162" s="385"/>
-      <c r="F162" s="385"/>
-      <c r="G162" s="385"/>
-      <c r="H162" s="385"/>
-      <c r="I162" s="385"/>
-      <c r="J162" s="385"/>
-      <c r="K162" s="385"/>
-      <c r="L162" s="385"/>
-      <c r="M162" s="385"/>
-      <c r="N162" s="385"/>
-      <c r="O162" s="385"/>
-      <c r="P162" s="385"/>
-      <c r="Q162" s="385"/>
-      <c r="R162" s="385"/>
-      <c r="S162" s="385"/>
-      <c r="T162" s="385"/>
-    </row>
-    <row r="163" spans="1:20" ht="49.65" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B163" s="386"/>
-      <c r="C163" s="386"/>
-      <c r="D163" s="386"/>
-      <c r="E163" s="386"/>
-      <c r="F163" s="386"/>
-      <c r="G163" s="386"/>
-      <c r="H163" s="386"/>
-      <c r="I163" s="386"/>
-      <c r="J163" s="386"/>
-      <c r="K163" s="386"/>
-      <c r="L163" s="386"/>
-      <c r="M163" s="386"/>
-      <c r="N163" s="386"/>
-      <c r="O163" s="386"/>
-      <c r="P163" s="386"/>
-      <c r="Q163" s="386"/>
-      <c r="R163" s="386"/>
-      <c r="S163" s="386"/>
-      <c r="T163" s="386"/>
-    </row>
-    <row r="164" spans="1:20" ht="13.65" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B164" s="386" t="s">
+      <c r="C162" s="389"/>
+      <c r="D162" s="389"/>
+      <c r="E162" s="389"/>
+      <c r="F162" s="389"/>
+      <c r="G162" s="389"/>
+      <c r="H162" s="389"/>
+      <c r="I162" s="389"/>
+      <c r="J162" s="389"/>
+      <c r="K162" s="389"/>
+      <c r="L162" s="389"/>
+      <c r="M162" s="389"/>
+      <c r="N162" s="389"/>
+      <c r="O162" s="389"/>
+      <c r="P162" s="389"/>
+      <c r="Q162" s="389"/>
+      <c r="R162" s="389"/>
+      <c r="S162" s="389"/>
+      <c r="T162" s="389"/>
+    </row>
+    <row r="163" spans="1:20" ht="49.7" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B163" s="390"/>
+      <c r="C163" s="390"/>
+      <c r="D163" s="390"/>
+      <c r="E163" s="390"/>
+      <c r="F163" s="390"/>
+      <c r="G163" s="390"/>
+      <c r="H163" s="390"/>
+      <c r="I163" s="390"/>
+      <c r="J163" s="390"/>
+      <c r="K163" s="390"/>
+      <c r="L163" s="390"/>
+      <c r="M163" s="390"/>
+      <c r="N163" s="390"/>
+      <c r="O163" s="390"/>
+      <c r="P163" s="390"/>
+      <c r="Q163" s="390"/>
+      <c r="R163" s="390"/>
+      <c r="S163" s="390"/>
+      <c r="T163" s="390"/>
+    </row>
+    <row r="164" spans="1:20" ht="13.7" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B164" s="390" t="s">
         <v>259</v>
       </c>
-      <c r="C164" s="386"/>
-      <c r="D164" s="386"/>
-      <c r="E164" s="386"/>
-      <c r="F164" s="386"/>
-      <c r="G164" s="386"/>
-      <c r="H164" s="386"/>
-      <c r="I164" s="386"/>
-      <c r="J164" s="386"/>
-      <c r="K164" s="386"/>
-      <c r="L164" s="386"/>
-      <c r="M164" s="386"/>
-      <c r="N164" s="386"/>
-      <c r="O164" s="386"/>
-      <c r="P164" s="386"/>
-      <c r="Q164" s="386"/>
-      <c r="R164" s="386"/>
-      <c r="S164" s="386"/>
-      <c r="T164" s="386"/>
-    </row>
-    <row r="165" spans="1:20" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B165" s="386"/>
-      <c r="C165" s="386"/>
-      <c r="D165" s="386"/>
-      <c r="E165" s="386"/>
-      <c r="F165" s="386"/>
-      <c r="G165" s="386"/>
-      <c r="H165" s="386"/>
-      <c r="I165" s="386"/>
-      <c r="J165" s="386"/>
-      <c r="K165" s="386"/>
-      <c r="L165" s="386"/>
-      <c r="M165" s="386"/>
-      <c r="N165" s="386"/>
-      <c r="O165" s="386"/>
-      <c r="P165" s="386"/>
-      <c r="Q165" s="386"/>
-      <c r="R165" s="386"/>
-      <c r="S165" s="386"/>
-      <c r="T165" s="386"/>
-    </row>
-    <row r="166" spans="1:20" ht="3.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B166" s="386"/>
-      <c r="C166" s="386"/>
-      <c r="D166" s="386"/>
-      <c r="E166" s="386"/>
-      <c r="F166" s="386"/>
-      <c r="G166" s="386"/>
-      <c r="H166" s="386"/>
-      <c r="I166" s="386"/>
-      <c r="J166" s="386"/>
-      <c r="K166" s="386"/>
-      <c r="L166" s="386"/>
-      <c r="M166" s="386"/>
-      <c r="N166" s="386"/>
-      <c r="O166" s="386"/>
-      <c r="P166" s="386"/>
-      <c r="Q166" s="386"/>
-      <c r="R166" s="386"/>
-      <c r="S166" s="386"/>
-      <c r="T166" s="386"/>
-    </row>
-    <row r="167" spans="1:20" ht="128.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B167" s="386"/>
-      <c r="C167" s="386"/>
-      <c r="D167" s="386"/>
-      <c r="E167" s="386"/>
-      <c r="F167" s="386"/>
-      <c r="G167" s="386"/>
-      <c r="H167" s="386"/>
-      <c r="I167" s="386"/>
-      <c r="J167" s="386"/>
-      <c r="K167" s="386"/>
-      <c r="L167" s="386"/>
-      <c r="M167" s="386"/>
-      <c r="N167" s="386"/>
-      <c r="O167" s="386"/>
-      <c r="P167" s="386"/>
-      <c r="Q167" s="386"/>
-      <c r="R167" s="386"/>
-      <c r="S167" s="386"/>
-      <c r="T167" s="386"/>
+      <c r="C164" s="390"/>
+      <c r="D164" s="390"/>
+      <c r="E164" s="390"/>
+      <c r="F164" s="390"/>
+      <c r="G164" s="390"/>
+      <c r="H164" s="390"/>
+      <c r="I164" s="390"/>
+      <c r="J164" s="390"/>
+      <c r="K164" s="390"/>
+      <c r="L164" s="390"/>
+      <c r="M164" s="390"/>
+      <c r="N164" s="390"/>
+      <c r="O164" s="390"/>
+      <c r="P164" s="390"/>
+      <c r="Q164" s="390"/>
+      <c r="R164" s="390"/>
+      <c r="S164" s="390"/>
+      <c r="T164" s="390"/>
+    </row>
+    <row r="165" spans="1:20" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B165" s="390"/>
+      <c r="C165" s="390"/>
+      <c r="D165" s="390"/>
+      <c r="E165" s="390"/>
+      <c r="F165" s="390"/>
+      <c r="G165" s="390"/>
+      <c r="H165" s="390"/>
+      <c r="I165" s="390"/>
+      <c r="J165" s="390"/>
+      <c r="K165" s="390"/>
+      <c r="L165" s="390"/>
+      <c r="M165" s="390"/>
+      <c r="N165" s="390"/>
+      <c r="O165" s="390"/>
+      <c r="P165" s="390"/>
+      <c r="Q165" s="390"/>
+      <c r="R165" s="390"/>
+      <c r="S165" s="390"/>
+      <c r="T165" s="390"/>
+    </row>
+    <row r="166" spans="1:20" ht="3.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B166" s="390"/>
+      <c r="C166" s="390"/>
+      <c r="D166" s="390"/>
+      <c r="E166" s="390"/>
+      <c r="F166" s="390"/>
+      <c r="G166" s="390"/>
+      <c r="H166" s="390"/>
+      <c r="I166" s="390"/>
+      <c r="J166" s="390"/>
+      <c r="K166" s="390"/>
+      <c r="L166" s="390"/>
+      <c r="M166" s="390"/>
+      <c r="N166" s="390"/>
+      <c r="O166" s="390"/>
+      <c r="P166" s="390"/>
+      <c r="Q166" s="390"/>
+      <c r="R166" s="390"/>
+      <c r="S166" s="390"/>
+      <c r="T166" s="390"/>
+    </row>
+    <row r="167" spans="1:20" ht="128.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B167" s="390"/>
+      <c r="C167" s="390"/>
+      <c r="D167" s="390"/>
+      <c r="E167" s="390"/>
+      <c r="F167" s="390"/>
+      <c r="G167" s="390"/>
+      <c r="H167" s="390"/>
+      <c r="I167" s="390"/>
+      <c r="J167" s="390"/>
+      <c r="K167" s="390"/>
+      <c r="L167" s="390"/>
+      <c r="M167" s="390"/>
+      <c r="N167" s="390"/>
+      <c r="O167" s="390"/>
+      <c r="P167" s="390"/>
+      <c r="Q167" s="390"/>
+      <c r="R167" s="390"/>
+      <c r="S167" s="390"/>
+      <c r="T167" s="390"/>
     </row>
   </sheetData>
   <mergeCells count="186">
@@ -17552,18 +17609,18 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{78D69DBA-AA88-413A-80A7-A9BAAE7F2C32}">
-  <dimension ref="C1:M225"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="C1:M243"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="8" max="8" width="10.88671875" customWidth="1"/>
-    <col min="10" max="10" width="24.44140625" customWidth="1"/>
-    <col min="11" max="11" width="11.44140625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="11.5546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.85546875" customWidth="1"/>
+    <col min="10" max="10" width="24.42578125" customWidth="1"/>
+    <col min="11" max="11" width="11.42578125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="11.5703125" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="13" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="3:12" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="2" spans="3:12" x14ac:dyDescent="0.3">
+    <row r="1" spans="3:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="2" spans="3:12" x14ac:dyDescent="0.25">
       <c r="C2" s="284" t="s">
         <v>158</v>
       </c>
@@ -17579,7 +17636,7 @@
       <c r="K2" s="33"/>
       <c r="L2" s="33"/>
     </row>
-    <row r="3" spans="3:12" x14ac:dyDescent="0.3">
+    <row r="3" spans="3:12" x14ac:dyDescent="0.25">
       <c r="C3" s="286"/>
       <c r="D3" s="287"/>
       <c r="E3" s="240"/>
@@ -17595,7 +17652,7 @@
       <c r="K3" s="33"/>
       <c r="L3" s="33"/>
     </row>
-    <row r="4" spans="3:12" x14ac:dyDescent="0.3">
+    <row r="4" spans="3:12" x14ac:dyDescent="0.25">
       <c r="C4" s="286" t="s">
         <v>159</v>
       </c>
@@ -17609,15 +17666,15 @@
       <c r="G4" s="33" t="s">
         <v>164</v>
       </c>
-      <c r="H4" s="417">
+      <c r="H4" s="421">
         <v>93</v>
       </c>
-      <c r="I4" s="417"/>
-      <c r="J4" s="418"/>
+      <c r="I4" s="421"/>
+      <c r="J4" s="422"/>
       <c r="K4" s="33"/>
       <c r="L4" s="33"/>
     </row>
-    <row r="5" spans="3:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="3:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C5" s="286" t="s">
         <v>162</v>
       </c>
@@ -17631,44 +17688,44 @@
       <c r="K5" s="33"/>
       <c r="L5" s="33"/>
     </row>
-    <row r="6" spans="3:12" x14ac:dyDescent="0.3">
-      <c r="C6" s="419" t="s">
+    <row r="6" spans="3:12" x14ac:dyDescent="0.25">
+      <c r="C6" s="423" t="s">
         <v>443</v>
       </c>
-      <c r="D6" s="420"/>
-      <c r="E6" s="420"/>
-      <c r="F6" s="420"/>
-      <c r="G6" s="420"/>
-      <c r="H6" s="420"/>
-      <c r="I6" s="420"/>
-      <c r="J6" s="421"/>
+      <c r="D6" s="424"/>
+      <c r="E6" s="424"/>
+      <c r="F6" s="424"/>
+      <c r="G6" s="424"/>
+      <c r="H6" s="424"/>
+      <c r="I6" s="424"/>
+      <c r="J6" s="425"/>
       <c r="K6" s="33"/>
       <c r="L6" s="33"/>
     </row>
-    <row r="7" spans="3:12" x14ac:dyDescent="0.3">
-      <c r="C7" s="422"/>
-      <c r="D7" s="423"/>
-      <c r="E7" s="423"/>
-      <c r="F7" s="423"/>
-      <c r="G7" s="423"/>
-      <c r="H7" s="423"/>
-      <c r="I7" s="423"/>
-      <c r="J7" s="424"/>
+    <row r="7" spans="3:12" x14ac:dyDescent="0.25">
+      <c r="C7" s="426"/>
+      <c r="D7" s="427"/>
+      <c r="E7" s="427"/>
+      <c r="F7" s="427"/>
+      <c r="G7" s="427"/>
+      <c r="H7" s="427"/>
+      <c r="I7" s="427"/>
+      <c r="J7" s="428"/>
       <c r="K7" s="33"/>
       <c r="L7" s="33"/>
     </row>
-    <row r="8" spans="3:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C8" s="425"/>
-      <c r="D8" s="426"/>
-      <c r="E8" s="426"/>
-      <c r="F8" s="426"/>
-      <c r="G8" s="426"/>
-      <c r="H8" s="426"/>
-      <c r="I8" s="426"/>
-      <c r="J8" s="427"/>
-    </row>
-    <row r="10" spans="3:12" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="11" spans="3:12" x14ac:dyDescent="0.3">
+    <row r="8" spans="3:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C8" s="429"/>
+      <c r="D8" s="430"/>
+      <c r="E8" s="430"/>
+      <c r="F8" s="430"/>
+      <c r="G8" s="430"/>
+      <c r="H8" s="430"/>
+      <c r="I8" s="430"/>
+      <c r="J8" s="431"/>
+    </row>
+    <row r="10" spans="3:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="11" spans="3:12" x14ac:dyDescent="0.25">
       <c r="C11" s="291" t="s">
         <v>158</v>
       </c>
@@ -17682,7 +17739,7 @@
       <c r="I11" s="237"/>
       <c r="J11" s="238"/>
     </row>
-    <row r="12" spans="3:12" x14ac:dyDescent="0.3">
+    <row r="12" spans="3:12" x14ac:dyDescent="0.25">
       <c r="C12" s="293"/>
       <c r="D12" s="294"/>
       <c r="E12" s="240"/>
@@ -17697,7 +17754,7 @@
       </c>
       <c r="J12" s="60"/>
     </row>
-    <row r="13" spans="3:12" x14ac:dyDescent="0.3">
+    <row r="13" spans="3:12" x14ac:dyDescent="0.25">
       <c r="C13" s="293" t="s">
         <v>159</v>
       </c>
@@ -17711,13 +17768,13 @@
       <c r="G13" s="33" t="s">
         <v>164</v>
       </c>
-      <c r="H13" s="417">
+      <c r="H13" s="421">
         <v>44</v>
       </c>
-      <c r="I13" s="417"/>
-      <c r="J13" s="418"/>
-    </row>
-    <row r="14" spans="3:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="I13" s="421"/>
+      <c r="J13" s="422"/>
+    </row>
+    <row r="14" spans="3:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C14" s="293" t="s">
         <v>162</v>
       </c>
@@ -17729,40 +17786,40 @@
       <c r="I14" s="33"/>
       <c r="J14" s="61"/>
     </row>
-    <row r="15" spans="3:12" x14ac:dyDescent="0.3">
-      <c r="C15" s="419" t="s">
+    <row r="15" spans="3:12" x14ac:dyDescent="0.25">
+      <c r="C15" s="423" t="s">
         <v>444</v>
       </c>
-      <c r="D15" s="420"/>
-      <c r="E15" s="420"/>
-      <c r="F15" s="420"/>
-      <c r="G15" s="420"/>
-      <c r="H15" s="420"/>
-      <c r="I15" s="420"/>
-      <c r="J15" s="421"/>
-    </row>
-    <row r="16" spans="3:12" x14ac:dyDescent="0.3">
-      <c r="C16" s="422"/>
-      <c r="D16" s="423"/>
-      <c r="E16" s="423"/>
-      <c r="F16" s="423"/>
-      <c r="G16" s="423"/>
-      <c r="H16" s="423"/>
-      <c r="I16" s="423"/>
-      <c r="J16" s="424"/>
-    </row>
-    <row r="17" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C17" s="425"/>
-      <c r="D17" s="426"/>
-      <c r="E17" s="426"/>
-      <c r="F17" s="426"/>
-      <c r="G17" s="426"/>
-      <c r="H17" s="426"/>
-      <c r="I17" s="426"/>
-      <c r="J17" s="427"/>
-    </row>
-    <row r="19" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="20" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="D15" s="424"/>
+      <c r="E15" s="424"/>
+      <c r="F15" s="424"/>
+      <c r="G15" s="424"/>
+      <c r="H15" s="424"/>
+      <c r="I15" s="424"/>
+      <c r="J15" s="425"/>
+    </row>
+    <row r="16" spans="3:12" x14ac:dyDescent="0.25">
+      <c r="C16" s="426"/>
+      <c r="D16" s="427"/>
+      <c r="E16" s="427"/>
+      <c r="F16" s="427"/>
+      <c r="G16" s="427"/>
+      <c r="H16" s="427"/>
+      <c r="I16" s="427"/>
+      <c r="J16" s="428"/>
+    </row>
+    <row r="17" spans="3:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C17" s="429"/>
+      <c r="D17" s="430"/>
+      <c r="E17" s="430"/>
+      <c r="F17" s="430"/>
+      <c r="G17" s="430"/>
+      <c r="H17" s="430"/>
+      <c r="I17" s="430"/>
+      <c r="J17" s="431"/>
+    </row>
+    <row r="19" spans="3:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="20" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C20" s="295" t="s">
         <v>158</v>
       </c>
@@ -17776,7 +17833,7 @@
       <c r="I20" s="237"/>
       <c r="J20" s="238"/>
     </row>
-    <row r="21" spans="3:10" x14ac:dyDescent="0.3">
+    <row r="21" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C21" s="297"/>
       <c r="D21" s="298"/>
       <c r="E21" s="240"/>
@@ -17791,7 +17848,7 @@
       </c>
       <c r="J21" s="60"/>
     </row>
-    <row r="22" spans="3:10" x14ac:dyDescent="0.3">
+    <row r="22" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C22" s="297" t="s">
         <v>159</v>
       </c>
@@ -17805,13 +17862,13 @@
       <c r="G22" s="33" t="s">
         <v>164</v>
       </c>
-      <c r="H22" s="417">
+      <c r="H22" s="421">
         <v>90</v>
       </c>
-      <c r="I22" s="417"/>
-      <c r="J22" s="418"/>
-    </row>
-    <row r="23" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="I22" s="421"/>
+      <c r="J22" s="422"/>
+    </row>
+    <row r="23" spans="3:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C23" s="297" t="s">
         <v>162</v>
       </c>
@@ -17823,40 +17880,40 @@
       <c r="I23" s="33"/>
       <c r="J23" s="61"/>
     </row>
-    <row r="24" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C24" s="419" t="s">
+    <row r="24" spans="3:10" x14ac:dyDescent="0.25">
+      <c r="C24" s="423" t="s">
         <v>445</v>
       </c>
-      <c r="D24" s="420"/>
-      <c r="E24" s="420"/>
-      <c r="F24" s="420"/>
-      <c r="G24" s="420"/>
-      <c r="H24" s="420"/>
-      <c r="I24" s="420"/>
-      <c r="J24" s="421"/>
-    </row>
-    <row r="25" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C25" s="422"/>
-      <c r="D25" s="423"/>
-      <c r="E25" s="423"/>
-      <c r="F25" s="423"/>
-      <c r="G25" s="423"/>
-      <c r="H25" s="423"/>
-      <c r="I25" s="423"/>
-      <c r="J25" s="424"/>
-    </row>
-    <row r="26" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C26" s="425"/>
-      <c r="D26" s="426"/>
-      <c r="E26" s="426"/>
-      <c r="F26" s="426"/>
-      <c r="G26" s="426"/>
-      <c r="H26" s="426"/>
-      <c r="I26" s="426"/>
-      <c r="J26" s="427"/>
-    </row>
-    <row r="28" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="29" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="D24" s="424"/>
+      <c r="E24" s="424"/>
+      <c r="F24" s="424"/>
+      <c r="G24" s="424"/>
+      <c r="H24" s="424"/>
+      <c r="I24" s="424"/>
+      <c r="J24" s="425"/>
+    </row>
+    <row r="25" spans="3:10" x14ac:dyDescent="0.25">
+      <c r="C25" s="426"/>
+      <c r="D25" s="427"/>
+      <c r="E25" s="427"/>
+      <c r="F25" s="427"/>
+      <c r="G25" s="427"/>
+      <c r="H25" s="427"/>
+      <c r="I25" s="427"/>
+      <c r="J25" s="428"/>
+    </row>
+    <row r="26" spans="3:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C26" s="429"/>
+      <c r="D26" s="430"/>
+      <c r="E26" s="430"/>
+      <c r="F26" s="430"/>
+      <c r="G26" s="430"/>
+      <c r="H26" s="430"/>
+      <c r="I26" s="430"/>
+      <c r="J26" s="431"/>
+    </row>
+    <row r="28" spans="3:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="29" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C29" s="301" t="s">
         <v>158</v>
       </c>
@@ -17870,7 +17927,7 @@
       <c r="I29" s="237"/>
       <c r="J29" s="238"/>
     </row>
-    <row r="30" spans="3:10" x14ac:dyDescent="0.3">
+    <row r="30" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C30" s="303"/>
       <c r="D30" s="304"/>
       <c r="E30" s="240"/>
@@ -17885,7 +17942,7 @@
       </c>
       <c r="J30" s="60"/>
     </row>
-    <row r="31" spans="3:10" x14ac:dyDescent="0.3">
+    <row r="31" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C31" s="303" t="s">
         <v>159</v>
       </c>
@@ -17899,13 +17956,13 @@
       <c r="G31" s="33" t="s">
         <v>164</v>
       </c>
-      <c r="H31" s="417">
+      <c r="H31" s="421">
         <v>78</v>
       </c>
-      <c r="I31" s="417"/>
-      <c r="J31" s="418"/>
-    </row>
-    <row r="32" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="I31" s="421"/>
+      <c r="J31" s="422"/>
+    </row>
+    <row r="32" spans="3:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C32" s="303" t="s">
         <v>162</v>
       </c>
@@ -17917,40 +17974,40 @@
       <c r="I32" s="33"/>
       <c r="J32" s="61"/>
     </row>
-    <row r="33" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C33" s="419" t="s">
+    <row r="33" spans="3:10" x14ac:dyDescent="0.25">
+      <c r="C33" s="423" t="s">
         <v>446</v>
       </c>
-      <c r="D33" s="420"/>
-      <c r="E33" s="420"/>
-      <c r="F33" s="420"/>
-      <c r="G33" s="420"/>
-      <c r="H33" s="420"/>
-      <c r="I33" s="420"/>
-      <c r="J33" s="421"/>
-    </row>
-    <row r="34" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C34" s="422"/>
-      <c r="D34" s="423"/>
-      <c r="E34" s="423"/>
-      <c r="F34" s="423"/>
-      <c r="G34" s="423"/>
-      <c r="H34" s="423"/>
-      <c r="I34" s="423"/>
-      <c r="J34" s="424"/>
-    </row>
-    <row r="35" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C35" s="425"/>
-      <c r="D35" s="426"/>
-      <c r="E35" s="426"/>
-      <c r="F35" s="426"/>
-      <c r="G35" s="426"/>
-      <c r="H35" s="426"/>
-      <c r="I35" s="426"/>
-      <c r="J35" s="427"/>
-    </row>
-    <row r="37" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="38" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="D33" s="424"/>
+      <c r="E33" s="424"/>
+      <c r="F33" s="424"/>
+      <c r="G33" s="424"/>
+      <c r="H33" s="424"/>
+      <c r="I33" s="424"/>
+      <c r="J33" s="425"/>
+    </row>
+    <row r="34" spans="3:10" x14ac:dyDescent="0.25">
+      <c r="C34" s="426"/>
+      <c r="D34" s="427"/>
+      <c r="E34" s="427"/>
+      <c r="F34" s="427"/>
+      <c r="G34" s="427"/>
+      <c r="H34" s="427"/>
+      <c r="I34" s="427"/>
+      <c r="J34" s="428"/>
+    </row>
+    <row r="35" spans="3:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C35" s="429"/>
+      <c r="D35" s="430"/>
+      <c r="E35" s="430"/>
+      <c r="F35" s="430"/>
+      <c r="G35" s="430"/>
+      <c r="H35" s="430"/>
+      <c r="I35" s="430"/>
+      <c r="J35" s="431"/>
+    </row>
+    <row r="37" spans="3:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="38" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C38" s="305" t="s">
         <v>158</v>
       </c>
@@ -17964,7 +18021,7 @@
       <c r="I38" s="237"/>
       <c r="J38" s="238"/>
     </row>
-    <row r="39" spans="3:10" x14ac:dyDescent="0.3">
+    <row r="39" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C39" s="307"/>
       <c r="D39" s="308"/>
       <c r="E39" s="240"/>
@@ -17979,7 +18036,7 @@
       </c>
       <c r="J39" s="60"/>
     </row>
-    <row r="40" spans="3:10" x14ac:dyDescent="0.3">
+    <row r="40" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C40" s="307" t="s">
         <v>159</v>
       </c>
@@ -17993,13 +18050,13 @@
       <c r="G40" s="33" t="s">
         <v>164</v>
       </c>
-      <c r="H40" s="417">
+      <c r="H40" s="421">
         <v>2</v>
       </c>
-      <c r="I40" s="417"/>
-      <c r="J40" s="418"/>
-    </row>
-    <row r="41" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="I40" s="421"/>
+      <c r="J40" s="422"/>
+    </row>
+    <row r="41" spans="3:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C41" s="307" t="s">
         <v>162</v>
       </c>
@@ -18011,40 +18068,40 @@
       <c r="I41" s="33"/>
       <c r="J41" s="61"/>
     </row>
-    <row r="42" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C42" s="419" t="s">
+    <row r="42" spans="3:10" x14ac:dyDescent="0.25">
+      <c r="C42" s="423" t="s">
         <v>447</v>
       </c>
-      <c r="D42" s="420"/>
-      <c r="E42" s="420"/>
-      <c r="F42" s="420"/>
-      <c r="G42" s="420"/>
-      <c r="H42" s="420"/>
-      <c r="I42" s="420"/>
-      <c r="J42" s="421"/>
-    </row>
-    <row r="43" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C43" s="422"/>
-      <c r="D43" s="423"/>
-      <c r="E43" s="423"/>
-      <c r="F43" s="423"/>
-      <c r="G43" s="423"/>
-      <c r="H43" s="423"/>
-      <c r="I43" s="423"/>
-      <c r="J43" s="424"/>
-    </row>
-    <row r="44" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C44" s="425"/>
-      <c r="D44" s="426"/>
-      <c r="E44" s="426"/>
-      <c r="F44" s="426"/>
-      <c r="G44" s="426"/>
-      <c r="H44" s="426"/>
-      <c r="I44" s="426"/>
-      <c r="J44" s="427"/>
-    </row>
-    <row r="46" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="47" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="D42" s="424"/>
+      <c r="E42" s="424"/>
+      <c r="F42" s="424"/>
+      <c r="G42" s="424"/>
+      <c r="H42" s="424"/>
+      <c r="I42" s="424"/>
+      <c r="J42" s="425"/>
+    </row>
+    <row r="43" spans="3:10" x14ac:dyDescent="0.25">
+      <c r="C43" s="426"/>
+      <c r="D43" s="427"/>
+      <c r="E43" s="427"/>
+      <c r="F43" s="427"/>
+      <c r="G43" s="427"/>
+      <c r="H43" s="427"/>
+      <c r="I43" s="427"/>
+      <c r="J43" s="428"/>
+    </row>
+    <row r="44" spans="3:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C44" s="429"/>
+      <c r="D44" s="430"/>
+      <c r="E44" s="430"/>
+      <c r="F44" s="430"/>
+      <c r="G44" s="430"/>
+      <c r="H44" s="430"/>
+      <c r="I44" s="430"/>
+      <c r="J44" s="431"/>
+    </row>
+    <row r="46" spans="3:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="47" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C47" s="310" t="s">
         <v>158</v>
       </c>
@@ -18058,7 +18115,7 @@
       <c r="I47" s="237"/>
       <c r="J47" s="238"/>
     </row>
-    <row r="48" spans="3:10" x14ac:dyDescent="0.3">
+    <row r="48" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C48" s="312"/>
       <c r="D48" s="313"/>
       <c r="E48" s="240"/>
@@ -18073,7 +18130,7 @@
       </c>
       <c r="J48" s="60"/>
     </row>
-    <row r="49" spans="3:10" x14ac:dyDescent="0.3">
+    <row r="49" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C49" s="312" t="s">
         <v>159</v>
       </c>
@@ -18087,13 +18144,13 @@
       <c r="G49" s="33" t="s">
         <v>164</v>
       </c>
-      <c r="H49" s="417">
+      <c r="H49" s="421">
         <v>59</v>
       </c>
-      <c r="I49" s="417"/>
-      <c r="J49" s="418"/>
-    </row>
-    <row r="50" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="I49" s="421"/>
+      <c r="J49" s="422"/>
+    </row>
+    <row r="50" spans="3:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C50" s="312" t="s">
         <v>162</v>
       </c>
@@ -18105,40 +18162,40 @@
       <c r="I50" s="33"/>
       <c r="J50" s="61"/>
     </row>
-    <row r="51" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C51" s="419" t="s">
+    <row r="51" spans="3:10" x14ac:dyDescent="0.25">
+      <c r="C51" s="423" t="s">
         <v>448</v>
       </c>
-      <c r="D51" s="420"/>
-      <c r="E51" s="420"/>
-      <c r="F51" s="420"/>
-      <c r="G51" s="420"/>
-      <c r="H51" s="420"/>
-      <c r="I51" s="420"/>
-      <c r="J51" s="421"/>
-    </row>
-    <row r="52" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C52" s="422"/>
-      <c r="D52" s="423"/>
-      <c r="E52" s="423"/>
-      <c r="F52" s="423"/>
-      <c r="G52" s="423"/>
-      <c r="H52" s="423"/>
-      <c r="I52" s="423"/>
-      <c r="J52" s="424"/>
-    </row>
-    <row r="53" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C53" s="425"/>
-      <c r="D53" s="426"/>
-      <c r="E53" s="426"/>
-      <c r="F53" s="426"/>
-      <c r="G53" s="426"/>
-      <c r="H53" s="426"/>
-      <c r="I53" s="426"/>
-      <c r="J53" s="427"/>
-    </row>
-    <row r="55" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="56" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="D51" s="424"/>
+      <c r="E51" s="424"/>
+      <c r="F51" s="424"/>
+      <c r="G51" s="424"/>
+      <c r="H51" s="424"/>
+      <c r="I51" s="424"/>
+      <c r="J51" s="425"/>
+    </row>
+    <row r="52" spans="3:10" x14ac:dyDescent="0.25">
+      <c r="C52" s="426"/>
+      <c r="D52" s="427"/>
+      <c r="E52" s="427"/>
+      <c r="F52" s="427"/>
+      <c r="G52" s="427"/>
+      <c r="H52" s="427"/>
+      <c r="I52" s="427"/>
+      <c r="J52" s="428"/>
+    </row>
+    <row r="53" spans="3:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C53" s="429"/>
+      <c r="D53" s="430"/>
+      <c r="E53" s="430"/>
+      <c r="F53" s="430"/>
+      <c r="G53" s="430"/>
+      <c r="H53" s="430"/>
+      <c r="I53" s="430"/>
+      <c r="J53" s="431"/>
+    </row>
+    <row r="55" spans="3:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="56" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C56" s="316" t="s">
         <v>158</v>
       </c>
@@ -18152,7 +18209,7 @@
       <c r="I56" s="237"/>
       <c r="J56" s="238"/>
     </row>
-    <row r="57" spans="3:10" x14ac:dyDescent="0.3">
+    <row r="57" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C57" s="318"/>
       <c r="D57" s="319"/>
       <c r="E57" s="240"/>
@@ -18167,7 +18224,7 @@
       </c>
       <c r="J57" s="60"/>
     </row>
-    <row r="58" spans="3:10" x14ac:dyDescent="0.3">
+    <row r="58" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C58" s="318" t="s">
         <v>159</v>
       </c>
@@ -18181,13 +18238,13 @@
       <c r="G58" s="33" t="s">
         <v>164</v>
       </c>
-      <c r="H58" s="417">
+      <c r="H58" s="421">
         <v>39</v>
       </c>
-      <c r="I58" s="417"/>
-      <c r="J58" s="418"/>
-    </row>
-    <row r="59" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="I58" s="421"/>
+      <c r="J58" s="422"/>
+    </row>
+    <row r="59" spans="3:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C59" s="318" t="s">
         <v>162</v>
       </c>
@@ -18199,40 +18256,40 @@
       <c r="I59" s="33"/>
       <c r="J59" s="61"/>
     </row>
-    <row r="60" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C60" s="419" t="s">
+    <row r="60" spans="3:10" x14ac:dyDescent="0.25">
+      <c r="C60" s="423" t="s">
         <v>449</v>
       </c>
-      <c r="D60" s="420"/>
-      <c r="E60" s="420"/>
-      <c r="F60" s="420"/>
-      <c r="G60" s="420"/>
-      <c r="H60" s="420"/>
-      <c r="I60" s="420"/>
-      <c r="J60" s="421"/>
-    </row>
-    <row r="61" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C61" s="422"/>
-      <c r="D61" s="423"/>
-      <c r="E61" s="423"/>
-      <c r="F61" s="423"/>
-      <c r="G61" s="423"/>
-      <c r="H61" s="423"/>
-      <c r="I61" s="423"/>
-      <c r="J61" s="424"/>
-    </row>
-    <row r="62" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C62" s="425"/>
-      <c r="D62" s="426"/>
-      <c r="E62" s="426"/>
-      <c r="F62" s="426"/>
-      <c r="G62" s="426"/>
-      <c r="H62" s="426"/>
-      <c r="I62" s="426"/>
-      <c r="J62" s="427"/>
-    </row>
-    <row r="64" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="65" spans="3:13" x14ac:dyDescent="0.3">
+      <c r="D60" s="424"/>
+      <c r="E60" s="424"/>
+      <c r="F60" s="424"/>
+      <c r="G60" s="424"/>
+      <c r="H60" s="424"/>
+      <c r="I60" s="424"/>
+      <c r="J60" s="425"/>
+    </row>
+    <row r="61" spans="3:10" x14ac:dyDescent="0.25">
+      <c r="C61" s="426"/>
+      <c r="D61" s="427"/>
+      <c r="E61" s="427"/>
+      <c r="F61" s="427"/>
+      <c r="G61" s="427"/>
+      <c r="H61" s="427"/>
+      <c r="I61" s="427"/>
+      <c r="J61" s="428"/>
+    </row>
+    <row r="62" spans="3:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C62" s="429"/>
+      <c r="D62" s="430"/>
+      <c r="E62" s="430"/>
+      <c r="F62" s="430"/>
+      <c r="G62" s="430"/>
+      <c r="H62" s="430"/>
+      <c r="I62" s="430"/>
+      <c r="J62" s="431"/>
+    </row>
+    <row r="64" spans="3:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="65" spans="3:13" x14ac:dyDescent="0.25">
       <c r="C65" s="320" t="s">
         <v>158</v>
       </c>
@@ -18245,13 +18302,13 @@
       <c r="H65" s="236"/>
       <c r="I65" s="237"/>
       <c r="J65" s="238"/>
-      <c r="K65" s="428" t="s">
+      <c r="K65" s="432" t="s">
         <v>450</v>
       </c>
-      <c r="L65" s="429"/>
-      <c r="M65" s="429"/>
-    </row>
-    <row r="66" spans="3:13" x14ac:dyDescent="0.3">
+      <c r="L65" s="433"/>
+      <c r="M65" s="433"/>
+    </row>
+    <row r="66" spans="3:13" x14ac:dyDescent="0.25">
       <c r="C66" s="322"/>
       <c r="D66" s="323"/>
       <c r="E66" s="240"/>
@@ -18265,11 +18322,11 @@
         <v>8</v>
       </c>
       <c r="J66" s="60"/>
-      <c r="K66" s="428"/>
-      <c r="L66" s="429"/>
-      <c r="M66" s="429"/>
-    </row>
-    <row r="67" spans="3:13" x14ac:dyDescent="0.3">
+      <c r="K66" s="432"/>
+      <c r="L66" s="433"/>
+      <c r="M66" s="433"/>
+    </row>
+    <row r="67" spans="3:13" x14ac:dyDescent="0.25">
       <c r="C67" s="322" t="s">
         <v>159</v>
       </c>
@@ -18283,16 +18340,16 @@
       <c r="G67" s="33" t="s">
         <v>164</v>
       </c>
-      <c r="H67" s="417">
+      <c r="H67" s="421">
         <v>104</v>
       </c>
-      <c r="I67" s="417"/>
-      <c r="J67" s="418"/>
-      <c r="K67" s="428"/>
-      <c r="L67" s="429"/>
-      <c r="M67" s="429"/>
-    </row>
-    <row r="68" spans="3:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="I67" s="421"/>
+      <c r="J67" s="422"/>
+      <c r="K67" s="432"/>
+      <c r="L67" s="433"/>
+      <c r="M67" s="433"/>
+    </row>
+    <row r="68" spans="3:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C68" s="322" t="s">
         <v>162</v>
       </c>
@@ -18303,53 +18360,53 @@
       <c r="H68" s="33"/>
       <c r="I68" s="33"/>
       <c r="J68" s="61"/>
-      <c r="K68" s="428"/>
-      <c r="L68" s="429"/>
-      <c r="M68" s="429"/>
-    </row>
-    <row r="69" spans="3:13" x14ac:dyDescent="0.3">
-      <c r="C69" s="419" t="s">
+      <c r="K68" s="432"/>
+      <c r="L68" s="433"/>
+      <c r="M68" s="433"/>
+    </row>
+    <row r="69" spans="3:13" x14ac:dyDescent="0.25">
+      <c r="C69" s="423" t="s">
         <v>451</v>
       </c>
-      <c r="D69" s="420"/>
-      <c r="E69" s="420"/>
-      <c r="F69" s="420"/>
-      <c r="G69" s="420"/>
-      <c r="H69" s="420"/>
-      <c r="I69" s="420"/>
-      <c r="J69" s="421"/>
-      <c r="K69" s="428"/>
-      <c r="L69" s="429"/>
-      <c r="M69" s="429"/>
-    </row>
-    <row r="70" spans="3:13" x14ac:dyDescent="0.3">
-      <c r="C70" s="422"/>
-      <c r="D70" s="423"/>
-      <c r="E70" s="423"/>
-      <c r="F70" s="423"/>
-      <c r="G70" s="423"/>
-      <c r="H70" s="423"/>
-      <c r="I70" s="423"/>
-      <c r="J70" s="424"/>
-      <c r="K70" s="428"/>
-      <c r="L70" s="429"/>
-      <c r="M70" s="429"/>
-    </row>
-    <row r="71" spans="3:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C71" s="425"/>
-      <c r="D71" s="426"/>
-      <c r="E71" s="426"/>
-      <c r="F71" s="426"/>
-      <c r="G71" s="426"/>
-      <c r="H71" s="426"/>
-      <c r="I71" s="426"/>
-      <c r="J71" s="427"/>
-      <c r="K71" s="428"/>
-      <c r="L71" s="429"/>
-      <c r="M71" s="429"/>
-    </row>
-    <row r="73" spans="3:13" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="74" spans="3:13" x14ac:dyDescent="0.3">
+      <c r="D69" s="424"/>
+      <c r="E69" s="424"/>
+      <c r="F69" s="424"/>
+      <c r="G69" s="424"/>
+      <c r="H69" s="424"/>
+      <c r="I69" s="424"/>
+      <c r="J69" s="425"/>
+      <c r="K69" s="432"/>
+      <c r="L69" s="433"/>
+      <c r="M69" s="433"/>
+    </row>
+    <row r="70" spans="3:13" x14ac:dyDescent="0.25">
+      <c r="C70" s="426"/>
+      <c r="D70" s="427"/>
+      <c r="E70" s="427"/>
+      <c r="F70" s="427"/>
+      <c r="G70" s="427"/>
+      <c r="H70" s="427"/>
+      <c r="I70" s="427"/>
+      <c r="J70" s="428"/>
+      <c r="K70" s="432"/>
+      <c r="L70" s="433"/>
+      <c r="M70" s="433"/>
+    </row>
+    <row r="71" spans="3:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C71" s="429"/>
+      <c r="D71" s="430"/>
+      <c r="E71" s="430"/>
+      <c r="F71" s="430"/>
+      <c r="G71" s="430"/>
+      <c r="H71" s="430"/>
+      <c r="I71" s="430"/>
+      <c r="J71" s="431"/>
+      <c r="K71" s="432"/>
+      <c r="L71" s="433"/>
+      <c r="M71" s="433"/>
+    </row>
+    <row r="73" spans="3:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="74" spans="3:13" x14ac:dyDescent="0.25">
       <c r="C74" s="325" t="s">
         <v>158</v>
       </c>
@@ -18363,7 +18420,7 @@
       <c r="I74" s="237"/>
       <c r="J74" s="238"/>
     </row>
-    <row r="75" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="75" spans="3:13" x14ac:dyDescent="0.25">
       <c r="C75" s="327"/>
       <c r="D75" s="328"/>
       <c r="E75" s="240"/>
@@ -18378,7 +18435,7 @@
       </c>
       <c r="J75" s="60"/>
     </row>
-    <row r="76" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="76" spans="3:13" x14ac:dyDescent="0.25">
       <c r="C76" s="327" t="s">
         <v>159</v>
       </c>
@@ -18392,13 +18449,13 @@
       <c r="G76" s="33" t="s">
         <v>164</v>
       </c>
-      <c r="H76" s="417">
+      <c r="H76" s="421">
         <v>119</v>
       </c>
-      <c r="I76" s="417"/>
-      <c r="J76" s="418"/>
-    </row>
-    <row r="77" spans="3:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="I76" s="421"/>
+      <c r="J76" s="422"/>
+    </row>
+    <row r="77" spans="3:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C77" s="327" t="s">
         <v>162</v>
       </c>
@@ -18410,40 +18467,40 @@
       <c r="I77" s="33"/>
       <c r="J77" s="61"/>
     </row>
-    <row r="78" spans="3:13" x14ac:dyDescent="0.3">
-      <c r="C78" s="419" t="s">
+    <row r="78" spans="3:13" x14ac:dyDescent="0.25">
+      <c r="C78" s="423" t="s">
         <v>452</v>
       </c>
-      <c r="D78" s="420"/>
-      <c r="E78" s="420"/>
-      <c r="F78" s="420"/>
-      <c r="G78" s="420"/>
-      <c r="H78" s="420"/>
-      <c r="I78" s="420"/>
-      <c r="J78" s="421"/>
-    </row>
-    <row r="79" spans="3:13" x14ac:dyDescent="0.3">
-      <c r="C79" s="422"/>
-      <c r="D79" s="423"/>
-      <c r="E79" s="423"/>
-      <c r="F79" s="423"/>
-      <c r="G79" s="423"/>
-      <c r="H79" s="423"/>
-      <c r="I79" s="423"/>
-      <c r="J79" s="424"/>
-    </row>
-    <row r="80" spans="3:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C80" s="425"/>
-      <c r="D80" s="426"/>
-      <c r="E80" s="426"/>
-      <c r="F80" s="426"/>
-      <c r="G80" s="426"/>
-      <c r="H80" s="426"/>
-      <c r="I80" s="426"/>
-      <c r="J80" s="427"/>
-    </row>
-    <row r="82" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="83" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="D78" s="424"/>
+      <c r="E78" s="424"/>
+      <c r="F78" s="424"/>
+      <c r="G78" s="424"/>
+      <c r="H78" s="424"/>
+      <c r="I78" s="424"/>
+      <c r="J78" s="425"/>
+    </row>
+    <row r="79" spans="3:13" x14ac:dyDescent="0.25">
+      <c r="C79" s="426"/>
+      <c r="D79" s="427"/>
+      <c r="E79" s="427"/>
+      <c r="F79" s="427"/>
+      <c r="G79" s="427"/>
+      <c r="H79" s="427"/>
+      <c r="I79" s="427"/>
+      <c r="J79" s="428"/>
+    </row>
+    <row r="80" spans="3:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C80" s="429"/>
+      <c r="D80" s="430"/>
+      <c r="E80" s="430"/>
+      <c r="F80" s="430"/>
+      <c r="G80" s="430"/>
+      <c r="H80" s="430"/>
+      <c r="I80" s="430"/>
+      <c r="J80" s="431"/>
+    </row>
+    <row r="82" spans="3:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="83" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C83" s="330" t="s">
         <v>158</v>
       </c>
@@ -18457,7 +18514,7 @@
       <c r="I83" s="237"/>
       <c r="J83" s="238"/>
     </row>
-    <row r="84" spans="3:10" x14ac:dyDescent="0.3">
+    <row r="84" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C84" s="332"/>
       <c r="D84" s="333"/>
       <c r="E84" s="240"/>
@@ -18472,7 +18529,7 @@
       </c>
       <c r="J84" s="60"/>
     </row>
-    <row r="85" spans="3:10" x14ac:dyDescent="0.3">
+    <row r="85" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C85" s="332" t="s">
         <v>159</v>
       </c>
@@ -18486,13 +18543,13 @@
       <c r="G85" s="33" t="s">
         <v>164</v>
       </c>
-      <c r="H85" s="417">
+      <c r="H85" s="421">
         <v>60</v>
       </c>
-      <c r="I85" s="417"/>
-      <c r="J85" s="418"/>
-    </row>
-    <row r="86" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="I85" s="421"/>
+      <c r="J85" s="422"/>
+    </row>
+    <row r="86" spans="3:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C86" s="332" t="s">
         <v>162</v>
       </c>
@@ -18504,40 +18561,40 @@
       <c r="I86" s="33"/>
       <c r="J86" s="61"/>
     </row>
-    <row r="87" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C87" s="419" t="s">
+    <row r="87" spans="3:10" x14ac:dyDescent="0.25">
+      <c r="C87" s="423" t="s">
         <v>453</v>
       </c>
-      <c r="D87" s="420"/>
-      <c r="E87" s="420"/>
-      <c r="F87" s="420"/>
-      <c r="G87" s="420"/>
-      <c r="H87" s="420"/>
-      <c r="I87" s="420"/>
-      <c r="J87" s="421"/>
-    </row>
-    <row r="88" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C88" s="422"/>
-      <c r="D88" s="423"/>
-      <c r="E88" s="423"/>
-      <c r="F88" s="423"/>
-      <c r="G88" s="423"/>
-      <c r="H88" s="423"/>
-      <c r="I88" s="423"/>
-      <c r="J88" s="424"/>
-    </row>
-    <row r="89" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C89" s="425"/>
-      <c r="D89" s="426"/>
-      <c r="E89" s="426"/>
-      <c r="F89" s="426"/>
-      <c r="G89" s="426"/>
-      <c r="H89" s="426"/>
-      <c r="I89" s="426"/>
-      <c r="J89" s="427"/>
-    </row>
-    <row r="91" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="92" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="D87" s="424"/>
+      <c r="E87" s="424"/>
+      <c r="F87" s="424"/>
+      <c r="G87" s="424"/>
+      <c r="H87" s="424"/>
+      <c r="I87" s="424"/>
+      <c r="J87" s="425"/>
+    </row>
+    <row r="88" spans="3:10" x14ac:dyDescent="0.25">
+      <c r="C88" s="426"/>
+      <c r="D88" s="427"/>
+      <c r="E88" s="427"/>
+      <c r="F88" s="427"/>
+      <c r="G88" s="427"/>
+      <c r="H88" s="427"/>
+      <c r="I88" s="427"/>
+      <c r="J88" s="428"/>
+    </row>
+    <row r="89" spans="3:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C89" s="429"/>
+      <c r="D89" s="430"/>
+      <c r="E89" s="430"/>
+      <c r="F89" s="430"/>
+      <c r="G89" s="430"/>
+      <c r="H89" s="430"/>
+      <c r="I89" s="430"/>
+      <c r="J89" s="431"/>
+    </row>
+    <row r="91" spans="3:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="92" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C92" s="343" t="s">
         <v>158</v>
       </c>
@@ -18551,7 +18608,7 @@
       <c r="I92" s="237"/>
       <c r="J92" s="238"/>
     </row>
-    <row r="93" spans="3:10" x14ac:dyDescent="0.3">
+    <row r="93" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C93" s="345"/>
       <c r="D93" s="346"/>
       <c r="E93" s="240"/>
@@ -18566,7 +18623,7 @@
       </c>
       <c r="J93" s="60"/>
     </row>
-    <row r="94" spans="3:10" x14ac:dyDescent="0.3">
+    <row r="94" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C94" s="345" t="s">
         <v>159</v>
       </c>
@@ -18580,13 +18637,13 @@
       <c r="G94" s="33" t="s">
         <v>164</v>
       </c>
-      <c r="H94" s="417">
+      <c r="H94" s="421">
         <v>105</v>
       </c>
-      <c r="I94" s="417"/>
-      <c r="J94" s="418"/>
-    </row>
-    <row r="95" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="I94" s="421"/>
+      <c r="J94" s="422"/>
+    </row>
+    <row r="95" spans="3:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C95" s="345" t="s">
         <v>162</v>
       </c>
@@ -18598,40 +18655,40 @@
       <c r="I95" s="33"/>
       <c r="J95" s="61"/>
     </row>
-    <row r="96" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C96" s="419" t="s">
+    <row r="96" spans="3:10" x14ac:dyDescent="0.25">
+      <c r="C96" s="423" t="s">
         <v>470</v>
       </c>
-      <c r="D96" s="420"/>
-      <c r="E96" s="420"/>
-      <c r="F96" s="420"/>
-      <c r="G96" s="420"/>
-      <c r="H96" s="420"/>
-      <c r="I96" s="420"/>
-      <c r="J96" s="421"/>
-    </row>
-    <row r="97" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C97" s="422"/>
-      <c r="D97" s="423"/>
-      <c r="E97" s="423"/>
-      <c r="F97" s="423"/>
-      <c r="G97" s="423"/>
-      <c r="H97" s="423"/>
-      <c r="I97" s="423"/>
-      <c r="J97" s="424"/>
-    </row>
-    <row r="98" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C98" s="425"/>
-      <c r="D98" s="426"/>
-      <c r="E98" s="426"/>
-      <c r="F98" s="426"/>
-      <c r="G98" s="426"/>
-      <c r="H98" s="426"/>
-      <c r="I98" s="426"/>
-      <c r="J98" s="427"/>
-    </row>
-    <row r="101" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="102" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="D96" s="424"/>
+      <c r="E96" s="424"/>
+      <c r="F96" s="424"/>
+      <c r="G96" s="424"/>
+      <c r="H96" s="424"/>
+      <c r="I96" s="424"/>
+      <c r="J96" s="425"/>
+    </row>
+    <row r="97" spans="3:10" x14ac:dyDescent="0.25">
+      <c r="C97" s="426"/>
+      <c r="D97" s="427"/>
+      <c r="E97" s="427"/>
+      <c r="F97" s="427"/>
+      <c r="G97" s="427"/>
+      <c r="H97" s="427"/>
+      <c r="I97" s="427"/>
+      <c r="J97" s="428"/>
+    </row>
+    <row r="98" spans="3:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C98" s="429"/>
+      <c r="D98" s="430"/>
+      <c r="E98" s="430"/>
+      <c r="F98" s="430"/>
+      <c r="G98" s="430"/>
+      <c r="H98" s="430"/>
+      <c r="I98" s="430"/>
+      <c r="J98" s="431"/>
+    </row>
+    <row r="101" spans="3:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="102" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C102" s="334" t="s">
         <v>158</v>
       </c>
@@ -18645,7 +18702,7 @@
       <c r="I102" s="237"/>
       <c r="J102" s="238"/>
     </row>
-    <row r="103" spans="3:10" x14ac:dyDescent="0.3">
+    <row r="103" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C103" s="336"/>
       <c r="D103" s="337"/>
       <c r="E103" s="240"/>
@@ -18660,7 +18717,7 @@
       </c>
       <c r="J103" s="60"/>
     </row>
-    <row r="104" spans="3:10" x14ac:dyDescent="0.3">
+    <row r="104" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C104" s="336" t="s">
         <v>159</v>
       </c>
@@ -18674,13 +18731,13 @@
       <c r="G104" s="33" t="s">
         <v>164</v>
       </c>
-      <c r="H104" s="417" t="s">
+      <c r="H104" s="421" t="s">
         <v>454</v>
       </c>
-      <c r="I104" s="417"/>
-      <c r="J104" s="418"/>
-    </row>
-    <row r="105" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="I104" s="421"/>
+      <c r="J104" s="422"/>
+    </row>
+    <row r="105" spans="3:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C105" s="336" t="s">
         <v>162</v>
       </c>
@@ -18692,40 +18749,40 @@
       <c r="I105" s="33"/>
       <c r="J105" s="61"/>
     </row>
-    <row r="106" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C106" s="419" t="s">
+    <row r="106" spans="3:10" x14ac:dyDescent="0.25">
+      <c r="C106" s="423" t="s">
         <v>455</v>
       </c>
-      <c r="D106" s="420"/>
-      <c r="E106" s="420"/>
-      <c r="F106" s="420"/>
-      <c r="G106" s="420"/>
-      <c r="H106" s="420"/>
-      <c r="I106" s="420"/>
-      <c r="J106" s="421"/>
-    </row>
-    <row r="107" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C107" s="422"/>
-      <c r="D107" s="423"/>
-      <c r="E107" s="423"/>
-      <c r="F107" s="423"/>
-      <c r="G107" s="423"/>
-      <c r="H107" s="423"/>
-      <c r="I107" s="423"/>
-      <c r="J107" s="424"/>
-    </row>
-    <row r="108" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C108" s="425"/>
-      <c r="D108" s="426"/>
-      <c r="E108" s="426"/>
-      <c r="F108" s="426"/>
-      <c r="G108" s="426"/>
-      <c r="H108" s="426"/>
-      <c r="I108" s="426"/>
-      <c r="J108" s="427"/>
-    </row>
-    <row r="110" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="111" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="D106" s="424"/>
+      <c r="E106" s="424"/>
+      <c r="F106" s="424"/>
+      <c r="G106" s="424"/>
+      <c r="H106" s="424"/>
+      <c r="I106" s="424"/>
+      <c r="J106" s="425"/>
+    </row>
+    <row r="107" spans="3:10" x14ac:dyDescent="0.25">
+      <c r="C107" s="426"/>
+      <c r="D107" s="427"/>
+      <c r="E107" s="427"/>
+      <c r="F107" s="427"/>
+      <c r="G107" s="427"/>
+      <c r="H107" s="427"/>
+      <c r="I107" s="427"/>
+      <c r="J107" s="428"/>
+    </row>
+    <row r="108" spans="3:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C108" s="429"/>
+      <c r="D108" s="430"/>
+      <c r="E108" s="430"/>
+      <c r="F108" s="430"/>
+      <c r="G108" s="430"/>
+      <c r="H108" s="430"/>
+      <c r="I108" s="430"/>
+      <c r="J108" s="431"/>
+    </row>
+    <row r="110" spans="3:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="111" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C111" s="284" t="s">
         <v>158</v>
       </c>
@@ -18739,7 +18796,7 @@
       <c r="I111" s="237"/>
       <c r="J111" s="238"/>
     </row>
-    <row r="112" spans="3:10" x14ac:dyDescent="0.3">
+    <row r="112" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C112" s="286"/>
       <c r="D112" s="287"/>
       <c r="E112" s="240"/>
@@ -18754,7 +18811,7 @@
       </c>
       <c r="J112" s="60"/>
     </row>
-    <row r="113" spans="3:10" x14ac:dyDescent="0.3">
+    <row r="113" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C113" s="286" t="s">
         <v>159</v>
       </c>
@@ -18768,13 +18825,13 @@
       <c r="G113" s="33" t="s">
         <v>164</v>
       </c>
-      <c r="H113" s="417">
+      <c r="H113" s="421">
         <v>36</v>
       </c>
-      <c r="I113" s="417"/>
-      <c r="J113" s="418"/>
-    </row>
-    <row r="114" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="I113" s="421"/>
+      <c r="J113" s="422"/>
+    </row>
+    <row r="114" spans="3:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C114" s="286" t="s">
         <v>162</v>
       </c>
@@ -18786,40 +18843,40 @@
       <c r="I114" s="33"/>
       <c r="J114" s="61"/>
     </row>
-    <row r="115" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C115" s="419" t="s">
+    <row r="115" spans="3:10" x14ac:dyDescent="0.25">
+      <c r="C115" s="423" t="s">
         <v>456</v>
       </c>
-      <c r="D115" s="420"/>
-      <c r="E115" s="420"/>
-      <c r="F115" s="420"/>
-      <c r="G115" s="420"/>
-      <c r="H115" s="420"/>
-      <c r="I115" s="420"/>
-      <c r="J115" s="421"/>
-    </row>
-    <row r="116" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C116" s="422"/>
-      <c r="D116" s="423"/>
-      <c r="E116" s="423"/>
-      <c r="F116" s="423"/>
-      <c r="G116" s="423"/>
-      <c r="H116" s="423"/>
-      <c r="I116" s="423"/>
-      <c r="J116" s="424"/>
-    </row>
-    <row r="117" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C117" s="425"/>
-      <c r="D117" s="426"/>
-      <c r="E117" s="426"/>
-      <c r="F117" s="426"/>
-      <c r="G117" s="426"/>
-      <c r="H117" s="426"/>
-      <c r="I117" s="426"/>
-      <c r="J117" s="427"/>
-    </row>
-    <row r="119" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="120" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="D115" s="424"/>
+      <c r="E115" s="424"/>
+      <c r="F115" s="424"/>
+      <c r="G115" s="424"/>
+      <c r="H115" s="424"/>
+      <c r="I115" s="424"/>
+      <c r="J115" s="425"/>
+    </row>
+    <row r="116" spans="3:10" x14ac:dyDescent="0.25">
+      <c r="C116" s="426"/>
+      <c r="D116" s="427"/>
+      <c r="E116" s="427"/>
+      <c r="F116" s="427"/>
+      <c r="G116" s="427"/>
+      <c r="H116" s="427"/>
+      <c r="I116" s="427"/>
+      <c r="J116" s="428"/>
+    </row>
+    <row r="117" spans="3:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C117" s="429"/>
+      <c r="D117" s="430"/>
+      <c r="E117" s="430"/>
+      <c r="F117" s="430"/>
+      <c r="G117" s="430"/>
+      <c r="H117" s="430"/>
+      <c r="I117" s="430"/>
+      <c r="J117" s="431"/>
+    </row>
+    <row r="119" spans="3:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="120" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C120" s="305" t="s">
         <v>158</v>
       </c>
@@ -18833,7 +18890,7 @@
       <c r="I120" s="237"/>
       <c r="J120" s="238"/>
     </row>
-    <row r="121" spans="3:10" x14ac:dyDescent="0.3">
+    <row r="121" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C121" s="307"/>
       <c r="D121" s="308"/>
       <c r="E121" s="240"/>
@@ -18848,7 +18905,7 @@
       </c>
       <c r="J121" s="60"/>
     </row>
-    <row r="122" spans="3:10" x14ac:dyDescent="0.3">
+    <row r="122" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C122" s="307" t="s">
         <v>159</v>
       </c>
@@ -18862,13 +18919,13 @@
       <c r="G122" s="33" t="s">
         <v>164</v>
       </c>
-      <c r="H122" s="417">
+      <c r="H122" s="421">
         <v>73</v>
       </c>
-      <c r="I122" s="417"/>
-      <c r="J122" s="418"/>
-    </row>
-    <row r="123" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="I122" s="421"/>
+      <c r="J122" s="422"/>
+    </row>
+    <row r="123" spans="3:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C123" s="307" t="s">
         <v>162</v>
       </c>
@@ -18880,40 +18937,40 @@
       <c r="I123" s="33"/>
       <c r="J123" s="61"/>
     </row>
-    <row r="124" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C124" s="419" t="s">
+    <row r="124" spans="3:10" x14ac:dyDescent="0.25">
+      <c r="C124" s="423" t="s">
         <v>457</v>
       </c>
-      <c r="D124" s="420"/>
-      <c r="E124" s="420"/>
-      <c r="F124" s="420"/>
-      <c r="G124" s="420"/>
-      <c r="H124" s="420"/>
-      <c r="I124" s="420"/>
-      <c r="J124" s="421"/>
-    </row>
-    <row r="125" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C125" s="422"/>
-      <c r="D125" s="423"/>
-      <c r="E125" s="423"/>
-      <c r="F125" s="423"/>
-      <c r="G125" s="423"/>
-      <c r="H125" s="423"/>
-      <c r="I125" s="423"/>
-      <c r="J125" s="424"/>
-    </row>
-    <row r="126" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C126" s="425"/>
-      <c r="D126" s="426"/>
-      <c r="E126" s="426"/>
-      <c r="F126" s="426"/>
-      <c r="G126" s="426"/>
-      <c r="H126" s="426"/>
-      <c r="I126" s="426"/>
-      <c r="J126" s="427"/>
-    </row>
-    <row r="128" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="129" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="D124" s="424"/>
+      <c r="E124" s="424"/>
+      <c r="F124" s="424"/>
+      <c r="G124" s="424"/>
+      <c r="H124" s="424"/>
+      <c r="I124" s="424"/>
+      <c r="J124" s="425"/>
+    </row>
+    <row r="125" spans="3:10" x14ac:dyDescent="0.25">
+      <c r="C125" s="426"/>
+      <c r="D125" s="427"/>
+      <c r="E125" s="427"/>
+      <c r="F125" s="427"/>
+      <c r="G125" s="427"/>
+      <c r="H125" s="427"/>
+      <c r="I125" s="427"/>
+      <c r="J125" s="428"/>
+    </row>
+    <row r="126" spans="3:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C126" s="429"/>
+      <c r="D126" s="430"/>
+      <c r="E126" s="430"/>
+      <c r="F126" s="430"/>
+      <c r="G126" s="430"/>
+      <c r="H126" s="430"/>
+      <c r="I126" s="430"/>
+      <c r="J126" s="431"/>
+    </row>
+    <row r="128" spans="3:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="129" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C129" s="339" t="s">
         <v>158</v>
       </c>
@@ -18927,7 +18984,7 @@
       <c r="I129" s="237"/>
       <c r="J129" s="238"/>
     </row>
-    <row r="130" spans="3:10" x14ac:dyDescent="0.3">
+    <row r="130" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C130" s="341"/>
       <c r="D130" s="342"/>
       <c r="E130" s="240"/>
@@ -18942,7 +18999,7 @@
       </c>
       <c r="J130" s="60"/>
     </row>
-    <row r="131" spans="3:10" x14ac:dyDescent="0.3">
+    <row r="131" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C131" s="341" t="s">
         <v>159</v>
       </c>
@@ -18956,13 +19013,13 @@
       <c r="G131" s="33" t="s">
         <v>164</v>
       </c>
-      <c r="H131" s="417">
+      <c r="H131" s="421">
         <v>77</v>
       </c>
-      <c r="I131" s="417"/>
-      <c r="J131" s="418"/>
-    </row>
-    <row r="132" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="I131" s="421"/>
+      <c r="J131" s="422"/>
+    </row>
+    <row r="132" spans="3:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C132" s="341" t="s">
         <v>162</v>
       </c>
@@ -18974,40 +19031,40 @@
       <c r="I132" s="33"/>
       <c r="J132" s="61"/>
     </row>
-    <row r="133" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C133" s="419" t="s">
+    <row r="133" spans="3:10" x14ac:dyDescent="0.25">
+      <c r="C133" s="423" t="s">
         <v>458</v>
       </c>
-      <c r="D133" s="420"/>
-      <c r="E133" s="420"/>
-      <c r="F133" s="420"/>
-      <c r="G133" s="420"/>
-      <c r="H133" s="420"/>
-      <c r="I133" s="420"/>
-      <c r="J133" s="421"/>
-    </row>
-    <row r="134" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C134" s="422"/>
-      <c r="D134" s="423"/>
-      <c r="E134" s="423"/>
-      <c r="F134" s="423"/>
-      <c r="G134" s="423"/>
-      <c r="H134" s="423"/>
-      <c r="I134" s="423"/>
-      <c r="J134" s="424"/>
-    </row>
-    <row r="135" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C135" s="425"/>
-      <c r="D135" s="426"/>
-      <c r="E135" s="426"/>
-      <c r="F135" s="426"/>
-      <c r="G135" s="426"/>
-      <c r="H135" s="426"/>
-      <c r="I135" s="426"/>
-      <c r="J135" s="427"/>
-    </row>
-    <row r="137" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="138" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="D133" s="424"/>
+      <c r="E133" s="424"/>
+      <c r="F133" s="424"/>
+      <c r="G133" s="424"/>
+      <c r="H133" s="424"/>
+      <c r="I133" s="424"/>
+      <c r="J133" s="425"/>
+    </row>
+    <row r="134" spans="3:10" x14ac:dyDescent="0.25">
+      <c r="C134" s="426"/>
+      <c r="D134" s="427"/>
+      <c r="E134" s="427"/>
+      <c r="F134" s="427"/>
+      <c r="G134" s="427"/>
+      <c r="H134" s="427"/>
+      <c r="I134" s="427"/>
+      <c r="J134" s="428"/>
+    </row>
+    <row r="135" spans="3:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C135" s="429"/>
+      <c r="D135" s="430"/>
+      <c r="E135" s="430"/>
+      <c r="F135" s="430"/>
+      <c r="G135" s="430"/>
+      <c r="H135" s="430"/>
+      <c r="I135" s="430"/>
+      <c r="J135" s="431"/>
+    </row>
+    <row r="137" spans="3:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="138" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C138" s="343" t="s">
         <v>158</v>
       </c>
@@ -19021,7 +19078,7 @@
       <c r="I138" s="237"/>
       <c r="J138" s="238"/>
     </row>
-    <row r="139" spans="3:10" x14ac:dyDescent="0.3">
+    <row r="139" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C139" s="345"/>
       <c r="D139" s="346"/>
       <c r="E139" s="240"/>
@@ -19036,7 +19093,7 @@
       </c>
       <c r="J139" s="60"/>
     </row>
-    <row r="140" spans="3:10" x14ac:dyDescent="0.3">
+    <row r="140" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C140" s="345" t="s">
         <v>159</v>
       </c>
@@ -19050,13 +19107,13 @@
       <c r="G140" s="33" t="s">
         <v>164</v>
       </c>
-      <c r="H140" s="417">
+      <c r="H140" s="421">
         <v>61</v>
       </c>
-      <c r="I140" s="417"/>
-      <c r="J140" s="418"/>
-    </row>
-    <row r="141" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="I140" s="421"/>
+      <c r="J140" s="422"/>
+    </row>
+    <row r="141" spans="3:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C141" s="345" t="s">
         <v>162</v>
       </c>
@@ -19068,40 +19125,40 @@
       <c r="I141" s="33"/>
       <c r="J141" s="61"/>
     </row>
-    <row r="142" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C142" s="419" t="s">
+    <row r="142" spans="3:10" x14ac:dyDescent="0.25">
+      <c r="C142" s="423" t="s">
         <v>459</v>
       </c>
-      <c r="D142" s="420"/>
-      <c r="E142" s="420"/>
-      <c r="F142" s="420"/>
-      <c r="G142" s="420"/>
-      <c r="H142" s="420"/>
-      <c r="I142" s="420"/>
-      <c r="J142" s="421"/>
-    </row>
-    <row r="143" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C143" s="422"/>
-      <c r="D143" s="423"/>
-      <c r="E143" s="423"/>
-      <c r="F143" s="423"/>
-      <c r="G143" s="423"/>
-      <c r="H143" s="423"/>
-      <c r="I143" s="423"/>
-      <c r="J143" s="424"/>
-    </row>
-    <row r="144" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C144" s="425"/>
-      <c r="D144" s="426"/>
-      <c r="E144" s="426"/>
-      <c r="F144" s="426"/>
-      <c r="G144" s="426"/>
-      <c r="H144" s="426"/>
-      <c r="I144" s="426"/>
-      <c r="J144" s="427"/>
-    </row>
-    <row r="146" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="147" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="D142" s="424"/>
+      <c r="E142" s="424"/>
+      <c r="F142" s="424"/>
+      <c r="G142" s="424"/>
+      <c r="H142" s="424"/>
+      <c r="I142" s="424"/>
+      <c r="J142" s="425"/>
+    </row>
+    <row r="143" spans="3:10" x14ac:dyDescent="0.25">
+      <c r="C143" s="426"/>
+      <c r="D143" s="427"/>
+      <c r="E143" s="427"/>
+      <c r="F143" s="427"/>
+      <c r="G143" s="427"/>
+      <c r="H143" s="427"/>
+      <c r="I143" s="427"/>
+      <c r="J143" s="428"/>
+    </row>
+    <row r="144" spans="3:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C144" s="429"/>
+      <c r="D144" s="430"/>
+      <c r="E144" s="430"/>
+      <c r="F144" s="430"/>
+      <c r="G144" s="430"/>
+      <c r="H144" s="430"/>
+      <c r="I144" s="430"/>
+      <c r="J144" s="431"/>
+    </row>
+    <row r="146" spans="3:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="147" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C147" s="343" t="s">
         <v>158</v>
       </c>
@@ -19115,7 +19172,7 @@
       <c r="I147" s="237"/>
       <c r="J147" s="238"/>
     </row>
-    <row r="148" spans="3:10" x14ac:dyDescent="0.3">
+    <row r="148" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C148" s="345"/>
       <c r="D148" s="346"/>
       <c r="E148" s="240"/>
@@ -19130,7 +19187,7 @@
       </c>
       <c r="J148" s="60"/>
     </row>
-    <row r="149" spans="3:10" x14ac:dyDescent="0.3">
+    <row r="149" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C149" s="345" t="s">
         <v>159</v>
       </c>
@@ -19144,13 +19201,13 @@
       <c r="G149" s="33" t="s">
         <v>164</v>
       </c>
-      <c r="H149" s="417">
+      <c r="H149" s="421">
         <v>88</v>
       </c>
-      <c r="I149" s="417"/>
-      <c r="J149" s="418"/>
-    </row>
-    <row r="150" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="I149" s="421"/>
+      <c r="J149" s="422"/>
+    </row>
+    <row r="150" spans="3:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C150" s="345" t="s">
         <v>162</v>
       </c>
@@ -19162,40 +19219,40 @@
       <c r="I150" s="33"/>
       <c r="J150" s="61"/>
     </row>
-    <row r="151" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C151" s="419" t="s">
+    <row r="151" spans="3:10" x14ac:dyDescent="0.25">
+      <c r="C151" s="423" t="s">
         <v>460</v>
       </c>
-      <c r="D151" s="420"/>
-      <c r="E151" s="420"/>
-      <c r="F151" s="420"/>
-      <c r="G151" s="420"/>
-      <c r="H151" s="420"/>
-      <c r="I151" s="420"/>
-      <c r="J151" s="421"/>
-    </row>
-    <row r="152" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C152" s="422"/>
-      <c r="D152" s="423"/>
-      <c r="E152" s="423"/>
-      <c r="F152" s="423"/>
-      <c r="G152" s="423"/>
-      <c r="H152" s="423"/>
-      <c r="I152" s="423"/>
-      <c r="J152" s="424"/>
-    </row>
-    <row r="153" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C153" s="425"/>
-      <c r="D153" s="426"/>
-      <c r="E153" s="426"/>
-      <c r="F153" s="426"/>
-      <c r="G153" s="426"/>
-      <c r="H153" s="426"/>
-      <c r="I153" s="426"/>
-      <c r="J153" s="427"/>
-    </row>
-    <row r="155" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="156" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="D151" s="424"/>
+      <c r="E151" s="424"/>
+      <c r="F151" s="424"/>
+      <c r="G151" s="424"/>
+      <c r="H151" s="424"/>
+      <c r="I151" s="424"/>
+      <c r="J151" s="425"/>
+    </row>
+    <row r="152" spans="3:10" x14ac:dyDescent="0.25">
+      <c r="C152" s="426"/>
+      <c r="D152" s="427"/>
+      <c r="E152" s="427"/>
+      <c r="F152" s="427"/>
+      <c r="G152" s="427"/>
+      <c r="H152" s="427"/>
+      <c r="I152" s="427"/>
+      <c r="J152" s="428"/>
+    </row>
+    <row r="153" spans="3:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C153" s="429"/>
+      <c r="D153" s="430"/>
+      <c r="E153" s="430"/>
+      <c r="F153" s="430"/>
+      <c r="G153" s="430"/>
+      <c r="H153" s="430"/>
+      <c r="I153" s="430"/>
+      <c r="J153" s="431"/>
+    </row>
+    <row r="155" spans="3:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="156" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C156" s="343" t="s">
         <v>158</v>
       </c>
@@ -19209,7 +19266,7 @@
       <c r="I156" s="237"/>
       <c r="J156" s="238"/>
     </row>
-    <row r="157" spans="3:10" x14ac:dyDescent="0.3">
+    <row r="157" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C157" s="345"/>
       <c r="D157" s="346"/>
       <c r="E157" s="240"/>
@@ -19224,7 +19281,7 @@
       </c>
       <c r="J157" s="60"/>
     </row>
-    <row r="158" spans="3:10" x14ac:dyDescent="0.3">
+    <row r="158" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C158" s="345" t="s">
         <v>159</v>
       </c>
@@ -19238,13 +19295,13 @@
       <c r="G158" s="33" t="s">
         <v>164</v>
       </c>
-      <c r="H158" s="417">
+      <c r="H158" s="421">
         <v>86</v>
       </c>
-      <c r="I158" s="417"/>
-      <c r="J158" s="418"/>
-    </row>
-    <row r="159" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="I158" s="421"/>
+      <c r="J158" s="422"/>
+    </row>
+    <row r="159" spans="3:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C159" s="345" t="s">
         <v>162</v>
       </c>
@@ -19256,40 +19313,40 @@
       <c r="I159" s="33"/>
       <c r="J159" s="61"/>
     </row>
-    <row r="160" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C160" s="419" t="s">
+    <row r="160" spans="3:10" x14ac:dyDescent="0.25">
+      <c r="C160" s="423" t="s">
         <v>461</v>
       </c>
-      <c r="D160" s="420"/>
-      <c r="E160" s="420"/>
-      <c r="F160" s="420"/>
-      <c r="G160" s="420"/>
-      <c r="H160" s="420"/>
-      <c r="I160" s="420"/>
-      <c r="J160" s="421"/>
-    </row>
-    <row r="161" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C161" s="422"/>
-      <c r="D161" s="423"/>
-      <c r="E161" s="423"/>
-      <c r="F161" s="423"/>
-      <c r="G161" s="423"/>
-      <c r="H161" s="423"/>
-      <c r="I161" s="423"/>
-      <c r="J161" s="424"/>
-    </row>
-    <row r="162" spans="3:10" ht="40.200000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C162" s="425"/>
-      <c r="D162" s="426"/>
-      <c r="E162" s="426"/>
-      <c r="F162" s="426"/>
-      <c r="G162" s="426"/>
-      <c r="H162" s="426"/>
-      <c r="I162" s="426"/>
-      <c r="J162" s="427"/>
-    </row>
-    <row r="164" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="165" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="D160" s="424"/>
+      <c r="E160" s="424"/>
+      <c r="F160" s="424"/>
+      <c r="G160" s="424"/>
+      <c r="H160" s="424"/>
+      <c r="I160" s="424"/>
+      <c r="J160" s="425"/>
+    </row>
+    <row r="161" spans="3:10" x14ac:dyDescent="0.25">
+      <c r="C161" s="426"/>
+      <c r="D161" s="427"/>
+      <c r="E161" s="427"/>
+      <c r="F161" s="427"/>
+      <c r="G161" s="427"/>
+      <c r="H161" s="427"/>
+      <c r="I161" s="427"/>
+      <c r="J161" s="428"/>
+    </row>
+    <row r="162" spans="3:10" ht="40.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C162" s="429"/>
+      <c r="D162" s="430"/>
+      <c r="E162" s="430"/>
+      <c r="F162" s="430"/>
+      <c r="G162" s="430"/>
+      <c r="H162" s="430"/>
+      <c r="I162" s="430"/>
+      <c r="J162" s="431"/>
+    </row>
+    <row r="164" spans="3:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="165" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C165" s="343" t="s">
         <v>158</v>
       </c>
@@ -19303,7 +19360,7 @@
       <c r="I165" s="237"/>
       <c r="J165" s="238"/>
     </row>
-    <row r="166" spans="3:10" x14ac:dyDescent="0.3">
+    <row r="166" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C166" s="345"/>
       <c r="D166" s="346"/>
       <c r="E166" s="240"/>
@@ -19318,7 +19375,7 @@
       </c>
       <c r="J166" s="60"/>
     </row>
-    <row r="167" spans="3:10" x14ac:dyDescent="0.3">
+    <row r="167" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C167" s="345" t="s">
         <v>159</v>
       </c>
@@ -19332,13 +19389,13 @@
       <c r="G167" s="33" t="s">
         <v>164</v>
       </c>
-      <c r="H167" s="417" t="s">
+      <c r="H167" s="421" t="s">
         <v>462</v>
       </c>
-      <c r="I167" s="417"/>
-      <c r="J167" s="418"/>
-    </row>
-    <row r="168" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="I167" s="421"/>
+      <c r="J167" s="422"/>
+    </row>
+    <row r="168" spans="3:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C168" s="345" t="s">
         <v>162</v>
       </c>
@@ -19350,40 +19407,40 @@
       <c r="I168" s="33"/>
       <c r="J168" s="61"/>
     </row>
-    <row r="169" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C169" s="419" t="s">
+    <row r="169" spans="3:10" x14ac:dyDescent="0.25">
+      <c r="C169" s="423" t="s">
         <v>463</v>
       </c>
-      <c r="D169" s="420"/>
-      <c r="E169" s="420"/>
-      <c r="F169" s="420"/>
-      <c r="G169" s="420"/>
-      <c r="H169" s="420"/>
-      <c r="I169" s="420"/>
-      <c r="J169" s="421"/>
-    </row>
-    <row r="170" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C170" s="422"/>
-      <c r="D170" s="423"/>
-      <c r="E170" s="423"/>
-      <c r="F170" s="423"/>
-      <c r="G170" s="423"/>
-      <c r="H170" s="423"/>
-      <c r="I170" s="423"/>
-      <c r="J170" s="424"/>
-    </row>
-    <row r="171" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C171" s="425"/>
-      <c r="D171" s="426"/>
-      <c r="E171" s="426"/>
-      <c r="F171" s="426"/>
-      <c r="G171" s="426"/>
-      <c r="H171" s="426"/>
-      <c r="I171" s="426"/>
-      <c r="J171" s="427"/>
-    </row>
-    <row r="173" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="174" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="D169" s="424"/>
+      <c r="E169" s="424"/>
+      <c r="F169" s="424"/>
+      <c r="G169" s="424"/>
+      <c r="H169" s="424"/>
+      <c r="I169" s="424"/>
+      <c r="J169" s="425"/>
+    </row>
+    <row r="170" spans="3:10" x14ac:dyDescent="0.25">
+      <c r="C170" s="426"/>
+      <c r="D170" s="427"/>
+      <c r="E170" s="427"/>
+      <c r="F170" s="427"/>
+      <c r="G170" s="427"/>
+      <c r="H170" s="427"/>
+      <c r="I170" s="427"/>
+      <c r="J170" s="428"/>
+    </row>
+    <row r="171" spans="3:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C171" s="429"/>
+      <c r="D171" s="430"/>
+      <c r="E171" s="430"/>
+      <c r="F171" s="430"/>
+      <c r="G171" s="430"/>
+      <c r="H171" s="430"/>
+      <c r="I171" s="430"/>
+      <c r="J171" s="431"/>
+    </row>
+    <row r="173" spans="3:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="174" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C174" s="343" t="s">
         <v>158</v>
       </c>
@@ -19397,7 +19454,7 @@
       <c r="I174" s="237"/>
       <c r="J174" s="238"/>
     </row>
-    <row r="175" spans="3:10" x14ac:dyDescent="0.3">
+    <row r="175" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C175" s="345"/>
       <c r="D175" s="346"/>
       <c r="E175" s="240"/>
@@ -19412,7 +19469,7 @@
       </c>
       <c r="J175" s="60"/>
     </row>
-    <row r="176" spans="3:10" x14ac:dyDescent="0.3">
+    <row r="176" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C176" s="345" t="s">
         <v>159</v>
       </c>
@@ -19426,13 +19483,13 @@
       <c r="G176" s="33" t="s">
         <v>164</v>
       </c>
-      <c r="H176" s="417">
+      <c r="H176" s="421">
         <v>102</v>
       </c>
-      <c r="I176" s="417"/>
-      <c r="J176" s="418"/>
-    </row>
-    <row r="177" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="I176" s="421"/>
+      <c r="J176" s="422"/>
+    </row>
+    <row r="177" spans="3:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C177" s="345" t="s">
         <v>162</v>
       </c>
@@ -19444,40 +19501,40 @@
       <c r="I177" s="33"/>
       <c r="J177" s="61"/>
     </row>
-    <row r="178" spans="3:10" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C178" s="419" t="s">
+    <row r="178" spans="3:10" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C178" s="423" t="s">
         <v>464</v>
       </c>
-      <c r="D178" s="420"/>
-      <c r="E178" s="420"/>
-      <c r="F178" s="420"/>
-      <c r="G178" s="420"/>
-      <c r="H178" s="420"/>
-      <c r="I178" s="420"/>
-      <c r="J178" s="421"/>
-    </row>
-    <row r="179" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C179" s="422"/>
-      <c r="D179" s="423"/>
-      <c r="E179" s="423"/>
-      <c r="F179" s="423"/>
-      <c r="G179" s="423"/>
-      <c r="H179" s="423"/>
-      <c r="I179" s="423"/>
-      <c r="J179" s="424"/>
-    </row>
-    <row r="180" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C180" s="425"/>
-      <c r="D180" s="426"/>
-      <c r="E180" s="426"/>
-      <c r="F180" s="426"/>
-      <c r="G180" s="426"/>
-      <c r="H180" s="426"/>
-      <c r="I180" s="426"/>
-      <c r="J180" s="427"/>
-    </row>
-    <row r="182" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="183" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="D178" s="424"/>
+      <c r="E178" s="424"/>
+      <c r="F178" s="424"/>
+      <c r="G178" s="424"/>
+      <c r="H178" s="424"/>
+      <c r="I178" s="424"/>
+      <c r="J178" s="425"/>
+    </row>
+    <row r="179" spans="3:10" x14ac:dyDescent="0.25">
+      <c r="C179" s="426"/>
+      <c r="D179" s="427"/>
+      <c r="E179" s="427"/>
+      <c r="F179" s="427"/>
+      <c r="G179" s="427"/>
+      <c r="H179" s="427"/>
+      <c r="I179" s="427"/>
+      <c r="J179" s="428"/>
+    </row>
+    <row r="180" spans="3:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C180" s="429"/>
+      <c r="D180" s="430"/>
+      <c r="E180" s="430"/>
+      <c r="F180" s="430"/>
+      <c r="G180" s="430"/>
+      <c r="H180" s="430"/>
+      <c r="I180" s="430"/>
+      <c r="J180" s="431"/>
+    </row>
+    <row r="182" spans="3:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="183" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C183" s="343" t="s">
         <v>158</v>
       </c>
@@ -19491,7 +19548,7 @@
       <c r="I183" s="237"/>
       <c r="J183" s="238"/>
     </row>
-    <row r="184" spans="3:10" x14ac:dyDescent="0.3">
+    <row r="184" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C184" s="345"/>
       <c r="D184" s="346"/>
       <c r="E184" s="240"/>
@@ -19506,7 +19563,7 @@
       </c>
       <c r="J184" s="60"/>
     </row>
-    <row r="185" spans="3:10" x14ac:dyDescent="0.3">
+    <row r="185" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C185" s="345" t="s">
         <v>159</v>
       </c>
@@ -19520,13 +19577,13 @@
       <c r="G185" s="33" t="s">
         <v>164</v>
       </c>
-      <c r="H185" s="417">
+      <c r="H185" s="421">
         <v>130</v>
       </c>
-      <c r="I185" s="417"/>
-      <c r="J185" s="418"/>
-    </row>
-    <row r="186" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="I185" s="421"/>
+      <c r="J185" s="422"/>
+    </row>
+    <row r="186" spans="3:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C186" s="345" t="s">
         <v>162</v>
       </c>
@@ -19538,40 +19595,40 @@
       <c r="I186" s="33"/>
       <c r="J186" s="61"/>
     </row>
-    <row r="187" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C187" s="419" t="s">
+    <row r="187" spans="3:10" x14ac:dyDescent="0.25">
+      <c r="C187" s="423" t="s">
         <v>465</v>
       </c>
-      <c r="D187" s="420"/>
-      <c r="E187" s="420"/>
-      <c r="F187" s="420"/>
-      <c r="G187" s="420"/>
-      <c r="H187" s="420"/>
-      <c r="I187" s="420"/>
-      <c r="J187" s="421"/>
-    </row>
-    <row r="188" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C188" s="422"/>
-      <c r="D188" s="423"/>
-      <c r="E188" s="423"/>
-      <c r="F188" s="423"/>
-      <c r="G188" s="423"/>
-      <c r="H188" s="423"/>
-      <c r="I188" s="423"/>
-      <c r="J188" s="424"/>
-    </row>
-    <row r="189" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C189" s="425"/>
-      <c r="D189" s="426"/>
-      <c r="E189" s="426"/>
-      <c r="F189" s="426"/>
-      <c r="G189" s="426"/>
-      <c r="H189" s="426"/>
-      <c r="I189" s="426"/>
-      <c r="J189" s="427"/>
-    </row>
-    <row r="191" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="192" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="D187" s="424"/>
+      <c r="E187" s="424"/>
+      <c r="F187" s="424"/>
+      <c r="G187" s="424"/>
+      <c r="H187" s="424"/>
+      <c r="I187" s="424"/>
+      <c r="J187" s="425"/>
+    </row>
+    <row r="188" spans="3:10" x14ac:dyDescent="0.25">
+      <c r="C188" s="426"/>
+      <c r="D188" s="427"/>
+      <c r="E188" s="427"/>
+      <c r="F188" s="427"/>
+      <c r="G188" s="427"/>
+      <c r="H188" s="427"/>
+      <c r="I188" s="427"/>
+      <c r="J188" s="428"/>
+    </row>
+    <row r="189" spans="3:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C189" s="429"/>
+      <c r="D189" s="430"/>
+      <c r="E189" s="430"/>
+      <c r="F189" s="430"/>
+      <c r="G189" s="430"/>
+      <c r="H189" s="430"/>
+      <c r="I189" s="430"/>
+      <c r="J189" s="431"/>
+    </row>
+    <row r="191" spans="3:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="192" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C192" s="343" t="s">
         <v>158</v>
       </c>
@@ -19585,7 +19642,7 @@
       <c r="I192" s="237"/>
       <c r="J192" s="238"/>
     </row>
-    <row r="193" spans="3:10" x14ac:dyDescent="0.3">
+    <row r="193" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C193" s="345"/>
       <c r="D193" s="346"/>
       <c r="E193" s="240"/>
@@ -19600,7 +19657,7 @@
       </c>
       <c r="J193" s="60"/>
     </row>
-    <row r="194" spans="3:10" x14ac:dyDescent="0.3">
+    <row r="194" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C194" s="345" t="s">
         <v>159</v>
       </c>
@@ -19614,13 +19671,13 @@
       <c r="G194" s="33" t="s">
         <v>164</v>
       </c>
-      <c r="H194" s="417">
+      <c r="H194" s="421">
         <v>8</v>
       </c>
-      <c r="I194" s="417"/>
-      <c r="J194" s="418"/>
-    </row>
-    <row r="195" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="I194" s="421"/>
+      <c r="J194" s="422"/>
+    </row>
+    <row r="195" spans="3:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C195" s="345" t="s">
         <v>162</v>
       </c>
@@ -19632,40 +19689,40 @@
       <c r="I195" s="33"/>
       <c r="J195" s="61"/>
     </row>
-    <row r="196" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C196" s="419" t="s">
+    <row r="196" spans="3:10" x14ac:dyDescent="0.25">
+      <c r="C196" s="423" t="s">
         <v>468</v>
       </c>
-      <c r="D196" s="420"/>
-      <c r="E196" s="420"/>
-      <c r="F196" s="420"/>
-      <c r="G196" s="420"/>
-      <c r="H196" s="420"/>
-      <c r="I196" s="420"/>
-      <c r="J196" s="421"/>
-    </row>
-    <row r="197" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C197" s="422"/>
-      <c r="D197" s="423"/>
-      <c r="E197" s="423"/>
-      <c r="F197" s="423"/>
-      <c r="G197" s="423"/>
-      <c r="H197" s="423"/>
-      <c r="I197" s="423"/>
-      <c r="J197" s="424"/>
-    </row>
-    <row r="198" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C198" s="425"/>
-      <c r="D198" s="426"/>
-      <c r="E198" s="426"/>
-      <c r="F198" s="426"/>
-      <c r="G198" s="426"/>
-      <c r="H198" s="426"/>
-      <c r="I198" s="426"/>
-      <c r="J198" s="427"/>
-    </row>
-    <row r="200" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="201" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="D196" s="424"/>
+      <c r="E196" s="424"/>
+      <c r="F196" s="424"/>
+      <c r="G196" s="424"/>
+      <c r="H196" s="424"/>
+      <c r="I196" s="424"/>
+      <c r="J196" s="425"/>
+    </row>
+    <row r="197" spans="3:10" x14ac:dyDescent="0.25">
+      <c r="C197" s="426"/>
+      <c r="D197" s="427"/>
+      <c r="E197" s="427"/>
+      <c r="F197" s="427"/>
+      <c r="G197" s="427"/>
+      <c r="H197" s="427"/>
+      <c r="I197" s="427"/>
+      <c r="J197" s="428"/>
+    </row>
+    <row r="198" spans="3:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C198" s="429"/>
+      <c r="D198" s="430"/>
+      <c r="E198" s="430"/>
+      <c r="F198" s="430"/>
+      <c r="G198" s="430"/>
+      <c r="H198" s="430"/>
+      <c r="I198" s="430"/>
+      <c r="J198" s="431"/>
+    </row>
+    <row r="200" spans="3:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="201" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C201" s="343" t="s">
         <v>158</v>
       </c>
@@ -19679,7 +19736,7 @@
       <c r="I201" s="237"/>
       <c r="J201" s="238"/>
     </row>
-    <row r="202" spans="3:10" x14ac:dyDescent="0.3">
+    <row r="202" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C202" s="345"/>
       <c r="D202" s="346"/>
       <c r="E202" s="240"/>
@@ -19694,7 +19751,7 @@
       </c>
       <c r="J202" s="60"/>
     </row>
-    <row r="203" spans="3:10" x14ac:dyDescent="0.3">
+    <row r="203" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C203" s="345" t="s">
         <v>159</v>
       </c>
@@ -19708,13 +19765,13 @@
       <c r="G203" s="33" t="s">
         <v>164</v>
       </c>
-      <c r="H203" s="417">
+      <c r="H203" s="421">
         <v>96</v>
       </c>
-      <c r="I203" s="417"/>
-      <c r="J203" s="418"/>
-    </row>
-    <row r="204" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="I203" s="421"/>
+      <c r="J203" s="422"/>
+    </row>
+    <row r="204" spans="3:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C204" s="345" t="s">
         <v>162</v>
       </c>
@@ -19726,40 +19783,40 @@
       <c r="I204" s="33"/>
       <c r="J204" s="61"/>
     </row>
-    <row r="205" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C205" s="419" t="s">
+    <row r="205" spans="3:10" x14ac:dyDescent="0.25">
+      <c r="C205" s="423" t="s">
         <v>466</v>
       </c>
-      <c r="D205" s="420"/>
-      <c r="E205" s="420"/>
-      <c r="F205" s="420"/>
-      <c r="G205" s="420"/>
-      <c r="H205" s="420"/>
-      <c r="I205" s="420"/>
-      <c r="J205" s="421"/>
-    </row>
-    <row r="206" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C206" s="422"/>
-      <c r="D206" s="423"/>
-      <c r="E206" s="423"/>
-      <c r="F206" s="423"/>
-      <c r="G206" s="423"/>
-      <c r="H206" s="423"/>
-      <c r="I206" s="423"/>
-      <c r="J206" s="424"/>
-    </row>
-    <row r="207" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C207" s="425"/>
-      <c r="D207" s="426"/>
-      <c r="E207" s="426"/>
-      <c r="F207" s="426"/>
-      <c r="G207" s="426"/>
-      <c r="H207" s="426"/>
-      <c r="I207" s="426"/>
-      <c r="J207" s="427"/>
-    </row>
-    <row r="209" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="210" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="D205" s="424"/>
+      <c r="E205" s="424"/>
+      <c r="F205" s="424"/>
+      <c r="G205" s="424"/>
+      <c r="H205" s="424"/>
+      <c r="I205" s="424"/>
+      <c r="J205" s="425"/>
+    </row>
+    <row r="206" spans="3:10" x14ac:dyDescent="0.25">
+      <c r="C206" s="426"/>
+      <c r="D206" s="427"/>
+      <c r="E206" s="427"/>
+      <c r="F206" s="427"/>
+      <c r="G206" s="427"/>
+      <c r="H206" s="427"/>
+      <c r="I206" s="427"/>
+      <c r="J206" s="428"/>
+    </row>
+    <row r="207" spans="3:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C207" s="429"/>
+      <c r="D207" s="430"/>
+      <c r="E207" s="430"/>
+      <c r="F207" s="430"/>
+      <c r="G207" s="430"/>
+      <c r="H207" s="430"/>
+      <c r="I207" s="430"/>
+      <c r="J207" s="431"/>
+    </row>
+    <row r="209" spans="3:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="210" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C210" s="343" t="s">
         <v>158</v>
       </c>
@@ -19773,7 +19830,7 @@
       <c r="I210" s="237"/>
       <c r="J210" s="238"/>
     </row>
-    <row r="211" spans="3:10" x14ac:dyDescent="0.3">
+    <row r="211" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C211" s="345"/>
       <c r="D211" s="346"/>
       <c r="E211" s="240"/>
@@ -19788,7 +19845,7 @@
       </c>
       <c r="J211" s="60"/>
     </row>
-    <row r="212" spans="3:10" x14ac:dyDescent="0.3">
+    <row r="212" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C212" s="345" t="s">
         <v>159</v>
       </c>
@@ -19802,13 +19859,13 @@
       <c r="G212" s="33" t="s">
         <v>164</v>
       </c>
-      <c r="H212" s="417">
+      <c r="H212" s="421">
         <v>138</v>
       </c>
-      <c r="I212" s="417"/>
-      <c r="J212" s="418"/>
-    </row>
-    <row r="213" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="I212" s="421"/>
+      <c r="J212" s="422"/>
+    </row>
+    <row r="213" spans="3:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C213" s="345" t="s">
         <v>162</v>
       </c>
@@ -19820,40 +19877,40 @@
       <c r="I213" s="33"/>
       <c r="J213" s="61"/>
     </row>
-    <row r="214" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C214" s="419" t="s">
+    <row r="214" spans="3:10" x14ac:dyDescent="0.25">
+      <c r="C214" s="423" t="s">
         <v>467</v>
       </c>
-      <c r="D214" s="420"/>
-      <c r="E214" s="420"/>
-      <c r="F214" s="420"/>
-      <c r="G214" s="420"/>
-      <c r="H214" s="420"/>
-      <c r="I214" s="420"/>
-      <c r="J214" s="421"/>
-    </row>
-    <row r="215" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C215" s="422"/>
-      <c r="D215" s="423"/>
-      <c r="E215" s="423"/>
-      <c r="F215" s="423"/>
-      <c r="G215" s="423"/>
-      <c r="H215" s="423"/>
-      <c r="I215" s="423"/>
-      <c r="J215" s="424"/>
-    </row>
-    <row r="216" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C216" s="425"/>
-      <c r="D216" s="426"/>
-      <c r="E216" s="426"/>
-      <c r="F216" s="426"/>
-      <c r="G216" s="426"/>
-      <c r="H216" s="426"/>
-      <c r="I216" s="426"/>
-      <c r="J216" s="427"/>
-    </row>
-    <row r="218" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="219" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="D214" s="424"/>
+      <c r="E214" s="424"/>
+      <c r="F214" s="424"/>
+      <c r="G214" s="424"/>
+      <c r="H214" s="424"/>
+      <c r="I214" s="424"/>
+      <c r="J214" s="425"/>
+    </row>
+    <row r="215" spans="3:10" x14ac:dyDescent="0.25">
+      <c r="C215" s="426"/>
+      <c r="D215" s="427"/>
+      <c r="E215" s="427"/>
+      <c r="F215" s="427"/>
+      <c r="G215" s="427"/>
+      <c r="H215" s="427"/>
+      <c r="I215" s="427"/>
+      <c r="J215" s="428"/>
+    </row>
+    <row r="216" spans="3:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C216" s="429"/>
+      <c r="D216" s="430"/>
+      <c r="E216" s="430"/>
+      <c r="F216" s="430"/>
+      <c r="G216" s="430"/>
+      <c r="H216" s="430"/>
+      <c r="I216" s="430"/>
+      <c r="J216" s="431"/>
+    </row>
+    <row r="218" spans="3:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="219" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C219" s="343" t="s">
         <v>158</v>
       </c>
@@ -19867,7 +19924,7 @@
       <c r="I219" s="237"/>
       <c r="J219" s="238"/>
     </row>
-    <row r="220" spans="3:10" x14ac:dyDescent="0.3">
+    <row r="220" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C220" s="345"/>
       <c r="D220" s="346"/>
       <c r="E220" s="240"/>
@@ -19882,7 +19939,7 @@
       </c>
       <c r="J220" s="60"/>
     </row>
-    <row r="221" spans="3:10" x14ac:dyDescent="0.3">
+    <row r="221" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C221" s="345" t="s">
         <v>159</v>
       </c>
@@ -19896,13 +19953,13 @@
       <c r="G221" s="33" t="s">
         <v>164</v>
       </c>
-      <c r="H221" s="417">
+      <c r="H221" s="421">
         <v>7</v>
       </c>
-      <c r="I221" s="417"/>
-      <c r="J221" s="418"/>
-    </row>
-    <row r="222" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="I221" s="421"/>
+      <c r="J221" s="422"/>
+    </row>
+    <row r="222" spans="3:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C222" s="345" t="s">
         <v>162</v>
       </c>
@@ -19914,51 +19971,241 @@
       <c r="I222" s="33"/>
       <c r="J222" s="61"/>
     </row>
-    <row r="223" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C223" s="419" t="s">
+    <row r="223" spans="3:10" x14ac:dyDescent="0.25">
+      <c r="C223" s="423" t="s">
         <v>469</v>
       </c>
-      <c r="D223" s="420"/>
-      <c r="E223" s="420"/>
-      <c r="F223" s="420"/>
-      <c r="G223" s="420"/>
-      <c r="H223" s="420"/>
-      <c r="I223" s="420"/>
-      <c r="J223" s="421"/>
-    </row>
-    <row r="224" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C224" s="422"/>
-      <c r="D224" s="423"/>
-      <c r="E224" s="423"/>
-      <c r="F224" s="423"/>
-      <c r="G224" s="423"/>
-      <c r="H224" s="423"/>
-      <c r="I224" s="423"/>
-      <c r="J224" s="424"/>
-    </row>
-    <row r="225" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C225" s="425"/>
-      <c r="D225" s="426"/>
-      <c r="E225" s="426"/>
-      <c r="F225" s="426"/>
-      <c r="G225" s="426"/>
-      <c r="H225" s="426"/>
-      <c r="I225" s="426"/>
-      <c r="J225" s="427"/>
+      <c r="D223" s="424"/>
+      <c r="E223" s="424"/>
+      <c r="F223" s="424"/>
+      <c r="G223" s="424"/>
+      <c r="H223" s="424"/>
+      <c r="I223" s="424"/>
+      <c r="J223" s="425"/>
+    </row>
+    <row r="224" spans="3:10" x14ac:dyDescent="0.25">
+      <c r="C224" s="426"/>
+      <c r="D224" s="427"/>
+      <c r="E224" s="427"/>
+      <c r="F224" s="427"/>
+      <c r="G224" s="427"/>
+      <c r="H224" s="427"/>
+      <c r="I224" s="427"/>
+      <c r="J224" s="428"/>
+    </row>
+    <row r="225" spans="3:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C225" s="429"/>
+      <c r="D225" s="430"/>
+      <c r="E225" s="430"/>
+      <c r="F225" s="430"/>
+      <c r="G225" s="430"/>
+      <c r="H225" s="430"/>
+      <c r="I225" s="430"/>
+      <c r="J225" s="431"/>
+    </row>
+    <row r="227" spans="3:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="228" spans="3:10" x14ac:dyDescent="0.25">
+      <c r="C228" s="343" t="s">
+        <v>158</v>
+      </c>
+      <c r="D228" s="344"/>
+      <c r="E228" s="235"/>
+      <c r="F228" s="58"/>
+      <c r="G228" s="58" t="s">
+        <v>163</v>
+      </c>
+      <c r="H228" s="236"/>
+      <c r="I228" s="237"/>
+      <c r="J228" s="238"/>
+    </row>
+    <row r="229" spans="3:10" x14ac:dyDescent="0.25">
+      <c r="C229" s="345"/>
+      <c r="D229" s="346"/>
+      <c r="E229" s="240"/>
+      <c r="F229" s="33"/>
+      <c r="G229" s="33" t="s">
+        <v>328</v>
+      </c>
+      <c r="H229" s="241"/>
+      <c r="I229" s="348">
+        <f>I220+1</f>
+        <v>25</v>
+      </c>
+      <c r="J229" s="349"/>
+    </row>
+    <row r="230" spans="3:10" x14ac:dyDescent="0.25">
+      <c r="C230" s="345" t="s">
+        <v>159</v>
+      </c>
+      <c r="D230" s="346" t="s">
+        <v>160</v>
+      </c>
+      <c r="E230" s="33" t="s">
+        <v>161</v>
+      </c>
+      <c r="F230" s="33"/>
+      <c r="G230" s="33" t="s">
+        <v>164</v>
+      </c>
+      <c r="H230" s="421">
+        <v>70</v>
+      </c>
+      <c r="I230" s="421"/>
+      <c r="J230" s="422"/>
+    </row>
+    <row r="231" spans="3:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C231" s="345" t="s">
+        <v>162</v>
+      </c>
+      <c r="D231" s="346"/>
+      <c r="E231" s="33"/>
+      <c r="F231" s="33"/>
+      <c r="G231" s="33"/>
+      <c r="H231" s="33"/>
+      <c r="I231" s="33"/>
+      <c r="J231" s="61"/>
+    </row>
+    <row r="232" spans="3:10" x14ac:dyDescent="0.25">
+      <c r="C232" s="423" t="s">
+        <v>471</v>
+      </c>
+      <c r="D232" s="424"/>
+      <c r="E232" s="424"/>
+      <c r="F232" s="424"/>
+      <c r="G232" s="424"/>
+      <c r="H232" s="424"/>
+      <c r="I232" s="424"/>
+      <c r="J232" s="425"/>
+    </row>
+    <row r="233" spans="3:10" x14ac:dyDescent="0.25">
+      <c r="C233" s="426"/>
+      <c r="D233" s="427"/>
+      <c r="E233" s="427"/>
+      <c r="F233" s="427"/>
+      <c r="G233" s="427"/>
+      <c r="H233" s="427"/>
+      <c r="I233" s="427"/>
+      <c r="J233" s="428"/>
+    </row>
+    <row r="234" spans="3:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C234" s="429"/>
+      <c r="D234" s="430"/>
+      <c r="E234" s="430"/>
+      <c r="F234" s="430"/>
+      <c r="G234" s="430"/>
+      <c r="H234" s="430"/>
+      <c r="I234" s="430"/>
+      <c r="J234" s="431"/>
+    </row>
+    <row r="236" spans="3:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="237" spans="3:10" x14ac:dyDescent="0.25">
+      <c r="C237" s="343" t="s">
+        <v>158</v>
+      </c>
+      <c r="D237" s="344"/>
+      <c r="E237" s="235"/>
+      <c r="F237" s="58"/>
+      <c r="G237" s="58" t="s">
+        <v>163</v>
+      </c>
+      <c r="H237" s="236"/>
+      <c r="I237" s="237"/>
+      <c r="J237" s="238"/>
+    </row>
+    <row r="238" spans="3:10" x14ac:dyDescent="0.25">
+      <c r="C238" s="345"/>
+      <c r="D238" s="346"/>
+      <c r="E238" s="240"/>
+      <c r="F238" s="33"/>
+      <c r="G238" s="33" t="s">
+        <v>328</v>
+      </c>
+      <c r="H238" s="241"/>
+      <c r="I238" s="350">
+        <f>I229+1</f>
+        <v>26</v>
+      </c>
+      <c r="J238" s="351"/>
+    </row>
+    <row r="239" spans="3:10" x14ac:dyDescent="0.25">
+      <c r="C239" s="345" t="s">
+        <v>159</v>
+      </c>
+      <c r="D239" s="346" t="s">
+        <v>160</v>
+      </c>
+      <c r="E239" s="33" t="s">
+        <v>161</v>
+      </c>
+      <c r="F239" s="33"/>
+      <c r="G239" s="33" t="s">
+        <v>164</v>
+      </c>
+      <c r="H239" s="421">
+        <v>109</v>
+      </c>
+      <c r="I239" s="421"/>
+      <c r="J239" s="422"/>
+    </row>
+    <row r="240" spans="3:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C240" s="345" t="s">
+        <v>162</v>
+      </c>
+      <c r="D240" s="346"/>
+      <c r="E240" s="33"/>
+      <c r="F240" s="33"/>
+      <c r="G240" s="33"/>
+      <c r="H240" s="33"/>
+      <c r="I240" s="33"/>
+      <c r="J240" s="61"/>
+    </row>
+    <row r="241" spans="3:10" x14ac:dyDescent="0.25">
+      <c r="C241" s="423" t="s">
+        <v>472</v>
+      </c>
+      <c r="D241" s="424"/>
+      <c r="E241" s="424"/>
+      <c r="F241" s="424"/>
+      <c r="G241" s="424"/>
+      <c r="H241" s="424"/>
+      <c r="I241" s="424"/>
+      <c r="J241" s="425"/>
+    </row>
+    <row r="242" spans="3:10" x14ac:dyDescent="0.25">
+      <c r="C242" s="426"/>
+      <c r="D242" s="427"/>
+      <c r="E242" s="427"/>
+      <c r="F242" s="427"/>
+      <c r="G242" s="427"/>
+      <c r="H242" s="427"/>
+      <c r="I242" s="427"/>
+      <c r="J242" s="428"/>
+    </row>
+    <row r="243" spans="3:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C243" s="429"/>
+      <c r="D243" s="430"/>
+      <c r="E243" s="430"/>
+      <c r="F243" s="430"/>
+      <c r="G243" s="430"/>
+      <c r="H243" s="430"/>
+      <c r="I243" s="430"/>
+      <c r="J243" s="431"/>
     </row>
   </sheetData>
-  <mergeCells count="51">
-    <mergeCell ref="H94:J94"/>
-    <mergeCell ref="C96:J98"/>
-    <mergeCell ref="H149:J149"/>
-    <mergeCell ref="C151:J153"/>
-    <mergeCell ref="H158:J158"/>
+  <mergeCells count="55">
+    <mergeCell ref="H239:J239"/>
+    <mergeCell ref="C241:J243"/>
     <mergeCell ref="C160:J162"/>
     <mergeCell ref="C87:J89"/>
     <mergeCell ref="H76:J76"/>
     <mergeCell ref="C78:J80"/>
     <mergeCell ref="H140:J140"/>
     <mergeCell ref="C142:J144"/>
+    <mergeCell ref="H94:J94"/>
+    <mergeCell ref="C96:J98"/>
+    <mergeCell ref="H149:J149"/>
+    <mergeCell ref="C151:J153"/>
+    <mergeCell ref="H158:J158"/>
     <mergeCell ref="H40:J40"/>
     <mergeCell ref="C42:J44"/>
     <mergeCell ref="H131:J131"/>
@@ -19990,15 +20237,17 @@
     <mergeCell ref="H176:J176"/>
     <mergeCell ref="C178:J180"/>
     <mergeCell ref="H185:J185"/>
-    <mergeCell ref="H221:J221"/>
-    <mergeCell ref="C223:J225"/>
-    <mergeCell ref="H212:J212"/>
-    <mergeCell ref="C214:J216"/>
     <mergeCell ref="C187:J189"/>
     <mergeCell ref="H194:J194"/>
     <mergeCell ref="C196:J198"/>
     <mergeCell ref="H203:J203"/>
     <mergeCell ref="C205:J207"/>
+    <mergeCell ref="H230:J230"/>
+    <mergeCell ref="C232:J234"/>
+    <mergeCell ref="H221:J221"/>
+    <mergeCell ref="C223:J225"/>
+    <mergeCell ref="H212:J212"/>
+    <mergeCell ref="C214:J216"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/BRISAS/EXPENSAS/2026/JULIO/BRISAS-JULIO.xlsx
+++ b/BRISAS/EXPENSAS/2026/JULIO/BRISAS-JULIO.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistemax\Desktop\rc-consorcio2025\BRISAS\EXPENSAS\2026\JULIO\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{52BDCC0C-D2D6-48F0-A2B6-F2092361B1DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C5EB9D2-5722-47E2-BBD4-8EA118FE52D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="850" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -19,7 +19,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="1">PRORRATEO!$B$1:$T$167</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">RESUMEN!$A$1:$E$202</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">RESUMEN!$A$1:$E$200</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
   <extLst>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="747" uniqueCount="472">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="745" uniqueCount="470">
   <si>
     <t>Dpto.</t>
   </si>
@@ -1041,9 +1041,6 @@
     <t xml:space="preserve">Edesur (Cuit.: 30-65511652-1) - Nuevos medidores - Nro de cliente. 06106720 </t>
   </si>
   <si>
-    <t>Transferencia ya identificada mes anterior</t>
-  </si>
-  <si>
     <t>QUERCIA LUCIO - QAM SRL - FLEBO TDR SRL - Grupo Logistico Srl - BinBay - La bella vida SRL</t>
   </si>
   <si>
@@ -1441,9 +1438,6 @@
     <t>TOTAL AL 01/08/2026</t>
   </si>
   <si>
-    <t>Punitorios mal cobrados L104</t>
-  </si>
-  <si>
     <t>Rescate 02/07</t>
   </si>
   <si>
@@ -1451,9 +1445,6 @@
   </si>
   <si>
     <t>Transferencia mal imputada mes anterior: se le imputo un pago al lote 04 que correspondia al 104</t>
-  </si>
-  <si>
-    <t>Punitorios mal cobrados L004</t>
   </si>
   <si>
     <t>En la columna denominada “Gastos Particulares” podrán visualizar distintas casillas asociadas a cada unidad funcional. Los colores tienen el siguiente significado:
@@ -1463,6 +1454,9 @@
 Amarillo: arquitectura.
 Negro: corresponde a multas por exceso de velocidad o por circular sin la protección correspondiente (por ejemplo, moto sin casco).
 Verde: infraccion en ingreso de proveedores.                                                                                                                                                                                                                                                                                      Rosa: uso de espacios comunes indebido.                                                                                                                                                                                                                                                                                                                                                 Ante cualquier duda o consulta sobre los importes allí detallados, quedamos a disposición.</t>
+  </si>
+  <si>
+    <t>Multa mal cobrada al L114 (correspondia al  L14)</t>
   </si>
 </sst>
 </file>
@@ -2320,7 +2314,7 @@
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="422">
+  <cellXfs count="424">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
@@ -2780,76 +2774,28 @@
     </xf>
     <xf numFmtId="44" fontId="17" fillId="2" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="13" fillId="35" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="8" fontId="4" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="4" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="44" fontId="4" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="168" fontId="4" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="4" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="168" fontId="4" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="168" fontId="4" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="13" fillId="16" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="17" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="17" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="30" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="30" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="8" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="8" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="8" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="8" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="8" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="8" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="8" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="8" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -2884,33 +2830,81 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="44" fontId="9" fillId="5" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="8" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="24" fillId="8" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="8" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="8" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="8" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="8" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="8" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="8" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="8" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="44" fontId="13" fillId="4" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="44" fontId="13" fillId="4" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="17" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="44" fontId="17" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="2" fillId="17" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="169" fontId="22" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="2" fillId="17" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="30" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="30" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="44" fontId="9" fillId="5" borderId="32" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="9" fillId="5" borderId="33" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="9" fillId="5" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="9" fillId="5" borderId="7" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="9" fillId="5" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="169" fontId="22" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="169" fontId="22" fillId="3" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -2969,10 +2963,24 @@
     <xf numFmtId="0" fontId="13" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="44" fontId="9" fillId="5" borderId="32" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="9" fillId="5" borderId="33" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="9" fillId="5" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="9" fillId="5" borderId="7" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="8" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="44" fontId="13" fillId="4" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="13" fillId="4" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="17" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="17" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -3012,19 +3020,7 @@
     <xf numFmtId="0" fontId="8" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="8" fontId="4" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="4" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="44" fontId="4" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="168" fontId="4" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="4" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="168" fontId="4" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="4" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
+    <xf numFmtId="165" fontId="13" fillId="21" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="5">
     <cellStyle name="Hipervínculo" xfId="3" builtinId="8"/>
@@ -3037,10 +3033,10 @@
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <mruColors>
+      <color rgb="FFFD95DD"/>
       <color rgb="FFCC6600"/>
       <color rgb="FFFF00FF"/>
       <color rgb="FFFFFF99"/>
-      <color rgb="FFFD95DD"/>
       <color rgb="FF00FF00"/>
       <color rgb="FF666633"/>
       <color rgb="FF1CB0B0"/>
@@ -3436,7 +3432,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:O202"/>
+  <dimension ref="A1:O200"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="37.5703125" customWidth="1"/>
@@ -3452,34 +3448,34 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="366"/>
-      <c r="B1" s="361" t="s">
+      <c r="A1" s="352"/>
+      <c r="B1" s="347" t="s">
         <v>155</v>
       </c>
-      <c r="C1" s="362"/>
-      <c r="D1" s="362"/>
-      <c r="E1" s="363"/>
+      <c r="C1" s="348"/>
+      <c r="D1" s="348"/>
+      <c r="E1" s="349"/>
     </row>
     <row r="2" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="367"/>
-      <c r="B2" s="361" t="s">
+      <c r="A2" s="353"/>
+      <c r="B2" s="347" t="s">
         <v>157</v>
       </c>
-      <c r="C2" s="362"/>
-      <c r="D2" s="362"/>
-      <c r="E2" s="363"/>
+      <c r="C2" s="348"/>
+      <c r="D2" s="348"/>
+      <c r="E2" s="349"/>
     </row>
     <row r="3" spans="1:5" ht="32.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="367"/>
-      <c r="B3" s="358" t="s">
+      <c r="A3" s="353"/>
+      <c r="B3" s="344" t="s">
         <v>153</v>
       </c>
-      <c r="C3" s="359"/>
-      <c r="D3" s="359"/>
-      <c r="E3" s="360"/>
+      <c r="C3" s="345"/>
+      <c r="D3" s="345"/>
+      <c r="E3" s="346"/>
     </row>
     <row r="4" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="367"/>
+      <c r="A4" s="353"/>
       <c r="B4" s="43" t="s">
         <v>154</v>
       </c>
@@ -3488,16 +3484,16 @@
       <c r="E4" s="42"/>
     </row>
     <row r="5" spans="1:5" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="367"/>
+      <c r="A5" s="353"/>
       <c r="B5" s="46" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="C5" s="44"/>
       <c r="D5" s="44"/>
       <c r="E5" s="45"/>
     </row>
     <row r="6" spans="1:5" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="367"/>
+      <c r="A6" s="353"/>
       <c r="B6" s="47" t="s">
         <v>282</v>
       </c>
@@ -3506,7 +3502,7 @@
       <c r="E6" s="45"/>
     </row>
     <row r="7" spans="1:5" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="367"/>
+      <c r="A7" s="353"/>
       <c r="B7" s="47" t="s">
         <v>281</v>
       </c>
@@ -3515,13 +3511,13 @@
       <c r="E7" s="45"/>
     </row>
     <row r="8" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="368"/>
-      <c r="B8" s="364" t="s">
+      <c r="A8" s="354"/>
+      <c r="B8" s="350" t="s">
         <v>156</v>
       </c>
-      <c r="C8" s="364"/>
-      <c r="D8" s="364"/>
-      <c r="E8" s="365"/>
+      <c r="C8" s="350"/>
+      <c r="D8" s="350"/>
+      <c r="E8" s="351"/>
     </row>
     <row r="9" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="30"/>
@@ -3531,27 +3527,27 @@
       <c r="E9" s="30"/>
     </row>
     <row r="10" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="343" t="s">
-        <v>372</v>
-      </c>
-      <c r="B10" s="344"/>
-      <c r="C10" s="344"/>
-      <c r="D10" s="344"/>
-      <c r="E10" s="345"/>
+      <c r="A10" s="355" t="s">
+        <v>371</v>
+      </c>
+      <c r="B10" s="356"/>
+      <c r="C10" s="356"/>
+      <c r="D10" s="356"/>
+      <c r="E10" s="357"/>
     </row>
     <row r="11" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="346"/>
-      <c r="B11" s="347"/>
-      <c r="C11" s="347"/>
-      <c r="D11" s="347"/>
-      <c r="E11" s="348"/>
+      <c r="A11" s="358"/>
+      <c r="B11" s="359"/>
+      <c r="C11" s="359"/>
+      <c r="D11" s="359"/>
+      <c r="E11" s="360"/>
     </row>
     <row r="12" spans="1:5" ht="14.45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="349"/>
-      <c r="B12" s="350"/>
-      <c r="C12" s="350"/>
-      <c r="D12" s="350"/>
-      <c r="E12" s="351"/>
+      <c r="A12" s="361"/>
+      <c r="B12" s="362"/>
+      <c r="C12" s="362"/>
+      <c r="D12" s="362"/>
+      <c r="E12" s="363"/>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" s="30"/>
@@ -3568,34 +3564,34 @@
       <c r="E14" s="30"/>
     </row>
     <row r="15" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="352" t="s">
+      <c r="A15" s="364" t="s">
         <v>240</v>
       </c>
-      <c r="B15" s="352"/>
-      <c r="C15" s="352"/>
-      <c r="D15" s="352"/>
-      <c r="E15" s="352"/>
+      <c r="B15" s="364"/>
+      <c r="C15" s="364"/>
+      <c r="D15" s="364"/>
+      <c r="E15" s="364"/>
     </row>
     <row r="16" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="352"/>
-      <c r="B16" s="352"/>
-      <c r="C16" s="352"/>
-      <c r="D16" s="352"/>
-      <c r="E16" s="352"/>
+      <c r="A16" s="364"/>
+      <c r="B16" s="364"/>
+      <c r="C16" s="364"/>
+      <c r="D16" s="364"/>
+      <c r="E16" s="364"/>
     </row>
     <row r="17" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="352"/>
-      <c r="B17" s="352"/>
-      <c r="C17" s="352"/>
-      <c r="D17" s="352"/>
-      <c r="E17" s="352"/>
+      <c r="A17" s="364"/>
+      <c r="B17" s="364"/>
+      <c r="C17" s="364"/>
+      <c r="D17" s="364"/>
+      <c r="E17" s="364"/>
     </row>
     <row r="18" spans="1:8" ht="243" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="352"/>
-      <c r="B18" s="352"/>
-      <c r="C18" s="352"/>
-      <c r="D18" s="352"/>
-      <c r="E18" s="352"/>
+      <c r="A18" s="364"/>
+      <c r="B18" s="364"/>
+      <c r="C18" s="364"/>
+      <c r="D18" s="364"/>
+      <c r="E18" s="364"/>
     </row>
     <row r="19" spans="1:8" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A19" s="30"/>
@@ -3642,7 +3638,7 @@
     </row>
     <row r="24" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="187" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="B24" s="264"/>
       <c r="C24" s="22"/>
@@ -3654,10 +3650,10 @@
       <c r="G24" s="252"/>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A25" s="354" t="s">
-        <v>375</v>
-      </c>
-      <c r="B25" s="355"/>
+      <c r="A25" s="365" t="s">
+        <v>374</v>
+      </c>
+      <c r="B25" s="366"/>
       <c r="C25" s="22"/>
       <c r="D25" s="266">
         <v>-491806.35</v>
@@ -3667,10 +3663,10 @@
       <c r="G25" s="253"/>
     </row>
     <row r="26" spans="1:8" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="356" t="s">
-        <v>376</v>
-      </c>
-      <c r="B26" s="357"/>
+      <c r="A26" s="367" t="s">
+        <v>375</v>
+      </c>
+      <c r="B26" s="368"/>
       <c r="C26" s="22"/>
       <c r="D26" s="266">
         <v>0</v>
@@ -3695,16 +3691,16 @@
       <c r="H27" s="71"/>
     </row>
     <row r="28" spans="1:8" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="335" t="s">
-        <v>336</v>
-      </c>
-      <c r="B28" s="336"/>
+      <c r="A28" s="341" t="s">
+        <v>335</v>
+      </c>
+      <c r="B28" s="343"/>
       <c r="C28" s="22"/>
-      <c r="D28" s="415">
+      <c r="D28" s="333">
         <v>1520000</v>
       </c>
       <c r="E28" s="22" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="F28" s="30"/>
       <c r="G28" s="253">
@@ -3753,32 +3749,32 @@
     </row>
     <row r="32" spans="1:8" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="22" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="B32" s="22"/>
       <c r="C32" s="97"/>
-      <c r="D32" s="416">
+      <c r="D32" s="334">
         <v>1552652.02</v>
       </c>
       <c r="E32" s="76" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="F32" s="254"/>
       <c r="G32" s="255"/>
     </row>
     <row r="33" spans="1:9" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="98" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="B33" s="22" t="s">
         <v>11</v>
       </c>
       <c r="C33" s="97"/>
-      <c r="D33" s="416">
+      <c r="D33" s="334">
         <v>153062.19</v>
       </c>
       <c r="E33" s="75" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="F33" s="254"/>
       <c r="G33" s="255"/>
@@ -3792,7 +3788,7 @@
         <v>20</v>
       </c>
       <c r="C34" s="97"/>
-      <c r="D34" s="416">
+      <c r="D34" s="334">
         <v>293725.82</v>
       </c>
       <c r="E34" s="75" t="str">
@@ -3811,7 +3807,7 @@
         <v>10</v>
       </c>
       <c r="C35" s="97"/>
-      <c r="D35" s="417">
+      <c r="D35" s="335">
         <v>17006.91</v>
       </c>
       <c r="E35" s="75" t="str">
@@ -3848,61 +3844,61 @@
       <c r="G37" s="30"/>
     </row>
     <row r="38" spans="1:9" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="335" t="s">
+      <c r="A38" s="341" t="s">
         <v>268</v>
       </c>
-      <c r="B38" s="336"/>
+      <c r="B38" s="343"/>
       <c r="C38" s="22"/>
       <c r="D38" s="198">
         <v>148518.18</v>
       </c>
       <c r="E38" s="76" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="F38" s="30"/>
       <c r="G38" s="30"/>
     </row>
     <row r="39" spans="1:9" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="335" t="s">
+      <c r="A39" s="341" t="s">
         <v>269</v>
       </c>
-      <c r="B39" s="336"/>
+      <c r="B39" s="343"/>
       <c r="C39" s="22"/>
       <c r="D39" s="198">
         <v>7805</v>
       </c>
       <c r="E39" s="76" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="F39" s="30"/>
       <c r="G39" s="30"/>
     </row>
     <row r="40" spans="1:9" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="335" t="s">
+      <c r="A40" s="341" t="s">
         <v>308</v>
       </c>
-      <c r="B40" s="336"/>
+      <c r="B40" s="343"/>
       <c r="C40" s="329"/>
       <c r="D40" s="198">
         <v>23573.47</v>
       </c>
       <c r="E40" s="76" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="F40" s="30"/>
       <c r="G40" s="30"/>
     </row>
     <row r="41" spans="1:9" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="335" t="s">
+      <c r="A41" s="341" t="s">
         <v>308</v>
       </c>
-      <c r="B41" s="336"/>
+      <c r="B41" s="343"/>
       <c r="C41" s="22"/>
       <c r="D41" s="198">
         <v>26214.080000000002</v>
       </c>
       <c r="E41" s="76" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="F41" s="30"/>
       <c r="G41" s="30"/>
@@ -3933,16 +3929,16 @@
       <c r="G43" s="30"/>
     </row>
     <row r="44" spans="1:9" ht="42.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="335" t="s">
-        <v>445</v>
-      </c>
-      <c r="B44" s="353"/>
+      <c r="A44" s="341" t="s">
+        <v>444</v>
+      </c>
+      <c r="B44" s="342"/>
       <c r="C44" s="101"/>
       <c r="D44" s="198">
         <v>46102546.960000001</v>
       </c>
       <c r="E44" s="76" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="F44" s="256">
         <f>D44</f>
@@ -3952,16 +3948,16 @@
       <c r="I44" s="37"/>
     </row>
     <row r="45" spans="1:9" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="335" t="s">
-        <v>418</v>
-      </c>
-      <c r="B45" s="353"/>
+      <c r="A45" s="341" t="s">
+        <v>417</v>
+      </c>
+      <c r="B45" s="342"/>
       <c r="C45" s="101"/>
       <c r="D45" s="198">
         <v>5702320.7999999998</v>
       </c>
       <c r="E45" s="29" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="F45" s="256"/>
       <c r="G45" s="30"/>
@@ -3994,100 +3990,100 @@
       <c r="G47" s="30"/>
     </row>
     <row r="48" spans="1:9" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A48" s="335" t="s">
-        <v>400</v>
-      </c>
-      <c r="B48" s="353"/>
+      <c r="A48" s="341" t="s">
+        <v>399</v>
+      </c>
+      <c r="B48" s="342"/>
       <c r="C48" s="101"/>
       <c r="D48" s="198">
         <v>1472058.6</v>
       </c>
       <c r="E48" s="29" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="F48" s="30"/>
       <c r="G48" s="30"/>
     </row>
     <row r="49" spans="1:8" ht="51.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A49" s="335" t="s">
-        <v>382</v>
-      </c>
-      <c r="B49" s="353"/>
+      <c r="A49" s="341" t="s">
+        <v>381</v>
+      </c>
+      <c r="B49" s="342"/>
       <c r="C49" s="101"/>
       <c r="D49" s="198">
         <v>756250</v>
       </c>
       <c r="E49" s="29" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="F49" s="30"/>
       <c r="G49" s="30"/>
     </row>
     <row r="50" spans="1:8" ht="51.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A50" s="335" t="s">
-        <v>401</v>
-      </c>
-      <c r="B50" s="353"/>
+      <c r="A50" s="341" t="s">
+        <v>400</v>
+      </c>
+      <c r="B50" s="342"/>
       <c r="C50" s="101"/>
       <c r="D50" s="198">
         <v>97574.399999999994</v>
       </c>
       <c r="E50" s="29" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="F50" s="30"/>
       <c r="G50" s="30"/>
     </row>
     <row r="51" spans="1:8" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A51" s="335" t="s">
-        <v>412</v>
-      </c>
-      <c r="B51" s="336"/>
+      <c r="A51" s="341" t="s">
+        <v>411</v>
+      </c>
+      <c r="B51" s="343"/>
       <c r="C51" s="102"/>
       <c r="D51" s="198">
         <v>6300000</v>
       </c>
       <c r="E51" s="262" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="F51" s="30"/>
       <c r="G51" s="30"/>
     </row>
     <row r="52" spans="1:8" ht="39" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A52" s="335" t="s">
-        <v>379</v>
-      </c>
-      <c r="B52" s="336"/>
+      <c r="A52" s="341" t="s">
+        <v>378</v>
+      </c>
+      <c r="B52" s="343"/>
       <c r="C52" s="102"/>
       <c r="D52" s="198">
         <v>228690</v>
       </c>
       <c r="E52" s="29" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="F52" s="30"/>
       <c r="G52" s="30"/>
     </row>
     <row r="53" spans="1:8" ht="48" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A53" s="335" t="s">
-        <v>339</v>
-      </c>
-      <c r="B53" s="336"/>
+      <c r="A53" s="341" t="s">
+        <v>338</v>
+      </c>
+      <c r="B53" s="343"/>
       <c r="C53" s="102"/>
       <c r="D53" s="198">
         <v>118400</v>
       </c>
       <c r="E53" s="77" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="F53" s="30"/>
       <c r="G53" s="30"/>
     </row>
     <row r="54" spans="1:8" ht="44.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A54" s="335" t="s">
-        <v>442</v>
-      </c>
-      <c r="B54" s="336"/>
+      <c r="A54" s="341" t="s">
+        <v>441</v>
+      </c>
+      <c r="B54" s="343"/>
       <c r="C54" s="102"/>
       <c r="D54" s="198">
         <v>0</v>
@@ -4097,121 +4093,121 @@
       <c r="G54" s="30"/>
     </row>
     <row r="55" spans="1:8" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A55" s="335" t="s">
-        <v>436</v>
-      </c>
-      <c r="B55" s="336"/>
+      <c r="A55" s="341" t="s">
+        <v>435</v>
+      </c>
+      <c r="B55" s="343"/>
       <c r="C55" s="102"/>
       <c r="D55" s="198">
         <v>820380</v>
       </c>
       <c r="E55" s="77" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="F55" s="30"/>
       <c r="G55" s="30"/>
     </row>
     <row r="56" spans="1:8" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A56" s="335" t="s">
-        <v>397</v>
-      </c>
-      <c r="B56" s="336"/>
+      <c r="A56" s="341" t="s">
+        <v>396</v>
+      </c>
+      <c r="B56" s="343"/>
       <c r="C56" s="102"/>
       <c r="D56" s="198">
         <v>220000</v>
       </c>
       <c r="E56" s="77" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="F56" s="30"/>
       <c r="G56" s="30"/>
     </row>
     <row r="57" spans="1:8" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A57" s="335" t="s">
-        <v>403</v>
-      </c>
-      <c r="B57" s="336"/>
+      <c r="A57" s="341" t="s">
+        <v>402</v>
+      </c>
+      <c r="B57" s="343"/>
       <c r="C57" s="102"/>
       <c r="D57" s="198">
         <v>110000</v>
       </c>
       <c r="E57" s="77" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="F57" s="30"/>
       <c r="G57" s="30"/>
     </row>
     <row r="58" spans="1:8" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A58" s="335" t="s">
-        <v>420</v>
-      </c>
-      <c r="B58" s="336"/>
+      <c r="A58" s="341" t="s">
+        <v>419</v>
+      </c>
+      <c r="B58" s="343"/>
       <c r="C58" s="102"/>
       <c r="D58" s="198">
         <v>110000</v>
       </c>
       <c r="E58" s="77" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="F58" s="30"/>
       <c r="G58" s="30"/>
     </row>
     <row r="59" spans="1:8" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A59" s="335" t="s">
-        <v>421</v>
-      </c>
-      <c r="B59" s="336"/>
+      <c r="A59" s="341" t="s">
+        <v>420</v>
+      </c>
+      <c r="B59" s="343"/>
       <c r="C59" s="102"/>
       <c r="D59" s="198">
         <v>110000</v>
       </c>
       <c r="E59" s="77" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="F59" s="30"/>
       <c r="G59" s="30"/>
     </row>
     <row r="60" spans="1:8" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A60" s="335" t="s">
-        <v>426</v>
-      </c>
-      <c r="B60" s="336"/>
+      <c r="A60" s="341" t="s">
+        <v>425</v>
+      </c>
+      <c r="B60" s="343"/>
       <c r="C60" s="102"/>
       <c r="D60" s="198">
         <v>150000</v>
       </c>
       <c r="E60" s="77" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="F60" s="30"/>
       <c r="G60" s="30"/>
     </row>
     <row r="61" spans="1:8" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A61" s="335" t="s">
-        <v>380</v>
-      </c>
-      <c r="B61" s="336"/>
+      <c r="A61" s="341" t="s">
+        <v>379</v>
+      </c>
+      <c r="B61" s="343"/>
       <c r="C61" s="102"/>
       <c r="D61" s="198">
         <v>1300000</v>
       </c>
       <c r="E61" s="77" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="F61" s="30"/>
       <c r="G61" s="30"/>
     </row>
     <row r="62" spans="1:8" ht="51" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A62" s="335" t="s">
-        <v>413</v>
-      </c>
-      <c r="B62" s="336"/>
+      <c r="A62" s="341" t="s">
+        <v>412</v>
+      </c>
+      <c r="B62" s="343"/>
       <c r="C62" s="22"/>
       <c r="D62" s="198">
         <v>2459883</v>
       </c>
       <c r="E62" s="77" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="F62" s="30"/>
       <c r="G62" s="257"/>
@@ -4243,406 +4239,406 @@
       <c r="G64" s="30"/>
     </row>
     <row r="65" spans="1:7" ht="42" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A65" s="335" t="s">
-        <v>402</v>
-      </c>
-      <c r="B65" s="336"/>
+      <c r="A65" s="341" t="s">
+        <v>401</v>
+      </c>
+      <c r="B65" s="343"/>
       <c r="C65" s="22"/>
-      <c r="D65" s="418">
+      <c r="D65" s="336">
         <v>120000</v>
       </c>
       <c r="E65" s="78" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="F65" s="30"/>
       <c r="G65" s="30"/>
     </row>
     <row r="66" spans="1:7" ht="63.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A66" s="335" t="s">
-        <v>407</v>
-      </c>
-      <c r="B66" s="353"/>
-      <c r="C66" s="336"/>
-      <c r="D66" s="418">
+      <c r="A66" s="341" t="s">
+        <v>406</v>
+      </c>
+      <c r="B66" s="342"/>
+      <c r="C66" s="343"/>
+      <c r="D66" s="336">
         <v>350000</v>
       </c>
       <c r="E66" s="78" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="F66" s="30"/>
       <c r="G66" s="30"/>
     </row>
     <row r="67" spans="1:7" ht="129.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A67" s="335" t="s">
-        <v>441</v>
-      </c>
-      <c r="B67" s="353"/>
-      <c r="C67" s="336"/>
-      <c r="D67" s="418">
+      <c r="A67" s="341" t="s">
+        <v>440</v>
+      </c>
+      <c r="B67" s="342"/>
+      <c r="C67" s="343"/>
+      <c r="D67" s="336">
         <v>2120000</v>
       </c>
       <c r="E67" s="78" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="F67" s="30"/>
       <c r="G67" s="30"/>
     </row>
     <row r="68" spans="1:7" ht="83.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A68" s="335" t="s">
-        <v>415</v>
-      </c>
-      <c r="B68" s="336"/>
+      <c r="A68" s="341" t="s">
+        <v>414</v>
+      </c>
+      <c r="B68" s="343"/>
       <c r="C68" s="22"/>
-      <c r="D68" s="418">
+      <c r="D68" s="336">
         <v>1250000</v>
       </c>
       <c r="E68" s="78" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="F68" s="30"/>
       <c r="G68" s="30"/>
     </row>
     <row r="69" spans="1:7" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A69" s="335" t="s">
-        <v>443</v>
-      </c>
-      <c r="B69" s="336"/>
+      <c r="A69" s="341" t="s">
+        <v>442</v>
+      </c>
+      <c r="B69" s="343"/>
       <c r="C69" s="98"/>
-      <c r="D69" s="418">
+      <c r="D69" s="336">
         <v>75000</v>
       </c>
       <c r="E69" s="143" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="F69" s="257"/>
       <c r="G69" s="30"/>
     </row>
     <row r="70" spans="1:7" ht="31.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70" s="231" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="B70" s="263"/>
       <c r="C70" s="98"/>
-      <c r="D70" s="418">
+      <c r="D70" s="336">
         <v>126600</v>
       </c>
       <c r="E70" s="143" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="F70" s="30"/>
       <c r="G70" s="30"/>
     </row>
     <row r="71" spans="1:7" ht="31.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A71" s="231" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="B71" s="263"/>
       <c r="C71" s="98"/>
-      <c r="D71" s="418">
+      <c r="D71" s="336">
         <v>108000</v>
       </c>
       <c r="E71" s="143" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="F71" s="30"/>
       <c r="G71" s="30"/>
     </row>
     <row r="72" spans="1:7" ht="31.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A72" s="231" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="B72" s="328"/>
       <c r="C72" s="98"/>
-      <c r="D72" s="418">
+      <c r="D72" s="336">
         <v>43800</v>
       </c>
       <c r="E72" s="143" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="F72" s="30"/>
       <c r="G72" s="30"/>
     </row>
     <row r="73" spans="1:7" ht="31.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A73" s="231" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="B73" s="328"/>
       <c r="C73" s="98"/>
-      <c r="D73" s="418">
+      <c r="D73" s="336">
         <v>130300</v>
       </c>
       <c r="E73" s="143" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="F73" s="30"/>
       <c r="G73" s="30"/>
     </row>
     <row r="74" spans="1:7" ht="54.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A74" s="335" t="s">
-        <v>459</v>
-      </c>
-      <c r="B74" s="336"/>
+      <c r="A74" s="341" t="s">
+        <v>458</v>
+      </c>
+      <c r="B74" s="343"/>
       <c r="C74" s="98"/>
-      <c r="D74" s="418">
+      <c r="D74" s="336">
         <v>1465520</v>
       </c>
       <c r="E74" s="143" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="F74" s="30"/>
       <c r="G74" s="30"/>
     </row>
     <row r="75" spans="1:7" ht="39" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A75" s="335" t="s">
+      <c r="A75" s="341" t="s">
+        <v>403</v>
+      </c>
+      <c r="B75" s="343"/>
+      <c r="C75" s="22"/>
+      <c r="D75" s="337">
+        <v>3179880</v>
+      </c>
+      <c r="E75" s="143" t="s">
         <v>404</v>
-      </c>
-      <c r="B75" s="336"/>
-      <c r="C75" s="22"/>
-      <c r="D75" s="419">
-        <v>3179880</v>
-      </c>
-      <c r="E75" s="143" t="s">
-        <v>405</v>
       </c>
       <c r="F75" s="30"/>
       <c r="G75" s="30"/>
     </row>
     <row r="76" spans="1:7" ht="61.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A76" s="335" t="s">
-        <v>435</v>
-      </c>
-      <c r="B76" s="336"/>
+      <c r="A76" s="341" t="s">
+        <v>434</v>
+      </c>
+      <c r="B76" s="343"/>
       <c r="C76" s="98"/>
-      <c r="D76" s="419">
+      <c r="D76" s="337">
         <v>946220</v>
       </c>
       <c r="E76" s="143" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="F76" s="30"/>
       <c r="G76" s="30"/>
     </row>
     <row r="77" spans="1:7" ht="42" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A77" s="335" t="s">
-        <v>422</v>
-      </c>
-      <c r="B77" s="336"/>
+      <c r="A77" s="341" t="s">
+        <v>421</v>
+      </c>
+      <c r="B77" s="343"/>
       <c r="C77" s="98"/>
-      <c r="D77" s="418">
+      <c r="D77" s="336">
         <v>1113200</v>
       </c>
       <c r="E77" s="143" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="F77" s="257"/>
       <c r="G77" s="30"/>
     </row>
     <row r="78" spans="1:7" ht="40.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A78" s="335" t="s">
+      <c r="A78" s="341" t="s">
+        <v>422</v>
+      </c>
+      <c r="B78" s="343"/>
+      <c r="C78" s="98"/>
+      <c r="D78" s="336">
+        <v>749938.04</v>
+      </c>
+      <c r="E78" s="143" t="s">
         <v>423</v>
-      </c>
-      <c r="B78" s="336"/>
-      <c r="C78" s="98"/>
-      <c r="D78" s="418">
-        <v>749938.04</v>
-      </c>
-      <c r="E78" s="143" t="s">
-        <v>424</v>
       </c>
       <c r="F78" s="257"/>
       <c r="G78" s="30"/>
     </row>
     <row r="79" spans="1:7" ht="40.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A79" s="335" t="s">
-        <v>419</v>
-      </c>
-      <c r="B79" s="336"/>
+      <c r="A79" s="341" t="s">
+        <v>418</v>
+      </c>
+      <c r="B79" s="343"/>
       <c r="C79" s="98"/>
-      <c r="D79" s="418">
+      <c r="D79" s="336">
         <v>1113200</v>
       </c>
       <c r="E79" s="143" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="F79" s="257"/>
       <c r="G79" s="30"/>
     </row>
     <row r="80" spans="1:7" ht="40.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A80" s="335" t="s">
+      <c r="A80" s="341" t="s">
+        <v>460</v>
+      </c>
+      <c r="B80" s="343"/>
+      <c r="C80" s="98"/>
+      <c r="D80" s="336">
+        <v>1669800</v>
+      </c>
+      <c r="E80" s="143" t="s">
         <v>461</v>
-      </c>
-      <c r="B80" s="336"/>
-      <c r="C80" s="98"/>
-      <c r="D80" s="418">
-        <v>1669800</v>
-      </c>
-      <c r="E80" s="143" t="s">
-        <v>462</v>
       </c>
       <c r="F80" s="257"/>
       <c r="G80" s="30"/>
     </row>
     <row r="81" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A81" s="335" t="s">
-        <v>414</v>
-      </c>
-      <c r="B81" s="336"/>
+      <c r="A81" s="341" t="s">
+        <v>413</v>
+      </c>
+      <c r="B81" s="343"/>
       <c r="C81" s="98"/>
-      <c r="D81" s="418">
+      <c r="D81" s="336">
         <v>46300</v>
       </c>
       <c r="E81" s="85" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="F81" s="30"/>
       <c r="G81" s="30"/>
     </row>
     <row r="82" spans="1:7" ht="55.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A82" s="335" t="s">
+      <c r="A82" s="341" t="s">
+        <v>397</v>
+      </c>
+      <c r="B82" s="343"/>
+      <c r="C82" s="98"/>
+      <c r="D82" s="336">
+        <v>95648.4</v>
+      </c>
+      <c r="E82" s="85" t="s">
         <v>398</v>
-      </c>
-      <c r="B82" s="336"/>
-      <c r="C82" s="98"/>
-      <c r="D82" s="418">
-        <v>95648.4</v>
-      </c>
-      <c r="E82" s="85" t="s">
-        <v>399</v>
       </c>
       <c r="F82" s="30"/>
       <c r="G82" s="30"/>
     </row>
     <row r="83" spans="1:7" ht="41.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A83" s="335" t="s">
+      <c r="A83" s="341" t="s">
+        <v>415</v>
+      </c>
+      <c r="B83" s="343"/>
+      <c r="C83" s="98"/>
+      <c r="D83" s="336">
+        <v>139099</v>
+      </c>
+      <c r="E83" s="85" t="s">
         <v>416</v>
-      </c>
-      <c r="B83" s="336"/>
-      <c r="C83" s="98"/>
-      <c r="D83" s="418">
-        <v>139099</v>
-      </c>
-      <c r="E83" s="85" t="s">
-        <v>417</v>
       </c>
       <c r="F83" s="30"/>
       <c r="G83" s="30"/>
     </row>
     <row r="84" spans="1:7" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A84" s="335" t="s">
+      <c r="A84" s="341" t="s">
+        <v>436</v>
+      </c>
+      <c r="B84" s="343"/>
+      <c r="C84" s="98"/>
+      <c r="D84" s="336">
+        <v>1250000</v>
+      </c>
+      <c r="E84" s="85" t="s">
         <v>437</v>
-      </c>
-      <c r="B84" s="336"/>
-      <c r="C84" s="98"/>
-      <c r="D84" s="418">
-        <v>1250000</v>
-      </c>
-      <c r="E84" s="85" t="s">
-        <v>438</v>
       </c>
       <c r="F84" s="30"/>
       <c r="G84" s="30"/>
     </row>
     <row r="85" spans="1:7" ht="25.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A85" s="335" t="s">
+      <c r="A85" s="341" t="s">
+        <v>383</v>
+      </c>
+      <c r="B85" s="343"/>
+      <c r="C85" s="98"/>
+      <c r="D85" s="336">
+        <v>1775000</v>
+      </c>
+      <c r="E85" s="143" t="s">
         <v>384</v>
-      </c>
-      <c r="B85" s="336"/>
-      <c r="C85" s="98"/>
-      <c r="D85" s="418">
-        <v>1775000</v>
-      </c>
-      <c r="E85" s="143" t="s">
-        <v>385</v>
       </c>
       <c r="F85" s="30"/>
       <c r="G85" s="30"/>
     </row>
     <row r="86" spans="1:7" ht="25.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A86" s="335" t="s">
+      <c r="A86" s="341" t="s">
+        <v>387</v>
+      </c>
+      <c r="B86" s="343"/>
+      <c r="C86" s="98"/>
+      <c r="D86" s="336">
+        <v>1000000</v>
+      </c>
+      <c r="E86" s="85" t="s">
         <v>388</v>
-      </c>
-      <c r="B86" s="336"/>
-      <c r="C86" s="98"/>
-      <c r="D86" s="418">
-        <v>1000000</v>
-      </c>
-      <c r="E86" s="85" t="s">
-        <v>389</v>
       </c>
       <c r="F86" s="30"/>
       <c r="G86" s="30"/>
     </row>
     <row r="87" spans="1:7" ht="25.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A87" s="335" t="s">
+      <c r="A87" s="341" t="s">
+        <v>385</v>
+      </c>
+      <c r="B87" s="343"/>
+      <c r="C87" s="98"/>
+      <c r="D87" s="336">
+        <v>1000000</v>
+      </c>
+      <c r="E87" s="85" t="s">
         <v>386</v>
-      </c>
-      <c r="B87" s="336"/>
-      <c r="C87" s="98"/>
-      <c r="D87" s="418">
-        <v>1000000</v>
-      </c>
-      <c r="E87" s="85" t="s">
-        <v>387</v>
       </c>
       <c r="F87" s="30"/>
       <c r="G87" s="30"/>
     </row>
     <row r="88" spans="1:7" ht="20.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A88" s="335" t="s">
-        <v>390</v>
-      </c>
-      <c r="B88" s="336"/>
+      <c r="A88" s="341" t="s">
+        <v>389</v>
+      </c>
+      <c r="B88" s="343"/>
       <c r="C88" s="98"/>
-      <c r="D88" s="418">
+      <c r="D88" s="336">
         <v>1250000</v>
       </c>
       <c r="E88" s="85" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="F88" s="30"/>
       <c r="G88" s="30"/>
     </row>
     <row r="89" spans="1:7" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A89" s="335" t="s">
-        <v>392</v>
-      </c>
-      <c r="B89" s="336"/>
+      <c r="A89" s="341" t="s">
+        <v>391</v>
+      </c>
+      <c r="B89" s="343"/>
       <c r="C89" s="98"/>
-      <c r="D89" s="418">
+      <c r="D89" s="336">
         <v>20500</v>
       </c>
       <c r="E89" s="85" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="F89" s="30"/>
       <c r="G89" s="30"/>
     </row>
     <row r="90" spans="1:7" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A90" s="335" t="s">
-        <v>393</v>
-      </c>
-      <c r="B90" s="336"/>
+      <c r="A90" s="341" t="s">
+        <v>392</v>
+      </c>
+      <c r="B90" s="343"/>
       <c r="C90" s="98"/>
-      <c r="D90" s="418">
+      <c r="D90" s="336">
         <v>48500</v>
       </c>
       <c r="E90" s="85" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="F90" s="30"/>
       <c r="G90" s="30"/>
     </row>
     <row r="91" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A91" s="335" t="s">
-        <v>432</v>
-      </c>
-      <c r="B91" s="336"/>
+      <c r="A91" s="341" t="s">
+        <v>431</v>
+      </c>
+      <c r="B91" s="343"/>
       <c r="C91" s="98"/>
-      <c r="D91" s="418">
+      <c r="D91" s="336">
         <v>315000</v>
       </c>
       <c r="E91" s="78" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="F91" s="30"/>
       <c r="G91" s="30"/>
@@ -4673,31 +4669,31 @@
       <c r="G93" s="30"/>
     </row>
     <row r="94" spans="1:7" ht="23.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A94" s="335" t="s">
-        <v>381</v>
-      </c>
-      <c r="B94" s="336"/>
+      <c r="A94" s="341" t="s">
+        <v>380</v>
+      </c>
+      <c r="B94" s="343"/>
       <c r="C94" s="22"/>
-      <c r="D94" s="420">
+      <c r="D94" s="338">
         <v>3218160</v>
       </c>
       <c r="E94" s="85" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="F94" s="30"/>
       <c r="G94" s="30"/>
     </row>
     <row r="95" spans="1:7" ht="68.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A95" s="335" t="s">
-        <v>447</v>
-      </c>
-      <c r="B95" s="336"/>
+      <c r="A95" s="341" t="s">
+        <v>446</v>
+      </c>
+      <c r="B95" s="343"/>
       <c r="C95" s="22"/>
-      <c r="D95" s="421">
+      <c r="D95" s="339">
         <v>250000</v>
       </c>
       <c r="E95" s="326" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="F95" s="30"/>
       <c r="G95" s="30"/>
@@ -4710,8 +4706,8 @@
       <c r="C96" s="96"/>
       <c r="D96" s="196"/>
       <c r="E96" s="81">
-        <f>SUM(D94:D94)</f>
-        <v>3218160</v>
+        <f>SUM(D94:D95)</f>
+        <v>3468160</v>
       </c>
       <c r="F96" s="30"/>
       <c r="G96" s="30"/>
@@ -4734,8 +4730,8 @@
       <c r="B98" s="22"/>
       <c r="C98" s="22"/>
       <c r="D98" s="198">
-        <f>318989.74+130083.39+2530.44+245372.05+50149.71+146783.18+69952.09+45193.1+73656.65+201270.88+65233+45041.81+82653.78+38641+100000-42</f>
-        <v>1615508.82</v>
+        <f>318989.74+130083.39+2530.44+245372.05+50149.71+146783.18+69952.09+45193.1+73656.65+201270.88+65233+45041.81+82653.78+38641-42-95894</f>
+        <v>1419614.82</v>
       </c>
       <c r="E98" s="29"/>
       <c r="F98" s="30"/>
@@ -4763,7 +4759,7 @@
       <c r="D100" s="204"/>
       <c r="E100" s="84">
         <f>SUM(D98:D99)</f>
-        <v>1684508.82</v>
+        <v>1488614.82</v>
       </c>
       <c r="F100" s="30"/>
       <c r="G100" s="30"/>
@@ -4795,7 +4791,7 @@
       <c r="D103" s="51"/>
       <c r="E103" s="141">
         <f>(SUM(E30:E101))</f>
-        <v>97974208.689999998</v>
+        <v>98028314.689999998</v>
       </c>
       <c r="F103" s="259"/>
       <c r="G103" s="30"/>
@@ -4830,10 +4826,10 @@
       <c r="G106" s="30"/>
     </row>
     <row r="107" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A107" s="335" t="s">
-        <v>338</v>
-      </c>
-      <c r="B107" s="336"/>
+      <c r="A107" s="341" t="s">
+        <v>337</v>
+      </c>
+      <c r="B107" s="343"/>
       <c r="C107" s="22"/>
       <c r="D107" s="198">
         <v>397708.95</v>
@@ -4845,25 +4841,25 @@
       <c r="G107" s="30"/>
     </row>
     <row r="108" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A108" s="335" t="s">
+      <c r="A108" s="341" t="s">
         <v>331</v>
       </c>
-      <c r="B108" s="336"/>
+      <c r="B108" s="343"/>
       <c r="C108" s="22"/>
       <c r="D108" s="198">
         <v>64376.63</v>
       </c>
       <c r="E108" s="248" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="F108" s="30"/>
       <c r="G108" s="30"/>
     </row>
     <row r="109" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A109" s="335" t="s">
+      <c r="A109" s="341" t="s">
         <v>332</v>
       </c>
-      <c r="B109" s="336"/>
+      <c r="B109" s="343"/>
       <c r="C109" s="22"/>
       <c r="D109" s="198">
         <v>64376.63</v>
@@ -4876,10 +4872,10 @@
       <c r="G109" s="30"/>
     </row>
     <row r="110" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A110" s="335" t="s">
+      <c r="A110" s="341" t="s">
         <v>333</v>
       </c>
-      <c r="B110" s="336"/>
+      <c r="B110" s="343"/>
       <c r="C110" s="22"/>
       <c r="D110" s="198">
         <v>64581.58</v>
@@ -4892,25 +4888,25 @@
       <c r="G110" s="30"/>
     </row>
     <row r="111" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A111" s="333" t="s">
-        <v>408</v>
-      </c>
-      <c r="B111" s="334"/>
+      <c r="A111" s="369" t="s">
+        <v>407</v>
+      </c>
+      <c r="B111" s="370"/>
       <c r="C111" s="22"/>
       <c r="D111" s="198">
         <v>1314489.94</v>
       </c>
       <c r="E111" s="78" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="F111" s="30"/>
       <c r="G111" s="30"/>
     </row>
     <row r="112" spans="1:7" ht="36.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A112" s="333" t="s">
-        <v>409</v>
-      </c>
-      <c r="B112" s="334"/>
+      <c r="A112" s="369" t="s">
+        <v>408</v>
+      </c>
+      <c r="B112" s="370"/>
       <c r="C112" s="22"/>
       <c r="D112" s="198">
         <v>458163.6</v>
@@ -4923,10 +4919,10 @@
       <c r="G112" s="30"/>
     </row>
     <row r="113" spans="1:7" ht="31.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A113" s="333" t="s">
-        <v>410</v>
-      </c>
-      <c r="B113" s="334"/>
+      <c r="A113" s="369" t="s">
+        <v>409</v>
+      </c>
+      <c r="B113" s="370"/>
       <c r="C113" s="22"/>
       <c r="D113" s="198">
         <v>124681.3</v>
@@ -4939,10 +4935,10 @@
       <c r="G113" s="30"/>
     </row>
     <row r="114" spans="1:7" ht="33.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A114" s="333" t="s">
-        <v>411</v>
-      </c>
-      <c r="B114" s="334"/>
+      <c r="A114" s="369" t="s">
+        <v>410</v>
+      </c>
+      <c r="B114" s="370"/>
       <c r="C114" s="22"/>
       <c r="D114" s="198">
         <v>92816.68</v>
@@ -4958,25 +4954,25 @@
       <c r="G114" s="30"/>
     </row>
     <row r="115" spans="1:7" ht="33.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A115" s="333" t="s">
-        <v>406</v>
-      </c>
-      <c r="B115" s="334"/>
+      <c r="A115" s="369" t="s">
+        <v>405</v>
+      </c>
+      <c r="B115" s="370"/>
       <c r="C115" s="22"/>
       <c r="D115" s="198">
         <v>646140</v>
       </c>
       <c r="E115" s="78" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="F115" s="256"/>
       <c r="G115" s="30"/>
     </row>
     <row r="116" spans="1:7" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A116" s="333" t="s">
+      <c r="A116" s="369" t="s">
         <v>189</v>
       </c>
-      <c r="B116" s="334"/>
+      <c r="B116" s="370"/>
       <c r="C116" s="22"/>
       <c r="D116" s="198">
         <v>117933.22</v>
@@ -4989,10 +4985,10 @@
       <c r="G116" s="30"/>
     </row>
     <row r="117" spans="1:7" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A117" s="333" t="s">
+      <c r="A117" s="369" t="s">
         <v>300</v>
       </c>
-      <c r="B117" s="334"/>
+      <c r="B117" s="370"/>
       <c r="C117" s="22"/>
       <c r="D117" s="198">
         <v>8811.25</v>
@@ -5040,61 +5036,61 @@
       <c r="G120" s="30"/>
     </row>
     <row r="121" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A121" s="333" t="s">
-        <v>433</v>
-      </c>
-      <c r="B121" s="334"/>
+      <c r="A121" s="369" t="s">
+        <v>432</v>
+      </c>
+      <c r="B121" s="370"/>
       <c r="C121" s="22"/>
-      <c r="D121" s="419">
+      <c r="D121" s="337">
         <v>9914839.9499999993</v>
       </c>
       <c r="E121" s="78" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="F121" s="30"/>
       <c r="G121" s="30"/>
     </row>
     <row r="122" spans="1:7" ht="114" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A122" s="333" t="s">
-        <v>391</v>
-      </c>
-      <c r="B122" s="334"/>
+      <c r="A122" s="369" t="s">
+        <v>390</v>
+      </c>
+      <c r="B122" s="370"/>
       <c r="C122" s="22"/>
-      <c r="D122" s="419">
+      <c r="D122" s="337">
         <v>15917020</v>
       </c>
       <c r="E122" s="78" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="F122" s="30"/>
       <c r="G122" s="30"/>
     </row>
     <row r="123" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A123" s="335" t="s">
-        <v>430</v>
-      </c>
-      <c r="B123" s="336"/>
+      <c r="A123" s="341" t="s">
+        <v>429</v>
+      </c>
+      <c r="B123" s="343"/>
       <c r="C123" s="22"/>
-      <c r="D123" s="419">
+      <c r="D123" s="337">
         <v>8064666.6699999999</v>
       </c>
       <c r="E123" s="143" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="F123" s="30"/>
       <c r="G123" s="30"/>
     </row>
     <row r="124" spans="1:7" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A124" s="335" t="s">
-        <v>434</v>
-      </c>
-      <c r="B124" s="336"/>
+      <c r="A124" s="341" t="s">
+        <v>433</v>
+      </c>
+      <c r="B124" s="343"/>
       <c r="C124" s="22"/>
-      <c r="D124" s="419">
+      <c r="D124" s="337">
         <v>1071600</v>
       </c>
       <c r="E124" s="143" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="F124" s="30"/>
       <c r="G124" s="30"/>
@@ -5175,10 +5171,10 @@
       <c r="G131" s="30"/>
     </row>
     <row r="132" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A132" s="338" t="s">
-        <v>446</v>
-      </c>
-      <c r="B132" s="338"/>
+      <c r="A132" s="372" t="s">
+        <v>445</v>
+      </c>
+      <c r="B132" s="372"/>
       <c r="C132" s="22"/>
       <c r="D132" s="198">
         <f>2038428-1520000</f>
@@ -5192,8 +5188,8 @@
       <c r="G132" s="256"/>
     </row>
     <row r="133" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A133" s="335"/>
-      <c r="B133" s="336"/>
+      <c r="A133" s="341"/>
+      <c r="B133" s="343"/>
       <c r="C133" s="98"/>
       <c r="D133" s="198"/>
       <c r="E133" s="26"/>
@@ -5265,7 +5261,7 @@
       </c>
       <c r="B141" s="213">
         <f>E103</f>
-        <v>97974208.689999998</v>
+        <v>98028314.689999998</v>
       </c>
       <c r="C141" s="30"/>
       <c r="D141" s="30"/>
@@ -5301,7 +5297,7 @@
       </c>
       <c r="B144" s="215">
         <f>B143+B141</f>
-        <v>101328288.47</v>
+        <v>101382394.47</v>
       </c>
       <c r="C144" s="30"/>
       <c r="D144" s="30"/>
@@ -5309,11 +5305,11 @@
     </row>
     <row r="145" spans="1:6" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A145" s="268" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="B145" s="215">
         <f>SUM(B141:B143)</f>
-        <v>136296415.09</v>
+        <v>136350521.09</v>
       </c>
       <c r="C145" s="30"/>
       <c r="D145" s="30"/>
@@ -5352,7 +5348,7 @@
       </c>
       <c r="B150" s="151">
         <f>PRORRATEO!F161</f>
-        <v>106045133.38999999</v>
+        <v>106269033.38999999</v>
       </c>
       <c r="C150" s="152"/>
     </row>
@@ -5361,262 +5357,267 @@
         <v>239</v>
       </c>
       <c r="B151" s="153">
-        <f>B201</f>
+        <f>B199</f>
         <v>0</v>
       </c>
       <c r="C151" s="152"/>
       <c r="D151" s="149"/>
     </row>
-    <row r="152" spans="1:6" s="148" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:6" s="148" customFormat="1" ht="51.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A152" s="7" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="B152" s="154">
-        <v>-23004</v>
+        <v>-767774.04</v>
       </c>
       <c r="C152" s="152"/>
       <c r="D152" s="149"/>
     </row>
-    <row r="153" spans="1:6" s="148" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:6" s="148" customFormat="1" ht="33" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A153" s="7" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="B153" s="154">
-        <v>-31102</v>
+        <v>-223900</v>
       </c>
       <c r="C153" s="152"/>
       <c r="D153" s="149"/>
     </row>
-    <row r="154" spans="1:6" s="148" customFormat="1" ht="51.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:6" s="148" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A154" s="7" t="s">
-        <v>469</v>
-      </c>
-      <c r="B154" s="154">
-        <v>-767774.04</v>
+        <v>447</v>
+      </c>
+      <c r="B154" s="153">
+        <f>-B189</f>
+        <v>50026212.090000004</v>
       </c>
       <c r="C154" s="152"/>
       <c r="D154" s="149"/>
     </row>
-    <row r="155" spans="1:6" s="148" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A155" s="7" t="s">
-        <v>334</v>
+    <row r="155" spans="1:6" s="148" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A155" s="133" t="s">
+        <v>294</v>
       </c>
       <c r="B155" s="154">
+        <f>-B173</f>
         <v>0</v>
       </c>
       <c r="C155" s="152"/>
       <c r="D155" s="149"/>
     </row>
-    <row r="156" spans="1:6" s="148" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:6" s="148" customFormat="1" ht="28.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A156" s="7" t="s">
-        <v>448</v>
-      </c>
-      <c r="B156" s="153">
-        <f>-B191</f>
-        <v>50026212.090000004</v>
+        <v>325</v>
+      </c>
+      <c r="B156" s="154">
+        <f>-B166</f>
+        <v>-904780.93536280002</v>
       </c>
       <c r="C156" s="152"/>
       <c r="D156" s="149"/>
     </row>
-    <row r="157" spans="1:6" s="148" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A157" s="133" t="s">
-        <v>294</v>
+    <row r="157" spans="1:6" s="148" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A157" s="32" t="s">
+        <v>186</v>
       </c>
       <c r="B157" s="154">
-        <f>-B175</f>
-        <v>0</v>
-      </c>
-      <c r="C157" s="152"/>
-      <c r="D157" s="149"/>
-    </row>
-    <row r="158" spans="1:6" s="148" customFormat="1" ht="28.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A158" s="7" t="s">
-        <v>325</v>
-      </c>
-      <c r="B158" s="154">
-        <f>-B168</f>
-        <v>-904780.93536280002</v>
-      </c>
-      <c r="C158" s="152"/>
-      <c r="D158" s="149"/>
-    </row>
-    <row r="159" spans="1:6" s="148" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A159" s="32" t="s">
-        <v>186</v>
-      </c>
-      <c r="B159" s="154">
         <f>-E138</f>
         <v>-518428</v>
       </c>
+      <c r="C157" s="152"/>
+      <c r="F157" s="155"/>
+    </row>
+    <row r="158" spans="1:6" s="148" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A158" s="7" t="s">
+        <v>152</v>
+      </c>
+      <c r="B158" s="154">
+        <f>-E118</f>
+        <v>-3354079.7800000003</v>
+      </c>
+      <c r="C158" s="152"/>
+      <c r="D158" s="155"/>
+    </row>
+    <row r="159" spans="1:6" s="148" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A159" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="B159" s="154">
+        <f>-E103</f>
+        <v>-98028314.689999998</v>
+      </c>
       <c r="C159" s="152"/>
-      <c r="F159" s="155"/>
+      <c r="D159" s="156"/>
+      <c r="E159" s="156"/>
+      <c r="F159" s="228"/>
     </row>
     <row r="160" spans="1:6" s="148" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A160" s="7" t="s">
-        <v>152</v>
+        <v>257</v>
       </c>
       <c r="B160" s="154">
-        <f>-E118</f>
-        <v>-3354079.7800000003</v>
-      </c>
-      <c r="C160" s="152"/>
-      <c r="D160" s="155"/>
-    </row>
-    <row r="161" spans="1:7" s="148" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A161" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="B161" s="154">
-        <f>-E103</f>
-        <v>-97974208.689999998</v>
-      </c>
-      <c r="C161" s="152"/>
-      <c r="D161" s="156"/>
-      <c r="E161" s="156"/>
-      <c r="F161" s="228"/>
-    </row>
-    <row r="162" spans="1:7" s="148" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A162" s="7" t="s">
-        <v>257</v>
-      </c>
-      <c r="B162" s="154">
         <f>-E129</f>
         <v>-34968126.619999997</v>
       </c>
-      <c r="C162" s="152"/>
-      <c r="E162" s="156"/>
-      <c r="F162" s="228"/>
-    </row>
-    <row r="163" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A163" s="131" t="s">
+      <c r="C160" s="152"/>
+      <c r="E160" s="156"/>
+      <c r="F160" s="228"/>
+    </row>
+    <row r="161" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A161" s="131" t="s">
         <v>4</v>
       </c>
-      <c r="B163" s="36">
-        <f>SUM(B149:B162)</f>
+      <c r="B161" s="36">
+        <f>SUM(B149:B160)</f>
         <v>26580407.381798334</v>
       </c>
+      <c r="C161" s="6"/>
+      <c r="D161" s="13"/>
+      <c r="E161" s="37"/>
+      <c r="F161" s="37"/>
+    </row>
+    <row r="162" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A162" s="132"/>
+      <c r="B162" s="11"/>
+      <c r="C162" s="6"/>
+      <c r="D162" s="13"/>
+      <c r="E162" s="34"/>
+      <c r="F162" s="74"/>
+    </row>
+    <row r="163" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A163" s="132"/>
+      <c r="B163" s="11"/>
       <c r="C163" s="6"/>
       <c r="D163" s="13"/>
-      <c r="E163" s="37"/>
-      <c r="F163" s="37"/>
+      <c r="E163" s="34"/>
+      <c r="F163" s="74"/>
     </row>
     <row r="164" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A164" s="132"/>
-      <c r="B164" s="11"/>
+      <c r="A164" s="375" t="s">
+        <v>326</v>
+      </c>
+      <c r="B164" s="376"/>
       <c r="C164" s="6"/>
       <c r="D164" s="13"/>
       <c r="E164" s="34"/>
       <c r="F164" s="74"/>
     </row>
-    <row r="165" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A165" s="132"/>
-      <c r="B165" s="11"/>
+    <row r="165" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A165" s="126" t="s">
+        <v>293</v>
+      </c>
+      <c r="B165" s="127">
+        <v>5509776.7375908</v>
+      </c>
       <c r="C165" s="6"/>
       <c r="D165" s="13"/>
       <c r="E165" s="34"/>
       <c r="F165" s="74"/>
     </row>
-    <row r="166" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A166" s="341" t="s">
-        <v>326</v>
-      </c>
-      <c r="B166" s="342"/>
+    <row r="166" spans="1:7" ht="66.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A166" s="232" t="s">
+        <v>327</v>
+      </c>
+      <c r="B166" s="191">
+        <f>1809561.8707256/2</f>
+        <v>904780.93536280002</v>
+      </c>
       <c r="C166" s="6"/>
       <c r="D166" s="13"/>
       <c r="E166" s="34"/>
       <c r="F166" s="74"/>
     </row>
-    <row r="167" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A167" s="126" t="s">
-        <v>293</v>
-      </c>
-      <c r="B167" s="127">
-        <v>5509776.7375908</v>
-      </c>
+    <row r="167" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A167" s="126"/>
+      <c r="B167" s="127"/>
       <c r="C167" s="6"/>
       <c r="D167" s="13"/>
       <c r="E167" s="34"/>
       <c r="F167" s="74"/>
     </row>
-    <row r="168" spans="1:7" ht="66.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A168" s="232" t="s">
-        <v>327</v>
-      </c>
-      <c r="B168" s="191">
-        <f>1809561.8707256/2</f>
-        <v>904780.93536280002</v>
+    <row r="168" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A168" s="233" t="s">
+        <v>4</v>
+      </c>
+      <c r="B168" s="234">
+        <f>SUM(B165:B167)</f>
+        <v>6414557.6729536001</v>
       </c>
       <c r="C168" s="6"/>
       <c r="D168" s="13"/>
       <c r="E168" s="34"/>
       <c r="F168" s="74"/>
     </row>
-    <row r="169" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A169" s="126"/>
-      <c r="B169" s="127"/>
+    <row r="169" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A169" s="132"/>
+      <c r="B169" s="11"/>
       <c r="C169" s="6"/>
       <c r="D169" s="13"/>
       <c r="E169" s="34"/>
       <c r="F169" s="74"/>
     </row>
     <row r="170" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A170" s="233" t="s">
-        <v>4</v>
-      </c>
-      <c r="B170" s="234">
-        <f>SUM(B167:B169)</f>
-        <v>6414557.6729536001</v>
-      </c>
+      <c r="A170" s="132"/>
+      <c r="B170" s="11"/>
       <c r="C170" s="6"/>
       <c r="D170" s="13"/>
       <c r="E170" s="34"/>
       <c r="F170" s="74"/>
     </row>
     <row r="171" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A171" s="132"/>
-      <c r="B171" s="11"/>
+      <c r="A171" s="373" t="s">
+        <v>292</v>
+      </c>
+      <c r="B171" s="374"/>
       <c r="C171" s="6"/>
       <c r="D171" s="13"/>
       <c r="E171" s="34"/>
       <c r="F171" s="74"/>
-    </row>
-    <row r="172" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A172" s="132"/>
-      <c r="B172" s="11"/>
+      <c r="G171" s="229"/>
+    </row>
+    <row r="172" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A172" s="126" t="s">
+        <v>293</v>
+      </c>
+      <c r="B172" s="127">
+        <v>4607864.5312480005</v>
+      </c>
       <c r="C172" s="6"/>
       <c r="D172" s="13"/>
       <c r="E172" s="34"/>
       <c r="F172" s="74"/>
     </row>
     <row r="173" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A173" s="339" t="s">
-        <v>292</v>
-      </c>
-      <c r="B173" s="340"/>
+      <c r="A173" s="126" t="s">
+        <v>294</v>
+      </c>
+      <c r="B173" s="191">
+        <v>0</v>
+      </c>
       <c r="C173" s="6"/>
       <c r="D173" s="13"/>
       <c r="E173" s="34"/>
       <c r="F173" s="74"/>
-      <c r="G173" s="229"/>
-    </row>
-    <row r="174" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="174" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A174" s="126" t="s">
-        <v>293</v>
+        <v>341</v>
       </c>
       <c r="B174" s="127">
-        <v>4607864.5312480005</v>
+        <v>0</v>
       </c>
       <c r="C174" s="6"/>
       <c r="D174" s="13"/>
       <c r="E174" s="34"/>
       <c r="F174" s="74"/>
     </row>
-    <row r="175" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A175" s="126" t="s">
-        <v>294</v>
-      </c>
-      <c r="B175" s="191">
-        <v>0</v>
+    <row r="175" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A175" s="128" t="s">
+        <v>4</v>
+      </c>
+      <c r="B175" s="129">
+        <f>SUM(B172:B174)</f>
+        <v>4607864.5312480005</v>
       </c>
       <c r="C175" s="6"/>
       <c r="D175" s="13"/>
@@ -5624,64 +5625,63 @@
       <c r="F175" s="74"/>
     </row>
     <row r="176" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A176" s="126" t="s">
-        <v>342</v>
-      </c>
-      <c r="B176" s="127">
-        <v>0</v>
-      </c>
+      <c r="A176" s="124"/>
+      <c r="B176" s="125"/>
       <c r="C176" s="6"/>
       <c r="D176" s="13"/>
       <c r="E176" s="34"/>
       <c r="F176" s="74"/>
     </row>
-    <row r="177" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A177" s="128" t="s">
-        <v>4</v>
-      </c>
-      <c r="B177" s="129">
-        <f>SUM(B174:B176)</f>
-        <v>4607864.5312480005</v>
+    <row r="177" spans="1:15" ht="42.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A177" s="140" t="s">
+        <v>329</v>
+      </c>
+      <c r="B177" s="139">
+        <f>B175+B161+B168</f>
+        <v>37602829.585999936</v>
       </c>
       <c r="C177" s="6"/>
       <c r="D177" s="13"/>
       <c r="E177" s="34"/>
       <c r="F177" s="74"/>
-    </row>
-    <row r="178" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A178" s="124"/>
-      <c r="B178" s="125"/>
+      <c r="G177" s="35"/>
+    </row>
+    <row r="178" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="B178" s="11"/>
       <c r="C178" s="6"/>
       <c r="D178" s="13"/>
       <c r="E178" s="34"/>
       <c r="F178" s="74"/>
     </row>
-    <row r="179" spans="1:15" ht="42.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A179" s="140" t="s">
-        <v>329</v>
-      </c>
-      <c r="B179" s="139">
-        <f>B177+B163+B170</f>
-        <v>37602829.585999936</v>
-      </c>
+    <row r="179" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A179" s="69" t="s">
+        <v>233</v>
+      </c>
+      <c r="B179" s="70"/>
       <c r="C179" s="6"/>
       <c r="D179" s="13"/>
       <c r="E179" s="34"/>
-      <c r="F179" s="74"/>
-      <c r="G179" s="35"/>
-    </row>
-    <row r="180" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="B180" s="11"/>
+      <c r="F179" s="35"/>
+    </row>
+    <row r="180" spans="1:15" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A180" s="88" t="s">
+        <v>293</v>
+      </c>
+      <c r="B180" s="134">
+        <v>30172.5</v>
+      </c>
       <c r="C180" s="6"/>
       <c r="D180" s="13"/>
       <c r="E180" s="34"/>
-      <c r="F180" s="74"/>
-    </row>
-    <row r="181" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A181" s="69" t="s">
-        <v>233</v>
-      </c>
-      <c r="B181" s="70"/>
+      <c r="F180" s="35"/>
+    </row>
+    <row r="181" spans="1:15" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A181" s="88" t="s">
+        <v>453</v>
+      </c>
+      <c r="B181" s="244">
+        <v>-4400</v>
+      </c>
       <c r="C181" s="6"/>
       <c r="D181" s="13"/>
       <c r="E181" s="34"/>
@@ -5689,22 +5689,22 @@
     </row>
     <row r="182" spans="1:15" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A182" s="88" t="s">
-        <v>293</v>
-      </c>
-      <c r="B182" s="134">
-        <v>30172.5</v>
+        <v>459</v>
+      </c>
+      <c r="B182" s="244">
+        <v>-7800</v>
       </c>
       <c r="C182" s="6"/>
       <c r="D182" s="13"/>
       <c r="E182" s="34"/>
       <c r="F182" s="35"/>
     </row>
-    <row r="183" spans="1:15" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:15" ht="51.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A183" s="88" t="s">
-        <v>454</v>
+        <v>463</v>
       </c>
       <c r="B183" s="244">
-        <v>-4400</v>
+        <v>-133200</v>
       </c>
       <c r="C183" s="6"/>
       <c r="D183" s="13"/>
@@ -5713,63 +5713,81 @@
     </row>
     <row r="184" spans="1:15" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A184" s="88" t="s">
-        <v>460</v>
-      </c>
-      <c r="B184" s="244">
-        <v>-7800</v>
-      </c>
+        <v>309</v>
+      </c>
+      <c r="B184" s="198"/>
       <c r="C184" s="6"/>
       <c r="D184" s="13"/>
       <c r="E184" s="34"/>
       <c r="F184" s="35"/>
     </row>
-    <row r="185" spans="1:15" ht="51.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A185" s="88" t="s">
-        <v>464</v>
-      </c>
-      <c r="B185" s="244">
-        <v>-133200</v>
+    <row r="185" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A185" s="69" t="s">
+        <v>4</v>
+      </c>
+      <c r="B185" s="70">
+        <f>SUM(B179:B184)</f>
+        <v>-115227.5</v>
       </c>
       <c r="C185" s="6"/>
       <c r="D185" s="13"/>
       <c r="E185" s="34"/>
       <c r="F185" s="35"/>
     </row>
-    <row r="186" spans="1:15" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A186" s="88" t="s">
-        <v>309</v>
-      </c>
-      <c r="B186" s="198"/>
+    <row r="186" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B186" s="11"/>
       <c r="C186" s="6"/>
       <c r="D186" s="13"/>
       <c r="E186" s="34"/>
       <c r="F186" s="35"/>
     </row>
     <row r="187" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A187" s="69" t="s">
-        <v>4</v>
-      </c>
-      <c r="B187" s="70">
-        <f>SUM(B181:B186)</f>
-        <v>-115227.5</v>
-      </c>
+      <c r="A187" s="122" t="s">
+        <v>228</v>
+      </c>
+      <c r="B187" s="65"/>
       <c r="C187" s="6"/>
-      <c r="D187" s="13"/>
-      <c r="E187" s="34"/>
-      <c r="F187" s="35"/>
-    </row>
-    <row r="188" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B188" s="11"/>
+      <c r="D187" s="73"/>
+      <c r="E187" s="137"/>
+      <c r="F187" s="138"/>
+      <c r="G187" s="33"/>
+      <c r="H187" s="33"/>
+      <c r="I187" s="33"/>
+      <c r="J187" s="33"/>
+      <c r="K187" s="33"/>
+      <c r="L187" s="33"/>
+      <c r="M187" s="33"/>
+      <c r="N187" s="33"/>
+      <c r="O187" s="33"/>
+    </row>
+    <row r="188" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A188" s="67" t="s">
+        <v>340</v>
+      </c>
+      <c r="B188" s="68">
+        <v>154917250.19</v>
+      </c>
       <c r="C188" s="6"/>
-      <c r="D188" s="13"/>
-      <c r="E188" s="34"/>
-      <c r="F188" s="35"/>
+      <c r="D188" s="73"/>
+      <c r="E188" s="137"/>
+      <c r="F188" s="138"/>
+      <c r="G188" s="33"/>
+      <c r="H188" s="33"/>
+      <c r="I188" s="33"/>
+      <c r="J188" s="33"/>
+      <c r="K188" s="33"/>
+      <c r="L188" s="33"/>
+      <c r="M188" s="33"/>
+      <c r="N188" s="33"/>
+      <c r="O188" s="33"/>
     </row>
     <row r="189" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A189" s="122" t="s">
-        <v>228</v>
-      </c>
-      <c r="B189" s="65"/>
+      <c r="A189" s="67" t="s">
+        <v>465</v>
+      </c>
+      <c r="B189" s="267">
+        <v>-50026212.090000004</v>
+      </c>
       <c r="C189" s="6"/>
       <c r="D189" s="73"/>
       <c r="E189" s="137"/>
@@ -5786,10 +5804,10 @@
     </row>
     <row r="190" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A190" s="67" t="s">
-        <v>341</v>
+        <v>466</v>
       </c>
       <c r="B190" s="68">
-        <v>154917250.19</v>
+        <v>4016377.55</v>
       </c>
       <c r="C190" s="6"/>
       <c r="D190" s="73"/>
@@ -5805,12 +5823,12 @@
       <c r="N190" s="33"/>
       <c r="O190" s="33"/>
     </row>
-    <row r="191" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A191" s="67" t="s">
-        <v>467</v>
-      </c>
-      <c r="B191" s="267">
-        <v>-50026212.090000004</v>
+    <row r="191" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A191" s="123" t="s">
+        <v>464</v>
+      </c>
+      <c r="B191" s="249">
+        <v>106403918.55</v>
       </c>
       <c r="C191" s="6"/>
       <c r="D191" s="73"/>
@@ -5827,12 +5845,7 @@
       <c r="O191" s="33"/>
     </row>
     <row r="192" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A192" s="67" t="s">
-        <v>468</v>
-      </c>
-      <c r="B192" s="68">
-        <v>4016377.55</v>
-      </c>
+      <c r="B192" s="11"/>
       <c r="C192" s="6"/>
       <c r="D192" s="73"/>
       <c r="E192" s="137"/>
@@ -5847,94 +5860,117 @@
       <c r="N192" s="33"/>
       <c r="O192" s="33"/>
     </row>
-    <row r="193" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A193" s="123" t="s">
-        <v>465</v>
-      </c>
-      <c r="B193" s="249">
-        <v>106403918.55</v>
-      </c>
+    <row r="193" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="B193" s="11"/>
       <c r="C193" s="6"/>
-      <c r="D193" s="73"/>
-      <c r="E193" s="137"/>
-      <c r="F193" s="138"/>
-      <c r="G193" s="33"/>
-      <c r="H193" s="33"/>
-      <c r="I193" s="33"/>
-      <c r="J193" s="33"/>
-      <c r="K193" s="33"/>
-      <c r="L193" s="33"/>
-      <c r="M193" s="33"/>
-      <c r="N193" s="33"/>
-      <c r="O193" s="33"/>
-    </row>
-    <row r="194" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="D193" s="13"/>
+      <c r="E193" s="34"/>
+      <c r="F193" s="35"/>
+    </row>
+    <row r="194" spans="1:13" x14ac:dyDescent="0.25">
       <c r="B194" s="11"/>
       <c r="C194" s="6"/>
-      <c r="D194" s="73"/>
-      <c r="E194" s="137"/>
-      <c r="F194" s="138"/>
-      <c r="G194" s="33"/>
-      <c r="H194" s="33"/>
-      <c r="I194" s="33"/>
-      <c r="J194" s="33"/>
-      <c r="K194" s="33"/>
-      <c r="L194" s="33"/>
-      <c r="M194" s="33"/>
-      <c r="N194" s="33"/>
-      <c r="O194" s="33"/>
-    </row>
-    <row r="195" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="B195" s="11"/>
-      <c r="C195" s="6"/>
-      <c r="D195" s="13"/>
-      <c r="E195" s="34"/>
-      <c r="F195" s="35"/>
-    </row>
-    <row r="196" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="B196" s="11"/>
-      <c r="C196" s="6"/>
-      <c r="D196" s="13"/>
-      <c r="E196" s="34"/>
-      <c r="F196" s="35"/>
-    </row>
-    <row r="197" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A197" s="337" t="s">
+      <c r="D194" s="13"/>
+      <c r="E194" s="34"/>
+      <c r="F194" s="35"/>
+    </row>
+    <row r="195" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A195" s="371" t="s">
         <v>17</v>
       </c>
-      <c r="B197" s="337"/>
-      <c r="C197" s="337"/>
-    </row>
-    <row r="198" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A198" s="337"/>
-      <c r="B198" s="337"/>
-      <c r="C198" s="337"/>
-    </row>
-    <row r="199" spans="1:15" ht="42" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A199" s="63"/>
-      <c r="B199" s="39"/>
-      <c r="C199" s="62"/>
-    </row>
-    <row r="200" spans="1:15" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A200" s="63"/>
-      <c r="B200" s="39"/>
-      <c r="C200" s="62"/>
-    </row>
-    <row r="201" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A201" s="14" t="s">
+      <c r="B195" s="371"/>
+      <c r="C195" s="371"/>
+    </row>
+    <row r="196" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A196" s="371"/>
+      <c r="B196" s="371"/>
+      <c r="C196" s="371"/>
+    </row>
+    <row r="197" spans="1:13" ht="42" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A197" s="63"/>
+      <c r="B197" s="39"/>
+      <c r="C197" s="62"/>
+    </row>
+    <row r="198" spans="1:13" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A198" s="63"/>
+      <c r="B198" s="39"/>
+      <c r="C198" s="62"/>
+    </row>
+    <row r="199" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A199" s="14" t="s">
         <v>4</v>
       </c>
-      <c r="B201" s="31">
-        <f>SUM(B199:B200)</f>
-        <v>0</v>
-      </c>
-      <c r="C201" s="15"/>
-    </row>
-    <row r="202" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="M202" s="3"/>
+      <c r="B199" s="31">
+        <f>SUM(B197:B198)</f>
+        <v>0</v>
+      </c>
+      <c r="C199" s="15"/>
+    </row>
+    <row r="200" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="M200" s="3"/>
     </row>
   </sheetData>
   <mergeCells count="76">
+    <mergeCell ref="A75:B75"/>
+    <mergeCell ref="A80:B80"/>
+    <mergeCell ref="A59:B59"/>
+    <mergeCell ref="A60:B60"/>
+    <mergeCell ref="A95:B95"/>
+    <mergeCell ref="A84:B84"/>
+    <mergeCell ref="A86:B86"/>
+    <mergeCell ref="A87:B87"/>
+    <mergeCell ref="A90:B90"/>
+    <mergeCell ref="A94:B94"/>
+    <mergeCell ref="A68:B68"/>
+    <mergeCell ref="A61:B61"/>
+    <mergeCell ref="A69:B69"/>
+    <mergeCell ref="A57:B57"/>
+    <mergeCell ref="A52:B52"/>
+    <mergeCell ref="A65:B65"/>
+    <mergeCell ref="A54:B54"/>
+    <mergeCell ref="A53:B53"/>
+    <mergeCell ref="A55:B55"/>
+    <mergeCell ref="A58:B58"/>
+    <mergeCell ref="A62:B62"/>
+    <mergeCell ref="A56:B56"/>
+    <mergeCell ref="A108:B108"/>
+    <mergeCell ref="A109:B109"/>
+    <mergeCell ref="A110:B110"/>
+    <mergeCell ref="A107:B107"/>
+    <mergeCell ref="A113:B113"/>
+    <mergeCell ref="A112:B112"/>
+    <mergeCell ref="A111:B111"/>
+    <mergeCell ref="A114:B114"/>
+    <mergeCell ref="A195:C196"/>
+    <mergeCell ref="A132:B132"/>
+    <mergeCell ref="A171:B171"/>
+    <mergeCell ref="A133:B133"/>
+    <mergeCell ref="A164:B164"/>
+    <mergeCell ref="A123:B123"/>
+    <mergeCell ref="A124:B124"/>
+    <mergeCell ref="A122:B122"/>
+    <mergeCell ref="A121:B121"/>
+    <mergeCell ref="A115:B115"/>
+    <mergeCell ref="A117:B117"/>
+    <mergeCell ref="A116:B116"/>
+    <mergeCell ref="A10:E12"/>
+    <mergeCell ref="A15:E18"/>
+    <mergeCell ref="A44:B44"/>
+    <mergeCell ref="A25:B25"/>
+    <mergeCell ref="A26:B26"/>
+    <mergeCell ref="A28:B28"/>
+    <mergeCell ref="A40:B40"/>
+    <mergeCell ref="B3:E3"/>
+    <mergeCell ref="B1:E1"/>
+    <mergeCell ref="B2:E2"/>
+    <mergeCell ref="B8:E8"/>
+    <mergeCell ref="A1:A8"/>
+    <mergeCell ref="A48:B48"/>
+    <mergeCell ref="A38:B38"/>
+    <mergeCell ref="A45:B45"/>
+    <mergeCell ref="A49:B49"/>
+    <mergeCell ref="A41:B41"/>
+    <mergeCell ref="A39:B39"/>
     <mergeCell ref="A50:B50"/>
     <mergeCell ref="A91:B91"/>
     <mergeCell ref="A83:B83"/>
@@ -5950,67 +5986,7 @@
     <mergeCell ref="A79:B79"/>
     <mergeCell ref="A66:C66"/>
     <mergeCell ref="A67:C67"/>
-    <mergeCell ref="A48:B48"/>
-    <mergeCell ref="A38:B38"/>
-    <mergeCell ref="A45:B45"/>
-    <mergeCell ref="A49:B49"/>
-    <mergeCell ref="A41:B41"/>
-    <mergeCell ref="A39:B39"/>
-    <mergeCell ref="B3:E3"/>
-    <mergeCell ref="B1:E1"/>
-    <mergeCell ref="B2:E2"/>
-    <mergeCell ref="B8:E8"/>
-    <mergeCell ref="A1:A8"/>
-    <mergeCell ref="A10:E12"/>
-    <mergeCell ref="A15:E18"/>
-    <mergeCell ref="A44:B44"/>
-    <mergeCell ref="A25:B25"/>
-    <mergeCell ref="A26:B26"/>
-    <mergeCell ref="A28:B28"/>
-    <mergeCell ref="A40:B40"/>
-    <mergeCell ref="A114:B114"/>
-    <mergeCell ref="A197:C198"/>
-    <mergeCell ref="A132:B132"/>
-    <mergeCell ref="A173:B173"/>
-    <mergeCell ref="A133:B133"/>
-    <mergeCell ref="A166:B166"/>
-    <mergeCell ref="A123:B123"/>
-    <mergeCell ref="A124:B124"/>
-    <mergeCell ref="A108:B108"/>
-    <mergeCell ref="A109:B109"/>
-    <mergeCell ref="A110:B110"/>
-    <mergeCell ref="A107:B107"/>
-    <mergeCell ref="A113:B113"/>
-    <mergeCell ref="A112:B112"/>
     <mergeCell ref="A51:B51"/>
-    <mergeCell ref="A68:B68"/>
-    <mergeCell ref="A61:B61"/>
-    <mergeCell ref="A69:B69"/>
-    <mergeCell ref="A57:B57"/>
-    <mergeCell ref="A52:B52"/>
-    <mergeCell ref="A65:B65"/>
-    <mergeCell ref="A54:B54"/>
-    <mergeCell ref="A53:B53"/>
-    <mergeCell ref="A55:B55"/>
-    <mergeCell ref="A58:B58"/>
-    <mergeCell ref="A62:B62"/>
-    <mergeCell ref="A56:B56"/>
-    <mergeCell ref="A122:B122"/>
-    <mergeCell ref="A75:B75"/>
-    <mergeCell ref="A80:B80"/>
-    <mergeCell ref="A59:B59"/>
-    <mergeCell ref="A60:B60"/>
-    <mergeCell ref="A95:B95"/>
-    <mergeCell ref="A121:B121"/>
-    <mergeCell ref="A84:B84"/>
-    <mergeCell ref="A86:B86"/>
-    <mergeCell ref="A87:B87"/>
-    <mergeCell ref="A90:B90"/>
-    <mergeCell ref="A115:B115"/>
-    <mergeCell ref="A117:B117"/>
-    <mergeCell ref="A111:B111"/>
-    <mergeCell ref="A116:B116"/>
-    <mergeCell ref="A94:B94"/>
   </mergeCells>
   <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup paperSize="3" scale="115" orientation="portrait" r:id="rId1"/>
@@ -6050,27 +6026,27 @@
     <row r="1" spans="1:24" ht="251.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="2"/>
       <c r="B1" s="2"/>
-      <c r="C1" s="382" t="s">
-        <v>471</v>
-      </c>
-      <c r="D1" s="383"/>
-      <c r="E1" s="383"/>
-      <c r="F1" s="383"/>
-      <c r="G1" s="383"/>
-      <c r="H1" s="383"/>
-      <c r="I1" s="383"/>
-      <c r="J1" s="383"/>
-      <c r="K1" s="383"/>
-      <c r="L1" s="383"/>
+      <c r="C1" s="388" t="s">
+        <v>468</v>
+      </c>
+      <c r="D1" s="389"/>
+      <c r="E1" s="389"/>
+      <c r="F1" s="389"/>
+      <c r="G1" s="389"/>
+      <c r="H1" s="389"/>
+      <c r="I1" s="389"/>
+      <c r="J1" s="389"/>
+      <c r="K1" s="389"/>
+      <c r="L1" s="389"/>
       <c r="M1" s="142"/>
-      <c r="N1" s="384" t="s">
+      <c r="N1" s="390" t="s">
         <v>310</v>
       </c>
-      <c r="O1" s="384"/>
-      <c r="P1" s="379">
+      <c r="O1" s="390"/>
+      <c r="P1" s="385">
         <v>30000000</v>
       </c>
-      <c r="Q1" s="379"/>
+      <c r="Q1" s="385"/>
       <c r="R1" s="164"/>
       <c r="S1" s="4"/>
       <c r="T1" s="2"/>
@@ -6084,35 +6060,35 @@
     <row r="2" spans="1:24" ht="34.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="2"/>
       <c r="B2" s="2"/>
-      <c r="C2" s="381" t="s">
+      <c r="C2" s="387" t="s">
         <v>226</v>
       </c>
-      <c r="D2" s="381"/>
-      <c r="E2" s="381"/>
+      <c r="D2" s="387"/>
+      <c r="E2" s="387"/>
       <c r="F2" s="142"/>
-      <c r="G2" s="376">
+      <c r="G2" s="384">
         <f>X2</f>
         <v>27518571.293111999</v>
       </c>
-      <c r="H2" s="376"/>
+      <c r="H2" s="384"/>
       <c r="I2" s="142" t="s">
         <v>274</v>
       </c>
       <c r="J2" s="142"/>
-      <c r="K2" s="376">
+      <c r="K2" s="384">
         <f>W1</f>
         <v>80675963.920000002</v>
       </c>
-      <c r="L2" s="376"/>
+      <c r="L2" s="384"/>
       <c r="M2" s="224"/>
       <c r="N2" s="225" t="s">
         <v>260</v>
       </c>
       <c r="O2" s="224"/>
-      <c r="P2" s="380">
-        <v>0</v>
-      </c>
-      <c r="Q2" s="380"/>
+      <c r="P2" s="386">
+        <v>0</v>
+      </c>
+      <c r="Q2" s="386"/>
       <c r="R2" s="165"/>
       <c r="T2" s="2"/>
       <c r="U2" t="s">
@@ -6124,51 +6100,51 @@
       </c>
     </row>
     <row r="3" spans="1:24" ht="91.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="389" t="str">
+      <c r="A3" s="395" t="str">
         <f>"ATENCIÓN: Si usted abona antes del " &amp; TEXT(RESUMEN!A10,"dd/mm/yyyy") &amp; ", deberá abonar el importe indicado en la columna de color naranja. En caso de abonar con posterioridad a dicha fecha, deberá abonar el monto indicado en la columna de color celeste."</f>
         <v>ATENCIÓN: Si usted abona antes del Primer Vencimiento:  17/08, deberá abonar el importe indicado en la columna de color naranja. En caso de abonar con posterioridad a dicha fecha, deberá abonar el monto indicado en la columna de color celeste.</v>
       </c>
-      <c r="B3" s="390"/>
-      <c r="C3" s="390"/>
-      <c r="D3" s="390"/>
-      <c r="E3" s="390"/>
-      <c r="F3" s="390"/>
-      <c r="G3" s="390"/>
-      <c r="H3" s="390"/>
-      <c r="I3" s="390"/>
-      <c r="J3" s="390"/>
-      <c r="K3" s="390"/>
-      <c r="L3" s="390"/>
-      <c r="M3" s="390"/>
-      <c r="N3" s="390"/>
-      <c r="O3" s="390"/>
-      <c r="P3" s="390"/>
-      <c r="Q3" s="390"/>
-      <c r="R3" s="390"/>
-      <c r="S3" s="390"/>
-      <c r="T3" s="391"/>
+      <c r="B3" s="396"/>
+      <c r="C3" s="396"/>
+      <c r="D3" s="396"/>
+      <c r="E3" s="396"/>
+      <c r="F3" s="396"/>
+      <c r="G3" s="396"/>
+      <c r="H3" s="396"/>
+      <c r="I3" s="396"/>
+      <c r="J3" s="396"/>
+      <c r="K3" s="396"/>
+      <c r="L3" s="396"/>
+      <c r="M3" s="396"/>
+      <c r="N3" s="396"/>
+      <c r="O3" s="396"/>
+      <c r="P3" s="396"/>
+      <c r="Q3" s="396"/>
+      <c r="R3" s="396"/>
+      <c r="S3" s="396"/>
+      <c r="T3" s="397"/>
       <c r="X3" s="37"/>
     </row>
     <row r="4" spans="1:24" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="392" t="s">
-        <v>0</v>
-      </c>
-      <c r="B4" s="394" t="s">
+      <c r="A4" s="398" t="s">
+        <v>0</v>
+      </c>
+      <c r="B4" s="400" t="s">
         <v>1</v>
       </c>
-      <c r="C4" s="394" t="s">
+      <c r="C4" s="400" t="s">
         <v>2</v>
       </c>
-      <c r="D4" s="394" t="s">
+      <c r="D4" s="400" t="s">
         <v>6</v>
       </c>
       <c r="E4" s="377" t="s">
         <v>181</v>
       </c>
-      <c r="F4" s="394" t="s">
+      <c r="F4" s="400" t="s">
         <v>3</v>
       </c>
-      <c r="G4" s="396" t="s">
+      <c r="G4" s="402" t="s">
         <v>16</v>
       </c>
       <c r="H4" s="377" t="s">
@@ -6193,27 +6169,27 @@
       <c r="O4" s="377" t="s">
         <v>320</v>
       </c>
-      <c r="P4" s="385" t="s">
+      <c r="P4" s="391" t="s">
         <v>318</v>
       </c>
-      <c r="Q4" s="386"/>
-      <c r="R4" s="385" t="s">
+      <c r="Q4" s="392"/>
+      <c r="R4" s="391" t="s">
         <v>313</v>
       </c>
-      <c r="S4" s="386"/>
+      <c r="S4" s="392"/>
       <c r="T4" s="377" t="s">
         <v>258</v>
       </c>
       <c r="U4" s="13"/>
     </row>
     <row r="5" spans="1:24" ht="25.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="393"/>
-      <c r="B5" s="395"/>
-      <c r="C5" s="395"/>
-      <c r="D5" s="395"/>
+      <c r="A5" s="399"/>
+      <c r="B5" s="401"/>
+      <c r="C5" s="401"/>
+      <c r="D5" s="401"/>
       <c r="E5" s="378"/>
-      <c r="F5" s="395"/>
-      <c r="G5" s="397"/>
+      <c r="F5" s="401"/>
+      <c r="G5" s="403"/>
       <c r="H5" s="378"/>
       <c r="I5" s="378"/>
       <c r="J5" s="378"/>
@@ -6222,13 +6198,13 @@
       <c r="M5" s="378"/>
       <c r="N5" s="378"/>
       <c r="O5" s="378"/>
-      <c r="P5" s="387" t="str">
+      <c r="P5" s="393" t="str">
         <f>RESUMEN!A10</f>
         <v>Primer Vencimiento:  17/08</v>
       </c>
-      <c r="Q5" s="388"/>
-      <c r="R5" s="387"/>
-      <c r="S5" s="388"/>
+      <c r="Q5" s="394"/>
+      <c r="R5" s="393"/>
+      <c r="S5" s="394"/>
       <c r="T5" s="378"/>
     </row>
     <row r="6" spans="1:24" ht="26.45" customHeight="1" x14ac:dyDescent="0.25">
@@ -6282,11 +6258,11 @@
       <c r="O6" s="185">
         <v>0</v>
       </c>
-      <c r="P6" s="398">
+      <c r="P6" s="379">
         <f t="shared" ref="P6:P37" si="2">ROUND(SUM(G6:O6),0) + S6</f>
         <v>759748.01</v>
       </c>
-      <c r="Q6" s="399"/>
+      <c r="Q6" s="380"/>
       <c r="R6" s="226">
         <f t="shared" ref="R6:R37" si="3">ROUND(P6+P6*3.033%,0) + S6</f>
         <v>782791.01</v>
@@ -6352,11 +6328,11 @@
       <c r="O7" s="185">
         <v>0</v>
       </c>
-      <c r="P7" s="400">
+      <c r="P7" s="381">
         <f t="shared" si="2"/>
         <v>3658299.02</v>
       </c>
-      <c r="Q7" s="401"/>
+      <c r="Q7" s="382"/>
       <c r="R7" s="226">
         <f t="shared" si="3"/>
         <v>3769255.02</v>
@@ -6421,11 +6397,11 @@
       <c r="O8" s="185">
         <v>0</v>
       </c>
-      <c r="P8" s="369">
+      <c r="P8" s="383">
         <f t="shared" si="2"/>
         <v>737362.03</v>
       </c>
-      <c r="Q8" s="369"/>
+      <c r="Q8" s="383"/>
       <c r="R8" s="226">
         <f t="shared" si="3"/>
         <v>759726.03</v>
@@ -6494,11 +6470,11 @@
       <c r="O9" s="185">
         <v>0</v>
       </c>
-      <c r="P9" s="369">
+      <c r="P9" s="383">
         <f t="shared" si="2"/>
         <v>3191997.04</v>
       </c>
-      <c r="Q9" s="369"/>
+      <c r="Q9" s="383"/>
       <c r="R9" s="226">
         <f t="shared" si="3"/>
         <v>3288810.04</v>
@@ -6568,11 +6544,11 @@
       <c r="O10" s="185">
         <v>0</v>
       </c>
-      <c r="P10" s="369">
+      <c r="P10" s="383">
         <f t="shared" si="2"/>
         <v>767816.05</v>
       </c>
-      <c r="Q10" s="369"/>
+      <c r="Q10" s="383"/>
       <c r="R10" s="226">
         <f t="shared" si="3"/>
         <v>791104.05</v>
@@ -6639,11 +6615,11 @@
       <c r="O11" s="185">
         <v>0</v>
       </c>
-      <c r="P11" s="369">
+      <c r="P11" s="383">
         <f t="shared" si="2"/>
         <v>751681.06</v>
       </c>
-      <c r="Q11" s="369"/>
+      <c r="Q11" s="383"/>
       <c r="R11" s="226">
         <f t="shared" si="3"/>
         <v>774480.06</v>
@@ -6711,11 +6687,11 @@
       <c r="O12" s="185">
         <v>0</v>
       </c>
-      <c r="P12" s="369">
+      <c r="P12" s="383">
         <f t="shared" si="2"/>
         <v>625812.06999999995</v>
       </c>
-      <c r="Q12" s="369"/>
+      <c r="Q12" s="383"/>
       <c r="R12" s="226">
         <f t="shared" si="3"/>
         <v>644793.06999999995</v>
@@ -6783,11 +6759,11 @@
       <c r="O13" s="185">
         <v>0</v>
       </c>
-      <c r="P13" s="369">
+      <c r="P13" s="383">
         <f t="shared" si="2"/>
         <v>763050.08</v>
       </c>
-      <c r="Q13" s="369"/>
+      <c r="Q13" s="383"/>
       <c r="R13" s="226">
         <f t="shared" si="3"/>
         <v>786193.08</v>
@@ -6855,11 +6831,11 @@
       <c r="O14" s="185">
         <v>0</v>
       </c>
-      <c r="P14" s="369">
+      <c r="P14" s="383">
         <f t="shared" si="2"/>
         <v>759482.09</v>
       </c>
-      <c r="Q14" s="369"/>
+      <c r="Q14" s="383"/>
       <c r="R14" s="226">
         <f t="shared" si="3"/>
         <v>782517.09</v>
@@ -6924,11 +6900,11 @@
       <c r="O15" s="185">
         <v>0</v>
       </c>
-      <c r="P15" s="369">
+      <c r="P15" s="383">
         <f t="shared" si="2"/>
         <v>744528.1</v>
       </c>
-      <c r="Q15" s="369"/>
+      <c r="Q15" s="383"/>
       <c r="R15" s="226">
         <f t="shared" si="3"/>
         <v>767110.1</v>
@@ -6996,11 +6972,11 @@
       <c r="O16" s="185">
         <v>0</v>
       </c>
-      <c r="P16" s="369">
+      <c r="P16" s="383">
         <f t="shared" si="2"/>
         <v>745214.11</v>
       </c>
-      <c r="Q16" s="369"/>
+      <c r="Q16" s="383"/>
       <c r="R16" s="226">
         <f t="shared" si="3"/>
         <v>767816.11</v>
@@ -7069,11 +7045,11 @@
       <c r="O17" s="185">
         <v>0</v>
       </c>
-      <c r="P17" s="369">
+      <c r="P17" s="383">
         <f t="shared" si="2"/>
         <v>4564903.12</v>
       </c>
-      <c r="Q17" s="369"/>
+      <c r="Q17" s="383"/>
       <c r="R17" s="226">
         <f t="shared" si="3"/>
         <v>4703357.12</v>
@@ -7142,11 +7118,11 @@
       <c r="O18" s="185">
         <v>0</v>
       </c>
-      <c r="P18" s="369">
+      <c r="P18" s="383">
         <f t="shared" si="2"/>
         <v>759748.13</v>
       </c>
-      <c r="Q18" s="369"/>
+      <c r="Q18" s="383"/>
       <c r="R18" s="226">
         <f t="shared" si="3"/>
         <v>782791.13</v>
@@ -7209,17 +7185,17 @@
       <c r="N19" s="185">
         <v>0</v>
       </c>
-      <c r="O19" s="185">
-        <v>0</v>
-      </c>
-      <c r="P19" s="369">
+      <c r="O19" s="423">
+        <v>223900</v>
+      </c>
+      <c r="P19" s="383">
         <f t="shared" si="2"/>
-        <v>767816.14</v>
-      </c>
-      <c r="Q19" s="369"/>
+        <v>991716.14</v>
+      </c>
+      <c r="Q19" s="383"/>
       <c r="R19" s="226">
         <f t="shared" si="3"/>
-        <v>791104.14</v>
+        <v>1021795.14</v>
       </c>
       <c r="S19" s="13">
         <f t="shared" si="4"/>
@@ -7285,11 +7261,11 @@
       <c r="O20" s="185">
         <v>0</v>
       </c>
-      <c r="P20" s="369">
+      <c r="P20" s="383">
         <f t="shared" si="2"/>
         <v>743613.15</v>
       </c>
-      <c r="Q20" s="369"/>
+      <c r="Q20" s="383"/>
       <c r="R20" s="226">
         <f t="shared" si="3"/>
         <v>766167.15</v>
@@ -7358,11 +7334,11 @@
       <c r="O21" s="185">
         <v>0</v>
       </c>
-      <c r="P21" s="369">
+      <c r="P21" s="383">
         <f t="shared" si="2"/>
         <v>759748.16</v>
       </c>
-      <c r="Q21" s="369"/>
+      <c r="Q21" s="383"/>
       <c r="R21" s="226">
         <f t="shared" si="3"/>
         <v>782791.16</v>
@@ -7427,11 +7403,11 @@
       <c r="O22" s="185">
         <v>0</v>
       </c>
-      <c r="P22" s="369">
+      <c r="P22" s="383">
         <f t="shared" si="2"/>
         <v>629697.17000000004</v>
       </c>
-      <c r="Q22" s="369"/>
+      <c r="Q22" s="383"/>
       <c r="R22" s="226">
         <f t="shared" si="3"/>
         <v>648796.17000000004</v>
@@ -7500,11 +7476,11 @@
       <c r="O23" s="185">
         <v>0</v>
       </c>
-      <c r="P23" s="369">
+      <c r="P23" s="383">
         <f t="shared" si="2"/>
         <v>759748.18</v>
       </c>
-      <c r="Q23" s="369"/>
+      <c r="Q23" s="383"/>
       <c r="R23" s="226">
         <f t="shared" si="3"/>
         <v>782791.18</v>
@@ -7573,11 +7549,11 @@
       <c r="O24" s="185">
         <v>0</v>
       </c>
-      <c r="P24" s="369">
+      <c r="P24" s="383">
         <f t="shared" si="2"/>
         <v>767816.19</v>
       </c>
-      <c r="Q24" s="369"/>
+      <c r="Q24" s="383"/>
       <c r="R24" s="226">
         <f t="shared" si="3"/>
         <v>791104.19</v>
@@ -7643,11 +7619,11 @@
       <c r="O25" s="185">
         <v>0</v>
       </c>
-      <c r="P25" s="369">
+      <c r="P25" s="383">
         <f t="shared" si="2"/>
         <v>767816.2</v>
       </c>
-      <c r="Q25" s="369"/>
+      <c r="Q25" s="383"/>
       <c r="R25" s="226">
         <f t="shared" si="3"/>
         <v>791104.2</v>
@@ -7713,11 +7689,11 @@
       <c r="O26" s="185">
         <v>0</v>
       </c>
-      <c r="P26" s="369">
+      <c r="P26" s="383">
         <f t="shared" si="2"/>
         <v>767816.21</v>
       </c>
-      <c r="Q26" s="369"/>
+      <c r="Q26" s="383"/>
       <c r="R26" s="226">
         <f t="shared" si="3"/>
         <v>791104.21</v>
@@ -7788,11 +7764,11 @@
       <c r="O27" s="185">
         <v>0</v>
       </c>
-      <c r="P27" s="369">
+      <c r="P27" s="383">
         <f t="shared" si="2"/>
         <v>745213.22</v>
       </c>
-      <c r="Q27" s="369"/>
+      <c r="Q27" s="383"/>
       <c r="R27" s="226">
         <f t="shared" si="3"/>
         <v>767816.22</v>
@@ -7860,11 +7836,11 @@
       <c r="O28" s="185">
         <v>0</v>
       </c>
-      <c r="P28" s="369">
+      <c r="P28" s="383">
         <f t="shared" si="2"/>
         <v>745264.23</v>
       </c>
-      <c r="Q28" s="369"/>
+      <c r="Q28" s="383"/>
       <c r="R28" s="226">
         <f t="shared" si="3"/>
         <v>767868.23</v>
@@ -7932,11 +7908,11 @@
       <c r="O29" s="185">
         <v>0</v>
       </c>
-      <c r="P29" s="369">
+      <c r="P29" s="383">
         <f t="shared" si="2"/>
         <v>745213.24</v>
       </c>
-      <c r="Q29" s="369"/>
+      <c r="Q29" s="383"/>
       <c r="R29" s="226">
         <f t="shared" si="3"/>
         <v>767816.24</v>
@@ -8005,11 +7981,11 @@
       <c r="O30" s="185">
         <v>0</v>
       </c>
-      <c r="P30" s="369">
+      <c r="P30" s="383">
         <f t="shared" si="2"/>
         <v>775884.25</v>
       </c>
-      <c r="Q30" s="369"/>
+      <c r="Q30" s="383"/>
       <c r="R30" s="226">
         <f t="shared" si="3"/>
         <v>799417.25</v>
@@ -8077,11 +8053,11 @@
       <c r="O31" s="185">
         <v>0</v>
       </c>
-      <c r="P31" s="369">
+      <c r="P31" s="383">
         <f t="shared" si="2"/>
         <v>775884.26</v>
       </c>
-      <c r="Q31" s="369"/>
+      <c r="Q31" s="383"/>
       <c r="R31" s="226">
         <f t="shared" si="3"/>
         <v>799417.26</v>
@@ -8150,11 +8126,11 @@
       <c r="O32" s="185">
         <v>0</v>
       </c>
-      <c r="P32" s="369">
+      <c r="P32" s="383">
         <f t="shared" si="2"/>
         <v>775884.27</v>
       </c>
-      <c r="Q32" s="369"/>
+      <c r="Q32" s="383"/>
       <c r="R32" s="226">
         <f t="shared" si="3"/>
         <v>799417.27</v>
@@ -8219,11 +8195,11 @@
       <c r="O33" s="185">
         <v>0</v>
       </c>
-      <c r="P33" s="369">
+      <c r="P33" s="383">
         <f t="shared" si="2"/>
         <v>728196.28</v>
       </c>
-      <c r="Q33" s="369"/>
+      <c r="Q33" s="383"/>
       <c r="R33" s="226">
         <f t="shared" si="3"/>
         <v>750282.28</v>
@@ -8291,11 +8267,11 @@
       <c r="O34" s="185">
         <v>0</v>
       </c>
-      <c r="P34" s="369">
+      <c r="P34" s="383">
         <f t="shared" si="2"/>
         <v>753043.29</v>
       </c>
-      <c r="Q34" s="369"/>
+      <c r="Q34" s="383"/>
       <c r="R34" s="226">
         <f t="shared" si="3"/>
         <v>775883.29</v>
@@ -8363,11 +8339,11 @@
       <c r="O35" s="185">
         <v>0</v>
       </c>
-      <c r="P35" s="369">
+      <c r="P35" s="383">
         <f t="shared" si="2"/>
         <v>729553.3</v>
       </c>
-      <c r="Q35" s="369"/>
+      <c r="Q35" s="383"/>
       <c r="R35" s="226">
         <f t="shared" si="3"/>
         <v>751681.3</v>
@@ -8433,11 +8409,11 @@
       <c r="O36" s="185">
         <v>0</v>
       </c>
-      <c r="P36" s="369">
+      <c r="P36" s="383">
         <f t="shared" si="2"/>
         <v>2403472.31</v>
       </c>
-      <c r="Q36" s="369"/>
+      <c r="Q36" s="383"/>
       <c r="R36" s="226">
         <f t="shared" si="3"/>
         <v>2476370.31</v>
@@ -8506,11 +8482,11 @@
       <c r="O37" s="185">
         <v>0</v>
       </c>
-      <c r="P37" s="369">
+      <c r="P37" s="383">
         <f t="shared" si="2"/>
         <v>618525.31999999995</v>
       </c>
-      <c r="Q37" s="369"/>
+      <c r="Q37" s="383"/>
       <c r="R37" s="226">
         <f t="shared" si="3"/>
         <v>637285.31999999995</v>
@@ -8575,11 +8551,11 @@
       <c r="O38" s="185">
         <v>0</v>
       </c>
-      <c r="P38" s="369">
+      <c r="P38" s="383">
         <f t="shared" ref="P38:P69" si="13">ROUND(SUM(G38:O38),0) + S38</f>
         <v>751681.33</v>
       </c>
-      <c r="Q38" s="369"/>
+      <c r="Q38" s="383"/>
       <c r="R38" s="226">
         <f t="shared" ref="R38:R69" si="14">ROUND(P38+P38*3.033%,0) + S38</f>
         <v>774480.33</v>
@@ -8643,11 +8619,11 @@
       <c r="O39" s="185">
         <v>0</v>
       </c>
-      <c r="P39" s="369">
+      <c r="P39" s="383">
         <f t="shared" si="13"/>
         <v>2448435.34</v>
       </c>
-      <c r="Q39" s="369"/>
+      <c r="Q39" s="383"/>
       <c r="R39" s="226">
         <f t="shared" si="14"/>
         <v>2522696.34</v>
@@ -8717,11 +8693,11 @@
       <c r="O40" s="185">
         <v>0</v>
       </c>
-      <c r="P40" s="369">
+      <c r="P40" s="383">
         <f t="shared" si="13"/>
         <v>759748.35</v>
       </c>
-      <c r="Q40" s="369"/>
+      <c r="Q40" s="383"/>
       <c r="R40" s="226">
         <f t="shared" si="14"/>
         <v>782792.35</v>
@@ -8790,11 +8766,11 @@
       <c r="O41" s="185">
         <v>0</v>
       </c>
-      <c r="P41" s="369">
+      <c r="P41" s="383">
         <f t="shared" si="13"/>
         <v>720580.36</v>
       </c>
-      <c r="Q41" s="369"/>
+      <c r="Q41" s="383"/>
       <c r="R41" s="226">
         <f t="shared" si="14"/>
         <v>742436.36</v>
@@ -8862,11 +8838,11 @@
       <c r="O42" s="185">
         <v>0</v>
       </c>
-      <c r="P42" s="369">
+      <c r="P42" s="383">
         <f t="shared" si="13"/>
         <v>751681.37</v>
       </c>
-      <c r="Q42" s="369"/>
+      <c r="Q42" s="383"/>
       <c r="R42" s="226">
         <f t="shared" si="14"/>
         <v>774480.37</v>
@@ -8934,11 +8910,11 @@
       <c r="O43" s="185">
         <v>0</v>
       </c>
-      <c r="P43" s="369">
+      <c r="P43" s="383">
         <f t="shared" si="13"/>
         <v>751681.38</v>
       </c>
-      <c r="Q43" s="369"/>
+      <c r="Q43" s="383"/>
       <c r="R43" s="226">
         <f t="shared" si="14"/>
         <v>774480.38</v>
@@ -9007,11 +8983,11 @@
       <c r="O44" s="185">
         <v>0</v>
       </c>
-      <c r="P44" s="369">
+      <c r="P44" s="383">
         <f t="shared" si="13"/>
         <v>751543.39</v>
       </c>
-      <c r="Q44" s="369"/>
+      <c r="Q44" s="383"/>
       <c r="R44" s="226">
         <f t="shared" si="14"/>
         <v>774338.39</v>
@@ -9080,11 +9056,11 @@
       <c r="O45" s="185">
         <v>0</v>
       </c>
-      <c r="P45" s="369">
+      <c r="P45" s="383">
         <f t="shared" si="13"/>
         <v>751681.4</v>
       </c>
-      <c r="Q45" s="369"/>
+      <c r="Q45" s="383"/>
       <c r="R45" s="226">
         <f t="shared" si="14"/>
         <v>774480.4</v>
@@ -9150,11 +9126,11 @@
       <c r="O46" s="185">
         <v>0</v>
       </c>
-      <c r="P46" s="369">
+      <c r="P46" s="383">
         <f t="shared" si="13"/>
         <v>729553.41</v>
       </c>
-      <c r="Q46" s="369"/>
+      <c r="Q46" s="383"/>
       <c r="R46" s="226">
         <f t="shared" si="14"/>
         <v>751681.41</v>
@@ -9224,11 +9200,11 @@
       <c r="O47" s="185">
         <v>0</v>
       </c>
-      <c r="P47" s="369">
+      <c r="P47" s="383">
         <f t="shared" si="13"/>
         <v>751681.42</v>
       </c>
-      <c r="Q47" s="369"/>
+      <c r="Q47" s="383"/>
       <c r="R47" s="226">
         <f t="shared" si="14"/>
         <v>774480.42</v>
@@ -9298,11 +9274,11 @@
       <c r="O48" s="185">
         <v>0</v>
       </c>
-      <c r="P48" s="369">
+      <c r="P48" s="383">
         <f t="shared" si="13"/>
         <v>679072.43</v>
       </c>
-      <c r="Q48" s="369"/>
+      <c r="Q48" s="383"/>
       <c r="R48" s="226">
         <f t="shared" si="14"/>
         <v>699669.43</v>
@@ -9368,11 +9344,11 @@
       <c r="O49" s="185">
         <v>0</v>
       </c>
-      <c r="P49" s="369">
+      <c r="P49" s="383">
         <f t="shared" si="13"/>
         <v>692960.44</v>
       </c>
-      <c r="Q49" s="369"/>
+      <c r="Q49" s="383"/>
       <c r="R49" s="226">
         <f t="shared" si="14"/>
         <v>713978.44</v>
@@ -9441,11 +9417,11 @@
       <c r="O50" s="185">
         <v>0</v>
       </c>
-      <c r="P50" s="369">
+      <c r="P50" s="383">
         <f t="shared" si="13"/>
         <v>1654405.45</v>
       </c>
-      <c r="Q50" s="369"/>
+      <c r="Q50" s="383"/>
       <c r="R50" s="226">
         <f t="shared" si="14"/>
         <v>1704584.45</v>
@@ -9511,11 +9487,11 @@
       <c r="O51" s="185">
         <v>0</v>
       </c>
-      <c r="P51" s="369">
+      <c r="P51" s="383">
         <f t="shared" si="13"/>
         <v>1451354.46</v>
       </c>
-      <c r="Q51" s="369"/>
+      <c r="Q51" s="383"/>
       <c r="R51" s="226">
         <f t="shared" si="14"/>
         <v>1495374.46</v>
@@ -9582,11 +9558,11 @@
       <c r="O52" s="185">
         <v>0</v>
       </c>
-      <c r="P52" s="369">
+      <c r="P52" s="383">
         <f t="shared" si="13"/>
         <v>3148838.47</v>
       </c>
-      <c r="Q52" s="369"/>
+      <c r="Q52" s="383"/>
       <c r="R52" s="226">
         <f t="shared" si="14"/>
         <v>3244343.47</v>
@@ -9657,11 +9633,11 @@
       <c r="O53" s="185">
         <v>0</v>
       </c>
-      <c r="P53" s="369">
+      <c r="P53" s="383">
         <f t="shared" si="13"/>
         <v>1187332.48</v>
       </c>
-      <c r="Q53" s="369"/>
+      <c r="Q53" s="383"/>
       <c r="R53" s="226">
         <f t="shared" si="14"/>
         <v>1223344.48</v>
@@ -9729,11 +9705,11 @@
       <c r="O54" s="185">
         <v>0</v>
       </c>
-      <c r="P54" s="369">
+      <c r="P54" s="383">
         <f t="shared" si="13"/>
         <v>751681.49</v>
       </c>
-      <c r="Q54" s="369"/>
+      <c r="Q54" s="383"/>
       <c r="R54" s="226">
         <f t="shared" si="14"/>
         <v>774480.49</v>
@@ -9803,11 +9779,11 @@
       <c r="O55" s="185">
         <v>0</v>
       </c>
-      <c r="P55" s="369">
+      <c r="P55" s="383">
         <f t="shared" si="13"/>
         <v>751681.5</v>
       </c>
-      <c r="Q55" s="369"/>
+      <c r="Q55" s="383"/>
       <c r="R55" s="226">
         <f t="shared" si="14"/>
         <v>774480.5</v>
@@ -9877,11 +9853,11 @@
       <c r="O56" s="185">
         <v>0</v>
       </c>
-      <c r="P56" s="369">
+      <c r="P56" s="383">
         <f t="shared" si="13"/>
         <v>751681.51</v>
       </c>
-      <c r="Q56" s="369"/>
+      <c r="Q56" s="383"/>
       <c r="R56" s="226">
         <f t="shared" si="14"/>
         <v>774480.51</v>
@@ -9951,11 +9927,11 @@
       <c r="O57" s="185">
         <v>0</v>
       </c>
-      <c r="P57" s="369">
+      <c r="P57" s="383">
         <f t="shared" si="13"/>
         <v>759748.52</v>
       </c>
-      <c r="Q57" s="369"/>
+      <c r="Q57" s="383"/>
       <c r="R57" s="226">
         <f t="shared" si="14"/>
         <v>782792.52</v>
@@ -10022,11 +9998,11 @@
       <c r="O58" s="185">
         <v>0</v>
       </c>
-      <c r="P58" s="369">
+      <c r="P58" s="383">
         <f t="shared" si="13"/>
         <v>4746223.53</v>
       </c>
-      <c r="Q58" s="369"/>
+      <c r="Q58" s="383"/>
       <c r="R58" s="226">
         <f t="shared" si="14"/>
         <v>4890176.53</v>
@@ -10093,11 +10069,11 @@
       <c r="O59" s="185">
         <v>0</v>
       </c>
-      <c r="P59" s="369">
+      <c r="P59" s="383">
         <f t="shared" si="13"/>
         <v>751681.54</v>
       </c>
-      <c r="Q59" s="369"/>
+      <c r="Q59" s="383"/>
       <c r="R59" s="226">
         <f t="shared" si="14"/>
         <v>774480.54</v>
@@ -10166,11 +10142,11 @@
       <c r="O60" s="185">
         <v>0</v>
       </c>
-      <c r="P60" s="369">
+      <c r="P60" s="383">
         <f t="shared" si="13"/>
         <v>729553.55</v>
       </c>
-      <c r="Q60" s="369"/>
+      <c r="Q60" s="383"/>
       <c r="R60" s="226">
         <f t="shared" si="14"/>
         <v>751681.55</v>
@@ -10240,11 +10216,11 @@
       <c r="O61" s="185">
         <v>0</v>
       </c>
-      <c r="P61" s="369">
+      <c r="P61" s="383">
         <f t="shared" si="13"/>
         <v>751681.56</v>
       </c>
-      <c r="Q61" s="369"/>
+      <c r="Q61" s="383"/>
       <c r="R61" s="226">
         <f t="shared" si="14"/>
         <v>774480.56</v>
@@ -10314,11 +10290,11 @@
       <c r="O62" s="185">
         <v>0</v>
       </c>
-      <c r="P62" s="369">
+      <c r="P62" s="383">
         <f t="shared" si="13"/>
         <v>751681.57</v>
       </c>
-      <c r="Q62" s="369"/>
+      <c r="Q62" s="383"/>
       <c r="R62" s="226">
         <f t="shared" si="14"/>
         <v>774480.57</v>
@@ -10384,11 +10360,11 @@
       <c r="O63" s="185">
         <v>0</v>
       </c>
-      <c r="P63" s="369">
+      <c r="P63" s="383">
         <f t="shared" si="13"/>
         <v>729553.58</v>
       </c>
-      <c r="Q63" s="369"/>
+      <c r="Q63" s="383"/>
       <c r="R63" s="226">
         <f t="shared" si="14"/>
         <v>751681.58</v>
@@ -10454,11 +10430,11 @@
       <c r="O64" s="185">
         <v>0</v>
       </c>
-      <c r="P64" s="369">
+      <c r="P64" s="383">
         <f t="shared" si="13"/>
         <v>718232.59</v>
       </c>
-      <c r="Q64" s="369"/>
+      <c r="Q64" s="383"/>
       <c r="R64" s="226">
         <f t="shared" si="14"/>
         <v>740017.59</v>
@@ -10527,11 +10503,11 @@
       <c r="O65" s="185">
         <v>0</v>
       </c>
-      <c r="P65" s="369">
+      <c r="P65" s="383">
         <f t="shared" si="13"/>
         <v>751232.6</v>
       </c>
-      <c r="Q65" s="369"/>
+      <c r="Q65" s="383"/>
       <c r="R65" s="226">
         <f t="shared" si="14"/>
         <v>774017.6</v>
@@ -10600,11 +10576,11 @@
       <c r="O66" s="185">
         <v>0</v>
       </c>
-      <c r="P66" s="369">
+      <c r="P66" s="383">
         <f t="shared" si="13"/>
         <v>751624.61</v>
       </c>
-      <c r="Q66" s="369"/>
+      <c r="Q66" s="383"/>
       <c r="R66" s="226">
         <f t="shared" si="14"/>
         <v>774421.61</v>
@@ -10673,11 +10649,11 @@
       <c r="O67" s="185">
         <v>0</v>
       </c>
-      <c r="P67" s="369">
+      <c r="P67" s="383">
         <f t="shared" si="13"/>
         <v>1529226.62</v>
       </c>
-      <c r="Q67" s="369"/>
+      <c r="Q67" s="383"/>
       <c r="R67" s="226">
         <f t="shared" si="14"/>
         <v>1575608.62</v>
@@ -10743,11 +10719,11 @@
       <c r="O68" s="185">
         <v>0</v>
       </c>
-      <c r="P68" s="369">
+      <c r="P68" s="383">
         <f t="shared" si="13"/>
         <v>728882.63</v>
       </c>
-      <c r="Q68" s="369"/>
+      <c r="Q68" s="383"/>
       <c r="R68" s="226">
         <f t="shared" si="14"/>
         <v>750990.63</v>
@@ -10817,11 +10793,11 @@
       <c r="O69" s="185">
         <v>0</v>
       </c>
-      <c r="P69" s="369">
+      <c r="P69" s="383">
         <f t="shared" si="13"/>
         <v>751681.64</v>
       </c>
-      <c r="Q69" s="369"/>
+      <c r="Q69" s="383"/>
       <c r="R69" s="226">
         <f t="shared" si="14"/>
         <v>774480.64</v>
@@ -10891,11 +10867,11 @@
       <c r="O70" s="185">
         <v>0</v>
       </c>
-      <c r="P70" s="369">
+      <c r="P70" s="383">
         <f t="shared" ref="P70:P101" si="21">ROUND(SUM(G70:O70),0) + S70</f>
         <v>751681.65</v>
       </c>
-      <c r="Q70" s="369"/>
+      <c r="Q70" s="383"/>
       <c r="R70" s="226">
         <f t="shared" ref="R70:R101" si="22">ROUND(P70+P70*3.033%,0) + S70</f>
         <v>774480.65</v>
@@ -10962,11 +10938,11 @@
       <c r="O71" s="185">
         <v>0</v>
       </c>
-      <c r="P71" s="369">
+      <c r="P71" s="383">
         <f t="shared" si="21"/>
         <v>751681.66</v>
       </c>
-      <c r="Q71" s="369"/>
+      <c r="Q71" s="383"/>
       <c r="R71" s="226">
         <f t="shared" si="22"/>
         <v>774480.66</v>
@@ -11035,11 +11011,11 @@
       <c r="O72" s="185">
         <v>0</v>
       </c>
-      <c r="P72" s="369">
+      <c r="P72" s="383">
         <f t="shared" si="21"/>
         <v>1527073.67</v>
       </c>
-      <c r="Q72" s="369"/>
+      <c r="Q72" s="383"/>
       <c r="R72" s="226">
         <f t="shared" si="22"/>
         <v>1573390.67</v>
@@ -11106,11 +11082,11 @@
       <c r="O73" s="185">
         <v>0</v>
       </c>
-      <c r="P73" s="369">
+      <c r="P73" s="383">
         <f t="shared" si="21"/>
         <v>4973793.68</v>
       </c>
-      <c r="Q73" s="369"/>
+      <c r="Q73" s="383"/>
       <c r="R73" s="226">
         <f t="shared" si="22"/>
         <v>5124649.68</v>
@@ -11176,11 +11152,11 @@
       <c r="O74" s="185">
         <v>0</v>
       </c>
-      <c r="P74" s="369">
+      <c r="P74" s="383">
         <f t="shared" si="21"/>
         <v>679072.69</v>
       </c>
-      <c r="Q74" s="369"/>
+      <c r="Q74" s="383"/>
       <c r="R74" s="226">
         <f t="shared" si="22"/>
         <v>699669.69</v>
@@ -11248,11 +11224,11 @@
       <c r="O75" s="185">
         <v>0</v>
       </c>
-      <c r="P75" s="369">
+      <c r="P75" s="383">
         <f t="shared" si="21"/>
         <v>1759862.7</v>
       </c>
-      <c r="Q75" s="369"/>
+      <c r="Q75" s="383"/>
       <c r="R75" s="226">
         <f t="shared" si="22"/>
         <v>1813239.7</v>
@@ -11320,11 +11296,11 @@
       <c r="O76" s="185">
         <v>0</v>
       </c>
-      <c r="P76" s="369">
+      <c r="P76" s="383">
         <f t="shared" si="21"/>
         <v>1469187.71</v>
       </c>
-      <c r="Q76" s="369"/>
+      <c r="Q76" s="383"/>
       <c r="R76" s="226">
         <f t="shared" si="22"/>
         <v>1513748.71</v>
@@ -11392,11 +11368,11 @@
       <c r="O77" s="185">
         <v>0</v>
       </c>
-      <c r="P77" s="369">
+      <c r="P77" s="383">
         <f t="shared" si="21"/>
         <v>689767.72</v>
       </c>
-      <c r="Q77" s="369"/>
+      <c r="Q77" s="383"/>
       <c r="R77" s="226">
         <f t="shared" si="22"/>
         <v>710688.72</v>
@@ -11464,11 +11440,11 @@
       <c r="O78" s="185">
         <v>0</v>
       </c>
-      <c r="P78" s="369">
+      <c r="P78" s="383">
         <f t="shared" si="21"/>
         <v>711063.73</v>
       </c>
-      <c r="Q78" s="369"/>
+      <c r="Q78" s="383"/>
       <c r="R78" s="226">
         <f t="shared" si="22"/>
         <v>732630.73</v>
@@ -11534,11 +11510,11 @@
       <c r="O79" s="185">
         <v>0</v>
       </c>
-      <c r="P79" s="369">
+      <c r="P79" s="383">
         <f t="shared" si="21"/>
         <v>743613.74</v>
       </c>
-      <c r="Q79" s="369"/>
+      <c r="Q79" s="383"/>
       <c r="R79" s="226">
         <f t="shared" si="22"/>
         <v>766168.74</v>
@@ -11603,11 +11579,11 @@
       <c r="O80" s="185">
         <v>0</v>
       </c>
-      <c r="P80" s="369">
+      <c r="P80" s="383">
         <f t="shared" si="21"/>
         <v>719410.75</v>
       </c>
-      <c r="Q80" s="369"/>
+      <c r="Q80" s="383"/>
       <c r="R80" s="226">
         <f t="shared" si="22"/>
         <v>741230.75</v>
@@ -11676,11 +11652,11 @@
       <c r="O81" s="185">
         <v>0</v>
       </c>
-      <c r="P81" s="369">
+      <c r="P81" s="383">
         <f t="shared" si="21"/>
         <v>751681.76</v>
       </c>
-      <c r="Q81" s="369"/>
+      <c r="Q81" s="383"/>
       <c r="R81" s="226">
         <f t="shared" si="22"/>
         <v>774480.76</v>
@@ -11745,11 +11721,11 @@
       <c r="O82" s="185">
         <v>0</v>
       </c>
-      <c r="P82" s="369">
+      <c r="P82" s="383">
         <f t="shared" si="21"/>
         <v>880410.77</v>
       </c>
-      <c r="Q82" s="369"/>
+      <c r="Q82" s="383"/>
       <c r="R82" s="226">
         <f t="shared" si="22"/>
         <v>907114.77</v>
@@ -11817,11 +11793,11 @@
       <c r="O83" s="185">
         <v>0</v>
       </c>
-      <c r="P83" s="369">
+      <c r="P83" s="383">
         <f t="shared" si="21"/>
         <v>752933.78</v>
       </c>
-      <c r="Q83" s="369"/>
+      <c r="Q83" s="383"/>
       <c r="R83" s="226">
         <f t="shared" si="22"/>
         <v>775770.78</v>
@@ -11890,11 +11866,11 @@
       <c r="O84" s="185">
         <v>0</v>
       </c>
-      <c r="P84" s="369">
+      <c r="P84" s="383">
         <f t="shared" si="21"/>
         <v>1526975.79</v>
       </c>
-      <c r="Q84" s="369"/>
+      <c r="Q84" s="383"/>
       <c r="R84" s="226">
         <f t="shared" si="22"/>
         <v>1573289.79</v>
@@ -11966,11 +11942,11 @@
       <c r="O85" s="185">
         <v>0</v>
       </c>
-      <c r="P85" s="369">
+      <c r="P85" s="383">
         <f t="shared" si="21"/>
         <v>751681.8</v>
       </c>
-      <c r="Q85" s="369"/>
+      <c r="Q85" s="383"/>
       <c r="R85" s="226">
         <f t="shared" si="22"/>
         <v>774480.8</v>
@@ -12039,11 +12015,11 @@
       <c r="O86" s="185">
         <v>0</v>
       </c>
-      <c r="P86" s="369">
+      <c r="P86" s="383">
         <f t="shared" si="21"/>
         <v>751681.81</v>
       </c>
-      <c r="Q86" s="369"/>
+      <c r="Q86" s="383"/>
       <c r="R86" s="226">
         <f t="shared" si="22"/>
         <v>774480.81</v>
@@ -12108,17 +12084,18 @@
       <c r="N87" s="185">
         <v>0</v>
       </c>
-      <c r="O87" s="185">
-        <v>0</v>
-      </c>
-      <c r="P87" s="369">
+      <c r="O87" s="340">
+        <f>I87/2</f>
+        <v>169419.524232</v>
+      </c>
+      <c r="P87" s="383">
         <f t="shared" si="21"/>
-        <v>1457539.82</v>
-      </c>
-      <c r="Q87" s="369"/>
+        <v>1626958.82</v>
+      </c>
+      <c r="Q87" s="383"/>
       <c r="R87" s="226">
         <f t="shared" si="22"/>
-        <v>1501747.82</v>
+        <v>1676304.82</v>
       </c>
       <c r="S87" s="13">
         <f t="shared" si="23"/>
@@ -12184,11 +12161,11 @@
       <c r="O88" s="185">
         <v>0</v>
       </c>
-      <c r="P88" s="369">
+      <c r="P88" s="383">
         <f t="shared" si="21"/>
         <v>775884.83</v>
       </c>
-      <c r="Q88" s="369"/>
+      <c r="Q88" s="383"/>
       <c r="R88" s="226">
         <f t="shared" si="22"/>
         <v>799417.83</v>
@@ -12253,11 +12230,11 @@
       <c r="O89" s="185">
         <v>0</v>
       </c>
-      <c r="P89" s="369">
+      <c r="P89" s="383">
         <f t="shared" si="21"/>
         <v>775884.84</v>
       </c>
-      <c r="Q89" s="369"/>
+      <c r="Q89" s="383"/>
       <c r="R89" s="226">
         <f t="shared" si="22"/>
         <v>799417.84</v>
@@ -12323,11 +12300,11 @@
       <c r="O90" s="185">
         <v>0</v>
       </c>
-      <c r="P90" s="369">
+      <c r="P90" s="383">
         <f t="shared" si="21"/>
         <v>775884.85</v>
       </c>
-      <c r="Q90" s="369"/>
+      <c r="Q90" s="383"/>
       <c r="R90" s="226">
         <f t="shared" si="22"/>
         <v>799417.85</v>
@@ -12398,11 +12375,11 @@
         <f>2239*100</f>
         <v>223900</v>
       </c>
-      <c r="P91" s="369">
+      <c r="P91" s="383">
         <f t="shared" si="21"/>
         <v>1394226.86</v>
       </c>
-      <c r="Q91" s="369"/>
+      <c r="Q91" s="383"/>
       <c r="R91" s="226">
         <f t="shared" si="22"/>
         <v>1436514.86</v>
@@ -12471,11 +12448,11 @@
       <c r="O92" s="185">
         <v>0</v>
       </c>
-      <c r="P92" s="369">
+      <c r="P92" s="383">
         <f t="shared" si="21"/>
         <v>775884.87</v>
       </c>
-      <c r="Q92" s="369"/>
+      <c r="Q92" s="383"/>
       <c r="R92" s="226">
         <f t="shared" si="22"/>
         <v>799417.87</v>
@@ -12540,11 +12517,11 @@
       <c r="O93" s="185">
         <v>0</v>
       </c>
-      <c r="P93" s="369">
+      <c r="P93" s="383">
         <f t="shared" si="21"/>
         <v>767654.88</v>
       </c>
-      <c r="Q93" s="369"/>
+      <c r="Q93" s="383"/>
       <c r="R93" s="226">
         <f t="shared" si="22"/>
         <v>790938.88</v>
@@ -12610,11 +12587,11 @@
       <c r="O94" s="185">
         <v>0</v>
       </c>
-      <c r="P94" s="369">
+      <c r="P94" s="383">
         <f t="shared" si="21"/>
         <v>775884.89</v>
       </c>
-      <c r="Q94" s="369"/>
+      <c r="Q94" s="383"/>
       <c r="R94" s="226">
         <f t="shared" si="22"/>
         <v>799417.89</v>
@@ -12683,11 +12660,11 @@
       <c r="O95" s="185">
         <v>0</v>
       </c>
-      <c r="P95" s="369">
+      <c r="P95" s="383">
         <f t="shared" si="21"/>
         <v>2097847.9</v>
       </c>
-      <c r="Q95" s="369"/>
+      <c r="Q95" s="383"/>
       <c r="R95" s="226">
         <f t="shared" si="22"/>
         <v>2161476.9</v>
@@ -12756,11 +12733,11 @@
       <c r="O96" s="185">
         <v>0</v>
       </c>
-      <c r="P96" s="369">
+      <c r="P96" s="383">
         <f t="shared" si="21"/>
         <v>775884.91</v>
       </c>
-      <c r="Q96" s="369"/>
+      <c r="Q96" s="383"/>
       <c r="R96" s="226">
         <f t="shared" si="22"/>
         <v>799417.91</v>
@@ -12829,11 +12806,11 @@
       <c r="O97" s="185">
         <v>0</v>
       </c>
-      <c r="P97" s="369">
+      <c r="P97" s="383">
         <f t="shared" si="21"/>
         <v>775884.92</v>
       </c>
-      <c r="Q97" s="369"/>
+      <c r="Q97" s="383"/>
       <c r="R97" s="226">
         <f t="shared" si="22"/>
         <v>799418.92</v>
@@ -12901,11 +12878,11 @@
       <c r="O98" s="185">
         <v>0</v>
       </c>
-      <c r="P98" s="369">
+      <c r="P98" s="383">
         <f t="shared" si="21"/>
         <v>1558282.93</v>
       </c>
-      <c r="Q98" s="369"/>
+      <c r="Q98" s="383"/>
       <c r="R98" s="226">
         <f t="shared" si="22"/>
         <v>1605546.93</v>
@@ -12974,11 +12951,11 @@
       <c r="O99" s="185">
         <v>0</v>
       </c>
-      <c r="P99" s="369">
+      <c r="P99" s="383">
         <f t="shared" si="21"/>
         <v>775884.94</v>
       </c>
-      <c r="Q99" s="369"/>
+      <c r="Q99" s="383"/>
       <c r="R99" s="226">
         <f t="shared" si="22"/>
         <v>799418.94</v>
@@ -13046,11 +13023,11 @@
       <c r="O100" s="185">
         <v>0</v>
       </c>
-      <c r="P100" s="369">
+      <c r="P100" s="383">
         <f t="shared" si="21"/>
         <v>5461803.9500000002</v>
       </c>
-      <c r="Q100" s="369"/>
+      <c r="Q100" s="383"/>
       <c r="R100" s="226">
         <f t="shared" si="22"/>
         <v>5627460.9500000002</v>
@@ -13115,11 +13092,11 @@
       <c r="O101" s="185">
         <v>0</v>
       </c>
-      <c r="P101" s="369">
+      <c r="P101" s="383">
         <f t="shared" si="21"/>
         <v>751813.96</v>
       </c>
-      <c r="Q101" s="369"/>
+      <c r="Q101" s="383"/>
       <c r="R101" s="226">
         <f t="shared" si="22"/>
         <v>774616.96</v>
@@ -13188,11 +13165,11 @@
       <c r="O102" s="185">
         <v>0</v>
       </c>
-      <c r="P102" s="369">
+      <c r="P102" s="383">
         <f t="shared" ref="P102:P133" si="30">ROUND(SUM(G102:O102),0) + S102</f>
         <v>775884.97</v>
       </c>
-      <c r="Q102" s="369"/>
+      <c r="Q102" s="383"/>
       <c r="R102" s="226">
         <f t="shared" ref="R102:R133" si="31">ROUND(P102+P102*3.033%,0) + S102</f>
         <v>799418.97</v>
@@ -13261,11 +13238,11 @@
       <c r="O103" s="185">
         <v>0</v>
       </c>
-      <c r="P103" s="369">
+      <c r="P103" s="383">
         <f t="shared" si="30"/>
         <v>775884.98</v>
       </c>
-      <c r="Q103" s="369"/>
+      <c r="Q103" s="383"/>
       <c r="R103" s="226">
         <f t="shared" si="31"/>
         <v>799418.98</v>
@@ -13331,11 +13308,11 @@
       <c r="O104" s="185">
         <v>0</v>
       </c>
-      <c r="P104" s="369">
+      <c r="P104" s="383">
         <f t="shared" si="30"/>
         <v>775884.99</v>
       </c>
-      <c r="Q104" s="369"/>
+      <c r="Q104" s="383"/>
       <c r="R104" s="226">
         <f t="shared" si="31"/>
         <v>799418.99</v>
@@ -13404,11 +13381,11 @@
       <c r="O105" s="185">
         <v>0</v>
       </c>
-      <c r="P105" s="369">
+      <c r="P105" s="383">
         <f t="shared" si="30"/>
         <v>775885</v>
       </c>
-      <c r="Q105" s="369"/>
+      <c r="Q105" s="383"/>
       <c r="R105" s="226">
         <f t="shared" si="31"/>
         <v>799419</v>
@@ -13474,11 +13451,11 @@
       <c r="O106" s="185">
         <v>0</v>
       </c>
-      <c r="P106" s="369">
+      <c r="P106" s="383">
         <f t="shared" si="30"/>
         <v>775885.01</v>
       </c>
-      <c r="Q106" s="369"/>
+      <c r="Q106" s="383"/>
       <c r="R106" s="226">
         <f t="shared" si="31"/>
         <v>799419.01</v>
@@ -13543,11 +13520,11 @@
       <c r="O107" s="185">
         <v>0</v>
       </c>
-      <c r="P107" s="369">
+      <c r="P107" s="383">
         <f t="shared" si="30"/>
         <v>764543.02</v>
       </c>
-      <c r="Q107" s="369"/>
+      <c r="Q107" s="383"/>
       <c r="R107" s="226">
         <f t="shared" si="31"/>
         <v>787733.02</v>
@@ -13613,11 +13590,11 @@
       <c r="O108" s="185">
         <v>0</v>
       </c>
-      <c r="P108" s="369">
+      <c r="P108" s="383">
         <f t="shared" si="30"/>
         <v>3224447.03</v>
       </c>
-      <c r="Q108" s="369"/>
+      <c r="Q108" s="383"/>
       <c r="R108" s="226">
         <f t="shared" si="31"/>
         <v>3322246.03</v>
@@ -13683,11 +13660,11 @@
       <c r="O109" s="185">
         <v>0</v>
       </c>
-      <c r="P109" s="369">
+      <c r="P109" s="383">
         <f t="shared" si="30"/>
         <v>767817.04</v>
       </c>
-      <c r="Q109" s="369"/>
+      <c r="Q109" s="383"/>
       <c r="R109" s="226">
         <f t="shared" si="31"/>
         <v>791106.04</v>
@@ -13701,7 +13678,7 @@
         <v>104</v>
       </c>
       <c r="U109" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
     </row>
     <row r="110" spans="1:22" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -13756,11 +13733,11 @@
       <c r="O110" s="185">
         <v>0</v>
       </c>
-      <c r="P110" s="369">
+      <c r="P110" s="383">
         <f t="shared" si="30"/>
         <v>727479.05</v>
       </c>
-      <c r="Q110" s="369"/>
+      <c r="Q110" s="383"/>
       <c r="R110" s="226">
         <f t="shared" si="31"/>
         <v>749544.05</v>
@@ -13774,7 +13751,7 @@
         <v>105</v>
       </c>
       <c r="U110" s="144" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="V110" s="33"/>
     </row>
@@ -13828,11 +13805,11 @@
       <c r="O111" s="185">
         <v>0</v>
       </c>
-      <c r="P111" s="369">
+      <c r="P111" s="383">
         <f t="shared" si="30"/>
         <v>3618180.06</v>
       </c>
-      <c r="Q111" s="369"/>
+      <c r="Q111" s="383"/>
       <c r="R111" s="226">
         <f t="shared" si="31"/>
         <v>3727920.06</v>
@@ -13901,11 +13878,11 @@
       <c r="O112" s="185">
         <v>0</v>
       </c>
-      <c r="P112" s="369">
+      <c r="P112" s="383">
         <f t="shared" si="30"/>
         <v>743614.07</v>
       </c>
-      <c r="Q112" s="369"/>
+      <c r="Q112" s="383"/>
       <c r="R112" s="226">
         <f t="shared" si="31"/>
         <v>766169.07</v>
@@ -13974,11 +13951,11 @@
       <c r="O113" s="185">
         <v>0</v>
       </c>
-      <c r="P113" s="369">
+      <c r="P113" s="383">
         <f t="shared" si="30"/>
         <v>743614.08</v>
       </c>
-      <c r="Q113" s="369"/>
+      <c r="Q113" s="383"/>
       <c r="R113" s="226">
         <f t="shared" si="31"/>
         <v>766169.08</v>
@@ -14043,11 +14020,11 @@
       <c r="O114" s="185">
         <v>0</v>
       </c>
-      <c r="P114" s="369">
+      <c r="P114" s="383">
         <f t="shared" si="30"/>
         <v>1469510.09</v>
       </c>
-      <c r="Q114" s="369"/>
+      <c r="Q114" s="383"/>
       <c r="R114" s="226">
         <f t="shared" si="31"/>
         <v>1514081.09</v>
@@ -14115,11 +14092,11 @@
       <c r="O115" s="185">
         <v>0</v>
       </c>
-      <c r="P115" s="369">
+      <c r="P115" s="383">
         <f t="shared" si="30"/>
         <v>1540074.1</v>
       </c>
-      <c r="Q115" s="369"/>
+      <c r="Q115" s="383"/>
       <c r="R115" s="226">
         <f t="shared" si="31"/>
         <v>1586786.1</v>
@@ -14189,11 +14166,11 @@
       <c r="O116" s="185">
         <v>0</v>
       </c>
-      <c r="P116" s="369">
+      <c r="P116" s="383">
         <f t="shared" si="30"/>
         <v>751682.11</v>
       </c>
-      <c r="Q116" s="369"/>
+      <c r="Q116" s="383"/>
       <c r="R116" s="226">
         <f t="shared" si="31"/>
         <v>774482.11</v>
@@ -14258,11 +14235,11 @@
       <c r="O117" s="185">
         <v>0</v>
       </c>
-      <c r="P117" s="369">
+      <c r="P117" s="383">
         <f t="shared" si="30"/>
         <v>1525913.12</v>
       </c>
-      <c r="Q117" s="369"/>
+      <c r="Q117" s="383"/>
       <c r="R117" s="226">
         <f t="shared" si="31"/>
         <v>1572195.12</v>
@@ -14330,11 +14307,11 @@
       <c r="O118" s="185">
         <v>0</v>
       </c>
-      <c r="P118" s="369">
+      <c r="P118" s="383">
         <f t="shared" si="30"/>
         <v>745213.13</v>
       </c>
-      <c r="Q118" s="369"/>
+      <c r="Q118" s="383"/>
       <c r="R118" s="226">
         <f t="shared" si="31"/>
         <v>767816.13</v>
@@ -14364,15 +14341,16 @@
         <v>975582.14</v>
       </c>
       <c r="F119" s="192">
-        <v>751682.14</v>
+        <f>223900+751682.14</f>
+        <v>975582.14</v>
       </c>
       <c r="G119" s="56">
         <f t="shared" si="19"/>
-        <v>223900</v>
+        <v>0</v>
       </c>
       <c r="H119" s="72">
         <f t="shared" si="27"/>
-        <v>6911.7930000000006</v>
+        <v>0</v>
       </c>
       <c r="I119" s="66">
         <f t="shared" si="34"/>
@@ -14399,14 +14377,14 @@
       <c r="O119" s="185">
         <v>0</v>
       </c>
-      <c r="P119" s="369">
+      <c r="P119" s="383">
         <f t="shared" si="30"/>
-        <v>982494.14</v>
-      </c>
-      <c r="Q119" s="369"/>
+        <v>751682.14</v>
+      </c>
+      <c r="Q119" s="383"/>
       <c r="R119" s="226">
         <f t="shared" si="31"/>
-        <v>1012294.14</v>
+        <v>774482.14</v>
       </c>
       <c r="S119" s="13">
         <f t="shared" si="32"/>
@@ -14469,11 +14447,11 @@
       <c r="O120" s="185">
         <v>0</v>
       </c>
-      <c r="P120" s="369">
+      <c r="P120" s="383">
         <f t="shared" si="30"/>
         <v>904966.15</v>
       </c>
-      <c r="Q120" s="369"/>
+      <c r="Q120" s="383"/>
       <c r="R120" s="226">
         <f t="shared" si="31"/>
         <v>932415.15</v>
@@ -14542,11 +14520,11 @@
       <c r="O121" s="185">
         <v>0</v>
       </c>
-      <c r="P121" s="369">
+      <c r="P121" s="383">
         <f t="shared" si="30"/>
         <v>831345.16</v>
       </c>
-      <c r="Q121" s="369"/>
+      <c r="Q121" s="383"/>
       <c r="R121" s="226">
         <f t="shared" si="31"/>
         <v>856561.16</v>
@@ -14612,11 +14590,11 @@
       <c r="O122" s="185">
         <v>0</v>
       </c>
-      <c r="P122" s="369">
+      <c r="P122" s="383">
         <f t="shared" si="30"/>
         <v>880763.17</v>
       </c>
-      <c r="Q122" s="369"/>
+      <c r="Q122" s="383"/>
       <c r="R122" s="226">
         <f t="shared" si="31"/>
         <v>907478.17</v>
@@ -14685,11 +14663,11 @@
       <c r="O123" s="185">
         <v>0</v>
       </c>
-      <c r="P123" s="369">
+      <c r="P123" s="383">
         <f t="shared" si="30"/>
         <v>855800.18</v>
       </c>
-      <c r="Q123" s="369"/>
+      <c r="Q123" s="383"/>
       <c r="R123" s="226">
         <f t="shared" si="31"/>
         <v>881758.18</v>
@@ -14757,11 +14735,11 @@
       <c r="O124" s="185">
         <v>0</v>
       </c>
-      <c r="P124" s="369">
+      <c r="P124" s="383">
         <f t="shared" si="30"/>
         <v>824214.19</v>
       </c>
-      <c r="Q124" s="369"/>
+      <c r="Q124" s="383"/>
       <c r="R124" s="226">
         <f t="shared" si="31"/>
         <v>849214.19</v>
@@ -14830,11 +14808,11 @@
       <c r="O125" s="185">
         <v>0</v>
       </c>
-      <c r="P125" s="369">
+      <c r="P125" s="383">
         <f t="shared" si="30"/>
         <v>759749.2</v>
       </c>
-      <c r="Q125" s="369"/>
+      <c r="Q125" s="383"/>
       <c r="R125" s="226">
         <f t="shared" si="31"/>
         <v>782793.2</v>
@@ -14903,11 +14881,11 @@
       <c r="O126" s="185">
         <v>0</v>
       </c>
-      <c r="P126" s="369">
+      <c r="P126" s="383">
         <f t="shared" si="30"/>
         <v>759749.21</v>
       </c>
-      <c r="Q126" s="369"/>
+      <c r="Q126" s="383"/>
       <c r="R126" s="226">
         <f t="shared" si="31"/>
         <v>782793.21</v>
@@ -14976,11 +14954,11 @@
       <c r="O127" s="185">
         <v>0</v>
       </c>
-      <c r="P127" s="369">
+      <c r="P127" s="383">
         <f t="shared" si="30"/>
         <v>759749.22</v>
       </c>
-      <c r="Q127" s="369"/>
+      <c r="Q127" s="383"/>
       <c r="R127" s="226">
         <f t="shared" si="31"/>
         <v>782793.22</v>
@@ -15046,11 +15024,11 @@
       <c r="O128" s="185">
         <v>0</v>
       </c>
-      <c r="P128" s="369">
+      <c r="P128" s="383">
         <f t="shared" si="30"/>
         <v>759749.23</v>
       </c>
-      <c r="Q128" s="369"/>
+      <c r="Q128" s="383"/>
       <c r="R128" s="226">
         <f t="shared" si="31"/>
         <v>782793.23</v>
@@ -15118,11 +15096,11 @@
       <c r="O129" s="185">
         <v>0</v>
       </c>
-      <c r="P129" s="369">
+      <c r="P129" s="383">
         <f t="shared" si="30"/>
         <v>737383.24</v>
       </c>
-      <c r="Q129" s="369"/>
+      <c r="Q129" s="383"/>
       <c r="R129" s="226">
         <f t="shared" si="31"/>
         <v>759749.24</v>
@@ -15188,11 +15166,11 @@
       <c r="O130" s="185">
         <v>0</v>
       </c>
-      <c r="P130" s="369">
+      <c r="P130" s="383">
         <f t="shared" si="30"/>
         <v>759749.25</v>
       </c>
-      <c r="Q130" s="369"/>
+      <c r="Q130" s="383"/>
       <c r="R130" s="226">
         <f t="shared" si="31"/>
         <v>782793.25</v>
@@ -15261,11 +15239,11 @@
       <c r="O131" s="185">
         <v>0</v>
       </c>
-      <c r="P131" s="369">
+      <c r="P131" s="383">
         <f t="shared" si="30"/>
         <v>759749.26</v>
       </c>
-      <c r="Q131" s="369"/>
+      <c r="Q131" s="383"/>
       <c r="R131" s="226">
         <f t="shared" si="31"/>
         <v>782793.26</v>
@@ -15331,11 +15309,11 @@
       <c r="O132" s="185">
         <v>0</v>
       </c>
-      <c r="P132" s="369">
+      <c r="P132" s="383">
         <f t="shared" si="30"/>
         <v>840425.27</v>
       </c>
-      <c r="Q132" s="369"/>
+      <c r="Q132" s="383"/>
       <c r="R132" s="226">
         <f t="shared" si="31"/>
         <v>865916.27</v>
@@ -15404,11 +15382,11 @@
       <c r="O133" s="185">
         <v>0</v>
       </c>
-      <c r="P133" s="369">
+      <c r="P133" s="383">
         <f t="shared" si="30"/>
         <v>880763.28</v>
       </c>
-      <c r="Q133" s="369"/>
+      <c r="Q133" s="383"/>
       <c r="R133" s="226">
         <f t="shared" si="31"/>
         <v>907478.28</v>
@@ -15474,11 +15452,11 @@
       <c r="O134" s="185">
         <v>0</v>
       </c>
-      <c r="P134" s="369">
+      <c r="P134" s="383">
         <f t="shared" ref="P134:P144" si="37">ROUND(SUM(G134:O134),0) + S134</f>
         <v>880763.29</v>
       </c>
-      <c r="Q134" s="369"/>
+      <c r="Q134" s="383"/>
       <c r="R134" s="226">
         <f t="shared" ref="R134:R144" si="38">ROUND(P134+P134*3.033%,0) + S134</f>
         <v>907478.29</v>
@@ -15546,11 +15524,11 @@
       <c r="O135" s="185">
         <v>0</v>
       </c>
-      <c r="P135" s="369">
+      <c r="P135" s="383">
         <f t="shared" si="37"/>
         <v>848330.3</v>
       </c>
-      <c r="Q135" s="369"/>
+      <c r="Q135" s="383"/>
       <c r="R135" s="226">
         <f t="shared" si="38"/>
         <v>874061.3</v>
@@ -15619,11 +15597,11 @@
       <c r="O136" s="185">
         <v>0</v>
       </c>
-      <c r="P136" s="369">
+      <c r="P136" s="383">
         <f t="shared" si="37"/>
         <v>880763.31</v>
       </c>
-      <c r="Q136" s="369"/>
+      <c r="Q136" s="383"/>
       <c r="R136" s="226">
         <f t="shared" si="38"/>
         <v>907478.31</v>
@@ -15692,11 +15670,11 @@
       <c r="O137" s="185">
         <v>0</v>
       </c>
-      <c r="P137" s="369">
+      <c r="P137" s="383">
         <f t="shared" si="37"/>
         <v>872696.31999999995</v>
       </c>
-      <c r="Q137" s="369"/>
+      <c r="Q137" s="383"/>
       <c r="R137" s="226">
         <f t="shared" si="38"/>
         <v>899166.32</v>
@@ -15765,11 +15743,11 @@
       <c r="O138" s="185">
         <v>0</v>
       </c>
-      <c r="P138" s="369">
+      <c r="P138" s="383">
         <f t="shared" si="37"/>
         <v>904966.33</v>
       </c>
-      <c r="Q138" s="369"/>
+      <c r="Q138" s="383"/>
       <c r="R138" s="226">
         <f t="shared" si="38"/>
         <v>932415.33</v>
@@ -15837,11 +15815,11 @@
       <c r="O139" s="185">
         <v>0</v>
       </c>
-      <c r="P139" s="369">
+      <c r="P139" s="383">
         <f t="shared" si="37"/>
         <v>792194.34</v>
       </c>
-      <c r="Q139" s="369"/>
+      <c r="Q139" s="383"/>
       <c r="R139" s="226">
         <f t="shared" si="38"/>
         <v>816223.34</v>
@@ -15909,11 +15887,11 @@
       <c r="O140" s="185">
         <v>0</v>
       </c>
-      <c r="P140" s="369">
+      <c r="P140" s="383">
         <f t="shared" si="37"/>
         <v>854834.35</v>
       </c>
-      <c r="Q140" s="369"/>
+      <c r="Q140" s="383"/>
       <c r="R140" s="226">
         <f t="shared" si="38"/>
         <v>880762.35</v>
@@ -15982,11 +15960,11 @@
       <c r="O141" s="185">
         <v>0</v>
       </c>
-      <c r="P141" s="369">
+      <c r="P141" s="383">
         <f t="shared" si="37"/>
         <v>888831.36</v>
       </c>
-      <c r="Q141" s="369"/>
+      <c r="Q141" s="383"/>
       <c r="R141" s="226">
         <f t="shared" si="38"/>
         <v>915791.35999999999</v>
@@ -16055,11 +16033,11 @@
       <c r="O142" s="185">
         <v>0</v>
       </c>
-      <c r="P142" s="369">
+      <c r="P142" s="383">
         <f t="shared" si="37"/>
         <v>824290.37</v>
       </c>
-      <c r="Q142" s="369"/>
+      <c r="Q142" s="383"/>
       <c r="R142" s="226">
         <f t="shared" si="38"/>
         <v>849292.37</v>
@@ -16124,11 +16102,11 @@
       <c r="O143" s="185">
         <v>0</v>
       </c>
-      <c r="P143" s="369">
+      <c r="P143" s="383">
         <f t="shared" si="37"/>
         <v>879189.38</v>
       </c>
-      <c r="Q143" s="369"/>
+      <c r="Q143" s="383"/>
       <c r="R143" s="226">
         <f t="shared" si="38"/>
         <v>905856.38</v>
@@ -16196,11 +16174,11 @@
       <c r="O144" s="185">
         <v>0</v>
       </c>
-      <c r="P144" s="369">
+      <c r="P144" s="383">
         <f t="shared" si="37"/>
         <v>2193265.39</v>
       </c>
-      <c r="Q144" s="369"/>
+      <c r="Q144" s="383"/>
       <c r="R144" s="226">
         <f t="shared" si="38"/>
         <v>2259788.39</v>
@@ -16246,8 +16224,8 @@
       <c r="O145" s="185">
         <v>0</v>
       </c>
-      <c r="P145" s="369"/>
-      <c r="Q145" s="369"/>
+      <c r="P145" s="383"/>
+      <c r="Q145" s="383"/>
       <c r="R145" s="227"/>
       <c r="S145" s="13">
         <f t="shared" si="39"/>
@@ -16287,8 +16265,8 @@
       <c r="O146" s="185">
         <v>0</v>
       </c>
-      <c r="P146" s="369"/>
-      <c r="Q146" s="369"/>
+      <c r="P146" s="383"/>
+      <c r="Q146" s="383"/>
       <c r="R146" s="227"/>
       <c r="S146" s="13">
         <f t="shared" si="39"/>
@@ -16321,8 +16299,8 @@
       <c r="O147" s="185">
         <v>0</v>
       </c>
-      <c r="P147" s="369"/>
-      <c r="Q147" s="369"/>
+      <c r="P147" s="383"/>
+      <c r="Q147" s="383"/>
       <c r="R147" s="227"/>
       <c r="S147" s="13">
         <f t="shared" si="39"/>
@@ -16355,8 +16333,8 @@
       <c r="O148" s="185">
         <v>0</v>
       </c>
-      <c r="P148" s="369"/>
-      <c r="Q148" s="369"/>
+      <c r="P148" s="383"/>
+      <c r="Q148" s="383"/>
       <c r="R148" s="227"/>
       <c r="S148" s="13">
         <f t="shared" si="39"/>
@@ -16418,11 +16396,11 @@
       <c r="O149" s="185">
         <v>0</v>
       </c>
-      <c r="P149" s="369">
+      <c r="P149" s="383">
         <f t="shared" ref="P149:P158" si="47">ROUND(SUM(G149:O149),0) + S149</f>
         <v>695209.46</v>
       </c>
-      <c r="Q149" s="369"/>
+      <c r="Q149" s="383"/>
       <c r="R149" s="226">
         <f t="shared" ref="R149:R158" si="48">ROUND(P149+P149*3.033%,0) + S149</f>
         <v>716296.46</v>
@@ -16485,11 +16463,11 @@
       <c r="O150" s="185">
         <v>0</v>
       </c>
-      <c r="P150" s="369">
+      <c r="P150" s="383">
         <f t="shared" si="47"/>
         <v>1139411.55</v>
       </c>
-      <c r="Q150" s="369"/>
+      <c r="Q150" s="383"/>
       <c r="R150" s="226">
         <f t="shared" si="48"/>
         <v>1173971.55</v>
@@ -16557,11 +16535,11 @@
       <c r="O151" s="185">
         <v>0</v>
       </c>
-      <c r="P151" s="369">
+      <c r="P151" s="383">
         <f t="shared" si="47"/>
         <v>759749.58</v>
       </c>
-      <c r="Q151" s="369"/>
+      <c r="Q151" s="383"/>
       <c r="R151" s="226">
         <f t="shared" si="48"/>
         <v>782794.58</v>
@@ -16626,11 +16604,11 @@
       <c r="O152" s="185">
         <v>0</v>
       </c>
-      <c r="P152" s="369">
+      <c r="P152" s="383">
         <f t="shared" si="47"/>
         <v>759749.59</v>
       </c>
-      <c r="Q152" s="369"/>
+      <c r="Q152" s="383"/>
       <c r="R152" s="226">
         <f t="shared" si="48"/>
         <v>782794.59</v>
@@ -16695,11 +16673,11 @@
       <c r="O153" s="185">
         <v>0</v>
       </c>
-      <c r="P153" s="369">
+      <c r="P153" s="383">
         <f t="shared" si="47"/>
         <v>759749.63</v>
       </c>
-      <c r="Q153" s="369"/>
+      <c r="Q153" s="383"/>
       <c r="R153" s="226">
         <f t="shared" si="48"/>
         <v>782794.63</v>
@@ -16764,11 +16742,11 @@
       <c r="O154" s="185">
         <v>0</v>
       </c>
-      <c r="P154" s="369">
+      <c r="P154" s="383">
         <f t="shared" si="47"/>
         <v>743614.68</v>
       </c>
-      <c r="Q154" s="369"/>
+      <c r="Q154" s="383"/>
       <c r="R154" s="226">
         <f t="shared" si="48"/>
         <v>766170.68</v>
@@ -16832,11 +16810,11 @@
       <c r="O155" s="185">
         <v>0</v>
       </c>
-      <c r="P155" s="369">
+      <c r="P155" s="383">
         <f t="shared" si="47"/>
         <v>737382.73</v>
       </c>
-      <c r="Q155" s="369"/>
+      <c r="Q155" s="383"/>
       <c r="R155" s="226">
         <f t="shared" si="48"/>
         <v>759749.73</v>
@@ -16903,11 +16881,11 @@
       <c r="O156" s="185">
         <v>0</v>
       </c>
-      <c r="P156" s="369">
+      <c r="P156" s="383">
         <f t="shared" si="47"/>
         <v>737382.75</v>
       </c>
-      <c r="Q156" s="369"/>
+      <c r="Q156" s="383"/>
       <c r="R156" s="226">
         <f t="shared" si="48"/>
         <v>759749.75</v>
@@ -16975,11 +16953,11 @@
       <c r="O157" s="185">
         <v>0</v>
       </c>
-      <c r="P157" s="369">
+      <c r="P157" s="383">
         <f t="shared" si="47"/>
         <v>759749.76</v>
       </c>
-      <c r="Q157" s="369"/>
+      <c r="Q157" s="383"/>
       <c r="R157" s="226">
         <f t="shared" si="48"/>
         <v>782794.76</v>
@@ -17043,11 +17021,11 @@
       <c r="O158" s="185">
         <v>0</v>
       </c>
-      <c r="P158" s="369">
+      <c r="P158" s="383">
         <f t="shared" si="47"/>
         <v>760897.04</v>
       </c>
-      <c r="Q158" s="369"/>
+      <c r="Q158" s="383"/>
       <c r="R158" s="226">
         <f t="shared" si="48"/>
         <v>783977.04</v>
@@ -17080,8 +17058,8 @@
       <c r="M159" s="20"/>
       <c r="N159" s="20"/>
       <c r="O159" s="66"/>
-      <c r="P159" s="374"/>
-      <c r="Q159" s="374"/>
+      <c r="P159" s="408"/>
+      <c r="Q159" s="408"/>
       <c r="R159" s="163"/>
       <c r="S159" s="13"/>
       <c r="T159" s="1"/>
@@ -17102,8 +17080,8 @@
       <c r="M160" s="174"/>
       <c r="N160" s="174"/>
       <c r="O160" s="223"/>
-      <c r="P160" s="375"/>
-      <c r="Q160" s="375"/>
+      <c r="P160" s="409"/>
+      <c r="Q160" s="409"/>
       <c r="R160" s="166"/>
       <c r="S160" s="13"/>
       <c r="T160" s="175"/>
@@ -17122,11 +17100,11 @@
       </c>
       <c r="F161" s="179">
         <f>SUM(F6:F160)</f>
-        <v>106045133.38999999</v>
+        <v>106269033.38999999</v>
       </c>
       <c r="G161" s="180">
         <f t="shared" si="51"/>
-        <v>41766488.75</v>
+        <v>41542588.75</v>
       </c>
       <c r="H161" s="181"/>
       <c r="I161" s="181">
@@ -17155,152 +17133,314 @@
       </c>
       <c r="O161" s="182">
         <f t="shared" si="51"/>
-        <v>223900</v>
-      </c>
-      <c r="P161" s="372">
+        <v>617219.524232</v>
+      </c>
+      <c r="P161" s="406">
         <f>SUM(P6:P160)</f>
-        <v>160637135.07000002</v>
-      </c>
-      <c r="Q161" s="373"/>
+        <v>160799642.07000002</v>
+      </c>
+      <c r="Q161" s="407"/>
       <c r="R161" s="167">
         <f>SUM(R6:R160)</f>
-        <v>165509374.06999999</v>
-      </c>
-      <c r="S161" s="372"/>
-      <c r="T161" s="373"/>
+        <v>165676810.06999999</v>
+      </c>
+      <c r="S161" s="406"/>
+      <c r="T161" s="407"/>
     </row>
     <row r="162" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B162" s="370" t="s">
+      <c r="B162" s="404" t="s">
         <v>314</v>
       </c>
-      <c r="C162" s="370"/>
-      <c r="D162" s="370"/>
-      <c r="E162" s="370"/>
-      <c r="F162" s="370"/>
-      <c r="G162" s="370"/>
-      <c r="H162" s="370"/>
-      <c r="I162" s="370"/>
-      <c r="J162" s="370"/>
-      <c r="K162" s="370"/>
-      <c r="L162" s="370"/>
-      <c r="M162" s="370"/>
-      <c r="N162" s="370"/>
-      <c r="O162" s="370"/>
-      <c r="P162" s="370"/>
-      <c r="Q162" s="370"/>
-      <c r="R162" s="370"/>
-      <c r="S162" s="370"/>
-      <c r="T162" s="370"/>
+      <c r="C162" s="404"/>
+      <c r="D162" s="404"/>
+      <c r="E162" s="404"/>
+      <c r="F162" s="404"/>
+      <c r="G162" s="404"/>
+      <c r="H162" s="404"/>
+      <c r="I162" s="404"/>
+      <c r="J162" s="404"/>
+      <c r="K162" s="404"/>
+      <c r="L162" s="404"/>
+      <c r="M162" s="404"/>
+      <c r="N162" s="404"/>
+      <c r="O162" s="404"/>
+      <c r="P162" s="404"/>
+      <c r="Q162" s="404"/>
+      <c r="R162" s="404"/>
+      <c r="S162" s="404"/>
+      <c r="T162" s="404"/>
     </row>
     <row r="163" spans="1:20" ht="49.7" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B163" s="371"/>
-      <c r="C163" s="371"/>
-      <c r="D163" s="371"/>
-      <c r="E163" s="371"/>
-      <c r="F163" s="371"/>
-      <c r="G163" s="371"/>
-      <c r="H163" s="371"/>
-      <c r="I163" s="371"/>
-      <c r="J163" s="371"/>
-      <c r="K163" s="371"/>
-      <c r="L163" s="371"/>
-      <c r="M163" s="371"/>
-      <c r="N163" s="371"/>
-      <c r="O163" s="371"/>
-      <c r="P163" s="371"/>
-      <c r="Q163" s="371"/>
-      <c r="R163" s="371"/>
-      <c r="S163" s="371"/>
-      <c r="T163" s="371"/>
+      <c r="B163" s="405"/>
+      <c r="C163" s="405"/>
+      <c r="D163" s="405"/>
+      <c r="E163" s="405"/>
+      <c r="F163" s="405"/>
+      <c r="G163" s="405"/>
+      <c r="H163" s="405"/>
+      <c r="I163" s="405"/>
+      <c r="J163" s="405"/>
+      <c r="K163" s="405"/>
+      <c r="L163" s="405"/>
+      <c r="M163" s="405"/>
+      <c r="N163" s="405"/>
+      <c r="O163" s="405"/>
+      <c r="P163" s="405"/>
+      <c r="Q163" s="405"/>
+      <c r="R163" s="405"/>
+      <c r="S163" s="405"/>
+      <c r="T163" s="405"/>
     </row>
     <row r="164" spans="1:20" ht="13.7" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B164" s="371" t="s">
+      <c r="B164" s="405" t="s">
         <v>259</v>
       </c>
-      <c r="C164" s="371"/>
-      <c r="D164" s="371"/>
-      <c r="E164" s="371"/>
-      <c r="F164" s="371"/>
-      <c r="G164" s="371"/>
-      <c r="H164" s="371"/>
-      <c r="I164" s="371"/>
-      <c r="J164" s="371"/>
-      <c r="K164" s="371"/>
-      <c r="L164" s="371"/>
-      <c r="M164" s="371"/>
-      <c r="N164" s="371"/>
-      <c r="O164" s="371"/>
-      <c r="P164" s="371"/>
-      <c r="Q164" s="371"/>
-      <c r="R164" s="371"/>
-      <c r="S164" s="371"/>
-      <c r="T164" s="371"/>
+      <c r="C164" s="405"/>
+      <c r="D164" s="405"/>
+      <c r="E164" s="405"/>
+      <c r="F164" s="405"/>
+      <c r="G164" s="405"/>
+      <c r="H164" s="405"/>
+      <c r="I164" s="405"/>
+      <c r="J164" s="405"/>
+      <c r="K164" s="405"/>
+      <c r="L164" s="405"/>
+      <c r="M164" s="405"/>
+      <c r="N164" s="405"/>
+      <c r="O164" s="405"/>
+      <c r="P164" s="405"/>
+      <c r="Q164" s="405"/>
+      <c r="R164" s="405"/>
+      <c r="S164" s="405"/>
+      <c r="T164" s="405"/>
     </row>
     <row r="165" spans="1:20" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B165" s="371"/>
-      <c r="C165" s="371"/>
-      <c r="D165" s="371"/>
-      <c r="E165" s="371"/>
-      <c r="F165" s="371"/>
-      <c r="G165" s="371"/>
-      <c r="H165" s="371"/>
-      <c r="I165" s="371"/>
-      <c r="J165" s="371"/>
-      <c r="K165" s="371"/>
-      <c r="L165" s="371"/>
-      <c r="M165" s="371"/>
-      <c r="N165" s="371"/>
-      <c r="O165" s="371"/>
-      <c r="P165" s="371"/>
-      <c r="Q165" s="371"/>
-      <c r="R165" s="371"/>
-      <c r="S165" s="371"/>
-      <c r="T165" s="371"/>
+      <c r="B165" s="405"/>
+      <c r="C165" s="405"/>
+      <c r="D165" s="405"/>
+      <c r="E165" s="405"/>
+      <c r="F165" s="405"/>
+      <c r="G165" s="405"/>
+      <c r="H165" s="405"/>
+      <c r="I165" s="405"/>
+      <c r="J165" s="405"/>
+      <c r="K165" s="405"/>
+      <c r="L165" s="405"/>
+      <c r="M165" s="405"/>
+      <c r="N165" s="405"/>
+      <c r="O165" s="405"/>
+      <c r="P165" s="405"/>
+      <c r="Q165" s="405"/>
+      <c r="R165" s="405"/>
+      <c r="S165" s="405"/>
+      <c r="T165" s="405"/>
     </row>
     <row r="166" spans="1:20" ht="3.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B166" s="371"/>
-      <c r="C166" s="371"/>
-      <c r="D166" s="371"/>
-      <c r="E166" s="371"/>
-      <c r="F166" s="371"/>
-      <c r="G166" s="371"/>
-      <c r="H166" s="371"/>
-      <c r="I166" s="371"/>
-      <c r="J166" s="371"/>
-      <c r="K166" s="371"/>
-      <c r="L166" s="371"/>
-      <c r="M166" s="371"/>
-      <c r="N166" s="371"/>
-      <c r="O166" s="371"/>
-      <c r="P166" s="371"/>
-      <c r="Q166" s="371"/>
-      <c r="R166" s="371"/>
-      <c r="S166" s="371"/>
-      <c r="T166" s="371"/>
+      <c r="B166" s="405"/>
+      <c r="C166" s="405"/>
+      <c r="D166" s="405"/>
+      <c r="E166" s="405"/>
+      <c r="F166" s="405"/>
+      <c r="G166" s="405"/>
+      <c r="H166" s="405"/>
+      <c r="I166" s="405"/>
+      <c r="J166" s="405"/>
+      <c r="K166" s="405"/>
+      <c r="L166" s="405"/>
+      <c r="M166" s="405"/>
+      <c r="N166" s="405"/>
+      <c r="O166" s="405"/>
+      <c r="P166" s="405"/>
+      <c r="Q166" s="405"/>
+      <c r="R166" s="405"/>
+      <c r="S166" s="405"/>
+      <c r="T166" s="405"/>
     </row>
     <row r="167" spans="1:20" ht="128.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B167" s="371"/>
-      <c r="C167" s="371"/>
-      <c r="D167" s="371"/>
-      <c r="E167" s="371"/>
-      <c r="F167" s="371"/>
-      <c r="G167" s="371"/>
-      <c r="H167" s="371"/>
-      <c r="I167" s="371"/>
-      <c r="J167" s="371"/>
-      <c r="K167" s="371"/>
-      <c r="L167" s="371"/>
-      <c r="M167" s="371"/>
-      <c r="N167" s="371"/>
-      <c r="O167" s="371"/>
-      <c r="P167" s="371"/>
-      <c r="Q167" s="371"/>
-      <c r="R167" s="371"/>
-      <c r="S167" s="371"/>
-      <c r="T167" s="371"/>
+      <c r="B167" s="405"/>
+      <c r="C167" s="405"/>
+      <c r="D167" s="405"/>
+      <c r="E167" s="405"/>
+      <c r="F167" s="405"/>
+      <c r="G167" s="405"/>
+      <c r="H167" s="405"/>
+      <c r="I167" s="405"/>
+      <c r="J167" s="405"/>
+      <c r="K167" s="405"/>
+      <c r="L167" s="405"/>
+      <c r="M167" s="405"/>
+      <c r="N167" s="405"/>
+      <c r="O167" s="405"/>
+      <c r="P167" s="405"/>
+      <c r="Q167" s="405"/>
+      <c r="R167" s="405"/>
+      <c r="S167" s="405"/>
+      <c r="T167" s="405"/>
     </row>
   </sheetData>
   <mergeCells count="186">
+    <mergeCell ref="P146:Q146"/>
+    <mergeCell ref="P147:Q147"/>
+    <mergeCell ref="P148:Q148"/>
+    <mergeCell ref="P149:Q149"/>
+    <mergeCell ref="P151:Q151"/>
+    <mergeCell ref="P141:Q141"/>
+    <mergeCell ref="P142:Q142"/>
+    <mergeCell ref="P143:Q143"/>
+    <mergeCell ref="P144:Q144"/>
+    <mergeCell ref="P145:Q145"/>
+    <mergeCell ref="P150:Q150"/>
+    <mergeCell ref="B162:T163"/>
+    <mergeCell ref="B164:T167"/>
+    <mergeCell ref="P157:Q157"/>
+    <mergeCell ref="P158:Q158"/>
+    <mergeCell ref="P161:Q161"/>
+    <mergeCell ref="P159:Q159"/>
+    <mergeCell ref="P160:Q160"/>
+    <mergeCell ref="P152:Q152"/>
+    <mergeCell ref="P153:Q153"/>
+    <mergeCell ref="P154:Q154"/>
+    <mergeCell ref="P155:Q155"/>
+    <mergeCell ref="P156:Q156"/>
+    <mergeCell ref="S161:T161"/>
+    <mergeCell ref="P136:Q136"/>
+    <mergeCell ref="P137:Q137"/>
+    <mergeCell ref="P138:Q138"/>
+    <mergeCell ref="P139:Q139"/>
+    <mergeCell ref="P140:Q140"/>
+    <mergeCell ref="P131:Q131"/>
+    <mergeCell ref="P132:Q132"/>
+    <mergeCell ref="P133:Q133"/>
+    <mergeCell ref="P134:Q134"/>
+    <mergeCell ref="P135:Q135"/>
+    <mergeCell ref="P126:Q126"/>
+    <mergeCell ref="P127:Q127"/>
+    <mergeCell ref="P128:Q128"/>
+    <mergeCell ref="P129:Q129"/>
+    <mergeCell ref="P130:Q130"/>
+    <mergeCell ref="P121:Q121"/>
+    <mergeCell ref="P122:Q122"/>
+    <mergeCell ref="P123:Q123"/>
+    <mergeCell ref="P124:Q124"/>
+    <mergeCell ref="P125:Q125"/>
+    <mergeCell ref="P116:Q116"/>
+    <mergeCell ref="P117:Q117"/>
+    <mergeCell ref="P118:Q118"/>
+    <mergeCell ref="P119:Q119"/>
+    <mergeCell ref="P120:Q120"/>
+    <mergeCell ref="P111:Q111"/>
+    <mergeCell ref="P112:Q112"/>
+    <mergeCell ref="P113:Q113"/>
+    <mergeCell ref="P114:Q114"/>
+    <mergeCell ref="P115:Q115"/>
+    <mergeCell ref="P106:Q106"/>
+    <mergeCell ref="P107:Q107"/>
+    <mergeCell ref="P108:Q108"/>
+    <mergeCell ref="P109:Q109"/>
+    <mergeCell ref="P110:Q110"/>
+    <mergeCell ref="P101:Q101"/>
+    <mergeCell ref="P102:Q102"/>
+    <mergeCell ref="P103:Q103"/>
+    <mergeCell ref="P104:Q104"/>
+    <mergeCell ref="P105:Q105"/>
+    <mergeCell ref="P96:Q96"/>
+    <mergeCell ref="P97:Q97"/>
+    <mergeCell ref="P98:Q98"/>
+    <mergeCell ref="P99:Q99"/>
+    <mergeCell ref="P100:Q100"/>
+    <mergeCell ref="P91:Q91"/>
+    <mergeCell ref="P92:Q92"/>
+    <mergeCell ref="P93:Q93"/>
+    <mergeCell ref="P94:Q94"/>
+    <mergeCell ref="P95:Q95"/>
+    <mergeCell ref="P86:Q86"/>
+    <mergeCell ref="P87:Q87"/>
+    <mergeCell ref="P88:Q88"/>
+    <mergeCell ref="P89:Q89"/>
+    <mergeCell ref="P90:Q90"/>
+    <mergeCell ref="P81:Q81"/>
+    <mergeCell ref="P82:Q82"/>
+    <mergeCell ref="P83:Q83"/>
+    <mergeCell ref="P84:Q84"/>
+    <mergeCell ref="P85:Q85"/>
+    <mergeCell ref="P76:Q76"/>
+    <mergeCell ref="P77:Q77"/>
+    <mergeCell ref="P78:Q78"/>
+    <mergeCell ref="P79:Q79"/>
+    <mergeCell ref="P80:Q80"/>
+    <mergeCell ref="P71:Q71"/>
+    <mergeCell ref="P72:Q72"/>
+    <mergeCell ref="P73:Q73"/>
+    <mergeCell ref="P74:Q74"/>
+    <mergeCell ref="P75:Q75"/>
+    <mergeCell ref="P66:Q66"/>
+    <mergeCell ref="P67:Q67"/>
+    <mergeCell ref="P68:Q68"/>
+    <mergeCell ref="P69:Q69"/>
+    <mergeCell ref="P70:Q70"/>
+    <mergeCell ref="P61:Q61"/>
+    <mergeCell ref="P62:Q62"/>
+    <mergeCell ref="P63:Q63"/>
+    <mergeCell ref="P64:Q64"/>
+    <mergeCell ref="P65:Q65"/>
+    <mergeCell ref="P56:Q56"/>
+    <mergeCell ref="P57:Q57"/>
+    <mergeCell ref="P58:Q58"/>
+    <mergeCell ref="P59:Q59"/>
+    <mergeCell ref="P60:Q60"/>
+    <mergeCell ref="P51:Q51"/>
+    <mergeCell ref="P52:Q52"/>
+    <mergeCell ref="P53:Q53"/>
+    <mergeCell ref="P54:Q54"/>
+    <mergeCell ref="P55:Q55"/>
+    <mergeCell ref="P27:Q27"/>
+    <mergeCell ref="P28:Q28"/>
+    <mergeCell ref="P29:Q29"/>
+    <mergeCell ref="P30:Q30"/>
+    <mergeCell ref="P46:Q46"/>
+    <mergeCell ref="P47:Q47"/>
+    <mergeCell ref="P48:Q48"/>
+    <mergeCell ref="P49:Q49"/>
+    <mergeCell ref="P50:Q50"/>
+    <mergeCell ref="P41:Q41"/>
+    <mergeCell ref="P42:Q42"/>
+    <mergeCell ref="P43:Q43"/>
+    <mergeCell ref="P44:Q44"/>
+    <mergeCell ref="P45:Q45"/>
+    <mergeCell ref="P36:Q36"/>
+    <mergeCell ref="P37:Q37"/>
+    <mergeCell ref="P38:Q38"/>
+    <mergeCell ref="P39:Q39"/>
+    <mergeCell ref="P40:Q40"/>
+    <mergeCell ref="P31:Q31"/>
+    <mergeCell ref="P32:Q32"/>
+    <mergeCell ref="P33:Q33"/>
+    <mergeCell ref="P34:Q34"/>
+    <mergeCell ref="P35:Q35"/>
+    <mergeCell ref="K2:L2"/>
+    <mergeCell ref="M4:M5"/>
+    <mergeCell ref="P1:Q1"/>
+    <mergeCell ref="P2:Q2"/>
+    <mergeCell ref="G2:H2"/>
+    <mergeCell ref="N4:N5"/>
+    <mergeCell ref="O4:O5"/>
+    <mergeCell ref="C2:E2"/>
+    <mergeCell ref="C1:L1"/>
+    <mergeCell ref="N1:O1"/>
+    <mergeCell ref="P4:Q4"/>
+    <mergeCell ref="P5:Q5"/>
+    <mergeCell ref="A3:T3"/>
+    <mergeCell ref="R4:S5"/>
+    <mergeCell ref="T4:T5"/>
+    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="B4:B5"/>
+    <mergeCell ref="C4:C5"/>
+    <mergeCell ref="D4:D5"/>
+    <mergeCell ref="K4:K5"/>
+    <mergeCell ref="H4:H5"/>
+    <mergeCell ref="E4:E5"/>
+    <mergeCell ref="F4:F5"/>
+    <mergeCell ref="G4:G5"/>
     <mergeCell ref="I4:I5"/>
     <mergeCell ref="J4:J5"/>
     <mergeCell ref="P6:Q6"/>
@@ -17325,168 +17465,6 @@
     <mergeCell ref="P23:Q23"/>
     <mergeCell ref="P24:Q24"/>
     <mergeCell ref="P25:Q25"/>
-    <mergeCell ref="K2:L2"/>
-    <mergeCell ref="M4:M5"/>
-    <mergeCell ref="P1:Q1"/>
-    <mergeCell ref="P2:Q2"/>
-    <mergeCell ref="G2:H2"/>
-    <mergeCell ref="N4:N5"/>
-    <mergeCell ref="O4:O5"/>
-    <mergeCell ref="C2:E2"/>
-    <mergeCell ref="C1:L1"/>
-    <mergeCell ref="N1:O1"/>
-    <mergeCell ref="P4:Q4"/>
-    <mergeCell ref="P5:Q5"/>
-    <mergeCell ref="A3:T3"/>
-    <mergeCell ref="R4:S5"/>
-    <mergeCell ref="T4:T5"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="B4:B5"/>
-    <mergeCell ref="C4:C5"/>
-    <mergeCell ref="D4:D5"/>
-    <mergeCell ref="K4:K5"/>
-    <mergeCell ref="H4:H5"/>
-    <mergeCell ref="E4:E5"/>
-    <mergeCell ref="F4:F5"/>
-    <mergeCell ref="G4:G5"/>
-    <mergeCell ref="P27:Q27"/>
-    <mergeCell ref="P28:Q28"/>
-    <mergeCell ref="P29:Q29"/>
-    <mergeCell ref="P30:Q30"/>
-    <mergeCell ref="P46:Q46"/>
-    <mergeCell ref="P47:Q47"/>
-    <mergeCell ref="P48:Q48"/>
-    <mergeCell ref="P49:Q49"/>
-    <mergeCell ref="P50:Q50"/>
-    <mergeCell ref="P41:Q41"/>
-    <mergeCell ref="P42:Q42"/>
-    <mergeCell ref="P43:Q43"/>
-    <mergeCell ref="P44:Q44"/>
-    <mergeCell ref="P45:Q45"/>
-    <mergeCell ref="P36:Q36"/>
-    <mergeCell ref="P37:Q37"/>
-    <mergeCell ref="P38:Q38"/>
-    <mergeCell ref="P39:Q39"/>
-    <mergeCell ref="P40:Q40"/>
-    <mergeCell ref="P31:Q31"/>
-    <mergeCell ref="P32:Q32"/>
-    <mergeCell ref="P33:Q33"/>
-    <mergeCell ref="P34:Q34"/>
-    <mergeCell ref="P35:Q35"/>
-    <mergeCell ref="P56:Q56"/>
-    <mergeCell ref="P57:Q57"/>
-    <mergeCell ref="P58:Q58"/>
-    <mergeCell ref="P59:Q59"/>
-    <mergeCell ref="P60:Q60"/>
-    <mergeCell ref="P51:Q51"/>
-    <mergeCell ref="P52:Q52"/>
-    <mergeCell ref="P53:Q53"/>
-    <mergeCell ref="P54:Q54"/>
-    <mergeCell ref="P55:Q55"/>
-    <mergeCell ref="P66:Q66"/>
-    <mergeCell ref="P67:Q67"/>
-    <mergeCell ref="P68:Q68"/>
-    <mergeCell ref="P69:Q69"/>
-    <mergeCell ref="P70:Q70"/>
-    <mergeCell ref="P61:Q61"/>
-    <mergeCell ref="P62:Q62"/>
-    <mergeCell ref="P63:Q63"/>
-    <mergeCell ref="P64:Q64"/>
-    <mergeCell ref="P65:Q65"/>
-    <mergeCell ref="P76:Q76"/>
-    <mergeCell ref="P77:Q77"/>
-    <mergeCell ref="P78:Q78"/>
-    <mergeCell ref="P79:Q79"/>
-    <mergeCell ref="P80:Q80"/>
-    <mergeCell ref="P71:Q71"/>
-    <mergeCell ref="P72:Q72"/>
-    <mergeCell ref="P73:Q73"/>
-    <mergeCell ref="P74:Q74"/>
-    <mergeCell ref="P75:Q75"/>
-    <mergeCell ref="P86:Q86"/>
-    <mergeCell ref="P87:Q87"/>
-    <mergeCell ref="P88:Q88"/>
-    <mergeCell ref="P89:Q89"/>
-    <mergeCell ref="P90:Q90"/>
-    <mergeCell ref="P81:Q81"/>
-    <mergeCell ref="P82:Q82"/>
-    <mergeCell ref="P83:Q83"/>
-    <mergeCell ref="P84:Q84"/>
-    <mergeCell ref="P85:Q85"/>
-    <mergeCell ref="P96:Q96"/>
-    <mergeCell ref="P97:Q97"/>
-    <mergeCell ref="P98:Q98"/>
-    <mergeCell ref="P99:Q99"/>
-    <mergeCell ref="P100:Q100"/>
-    <mergeCell ref="P91:Q91"/>
-    <mergeCell ref="P92:Q92"/>
-    <mergeCell ref="P93:Q93"/>
-    <mergeCell ref="P94:Q94"/>
-    <mergeCell ref="P95:Q95"/>
-    <mergeCell ref="P106:Q106"/>
-    <mergeCell ref="P107:Q107"/>
-    <mergeCell ref="P108:Q108"/>
-    <mergeCell ref="P109:Q109"/>
-    <mergeCell ref="P110:Q110"/>
-    <mergeCell ref="P101:Q101"/>
-    <mergeCell ref="P102:Q102"/>
-    <mergeCell ref="P103:Q103"/>
-    <mergeCell ref="P104:Q104"/>
-    <mergeCell ref="P105:Q105"/>
-    <mergeCell ref="P116:Q116"/>
-    <mergeCell ref="P117:Q117"/>
-    <mergeCell ref="P118:Q118"/>
-    <mergeCell ref="P119:Q119"/>
-    <mergeCell ref="P120:Q120"/>
-    <mergeCell ref="P111:Q111"/>
-    <mergeCell ref="P112:Q112"/>
-    <mergeCell ref="P113:Q113"/>
-    <mergeCell ref="P114:Q114"/>
-    <mergeCell ref="P115:Q115"/>
-    <mergeCell ref="P126:Q126"/>
-    <mergeCell ref="P127:Q127"/>
-    <mergeCell ref="P128:Q128"/>
-    <mergeCell ref="P129:Q129"/>
-    <mergeCell ref="P130:Q130"/>
-    <mergeCell ref="P121:Q121"/>
-    <mergeCell ref="P122:Q122"/>
-    <mergeCell ref="P123:Q123"/>
-    <mergeCell ref="P124:Q124"/>
-    <mergeCell ref="P125:Q125"/>
-    <mergeCell ref="P136:Q136"/>
-    <mergeCell ref="P137:Q137"/>
-    <mergeCell ref="P138:Q138"/>
-    <mergeCell ref="P139:Q139"/>
-    <mergeCell ref="P140:Q140"/>
-    <mergeCell ref="P131:Q131"/>
-    <mergeCell ref="P132:Q132"/>
-    <mergeCell ref="P133:Q133"/>
-    <mergeCell ref="P134:Q134"/>
-    <mergeCell ref="P135:Q135"/>
-    <mergeCell ref="B162:T163"/>
-    <mergeCell ref="B164:T167"/>
-    <mergeCell ref="P157:Q157"/>
-    <mergeCell ref="P158:Q158"/>
-    <mergeCell ref="P161:Q161"/>
-    <mergeCell ref="P159:Q159"/>
-    <mergeCell ref="P160:Q160"/>
-    <mergeCell ref="P152:Q152"/>
-    <mergeCell ref="P153:Q153"/>
-    <mergeCell ref="P154:Q154"/>
-    <mergeCell ref="P155:Q155"/>
-    <mergeCell ref="P156:Q156"/>
-    <mergeCell ref="S161:T161"/>
-    <mergeCell ref="P146:Q146"/>
-    <mergeCell ref="P147:Q147"/>
-    <mergeCell ref="P148:Q148"/>
-    <mergeCell ref="P149:Q149"/>
-    <mergeCell ref="P151:Q151"/>
-    <mergeCell ref="P141:Q141"/>
-    <mergeCell ref="P142:Q142"/>
-    <mergeCell ref="P143:Q143"/>
-    <mergeCell ref="P144:Q144"/>
-    <mergeCell ref="P145:Q145"/>
-    <mergeCell ref="P150:Q150"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="U66" r:id="rId1" xr:uid="{60CCA824-04D7-4098-BB5B-CC4EC0E5DE92}"/>
@@ -17558,11 +17536,11 @@
       <c r="G4" s="33" t="s">
         <v>164</v>
       </c>
-      <c r="H4" s="402">
+      <c r="H4" s="410">
         <v>93</v>
       </c>
-      <c r="I4" s="402"/>
-      <c r="J4" s="403"/>
+      <c r="I4" s="410"/>
+      <c r="J4" s="411"/>
       <c r="K4" s="324"/>
       <c r="L4" s="324"/>
     </row>
@@ -17581,40 +17559,40 @@
       <c r="L5" s="324"/>
     </row>
     <row r="6" spans="3:12" x14ac:dyDescent="0.25">
-      <c r="C6" s="404" t="s">
-        <v>344</v>
-      </c>
-      <c r="D6" s="405"/>
-      <c r="E6" s="405"/>
-      <c r="F6" s="405"/>
-      <c r="G6" s="405"/>
-      <c r="H6" s="405"/>
-      <c r="I6" s="405"/>
-      <c r="J6" s="406"/>
+      <c r="C6" s="412" t="s">
+        <v>343</v>
+      </c>
+      <c r="D6" s="413"/>
+      <c r="E6" s="413"/>
+      <c r="F6" s="413"/>
+      <c r="G6" s="413"/>
+      <c r="H6" s="413"/>
+      <c r="I6" s="413"/>
+      <c r="J6" s="414"/>
       <c r="K6" s="324"/>
       <c r="L6" s="324"/>
     </row>
     <row r="7" spans="3:12" x14ac:dyDescent="0.25">
-      <c r="C7" s="407"/>
-      <c r="D7" s="408"/>
-      <c r="E7" s="408"/>
-      <c r="F7" s="408"/>
-      <c r="G7" s="408"/>
-      <c r="H7" s="408"/>
-      <c r="I7" s="408"/>
-      <c r="J7" s="409"/>
+      <c r="C7" s="415"/>
+      <c r="D7" s="416"/>
+      <c r="E7" s="416"/>
+      <c r="F7" s="416"/>
+      <c r="G7" s="416"/>
+      <c r="H7" s="416"/>
+      <c r="I7" s="416"/>
+      <c r="J7" s="417"/>
       <c r="K7" s="33"/>
       <c r="L7" s="33"/>
     </row>
     <row r="8" spans="3:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C8" s="410"/>
-      <c r="D8" s="411"/>
-      <c r="E8" s="411"/>
-      <c r="F8" s="411"/>
-      <c r="G8" s="411"/>
-      <c r="H8" s="411"/>
-      <c r="I8" s="411"/>
-      <c r="J8" s="412"/>
+      <c r="C8" s="418"/>
+      <c r="D8" s="419"/>
+      <c r="E8" s="419"/>
+      <c r="F8" s="419"/>
+      <c r="G8" s="419"/>
+      <c r="H8" s="419"/>
+      <c r="I8" s="419"/>
+      <c r="J8" s="420"/>
     </row>
     <row r="10" spans="3:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="11" spans="3:12" x14ac:dyDescent="0.25">
@@ -17662,11 +17640,11 @@
       <c r="G13" s="33" t="s">
         <v>164</v>
       </c>
-      <c r="H13" s="402">
+      <c r="H13" s="410">
         <v>44</v>
       </c>
-      <c r="I13" s="402"/>
-      <c r="J13" s="403"/>
+      <c r="I13" s="410"/>
+      <c r="J13" s="411"/>
       <c r="K13" s="324"/>
       <c r="L13" s="324"/>
     </row>
@@ -17685,40 +17663,40 @@
       <c r="L14" s="324"/>
     </row>
     <row r="15" spans="3:12" x14ac:dyDescent="0.25">
-      <c r="C15" s="404" t="s">
-        <v>345</v>
-      </c>
-      <c r="D15" s="405"/>
-      <c r="E15" s="405"/>
-      <c r="F15" s="405"/>
-      <c r="G15" s="405"/>
-      <c r="H15" s="405"/>
-      <c r="I15" s="405"/>
-      <c r="J15" s="406"/>
+      <c r="C15" s="412" t="s">
+        <v>344</v>
+      </c>
+      <c r="D15" s="413"/>
+      <c r="E15" s="413"/>
+      <c r="F15" s="413"/>
+      <c r="G15" s="413"/>
+      <c r="H15" s="413"/>
+      <c r="I15" s="413"/>
+      <c r="J15" s="414"/>
       <c r="K15" s="324"/>
       <c r="L15" s="324"/>
     </row>
     <row r="16" spans="3:12" x14ac:dyDescent="0.25">
-      <c r="C16" s="407"/>
-      <c r="D16" s="408"/>
-      <c r="E16" s="408"/>
-      <c r="F16" s="408"/>
-      <c r="G16" s="408"/>
-      <c r="H16" s="408"/>
-      <c r="I16" s="408"/>
-      <c r="J16" s="409"/>
+      <c r="C16" s="415"/>
+      <c r="D16" s="416"/>
+      <c r="E16" s="416"/>
+      <c r="F16" s="416"/>
+      <c r="G16" s="416"/>
+      <c r="H16" s="416"/>
+      <c r="I16" s="416"/>
+      <c r="J16" s="417"/>
       <c r="K16" s="324"/>
       <c r="L16" s="324"/>
     </row>
     <row r="17" spans="3:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C17" s="410"/>
-      <c r="D17" s="411"/>
-      <c r="E17" s="411"/>
-      <c r="F17" s="411"/>
-      <c r="G17" s="411"/>
-      <c r="H17" s="411"/>
-      <c r="I17" s="411"/>
-      <c r="J17" s="412"/>
+      <c r="C17" s="418"/>
+      <c r="D17" s="419"/>
+      <c r="E17" s="419"/>
+      <c r="F17" s="419"/>
+      <c r="G17" s="419"/>
+      <c r="H17" s="419"/>
+      <c r="I17" s="419"/>
+      <c r="J17" s="420"/>
     </row>
     <row r="19" spans="3:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="20" spans="3:13" x14ac:dyDescent="0.25">
@@ -17767,11 +17745,11 @@
       <c r="G22" s="33" t="s">
         <v>164</v>
       </c>
-      <c r="H22" s="402">
+      <c r="H22" s="410">
         <v>90</v>
       </c>
-      <c r="I22" s="402"/>
-      <c r="J22" s="403"/>
+      <c r="I22" s="410"/>
+      <c r="J22" s="411"/>
       <c r="K22" s="324"/>
       <c r="L22" s="324"/>
       <c r="M22" s="324"/>
@@ -17792,42 +17770,42 @@
       <c r="M23" s="324"/>
     </row>
     <row r="24" spans="3:13" x14ac:dyDescent="0.25">
-      <c r="C24" s="404" t="s">
-        <v>346</v>
-      </c>
-      <c r="D24" s="405"/>
-      <c r="E24" s="405"/>
-      <c r="F24" s="405"/>
-      <c r="G24" s="405"/>
-      <c r="H24" s="405"/>
-      <c r="I24" s="405"/>
-      <c r="J24" s="406"/>
+      <c r="C24" s="412" t="s">
+        <v>345</v>
+      </c>
+      <c r="D24" s="413"/>
+      <c r="E24" s="413"/>
+      <c r="F24" s="413"/>
+      <c r="G24" s="413"/>
+      <c r="H24" s="413"/>
+      <c r="I24" s="413"/>
+      <c r="J24" s="414"/>
       <c r="K24" s="324"/>
       <c r="L24" s="324"/>
       <c r="M24" s="324"/>
     </row>
     <row r="25" spans="3:13" x14ac:dyDescent="0.25">
-      <c r="C25" s="407"/>
-      <c r="D25" s="408"/>
-      <c r="E25" s="408"/>
-      <c r="F25" s="408"/>
-      <c r="G25" s="408"/>
-      <c r="H25" s="408"/>
-      <c r="I25" s="408"/>
-      <c r="J25" s="409"/>
+      <c r="C25" s="415"/>
+      <c r="D25" s="416"/>
+      <c r="E25" s="416"/>
+      <c r="F25" s="416"/>
+      <c r="G25" s="416"/>
+      <c r="H25" s="416"/>
+      <c r="I25" s="416"/>
+      <c r="J25" s="417"/>
       <c r="K25" s="324"/>
       <c r="L25" s="324"/>
       <c r="M25" s="324"/>
     </row>
     <row r="26" spans="3:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C26" s="410"/>
-      <c r="D26" s="411"/>
-      <c r="E26" s="411"/>
-      <c r="F26" s="411"/>
-      <c r="G26" s="411"/>
-      <c r="H26" s="411"/>
-      <c r="I26" s="411"/>
-      <c r="J26" s="412"/>
+      <c r="C26" s="418"/>
+      <c r="D26" s="419"/>
+      <c r="E26" s="419"/>
+      <c r="F26" s="419"/>
+      <c r="G26" s="419"/>
+      <c r="H26" s="419"/>
+      <c r="I26" s="419"/>
+      <c r="J26" s="420"/>
       <c r="K26" s="324"/>
       <c r="L26" s="324"/>
       <c r="M26" s="324"/>
@@ -17878,11 +17856,11 @@
       <c r="G31" s="33" t="s">
         <v>164</v>
       </c>
-      <c r="H31" s="402">
+      <c r="H31" s="410">
         <v>78</v>
       </c>
-      <c r="I31" s="402"/>
-      <c r="J31" s="403"/>
+      <c r="I31" s="410"/>
+      <c r="J31" s="411"/>
       <c r="K31" s="324"/>
       <c r="L31" s="324"/>
     </row>
@@ -17901,40 +17879,40 @@
       <c r="L32" s="324"/>
     </row>
     <row r="33" spans="3:12" x14ac:dyDescent="0.25">
-      <c r="C33" s="404" t="s">
-        <v>347</v>
-      </c>
-      <c r="D33" s="405"/>
-      <c r="E33" s="405"/>
-      <c r="F33" s="405"/>
-      <c r="G33" s="405"/>
-      <c r="H33" s="405"/>
-      <c r="I33" s="405"/>
-      <c r="J33" s="406"/>
+      <c r="C33" s="412" t="s">
+        <v>346</v>
+      </c>
+      <c r="D33" s="413"/>
+      <c r="E33" s="413"/>
+      <c r="F33" s="413"/>
+      <c r="G33" s="413"/>
+      <c r="H33" s="413"/>
+      <c r="I33" s="413"/>
+      <c r="J33" s="414"/>
       <c r="K33" s="324"/>
       <c r="L33" s="324"/>
     </row>
     <row r="34" spans="3:12" x14ac:dyDescent="0.25">
-      <c r="C34" s="407"/>
-      <c r="D34" s="408"/>
-      <c r="E34" s="408"/>
-      <c r="F34" s="408"/>
-      <c r="G34" s="408"/>
-      <c r="H34" s="408"/>
-      <c r="I34" s="408"/>
-      <c r="J34" s="409"/>
+      <c r="C34" s="415"/>
+      <c r="D34" s="416"/>
+      <c r="E34" s="416"/>
+      <c r="F34" s="416"/>
+      <c r="G34" s="416"/>
+      <c r="H34" s="416"/>
+      <c r="I34" s="416"/>
+      <c r="J34" s="417"/>
       <c r="K34" s="324"/>
       <c r="L34" s="324"/>
     </row>
     <row r="35" spans="3:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C35" s="410"/>
-      <c r="D35" s="411"/>
-      <c r="E35" s="411"/>
-      <c r="F35" s="411"/>
-      <c r="G35" s="411"/>
-      <c r="H35" s="411"/>
-      <c r="I35" s="411"/>
-      <c r="J35" s="412"/>
+      <c r="C35" s="418"/>
+      <c r="D35" s="419"/>
+      <c r="E35" s="419"/>
+      <c r="F35" s="419"/>
+      <c r="G35" s="419"/>
+      <c r="H35" s="419"/>
+      <c r="I35" s="419"/>
+      <c r="J35" s="420"/>
     </row>
     <row r="37" spans="3:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="38" spans="3:12" x14ac:dyDescent="0.25">
@@ -17980,11 +17958,11 @@
       <c r="G40" s="33" t="s">
         <v>164</v>
       </c>
-      <c r="H40" s="402">
+      <c r="H40" s="410">
         <v>2</v>
       </c>
-      <c r="I40" s="402"/>
-      <c r="J40" s="403"/>
+      <c r="I40" s="410"/>
+      <c r="J40" s="411"/>
     </row>
     <row r="41" spans="3:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C41" s="291" t="s">
@@ -17999,36 +17977,36 @@
       <c r="J41" s="61"/>
     </row>
     <row r="42" spans="3:12" x14ac:dyDescent="0.25">
-      <c r="C42" s="404" t="s">
-        <v>348</v>
-      </c>
-      <c r="D42" s="405"/>
-      <c r="E42" s="405"/>
-      <c r="F42" s="405"/>
-      <c r="G42" s="405"/>
-      <c r="H42" s="405"/>
-      <c r="I42" s="405"/>
-      <c r="J42" s="406"/>
+      <c r="C42" s="412" t="s">
+        <v>347</v>
+      </c>
+      <c r="D42" s="413"/>
+      <c r="E42" s="413"/>
+      <c r="F42" s="413"/>
+      <c r="G42" s="413"/>
+      <c r="H42" s="413"/>
+      <c r="I42" s="413"/>
+      <c r="J42" s="414"/>
     </row>
     <row r="43" spans="3:12" x14ac:dyDescent="0.25">
-      <c r="C43" s="407"/>
-      <c r="D43" s="408"/>
-      <c r="E43" s="408"/>
-      <c r="F43" s="408"/>
-      <c r="G43" s="408"/>
-      <c r="H43" s="408"/>
-      <c r="I43" s="408"/>
-      <c r="J43" s="409"/>
+      <c r="C43" s="415"/>
+      <c r="D43" s="416"/>
+      <c r="E43" s="416"/>
+      <c r="F43" s="416"/>
+      <c r="G43" s="416"/>
+      <c r="H43" s="416"/>
+      <c r="I43" s="416"/>
+      <c r="J43" s="417"/>
     </row>
     <row r="44" spans="3:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C44" s="410"/>
-      <c r="D44" s="411"/>
-      <c r="E44" s="411"/>
-      <c r="F44" s="411"/>
-      <c r="G44" s="411"/>
-      <c r="H44" s="411"/>
-      <c r="I44" s="411"/>
-      <c r="J44" s="412"/>
+      <c r="C44" s="418"/>
+      <c r="D44" s="419"/>
+      <c r="E44" s="419"/>
+      <c r="F44" s="419"/>
+      <c r="G44" s="419"/>
+      <c r="H44" s="419"/>
+      <c r="I44" s="419"/>
+      <c r="J44" s="420"/>
     </row>
     <row r="46" spans="3:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="47" spans="3:12" x14ac:dyDescent="0.25">
@@ -18076,11 +18054,11 @@
       <c r="G49" s="33" t="s">
         <v>164</v>
       </c>
-      <c r="H49" s="402">
+      <c r="H49" s="410">
         <v>59</v>
       </c>
-      <c r="I49" s="402"/>
-      <c r="J49" s="403"/>
+      <c r="I49" s="410"/>
+      <c r="J49" s="411"/>
       <c r="K49" s="324"/>
       <c r="L49" s="324"/>
     </row>
@@ -18099,38 +18077,38 @@
       <c r="L50" s="324"/>
     </row>
     <row r="51" spans="3:12" x14ac:dyDescent="0.25">
-      <c r="C51" s="404" t="s">
-        <v>439</v>
-      </c>
-      <c r="D51" s="405"/>
-      <c r="E51" s="405"/>
-      <c r="F51" s="405"/>
-      <c r="G51" s="405"/>
-      <c r="H51" s="405"/>
-      <c r="I51" s="405"/>
-      <c r="J51" s="406"/>
+      <c r="C51" s="412" t="s">
+        <v>438</v>
+      </c>
+      <c r="D51" s="413"/>
+      <c r="E51" s="413"/>
+      <c r="F51" s="413"/>
+      <c r="G51" s="413"/>
+      <c r="H51" s="413"/>
+      <c r="I51" s="413"/>
+      <c r="J51" s="414"/>
       <c r="K51" s="324"/>
       <c r="L51" s="324"/>
     </row>
     <row r="52" spans="3:12" x14ac:dyDescent="0.25">
-      <c r="C52" s="407"/>
-      <c r="D52" s="408"/>
-      <c r="E52" s="408"/>
-      <c r="F52" s="408"/>
-      <c r="G52" s="408"/>
-      <c r="H52" s="408"/>
-      <c r="I52" s="408"/>
-      <c r="J52" s="409"/>
+      <c r="C52" s="415"/>
+      <c r="D52" s="416"/>
+      <c r="E52" s="416"/>
+      <c r="F52" s="416"/>
+      <c r="G52" s="416"/>
+      <c r="H52" s="416"/>
+      <c r="I52" s="416"/>
+      <c r="J52" s="417"/>
     </row>
     <row r="53" spans="3:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C53" s="410"/>
-      <c r="D53" s="411"/>
-      <c r="E53" s="411"/>
-      <c r="F53" s="411"/>
-      <c r="G53" s="411"/>
-      <c r="H53" s="411"/>
-      <c r="I53" s="411"/>
-      <c r="J53" s="412"/>
+      <c r="C53" s="418"/>
+      <c r="D53" s="419"/>
+      <c r="E53" s="419"/>
+      <c r="F53" s="419"/>
+      <c r="G53" s="419"/>
+      <c r="H53" s="419"/>
+      <c r="I53" s="419"/>
+      <c r="J53" s="420"/>
     </row>
     <row r="55" spans="3:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="56" spans="3:12" x14ac:dyDescent="0.25">
@@ -18176,11 +18154,11 @@
       <c r="G58" s="33" t="s">
         <v>164</v>
       </c>
-      <c r="H58" s="402">
+      <c r="H58" s="410">
         <v>39</v>
       </c>
-      <c r="I58" s="402"/>
-      <c r="J58" s="403"/>
+      <c r="I58" s="410"/>
+      <c r="J58" s="411"/>
       <c r="K58" s="324"/>
       <c r="L58" s="324"/>
     </row>
@@ -18199,40 +18177,40 @@
       <c r="L59" s="324"/>
     </row>
     <row r="60" spans="3:12" x14ac:dyDescent="0.25">
-      <c r="C60" s="404" t="s">
-        <v>349</v>
-      </c>
-      <c r="D60" s="405"/>
-      <c r="E60" s="405"/>
-      <c r="F60" s="405"/>
-      <c r="G60" s="405"/>
-      <c r="H60" s="405"/>
-      <c r="I60" s="405"/>
-      <c r="J60" s="406"/>
+      <c r="C60" s="412" t="s">
+        <v>348</v>
+      </c>
+      <c r="D60" s="413"/>
+      <c r="E60" s="413"/>
+      <c r="F60" s="413"/>
+      <c r="G60" s="413"/>
+      <c r="H60" s="413"/>
+      <c r="I60" s="413"/>
+      <c r="J60" s="414"/>
       <c r="K60" s="324"/>
       <c r="L60" s="324"/>
     </row>
     <row r="61" spans="3:12" x14ac:dyDescent="0.25">
-      <c r="C61" s="407"/>
-      <c r="D61" s="408"/>
-      <c r="E61" s="408"/>
-      <c r="F61" s="408"/>
-      <c r="G61" s="408"/>
-      <c r="H61" s="408"/>
-      <c r="I61" s="408"/>
-      <c r="J61" s="409"/>
+      <c r="C61" s="415"/>
+      <c r="D61" s="416"/>
+      <c r="E61" s="416"/>
+      <c r="F61" s="416"/>
+      <c r="G61" s="416"/>
+      <c r="H61" s="416"/>
+      <c r="I61" s="416"/>
+      <c r="J61" s="417"/>
       <c r="K61" s="324"/>
       <c r="L61" s="324"/>
     </row>
     <row r="62" spans="3:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C62" s="410"/>
-      <c r="D62" s="411"/>
-      <c r="E62" s="411"/>
-      <c r="F62" s="411"/>
-      <c r="G62" s="411"/>
-      <c r="H62" s="411"/>
-      <c r="I62" s="411"/>
-      <c r="J62" s="412"/>
+      <c r="C62" s="418"/>
+      <c r="D62" s="419"/>
+      <c r="E62" s="419"/>
+      <c r="F62" s="419"/>
+      <c r="G62" s="419"/>
+      <c r="H62" s="419"/>
+      <c r="I62" s="419"/>
+      <c r="J62" s="420"/>
     </row>
     <row r="64" spans="3:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="65" spans="3:13" x14ac:dyDescent="0.25">
@@ -18248,11 +18226,11 @@
       <c r="H65" s="236"/>
       <c r="I65" s="237"/>
       <c r="J65" s="238"/>
-      <c r="K65" s="413" t="s">
-        <v>350</v>
-      </c>
-      <c r="L65" s="414"/>
-      <c r="M65" s="414"/>
+      <c r="K65" s="421" t="s">
+        <v>349</v>
+      </c>
+      <c r="L65" s="422"/>
+      <c r="M65" s="422"/>
     </row>
     <row r="66" spans="3:13" x14ac:dyDescent="0.25">
       <c r="C66" s="303"/>
@@ -18268,9 +18246,9 @@
         <v>8</v>
       </c>
       <c r="J66" s="60"/>
-      <c r="K66" s="413"/>
-      <c r="L66" s="414"/>
-      <c r="M66" s="414"/>
+      <c r="K66" s="421"/>
+      <c r="L66" s="422"/>
+      <c r="M66" s="422"/>
     </row>
     <row r="67" spans="3:13" x14ac:dyDescent="0.25">
       <c r="C67" s="303" t="s">
@@ -18286,14 +18264,14 @@
       <c r="G67" s="33" t="s">
         <v>164</v>
       </c>
-      <c r="H67" s="402">
+      <c r="H67" s="410">
         <v>104</v>
       </c>
-      <c r="I67" s="402"/>
-      <c r="J67" s="403"/>
-      <c r="K67" s="413"/>
-      <c r="L67" s="414"/>
-      <c r="M67" s="414"/>
+      <c r="I67" s="410"/>
+      <c r="J67" s="411"/>
+      <c r="K67" s="421"/>
+      <c r="L67" s="422"/>
+      <c r="M67" s="422"/>
     </row>
     <row r="68" spans="3:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C68" s="303" t="s">
@@ -18306,50 +18284,50 @@
       <c r="H68" s="33"/>
       <c r="I68" s="33"/>
       <c r="J68" s="61"/>
-      <c r="K68" s="413"/>
-      <c r="L68" s="414"/>
-      <c r="M68" s="414"/>
+      <c r="K68" s="421"/>
+      <c r="L68" s="422"/>
+      <c r="M68" s="422"/>
     </row>
     <row r="69" spans="3:13" x14ac:dyDescent="0.25">
-      <c r="C69" s="404" t="s">
-        <v>351</v>
-      </c>
-      <c r="D69" s="405"/>
-      <c r="E69" s="405"/>
-      <c r="F69" s="405"/>
-      <c r="G69" s="405"/>
-      <c r="H69" s="405"/>
-      <c r="I69" s="405"/>
-      <c r="J69" s="406"/>
-      <c r="K69" s="413"/>
-      <c r="L69" s="414"/>
-      <c r="M69" s="414"/>
+      <c r="C69" s="412" t="s">
+        <v>350</v>
+      </c>
+      <c r="D69" s="413"/>
+      <c r="E69" s="413"/>
+      <c r="F69" s="413"/>
+      <c r="G69" s="413"/>
+      <c r="H69" s="413"/>
+      <c r="I69" s="413"/>
+      <c r="J69" s="414"/>
+      <c r="K69" s="421"/>
+      <c r="L69" s="422"/>
+      <c r="M69" s="422"/>
     </row>
     <row r="70" spans="3:13" x14ac:dyDescent="0.25">
-      <c r="C70" s="407"/>
-      <c r="D70" s="408"/>
-      <c r="E70" s="408"/>
-      <c r="F70" s="408"/>
-      <c r="G70" s="408"/>
-      <c r="H70" s="408"/>
-      <c r="I70" s="408"/>
-      <c r="J70" s="409"/>
-      <c r="K70" s="413"/>
-      <c r="L70" s="414"/>
-      <c r="M70" s="414"/>
+      <c r="C70" s="415"/>
+      <c r="D70" s="416"/>
+      <c r="E70" s="416"/>
+      <c r="F70" s="416"/>
+      <c r="G70" s="416"/>
+      <c r="H70" s="416"/>
+      <c r="I70" s="416"/>
+      <c r="J70" s="417"/>
+      <c r="K70" s="421"/>
+      <c r="L70" s="422"/>
+      <c r="M70" s="422"/>
     </row>
     <row r="71" spans="3:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C71" s="410"/>
-      <c r="D71" s="411"/>
-      <c r="E71" s="411"/>
-      <c r="F71" s="411"/>
-      <c r="G71" s="411"/>
-      <c r="H71" s="411"/>
-      <c r="I71" s="411"/>
-      <c r="J71" s="412"/>
-      <c r="K71" s="413"/>
-      <c r="L71" s="414"/>
-      <c r="M71" s="414"/>
+      <c r="C71" s="418"/>
+      <c r="D71" s="419"/>
+      <c r="E71" s="419"/>
+      <c r="F71" s="419"/>
+      <c r="G71" s="419"/>
+      <c r="H71" s="419"/>
+      <c r="I71" s="419"/>
+      <c r="J71" s="420"/>
+      <c r="K71" s="421"/>
+      <c r="L71" s="422"/>
+      <c r="M71" s="422"/>
     </row>
     <row r="73" spans="3:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="74" spans="3:13" x14ac:dyDescent="0.25">
@@ -18397,11 +18375,11 @@
       <c r="G76" s="33" t="s">
         <v>164</v>
       </c>
-      <c r="H76" s="402">
+      <c r="H76" s="410">
         <v>119</v>
       </c>
-      <c r="I76" s="402"/>
-      <c r="J76" s="403"/>
+      <c r="I76" s="410"/>
+      <c r="J76" s="411"/>
       <c r="K76" s="324"/>
       <c r="L76" s="324"/>
     </row>
@@ -18420,40 +18398,40 @@
       <c r="L77" s="324"/>
     </row>
     <row r="78" spans="3:13" x14ac:dyDescent="0.25">
-      <c r="C78" s="404" t="s">
-        <v>352</v>
-      </c>
-      <c r="D78" s="405"/>
-      <c r="E78" s="405"/>
-      <c r="F78" s="405"/>
-      <c r="G78" s="405"/>
-      <c r="H78" s="405"/>
-      <c r="I78" s="405"/>
-      <c r="J78" s="406"/>
+      <c r="C78" s="412" t="s">
+        <v>351</v>
+      </c>
+      <c r="D78" s="413"/>
+      <c r="E78" s="413"/>
+      <c r="F78" s="413"/>
+      <c r="G78" s="413"/>
+      <c r="H78" s="413"/>
+      <c r="I78" s="413"/>
+      <c r="J78" s="414"/>
       <c r="K78" s="324"/>
       <c r="L78" s="324"/>
     </row>
     <row r="79" spans="3:13" x14ac:dyDescent="0.25">
-      <c r="C79" s="407"/>
-      <c r="D79" s="408"/>
-      <c r="E79" s="408"/>
-      <c r="F79" s="408"/>
-      <c r="G79" s="408"/>
-      <c r="H79" s="408"/>
-      <c r="I79" s="408"/>
-      <c r="J79" s="409"/>
+      <c r="C79" s="415"/>
+      <c r="D79" s="416"/>
+      <c r="E79" s="416"/>
+      <c r="F79" s="416"/>
+      <c r="G79" s="416"/>
+      <c r="H79" s="416"/>
+      <c r="I79" s="416"/>
+      <c r="J79" s="417"/>
       <c r="K79" s="324"/>
       <c r="L79" s="324"/>
     </row>
     <row r="80" spans="3:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C80" s="410"/>
-      <c r="D80" s="411"/>
-      <c r="E80" s="411"/>
-      <c r="F80" s="411"/>
-      <c r="G80" s="411"/>
-      <c r="H80" s="411"/>
-      <c r="I80" s="411"/>
-      <c r="J80" s="412"/>
+      <c r="C80" s="418"/>
+      <c r="D80" s="419"/>
+      <c r="E80" s="419"/>
+      <c r="F80" s="419"/>
+      <c r="G80" s="419"/>
+      <c r="H80" s="419"/>
+      <c r="I80" s="419"/>
+      <c r="J80" s="420"/>
       <c r="K80" s="324"/>
       <c r="L80" s="324"/>
     </row>
@@ -18503,11 +18481,11 @@
       <c r="G85" s="33" t="s">
         <v>164</v>
       </c>
-      <c r="H85" s="402">
+      <c r="H85" s="410">
         <v>60</v>
       </c>
-      <c r="I85" s="402"/>
-      <c r="J85" s="403"/>
+      <c r="I85" s="410"/>
+      <c r="J85" s="411"/>
       <c r="K85" s="324"/>
       <c r="L85" s="324"/>
     </row>
@@ -18526,40 +18504,40 @@
       <c r="L86" s="324"/>
     </row>
     <row r="87" spans="3:12" x14ac:dyDescent="0.25">
-      <c r="C87" s="404" t="s">
-        <v>353</v>
-      </c>
-      <c r="D87" s="405"/>
-      <c r="E87" s="405"/>
-      <c r="F87" s="405"/>
-      <c r="G87" s="405"/>
-      <c r="H87" s="405"/>
-      <c r="I87" s="405"/>
-      <c r="J87" s="406"/>
+      <c r="C87" s="412" t="s">
+        <v>352</v>
+      </c>
+      <c r="D87" s="413"/>
+      <c r="E87" s="413"/>
+      <c r="F87" s="413"/>
+      <c r="G87" s="413"/>
+      <c r="H87" s="413"/>
+      <c r="I87" s="413"/>
+      <c r="J87" s="414"/>
       <c r="K87" s="324"/>
       <c r="L87" s="324"/>
     </row>
     <row r="88" spans="3:12" x14ac:dyDescent="0.25">
-      <c r="C88" s="407"/>
-      <c r="D88" s="408"/>
-      <c r="E88" s="408"/>
-      <c r="F88" s="408"/>
-      <c r="G88" s="408"/>
-      <c r="H88" s="408"/>
-      <c r="I88" s="408"/>
-      <c r="J88" s="409"/>
+      <c r="C88" s="415"/>
+      <c r="D88" s="416"/>
+      <c r="E88" s="416"/>
+      <c r="F88" s="416"/>
+      <c r="G88" s="416"/>
+      <c r="H88" s="416"/>
+      <c r="I88" s="416"/>
+      <c r="J88" s="417"/>
       <c r="K88" s="324"/>
       <c r="L88" s="324"/>
     </row>
     <row r="89" spans="3:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C89" s="410"/>
-      <c r="D89" s="411"/>
-      <c r="E89" s="411"/>
-      <c r="F89" s="411"/>
-      <c r="G89" s="411"/>
-      <c r="H89" s="411"/>
-      <c r="I89" s="411"/>
-      <c r="J89" s="412"/>
+      <c r="C89" s="418"/>
+      <c r="D89" s="419"/>
+      <c r="E89" s="419"/>
+      <c r="F89" s="419"/>
+      <c r="G89" s="419"/>
+      <c r="H89" s="419"/>
+      <c r="I89" s="419"/>
+      <c r="J89" s="420"/>
     </row>
     <row r="91" spans="3:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="92" spans="3:12" x14ac:dyDescent="0.25">
@@ -18607,11 +18585,11 @@
       <c r="G94" s="33" t="s">
         <v>164</v>
       </c>
-      <c r="H94" s="402">
+      <c r="H94" s="410">
         <v>105</v>
       </c>
-      <c r="I94" s="402"/>
-      <c r="J94" s="403"/>
+      <c r="I94" s="410"/>
+      <c r="J94" s="411"/>
       <c r="K94" s="324"/>
       <c r="L94" s="324"/>
     </row>
@@ -18630,40 +18608,40 @@
       <c r="L95" s="324"/>
     </row>
     <row r="96" spans="3:12" x14ac:dyDescent="0.25">
-      <c r="C96" s="404" t="s">
-        <v>369</v>
-      </c>
-      <c r="D96" s="405"/>
-      <c r="E96" s="405"/>
-      <c r="F96" s="405"/>
-      <c r="G96" s="405"/>
-      <c r="H96" s="405"/>
-      <c r="I96" s="405"/>
-      <c r="J96" s="406"/>
+      <c r="C96" s="412" t="s">
+        <v>368</v>
+      </c>
+      <c r="D96" s="413"/>
+      <c r="E96" s="413"/>
+      <c r="F96" s="413"/>
+      <c r="G96" s="413"/>
+      <c r="H96" s="413"/>
+      <c r="I96" s="413"/>
+      <c r="J96" s="414"/>
       <c r="K96" s="324"/>
       <c r="L96" s="324"/>
     </row>
     <row r="97" spans="3:13" x14ac:dyDescent="0.25">
-      <c r="C97" s="407"/>
-      <c r="D97" s="408"/>
-      <c r="E97" s="408"/>
-      <c r="F97" s="408"/>
-      <c r="G97" s="408"/>
-      <c r="H97" s="408"/>
-      <c r="I97" s="408"/>
-      <c r="J97" s="409"/>
+      <c r="C97" s="415"/>
+      <c r="D97" s="416"/>
+      <c r="E97" s="416"/>
+      <c r="F97" s="416"/>
+      <c r="G97" s="416"/>
+      <c r="H97" s="416"/>
+      <c r="I97" s="416"/>
+      <c r="J97" s="417"/>
       <c r="K97" s="324"/>
       <c r="L97" s="324"/>
     </row>
     <row r="98" spans="3:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C98" s="410"/>
-      <c r="D98" s="411"/>
-      <c r="E98" s="411"/>
-      <c r="F98" s="411"/>
-      <c r="G98" s="411"/>
-      <c r="H98" s="411"/>
-      <c r="I98" s="411"/>
-      <c r="J98" s="412"/>
+      <c r="C98" s="418"/>
+      <c r="D98" s="419"/>
+      <c r="E98" s="419"/>
+      <c r="F98" s="419"/>
+      <c r="G98" s="419"/>
+      <c r="H98" s="419"/>
+      <c r="I98" s="419"/>
+      <c r="J98" s="420"/>
     </row>
     <row r="101" spans="3:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="102" spans="3:13" x14ac:dyDescent="0.25">
@@ -18713,11 +18691,11 @@
       <c r="G104" s="33" t="s">
         <v>164</v>
       </c>
-      <c r="H104" s="402" t="s">
-        <v>354</v>
-      </c>
-      <c r="I104" s="402"/>
-      <c r="J104" s="403"/>
+      <c r="H104" s="410" t="s">
+        <v>353</v>
+      </c>
+      <c r="I104" s="410"/>
+      <c r="J104" s="411"/>
       <c r="L104" s="324"/>
       <c r="M104" s="324"/>
     </row>
@@ -18736,40 +18714,40 @@
       <c r="M105" s="324"/>
     </row>
     <row r="106" spans="3:13" x14ac:dyDescent="0.25">
-      <c r="C106" s="404" t="s">
-        <v>355</v>
-      </c>
-      <c r="D106" s="405"/>
-      <c r="E106" s="405"/>
-      <c r="F106" s="405"/>
-      <c r="G106" s="405"/>
-      <c r="H106" s="405"/>
-      <c r="I106" s="405"/>
-      <c r="J106" s="406"/>
+      <c r="C106" s="412" t="s">
+        <v>354</v>
+      </c>
+      <c r="D106" s="413"/>
+      <c r="E106" s="413"/>
+      <c r="F106" s="413"/>
+      <c r="G106" s="413"/>
+      <c r="H106" s="413"/>
+      <c r="I106" s="413"/>
+      <c r="J106" s="414"/>
       <c r="L106" s="324"/>
       <c r="M106" s="324"/>
     </row>
     <row r="107" spans="3:13" x14ac:dyDescent="0.25">
-      <c r="C107" s="407"/>
-      <c r="D107" s="408"/>
-      <c r="E107" s="408"/>
-      <c r="F107" s="408"/>
-      <c r="G107" s="408"/>
-      <c r="H107" s="408"/>
-      <c r="I107" s="408"/>
-      <c r="J107" s="409"/>
+      <c r="C107" s="415"/>
+      <c r="D107" s="416"/>
+      <c r="E107" s="416"/>
+      <c r="F107" s="416"/>
+      <c r="G107" s="416"/>
+      <c r="H107" s="416"/>
+      <c r="I107" s="416"/>
+      <c r="J107" s="417"/>
       <c r="L107" s="324"/>
       <c r="M107" s="324"/>
     </row>
     <row r="108" spans="3:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C108" s="410"/>
-      <c r="D108" s="411"/>
-      <c r="E108" s="411"/>
-      <c r="F108" s="411"/>
-      <c r="G108" s="411"/>
-      <c r="H108" s="411"/>
-      <c r="I108" s="411"/>
-      <c r="J108" s="412"/>
+      <c r="C108" s="418"/>
+      <c r="D108" s="419"/>
+      <c r="E108" s="419"/>
+      <c r="F108" s="419"/>
+      <c r="G108" s="419"/>
+      <c r="H108" s="419"/>
+      <c r="I108" s="419"/>
+      <c r="J108" s="420"/>
       <c r="L108" s="324"/>
       <c r="M108" s="324"/>
     </row>
@@ -18823,11 +18801,11 @@
       <c r="G113" s="33" t="s">
         <v>164</v>
       </c>
-      <c r="H113" s="402">
+      <c r="H113" s="410">
         <v>36</v>
       </c>
-      <c r="I113" s="402"/>
-      <c r="J113" s="403"/>
+      <c r="I113" s="410"/>
+      <c r="J113" s="411"/>
       <c r="K113" s="324"/>
       <c r="L113" s="324"/>
       <c r="M113" s="324"/>
@@ -18848,42 +18826,42 @@
       <c r="M114" s="324"/>
     </row>
     <row r="115" spans="3:13" x14ac:dyDescent="0.25">
-      <c r="C115" s="404" t="s">
-        <v>356</v>
-      </c>
-      <c r="D115" s="405"/>
-      <c r="E115" s="405"/>
-      <c r="F115" s="405"/>
-      <c r="G115" s="405"/>
-      <c r="H115" s="405"/>
-      <c r="I115" s="405"/>
-      <c r="J115" s="406"/>
+      <c r="C115" s="412" t="s">
+        <v>355</v>
+      </c>
+      <c r="D115" s="413"/>
+      <c r="E115" s="413"/>
+      <c r="F115" s="413"/>
+      <c r="G115" s="413"/>
+      <c r="H115" s="413"/>
+      <c r="I115" s="413"/>
+      <c r="J115" s="414"/>
       <c r="K115" s="324"/>
       <c r="L115" s="324"/>
       <c r="M115" s="324"/>
     </row>
     <row r="116" spans="3:13" x14ac:dyDescent="0.25">
-      <c r="C116" s="407"/>
-      <c r="D116" s="408"/>
-      <c r="E116" s="408"/>
-      <c r="F116" s="408"/>
-      <c r="G116" s="408"/>
-      <c r="H116" s="408"/>
-      <c r="I116" s="408"/>
-      <c r="J116" s="409"/>
+      <c r="C116" s="415"/>
+      <c r="D116" s="416"/>
+      <c r="E116" s="416"/>
+      <c r="F116" s="416"/>
+      <c r="G116" s="416"/>
+      <c r="H116" s="416"/>
+      <c r="I116" s="416"/>
+      <c r="J116" s="417"/>
       <c r="K116" s="324"/>
       <c r="L116" s="324"/>
       <c r="M116" s="324"/>
     </row>
     <row r="117" spans="3:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C117" s="410"/>
-      <c r="D117" s="411"/>
-      <c r="E117" s="411"/>
-      <c r="F117" s="411"/>
-      <c r="G117" s="411"/>
-      <c r="H117" s="411"/>
-      <c r="I117" s="411"/>
-      <c r="J117" s="412"/>
+      <c r="C117" s="418"/>
+      <c r="D117" s="419"/>
+      <c r="E117" s="419"/>
+      <c r="F117" s="419"/>
+      <c r="G117" s="419"/>
+      <c r="H117" s="419"/>
+      <c r="I117" s="419"/>
+      <c r="J117" s="420"/>
       <c r="K117" s="324"/>
       <c r="L117" s="324"/>
       <c r="M117" s="324"/>
@@ -18941,11 +18919,11 @@
       <c r="G122" s="33" t="s">
         <v>164</v>
       </c>
-      <c r="H122" s="402">
+      <c r="H122" s="410">
         <v>73</v>
       </c>
-      <c r="I122" s="402"/>
-      <c r="J122" s="403"/>
+      <c r="I122" s="410"/>
+      <c r="J122" s="411"/>
       <c r="K122" s="324"/>
       <c r="L122" s="324"/>
     </row>
@@ -18964,40 +18942,40 @@
       <c r="L123" s="324"/>
     </row>
     <row r="124" spans="3:13" x14ac:dyDescent="0.25">
-      <c r="C124" s="404" t="s">
-        <v>357</v>
-      </c>
-      <c r="D124" s="405"/>
-      <c r="E124" s="405"/>
-      <c r="F124" s="405"/>
-      <c r="G124" s="405"/>
-      <c r="H124" s="405"/>
-      <c r="I124" s="405"/>
-      <c r="J124" s="406"/>
+      <c r="C124" s="412" t="s">
+        <v>356</v>
+      </c>
+      <c r="D124" s="413"/>
+      <c r="E124" s="413"/>
+      <c r="F124" s="413"/>
+      <c r="G124" s="413"/>
+      <c r="H124" s="413"/>
+      <c r="I124" s="413"/>
+      <c r="J124" s="414"/>
       <c r="K124" s="324"/>
       <c r="L124" s="324"/>
     </row>
     <row r="125" spans="3:13" x14ac:dyDescent="0.25">
-      <c r="C125" s="407"/>
-      <c r="D125" s="408"/>
-      <c r="E125" s="408"/>
-      <c r="F125" s="408"/>
-      <c r="G125" s="408"/>
-      <c r="H125" s="408"/>
-      <c r="I125" s="408"/>
-      <c r="J125" s="409"/>
+      <c r="C125" s="415"/>
+      <c r="D125" s="416"/>
+      <c r="E125" s="416"/>
+      <c r="F125" s="416"/>
+      <c r="G125" s="416"/>
+      <c r="H125" s="416"/>
+      <c r="I125" s="416"/>
+      <c r="J125" s="417"/>
       <c r="K125" s="324"/>
       <c r="L125" s="324"/>
     </row>
     <row r="126" spans="3:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C126" s="410"/>
-      <c r="D126" s="411"/>
-      <c r="E126" s="411"/>
-      <c r="F126" s="411"/>
-      <c r="G126" s="411"/>
-      <c r="H126" s="411"/>
-      <c r="I126" s="411"/>
-      <c r="J126" s="412"/>
+      <c r="C126" s="418"/>
+      <c r="D126" s="419"/>
+      <c r="E126" s="419"/>
+      <c r="F126" s="419"/>
+      <c r="G126" s="419"/>
+      <c r="H126" s="419"/>
+      <c r="I126" s="419"/>
+      <c r="J126" s="420"/>
     </row>
     <row r="128" spans="3:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="129" spans="3:12" x14ac:dyDescent="0.25">
@@ -19043,11 +19021,11 @@
       <c r="G131" s="33" t="s">
         <v>164</v>
       </c>
-      <c r="H131" s="402">
+      <c r="H131" s="410">
         <v>77</v>
       </c>
-      <c r="I131" s="402"/>
-      <c r="J131" s="403"/>
+      <c r="I131" s="410"/>
+      <c r="J131" s="411"/>
       <c r="K131" s="324"/>
       <c r="L131" s="324"/>
     </row>
@@ -19066,40 +19044,40 @@
       <c r="L132" s="324"/>
     </row>
     <row r="133" spans="3:12" x14ac:dyDescent="0.25">
-      <c r="C133" s="404" t="s">
-        <v>358</v>
-      </c>
-      <c r="D133" s="405"/>
-      <c r="E133" s="405"/>
-      <c r="F133" s="405"/>
-      <c r="G133" s="405"/>
-      <c r="H133" s="405"/>
-      <c r="I133" s="405"/>
-      <c r="J133" s="406"/>
+      <c r="C133" s="412" t="s">
+        <v>357</v>
+      </c>
+      <c r="D133" s="413"/>
+      <c r="E133" s="413"/>
+      <c r="F133" s="413"/>
+      <c r="G133" s="413"/>
+      <c r="H133" s="413"/>
+      <c r="I133" s="413"/>
+      <c r="J133" s="414"/>
       <c r="K133" s="324"/>
       <c r="L133" s="324"/>
     </row>
     <row r="134" spans="3:12" x14ac:dyDescent="0.25">
-      <c r="C134" s="407"/>
-      <c r="D134" s="408"/>
-      <c r="E134" s="408"/>
-      <c r="F134" s="408"/>
-      <c r="G134" s="408"/>
-      <c r="H134" s="408"/>
-      <c r="I134" s="408"/>
-      <c r="J134" s="409"/>
+      <c r="C134" s="415"/>
+      <c r="D134" s="416"/>
+      <c r="E134" s="416"/>
+      <c r="F134" s="416"/>
+      <c r="G134" s="416"/>
+      <c r="H134" s="416"/>
+      <c r="I134" s="416"/>
+      <c r="J134" s="417"/>
       <c r="K134" s="324"/>
       <c r="L134" s="324"/>
     </row>
     <row r="135" spans="3:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C135" s="410"/>
-      <c r="D135" s="411"/>
-      <c r="E135" s="411"/>
-      <c r="F135" s="411"/>
-      <c r="G135" s="411"/>
-      <c r="H135" s="411"/>
-      <c r="I135" s="411"/>
-      <c r="J135" s="412"/>
+      <c r="C135" s="418"/>
+      <c r="D135" s="419"/>
+      <c r="E135" s="419"/>
+      <c r="F135" s="419"/>
+      <c r="G135" s="419"/>
+      <c r="H135" s="419"/>
+      <c r="I135" s="419"/>
+      <c r="J135" s="420"/>
     </row>
     <row r="137" spans="3:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="138" spans="3:12" x14ac:dyDescent="0.25">
@@ -19147,11 +19125,11 @@
       <c r="G140" s="33" t="s">
         <v>164</v>
       </c>
-      <c r="H140" s="402">
+      <c r="H140" s="410">
         <v>61</v>
       </c>
-      <c r="I140" s="402"/>
-      <c r="J140" s="403"/>
+      <c r="I140" s="410"/>
+      <c r="J140" s="411"/>
       <c r="K140" s="324"/>
       <c r="L140" s="324"/>
     </row>
@@ -19170,40 +19148,40 @@
       <c r="L141" s="324"/>
     </row>
     <row r="142" spans="3:12" x14ac:dyDescent="0.25">
-      <c r="C142" s="404" t="s">
-        <v>359</v>
-      </c>
-      <c r="D142" s="405"/>
-      <c r="E142" s="405"/>
-      <c r="F142" s="405"/>
-      <c r="G142" s="405"/>
-      <c r="H142" s="405"/>
-      <c r="I142" s="405"/>
-      <c r="J142" s="406"/>
+      <c r="C142" s="412" t="s">
+        <v>358</v>
+      </c>
+      <c r="D142" s="413"/>
+      <c r="E142" s="413"/>
+      <c r="F142" s="413"/>
+      <c r="G142" s="413"/>
+      <c r="H142" s="413"/>
+      <c r="I142" s="413"/>
+      <c r="J142" s="414"/>
       <c r="K142" s="324"/>
       <c r="L142" s="324"/>
     </row>
     <row r="143" spans="3:12" x14ac:dyDescent="0.25">
-      <c r="C143" s="407"/>
-      <c r="D143" s="408"/>
-      <c r="E143" s="408"/>
-      <c r="F143" s="408"/>
-      <c r="G143" s="408"/>
-      <c r="H143" s="408"/>
-      <c r="I143" s="408"/>
-      <c r="J143" s="409"/>
+      <c r="C143" s="415"/>
+      <c r="D143" s="416"/>
+      <c r="E143" s="416"/>
+      <c r="F143" s="416"/>
+      <c r="G143" s="416"/>
+      <c r="H143" s="416"/>
+      <c r="I143" s="416"/>
+      <c r="J143" s="417"/>
       <c r="K143" s="324"/>
       <c r="L143" s="324"/>
     </row>
     <row r="144" spans="3:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C144" s="410"/>
-      <c r="D144" s="411"/>
-      <c r="E144" s="411"/>
-      <c r="F144" s="411"/>
-      <c r="G144" s="411"/>
-      <c r="H144" s="411"/>
-      <c r="I144" s="411"/>
-      <c r="J144" s="412"/>
+      <c r="C144" s="418"/>
+      <c r="D144" s="419"/>
+      <c r="E144" s="419"/>
+      <c r="F144" s="419"/>
+      <c r="G144" s="419"/>
+      <c r="H144" s="419"/>
+      <c r="I144" s="419"/>
+      <c r="J144" s="420"/>
     </row>
     <row r="146" spans="3:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="147" spans="3:12" x14ac:dyDescent="0.25">
@@ -19251,11 +19229,11 @@
       <c r="G149" s="33" t="s">
         <v>164</v>
       </c>
-      <c r="H149" s="402">
+      <c r="H149" s="410">
         <v>88</v>
       </c>
-      <c r="I149" s="402"/>
-      <c r="J149" s="403"/>
+      <c r="I149" s="410"/>
+      <c r="J149" s="411"/>
       <c r="K149" s="324"/>
       <c r="L149" s="324"/>
     </row>
@@ -19274,40 +19252,40 @@
       <c r="L150" s="324"/>
     </row>
     <row r="151" spans="3:12" x14ac:dyDescent="0.25">
-      <c r="C151" s="404" t="s">
-        <v>360</v>
-      </c>
-      <c r="D151" s="405"/>
-      <c r="E151" s="405"/>
-      <c r="F151" s="405"/>
-      <c r="G151" s="405"/>
-      <c r="H151" s="405"/>
-      <c r="I151" s="405"/>
-      <c r="J151" s="406"/>
+      <c r="C151" s="412" t="s">
+        <v>359</v>
+      </c>
+      <c r="D151" s="413"/>
+      <c r="E151" s="413"/>
+      <c r="F151" s="413"/>
+      <c r="G151" s="413"/>
+      <c r="H151" s="413"/>
+      <c r="I151" s="413"/>
+      <c r="J151" s="414"/>
       <c r="K151" s="324"/>
       <c r="L151" s="324"/>
     </row>
     <row r="152" spans="3:12" x14ac:dyDescent="0.25">
-      <c r="C152" s="407"/>
-      <c r="D152" s="408"/>
-      <c r="E152" s="408"/>
-      <c r="F152" s="408"/>
-      <c r="G152" s="408"/>
-      <c r="H152" s="408"/>
-      <c r="I152" s="408"/>
-      <c r="J152" s="409"/>
+      <c r="C152" s="415"/>
+      <c r="D152" s="416"/>
+      <c r="E152" s="416"/>
+      <c r="F152" s="416"/>
+      <c r="G152" s="416"/>
+      <c r="H152" s="416"/>
+      <c r="I152" s="416"/>
+      <c r="J152" s="417"/>
       <c r="K152" s="324"/>
       <c r="L152" s="324"/>
     </row>
     <row r="153" spans="3:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C153" s="410"/>
-      <c r="D153" s="411"/>
-      <c r="E153" s="411"/>
-      <c r="F153" s="411"/>
-      <c r="G153" s="411"/>
-      <c r="H153" s="411"/>
-      <c r="I153" s="411"/>
-      <c r="J153" s="412"/>
+      <c r="C153" s="418"/>
+      <c r="D153" s="419"/>
+      <c r="E153" s="419"/>
+      <c r="F153" s="419"/>
+      <c r="G153" s="419"/>
+      <c r="H153" s="419"/>
+      <c r="I153" s="419"/>
+      <c r="J153" s="420"/>
       <c r="K153" s="324"/>
       <c r="L153" s="324"/>
     </row>
@@ -19357,11 +19335,11 @@
       <c r="G158" s="33" t="s">
         <v>164</v>
       </c>
-      <c r="H158" s="402">
+      <c r="H158" s="410">
         <v>86</v>
       </c>
-      <c r="I158" s="402"/>
-      <c r="J158" s="403"/>
+      <c r="I158" s="410"/>
+      <c r="J158" s="411"/>
       <c r="K158" s="324"/>
       <c r="L158" s="324"/>
     </row>
@@ -19380,40 +19358,40 @@
       <c r="L159" s="324"/>
     </row>
     <row r="160" spans="3:12" x14ac:dyDescent="0.25">
-      <c r="C160" s="404" t="s">
-        <v>361</v>
-      </c>
-      <c r="D160" s="405"/>
-      <c r="E160" s="405"/>
-      <c r="F160" s="405"/>
-      <c r="G160" s="405"/>
-      <c r="H160" s="405"/>
-      <c r="I160" s="405"/>
-      <c r="J160" s="406"/>
+      <c r="C160" s="412" t="s">
+        <v>360</v>
+      </c>
+      <c r="D160" s="413"/>
+      <c r="E160" s="413"/>
+      <c r="F160" s="413"/>
+      <c r="G160" s="413"/>
+      <c r="H160" s="413"/>
+      <c r="I160" s="413"/>
+      <c r="J160" s="414"/>
       <c r="K160" s="324"/>
       <c r="L160" s="324"/>
     </row>
     <row r="161" spans="3:13" x14ac:dyDescent="0.25">
-      <c r="C161" s="407"/>
-      <c r="D161" s="408"/>
-      <c r="E161" s="408"/>
-      <c r="F161" s="408"/>
-      <c r="G161" s="408"/>
-      <c r="H161" s="408"/>
-      <c r="I161" s="408"/>
-      <c r="J161" s="409"/>
+      <c r="C161" s="415"/>
+      <c r="D161" s="416"/>
+      <c r="E161" s="416"/>
+      <c r="F161" s="416"/>
+      <c r="G161" s="416"/>
+      <c r="H161" s="416"/>
+      <c r="I161" s="416"/>
+      <c r="J161" s="417"/>
       <c r="K161" s="324"/>
       <c r="L161" s="324"/>
     </row>
     <row r="162" spans="3:13" ht="56.45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C162" s="410"/>
-      <c r="D162" s="411"/>
-      <c r="E162" s="411"/>
-      <c r="F162" s="411"/>
-      <c r="G162" s="411"/>
-      <c r="H162" s="411"/>
-      <c r="I162" s="411"/>
-      <c r="J162" s="412"/>
+      <c r="C162" s="418"/>
+      <c r="D162" s="419"/>
+      <c r="E162" s="419"/>
+      <c r="F162" s="419"/>
+      <c r="G162" s="419"/>
+      <c r="H162" s="419"/>
+      <c r="I162" s="419"/>
+      <c r="J162" s="420"/>
       <c r="K162" s="324"/>
       <c r="L162" s="324"/>
     </row>
@@ -19464,11 +19442,11 @@
       <c r="G167" s="33" t="s">
         <v>164</v>
       </c>
-      <c r="H167" s="402" t="s">
-        <v>362</v>
-      </c>
-      <c r="I167" s="402"/>
-      <c r="J167" s="403"/>
+      <c r="H167" s="410" t="s">
+        <v>361</v>
+      </c>
+      <c r="I167" s="410"/>
+      <c r="J167" s="411"/>
       <c r="K167" s="324"/>
       <c r="L167" s="324"/>
       <c r="M167" s="324"/>
@@ -19489,42 +19467,42 @@
       <c r="M168" s="324"/>
     </row>
     <row r="169" spans="3:13" x14ac:dyDescent="0.25">
-      <c r="C169" s="404" t="s">
-        <v>363</v>
-      </c>
-      <c r="D169" s="405"/>
-      <c r="E169" s="405"/>
-      <c r="F169" s="405"/>
-      <c r="G169" s="405"/>
-      <c r="H169" s="405"/>
-      <c r="I169" s="405"/>
-      <c r="J169" s="406"/>
+      <c r="C169" s="412" t="s">
+        <v>362</v>
+      </c>
+      <c r="D169" s="413"/>
+      <c r="E169" s="413"/>
+      <c r="F169" s="413"/>
+      <c r="G169" s="413"/>
+      <c r="H169" s="413"/>
+      <c r="I169" s="413"/>
+      <c r="J169" s="414"/>
       <c r="K169" s="324"/>
       <c r="L169" s="324"/>
       <c r="M169" s="324"/>
     </row>
     <row r="170" spans="3:13" x14ac:dyDescent="0.25">
-      <c r="C170" s="407"/>
-      <c r="D170" s="408"/>
-      <c r="E170" s="408"/>
-      <c r="F170" s="408"/>
-      <c r="G170" s="408"/>
-      <c r="H170" s="408"/>
-      <c r="I170" s="408"/>
-      <c r="J170" s="409"/>
+      <c r="C170" s="415"/>
+      <c r="D170" s="416"/>
+      <c r="E170" s="416"/>
+      <c r="F170" s="416"/>
+      <c r="G170" s="416"/>
+      <c r="H170" s="416"/>
+      <c r="I170" s="416"/>
+      <c r="J170" s="417"/>
       <c r="K170" s="324"/>
       <c r="L170" s="324"/>
       <c r="M170" s="324"/>
     </row>
     <row r="171" spans="3:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C171" s="410"/>
-      <c r="D171" s="411"/>
-      <c r="E171" s="411"/>
-      <c r="F171" s="411"/>
-      <c r="G171" s="411"/>
-      <c r="H171" s="411"/>
-      <c r="I171" s="411"/>
-      <c r="J171" s="412"/>
+      <c r="C171" s="418"/>
+      <c r="D171" s="419"/>
+      <c r="E171" s="419"/>
+      <c r="F171" s="419"/>
+      <c r="G171" s="419"/>
+      <c r="H171" s="419"/>
+      <c r="I171" s="419"/>
+      <c r="J171" s="420"/>
       <c r="K171" s="324"/>
       <c r="L171" s="324"/>
       <c r="M171" s="324"/>
@@ -19575,11 +19553,11 @@
       <c r="G176" s="33" t="s">
         <v>164</v>
       </c>
-      <c r="H176" s="402">
+      <c r="H176" s="410">
         <v>102</v>
       </c>
-      <c r="I176" s="402"/>
-      <c r="J176" s="403"/>
+      <c r="I176" s="410"/>
+      <c r="J176" s="411"/>
       <c r="K176" s="324"/>
       <c r="L176" s="324"/>
     </row>
@@ -19598,40 +19576,40 @@
       <c r="L177" s="324"/>
     </row>
     <row r="178" spans="3:13" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C178" s="404" t="s">
-        <v>364</v>
-      </c>
-      <c r="D178" s="405"/>
-      <c r="E178" s="405"/>
-      <c r="F178" s="405"/>
-      <c r="G178" s="405"/>
-      <c r="H178" s="405"/>
-      <c r="I178" s="405"/>
-      <c r="J178" s="406"/>
+      <c r="C178" s="412" t="s">
+        <v>363</v>
+      </c>
+      <c r="D178" s="413"/>
+      <c r="E178" s="413"/>
+      <c r="F178" s="413"/>
+      <c r="G178" s="413"/>
+      <c r="H178" s="413"/>
+      <c r="I178" s="413"/>
+      <c r="J178" s="414"/>
       <c r="K178" s="324"/>
       <c r="L178" s="324"/>
     </row>
     <row r="179" spans="3:13" x14ac:dyDescent="0.25">
-      <c r="C179" s="407"/>
-      <c r="D179" s="408"/>
-      <c r="E179" s="408"/>
-      <c r="F179" s="408"/>
-      <c r="G179" s="408"/>
-      <c r="H179" s="408"/>
-      <c r="I179" s="408"/>
-      <c r="J179" s="409"/>
+      <c r="C179" s="415"/>
+      <c r="D179" s="416"/>
+      <c r="E179" s="416"/>
+      <c r="F179" s="416"/>
+      <c r="G179" s="416"/>
+      <c r="H179" s="416"/>
+      <c r="I179" s="416"/>
+      <c r="J179" s="417"/>
       <c r="K179" s="324"/>
       <c r="L179" s="324"/>
     </row>
     <row r="180" spans="3:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C180" s="410"/>
-      <c r="D180" s="411"/>
-      <c r="E180" s="411"/>
-      <c r="F180" s="411"/>
-      <c r="G180" s="411"/>
-      <c r="H180" s="411"/>
-      <c r="I180" s="411"/>
-      <c r="J180" s="412"/>
+      <c r="C180" s="418"/>
+      <c r="D180" s="419"/>
+      <c r="E180" s="419"/>
+      <c r="F180" s="419"/>
+      <c r="G180" s="419"/>
+      <c r="H180" s="419"/>
+      <c r="I180" s="419"/>
+      <c r="J180" s="420"/>
     </row>
     <row r="182" spans="3:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="183" spans="3:13" x14ac:dyDescent="0.25">
@@ -19680,11 +19658,11 @@
       <c r="G185" s="33" t="s">
         <v>164</v>
       </c>
-      <c r="H185" s="402">
+      <c r="H185" s="410">
         <v>130</v>
       </c>
-      <c r="I185" s="402"/>
-      <c r="J185" s="403"/>
+      <c r="I185" s="410"/>
+      <c r="J185" s="411"/>
       <c r="K185" s="324"/>
       <c r="L185" s="324"/>
       <c r="M185" s="324"/>
@@ -19705,39 +19683,39 @@
       <c r="M186" s="324"/>
     </row>
     <row r="187" spans="3:13" x14ac:dyDescent="0.25">
-      <c r="C187" s="404" t="s">
-        <v>365</v>
-      </c>
-      <c r="D187" s="405"/>
-      <c r="E187" s="405"/>
-      <c r="F187" s="405"/>
-      <c r="G187" s="405"/>
-      <c r="H187" s="405"/>
-      <c r="I187" s="405"/>
-      <c r="J187" s="406"/>
+      <c r="C187" s="412" t="s">
+        <v>364</v>
+      </c>
+      <c r="D187" s="413"/>
+      <c r="E187" s="413"/>
+      <c r="F187" s="413"/>
+      <c r="G187" s="413"/>
+      <c r="H187" s="413"/>
+      <c r="I187" s="413"/>
+      <c r="J187" s="414"/>
       <c r="K187" s="324"/>
       <c r="L187" s="324"/>
       <c r="M187" s="324"/>
     </row>
     <row r="188" spans="3:13" x14ac:dyDescent="0.25">
-      <c r="C188" s="407"/>
-      <c r="D188" s="408"/>
-      <c r="E188" s="408"/>
-      <c r="F188" s="408"/>
-      <c r="G188" s="408"/>
-      <c r="H188" s="408"/>
-      <c r="I188" s="408"/>
-      <c r="J188" s="409"/>
+      <c r="C188" s="415"/>
+      <c r="D188" s="416"/>
+      <c r="E188" s="416"/>
+      <c r="F188" s="416"/>
+      <c r="G188" s="416"/>
+      <c r="H188" s="416"/>
+      <c r="I188" s="416"/>
+      <c r="J188" s="417"/>
     </row>
     <row r="189" spans="3:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C189" s="410"/>
-      <c r="D189" s="411"/>
-      <c r="E189" s="411"/>
-      <c r="F189" s="411"/>
-      <c r="G189" s="411"/>
-      <c r="H189" s="411"/>
-      <c r="I189" s="411"/>
-      <c r="J189" s="412"/>
+      <c r="C189" s="418"/>
+      <c r="D189" s="419"/>
+      <c r="E189" s="419"/>
+      <c r="F189" s="419"/>
+      <c r="G189" s="419"/>
+      <c r="H189" s="419"/>
+      <c r="I189" s="419"/>
+      <c r="J189" s="420"/>
     </row>
     <row r="191" spans="3:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="192" spans="3:13" x14ac:dyDescent="0.25">
@@ -19785,11 +19763,11 @@
       <c r="G194" s="33" t="s">
         <v>164</v>
       </c>
-      <c r="H194" s="402">
+      <c r="H194" s="410">
         <v>8</v>
       </c>
-      <c r="I194" s="402"/>
-      <c r="J194" s="403"/>
+      <c r="I194" s="410"/>
+      <c r="J194" s="411"/>
       <c r="K194" s="324"/>
       <c r="L194" s="324"/>
     </row>
@@ -19808,40 +19786,40 @@
       <c r="L195" s="324"/>
     </row>
     <row r="196" spans="3:12" x14ac:dyDescent="0.25">
-      <c r="C196" s="404" t="s">
-        <v>367</v>
-      </c>
-      <c r="D196" s="405"/>
-      <c r="E196" s="405"/>
-      <c r="F196" s="405"/>
-      <c r="G196" s="405"/>
-      <c r="H196" s="405"/>
-      <c r="I196" s="405"/>
-      <c r="J196" s="406"/>
+      <c r="C196" s="412" t="s">
+        <v>366</v>
+      </c>
+      <c r="D196" s="413"/>
+      <c r="E196" s="413"/>
+      <c r="F196" s="413"/>
+      <c r="G196" s="413"/>
+      <c r="H196" s="413"/>
+      <c r="I196" s="413"/>
+      <c r="J196" s="414"/>
       <c r="K196" s="324"/>
       <c r="L196" s="324"/>
     </row>
     <row r="197" spans="3:12" x14ac:dyDescent="0.25">
-      <c r="C197" s="407"/>
-      <c r="D197" s="408"/>
-      <c r="E197" s="408"/>
-      <c r="F197" s="408"/>
-      <c r="G197" s="408"/>
-      <c r="H197" s="408"/>
-      <c r="I197" s="408"/>
-      <c r="J197" s="409"/>
+      <c r="C197" s="415"/>
+      <c r="D197" s="416"/>
+      <c r="E197" s="416"/>
+      <c r="F197" s="416"/>
+      <c r="G197" s="416"/>
+      <c r="H197" s="416"/>
+      <c r="I197" s="416"/>
+      <c r="J197" s="417"/>
       <c r="K197" s="324"/>
       <c r="L197" s="324"/>
     </row>
     <row r="198" spans="3:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C198" s="410"/>
-      <c r="D198" s="411"/>
-      <c r="E198" s="411"/>
-      <c r="F198" s="411"/>
-      <c r="G198" s="411"/>
-      <c r="H198" s="411"/>
-      <c r="I198" s="411"/>
-      <c r="J198" s="412"/>
+      <c r="C198" s="418"/>
+      <c r="D198" s="419"/>
+      <c r="E198" s="419"/>
+      <c r="F198" s="419"/>
+      <c r="G198" s="419"/>
+      <c r="H198" s="419"/>
+      <c r="I198" s="419"/>
+      <c r="J198" s="420"/>
     </row>
     <row r="200" spans="3:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="201" spans="3:12" x14ac:dyDescent="0.25">
@@ -19887,11 +19865,11 @@
       <c r="G203" s="33" t="s">
         <v>164</v>
       </c>
-      <c r="H203" s="402">
+      <c r="H203" s="410">
         <v>96</v>
       </c>
-      <c r="I203" s="402"/>
-      <c r="J203" s="403"/>
+      <c r="I203" s="410"/>
+      <c r="J203" s="411"/>
       <c r="K203" s="324"/>
       <c r="L203" s="324"/>
     </row>
@@ -19910,38 +19888,38 @@
       <c r="L204" s="324"/>
     </row>
     <row r="205" spans="3:12" x14ac:dyDescent="0.25">
-      <c r="C205" s="404" t="s">
-        <v>366</v>
-      </c>
-      <c r="D205" s="405"/>
-      <c r="E205" s="405"/>
-      <c r="F205" s="405"/>
-      <c r="G205" s="405"/>
-      <c r="H205" s="405"/>
-      <c r="I205" s="405"/>
-      <c r="J205" s="406"/>
+      <c r="C205" s="412" t="s">
+        <v>365</v>
+      </c>
+      <c r="D205" s="413"/>
+      <c r="E205" s="413"/>
+      <c r="F205" s="413"/>
+      <c r="G205" s="413"/>
+      <c r="H205" s="413"/>
+      <c r="I205" s="413"/>
+      <c r="J205" s="414"/>
       <c r="K205" s="324"/>
       <c r="L205" s="324"/>
     </row>
     <row r="206" spans="3:12" x14ac:dyDescent="0.25">
-      <c r="C206" s="407"/>
-      <c r="D206" s="408"/>
-      <c r="E206" s="408"/>
-      <c r="F206" s="408"/>
-      <c r="G206" s="408"/>
-      <c r="H206" s="408"/>
-      <c r="I206" s="408"/>
-      <c r="J206" s="409"/>
+      <c r="C206" s="415"/>
+      <c r="D206" s="416"/>
+      <c r="E206" s="416"/>
+      <c r="F206" s="416"/>
+      <c r="G206" s="416"/>
+      <c r="H206" s="416"/>
+      <c r="I206" s="416"/>
+      <c r="J206" s="417"/>
     </row>
     <row r="207" spans="3:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C207" s="410"/>
-      <c r="D207" s="411"/>
-      <c r="E207" s="411"/>
-      <c r="F207" s="411"/>
-      <c r="G207" s="411"/>
-      <c r="H207" s="411"/>
-      <c r="I207" s="411"/>
-      <c r="J207" s="412"/>
+      <c r="C207" s="418"/>
+      <c r="D207" s="419"/>
+      <c r="E207" s="419"/>
+      <c r="F207" s="419"/>
+      <c r="G207" s="419"/>
+      <c r="H207" s="419"/>
+      <c r="I207" s="419"/>
+      <c r="J207" s="420"/>
     </row>
     <row r="209" spans="3:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="210" spans="3:12" x14ac:dyDescent="0.25">
@@ -19989,11 +19967,11 @@
       <c r="G212" s="33" t="s">
         <v>164</v>
       </c>
-      <c r="H212" s="402">
+      <c r="H212" s="410">
         <v>138</v>
       </c>
-      <c r="I212" s="402"/>
-      <c r="J212" s="403"/>
+      <c r="I212" s="410"/>
+      <c r="J212" s="411"/>
       <c r="K212" s="324"/>
       <c r="L212" s="324"/>
     </row>
@@ -20012,38 +19990,38 @@
       <c r="L213" s="324"/>
     </row>
     <row r="214" spans="3:12" x14ac:dyDescent="0.25">
-      <c r="C214" s="404" t="s">
-        <v>440</v>
-      </c>
-      <c r="D214" s="405"/>
-      <c r="E214" s="405"/>
-      <c r="F214" s="405"/>
-      <c r="G214" s="405"/>
-      <c r="H214" s="405"/>
-      <c r="I214" s="405"/>
-      <c r="J214" s="406"/>
+      <c r="C214" s="412" t="s">
+        <v>439</v>
+      </c>
+      <c r="D214" s="413"/>
+      <c r="E214" s="413"/>
+      <c r="F214" s="413"/>
+      <c r="G214" s="413"/>
+      <c r="H214" s="413"/>
+      <c r="I214" s="413"/>
+      <c r="J214" s="414"/>
       <c r="K214" s="324"/>
       <c r="L214" s="324"/>
     </row>
     <row r="215" spans="3:12" x14ac:dyDescent="0.25">
-      <c r="C215" s="407"/>
-      <c r="D215" s="408"/>
-      <c r="E215" s="408"/>
-      <c r="F215" s="408"/>
-      <c r="G215" s="408"/>
-      <c r="H215" s="408"/>
-      <c r="I215" s="408"/>
-      <c r="J215" s="409"/>
+      <c r="C215" s="415"/>
+      <c r="D215" s="416"/>
+      <c r="E215" s="416"/>
+      <c r="F215" s="416"/>
+      <c r="G215" s="416"/>
+      <c r="H215" s="416"/>
+      <c r="I215" s="416"/>
+      <c r="J215" s="417"/>
     </row>
     <row r="216" spans="3:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C216" s="410"/>
-      <c r="D216" s="411"/>
-      <c r="E216" s="411"/>
-      <c r="F216" s="411"/>
-      <c r="G216" s="411"/>
-      <c r="H216" s="411"/>
-      <c r="I216" s="411"/>
-      <c r="J216" s="412"/>
+      <c r="C216" s="418"/>
+      <c r="D216" s="419"/>
+      <c r="E216" s="419"/>
+      <c r="F216" s="419"/>
+      <c r="G216" s="419"/>
+      <c r="H216" s="419"/>
+      <c r="I216" s="419"/>
+      <c r="J216" s="420"/>
     </row>
     <row r="218" spans="3:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="219" spans="3:12" x14ac:dyDescent="0.25">
@@ -20091,11 +20069,11 @@
       <c r="G221" s="33" t="s">
         <v>164</v>
       </c>
-      <c r="H221" s="402">
+      <c r="H221" s="410">
         <v>7</v>
       </c>
-      <c r="I221" s="402"/>
-      <c r="J221" s="403"/>
+      <c r="I221" s="410"/>
+      <c r="J221" s="411"/>
       <c r="K221" s="324"/>
       <c r="L221" s="324"/>
     </row>
@@ -20114,40 +20092,40 @@
       <c r="L222" s="324"/>
     </row>
     <row r="223" spans="3:12" x14ac:dyDescent="0.25">
-      <c r="C223" s="404" t="s">
-        <v>368</v>
-      </c>
-      <c r="D223" s="405"/>
-      <c r="E223" s="405"/>
-      <c r="F223" s="405"/>
-      <c r="G223" s="405"/>
-      <c r="H223" s="405"/>
-      <c r="I223" s="405"/>
-      <c r="J223" s="406"/>
+      <c r="C223" s="412" t="s">
+        <v>367</v>
+      </c>
+      <c r="D223" s="413"/>
+      <c r="E223" s="413"/>
+      <c r="F223" s="413"/>
+      <c r="G223" s="413"/>
+      <c r="H223" s="413"/>
+      <c r="I223" s="413"/>
+      <c r="J223" s="414"/>
       <c r="K223" s="324"/>
       <c r="L223" s="324"/>
     </row>
     <row r="224" spans="3:12" x14ac:dyDescent="0.25">
-      <c r="C224" s="407"/>
-      <c r="D224" s="408"/>
-      <c r="E224" s="408"/>
-      <c r="F224" s="408"/>
-      <c r="G224" s="408"/>
-      <c r="H224" s="408"/>
-      <c r="I224" s="408"/>
-      <c r="J224" s="409"/>
+      <c r="C224" s="415"/>
+      <c r="D224" s="416"/>
+      <c r="E224" s="416"/>
+      <c r="F224" s="416"/>
+      <c r="G224" s="416"/>
+      <c r="H224" s="416"/>
+      <c r="I224" s="416"/>
+      <c r="J224" s="417"/>
       <c r="K224" s="324"/>
       <c r="L224" s="324"/>
     </row>
     <row r="225" spans="3:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C225" s="410"/>
-      <c r="D225" s="411"/>
-      <c r="E225" s="411"/>
-      <c r="F225" s="411"/>
-      <c r="G225" s="411"/>
-      <c r="H225" s="411"/>
-      <c r="I225" s="411"/>
-      <c r="J225" s="412"/>
+      <c r="C225" s="418"/>
+      <c r="D225" s="419"/>
+      <c r="E225" s="419"/>
+      <c r="F225" s="419"/>
+      <c r="G225" s="419"/>
+      <c r="H225" s="419"/>
+      <c r="I225" s="419"/>
+      <c r="J225" s="420"/>
       <c r="K225" s="324"/>
       <c r="L225" s="324"/>
     </row>
@@ -20197,11 +20175,11 @@
       <c r="G230" s="33" t="s">
         <v>164</v>
       </c>
-      <c r="H230" s="402">
+      <c r="H230" s="410">
         <v>70</v>
       </c>
-      <c r="I230" s="402"/>
-      <c r="J230" s="403"/>
+      <c r="I230" s="410"/>
+      <c r="J230" s="411"/>
       <c r="K230" s="324"/>
       <c r="L230" s="324"/>
     </row>
@@ -20220,40 +20198,40 @@
       <c r="L231" s="324"/>
     </row>
     <row r="232" spans="3:13" x14ac:dyDescent="0.25">
-      <c r="C232" s="404" t="s">
-        <v>370</v>
-      </c>
-      <c r="D232" s="405"/>
-      <c r="E232" s="405"/>
-      <c r="F232" s="405"/>
-      <c r="G232" s="405"/>
-      <c r="H232" s="405"/>
-      <c r="I232" s="405"/>
-      <c r="J232" s="406"/>
+      <c r="C232" s="412" t="s">
+        <v>369</v>
+      </c>
+      <c r="D232" s="413"/>
+      <c r="E232" s="413"/>
+      <c r="F232" s="413"/>
+      <c r="G232" s="413"/>
+      <c r="H232" s="413"/>
+      <c r="I232" s="413"/>
+      <c r="J232" s="414"/>
       <c r="K232" s="324"/>
       <c r="L232" s="324"/>
     </row>
     <row r="233" spans="3:13" x14ac:dyDescent="0.25">
-      <c r="C233" s="407"/>
-      <c r="D233" s="408"/>
-      <c r="E233" s="408"/>
-      <c r="F233" s="408"/>
-      <c r="G233" s="408"/>
-      <c r="H233" s="408"/>
-      <c r="I233" s="408"/>
-      <c r="J233" s="409"/>
+      <c r="C233" s="415"/>
+      <c r="D233" s="416"/>
+      <c r="E233" s="416"/>
+      <c r="F233" s="416"/>
+      <c r="G233" s="416"/>
+      <c r="H233" s="416"/>
+      <c r="I233" s="416"/>
+      <c r="J233" s="417"/>
       <c r="K233" s="324"/>
       <c r="L233" s="324"/>
     </row>
     <row r="234" spans="3:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C234" s="410"/>
-      <c r="D234" s="411"/>
-      <c r="E234" s="411"/>
-      <c r="F234" s="411"/>
-      <c r="G234" s="411"/>
-      <c r="H234" s="411"/>
-      <c r="I234" s="411"/>
-      <c r="J234" s="412"/>
+      <c r="C234" s="418"/>
+      <c r="D234" s="419"/>
+      <c r="E234" s="419"/>
+      <c r="F234" s="419"/>
+      <c r="G234" s="419"/>
+      <c r="H234" s="419"/>
+      <c r="I234" s="419"/>
+      <c r="J234" s="420"/>
       <c r="K234" s="324"/>
       <c r="L234" s="324"/>
     </row>
@@ -20306,11 +20284,11 @@
       <c r="G239" s="33" t="s">
         <v>164</v>
       </c>
-      <c r="H239" s="402">
+      <c r="H239" s="410">
         <v>109</v>
       </c>
-      <c r="I239" s="402"/>
-      <c r="J239" s="403"/>
+      <c r="I239" s="410"/>
+      <c r="J239" s="411"/>
       <c r="K239" s="327"/>
       <c r="L239" s="327"/>
       <c r="M239" s="57"/>
@@ -20331,44 +20309,83 @@
       <c r="M240" s="57"/>
     </row>
     <row r="241" spans="3:13" x14ac:dyDescent="0.25">
-      <c r="C241" s="404" t="s">
-        <v>371</v>
-      </c>
-      <c r="D241" s="405"/>
-      <c r="E241" s="405"/>
-      <c r="F241" s="405"/>
-      <c r="G241" s="405"/>
-      <c r="H241" s="405"/>
-      <c r="I241" s="405"/>
-      <c r="J241" s="406"/>
+      <c r="C241" s="412" t="s">
+        <v>370</v>
+      </c>
+      <c r="D241" s="413"/>
+      <c r="E241" s="413"/>
+      <c r="F241" s="413"/>
+      <c r="G241" s="413"/>
+      <c r="H241" s="413"/>
+      <c r="I241" s="413"/>
+      <c r="J241" s="414"/>
       <c r="K241" s="327"/>
       <c r="L241" s="327"/>
       <c r="M241" s="57"/>
     </row>
     <row r="242" spans="3:13" x14ac:dyDescent="0.25">
-      <c r="C242" s="407"/>
-      <c r="D242" s="408"/>
-      <c r="E242" s="408"/>
-      <c r="F242" s="408"/>
-      <c r="G242" s="408"/>
-      <c r="H242" s="408"/>
-      <c r="I242" s="408"/>
-      <c r="J242" s="409"/>
+      <c r="C242" s="415"/>
+      <c r="D242" s="416"/>
+      <c r="E242" s="416"/>
+      <c r="F242" s="416"/>
+      <c r="G242" s="416"/>
+      <c r="H242" s="416"/>
+      <c r="I242" s="416"/>
+      <c r="J242" s="417"/>
       <c r="K242" s="324"/>
       <c r="L242" s="324"/>
     </row>
     <row r="243" spans="3:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C243" s="410"/>
-      <c r="D243" s="411"/>
-      <c r="E243" s="411"/>
-      <c r="F243" s="411"/>
-      <c r="G243" s="411"/>
-      <c r="H243" s="411"/>
-      <c r="I243" s="411"/>
-      <c r="J243" s="412"/>
+      <c r="C243" s="418"/>
+      <c r="D243" s="419"/>
+      <c r="E243" s="419"/>
+      <c r="F243" s="419"/>
+      <c r="G243" s="419"/>
+      <c r="H243" s="419"/>
+      <c r="I243" s="419"/>
+      <c r="J243" s="420"/>
     </row>
   </sheetData>
   <mergeCells count="55">
+    <mergeCell ref="H203:J203"/>
+    <mergeCell ref="C205:J207"/>
+    <mergeCell ref="H230:J230"/>
+    <mergeCell ref="C232:J234"/>
+    <mergeCell ref="H221:J221"/>
+    <mergeCell ref="C223:J225"/>
+    <mergeCell ref="H212:J212"/>
+    <mergeCell ref="C214:J216"/>
+    <mergeCell ref="C178:J180"/>
+    <mergeCell ref="H185:J185"/>
+    <mergeCell ref="C187:J189"/>
+    <mergeCell ref="H194:J194"/>
+    <mergeCell ref="C196:J198"/>
+    <mergeCell ref="K65:M71"/>
+    <mergeCell ref="H49:J49"/>
+    <mergeCell ref="C51:J53"/>
+    <mergeCell ref="H58:J58"/>
+    <mergeCell ref="C60:J62"/>
+    <mergeCell ref="H67:J67"/>
+    <mergeCell ref="C69:J71"/>
+    <mergeCell ref="C24:J26"/>
+    <mergeCell ref="H31:J31"/>
+    <mergeCell ref="C33:J35"/>
+    <mergeCell ref="H4:J4"/>
+    <mergeCell ref="C6:J8"/>
+    <mergeCell ref="H13:J13"/>
+    <mergeCell ref="C15:J17"/>
+    <mergeCell ref="H22:J22"/>
+    <mergeCell ref="H40:J40"/>
+    <mergeCell ref="C42:J44"/>
+    <mergeCell ref="H131:J131"/>
+    <mergeCell ref="C133:J135"/>
+    <mergeCell ref="H122:J122"/>
+    <mergeCell ref="C124:J126"/>
+    <mergeCell ref="H113:J113"/>
+    <mergeCell ref="C115:J117"/>
+    <mergeCell ref="H104:J104"/>
+    <mergeCell ref="C106:J108"/>
+    <mergeCell ref="H85:J85"/>
     <mergeCell ref="H239:J239"/>
     <mergeCell ref="C241:J243"/>
     <mergeCell ref="C160:J162"/>
@@ -20385,45 +20402,6 @@
     <mergeCell ref="H167:J167"/>
     <mergeCell ref="C169:J171"/>
     <mergeCell ref="H176:J176"/>
-    <mergeCell ref="H40:J40"/>
-    <mergeCell ref="C42:J44"/>
-    <mergeCell ref="H131:J131"/>
-    <mergeCell ref="C133:J135"/>
-    <mergeCell ref="H122:J122"/>
-    <mergeCell ref="C124:J126"/>
-    <mergeCell ref="H113:J113"/>
-    <mergeCell ref="C115:J117"/>
-    <mergeCell ref="H104:J104"/>
-    <mergeCell ref="C106:J108"/>
-    <mergeCell ref="H85:J85"/>
-    <mergeCell ref="C24:J26"/>
-    <mergeCell ref="H31:J31"/>
-    <mergeCell ref="C33:J35"/>
-    <mergeCell ref="H4:J4"/>
-    <mergeCell ref="C6:J8"/>
-    <mergeCell ref="H13:J13"/>
-    <mergeCell ref="C15:J17"/>
-    <mergeCell ref="H22:J22"/>
-    <mergeCell ref="K65:M71"/>
-    <mergeCell ref="H49:J49"/>
-    <mergeCell ref="C51:J53"/>
-    <mergeCell ref="H58:J58"/>
-    <mergeCell ref="C60:J62"/>
-    <mergeCell ref="H67:J67"/>
-    <mergeCell ref="C69:J71"/>
-    <mergeCell ref="C178:J180"/>
-    <mergeCell ref="H185:J185"/>
-    <mergeCell ref="C187:J189"/>
-    <mergeCell ref="H194:J194"/>
-    <mergeCell ref="C196:J198"/>
-    <mergeCell ref="H203:J203"/>
-    <mergeCell ref="C205:J207"/>
-    <mergeCell ref="H230:J230"/>
-    <mergeCell ref="C232:J234"/>
-    <mergeCell ref="H221:J221"/>
-    <mergeCell ref="C223:J225"/>
-    <mergeCell ref="H212:J212"/>
-    <mergeCell ref="C214:J216"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/BRISAS/EXPENSAS/2026/JULIO/BRISAS-JULIO.xlsx
+++ b/BRISAS/EXPENSAS/2026/JULIO/BRISAS-JULIO.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistemax\Desktop\rc-consorcio2025\BRISAS\EXPENSAS\2026\JULIO\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C5EB9D2-5722-47E2-BBD4-8EA118FE52D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{05C91EBF-EA56-4C3F-80C4-73862639885A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="850" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1192,27 +1192,15 @@
     <t>Transf 23/07</t>
   </si>
   <si>
-    <t>Ayala Leon - Fc. 00008 - CUIT: 20949096654 - Servicios</t>
-  </si>
-  <si>
     <t>Transf 24/07</t>
   </si>
   <si>
-    <t>Ayala Leon - Fc. 00006 - CUIT: 20949096654 - Servicios</t>
-  </si>
-  <si>
     <t>Transf 10/07</t>
   </si>
   <si>
-    <t>Ayala Leon - Fc. 00007 - CUIT: 20949096654 - Servicios</t>
-  </si>
-  <si>
     <t>Transf 17/07</t>
   </si>
   <si>
-    <t>Ayala Leon - Fc. 00005 - CUIT: 20949096654 - Servicios</t>
-  </si>
-  <si>
     <t>Plegados del sur - Fc. 00009 - CUIT: 3071870758 - Fabricacion y pintura de cerco perimetral metalico : 11 columnas de 8m - Perfil C negro - 17 columnas de 7m - Perfil C negro - Travesaños horizontales de vinculacion - Perfil C negro - Empotramiento de columnas a 1m bajo terreno, preparadas para llenado de hormigon. Pintura: antioxido + exmalte sintetico</t>
   </si>
   <si>
@@ -1349,9 +1337,6 @@
   </si>
   <si>
     <t xml:space="preserve">Alonso Bado - Alquiler de vehiculo electrico - Fc. 000001315 - CUIT: 20138813232 </t>
-  </si>
-  <si>
-    <t>Ayala Leon - Fc. 00009 - CUIT: 20949096654 - Servicios</t>
   </si>
   <si>
     <t>Transf 31/07</t>
@@ -1457,6 +1442,21 @@
   </si>
   <si>
     <t>Multa mal cobrada al L114 (correspondia al  L14)</t>
+  </si>
+  <si>
+    <t>Ayala Leon - Fc. 00009 - CUIT: 20949096654 - Servicios - Descripcion de trabajos adjuntados en el Drive del mes</t>
+  </si>
+  <si>
+    <t>Ayala Leon - Fc. 00008 - CUIT: 20949096654 - Servicios - Descripcion de trabajos adjuntados en el Drive del mes</t>
+  </si>
+  <si>
+    <t>Ayala Leon - Fc. 00007 - CUIT: 20949096654 - Servicios - Descripcion de trabajos adjuntados en el Drive del mes</t>
+  </si>
+  <si>
+    <t>Ayala Leon - Fc. 00006 - CUIT: 20949096654 - Servicios - Descripcion de trabajos adjuntados en el Drive del mes</t>
+  </si>
+  <si>
+    <t>Ayala Leon - Fc. 00005 - CUIT: 20949096654 - Servicios - Descripcion de trabajos adjuntados en el Drive del mes</t>
   </si>
 </sst>
 </file>
@@ -2788,14 +2788,77 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="165" fontId="13" fillId="16" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="13" fillId="21" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="17" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="17" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="30" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="30" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="8" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="8" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="8" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="8" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="8" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="8" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="8" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="8" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -2830,81 +2893,33 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="8" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="8" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="8" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="8" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="8" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="8" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="8" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="8" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="9" fillId="5" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="8" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="44" fontId="13" fillId="4" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="44" fontId="13" fillId="4" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="44" fontId="17" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="17" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+    <xf numFmtId="44" fontId="17" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="17" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="30" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="30" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+    <xf numFmtId="169" fontId="22" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="44" fontId="9" fillId="5" borderId="32" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="9" fillId="5" borderId="33" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="9" fillId="5" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="9" fillId="5" borderId="7" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="9" fillId="5" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="169" fontId="22" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="169" fontId="22" fillId="3" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -2963,24 +2978,10 @@
     <xf numFmtId="0" fontId="13" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="8" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="44" fontId="13" fillId="4" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="13" fillId="4" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="17" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="17" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
+    <xf numFmtId="44" fontId="9" fillId="5" borderId="32" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="9" fillId="5" borderId="33" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="9" fillId="5" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="9" fillId="5" borderId="7" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -3020,7 +3021,6 @@
     <xf numFmtId="0" fontId="8" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="13" fillId="21" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="5">
     <cellStyle name="Hipervínculo" xfId="3" builtinId="8"/>
@@ -3448,34 +3448,34 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="352"/>
-      <c r="B1" s="347" t="s">
+      <c r="A1" s="375"/>
+      <c r="B1" s="370" t="s">
         <v>155</v>
       </c>
-      <c r="C1" s="348"/>
-      <c r="D1" s="348"/>
-      <c r="E1" s="349"/>
+      <c r="C1" s="371"/>
+      <c r="D1" s="371"/>
+      <c r="E1" s="372"/>
     </row>
     <row r="2" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="353"/>
-      <c r="B2" s="347" t="s">
+      <c r="A2" s="376"/>
+      <c r="B2" s="370" t="s">
         <v>157</v>
       </c>
-      <c r="C2" s="348"/>
-      <c r="D2" s="348"/>
-      <c r="E2" s="349"/>
+      <c r="C2" s="371"/>
+      <c r="D2" s="371"/>
+      <c r="E2" s="372"/>
     </row>
     <row r="3" spans="1:5" ht="32.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="353"/>
-      <c r="B3" s="344" t="s">
+      <c r="A3" s="376"/>
+      <c r="B3" s="367" t="s">
         <v>153</v>
       </c>
-      <c r="C3" s="345"/>
-      <c r="D3" s="345"/>
-      <c r="E3" s="346"/>
+      <c r="C3" s="368"/>
+      <c r="D3" s="368"/>
+      <c r="E3" s="369"/>
     </row>
     <row r="4" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="353"/>
+      <c r="A4" s="376"/>
       <c r="B4" s="43" t="s">
         <v>154</v>
       </c>
@@ -3484,7 +3484,7 @@
       <c r="E4" s="42"/>
     </row>
     <row r="5" spans="1:5" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="353"/>
+      <c r="A5" s="376"/>
       <c r="B5" s="46" t="s">
         <v>372</v>
       </c>
@@ -3493,7 +3493,7 @@
       <c r="E5" s="45"/>
     </row>
     <row r="6" spans="1:5" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="353"/>
+      <c r="A6" s="376"/>
       <c r="B6" s="47" t="s">
         <v>282</v>
       </c>
@@ -3502,7 +3502,7 @@
       <c r="E6" s="45"/>
     </row>
     <row r="7" spans="1:5" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="353"/>
+      <c r="A7" s="376"/>
       <c r="B7" s="47" t="s">
         <v>281</v>
       </c>
@@ -3511,13 +3511,13 @@
       <c r="E7" s="45"/>
     </row>
     <row r="8" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="354"/>
-      <c r="B8" s="350" t="s">
+      <c r="A8" s="377"/>
+      <c r="B8" s="373" t="s">
         <v>156</v>
       </c>
-      <c r="C8" s="350"/>
-      <c r="D8" s="350"/>
-      <c r="E8" s="351"/>
+      <c r="C8" s="373"/>
+      <c r="D8" s="373"/>
+      <c r="E8" s="374"/>
     </row>
     <row r="9" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="30"/>
@@ -3527,27 +3527,27 @@
       <c r="E9" s="30"/>
     </row>
     <row r="10" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="355" t="s">
+      <c r="A10" s="352" t="s">
         <v>371</v>
       </c>
-      <c r="B10" s="356"/>
-      <c r="C10" s="356"/>
-      <c r="D10" s="356"/>
-      <c r="E10" s="357"/>
+      <c r="B10" s="353"/>
+      <c r="C10" s="353"/>
+      <c r="D10" s="353"/>
+      <c r="E10" s="354"/>
     </row>
     <row r="11" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="358"/>
-      <c r="B11" s="359"/>
-      <c r="C11" s="359"/>
-      <c r="D11" s="359"/>
-      <c r="E11" s="360"/>
+      <c r="A11" s="355"/>
+      <c r="B11" s="356"/>
+      <c r="C11" s="356"/>
+      <c r="D11" s="356"/>
+      <c r="E11" s="357"/>
     </row>
     <row r="12" spans="1:5" ht="14.45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="361"/>
-      <c r="B12" s="362"/>
-      <c r="C12" s="362"/>
-      <c r="D12" s="362"/>
-      <c r="E12" s="363"/>
+      <c r="A12" s="358"/>
+      <c r="B12" s="359"/>
+      <c r="C12" s="359"/>
+      <c r="D12" s="359"/>
+      <c r="E12" s="360"/>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" s="30"/>
@@ -3564,34 +3564,34 @@
       <c r="E14" s="30"/>
     </row>
     <row r="15" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="364" t="s">
+      <c r="A15" s="361" t="s">
         <v>240</v>
       </c>
-      <c r="B15" s="364"/>
-      <c r="C15" s="364"/>
-      <c r="D15" s="364"/>
-      <c r="E15" s="364"/>
+      <c r="B15" s="361"/>
+      <c r="C15" s="361"/>
+      <c r="D15" s="361"/>
+      <c r="E15" s="361"/>
     </row>
     <row r="16" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="364"/>
-      <c r="B16" s="364"/>
-      <c r="C16" s="364"/>
-      <c r="D16" s="364"/>
-      <c r="E16" s="364"/>
+      <c r="A16" s="361"/>
+      <c r="B16" s="361"/>
+      <c r="C16" s="361"/>
+      <c r="D16" s="361"/>
+      <c r="E16" s="361"/>
     </row>
     <row r="17" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="364"/>
-      <c r="B17" s="364"/>
-      <c r="C17" s="364"/>
-      <c r="D17" s="364"/>
-      <c r="E17" s="364"/>
+      <c r="A17" s="361"/>
+      <c r="B17" s="361"/>
+      <c r="C17" s="361"/>
+      <c r="D17" s="361"/>
+      <c r="E17" s="361"/>
     </row>
     <row r="18" spans="1:8" ht="243" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="364"/>
-      <c r="B18" s="364"/>
-      <c r="C18" s="364"/>
-      <c r="D18" s="364"/>
-      <c r="E18" s="364"/>
+      <c r="A18" s="361"/>
+      <c r="B18" s="361"/>
+      <c r="C18" s="361"/>
+      <c r="D18" s="361"/>
+      <c r="E18" s="361"/>
     </row>
     <row r="19" spans="1:8" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A19" s="30"/>
@@ -3650,10 +3650,10 @@
       <c r="G24" s="252"/>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A25" s="365" t="s">
+      <c r="A25" s="363" t="s">
         <v>374</v>
       </c>
-      <c r="B25" s="366"/>
+      <c r="B25" s="364"/>
       <c r="C25" s="22"/>
       <c r="D25" s="266">
         <v>-491806.35</v>
@@ -3663,10 +3663,10 @@
       <c r="G25" s="253"/>
     </row>
     <row r="26" spans="1:8" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="367" t="s">
+      <c r="A26" s="365" t="s">
         <v>375</v>
       </c>
-      <c r="B26" s="368"/>
+      <c r="B26" s="366"/>
       <c r="C26" s="22"/>
       <c r="D26" s="266">
         <v>0</v>
@@ -3691,7 +3691,7 @@
       <c r="H27" s="71"/>
     </row>
     <row r="28" spans="1:8" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="341" t="s">
+      <c r="A28" s="342" t="s">
         <v>335</v>
       </c>
       <c r="B28" s="343"/>
@@ -3700,7 +3700,7 @@
         <v>1520000</v>
       </c>
       <c r="E28" s="22" t="s">
-        <v>426</v>
+        <v>422</v>
       </c>
       <c r="F28" s="30"/>
       <c r="G28" s="253">
@@ -3757,7 +3757,7 @@
         <v>1552652.02</v>
       </c>
       <c r="E32" s="76" t="s">
-        <v>427</v>
+        <v>423</v>
       </c>
       <c r="F32" s="254"/>
       <c r="G32" s="255"/>
@@ -3774,7 +3774,7 @@
         <v>153062.19</v>
       </c>
       <c r="E33" s="75" t="s">
-        <v>450</v>
+        <v>445</v>
       </c>
       <c r="F33" s="254"/>
       <c r="G33" s="255"/>
@@ -3844,7 +3844,7 @@
       <c r="G37" s="30"/>
     </row>
     <row r="38" spans="1:9" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="341" t="s">
+      <c r="A38" s="342" t="s">
         <v>268</v>
       </c>
       <c r="B38" s="343"/>
@@ -3853,13 +3853,13 @@
         <v>148518.18</v>
       </c>
       <c r="E38" s="76" t="s">
-        <v>443</v>
+        <v>438</v>
       </c>
       <c r="F38" s="30"/>
       <c r="G38" s="30"/>
     </row>
     <row r="39" spans="1:9" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="341" t="s">
+      <c r="A39" s="342" t="s">
         <v>269</v>
       </c>
       <c r="B39" s="343"/>
@@ -3868,13 +3868,13 @@
         <v>7805</v>
       </c>
       <c r="E39" s="76" t="s">
-        <v>462</v>
+        <v>457</v>
       </c>
       <c r="F39" s="30"/>
       <c r="G39" s="30"/>
     </row>
     <row r="40" spans="1:9" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="341" t="s">
+      <c r="A40" s="342" t="s">
         <v>308</v>
       </c>
       <c r="B40" s="343"/>
@@ -3883,13 +3883,13 @@
         <v>23573.47</v>
       </c>
       <c r="E40" s="76" t="s">
-        <v>451</v>
+        <v>446</v>
       </c>
       <c r="F40" s="30"/>
       <c r="G40" s="30"/>
     </row>
     <row r="41" spans="1:9" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="341" t="s">
+      <c r="A41" s="342" t="s">
         <v>308</v>
       </c>
       <c r="B41" s="343"/>
@@ -3898,7 +3898,7 @@
         <v>26214.080000000002</v>
       </c>
       <c r="E41" s="76" t="s">
-        <v>427</v>
+        <v>423</v>
       </c>
       <c r="F41" s="30"/>
       <c r="G41" s="30"/>
@@ -3929,16 +3929,16 @@
       <c r="G43" s="30"/>
     </row>
     <row r="44" spans="1:9" ht="42.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="341" t="s">
-        <v>444</v>
-      </c>
-      <c r="B44" s="342"/>
+      <c r="A44" s="342" t="s">
+        <v>439</v>
+      </c>
+      <c r="B44" s="362"/>
       <c r="C44" s="101"/>
       <c r="D44" s="198">
         <v>46102546.960000001</v>
       </c>
       <c r="E44" s="76" t="s">
-        <v>443</v>
+        <v>438</v>
       </c>
       <c r="F44" s="256">
         <f>D44</f>
@@ -3948,16 +3948,16 @@
       <c r="I44" s="37"/>
     </row>
     <row r="45" spans="1:9" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="341" t="s">
-        <v>417</v>
-      </c>
-      <c r="B45" s="342"/>
+      <c r="A45" s="342" t="s">
+        <v>413</v>
+      </c>
+      <c r="B45" s="362"/>
       <c r="C45" s="101"/>
       <c r="D45" s="198">
         <v>5702320.7999999998</v>
       </c>
       <c r="E45" s="29" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="F45" s="256"/>
       <c r="G45" s="30"/>
@@ -3990,25 +3990,25 @@
       <c r="G47" s="30"/>
     </row>
     <row r="48" spans="1:9" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A48" s="341" t="s">
-        <v>399</v>
-      </c>
-      <c r="B48" s="342"/>
+      <c r="A48" s="342" t="s">
+        <v>395</v>
+      </c>
+      <c r="B48" s="362"/>
       <c r="C48" s="101"/>
       <c r="D48" s="198">
         <v>1472058.6</v>
       </c>
       <c r="E48" s="29" t="s">
-        <v>393</v>
+        <v>389</v>
       </c>
       <c r="F48" s="30"/>
       <c r="G48" s="30"/>
     </row>
     <row r="49" spans="1:8" ht="51.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A49" s="341" t="s">
+      <c r="A49" s="342" t="s">
         <v>381</v>
       </c>
-      <c r="B49" s="342"/>
+      <c r="B49" s="362"/>
       <c r="C49" s="101"/>
       <c r="D49" s="198">
         <v>756250</v>
@@ -4020,23 +4020,23 @@
       <c r="G49" s="30"/>
     </row>
     <row r="50" spans="1:8" ht="51.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A50" s="341" t="s">
-        <v>400</v>
-      </c>
-      <c r="B50" s="342"/>
+      <c r="A50" s="342" t="s">
+        <v>396</v>
+      </c>
+      <c r="B50" s="362"/>
       <c r="C50" s="101"/>
       <c r="D50" s="198">
         <v>97574.399999999994</v>
       </c>
       <c r="E50" s="29" t="s">
-        <v>393</v>
+        <v>389</v>
       </c>
       <c r="F50" s="30"/>
       <c r="G50" s="30"/>
     </row>
     <row r="51" spans="1:8" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A51" s="341" t="s">
-        <v>411</v>
+      <c r="A51" s="342" t="s">
+        <v>407</v>
       </c>
       <c r="B51" s="343"/>
       <c r="C51" s="102"/>
@@ -4044,13 +4044,13 @@
         <v>6300000</v>
       </c>
       <c r="E51" s="262" t="s">
-        <v>398</v>
+        <v>394</v>
       </c>
       <c r="F51" s="30"/>
       <c r="G51" s="30"/>
     </row>
     <row r="52" spans="1:8" ht="39" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A52" s="341" t="s">
+      <c r="A52" s="342" t="s">
         <v>378</v>
       </c>
       <c r="B52" s="343"/>
@@ -4059,13 +4059,13 @@
         <v>228690</v>
       </c>
       <c r="E52" s="29" t="s">
-        <v>424</v>
+        <v>420</v>
       </c>
       <c r="F52" s="30"/>
       <c r="G52" s="30"/>
     </row>
     <row r="53" spans="1:8" ht="48" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A53" s="341" t="s">
+      <c r="A53" s="342" t="s">
         <v>338</v>
       </c>
       <c r="B53" s="343"/>
@@ -4074,14 +4074,14 @@
         <v>118400</v>
       </c>
       <c r="E53" s="77" t="s">
-        <v>454</v>
+        <v>449</v>
       </c>
       <c r="F53" s="30"/>
       <c r="G53" s="30"/>
     </row>
     <row r="54" spans="1:8" ht="44.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A54" s="341" t="s">
-        <v>441</v>
+      <c r="A54" s="342" t="s">
+        <v>436</v>
       </c>
       <c r="B54" s="343"/>
       <c r="C54" s="102"/>
@@ -4093,8 +4093,8 @@
       <c r="G54" s="30"/>
     </row>
     <row r="55" spans="1:8" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A55" s="341" t="s">
-        <v>435</v>
+      <c r="A55" s="342" t="s">
+        <v>431</v>
       </c>
       <c r="B55" s="343"/>
       <c r="C55" s="102"/>
@@ -4102,14 +4102,14 @@
         <v>820380</v>
       </c>
       <c r="E55" s="77" t="s">
-        <v>424</v>
+        <v>420</v>
       </c>
       <c r="F55" s="30"/>
       <c r="G55" s="30"/>
     </row>
     <row r="56" spans="1:8" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A56" s="341" t="s">
-        <v>396</v>
+      <c r="A56" s="342" t="s">
+        <v>392</v>
       </c>
       <c r="B56" s="343"/>
       <c r="C56" s="102"/>
@@ -4117,14 +4117,14 @@
         <v>220000</v>
       </c>
       <c r="E56" s="77" t="s">
-        <v>393</v>
+        <v>389</v>
       </c>
       <c r="F56" s="30"/>
       <c r="G56" s="30"/>
     </row>
     <row r="57" spans="1:8" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A57" s="341" t="s">
-        <v>402</v>
+      <c r="A57" s="342" t="s">
+        <v>398</v>
       </c>
       <c r="B57" s="343"/>
       <c r="C57" s="102"/>
@@ -4138,8 +4138,8 @@
       <c r="G57" s="30"/>
     </row>
     <row r="58" spans="1:8" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A58" s="341" t="s">
-        <v>419</v>
+      <c r="A58" s="342" t="s">
+        <v>415</v>
       </c>
       <c r="B58" s="343"/>
       <c r="C58" s="102"/>
@@ -4147,14 +4147,14 @@
         <v>110000</v>
       </c>
       <c r="E58" s="77" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="F58" s="30"/>
       <c r="G58" s="30"/>
     </row>
     <row r="59" spans="1:8" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A59" s="341" t="s">
-        <v>420</v>
+      <c r="A59" s="342" t="s">
+        <v>416</v>
       </c>
       <c r="B59" s="343"/>
       <c r="C59" s="102"/>
@@ -4162,14 +4162,14 @@
         <v>110000</v>
       </c>
       <c r="E59" s="77" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="F59" s="30"/>
       <c r="G59" s="30"/>
     </row>
     <row r="60" spans="1:8" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A60" s="341" t="s">
-        <v>425</v>
+      <c r="A60" s="342" t="s">
+        <v>421</v>
       </c>
       <c r="B60" s="343"/>
       <c r="C60" s="102"/>
@@ -4177,13 +4177,13 @@
         <v>150000</v>
       </c>
       <c r="E60" s="77" t="s">
-        <v>393</v>
+        <v>389</v>
       </c>
       <c r="F60" s="30"/>
       <c r="G60" s="30"/>
     </row>
     <row r="61" spans="1:8" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A61" s="341" t="s">
+      <c r="A61" s="342" t="s">
         <v>379</v>
       </c>
       <c r="B61" s="343"/>
@@ -4192,14 +4192,14 @@
         <v>1300000</v>
       </c>
       <c r="E61" s="77" t="s">
-        <v>424</v>
+        <v>420</v>
       </c>
       <c r="F61" s="30"/>
       <c r="G61" s="30"/>
     </row>
     <row r="62" spans="1:8" ht="51" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A62" s="341" t="s">
-        <v>412</v>
+      <c r="A62" s="342" t="s">
+        <v>408</v>
       </c>
       <c r="B62" s="343"/>
       <c r="C62" s="22"/>
@@ -4207,7 +4207,7 @@
         <v>2459883</v>
       </c>
       <c r="E62" s="77" t="s">
-        <v>398</v>
+        <v>394</v>
       </c>
       <c r="F62" s="30"/>
       <c r="G62" s="257"/>
@@ -4239,8 +4239,8 @@
       <c r="G64" s="30"/>
     </row>
     <row r="65" spans="1:7" ht="42" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A65" s="341" t="s">
-        <v>401</v>
+      <c r="A65" s="342" t="s">
+        <v>397</v>
       </c>
       <c r="B65" s="343"/>
       <c r="C65" s="22"/>
@@ -4254,10 +4254,10 @@
       <c r="G65" s="30"/>
     </row>
     <row r="66" spans="1:7" ht="63.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A66" s="341" t="s">
-        <v>406</v>
-      </c>
-      <c r="B66" s="342"/>
+      <c r="A66" s="342" t="s">
+        <v>402</v>
+      </c>
+      <c r="B66" s="362"/>
       <c r="C66" s="343"/>
       <c r="D66" s="336">
         <v>350000</v>
@@ -4269,23 +4269,23 @@
       <c r="G66" s="30"/>
     </row>
     <row r="67" spans="1:7" ht="129.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A67" s="341" t="s">
-        <v>440</v>
-      </c>
-      <c r="B67" s="342"/>
+      <c r="A67" s="342" t="s">
+        <v>435</v>
+      </c>
+      <c r="B67" s="362"/>
       <c r="C67" s="343"/>
       <c r="D67" s="336">
         <v>2120000</v>
       </c>
       <c r="E67" s="78" t="s">
-        <v>437</v>
+        <v>432</v>
       </c>
       <c r="F67" s="30"/>
       <c r="G67" s="30"/>
     </row>
     <row r="68" spans="1:7" ht="83.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A68" s="341" t="s">
-        <v>414</v>
+      <c r="A68" s="342" t="s">
+        <v>410</v>
       </c>
       <c r="B68" s="343"/>
       <c r="C68" s="22"/>
@@ -4293,14 +4293,14 @@
         <v>1250000</v>
       </c>
       <c r="E68" s="78" t="s">
-        <v>398</v>
+        <v>394</v>
       </c>
       <c r="F68" s="30"/>
       <c r="G68" s="30"/>
     </row>
     <row r="69" spans="1:7" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A69" s="341" t="s">
-        <v>442</v>
+      <c r="A69" s="342" t="s">
+        <v>437</v>
       </c>
       <c r="B69" s="343"/>
       <c r="C69" s="98"/>
@@ -4308,14 +4308,14 @@
         <v>75000</v>
       </c>
       <c r="E69" s="143" t="s">
-        <v>428</v>
+        <v>424</v>
       </c>
       <c r="F69" s="257"/>
       <c r="G69" s="30"/>
     </row>
     <row r="70" spans="1:7" ht="31.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70" s="231" t="s">
-        <v>395</v>
+        <v>391</v>
       </c>
       <c r="B70" s="263"/>
       <c r="C70" s="98"/>
@@ -4323,14 +4323,14 @@
         <v>126600</v>
       </c>
       <c r="E70" s="143" t="s">
-        <v>393</v>
+        <v>389</v>
       </c>
       <c r="F70" s="30"/>
       <c r="G70" s="30"/>
     </row>
     <row r="71" spans="1:7" ht="31.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A71" s="231" t="s">
-        <v>394</v>
+        <v>390</v>
       </c>
       <c r="B71" s="263"/>
       <c r="C71" s="98"/>
@@ -4338,14 +4338,14 @@
         <v>108000</v>
       </c>
       <c r="E71" s="143" t="s">
-        <v>393</v>
+        <v>389</v>
       </c>
       <c r="F71" s="30"/>
       <c r="G71" s="30"/>
     </row>
     <row r="72" spans="1:7" ht="31.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A72" s="231" t="s">
-        <v>456</v>
+        <v>451</v>
       </c>
       <c r="B72" s="328"/>
       <c r="C72" s="98"/>
@@ -4353,14 +4353,14 @@
         <v>43800</v>
       </c>
       <c r="E72" s="143" t="s">
-        <v>455</v>
+        <v>450</v>
       </c>
       <c r="F72" s="30"/>
       <c r="G72" s="30"/>
     </row>
     <row r="73" spans="1:7" ht="31.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A73" s="231" t="s">
-        <v>457</v>
+        <v>452</v>
       </c>
       <c r="B73" s="328"/>
       <c r="C73" s="98"/>
@@ -4368,14 +4368,14 @@
         <v>130300</v>
       </c>
       <c r="E73" s="143" t="s">
-        <v>455</v>
+        <v>450</v>
       </c>
       <c r="F73" s="30"/>
       <c r="G73" s="30"/>
     </row>
     <row r="74" spans="1:7" ht="54.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A74" s="341" t="s">
-        <v>458</v>
+      <c r="A74" s="342" t="s">
+        <v>453</v>
       </c>
       <c r="B74" s="343"/>
       <c r="C74" s="98"/>
@@ -4383,14 +4383,14 @@
         <v>1465520</v>
       </c>
       <c r="E74" s="143" t="s">
-        <v>455</v>
+        <v>450</v>
       </c>
       <c r="F74" s="30"/>
       <c r="G74" s="30"/>
     </row>
     <row r="75" spans="1:7" ht="39" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A75" s="341" t="s">
-        <v>403</v>
+      <c r="A75" s="342" t="s">
+        <v>399</v>
       </c>
       <c r="B75" s="343"/>
       <c r="C75" s="22"/>
@@ -4398,14 +4398,14 @@
         <v>3179880</v>
       </c>
       <c r="E75" s="143" t="s">
-        <v>404</v>
+        <v>400</v>
       </c>
       <c r="F75" s="30"/>
       <c r="G75" s="30"/>
     </row>
     <row r="76" spans="1:7" ht="61.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A76" s="341" t="s">
-        <v>434</v>
+      <c r="A76" s="342" t="s">
+        <v>430</v>
       </c>
       <c r="B76" s="343"/>
       <c r="C76" s="98"/>
@@ -4413,14 +4413,14 @@
         <v>946220</v>
       </c>
       <c r="E76" s="143" t="s">
-        <v>424</v>
+        <v>420</v>
       </c>
       <c r="F76" s="30"/>
       <c r="G76" s="30"/>
     </row>
     <row r="77" spans="1:7" ht="42" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A77" s="341" t="s">
-        <v>421</v>
+      <c r="A77" s="342" t="s">
+        <v>417</v>
       </c>
       <c r="B77" s="343"/>
       <c r="C77" s="98"/>
@@ -4428,14 +4428,14 @@
         <v>1113200</v>
       </c>
       <c r="E77" s="143" t="s">
-        <v>448</v>
+        <v>443</v>
       </c>
       <c r="F77" s="257"/>
       <c r="G77" s="30"/>
     </row>
     <row r="78" spans="1:7" ht="40.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A78" s="341" t="s">
-        <v>422</v>
+      <c r="A78" s="342" t="s">
+        <v>418</v>
       </c>
       <c r="B78" s="343"/>
       <c r="C78" s="98"/>
@@ -4443,14 +4443,14 @@
         <v>749938.04</v>
       </c>
       <c r="E78" s="143" t="s">
-        <v>423</v>
+        <v>419</v>
       </c>
       <c r="F78" s="257"/>
       <c r="G78" s="30"/>
     </row>
     <row r="79" spans="1:7" ht="40.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A79" s="341" t="s">
-        <v>418</v>
+      <c r="A79" s="342" t="s">
+        <v>414</v>
       </c>
       <c r="B79" s="343"/>
       <c r="C79" s="98"/>
@@ -4458,14 +4458,14 @@
         <v>1113200</v>
       </c>
       <c r="E79" s="143" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="F79" s="257"/>
       <c r="G79" s="30"/>
     </row>
     <row r="80" spans="1:7" ht="40.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A80" s="341" t="s">
-        <v>460</v>
+      <c r="A80" s="342" t="s">
+        <v>455</v>
       </c>
       <c r="B80" s="343"/>
       <c r="C80" s="98"/>
@@ -4473,14 +4473,14 @@
         <v>1669800</v>
       </c>
       <c r="E80" s="143" t="s">
-        <v>461</v>
+        <v>456</v>
       </c>
       <c r="F80" s="257"/>
       <c r="G80" s="30"/>
     </row>
     <row r="81" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A81" s="341" t="s">
-        <v>413</v>
+      <c r="A81" s="342" t="s">
+        <v>409</v>
       </c>
       <c r="B81" s="343"/>
       <c r="C81" s="98"/>
@@ -4488,14 +4488,14 @@
         <v>46300</v>
       </c>
       <c r="E81" s="85" t="s">
-        <v>398</v>
+        <v>394</v>
       </c>
       <c r="F81" s="30"/>
       <c r="G81" s="30"/>
     </row>
     <row r="82" spans="1:7" ht="55.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A82" s="341" t="s">
-        <v>397</v>
+      <c r="A82" s="342" t="s">
+        <v>393</v>
       </c>
       <c r="B82" s="343"/>
       <c r="C82" s="98"/>
@@ -4503,14 +4503,14 @@
         <v>95648.4</v>
       </c>
       <c r="E82" s="85" t="s">
-        <v>398</v>
+        <v>394</v>
       </c>
       <c r="F82" s="30"/>
       <c r="G82" s="30"/>
     </row>
     <row r="83" spans="1:7" ht="41.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A83" s="341" t="s">
-        <v>415</v>
+      <c r="A83" s="342" t="s">
+        <v>411</v>
       </c>
       <c r="B83" s="343"/>
       <c r="C83" s="98"/>
@@ -4518,14 +4518,14 @@
         <v>139099</v>
       </c>
       <c r="E83" s="85" t="s">
-        <v>416</v>
+        <v>412</v>
       </c>
       <c r="F83" s="30"/>
       <c r="G83" s="30"/>
     </row>
-    <row r="84" spans="1:7" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A84" s="341" t="s">
-        <v>436</v>
+    <row r="84" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A84" s="342" t="s">
+        <v>465</v>
       </c>
       <c r="B84" s="343"/>
       <c r="C84" s="98"/>
@@ -4533,14 +4533,14 @@
         <v>1250000</v>
       </c>
       <c r="E84" s="85" t="s">
-        <v>437</v>
+        <v>432</v>
       </c>
       <c r="F84" s="30"/>
       <c r="G84" s="30"/>
     </row>
-    <row r="85" spans="1:7" ht="25.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A85" s="341" t="s">
-        <v>383</v>
+    <row r="85" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A85" s="342" t="s">
+        <v>466</v>
       </c>
       <c r="B85" s="343"/>
       <c r="C85" s="98"/>
@@ -4548,14 +4548,14 @@
         <v>1775000</v>
       </c>
       <c r="E85" s="143" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="F85" s="30"/>
       <c r="G85" s="30"/>
     </row>
-    <row r="86" spans="1:7" ht="25.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A86" s="341" t="s">
-        <v>387</v>
+    <row r="86" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A86" s="342" t="s">
+        <v>467</v>
       </c>
       <c r="B86" s="343"/>
       <c r="C86" s="98"/>
@@ -4563,14 +4563,14 @@
         <v>1000000</v>
       </c>
       <c r="E86" s="85" t="s">
-        <v>388</v>
+        <v>385</v>
       </c>
       <c r="F86" s="30"/>
       <c r="G86" s="30"/>
     </row>
-    <row r="87" spans="1:7" ht="25.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A87" s="341" t="s">
-        <v>385</v>
+    <row r="87" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A87" s="342" t="s">
+        <v>468</v>
       </c>
       <c r="B87" s="343"/>
       <c r="C87" s="98"/>
@@ -4578,14 +4578,14 @@
         <v>1000000</v>
       </c>
       <c r="E87" s="85" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="F87" s="30"/>
       <c r="G87" s="30"/>
     </row>
-    <row r="88" spans="1:7" ht="20.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A88" s="341" t="s">
-        <v>389</v>
+    <row r="88" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A88" s="342" t="s">
+        <v>469</v>
       </c>
       <c r="B88" s="343"/>
       <c r="C88" s="98"/>
@@ -4593,14 +4593,14 @@
         <v>1250000</v>
       </c>
       <c r="E88" s="85" t="s">
-        <v>449</v>
+        <v>444</v>
       </c>
       <c r="F88" s="30"/>
       <c r="G88" s="30"/>
     </row>
     <row r="89" spans="1:7" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A89" s="341" t="s">
-        <v>391</v>
+      <c r="A89" s="342" t="s">
+        <v>387</v>
       </c>
       <c r="B89" s="343"/>
       <c r="C89" s="98"/>
@@ -4608,14 +4608,14 @@
         <v>20500</v>
       </c>
       <c r="E89" s="85" t="s">
-        <v>388</v>
+        <v>385</v>
       </c>
       <c r="F89" s="30"/>
       <c r="G89" s="30"/>
     </row>
     <row r="90" spans="1:7" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A90" s="341" t="s">
-        <v>392</v>
+      <c r="A90" s="342" t="s">
+        <v>388</v>
       </c>
       <c r="B90" s="343"/>
       <c r="C90" s="98"/>
@@ -4623,14 +4623,14 @@
         <v>48500</v>
       </c>
       <c r="E90" s="85" t="s">
-        <v>388</v>
+        <v>385</v>
       </c>
       <c r="F90" s="30"/>
       <c r="G90" s="30"/>
     </row>
     <row r="91" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A91" s="341" t="s">
-        <v>431</v>
+      <c r="A91" s="342" t="s">
+        <v>427</v>
       </c>
       <c r="B91" s="343"/>
       <c r="C91" s="98"/>
@@ -4638,7 +4638,7 @@
         <v>315000</v>
       </c>
       <c r="E91" s="78" t="s">
-        <v>398</v>
+        <v>394</v>
       </c>
       <c r="F91" s="30"/>
       <c r="G91" s="30"/>
@@ -4669,7 +4669,7 @@
       <c r="G93" s="30"/>
     </row>
     <row r="94" spans="1:7" ht="23.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A94" s="341" t="s">
+      <c r="A94" s="342" t="s">
         <v>380</v>
       </c>
       <c r="B94" s="343"/>
@@ -4678,14 +4678,14 @@
         <v>3218160</v>
       </c>
       <c r="E94" s="85" t="s">
-        <v>426</v>
+        <v>422</v>
       </c>
       <c r="F94" s="30"/>
       <c r="G94" s="30"/>
     </row>
     <row r="95" spans="1:7" ht="68.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A95" s="341" t="s">
-        <v>446</v>
+      <c r="A95" s="342" t="s">
+        <v>441</v>
       </c>
       <c r="B95" s="343"/>
       <c r="C95" s="22"/>
@@ -4693,7 +4693,7 @@
         <v>250000</v>
       </c>
       <c r="E95" s="326" t="s">
-        <v>430</v>
+        <v>426</v>
       </c>
       <c r="F95" s="30"/>
       <c r="G95" s="30"/>
@@ -4826,7 +4826,7 @@
       <c r="G106" s="30"/>
     </row>
     <row r="107" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A107" s="341" t="s">
+      <c r="A107" s="342" t="s">
         <v>337</v>
       </c>
       <c r="B107" s="343"/>
@@ -4841,7 +4841,7 @@
       <c r="G107" s="30"/>
     </row>
     <row r="108" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A108" s="341" t="s">
+      <c r="A108" s="342" t="s">
         <v>331</v>
       </c>
       <c r="B108" s="343"/>
@@ -4850,13 +4850,13 @@
         <v>64376.63</v>
       </c>
       <c r="E108" s="248" t="s">
-        <v>452</v>
+        <v>447</v>
       </c>
       <c r="F108" s="30"/>
       <c r="G108" s="30"/>
     </row>
     <row r="109" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A109" s="341" t="s">
+      <c r="A109" s="342" t="s">
         <v>332</v>
       </c>
       <c r="B109" s="343"/>
@@ -4872,7 +4872,7 @@
       <c r="G109" s="30"/>
     </row>
     <row r="110" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A110" s="341" t="s">
+      <c r="A110" s="342" t="s">
         <v>333</v>
       </c>
       <c r="B110" s="343"/>
@@ -4888,25 +4888,25 @@
       <c r="G110" s="30"/>
     </row>
     <row r="111" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A111" s="369" t="s">
-        <v>407</v>
-      </c>
-      <c r="B111" s="370"/>
+      <c r="A111" s="344" t="s">
+        <v>403</v>
+      </c>
+      <c r="B111" s="345"/>
       <c r="C111" s="22"/>
       <c r="D111" s="198">
         <v>1314489.94</v>
       </c>
       <c r="E111" s="78" t="s">
-        <v>398</v>
+        <v>394</v>
       </c>
       <c r="F111" s="30"/>
       <c r="G111" s="30"/>
     </row>
     <row r="112" spans="1:7" ht="36.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A112" s="369" t="s">
-        <v>408</v>
-      </c>
-      <c r="B112" s="370"/>
+      <c r="A112" s="344" t="s">
+        <v>404</v>
+      </c>
+      <c r="B112" s="345"/>
       <c r="C112" s="22"/>
       <c r="D112" s="198">
         <v>458163.6</v>
@@ -4919,10 +4919,10 @@
       <c r="G112" s="30"/>
     </row>
     <row r="113" spans="1:7" ht="31.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A113" s="369" t="s">
-        <v>409</v>
-      </c>
-      <c r="B113" s="370"/>
+      <c r="A113" s="344" t="s">
+        <v>405</v>
+      </c>
+      <c r="B113" s="345"/>
       <c r="C113" s="22"/>
       <c r="D113" s="198">
         <v>124681.3</v>
@@ -4935,10 +4935,10 @@
       <c r="G113" s="30"/>
     </row>
     <row r="114" spans="1:7" ht="33.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A114" s="369" t="s">
-        <v>410</v>
-      </c>
-      <c r="B114" s="370"/>
+      <c r="A114" s="344" t="s">
+        <v>406</v>
+      </c>
+      <c r="B114" s="345"/>
       <c r="C114" s="22"/>
       <c r="D114" s="198">
         <v>92816.68</v>
@@ -4954,10 +4954,10 @@
       <c r="G114" s="30"/>
     </row>
     <row r="115" spans="1:7" ht="33.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A115" s="369" t="s">
-        <v>405</v>
-      </c>
-      <c r="B115" s="370"/>
+      <c r="A115" s="344" t="s">
+        <v>401</v>
+      </c>
+      <c r="B115" s="345"/>
       <c r="C115" s="22"/>
       <c r="D115" s="198">
         <v>646140</v>
@@ -4969,10 +4969,10 @@
       <c r="G115" s="30"/>
     </row>
     <row r="116" spans="1:7" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A116" s="369" t="s">
+      <c r="A116" s="344" t="s">
         <v>189</v>
       </c>
-      <c r="B116" s="370"/>
+      <c r="B116" s="345"/>
       <c r="C116" s="22"/>
       <c r="D116" s="198">
         <v>117933.22</v>
@@ -4985,10 +4985,10 @@
       <c r="G116" s="30"/>
     </row>
     <row r="117" spans="1:7" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A117" s="369" t="s">
+      <c r="A117" s="344" t="s">
         <v>300</v>
       </c>
-      <c r="B117" s="370"/>
+      <c r="B117" s="345"/>
       <c r="C117" s="22"/>
       <c r="D117" s="198">
         <v>8811.25</v>
@@ -5036,38 +5036,38 @@
       <c r="G120" s="30"/>
     </row>
     <row r="121" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A121" s="369" t="s">
-        <v>432</v>
-      </c>
-      <c r="B121" s="370"/>
+      <c r="A121" s="344" t="s">
+        <v>428</v>
+      </c>
+      <c r="B121" s="345"/>
       <c r="C121" s="22"/>
       <c r="D121" s="337">
         <v>9914839.9499999993</v>
       </c>
       <c r="E121" s="78" t="s">
-        <v>398</v>
+        <v>394</v>
       </c>
       <c r="F121" s="30"/>
       <c r="G121" s="30"/>
     </row>
     <row r="122" spans="1:7" ht="114" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A122" s="369" t="s">
-        <v>390</v>
-      </c>
-      <c r="B122" s="370"/>
+      <c r="A122" s="344" t="s">
+        <v>386</v>
+      </c>
+      <c r="B122" s="345"/>
       <c r="C122" s="22"/>
       <c r="D122" s="337">
         <v>15917020</v>
       </c>
       <c r="E122" s="78" t="s">
-        <v>388</v>
+        <v>385</v>
       </c>
       <c r="F122" s="30"/>
       <c r="G122" s="30"/>
     </row>
     <row r="123" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A123" s="341" t="s">
-        <v>429</v>
+      <c r="A123" s="342" t="s">
+        <v>425</v>
       </c>
       <c r="B123" s="343"/>
       <c r="C123" s="22"/>
@@ -5081,8 +5081,8 @@
       <c r="G123" s="30"/>
     </row>
     <row r="124" spans="1:7" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A124" s="341" t="s">
-        <v>433</v>
+      <c r="A124" s="342" t="s">
+        <v>429</v>
       </c>
       <c r="B124" s="343"/>
       <c r="C124" s="22"/>
@@ -5090,7 +5090,7 @@
         <v>1071600</v>
       </c>
       <c r="E124" s="143" t="s">
-        <v>424</v>
+        <v>420</v>
       </c>
       <c r="F124" s="30"/>
       <c r="G124" s="30"/>
@@ -5171,10 +5171,10 @@
       <c r="G131" s="30"/>
     </row>
     <row r="132" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A132" s="372" t="s">
-        <v>445</v>
-      </c>
-      <c r="B132" s="372"/>
+      <c r="A132" s="347" t="s">
+        <v>440</v>
+      </c>
+      <c r="B132" s="347"/>
       <c r="C132" s="22"/>
       <c r="D132" s="198">
         <f>2038428-1520000</f>
@@ -5188,7 +5188,7 @@
       <c r="G132" s="256"/>
     </row>
     <row r="133" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A133" s="341"/>
+      <c r="A133" s="342"/>
       <c r="B133" s="343"/>
       <c r="C133" s="98"/>
       <c r="D133" s="198"/>
@@ -5365,7 +5365,7 @@
     </row>
     <row r="152" spans="1:6" s="148" customFormat="1" ht="51.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A152" s="7" t="s">
-        <v>467</v>
+        <v>462</v>
       </c>
       <c r="B152" s="154">
         <v>-767774.04</v>
@@ -5375,7 +5375,7 @@
     </row>
     <row r="153" spans="1:6" s="148" customFormat="1" ht="33" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A153" s="7" t="s">
-        <v>469</v>
+        <v>464</v>
       </c>
       <c r="B153" s="154">
         <v>-223900</v>
@@ -5385,7 +5385,7 @@
     </row>
     <row r="154" spans="1:6" s="148" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A154" s="7" t="s">
-        <v>447</v>
+        <v>442</v>
       </c>
       <c r="B154" s="153">
         <f>-B189</f>
@@ -5493,10 +5493,10 @@
       <c r="F163" s="74"/>
     </row>
     <row r="164" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A164" s="375" t="s">
+      <c r="A164" s="350" t="s">
         <v>326</v>
       </c>
-      <c r="B164" s="376"/>
+      <c r="B164" s="351"/>
       <c r="C164" s="6"/>
       <c r="D164" s="13"/>
       <c r="E164" s="34"/>
@@ -5565,10 +5565,10 @@
       <c r="F170" s="74"/>
     </row>
     <row r="171" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A171" s="373" t="s">
+      <c r="A171" s="348" t="s">
         <v>292</v>
       </c>
-      <c r="B171" s="374"/>
+      <c r="B171" s="349"/>
       <c r="C171" s="6"/>
       <c r="D171" s="13"/>
       <c r="E171" s="34"/>
@@ -5677,7 +5677,7 @@
     </row>
     <row r="181" spans="1:15" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A181" s="88" t="s">
-        <v>453</v>
+        <v>448</v>
       </c>
       <c r="B181" s="244">
         <v>-4400</v>
@@ -5689,7 +5689,7 @@
     </row>
     <row r="182" spans="1:15" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A182" s="88" t="s">
-        <v>459</v>
+        <v>454</v>
       </c>
       <c r="B182" s="244">
         <v>-7800</v>
@@ -5701,7 +5701,7 @@
     </row>
     <row r="183" spans="1:15" ht="51.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A183" s="88" t="s">
-        <v>463</v>
+        <v>458</v>
       </c>
       <c r="B183" s="244">
         <v>-133200</v>
@@ -5783,7 +5783,7 @@
     </row>
     <row r="189" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A189" s="67" t="s">
-        <v>465</v>
+        <v>460</v>
       </c>
       <c r="B189" s="267">
         <v>-50026212.090000004</v>
@@ -5804,7 +5804,7 @@
     </row>
     <row r="190" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A190" s="67" t="s">
-        <v>466</v>
+        <v>461</v>
       </c>
       <c r="B190" s="68">
         <v>4016377.55</v>
@@ -5825,7 +5825,7 @@
     </row>
     <row r="191" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A191" s="123" t="s">
-        <v>464</v>
+        <v>459</v>
       </c>
       <c r="B191" s="249">
         <v>106403918.55</v>
@@ -5875,16 +5875,16 @@
       <c r="F194" s="35"/>
     </row>
     <row r="195" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A195" s="371" t="s">
+      <c r="A195" s="346" t="s">
         <v>17</v>
       </c>
-      <c r="B195" s="371"/>
-      <c r="C195" s="371"/>
+      <c r="B195" s="346"/>
+      <c r="C195" s="346"/>
     </row>
     <row r="196" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A196" s="371"/>
-      <c r="B196" s="371"/>
-      <c r="C196" s="371"/>
+      <c r="A196" s="346"/>
+      <c r="B196" s="346"/>
+      <c r="C196" s="346"/>
     </row>
     <row r="197" spans="1:13" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A197" s="63"/>
@@ -5911,66 +5911,6 @@
     </row>
   </sheetData>
   <mergeCells count="76">
-    <mergeCell ref="A75:B75"/>
-    <mergeCell ref="A80:B80"/>
-    <mergeCell ref="A59:B59"/>
-    <mergeCell ref="A60:B60"/>
-    <mergeCell ref="A95:B95"/>
-    <mergeCell ref="A84:B84"/>
-    <mergeCell ref="A86:B86"/>
-    <mergeCell ref="A87:B87"/>
-    <mergeCell ref="A90:B90"/>
-    <mergeCell ref="A94:B94"/>
-    <mergeCell ref="A68:B68"/>
-    <mergeCell ref="A61:B61"/>
-    <mergeCell ref="A69:B69"/>
-    <mergeCell ref="A57:B57"/>
-    <mergeCell ref="A52:B52"/>
-    <mergeCell ref="A65:B65"/>
-    <mergeCell ref="A54:B54"/>
-    <mergeCell ref="A53:B53"/>
-    <mergeCell ref="A55:B55"/>
-    <mergeCell ref="A58:B58"/>
-    <mergeCell ref="A62:B62"/>
-    <mergeCell ref="A56:B56"/>
-    <mergeCell ref="A108:B108"/>
-    <mergeCell ref="A109:B109"/>
-    <mergeCell ref="A110:B110"/>
-    <mergeCell ref="A107:B107"/>
-    <mergeCell ref="A113:B113"/>
-    <mergeCell ref="A112:B112"/>
-    <mergeCell ref="A111:B111"/>
-    <mergeCell ref="A114:B114"/>
-    <mergeCell ref="A195:C196"/>
-    <mergeCell ref="A132:B132"/>
-    <mergeCell ref="A171:B171"/>
-    <mergeCell ref="A133:B133"/>
-    <mergeCell ref="A164:B164"/>
-    <mergeCell ref="A123:B123"/>
-    <mergeCell ref="A124:B124"/>
-    <mergeCell ref="A122:B122"/>
-    <mergeCell ref="A121:B121"/>
-    <mergeCell ref="A115:B115"/>
-    <mergeCell ref="A117:B117"/>
-    <mergeCell ref="A116:B116"/>
-    <mergeCell ref="A10:E12"/>
-    <mergeCell ref="A15:E18"/>
-    <mergeCell ref="A44:B44"/>
-    <mergeCell ref="A25:B25"/>
-    <mergeCell ref="A26:B26"/>
-    <mergeCell ref="A28:B28"/>
-    <mergeCell ref="A40:B40"/>
-    <mergeCell ref="B3:E3"/>
-    <mergeCell ref="B1:E1"/>
-    <mergeCell ref="B2:E2"/>
-    <mergeCell ref="B8:E8"/>
-    <mergeCell ref="A1:A8"/>
-    <mergeCell ref="A48:B48"/>
-    <mergeCell ref="A38:B38"/>
-    <mergeCell ref="A45:B45"/>
-    <mergeCell ref="A49:B49"/>
-    <mergeCell ref="A41:B41"/>
-    <mergeCell ref="A39:B39"/>
     <mergeCell ref="A50:B50"/>
     <mergeCell ref="A91:B91"/>
     <mergeCell ref="A83:B83"/>
@@ -5987,6 +5927,66 @@
     <mergeCell ref="A66:C66"/>
     <mergeCell ref="A67:C67"/>
     <mergeCell ref="A51:B51"/>
+    <mergeCell ref="A48:B48"/>
+    <mergeCell ref="A38:B38"/>
+    <mergeCell ref="A45:B45"/>
+    <mergeCell ref="A49:B49"/>
+    <mergeCell ref="A41:B41"/>
+    <mergeCell ref="A39:B39"/>
+    <mergeCell ref="B3:E3"/>
+    <mergeCell ref="B1:E1"/>
+    <mergeCell ref="B2:E2"/>
+    <mergeCell ref="B8:E8"/>
+    <mergeCell ref="A1:A8"/>
+    <mergeCell ref="A10:E12"/>
+    <mergeCell ref="A15:E18"/>
+    <mergeCell ref="A44:B44"/>
+    <mergeCell ref="A25:B25"/>
+    <mergeCell ref="A26:B26"/>
+    <mergeCell ref="A28:B28"/>
+    <mergeCell ref="A40:B40"/>
+    <mergeCell ref="A114:B114"/>
+    <mergeCell ref="A195:C196"/>
+    <mergeCell ref="A132:B132"/>
+    <mergeCell ref="A171:B171"/>
+    <mergeCell ref="A133:B133"/>
+    <mergeCell ref="A164:B164"/>
+    <mergeCell ref="A123:B123"/>
+    <mergeCell ref="A124:B124"/>
+    <mergeCell ref="A122:B122"/>
+    <mergeCell ref="A121:B121"/>
+    <mergeCell ref="A115:B115"/>
+    <mergeCell ref="A117:B117"/>
+    <mergeCell ref="A116:B116"/>
+    <mergeCell ref="A108:B108"/>
+    <mergeCell ref="A109:B109"/>
+    <mergeCell ref="A110:B110"/>
+    <mergeCell ref="A107:B107"/>
+    <mergeCell ref="A113:B113"/>
+    <mergeCell ref="A112:B112"/>
+    <mergeCell ref="A111:B111"/>
+    <mergeCell ref="A57:B57"/>
+    <mergeCell ref="A52:B52"/>
+    <mergeCell ref="A65:B65"/>
+    <mergeCell ref="A54:B54"/>
+    <mergeCell ref="A53:B53"/>
+    <mergeCell ref="A55:B55"/>
+    <mergeCell ref="A58:B58"/>
+    <mergeCell ref="A62:B62"/>
+    <mergeCell ref="A56:B56"/>
+    <mergeCell ref="A75:B75"/>
+    <mergeCell ref="A80:B80"/>
+    <mergeCell ref="A59:B59"/>
+    <mergeCell ref="A60:B60"/>
+    <mergeCell ref="A95:B95"/>
+    <mergeCell ref="A84:B84"/>
+    <mergeCell ref="A86:B86"/>
+    <mergeCell ref="A87:B87"/>
+    <mergeCell ref="A90:B90"/>
+    <mergeCell ref="A94:B94"/>
+    <mergeCell ref="A68:B68"/>
+    <mergeCell ref="A61:B61"/>
+    <mergeCell ref="A69:B69"/>
   </mergeCells>
   <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup paperSize="3" scale="115" orientation="portrait" r:id="rId1"/>
@@ -6026,27 +6026,27 @@
     <row r="1" spans="1:24" ht="251.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="2"/>
       <c r="B1" s="2"/>
-      <c r="C1" s="388" t="s">
-        <v>468</v>
-      </c>
-      <c r="D1" s="389"/>
-      <c r="E1" s="389"/>
-      <c r="F1" s="389"/>
-      <c r="G1" s="389"/>
-      <c r="H1" s="389"/>
-      <c r="I1" s="389"/>
-      <c r="J1" s="389"/>
-      <c r="K1" s="389"/>
-      <c r="L1" s="389"/>
+      <c r="C1" s="391" t="s">
+        <v>463</v>
+      </c>
+      <c r="D1" s="392"/>
+      <c r="E1" s="392"/>
+      <c r="F1" s="392"/>
+      <c r="G1" s="392"/>
+      <c r="H1" s="392"/>
+      <c r="I1" s="392"/>
+      <c r="J1" s="392"/>
+      <c r="K1" s="392"/>
+      <c r="L1" s="392"/>
       <c r="M1" s="142"/>
-      <c r="N1" s="390" t="s">
+      <c r="N1" s="393" t="s">
         <v>310</v>
       </c>
-      <c r="O1" s="390"/>
-      <c r="P1" s="385">
+      <c r="O1" s="393"/>
+      <c r="P1" s="388">
         <v>30000000</v>
       </c>
-      <c r="Q1" s="385"/>
+      <c r="Q1" s="388"/>
       <c r="R1" s="164"/>
       <c r="S1" s="4"/>
       <c r="T1" s="2"/>
@@ -6060,35 +6060,35 @@
     <row r="2" spans="1:24" ht="34.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="2"/>
       <c r="B2" s="2"/>
-      <c r="C2" s="387" t="s">
+      <c r="C2" s="390" t="s">
         <v>226</v>
       </c>
-      <c r="D2" s="387"/>
-      <c r="E2" s="387"/>
+      <c r="D2" s="390"/>
+      <c r="E2" s="390"/>
       <c r="F2" s="142"/>
-      <c r="G2" s="384">
+      <c r="G2" s="385">
         <f>X2</f>
         <v>27518571.293111999</v>
       </c>
-      <c r="H2" s="384"/>
+      <c r="H2" s="385"/>
       <c r="I2" s="142" t="s">
         <v>274</v>
       </c>
       <c r="J2" s="142"/>
-      <c r="K2" s="384">
+      <c r="K2" s="385">
         <f>W1</f>
         <v>80675963.920000002</v>
       </c>
-      <c r="L2" s="384"/>
+      <c r="L2" s="385"/>
       <c r="M2" s="224"/>
       <c r="N2" s="225" t="s">
         <v>260</v>
       </c>
       <c r="O2" s="224"/>
-      <c r="P2" s="386">
-        <v>0</v>
-      </c>
-      <c r="Q2" s="386"/>
+      <c r="P2" s="389">
+        <v>0</v>
+      </c>
+      <c r="Q2" s="389"/>
       <c r="R2" s="165"/>
       <c r="T2" s="2"/>
       <c r="U2" t="s">
@@ -6100,112 +6100,112 @@
       </c>
     </row>
     <row r="3" spans="1:24" ht="91.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="395" t="str">
+      <c r="A3" s="398" t="str">
         <f>"ATENCIÓN: Si usted abona antes del " &amp; TEXT(RESUMEN!A10,"dd/mm/yyyy") &amp; ", deberá abonar el importe indicado en la columna de color naranja. En caso de abonar con posterioridad a dicha fecha, deberá abonar el monto indicado en la columna de color celeste."</f>
         <v>ATENCIÓN: Si usted abona antes del Primer Vencimiento:  17/08, deberá abonar el importe indicado en la columna de color naranja. En caso de abonar con posterioridad a dicha fecha, deberá abonar el monto indicado en la columna de color celeste.</v>
       </c>
-      <c r="B3" s="396"/>
-      <c r="C3" s="396"/>
-      <c r="D3" s="396"/>
-      <c r="E3" s="396"/>
-      <c r="F3" s="396"/>
-      <c r="G3" s="396"/>
-      <c r="H3" s="396"/>
-      <c r="I3" s="396"/>
-      <c r="J3" s="396"/>
-      <c r="K3" s="396"/>
-      <c r="L3" s="396"/>
-      <c r="M3" s="396"/>
-      <c r="N3" s="396"/>
-      <c r="O3" s="396"/>
-      <c r="P3" s="396"/>
-      <c r="Q3" s="396"/>
-      <c r="R3" s="396"/>
-      <c r="S3" s="396"/>
-      <c r="T3" s="397"/>
+      <c r="B3" s="399"/>
+      <c r="C3" s="399"/>
+      <c r="D3" s="399"/>
+      <c r="E3" s="399"/>
+      <c r="F3" s="399"/>
+      <c r="G3" s="399"/>
+      <c r="H3" s="399"/>
+      <c r="I3" s="399"/>
+      <c r="J3" s="399"/>
+      <c r="K3" s="399"/>
+      <c r="L3" s="399"/>
+      <c r="M3" s="399"/>
+      <c r="N3" s="399"/>
+      <c r="O3" s="399"/>
+      <c r="P3" s="399"/>
+      <c r="Q3" s="399"/>
+      <c r="R3" s="399"/>
+      <c r="S3" s="399"/>
+      <c r="T3" s="400"/>
       <c r="X3" s="37"/>
     </row>
     <row r="4" spans="1:24" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="398" t="s">
-        <v>0</v>
-      </c>
-      <c r="B4" s="400" t="s">
+      <c r="A4" s="401" t="s">
+        <v>0</v>
+      </c>
+      <c r="B4" s="403" t="s">
         <v>1</v>
       </c>
-      <c r="C4" s="400" t="s">
+      <c r="C4" s="403" t="s">
         <v>2</v>
       </c>
-      <c r="D4" s="400" t="s">
+      <c r="D4" s="403" t="s">
         <v>6</v>
       </c>
-      <c r="E4" s="377" t="s">
+      <c r="E4" s="386" t="s">
         <v>181</v>
       </c>
-      <c r="F4" s="400" t="s">
+      <c r="F4" s="403" t="s">
         <v>3</v>
       </c>
-      <c r="G4" s="402" t="s">
+      <c r="G4" s="405" t="s">
         <v>16</v>
       </c>
-      <c r="H4" s="377" t="s">
+      <c r="H4" s="386" t="s">
         <v>232</v>
       </c>
-      <c r="I4" s="377" t="s">
+      <c r="I4" s="386" t="s">
         <v>15</v>
       </c>
-      <c r="J4" s="377"/>
-      <c r="K4" s="377" t="s">
+      <c r="J4" s="386"/>
+      <c r="K4" s="386" t="s">
         <v>182</v>
       </c>
-      <c r="L4" s="377" t="s">
+      <c r="L4" s="386" t="s">
         <v>146</v>
       </c>
-      <c r="M4" s="377" t="s">
+      <c r="M4" s="386" t="s">
         <v>184</v>
       </c>
-      <c r="N4" s="377" t="s">
+      <c r="N4" s="386" t="s">
         <v>183</v>
       </c>
-      <c r="O4" s="377" t="s">
+      <c r="O4" s="386" t="s">
         <v>320</v>
       </c>
-      <c r="P4" s="391" t="s">
+      <c r="P4" s="394" t="s">
         <v>318</v>
       </c>
-      <c r="Q4" s="392"/>
-      <c r="R4" s="391" t="s">
+      <c r="Q4" s="395"/>
+      <c r="R4" s="394" t="s">
         <v>313</v>
       </c>
-      <c r="S4" s="392"/>
-      <c r="T4" s="377" t="s">
+      <c r="S4" s="395"/>
+      <c r="T4" s="386" t="s">
         <v>258</v>
       </c>
       <c r="U4" s="13"/>
     </row>
     <row r="5" spans="1:24" ht="25.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="399"/>
-      <c r="B5" s="401"/>
-      <c r="C5" s="401"/>
-      <c r="D5" s="401"/>
-      <c r="E5" s="378"/>
-      <c r="F5" s="401"/>
-      <c r="G5" s="403"/>
-      <c r="H5" s="378"/>
-      <c r="I5" s="378"/>
-      <c r="J5" s="378"/>
-      <c r="K5" s="378"/>
-      <c r="L5" s="378"/>
-      <c r="M5" s="378"/>
-      <c r="N5" s="378"/>
-      <c r="O5" s="378"/>
-      <c r="P5" s="393" t="str">
+      <c r="A5" s="402"/>
+      <c r="B5" s="404"/>
+      <c r="C5" s="404"/>
+      <c r="D5" s="404"/>
+      <c r="E5" s="387"/>
+      <c r="F5" s="404"/>
+      <c r="G5" s="406"/>
+      <c r="H5" s="387"/>
+      <c r="I5" s="387"/>
+      <c r="J5" s="387"/>
+      <c r="K5" s="387"/>
+      <c r="L5" s="387"/>
+      <c r="M5" s="387"/>
+      <c r="N5" s="387"/>
+      <c r="O5" s="387"/>
+      <c r="P5" s="396" t="str">
         <f>RESUMEN!A10</f>
         <v>Primer Vencimiento:  17/08</v>
       </c>
-      <c r="Q5" s="394"/>
-      <c r="R5" s="393"/>
-      <c r="S5" s="394"/>
-      <c r="T5" s="378"/>
+      <c r="Q5" s="397"/>
+      <c r="R5" s="396"/>
+      <c r="S5" s="397"/>
+      <c r="T5" s="387"/>
     </row>
     <row r="6" spans="1:24" ht="26.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="184"/>
@@ -6258,11 +6258,11 @@
       <c r="O6" s="185">
         <v>0</v>
       </c>
-      <c r="P6" s="379">
+      <c r="P6" s="407">
         <f t="shared" ref="P6:P37" si="2">ROUND(SUM(G6:O6),0) + S6</f>
         <v>759748.01</v>
       </c>
-      <c r="Q6" s="380"/>
+      <c r="Q6" s="408"/>
       <c r="R6" s="226">
         <f t="shared" ref="R6:R37" si="3">ROUND(P6+P6*3.033%,0) + S6</f>
         <v>782791.01</v>
@@ -6328,11 +6328,11 @@
       <c r="O7" s="185">
         <v>0</v>
       </c>
-      <c r="P7" s="381">
+      <c r="P7" s="409">
         <f t="shared" si="2"/>
         <v>3658299.02</v>
       </c>
-      <c r="Q7" s="382"/>
+      <c r="Q7" s="410"/>
       <c r="R7" s="226">
         <f t="shared" si="3"/>
         <v>3769255.02</v>
@@ -6397,11 +6397,11 @@
       <c r="O8" s="185">
         <v>0</v>
       </c>
-      <c r="P8" s="383">
+      <c r="P8" s="378">
         <f t="shared" si="2"/>
         <v>737362.03</v>
       </c>
-      <c r="Q8" s="383"/>
+      <c r="Q8" s="378"/>
       <c r="R8" s="226">
         <f t="shared" si="3"/>
         <v>759726.03</v>
@@ -6470,11 +6470,11 @@
       <c r="O9" s="185">
         <v>0</v>
       </c>
-      <c r="P9" s="383">
+      <c r="P9" s="378">
         <f t="shared" si="2"/>
         <v>3191997.04</v>
       </c>
-      <c r="Q9" s="383"/>
+      <c r="Q9" s="378"/>
       <c r="R9" s="226">
         <f t="shared" si="3"/>
         <v>3288810.04</v>
@@ -6544,11 +6544,11 @@
       <c r="O10" s="185">
         <v>0</v>
       </c>
-      <c r="P10" s="383">
+      <c r="P10" s="378">
         <f t="shared" si="2"/>
         <v>767816.05</v>
       </c>
-      <c r="Q10" s="383"/>
+      <c r="Q10" s="378"/>
       <c r="R10" s="226">
         <f t="shared" si="3"/>
         <v>791104.05</v>
@@ -6615,11 +6615,11 @@
       <c r="O11" s="185">
         <v>0</v>
       </c>
-      <c r="P11" s="383">
+      <c r="P11" s="378">
         <f t="shared" si="2"/>
         <v>751681.06</v>
       </c>
-      <c r="Q11" s="383"/>
+      <c r="Q11" s="378"/>
       <c r="R11" s="226">
         <f t="shared" si="3"/>
         <v>774480.06</v>
@@ -6687,11 +6687,11 @@
       <c r="O12" s="185">
         <v>0</v>
       </c>
-      <c r="P12" s="383">
+      <c r="P12" s="378">
         <f t="shared" si="2"/>
         <v>625812.06999999995</v>
       </c>
-      <c r="Q12" s="383"/>
+      <c r="Q12" s="378"/>
       <c r="R12" s="226">
         <f t="shared" si="3"/>
         <v>644793.06999999995</v>
@@ -6759,11 +6759,11 @@
       <c r="O13" s="185">
         <v>0</v>
       </c>
-      <c r="P13" s="383">
+      <c r="P13" s="378">
         <f t="shared" si="2"/>
         <v>763050.08</v>
       </c>
-      <c r="Q13" s="383"/>
+      <c r="Q13" s="378"/>
       <c r="R13" s="226">
         <f t="shared" si="3"/>
         <v>786193.08</v>
@@ -6831,11 +6831,11 @@
       <c r="O14" s="185">
         <v>0</v>
       </c>
-      <c r="P14" s="383">
+      <c r="P14" s="378">
         <f t="shared" si="2"/>
         <v>759482.09</v>
       </c>
-      <c r="Q14" s="383"/>
+      <c r="Q14" s="378"/>
       <c r="R14" s="226">
         <f t="shared" si="3"/>
         <v>782517.09</v>
@@ -6900,11 +6900,11 @@
       <c r="O15" s="185">
         <v>0</v>
       </c>
-      <c r="P15" s="383">
+      <c r="P15" s="378">
         <f t="shared" si="2"/>
         <v>744528.1</v>
       </c>
-      <c r="Q15" s="383"/>
+      <c r="Q15" s="378"/>
       <c r="R15" s="226">
         <f t="shared" si="3"/>
         <v>767110.1</v>
@@ -6972,11 +6972,11 @@
       <c r="O16" s="185">
         <v>0</v>
       </c>
-      <c r="P16" s="383">
+      <c r="P16" s="378">
         <f t="shared" si="2"/>
         <v>745214.11</v>
       </c>
-      <c r="Q16" s="383"/>
+      <c r="Q16" s="378"/>
       <c r="R16" s="226">
         <f t="shared" si="3"/>
         <v>767816.11</v>
@@ -7045,11 +7045,11 @@
       <c r="O17" s="185">
         <v>0</v>
       </c>
-      <c r="P17" s="383">
+      <c r="P17" s="378">
         <f t="shared" si="2"/>
         <v>4564903.12</v>
       </c>
-      <c r="Q17" s="383"/>
+      <c r="Q17" s="378"/>
       <c r="R17" s="226">
         <f t="shared" si="3"/>
         <v>4703357.12</v>
@@ -7118,11 +7118,11 @@
       <c r="O18" s="185">
         <v>0</v>
       </c>
-      <c r="P18" s="383">
+      <c r="P18" s="378">
         <f t="shared" si="2"/>
         <v>759748.13</v>
       </c>
-      <c r="Q18" s="383"/>
+      <c r="Q18" s="378"/>
       <c r="R18" s="226">
         <f t="shared" si="3"/>
         <v>782791.13</v>
@@ -7185,14 +7185,14 @@
       <c r="N19" s="185">
         <v>0</v>
       </c>
-      <c r="O19" s="423">
+      <c r="O19" s="341">
         <v>223900</v>
       </c>
-      <c r="P19" s="383">
+      <c r="P19" s="378">
         <f t="shared" si="2"/>
         <v>991716.14</v>
       </c>
-      <c r="Q19" s="383"/>
+      <c r="Q19" s="378"/>
       <c r="R19" s="226">
         <f t="shared" si="3"/>
         <v>1021795.14</v>
@@ -7261,11 +7261,11 @@
       <c r="O20" s="185">
         <v>0</v>
       </c>
-      <c r="P20" s="383">
+      <c r="P20" s="378">
         <f t="shared" si="2"/>
         <v>743613.15</v>
       </c>
-      <c r="Q20" s="383"/>
+      <c r="Q20" s="378"/>
       <c r="R20" s="226">
         <f t="shared" si="3"/>
         <v>766167.15</v>
@@ -7334,11 +7334,11 @@
       <c r="O21" s="185">
         <v>0</v>
       </c>
-      <c r="P21" s="383">
+      <c r="P21" s="378">
         <f t="shared" si="2"/>
         <v>759748.16</v>
       </c>
-      <c r="Q21" s="383"/>
+      <c r="Q21" s="378"/>
       <c r="R21" s="226">
         <f t="shared" si="3"/>
         <v>782791.16</v>
@@ -7403,11 +7403,11 @@
       <c r="O22" s="185">
         <v>0</v>
       </c>
-      <c r="P22" s="383">
+      <c r="P22" s="378">
         <f t="shared" si="2"/>
         <v>629697.17000000004</v>
       </c>
-      <c r="Q22" s="383"/>
+      <c r="Q22" s="378"/>
       <c r="R22" s="226">
         <f t="shared" si="3"/>
         <v>648796.17000000004</v>
@@ -7476,11 +7476,11 @@
       <c r="O23" s="185">
         <v>0</v>
       </c>
-      <c r="P23" s="383">
+      <c r="P23" s="378">
         <f t="shared" si="2"/>
         <v>759748.18</v>
       </c>
-      <c r="Q23" s="383"/>
+      <c r="Q23" s="378"/>
       <c r="R23" s="226">
         <f t="shared" si="3"/>
         <v>782791.18</v>
@@ -7549,11 +7549,11 @@
       <c r="O24" s="185">
         <v>0</v>
       </c>
-      <c r="P24" s="383">
+      <c r="P24" s="378">
         <f t="shared" si="2"/>
         <v>767816.19</v>
       </c>
-      <c r="Q24" s="383"/>
+      <c r="Q24" s="378"/>
       <c r="R24" s="226">
         <f t="shared" si="3"/>
         <v>791104.19</v>
@@ -7619,11 +7619,11 @@
       <c r="O25" s="185">
         <v>0</v>
       </c>
-      <c r="P25" s="383">
+      <c r="P25" s="378">
         <f t="shared" si="2"/>
         <v>767816.2</v>
       </c>
-      <c r="Q25" s="383"/>
+      <c r="Q25" s="378"/>
       <c r="R25" s="226">
         <f t="shared" si="3"/>
         <v>791104.2</v>
@@ -7689,11 +7689,11 @@
       <c r="O26" s="185">
         <v>0</v>
       </c>
-      <c r="P26" s="383">
+      <c r="P26" s="378">
         <f t="shared" si="2"/>
         <v>767816.21</v>
       </c>
-      <c r="Q26" s="383"/>
+      <c r="Q26" s="378"/>
       <c r="R26" s="226">
         <f t="shared" si="3"/>
         <v>791104.21</v>
@@ -7764,11 +7764,11 @@
       <c r="O27" s="185">
         <v>0</v>
       </c>
-      <c r="P27" s="383">
+      <c r="P27" s="378">
         <f t="shared" si="2"/>
         <v>745213.22</v>
       </c>
-      <c r="Q27" s="383"/>
+      <c r="Q27" s="378"/>
       <c r="R27" s="226">
         <f t="shared" si="3"/>
         <v>767816.22</v>
@@ -7836,11 +7836,11 @@
       <c r="O28" s="185">
         <v>0</v>
       </c>
-      <c r="P28" s="383">
+      <c r="P28" s="378">
         <f t="shared" si="2"/>
         <v>745264.23</v>
       </c>
-      <c r="Q28" s="383"/>
+      <c r="Q28" s="378"/>
       <c r="R28" s="226">
         <f t="shared" si="3"/>
         <v>767868.23</v>
@@ -7908,11 +7908,11 @@
       <c r="O29" s="185">
         <v>0</v>
       </c>
-      <c r="P29" s="383">
+      <c r="P29" s="378">
         <f t="shared" si="2"/>
         <v>745213.24</v>
       </c>
-      <c r="Q29" s="383"/>
+      <c r="Q29" s="378"/>
       <c r="R29" s="226">
         <f t="shared" si="3"/>
         <v>767816.24</v>
@@ -7981,11 +7981,11 @@
       <c r="O30" s="185">
         <v>0</v>
       </c>
-      <c r="P30" s="383">
+      <c r="P30" s="378">
         <f t="shared" si="2"/>
         <v>775884.25</v>
       </c>
-      <c r="Q30" s="383"/>
+      <c r="Q30" s="378"/>
       <c r="R30" s="226">
         <f t="shared" si="3"/>
         <v>799417.25</v>
@@ -8053,11 +8053,11 @@
       <c r="O31" s="185">
         <v>0</v>
       </c>
-      <c r="P31" s="383">
+      <c r="P31" s="378">
         <f t="shared" si="2"/>
         <v>775884.26</v>
       </c>
-      <c r="Q31" s="383"/>
+      <c r="Q31" s="378"/>
       <c r="R31" s="226">
         <f t="shared" si="3"/>
         <v>799417.26</v>
@@ -8126,11 +8126,11 @@
       <c r="O32" s="185">
         <v>0</v>
       </c>
-      <c r="P32" s="383">
+      <c r="P32" s="378">
         <f t="shared" si="2"/>
         <v>775884.27</v>
       </c>
-      <c r="Q32" s="383"/>
+      <c r="Q32" s="378"/>
       <c r="R32" s="226">
         <f t="shared" si="3"/>
         <v>799417.27</v>
@@ -8195,11 +8195,11 @@
       <c r="O33" s="185">
         <v>0</v>
       </c>
-      <c r="P33" s="383">
+      <c r="P33" s="378">
         <f t="shared" si="2"/>
         <v>728196.28</v>
       </c>
-      <c r="Q33" s="383"/>
+      <c r="Q33" s="378"/>
       <c r="R33" s="226">
         <f t="shared" si="3"/>
         <v>750282.28</v>
@@ -8267,11 +8267,11 @@
       <c r="O34" s="185">
         <v>0</v>
       </c>
-      <c r="P34" s="383">
+      <c r="P34" s="378">
         <f t="shared" si="2"/>
         <v>753043.29</v>
       </c>
-      <c r="Q34" s="383"/>
+      <c r="Q34" s="378"/>
       <c r="R34" s="226">
         <f t="shared" si="3"/>
         <v>775883.29</v>
@@ -8339,11 +8339,11 @@
       <c r="O35" s="185">
         <v>0</v>
       </c>
-      <c r="P35" s="383">
+      <c r="P35" s="378">
         <f t="shared" si="2"/>
         <v>729553.3</v>
       </c>
-      <c r="Q35" s="383"/>
+      <c r="Q35" s="378"/>
       <c r="R35" s="226">
         <f t="shared" si="3"/>
         <v>751681.3</v>
@@ -8409,11 +8409,11 @@
       <c r="O36" s="185">
         <v>0</v>
       </c>
-      <c r="P36" s="383">
+      <c r="P36" s="378">
         <f t="shared" si="2"/>
         <v>2403472.31</v>
       </c>
-      <c r="Q36" s="383"/>
+      <c r="Q36" s="378"/>
       <c r="R36" s="226">
         <f t="shared" si="3"/>
         <v>2476370.31</v>
@@ -8482,11 +8482,11 @@
       <c r="O37" s="185">
         <v>0</v>
       </c>
-      <c r="P37" s="383">
+      <c r="P37" s="378">
         <f t="shared" si="2"/>
         <v>618525.31999999995</v>
       </c>
-      <c r="Q37" s="383"/>
+      <c r="Q37" s="378"/>
       <c r="R37" s="226">
         <f t="shared" si="3"/>
         <v>637285.31999999995</v>
@@ -8551,11 +8551,11 @@
       <c r="O38" s="185">
         <v>0</v>
       </c>
-      <c r="P38" s="383">
+      <c r="P38" s="378">
         <f t="shared" ref="P38:P69" si="13">ROUND(SUM(G38:O38),0) + S38</f>
         <v>751681.33</v>
       </c>
-      <c r="Q38" s="383"/>
+      <c r="Q38" s="378"/>
       <c r="R38" s="226">
         <f t="shared" ref="R38:R69" si="14">ROUND(P38+P38*3.033%,0) + S38</f>
         <v>774480.33</v>
@@ -8619,11 +8619,11 @@
       <c r="O39" s="185">
         <v>0</v>
       </c>
-      <c r="P39" s="383">
+      <c r="P39" s="378">
         <f t="shared" si="13"/>
         <v>2448435.34</v>
       </c>
-      <c r="Q39" s="383"/>
+      <c r="Q39" s="378"/>
       <c r="R39" s="226">
         <f t="shared" si="14"/>
         <v>2522696.34</v>
@@ -8693,11 +8693,11 @@
       <c r="O40" s="185">
         <v>0</v>
       </c>
-      <c r="P40" s="383">
+      <c r="P40" s="378">
         <f t="shared" si="13"/>
         <v>759748.35</v>
       </c>
-      <c r="Q40" s="383"/>
+      <c r="Q40" s="378"/>
       <c r="R40" s="226">
         <f t="shared" si="14"/>
         <v>782792.35</v>
@@ -8766,11 +8766,11 @@
       <c r="O41" s="185">
         <v>0</v>
       </c>
-      <c r="P41" s="383">
+      <c r="P41" s="378">
         <f t="shared" si="13"/>
         <v>720580.36</v>
       </c>
-      <c r="Q41" s="383"/>
+      <c r="Q41" s="378"/>
       <c r="R41" s="226">
         <f t="shared" si="14"/>
         <v>742436.36</v>
@@ -8838,11 +8838,11 @@
       <c r="O42" s="185">
         <v>0</v>
       </c>
-      <c r="P42" s="383">
+      <c r="P42" s="378">
         <f t="shared" si="13"/>
         <v>751681.37</v>
       </c>
-      <c r="Q42" s="383"/>
+      <c r="Q42" s="378"/>
       <c r="R42" s="226">
         <f t="shared" si="14"/>
         <v>774480.37</v>
@@ -8910,11 +8910,11 @@
       <c r="O43" s="185">
         <v>0</v>
       </c>
-      <c r="P43" s="383">
+      <c r="P43" s="378">
         <f t="shared" si="13"/>
         <v>751681.38</v>
       </c>
-      <c r="Q43" s="383"/>
+      <c r="Q43" s="378"/>
       <c r="R43" s="226">
         <f t="shared" si="14"/>
         <v>774480.38</v>
@@ -8983,11 +8983,11 @@
       <c r="O44" s="185">
         <v>0</v>
       </c>
-      <c r="P44" s="383">
+      <c r="P44" s="378">
         <f t="shared" si="13"/>
         <v>751543.39</v>
       </c>
-      <c r="Q44" s="383"/>
+      <c r="Q44" s="378"/>
       <c r="R44" s="226">
         <f t="shared" si="14"/>
         <v>774338.39</v>
@@ -9056,11 +9056,11 @@
       <c r="O45" s="185">
         <v>0</v>
       </c>
-      <c r="P45" s="383">
+      <c r="P45" s="378">
         <f t="shared" si="13"/>
         <v>751681.4</v>
       </c>
-      <c r="Q45" s="383"/>
+      <c r="Q45" s="378"/>
       <c r="R45" s="226">
         <f t="shared" si="14"/>
         <v>774480.4</v>
@@ -9126,11 +9126,11 @@
       <c r="O46" s="185">
         <v>0</v>
       </c>
-      <c r="P46" s="383">
+      <c r="P46" s="378">
         <f t="shared" si="13"/>
         <v>729553.41</v>
       </c>
-      <c r="Q46" s="383"/>
+      <c r="Q46" s="378"/>
       <c r="R46" s="226">
         <f t="shared" si="14"/>
         <v>751681.41</v>
@@ -9200,11 +9200,11 @@
       <c r="O47" s="185">
         <v>0</v>
       </c>
-      <c r="P47" s="383">
+      <c r="P47" s="378">
         <f t="shared" si="13"/>
         <v>751681.42</v>
       </c>
-      <c r="Q47" s="383"/>
+      <c r="Q47" s="378"/>
       <c r="R47" s="226">
         <f t="shared" si="14"/>
         <v>774480.42</v>
@@ -9274,11 +9274,11 @@
       <c r="O48" s="185">
         <v>0</v>
       </c>
-      <c r="P48" s="383">
+      <c r="P48" s="378">
         <f t="shared" si="13"/>
         <v>679072.43</v>
       </c>
-      <c r="Q48" s="383"/>
+      <c r="Q48" s="378"/>
       <c r="R48" s="226">
         <f t="shared" si="14"/>
         <v>699669.43</v>
@@ -9344,11 +9344,11 @@
       <c r="O49" s="185">
         <v>0</v>
       </c>
-      <c r="P49" s="383">
+      <c r="P49" s="378">
         <f t="shared" si="13"/>
         <v>692960.44</v>
       </c>
-      <c r="Q49" s="383"/>
+      <c r="Q49" s="378"/>
       <c r="R49" s="226">
         <f t="shared" si="14"/>
         <v>713978.44</v>
@@ -9417,11 +9417,11 @@
       <c r="O50" s="185">
         <v>0</v>
       </c>
-      <c r="P50" s="383">
+      <c r="P50" s="378">
         <f t="shared" si="13"/>
         <v>1654405.45</v>
       </c>
-      <c r="Q50" s="383"/>
+      <c r="Q50" s="378"/>
       <c r="R50" s="226">
         <f t="shared" si="14"/>
         <v>1704584.45</v>
@@ -9487,11 +9487,11 @@
       <c r="O51" s="185">
         <v>0</v>
       </c>
-      <c r="P51" s="383">
+      <c r="P51" s="378">
         <f t="shared" si="13"/>
         <v>1451354.46</v>
       </c>
-      <c r="Q51" s="383"/>
+      <c r="Q51" s="378"/>
       <c r="R51" s="226">
         <f t="shared" si="14"/>
         <v>1495374.46</v>
@@ -9558,11 +9558,11 @@
       <c r="O52" s="185">
         <v>0</v>
       </c>
-      <c r="P52" s="383">
+      <c r="P52" s="378">
         <f t="shared" si="13"/>
         <v>3148838.47</v>
       </c>
-      <c r="Q52" s="383"/>
+      <c r="Q52" s="378"/>
       <c r="R52" s="226">
         <f t="shared" si="14"/>
         <v>3244343.47</v>
@@ -9633,11 +9633,11 @@
       <c r="O53" s="185">
         <v>0</v>
       </c>
-      <c r="P53" s="383">
+      <c r="P53" s="378">
         <f t="shared" si="13"/>
         <v>1187332.48</v>
       </c>
-      <c r="Q53" s="383"/>
+      <c r="Q53" s="378"/>
       <c r="R53" s="226">
         <f t="shared" si="14"/>
         <v>1223344.48</v>
@@ -9705,11 +9705,11 @@
       <c r="O54" s="185">
         <v>0</v>
       </c>
-      <c r="P54" s="383">
+      <c r="P54" s="378">
         <f t="shared" si="13"/>
         <v>751681.49</v>
       </c>
-      <c r="Q54" s="383"/>
+      <c r="Q54" s="378"/>
       <c r="R54" s="226">
         <f t="shared" si="14"/>
         <v>774480.49</v>
@@ -9779,11 +9779,11 @@
       <c r="O55" s="185">
         <v>0</v>
       </c>
-      <c r="P55" s="383">
+      <c r="P55" s="378">
         <f t="shared" si="13"/>
         <v>751681.5</v>
       </c>
-      <c r="Q55" s="383"/>
+      <c r="Q55" s="378"/>
       <c r="R55" s="226">
         <f t="shared" si="14"/>
         <v>774480.5</v>
@@ -9853,11 +9853,11 @@
       <c r="O56" s="185">
         <v>0</v>
       </c>
-      <c r="P56" s="383">
+      <c r="P56" s="378">
         <f t="shared" si="13"/>
         <v>751681.51</v>
       </c>
-      <c r="Q56" s="383"/>
+      <c r="Q56" s="378"/>
       <c r="R56" s="226">
         <f t="shared" si="14"/>
         <v>774480.51</v>
@@ -9927,11 +9927,11 @@
       <c r="O57" s="185">
         <v>0</v>
       </c>
-      <c r="P57" s="383">
+      <c r="P57" s="378">
         <f t="shared" si="13"/>
         <v>759748.52</v>
       </c>
-      <c r="Q57" s="383"/>
+      <c r="Q57" s="378"/>
       <c r="R57" s="226">
         <f t="shared" si="14"/>
         <v>782792.52</v>
@@ -9998,11 +9998,11 @@
       <c r="O58" s="185">
         <v>0</v>
       </c>
-      <c r="P58" s="383">
+      <c r="P58" s="378">
         <f t="shared" si="13"/>
         <v>4746223.53</v>
       </c>
-      <c r="Q58" s="383"/>
+      <c r="Q58" s="378"/>
       <c r="R58" s="226">
         <f t="shared" si="14"/>
         <v>4890176.53</v>
@@ -10069,11 +10069,11 @@
       <c r="O59" s="185">
         <v>0</v>
       </c>
-      <c r="P59" s="383">
+      <c r="P59" s="378">
         <f t="shared" si="13"/>
         <v>751681.54</v>
       </c>
-      <c r="Q59" s="383"/>
+      <c r="Q59" s="378"/>
       <c r="R59" s="226">
         <f t="shared" si="14"/>
         <v>774480.54</v>
@@ -10142,11 +10142,11 @@
       <c r="O60" s="185">
         <v>0</v>
       </c>
-      <c r="P60" s="383">
+      <c r="P60" s="378">
         <f t="shared" si="13"/>
         <v>729553.55</v>
       </c>
-      <c r="Q60" s="383"/>
+      <c r="Q60" s="378"/>
       <c r="R60" s="226">
         <f t="shared" si="14"/>
         <v>751681.55</v>
@@ -10216,11 +10216,11 @@
       <c r="O61" s="185">
         <v>0</v>
       </c>
-      <c r="P61" s="383">
+      <c r="P61" s="378">
         <f t="shared" si="13"/>
         <v>751681.56</v>
       </c>
-      <c r="Q61" s="383"/>
+      <c r="Q61" s="378"/>
       <c r="R61" s="226">
         <f t="shared" si="14"/>
         <v>774480.56</v>
@@ -10290,11 +10290,11 @@
       <c r="O62" s="185">
         <v>0</v>
       </c>
-      <c r="P62" s="383">
+      <c r="P62" s="378">
         <f t="shared" si="13"/>
         <v>751681.57</v>
       </c>
-      <c r="Q62" s="383"/>
+      <c r="Q62" s="378"/>
       <c r="R62" s="226">
         <f t="shared" si="14"/>
         <v>774480.57</v>
@@ -10360,11 +10360,11 @@
       <c r="O63" s="185">
         <v>0</v>
       </c>
-      <c r="P63" s="383">
+      <c r="P63" s="378">
         <f t="shared" si="13"/>
         <v>729553.58</v>
       </c>
-      <c r="Q63" s="383"/>
+      <c r="Q63" s="378"/>
       <c r="R63" s="226">
         <f t="shared" si="14"/>
         <v>751681.58</v>
@@ -10430,11 +10430,11 @@
       <c r="O64" s="185">
         <v>0</v>
       </c>
-      <c r="P64" s="383">
+      <c r="P64" s="378">
         <f t="shared" si="13"/>
         <v>718232.59</v>
       </c>
-      <c r="Q64" s="383"/>
+      <c r="Q64" s="378"/>
       <c r="R64" s="226">
         <f t="shared" si="14"/>
         <v>740017.59</v>
@@ -10503,11 +10503,11 @@
       <c r="O65" s="185">
         <v>0</v>
       </c>
-      <c r="P65" s="383">
+      <c r="P65" s="378">
         <f t="shared" si="13"/>
         <v>751232.6</v>
       </c>
-      <c r="Q65" s="383"/>
+      <c r="Q65" s="378"/>
       <c r="R65" s="226">
         <f t="shared" si="14"/>
         <v>774017.6</v>
@@ -10576,11 +10576,11 @@
       <c r="O66" s="185">
         <v>0</v>
       </c>
-      <c r="P66" s="383">
+      <c r="P66" s="378">
         <f t="shared" si="13"/>
         <v>751624.61</v>
       </c>
-      <c r="Q66" s="383"/>
+      <c r="Q66" s="378"/>
       <c r="R66" s="226">
         <f t="shared" si="14"/>
         <v>774421.61</v>
@@ -10649,11 +10649,11 @@
       <c r="O67" s="185">
         <v>0</v>
       </c>
-      <c r="P67" s="383">
+      <c r="P67" s="378">
         <f t="shared" si="13"/>
         <v>1529226.62</v>
       </c>
-      <c r="Q67" s="383"/>
+      <c r="Q67" s="378"/>
       <c r="R67" s="226">
         <f t="shared" si="14"/>
         <v>1575608.62</v>
@@ -10719,11 +10719,11 @@
       <c r="O68" s="185">
         <v>0</v>
       </c>
-      <c r="P68" s="383">
+      <c r="P68" s="378">
         <f t="shared" si="13"/>
         <v>728882.63</v>
       </c>
-      <c r="Q68" s="383"/>
+      <c r="Q68" s="378"/>
       <c r="R68" s="226">
         <f t="shared" si="14"/>
         <v>750990.63</v>
@@ -10793,11 +10793,11 @@
       <c r="O69" s="185">
         <v>0</v>
       </c>
-      <c r="P69" s="383">
+      <c r="P69" s="378">
         <f t="shared" si="13"/>
         <v>751681.64</v>
       </c>
-      <c r="Q69" s="383"/>
+      <c r="Q69" s="378"/>
       <c r="R69" s="226">
         <f t="shared" si="14"/>
         <v>774480.64</v>
@@ -10867,11 +10867,11 @@
       <c r="O70" s="185">
         <v>0</v>
       </c>
-      <c r="P70" s="383">
+      <c r="P70" s="378">
         <f t="shared" ref="P70:P101" si="21">ROUND(SUM(G70:O70),0) + S70</f>
         <v>751681.65</v>
       </c>
-      <c r="Q70" s="383"/>
+      <c r="Q70" s="378"/>
       <c r="R70" s="226">
         <f t="shared" ref="R70:R101" si="22">ROUND(P70+P70*3.033%,0) + S70</f>
         <v>774480.65</v>
@@ -10938,11 +10938,11 @@
       <c r="O71" s="185">
         <v>0</v>
       </c>
-      <c r="P71" s="383">
+      <c r="P71" s="378">
         <f t="shared" si="21"/>
         <v>751681.66</v>
       </c>
-      <c r="Q71" s="383"/>
+      <c r="Q71" s="378"/>
       <c r="R71" s="226">
         <f t="shared" si="22"/>
         <v>774480.66</v>
@@ -11011,11 +11011,11 @@
       <c r="O72" s="185">
         <v>0</v>
       </c>
-      <c r="P72" s="383">
+      <c r="P72" s="378">
         <f t="shared" si="21"/>
         <v>1527073.67</v>
       </c>
-      <c r="Q72" s="383"/>
+      <c r="Q72" s="378"/>
       <c r="R72" s="226">
         <f t="shared" si="22"/>
         <v>1573390.67</v>
@@ -11082,11 +11082,11 @@
       <c r="O73" s="185">
         <v>0</v>
       </c>
-      <c r="P73" s="383">
+      <c r="P73" s="378">
         <f t="shared" si="21"/>
         <v>4973793.68</v>
       </c>
-      <c r="Q73" s="383"/>
+      <c r="Q73" s="378"/>
       <c r="R73" s="226">
         <f t="shared" si="22"/>
         <v>5124649.68</v>
@@ -11152,11 +11152,11 @@
       <c r="O74" s="185">
         <v>0</v>
       </c>
-      <c r="P74" s="383">
+      <c r="P74" s="378">
         <f t="shared" si="21"/>
         <v>679072.69</v>
       </c>
-      <c r="Q74" s="383"/>
+      <c r="Q74" s="378"/>
       <c r="R74" s="226">
         <f t="shared" si="22"/>
         <v>699669.69</v>
@@ -11224,11 +11224,11 @@
       <c r="O75" s="185">
         <v>0</v>
       </c>
-      <c r="P75" s="383">
+      <c r="P75" s="378">
         <f t="shared" si="21"/>
         <v>1759862.7</v>
       </c>
-      <c r="Q75" s="383"/>
+      <c r="Q75" s="378"/>
       <c r="R75" s="226">
         <f t="shared" si="22"/>
         <v>1813239.7</v>
@@ -11296,11 +11296,11 @@
       <c r="O76" s="185">
         <v>0</v>
       </c>
-      <c r="P76" s="383">
+      <c r="P76" s="378">
         <f t="shared" si="21"/>
         <v>1469187.71</v>
       </c>
-      <c r="Q76" s="383"/>
+      <c r="Q76" s="378"/>
       <c r="R76" s="226">
         <f t="shared" si="22"/>
         <v>1513748.71</v>
@@ -11368,11 +11368,11 @@
       <c r="O77" s="185">
         <v>0</v>
       </c>
-      <c r="P77" s="383">
+      <c r="P77" s="378">
         <f t="shared" si="21"/>
         <v>689767.72</v>
       </c>
-      <c r="Q77" s="383"/>
+      <c r="Q77" s="378"/>
       <c r="R77" s="226">
         <f t="shared" si="22"/>
         <v>710688.72</v>
@@ -11440,11 +11440,11 @@
       <c r="O78" s="185">
         <v>0</v>
       </c>
-      <c r="P78" s="383">
+      <c r="P78" s="378">
         <f t="shared" si="21"/>
         <v>711063.73</v>
       </c>
-      <c r="Q78" s="383"/>
+      <c r="Q78" s="378"/>
       <c r="R78" s="226">
         <f t="shared" si="22"/>
         <v>732630.73</v>
@@ -11510,11 +11510,11 @@
       <c r="O79" s="185">
         <v>0</v>
       </c>
-      <c r="P79" s="383">
+      <c r="P79" s="378">
         <f t="shared" si="21"/>
         <v>743613.74</v>
       </c>
-      <c r="Q79" s="383"/>
+      <c r="Q79" s="378"/>
       <c r="R79" s="226">
         <f t="shared" si="22"/>
         <v>766168.74</v>
@@ -11579,11 +11579,11 @@
       <c r="O80" s="185">
         <v>0</v>
       </c>
-      <c r="P80" s="383">
+      <c r="P80" s="378">
         <f t="shared" si="21"/>
         <v>719410.75</v>
       </c>
-      <c r="Q80" s="383"/>
+      <c r="Q80" s="378"/>
       <c r="R80" s="226">
         <f t="shared" si="22"/>
         <v>741230.75</v>
@@ -11652,11 +11652,11 @@
       <c r="O81" s="185">
         <v>0</v>
       </c>
-      <c r="P81" s="383">
+      <c r="P81" s="378">
         <f t="shared" si="21"/>
         <v>751681.76</v>
       </c>
-      <c r="Q81" s="383"/>
+      <c r="Q81" s="378"/>
       <c r="R81" s="226">
         <f t="shared" si="22"/>
         <v>774480.76</v>
@@ -11721,11 +11721,11 @@
       <c r="O82" s="185">
         <v>0</v>
       </c>
-      <c r="P82" s="383">
+      <c r="P82" s="378">
         <f t="shared" si="21"/>
         <v>880410.77</v>
       </c>
-      <c r="Q82" s="383"/>
+      <c r="Q82" s="378"/>
       <c r="R82" s="226">
         <f t="shared" si="22"/>
         <v>907114.77</v>
@@ -11793,11 +11793,11 @@
       <c r="O83" s="185">
         <v>0</v>
       </c>
-      <c r="P83" s="383">
+      <c r="P83" s="378">
         <f t="shared" si="21"/>
         <v>752933.78</v>
       </c>
-      <c r="Q83" s="383"/>
+      <c r="Q83" s="378"/>
       <c r="R83" s="226">
         <f t="shared" si="22"/>
         <v>775770.78</v>
@@ -11866,11 +11866,11 @@
       <c r="O84" s="185">
         <v>0</v>
       </c>
-      <c r="P84" s="383">
+      <c r="P84" s="378">
         <f t="shared" si="21"/>
         <v>1526975.79</v>
       </c>
-      <c r="Q84" s="383"/>
+      <c r="Q84" s="378"/>
       <c r="R84" s="226">
         <f t="shared" si="22"/>
         <v>1573289.79</v>
@@ -11942,11 +11942,11 @@
       <c r="O85" s="185">
         <v>0</v>
       </c>
-      <c r="P85" s="383">
+      <c r="P85" s="378">
         <f t="shared" si="21"/>
         <v>751681.8</v>
       </c>
-      <c r="Q85" s="383"/>
+      <c r="Q85" s="378"/>
       <c r="R85" s="226">
         <f t="shared" si="22"/>
         <v>774480.8</v>
@@ -12015,11 +12015,11 @@
       <c r="O86" s="185">
         <v>0</v>
       </c>
-      <c r="P86" s="383">
+      <c r="P86" s="378">
         <f t="shared" si="21"/>
         <v>751681.81</v>
       </c>
-      <c r="Q86" s="383"/>
+      <c r="Q86" s="378"/>
       <c r="R86" s="226">
         <f t="shared" si="22"/>
         <v>774480.81</v>
@@ -12088,11 +12088,11 @@
         <f>I87/2</f>
         <v>169419.524232</v>
       </c>
-      <c r="P87" s="383">
+      <c r="P87" s="378">
         <f t="shared" si="21"/>
         <v>1626958.82</v>
       </c>
-      <c r="Q87" s="383"/>
+      <c r="Q87" s="378"/>
       <c r="R87" s="226">
         <f t="shared" si="22"/>
         <v>1676304.82</v>
@@ -12161,11 +12161,11 @@
       <c r="O88" s="185">
         <v>0</v>
       </c>
-      <c r="P88" s="383">
+      <c r="P88" s="378">
         <f t="shared" si="21"/>
         <v>775884.83</v>
       </c>
-      <c r="Q88" s="383"/>
+      <c r="Q88" s="378"/>
       <c r="R88" s="226">
         <f t="shared" si="22"/>
         <v>799417.83</v>
@@ -12230,11 +12230,11 @@
       <c r="O89" s="185">
         <v>0</v>
       </c>
-      <c r="P89" s="383">
+      <c r="P89" s="378">
         <f t="shared" si="21"/>
         <v>775884.84</v>
       </c>
-      <c r="Q89" s="383"/>
+      <c r="Q89" s="378"/>
       <c r="R89" s="226">
         <f t="shared" si="22"/>
         <v>799417.84</v>
@@ -12300,11 +12300,11 @@
       <c r="O90" s="185">
         <v>0</v>
       </c>
-      <c r="P90" s="383">
+      <c r="P90" s="378">
         <f t="shared" si="21"/>
         <v>775884.85</v>
       </c>
-      <c r="Q90" s="383"/>
+      <c r="Q90" s="378"/>
       <c r="R90" s="226">
         <f t="shared" si="22"/>
         <v>799417.85</v>
@@ -12375,11 +12375,11 @@
         <f>2239*100</f>
         <v>223900</v>
       </c>
-      <c r="P91" s="383">
+      <c r="P91" s="378">
         <f t="shared" si="21"/>
         <v>1394226.86</v>
       </c>
-      <c r="Q91" s="383"/>
+      <c r="Q91" s="378"/>
       <c r="R91" s="226">
         <f t="shared" si="22"/>
         <v>1436514.86</v>
@@ -12448,11 +12448,11 @@
       <c r="O92" s="185">
         <v>0</v>
       </c>
-      <c r="P92" s="383">
+      <c r="P92" s="378">
         <f t="shared" si="21"/>
         <v>775884.87</v>
       </c>
-      <c r="Q92" s="383"/>
+      <c r="Q92" s="378"/>
       <c r="R92" s="226">
         <f t="shared" si="22"/>
         <v>799417.87</v>
@@ -12517,11 +12517,11 @@
       <c r="O93" s="185">
         <v>0</v>
       </c>
-      <c r="P93" s="383">
+      <c r="P93" s="378">
         <f t="shared" si="21"/>
         <v>767654.88</v>
       </c>
-      <c r="Q93" s="383"/>
+      <c r="Q93" s="378"/>
       <c r="R93" s="226">
         <f t="shared" si="22"/>
         <v>790938.88</v>
@@ -12587,11 +12587,11 @@
       <c r="O94" s="185">
         <v>0</v>
       </c>
-      <c r="P94" s="383">
+      <c r="P94" s="378">
         <f t="shared" si="21"/>
         <v>775884.89</v>
       </c>
-      <c r="Q94" s="383"/>
+      <c r="Q94" s="378"/>
       <c r="R94" s="226">
         <f t="shared" si="22"/>
         <v>799417.89</v>
@@ -12660,11 +12660,11 @@
       <c r="O95" s="185">
         <v>0</v>
       </c>
-      <c r="P95" s="383">
+      <c r="P95" s="378">
         <f t="shared" si="21"/>
         <v>2097847.9</v>
       </c>
-      <c r="Q95" s="383"/>
+      <c r="Q95" s="378"/>
       <c r="R95" s="226">
         <f t="shared" si="22"/>
         <v>2161476.9</v>
@@ -12733,11 +12733,11 @@
       <c r="O96" s="185">
         <v>0</v>
       </c>
-      <c r="P96" s="383">
+      <c r="P96" s="378">
         <f t="shared" si="21"/>
         <v>775884.91</v>
       </c>
-      <c r="Q96" s="383"/>
+      <c r="Q96" s="378"/>
       <c r="R96" s="226">
         <f t="shared" si="22"/>
         <v>799417.91</v>
@@ -12806,11 +12806,11 @@
       <c r="O97" s="185">
         <v>0</v>
       </c>
-      <c r="P97" s="383">
+      <c r="P97" s="378">
         <f t="shared" si="21"/>
         <v>775884.92</v>
       </c>
-      <c r="Q97" s="383"/>
+      <c r="Q97" s="378"/>
       <c r="R97" s="226">
         <f t="shared" si="22"/>
         <v>799418.92</v>
@@ -12878,11 +12878,11 @@
       <c r="O98" s="185">
         <v>0</v>
       </c>
-      <c r="P98" s="383">
+      <c r="P98" s="378">
         <f t="shared" si="21"/>
         <v>1558282.93</v>
       </c>
-      <c r="Q98" s="383"/>
+      <c r="Q98" s="378"/>
       <c r="R98" s="226">
         <f t="shared" si="22"/>
         <v>1605546.93</v>
@@ -12951,11 +12951,11 @@
       <c r="O99" s="185">
         <v>0</v>
       </c>
-      <c r="P99" s="383">
+      <c r="P99" s="378">
         <f t="shared" si="21"/>
         <v>775884.94</v>
       </c>
-      <c r="Q99" s="383"/>
+      <c r="Q99" s="378"/>
       <c r="R99" s="226">
         <f t="shared" si="22"/>
         <v>799418.94</v>
@@ -13023,11 +13023,11 @@
       <c r="O100" s="185">
         <v>0</v>
       </c>
-      <c r="P100" s="383">
+      <c r="P100" s="378">
         <f t="shared" si="21"/>
         <v>5461803.9500000002</v>
       </c>
-      <c r="Q100" s="383"/>
+      <c r="Q100" s="378"/>
       <c r="R100" s="226">
         <f t="shared" si="22"/>
         <v>5627460.9500000002</v>
@@ -13092,11 +13092,11 @@
       <c r="O101" s="185">
         <v>0</v>
       </c>
-      <c r="P101" s="383">
+      <c r="P101" s="378">
         <f t="shared" si="21"/>
         <v>751813.96</v>
       </c>
-      <c r="Q101" s="383"/>
+      <c r="Q101" s="378"/>
       <c r="R101" s="226">
         <f t="shared" si="22"/>
         <v>774616.96</v>
@@ -13165,11 +13165,11 @@
       <c r="O102" s="185">
         <v>0</v>
       </c>
-      <c r="P102" s="383">
+      <c r="P102" s="378">
         <f t="shared" ref="P102:P133" si="30">ROUND(SUM(G102:O102),0) + S102</f>
         <v>775884.97</v>
       </c>
-      <c r="Q102" s="383"/>
+      <c r="Q102" s="378"/>
       <c r="R102" s="226">
         <f t="shared" ref="R102:R133" si="31">ROUND(P102+P102*3.033%,0) + S102</f>
         <v>799418.97</v>
@@ -13238,11 +13238,11 @@
       <c r="O103" s="185">
         <v>0</v>
       </c>
-      <c r="P103" s="383">
+      <c r="P103" s="378">
         <f t="shared" si="30"/>
         <v>775884.98</v>
       </c>
-      <c r="Q103" s="383"/>
+      <c r="Q103" s="378"/>
       <c r="R103" s="226">
         <f t="shared" si="31"/>
         <v>799418.98</v>
@@ -13308,11 +13308,11 @@
       <c r="O104" s="185">
         <v>0</v>
       </c>
-      <c r="P104" s="383">
+      <c r="P104" s="378">
         <f t="shared" si="30"/>
         <v>775884.99</v>
       </c>
-      <c r="Q104" s="383"/>
+      <c r="Q104" s="378"/>
       <c r="R104" s="226">
         <f t="shared" si="31"/>
         <v>799418.99</v>
@@ -13381,11 +13381,11 @@
       <c r="O105" s="185">
         <v>0</v>
       </c>
-      <c r="P105" s="383">
+      <c r="P105" s="378">
         <f t="shared" si="30"/>
         <v>775885</v>
       </c>
-      <c r="Q105" s="383"/>
+      <c r="Q105" s="378"/>
       <c r="R105" s="226">
         <f t="shared" si="31"/>
         <v>799419</v>
@@ -13451,11 +13451,11 @@
       <c r="O106" s="185">
         <v>0</v>
       </c>
-      <c r="P106" s="383">
+      <c r="P106" s="378">
         <f t="shared" si="30"/>
         <v>775885.01</v>
       </c>
-      <c r="Q106" s="383"/>
+      <c r="Q106" s="378"/>
       <c r="R106" s="226">
         <f t="shared" si="31"/>
         <v>799419.01</v>
@@ -13520,11 +13520,11 @@
       <c r="O107" s="185">
         <v>0</v>
       </c>
-      <c r="P107" s="383">
+      <c r="P107" s="378">
         <f t="shared" si="30"/>
         <v>764543.02</v>
       </c>
-      <c r="Q107" s="383"/>
+      <c r="Q107" s="378"/>
       <c r="R107" s="226">
         <f t="shared" si="31"/>
         <v>787733.02</v>
@@ -13590,11 +13590,11 @@
       <c r="O108" s="185">
         <v>0</v>
       </c>
-      <c r="P108" s="383">
+      <c r="P108" s="378">
         <f t="shared" si="30"/>
         <v>3224447.03</v>
       </c>
-      <c r="Q108" s="383"/>
+      <c r="Q108" s="378"/>
       <c r="R108" s="226">
         <f t="shared" si="31"/>
         <v>3322246.03</v>
@@ -13660,11 +13660,11 @@
       <c r="O109" s="185">
         <v>0</v>
       </c>
-      <c r="P109" s="383">
+      <c r="P109" s="378">
         <f t="shared" si="30"/>
         <v>767817.04</v>
       </c>
-      <c r="Q109" s="383"/>
+      <c r="Q109" s="378"/>
       <c r="R109" s="226">
         <f t="shared" si="31"/>
         <v>791106.04</v>
@@ -13733,11 +13733,11 @@
       <c r="O110" s="185">
         <v>0</v>
       </c>
-      <c r="P110" s="383">
+      <c r="P110" s="378">
         <f t="shared" si="30"/>
         <v>727479.05</v>
       </c>
-      <c r="Q110" s="383"/>
+      <c r="Q110" s="378"/>
       <c r="R110" s="226">
         <f t="shared" si="31"/>
         <v>749544.05</v>
@@ -13805,11 +13805,11 @@
       <c r="O111" s="185">
         <v>0</v>
       </c>
-      <c r="P111" s="383">
+      <c r="P111" s="378">
         <f t="shared" si="30"/>
         <v>3618180.06</v>
       </c>
-      <c r="Q111" s="383"/>
+      <c r="Q111" s="378"/>
       <c r="R111" s="226">
         <f t="shared" si="31"/>
         <v>3727920.06</v>
@@ -13878,11 +13878,11 @@
       <c r="O112" s="185">
         <v>0</v>
       </c>
-      <c r="P112" s="383">
+      <c r="P112" s="378">
         <f t="shared" si="30"/>
         <v>743614.07</v>
       </c>
-      <c r="Q112" s="383"/>
+      <c r="Q112" s="378"/>
       <c r="R112" s="226">
         <f t="shared" si="31"/>
         <v>766169.07</v>
@@ -13951,11 +13951,11 @@
       <c r="O113" s="185">
         <v>0</v>
       </c>
-      <c r="P113" s="383">
+      <c r="P113" s="378">
         <f t="shared" si="30"/>
         <v>743614.08</v>
       </c>
-      <c r="Q113" s="383"/>
+      <c r="Q113" s="378"/>
       <c r="R113" s="226">
         <f t="shared" si="31"/>
         <v>766169.08</v>
@@ -14020,11 +14020,11 @@
       <c r="O114" s="185">
         <v>0</v>
       </c>
-      <c r="P114" s="383">
+      <c r="P114" s="378">
         <f t="shared" si="30"/>
         <v>1469510.09</v>
       </c>
-      <c r="Q114" s="383"/>
+      <c r="Q114" s="378"/>
       <c r="R114" s="226">
         <f t="shared" si="31"/>
         <v>1514081.09</v>
@@ -14092,11 +14092,11 @@
       <c r="O115" s="185">
         <v>0</v>
       </c>
-      <c r="P115" s="383">
+      <c r="P115" s="378">
         <f t="shared" si="30"/>
         <v>1540074.1</v>
       </c>
-      <c r="Q115" s="383"/>
+      <c r="Q115" s="378"/>
       <c r="R115" s="226">
         <f t="shared" si="31"/>
         <v>1586786.1</v>
@@ -14166,11 +14166,11 @@
       <c r="O116" s="185">
         <v>0</v>
       </c>
-      <c r="P116" s="383">
+      <c r="P116" s="378">
         <f t="shared" si="30"/>
         <v>751682.11</v>
       </c>
-      <c r="Q116" s="383"/>
+      <c r="Q116" s="378"/>
       <c r="R116" s="226">
         <f t="shared" si="31"/>
         <v>774482.11</v>
@@ -14235,11 +14235,11 @@
       <c r="O117" s="185">
         <v>0</v>
       </c>
-      <c r="P117" s="383">
+      <c r="P117" s="378">
         <f t="shared" si="30"/>
         <v>1525913.12</v>
       </c>
-      <c r="Q117" s="383"/>
+      <c r="Q117" s="378"/>
       <c r="R117" s="226">
         <f t="shared" si="31"/>
         <v>1572195.12</v>
@@ -14307,11 +14307,11 @@
       <c r="O118" s="185">
         <v>0</v>
       </c>
-      <c r="P118" s="383">
+      <c r="P118" s="378">
         <f t="shared" si="30"/>
         <v>745213.13</v>
       </c>
-      <c r="Q118" s="383"/>
+      <c r="Q118" s="378"/>
       <c r="R118" s="226">
         <f t="shared" si="31"/>
         <v>767816.13</v>
@@ -14377,11 +14377,11 @@
       <c r="O119" s="185">
         <v>0</v>
       </c>
-      <c r="P119" s="383">
+      <c r="P119" s="378">
         <f t="shared" si="30"/>
         <v>751682.14</v>
       </c>
-      <c r="Q119" s="383"/>
+      <c r="Q119" s="378"/>
       <c r="R119" s="226">
         <f t="shared" si="31"/>
         <v>774482.14</v>
@@ -14447,11 +14447,11 @@
       <c r="O120" s="185">
         <v>0</v>
       </c>
-      <c r="P120" s="383">
+      <c r="P120" s="378">
         <f t="shared" si="30"/>
         <v>904966.15</v>
       </c>
-      <c r="Q120" s="383"/>
+      <c r="Q120" s="378"/>
       <c r="R120" s="226">
         <f t="shared" si="31"/>
         <v>932415.15</v>
@@ -14520,11 +14520,11 @@
       <c r="O121" s="185">
         <v>0</v>
       </c>
-      <c r="P121" s="383">
+      <c r="P121" s="378">
         <f t="shared" si="30"/>
         <v>831345.16</v>
       </c>
-      <c r="Q121" s="383"/>
+      <c r="Q121" s="378"/>
       <c r="R121" s="226">
         <f t="shared" si="31"/>
         <v>856561.16</v>
@@ -14590,11 +14590,11 @@
       <c r="O122" s="185">
         <v>0</v>
       </c>
-      <c r="P122" s="383">
+      <c r="P122" s="378">
         <f t="shared" si="30"/>
         <v>880763.17</v>
       </c>
-      <c r="Q122" s="383"/>
+      <c r="Q122" s="378"/>
       <c r="R122" s="226">
         <f t="shared" si="31"/>
         <v>907478.17</v>
@@ -14663,11 +14663,11 @@
       <c r="O123" s="185">
         <v>0</v>
       </c>
-      <c r="P123" s="383">
+      <c r="P123" s="378">
         <f t="shared" si="30"/>
         <v>855800.18</v>
       </c>
-      <c r="Q123" s="383"/>
+      <c r="Q123" s="378"/>
       <c r="R123" s="226">
         <f t="shared" si="31"/>
         <v>881758.18</v>
@@ -14735,11 +14735,11 @@
       <c r="O124" s="185">
         <v>0</v>
       </c>
-      <c r="P124" s="383">
+      <c r="P124" s="378">
         <f t="shared" si="30"/>
         <v>824214.19</v>
       </c>
-      <c r="Q124" s="383"/>
+      <c r="Q124" s="378"/>
       <c r="R124" s="226">
         <f t="shared" si="31"/>
         <v>849214.19</v>
@@ -14808,11 +14808,11 @@
       <c r="O125" s="185">
         <v>0</v>
       </c>
-      <c r="P125" s="383">
+      <c r="P125" s="378">
         <f t="shared" si="30"/>
         <v>759749.2</v>
       </c>
-      <c r="Q125" s="383"/>
+      <c r="Q125" s="378"/>
       <c r="R125" s="226">
         <f t="shared" si="31"/>
         <v>782793.2</v>
@@ -14881,11 +14881,11 @@
       <c r="O126" s="185">
         <v>0</v>
       </c>
-      <c r="P126" s="383">
+      <c r="P126" s="378">
         <f t="shared" si="30"/>
         <v>759749.21</v>
       </c>
-      <c r="Q126" s="383"/>
+      <c r="Q126" s="378"/>
       <c r="R126" s="226">
         <f t="shared" si="31"/>
         <v>782793.21</v>
@@ -14954,11 +14954,11 @@
       <c r="O127" s="185">
         <v>0</v>
       </c>
-      <c r="P127" s="383">
+      <c r="P127" s="378">
         <f t="shared" si="30"/>
         <v>759749.22</v>
       </c>
-      <c r="Q127" s="383"/>
+      <c r="Q127" s="378"/>
       <c r="R127" s="226">
         <f t="shared" si="31"/>
         <v>782793.22</v>
@@ -15024,11 +15024,11 @@
       <c r="O128" s="185">
         <v>0</v>
       </c>
-      <c r="P128" s="383">
+      <c r="P128" s="378">
         <f t="shared" si="30"/>
         <v>759749.23</v>
       </c>
-      <c r="Q128" s="383"/>
+      <c r="Q128" s="378"/>
       <c r="R128" s="226">
         <f t="shared" si="31"/>
         <v>782793.23</v>
@@ -15096,11 +15096,11 @@
       <c r="O129" s="185">
         <v>0</v>
       </c>
-      <c r="P129" s="383">
+      <c r="P129" s="378">
         <f t="shared" si="30"/>
         <v>737383.24</v>
       </c>
-      <c r="Q129" s="383"/>
+      <c r="Q129" s="378"/>
       <c r="R129" s="226">
         <f t="shared" si="31"/>
         <v>759749.24</v>
@@ -15166,11 +15166,11 @@
       <c r="O130" s="185">
         <v>0</v>
       </c>
-      <c r="P130" s="383">
+      <c r="P130" s="378">
         <f t="shared" si="30"/>
         <v>759749.25</v>
       </c>
-      <c r="Q130" s="383"/>
+      <c r="Q130" s="378"/>
       <c r="R130" s="226">
         <f t="shared" si="31"/>
         <v>782793.25</v>
@@ -15239,11 +15239,11 @@
       <c r="O131" s="185">
         <v>0</v>
       </c>
-      <c r="P131" s="383">
+      <c r="P131" s="378">
         <f t="shared" si="30"/>
         <v>759749.26</v>
       </c>
-      <c r="Q131" s="383"/>
+      <c r="Q131" s="378"/>
       <c r="R131" s="226">
         <f t="shared" si="31"/>
         <v>782793.26</v>
@@ -15309,11 +15309,11 @@
       <c r="O132" s="185">
         <v>0</v>
       </c>
-      <c r="P132" s="383">
+      <c r="P132" s="378">
         <f t="shared" si="30"/>
         <v>840425.27</v>
       </c>
-      <c r="Q132" s="383"/>
+      <c r="Q132" s="378"/>
       <c r="R132" s="226">
         <f t="shared" si="31"/>
         <v>865916.27</v>
@@ -15382,11 +15382,11 @@
       <c r="O133" s="185">
         <v>0</v>
       </c>
-      <c r="P133" s="383">
+      <c r="P133" s="378">
         <f t="shared" si="30"/>
         <v>880763.28</v>
       </c>
-      <c r="Q133" s="383"/>
+      <c r="Q133" s="378"/>
       <c r="R133" s="226">
         <f t="shared" si="31"/>
         <v>907478.28</v>
@@ -15452,11 +15452,11 @@
       <c r="O134" s="185">
         <v>0</v>
       </c>
-      <c r="P134" s="383">
+      <c r="P134" s="378">
         <f t="shared" ref="P134:P144" si="37">ROUND(SUM(G134:O134),0) + S134</f>
         <v>880763.29</v>
       </c>
-      <c r="Q134" s="383"/>
+      <c r="Q134" s="378"/>
       <c r="R134" s="226">
         <f t="shared" ref="R134:R144" si="38">ROUND(P134+P134*3.033%,0) + S134</f>
         <v>907478.29</v>
@@ -15524,11 +15524,11 @@
       <c r="O135" s="185">
         <v>0</v>
       </c>
-      <c r="P135" s="383">
+      <c r="P135" s="378">
         <f t="shared" si="37"/>
         <v>848330.3</v>
       </c>
-      <c r="Q135" s="383"/>
+      <c r="Q135" s="378"/>
       <c r="R135" s="226">
         <f t="shared" si="38"/>
         <v>874061.3</v>
@@ -15597,11 +15597,11 @@
       <c r="O136" s="185">
         <v>0</v>
       </c>
-      <c r="P136" s="383">
+      <c r="P136" s="378">
         <f t="shared" si="37"/>
         <v>880763.31</v>
       </c>
-      <c r="Q136" s="383"/>
+      <c r="Q136" s="378"/>
       <c r="R136" s="226">
         <f t="shared" si="38"/>
         <v>907478.31</v>
@@ -15670,11 +15670,11 @@
       <c r="O137" s="185">
         <v>0</v>
       </c>
-      <c r="P137" s="383">
+      <c r="P137" s="378">
         <f t="shared" si="37"/>
         <v>872696.31999999995</v>
       </c>
-      <c r="Q137" s="383"/>
+      <c r="Q137" s="378"/>
       <c r="R137" s="226">
         <f t="shared" si="38"/>
         <v>899166.32</v>
@@ -15743,11 +15743,11 @@
       <c r="O138" s="185">
         <v>0</v>
       </c>
-      <c r="P138" s="383">
+      <c r="P138" s="378">
         <f t="shared" si="37"/>
         <v>904966.33</v>
       </c>
-      <c r="Q138" s="383"/>
+      <c r="Q138" s="378"/>
       <c r="R138" s="226">
         <f t="shared" si="38"/>
         <v>932415.33</v>
@@ -15815,11 +15815,11 @@
       <c r="O139" s="185">
         <v>0</v>
       </c>
-      <c r="P139" s="383">
+      <c r="P139" s="378">
         <f t="shared" si="37"/>
         <v>792194.34</v>
       </c>
-      <c r="Q139" s="383"/>
+      <c r="Q139" s="378"/>
       <c r="R139" s="226">
         <f t="shared" si="38"/>
         <v>816223.34</v>
@@ -15887,11 +15887,11 @@
       <c r="O140" s="185">
         <v>0</v>
       </c>
-      <c r="P140" s="383">
+      <c r="P140" s="378">
         <f t="shared" si="37"/>
         <v>854834.35</v>
       </c>
-      <c r="Q140" s="383"/>
+      <c r="Q140" s="378"/>
       <c r="R140" s="226">
         <f t="shared" si="38"/>
         <v>880762.35</v>
@@ -15960,11 +15960,11 @@
       <c r="O141" s="185">
         <v>0</v>
       </c>
-      <c r="P141" s="383">
+      <c r="P141" s="378">
         <f t="shared" si="37"/>
         <v>888831.36</v>
       </c>
-      <c r="Q141" s="383"/>
+      <c r="Q141" s="378"/>
       <c r="R141" s="226">
         <f t="shared" si="38"/>
         <v>915791.35999999999</v>
@@ -16033,11 +16033,11 @@
       <c r="O142" s="185">
         <v>0</v>
       </c>
-      <c r="P142" s="383">
+      <c r="P142" s="378">
         <f t="shared" si="37"/>
         <v>824290.37</v>
       </c>
-      <c r="Q142" s="383"/>
+      <c r="Q142" s="378"/>
       <c r="R142" s="226">
         <f t="shared" si="38"/>
         <v>849292.37</v>
@@ -16102,11 +16102,11 @@
       <c r="O143" s="185">
         <v>0</v>
       </c>
-      <c r="P143" s="383">
+      <c r="P143" s="378">
         <f t="shared" si="37"/>
         <v>879189.38</v>
       </c>
-      <c r="Q143" s="383"/>
+      <c r="Q143" s="378"/>
       <c r="R143" s="226">
         <f t="shared" si="38"/>
         <v>905856.38</v>
@@ -16174,11 +16174,11 @@
       <c r="O144" s="185">
         <v>0</v>
       </c>
-      <c r="P144" s="383">
+      <c r="P144" s="378">
         <f t="shared" si="37"/>
         <v>2193265.39</v>
       </c>
-      <c r="Q144" s="383"/>
+      <c r="Q144" s="378"/>
       <c r="R144" s="226">
         <f t="shared" si="38"/>
         <v>2259788.39</v>
@@ -16224,8 +16224,8 @@
       <c r="O145" s="185">
         <v>0</v>
       </c>
-      <c r="P145" s="383"/>
-      <c r="Q145" s="383"/>
+      <c r="P145" s="378"/>
+      <c r="Q145" s="378"/>
       <c r="R145" s="227"/>
       <c r="S145" s="13">
         <f t="shared" si="39"/>
@@ -16265,8 +16265,8 @@
       <c r="O146" s="185">
         <v>0</v>
       </c>
-      <c r="P146" s="383"/>
-      <c r="Q146" s="383"/>
+      <c r="P146" s="378"/>
+      <c r="Q146" s="378"/>
       <c r="R146" s="227"/>
       <c r="S146" s="13">
         <f t="shared" si="39"/>
@@ -16299,8 +16299,8 @@
       <c r="O147" s="185">
         <v>0</v>
       </c>
-      <c r="P147" s="383"/>
-      <c r="Q147" s="383"/>
+      <c r="P147" s="378"/>
+      <c r="Q147" s="378"/>
       <c r="R147" s="227"/>
       <c r="S147" s="13">
         <f t="shared" si="39"/>
@@ -16333,8 +16333,8 @@
       <c r="O148" s="185">
         <v>0</v>
       </c>
-      <c r="P148" s="383"/>
-      <c r="Q148" s="383"/>
+      <c r="P148" s="378"/>
+      <c r="Q148" s="378"/>
       <c r="R148" s="227"/>
       <c r="S148" s="13">
         <f t="shared" si="39"/>
@@ -16396,11 +16396,11 @@
       <c r="O149" s="185">
         <v>0</v>
       </c>
-      <c r="P149" s="383">
+      <c r="P149" s="378">
         <f t="shared" ref="P149:P158" si="47">ROUND(SUM(G149:O149),0) + S149</f>
         <v>695209.46</v>
       </c>
-      <c r="Q149" s="383"/>
+      <c r="Q149" s="378"/>
       <c r="R149" s="226">
         <f t="shared" ref="R149:R158" si="48">ROUND(P149+P149*3.033%,0) + S149</f>
         <v>716296.46</v>
@@ -16463,11 +16463,11 @@
       <c r="O150" s="185">
         <v>0</v>
       </c>
-      <c r="P150" s="383">
+      <c r="P150" s="378">
         <f t="shared" si="47"/>
         <v>1139411.55</v>
       </c>
-      <c r="Q150" s="383"/>
+      <c r="Q150" s="378"/>
       <c r="R150" s="226">
         <f t="shared" si="48"/>
         <v>1173971.55</v>
@@ -16535,11 +16535,11 @@
       <c r="O151" s="185">
         <v>0</v>
       </c>
-      <c r="P151" s="383">
+      <c r="P151" s="378">
         <f t="shared" si="47"/>
         <v>759749.58</v>
       </c>
-      <c r="Q151" s="383"/>
+      <c r="Q151" s="378"/>
       <c r="R151" s="226">
         <f t="shared" si="48"/>
         <v>782794.58</v>
@@ -16604,11 +16604,11 @@
       <c r="O152" s="185">
         <v>0</v>
       </c>
-      <c r="P152" s="383">
+      <c r="P152" s="378">
         <f t="shared" si="47"/>
         <v>759749.59</v>
       </c>
-      <c r="Q152" s="383"/>
+      <c r="Q152" s="378"/>
       <c r="R152" s="226">
         <f t="shared" si="48"/>
         <v>782794.59</v>
@@ -16673,11 +16673,11 @@
       <c r="O153" s="185">
         <v>0</v>
       </c>
-      <c r="P153" s="383">
+      <c r="P153" s="378">
         <f t="shared" si="47"/>
         <v>759749.63</v>
       </c>
-      <c r="Q153" s="383"/>
+      <c r="Q153" s="378"/>
       <c r="R153" s="226">
         <f t="shared" si="48"/>
         <v>782794.63</v>
@@ -16742,11 +16742,11 @@
       <c r="O154" s="185">
         <v>0</v>
       </c>
-      <c r="P154" s="383">
+      <c r="P154" s="378">
         <f t="shared" si="47"/>
         <v>743614.68</v>
       </c>
-      <c r="Q154" s="383"/>
+      <c r="Q154" s="378"/>
       <c r="R154" s="226">
         <f t="shared" si="48"/>
         <v>766170.68</v>
@@ -16810,11 +16810,11 @@
       <c r="O155" s="185">
         <v>0</v>
       </c>
-      <c r="P155" s="383">
+      <c r="P155" s="378">
         <f t="shared" si="47"/>
         <v>737382.73</v>
       </c>
-      <c r="Q155" s="383"/>
+      <c r="Q155" s="378"/>
       <c r="R155" s="226">
         <f t="shared" si="48"/>
         <v>759749.73</v>
@@ -16881,11 +16881,11 @@
       <c r="O156" s="185">
         <v>0</v>
       </c>
-      <c r="P156" s="383">
+      <c r="P156" s="378">
         <f t="shared" si="47"/>
         <v>737382.75</v>
       </c>
-      <c r="Q156" s="383"/>
+      <c r="Q156" s="378"/>
       <c r="R156" s="226">
         <f t="shared" si="48"/>
         <v>759749.75</v>
@@ -16953,11 +16953,11 @@
       <c r="O157" s="185">
         <v>0</v>
       </c>
-      <c r="P157" s="383">
+      <c r="P157" s="378">
         <f t="shared" si="47"/>
         <v>759749.76</v>
       </c>
-      <c r="Q157" s="383"/>
+      <c r="Q157" s="378"/>
       <c r="R157" s="226">
         <f t="shared" si="48"/>
         <v>782794.76</v>
@@ -17021,11 +17021,11 @@
       <c r="O158" s="185">
         <v>0</v>
       </c>
-      <c r="P158" s="383">
+      <c r="P158" s="378">
         <f t="shared" si="47"/>
         <v>760897.04</v>
       </c>
-      <c r="Q158" s="383"/>
+      <c r="Q158" s="378"/>
       <c r="R158" s="226">
         <f t="shared" si="48"/>
         <v>783977.04</v>
@@ -17058,8 +17058,8 @@
       <c r="M159" s="20"/>
       <c r="N159" s="20"/>
       <c r="O159" s="66"/>
-      <c r="P159" s="408"/>
-      <c r="Q159" s="408"/>
+      <c r="P159" s="383"/>
+      <c r="Q159" s="383"/>
       <c r="R159" s="163"/>
       <c r="S159" s="13"/>
       <c r="T159" s="1"/>
@@ -17080,8 +17080,8 @@
       <c r="M160" s="174"/>
       <c r="N160" s="174"/>
       <c r="O160" s="223"/>
-      <c r="P160" s="409"/>
-      <c r="Q160" s="409"/>
+      <c r="P160" s="384"/>
+      <c r="Q160" s="384"/>
       <c r="R160" s="166"/>
       <c r="S160" s="13"/>
       <c r="T160" s="175"/>
@@ -17135,264 +17135,198 @@
         <f t="shared" si="51"/>
         <v>617219.524232</v>
       </c>
-      <c r="P161" s="406">
+      <c r="P161" s="381">
         <f>SUM(P6:P160)</f>
         <v>160799642.07000002</v>
       </c>
-      <c r="Q161" s="407"/>
+      <c r="Q161" s="382"/>
       <c r="R161" s="167">
         <f>SUM(R6:R160)</f>
         <v>165676810.06999999</v>
       </c>
-      <c r="S161" s="406"/>
-      <c r="T161" s="407"/>
+      <c r="S161" s="381"/>
+      <c r="T161" s="382"/>
     </row>
     <row r="162" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B162" s="404" t="s">
+      <c r="B162" s="379" t="s">
         <v>314</v>
       </c>
-      <c r="C162" s="404"/>
-      <c r="D162" s="404"/>
-      <c r="E162" s="404"/>
-      <c r="F162" s="404"/>
-      <c r="G162" s="404"/>
-      <c r="H162" s="404"/>
-      <c r="I162" s="404"/>
-      <c r="J162" s="404"/>
-      <c r="K162" s="404"/>
-      <c r="L162" s="404"/>
-      <c r="M162" s="404"/>
-      <c r="N162" s="404"/>
-      <c r="O162" s="404"/>
-      <c r="P162" s="404"/>
-      <c r="Q162" s="404"/>
-      <c r="R162" s="404"/>
-      <c r="S162" s="404"/>
-      <c r="T162" s="404"/>
+      <c r="C162" s="379"/>
+      <c r="D162" s="379"/>
+      <c r="E162" s="379"/>
+      <c r="F162" s="379"/>
+      <c r="G162" s="379"/>
+      <c r="H162" s="379"/>
+      <c r="I162" s="379"/>
+      <c r="J162" s="379"/>
+      <c r="K162" s="379"/>
+      <c r="L162" s="379"/>
+      <c r="M162" s="379"/>
+      <c r="N162" s="379"/>
+      <c r="O162" s="379"/>
+      <c r="P162" s="379"/>
+      <c r="Q162" s="379"/>
+      <c r="R162" s="379"/>
+      <c r="S162" s="379"/>
+      <c r="T162" s="379"/>
     </row>
     <row r="163" spans="1:20" ht="49.7" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B163" s="405"/>
-      <c r="C163" s="405"/>
-      <c r="D163" s="405"/>
-      <c r="E163" s="405"/>
-      <c r="F163" s="405"/>
-      <c r="G163" s="405"/>
-      <c r="H163" s="405"/>
-      <c r="I163" s="405"/>
-      <c r="J163" s="405"/>
-      <c r="K163" s="405"/>
-      <c r="L163" s="405"/>
-      <c r="M163" s="405"/>
-      <c r="N163" s="405"/>
-      <c r="O163" s="405"/>
-      <c r="P163" s="405"/>
-      <c r="Q163" s="405"/>
-      <c r="R163" s="405"/>
-      <c r="S163" s="405"/>
-      <c r="T163" s="405"/>
+      <c r="B163" s="380"/>
+      <c r="C163" s="380"/>
+      <c r="D163" s="380"/>
+      <c r="E163" s="380"/>
+      <c r="F163" s="380"/>
+      <c r="G163" s="380"/>
+      <c r="H163" s="380"/>
+      <c r="I163" s="380"/>
+      <c r="J163" s="380"/>
+      <c r="K163" s="380"/>
+      <c r="L163" s="380"/>
+      <c r="M163" s="380"/>
+      <c r="N163" s="380"/>
+      <c r="O163" s="380"/>
+      <c r="P163" s="380"/>
+      <c r="Q163" s="380"/>
+      <c r="R163" s="380"/>
+      <c r="S163" s="380"/>
+      <c r="T163" s="380"/>
     </row>
     <row r="164" spans="1:20" ht="13.7" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B164" s="405" t="s">
+      <c r="B164" s="380" t="s">
         <v>259</v>
       </c>
-      <c r="C164" s="405"/>
-      <c r="D164" s="405"/>
-      <c r="E164" s="405"/>
-      <c r="F164" s="405"/>
-      <c r="G164" s="405"/>
-      <c r="H164" s="405"/>
-      <c r="I164" s="405"/>
-      <c r="J164" s="405"/>
-      <c r="K164" s="405"/>
-      <c r="L164" s="405"/>
-      <c r="M164" s="405"/>
-      <c r="N164" s="405"/>
-      <c r="O164" s="405"/>
-      <c r="P164" s="405"/>
-      <c r="Q164" s="405"/>
-      <c r="R164" s="405"/>
-      <c r="S164" s="405"/>
-      <c r="T164" s="405"/>
+      <c r="C164" s="380"/>
+      <c r="D164" s="380"/>
+      <c r="E164" s="380"/>
+      <c r="F164" s="380"/>
+      <c r="G164" s="380"/>
+      <c r="H164" s="380"/>
+      <c r="I164" s="380"/>
+      <c r="J164" s="380"/>
+      <c r="K164" s="380"/>
+      <c r="L164" s="380"/>
+      <c r="M164" s="380"/>
+      <c r="N164" s="380"/>
+      <c r="O164" s="380"/>
+      <c r="P164" s="380"/>
+      <c r="Q164" s="380"/>
+      <c r="R164" s="380"/>
+      <c r="S164" s="380"/>
+      <c r="T164" s="380"/>
     </row>
     <row r="165" spans="1:20" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B165" s="405"/>
-      <c r="C165" s="405"/>
-      <c r="D165" s="405"/>
-      <c r="E165" s="405"/>
-      <c r="F165" s="405"/>
-      <c r="G165" s="405"/>
-      <c r="H165" s="405"/>
-      <c r="I165" s="405"/>
-      <c r="J165" s="405"/>
-      <c r="K165" s="405"/>
-      <c r="L165" s="405"/>
-      <c r="M165" s="405"/>
-      <c r="N165" s="405"/>
-      <c r="O165" s="405"/>
-      <c r="P165" s="405"/>
-      <c r="Q165" s="405"/>
-      <c r="R165" s="405"/>
-      <c r="S165" s="405"/>
-      <c r="T165" s="405"/>
+      <c r="B165" s="380"/>
+      <c r="C165" s="380"/>
+      <c r="D165" s="380"/>
+      <c r="E165" s="380"/>
+      <c r="F165" s="380"/>
+      <c r="G165" s="380"/>
+      <c r="H165" s="380"/>
+      <c r="I165" s="380"/>
+      <c r="J165" s="380"/>
+      <c r="K165" s="380"/>
+      <c r="L165" s="380"/>
+      <c r="M165" s="380"/>
+      <c r="N165" s="380"/>
+      <c r="O165" s="380"/>
+      <c r="P165" s="380"/>
+      <c r="Q165" s="380"/>
+      <c r="R165" s="380"/>
+      <c r="S165" s="380"/>
+      <c r="T165" s="380"/>
     </row>
     <row r="166" spans="1:20" ht="3.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B166" s="405"/>
-      <c r="C166" s="405"/>
-      <c r="D166" s="405"/>
-      <c r="E166" s="405"/>
-      <c r="F166" s="405"/>
-      <c r="G166" s="405"/>
-      <c r="H166" s="405"/>
-      <c r="I166" s="405"/>
-      <c r="J166" s="405"/>
-      <c r="K166" s="405"/>
-      <c r="L166" s="405"/>
-      <c r="M166" s="405"/>
-      <c r="N166" s="405"/>
-      <c r="O166" s="405"/>
-      <c r="P166" s="405"/>
-      <c r="Q166" s="405"/>
-      <c r="R166" s="405"/>
-      <c r="S166" s="405"/>
-      <c r="T166" s="405"/>
+      <c r="B166" s="380"/>
+      <c r="C166" s="380"/>
+      <c r="D166" s="380"/>
+      <c r="E166" s="380"/>
+      <c r="F166" s="380"/>
+      <c r="G166" s="380"/>
+      <c r="H166" s="380"/>
+      <c r="I166" s="380"/>
+      <c r="J166" s="380"/>
+      <c r="K166" s="380"/>
+      <c r="L166" s="380"/>
+      <c r="M166" s="380"/>
+      <c r="N166" s="380"/>
+      <c r="O166" s="380"/>
+      <c r="P166" s="380"/>
+      <c r="Q166" s="380"/>
+      <c r="R166" s="380"/>
+      <c r="S166" s="380"/>
+      <c r="T166" s="380"/>
     </row>
     <row r="167" spans="1:20" ht="128.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B167" s="405"/>
-      <c r="C167" s="405"/>
-      <c r="D167" s="405"/>
-      <c r="E167" s="405"/>
-      <c r="F167" s="405"/>
-      <c r="G167" s="405"/>
-      <c r="H167" s="405"/>
-      <c r="I167" s="405"/>
-      <c r="J167" s="405"/>
-      <c r="K167" s="405"/>
-      <c r="L167" s="405"/>
-      <c r="M167" s="405"/>
-      <c r="N167" s="405"/>
-      <c r="O167" s="405"/>
-      <c r="P167" s="405"/>
-      <c r="Q167" s="405"/>
-      <c r="R167" s="405"/>
-      <c r="S167" s="405"/>
-      <c r="T167" s="405"/>
+      <c r="B167" s="380"/>
+      <c r="C167" s="380"/>
+      <c r="D167" s="380"/>
+      <c r="E167" s="380"/>
+      <c r="F167" s="380"/>
+      <c r="G167" s="380"/>
+      <c r="H167" s="380"/>
+      <c r="I167" s="380"/>
+      <c r="J167" s="380"/>
+      <c r="K167" s="380"/>
+      <c r="L167" s="380"/>
+      <c r="M167" s="380"/>
+      <c r="N167" s="380"/>
+      <c r="O167" s="380"/>
+      <c r="P167" s="380"/>
+      <c r="Q167" s="380"/>
+      <c r="R167" s="380"/>
+      <c r="S167" s="380"/>
+      <c r="T167" s="380"/>
     </row>
   </sheetData>
   <mergeCells count="186">
-    <mergeCell ref="P146:Q146"/>
-    <mergeCell ref="P147:Q147"/>
-    <mergeCell ref="P148:Q148"/>
-    <mergeCell ref="P149:Q149"/>
-    <mergeCell ref="P151:Q151"/>
-    <mergeCell ref="P141:Q141"/>
-    <mergeCell ref="P142:Q142"/>
-    <mergeCell ref="P143:Q143"/>
-    <mergeCell ref="P144:Q144"/>
-    <mergeCell ref="P145:Q145"/>
-    <mergeCell ref="P150:Q150"/>
-    <mergeCell ref="B162:T163"/>
-    <mergeCell ref="B164:T167"/>
-    <mergeCell ref="P157:Q157"/>
-    <mergeCell ref="P158:Q158"/>
-    <mergeCell ref="P161:Q161"/>
-    <mergeCell ref="P159:Q159"/>
-    <mergeCell ref="P160:Q160"/>
-    <mergeCell ref="P152:Q152"/>
-    <mergeCell ref="P153:Q153"/>
-    <mergeCell ref="P154:Q154"/>
-    <mergeCell ref="P155:Q155"/>
-    <mergeCell ref="P156:Q156"/>
-    <mergeCell ref="S161:T161"/>
-    <mergeCell ref="P136:Q136"/>
-    <mergeCell ref="P137:Q137"/>
-    <mergeCell ref="P138:Q138"/>
-    <mergeCell ref="P139:Q139"/>
-    <mergeCell ref="P140:Q140"/>
-    <mergeCell ref="P131:Q131"/>
-    <mergeCell ref="P132:Q132"/>
-    <mergeCell ref="P133:Q133"/>
-    <mergeCell ref="P134:Q134"/>
-    <mergeCell ref="P135:Q135"/>
-    <mergeCell ref="P126:Q126"/>
-    <mergeCell ref="P127:Q127"/>
-    <mergeCell ref="P128:Q128"/>
-    <mergeCell ref="P129:Q129"/>
-    <mergeCell ref="P130:Q130"/>
-    <mergeCell ref="P121:Q121"/>
-    <mergeCell ref="P122:Q122"/>
-    <mergeCell ref="P123:Q123"/>
-    <mergeCell ref="P124:Q124"/>
-    <mergeCell ref="P125:Q125"/>
-    <mergeCell ref="P116:Q116"/>
-    <mergeCell ref="P117:Q117"/>
-    <mergeCell ref="P118:Q118"/>
-    <mergeCell ref="P119:Q119"/>
-    <mergeCell ref="P120:Q120"/>
-    <mergeCell ref="P111:Q111"/>
-    <mergeCell ref="P112:Q112"/>
-    <mergeCell ref="P113:Q113"/>
-    <mergeCell ref="P114:Q114"/>
-    <mergeCell ref="P115:Q115"/>
-    <mergeCell ref="P106:Q106"/>
-    <mergeCell ref="P107:Q107"/>
-    <mergeCell ref="P108:Q108"/>
-    <mergeCell ref="P109:Q109"/>
-    <mergeCell ref="P110:Q110"/>
-    <mergeCell ref="P101:Q101"/>
-    <mergeCell ref="P102:Q102"/>
-    <mergeCell ref="P103:Q103"/>
-    <mergeCell ref="P104:Q104"/>
-    <mergeCell ref="P105:Q105"/>
-    <mergeCell ref="P96:Q96"/>
-    <mergeCell ref="P97:Q97"/>
-    <mergeCell ref="P98:Q98"/>
-    <mergeCell ref="P99:Q99"/>
-    <mergeCell ref="P100:Q100"/>
-    <mergeCell ref="P91:Q91"/>
-    <mergeCell ref="P92:Q92"/>
-    <mergeCell ref="P93:Q93"/>
-    <mergeCell ref="P94:Q94"/>
-    <mergeCell ref="P95:Q95"/>
-    <mergeCell ref="P86:Q86"/>
-    <mergeCell ref="P87:Q87"/>
-    <mergeCell ref="P88:Q88"/>
-    <mergeCell ref="P89:Q89"/>
-    <mergeCell ref="P90:Q90"/>
-    <mergeCell ref="P81:Q81"/>
-    <mergeCell ref="P82:Q82"/>
-    <mergeCell ref="P83:Q83"/>
-    <mergeCell ref="P84:Q84"/>
-    <mergeCell ref="P85:Q85"/>
-    <mergeCell ref="P76:Q76"/>
-    <mergeCell ref="P77:Q77"/>
-    <mergeCell ref="P78:Q78"/>
-    <mergeCell ref="P79:Q79"/>
-    <mergeCell ref="P80:Q80"/>
-    <mergeCell ref="P71:Q71"/>
-    <mergeCell ref="P72:Q72"/>
-    <mergeCell ref="P73:Q73"/>
-    <mergeCell ref="P74:Q74"/>
-    <mergeCell ref="P75:Q75"/>
-    <mergeCell ref="P66:Q66"/>
-    <mergeCell ref="P67:Q67"/>
-    <mergeCell ref="P68:Q68"/>
-    <mergeCell ref="P69:Q69"/>
-    <mergeCell ref="P70:Q70"/>
-    <mergeCell ref="P61:Q61"/>
-    <mergeCell ref="P62:Q62"/>
-    <mergeCell ref="P63:Q63"/>
-    <mergeCell ref="P64:Q64"/>
-    <mergeCell ref="P65:Q65"/>
-    <mergeCell ref="P56:Q56"/>
-    <mergeCell ref="P57:Q57"/>
-    <mergeCell ref="P58:Q58"/>
-    <mergeCell ref="P59:Q59"/>
-    <mergeCell ref="P60:Q60"/>
-    <mergeCell ref="P51:Q51"/>
-    <mergeCell ref="P52:Q52"/>
-    <mergeCell ref="P53:Q53"/>
-    <mergeCell ref="P54:Q54"/>
-    <mergeCell ref="P55:Q55"/>
+    <mergeCell ref="I4:I5"/>
+    <mergeCell ref="J4:J5"/>
+    <mergeCell ref="P6:Q6"/>
+    <mergeCell ref="P7:Q7"/>
+    <mergeCell ref="P8:Q8"/>
+    <mergeCell ref="P9:Q9"/>
+    <mergeCell ref="P10:Q10"/>
+    <mergeCell ref="P26:Q26"/>
+    <mergeCell ref="P21:Q21"/>
+    <mergeCell ref="P16:Q16"/>
+    <mergeCell ref="P17:Q17"/>
+    <mergeCell ref="P18:Q18"/>
+    <mergeCell ref="P19:Q19"/>
+    <mergeCell ref="P20:Q20"/>
+    <mergeCell ref="P11:Q11"/>
+    <mergeCell ref="P12:Q12"/>
+    <mergeCell ref="P13:Q13"/>
+    <mergeCell ref="P14:Q14"/>
+    <mergeCell ref="P15:Q15"/>
+    <mergeCell ref="L4:L5"/>
+    <mergeCell ref="P22:Q22"/>
+    <mergeCell ref="P23:Q23"/>
+    <mergeCell ref="P24:Q24"/>
+    <mergeCell ref="P25:Q25"/>
+    <mergeCell ref="K2:L2"/>
+    <mergeCell ref="M4:M5"/>
+    <mergeCell ref="P1:Q1"/>
+    <mergeCell ref="P2:Q2"/>
+    <mergeCell ref="G2:H2"/>
+    <mergeCell ref="N4:N5"/>
+    <mergeCell ref="O4:O5"/>
+    <mergeCell ref="C2:E2"/>
+    <mergeCell ref="C1:L1"/>
+    <mergeCell ref="N1:O1"/>
+    <mergeCell ref="P4:Q4"/>
+    <mergeCell ref="P5:Q5"/>
+    <mergeCell ref="A3:T3"/>
+    <mergeCell ref="R4:S5"/>
+    <mergeCell ref="T4:T5"/>
+    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="B4:B5"/>
+    <mergeCell ref="C4:C5"/>
+    <mergeCell ref="D4:D5"/>
+    <mergeCell ref="K4:K5"/>
+    <mergeCell ref="H4:H5"/>
+    <mergeCell ref="E4:E5"/>
+    <mergeCell ref="F4:F5"/>
+    <mergeCell ref="G4:G5"/>
     <mergeCell ref="P27:Q27"/>
     <mergeCell ref="P28:Q28"/>
     <mergeCell ref="P29:Q29"/>
@@ -17417,54 +17351,120 @@
     <mergeCell ref="P33:Q33"/>
     <mergeCell ref="P34:Q34"/>
     <mergeCell ref="P35:Q35"/>
-    <mergeCell ref="K2:L2"/>
-    <mergeCell ref="M4:M5"/>
-    <mergeCell ref="P1:Q1"/>
-    <mergeCell ref="P2:Q2"/>
-    <mergeCell ref="G2:H2"/>
-    <mergeCell ref="N4:N5"/>
-    <mergeCell ref="O4:O5"/>
-    <mergeCell ref="C2:E2"/>
-    <mergeCell ref="C1:L1"/>
-    <mergeCell ref="N1:O1"/>
-    <mergeCell ref="P4:Q4"/>
-    <mergeCell ref="P5:Q5"/>
-    <mergeCell ref="A3:T3"/>
-    <mergeCell ref="R4:S5"/>
-    <mergeCell ref="T4:T5"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="B4:B5"/>
-    <mergeCell ref="C4:C5"/>
-    <mergeCell ref="D4:D5"/>
-    <mergeCell ref="K4:K5"/>
-    <mergeCell ref="H4:H5"/>
-    <mergeCell ref="E4:E5"/>
-    <mergeCell ref="F4:F5"/>
-    <mergeCell ref="G4:G5"/>
-    <mergeCell ref="I4:I5"/>
-    <mergeCell ref="J4:J5"/>
-    <mergeCell ref="P6:Q6"/>
-    <mergeCell ref="P7:Q7"/>
-    <mergeCell ref="P8:Q8"/>
-    <mergeCell ref="P9:Q9"/>
-    <mergeCell ref="P10:Q10"/>
-    <mergeCell ref="P26:Q26"/>
-    <mergeCell ref="P21:Q21"/>
-    <mergeCell ref="P16:Q16"/>
-    <mergeCell ref="P17:Q17"/>
-    <mergeCell ref="P18:Q18"/>
-    <mergeCell ref="P19:Q19"/>
-    <mergeCell ref="P20:Q20"/>
-    <mergeCell ref="P11:Q11"/>
-    <mergeCell ref="P12:Q12"/>
-    <mergeCell ref="P13:Q13"/>
-    <mergeCell ref="P14:Q14"/>
-    <mergeCell ref="P15:Q15"/>
-    <mergeCell ref="L4:L5"/>
-    <mergeCell ref="P22:Q22"/>
-    <mergeCell ref="P23:Q23"/>
-    <mergeCell ref="P24:Q24"/>
-    <mergeCell ref="P25:Q25"/>
+    <mergeCell ref="P56:Q56"/>
+    <mergeCell ref="P57:Q57"/>
+    <mergeCell ref="P58:Q58"/>
+    <mergeCell ref="P59:Q59"/>
+    <mergeCell ref="P60:Q60"/>
+    <mergeCell ref="P51:Q51"/>
+    <mergeCell ref="P52:Q52"/>
+    <mergeCell ref="P53:Q53"/>
+    <mergeCell ref="P54:Q54"/>
+    <mergeCell ref="P55:Q55"/>
+    <mergeCell ref="P66:Q66"/>
+    <mergeCell ref="P67:Q67"/>
+    <mergeCell ref="P68:Q68"/>
+    <mergeCell ref="P69:Q69"/>
+    <mergeCell ref="P70:Q70"/>
+    <mergeCell ref="P61:Q61"/>
+    <mergeCell ref="P62:Q62"/>
+    <mergeCell ref="P63:Q63"/>
+    <mergeCell ref="P64:Q64"/>
+    <mergeCell ref="P65:Q65"/>
+    <mergeCell ref="P76:Q76"/>
+    <mergeCell ref="P77:Q77"/>
+    <mergeCell ref="P78:Q78"/>
+    <mergeCell ref="P79:Q79"/>
+    <mergeCell ref="P80:Q80"/>
+    <mergeCell ref="P71:Q71"/>
+    <mergeCell ref="P72:Q72"/>
+    <mergeCell ref="P73:Q73"/>
+    <mergeCell ref="P74:Q74"/>
+    <mergeCell ref="P75:Q75"/>
+    <mergeCell ref="P86:Q86"/>
+    <mergeCell ref="P87:Q87"/>
+    <mergeCell ref="P88:Q88"/>
+    <mergeCell ref="P89:Q89"/>
+    <mergeCell ref="P90:Q90"/>
+    <mergeCell ref="P81:Q81"/>
+    <mergeCell ref="P82:Q82"/>
+    <mergeCell ref="P83:Q83"/>
+    <mergeCell ref="P84:Q84"/>
+    <mergeCell ref="P85:Q85"/>
+    <mergeCell ref="P96:Q96"/>
+    <mergeCell ref="P97:Q97"/>
+    <mergeCell ref="P98:Q98"/>
+    <mergeCell ref="P99:Q99"/>
+    <mergeCell ref="P100:Q100"/>
+    <mergeCell ref="P91:Q91"/>
+    <mergeCell ref="P92:Q92"/>
+    <mergeCell ref="P93:Q93"/>
+    <mergeCell ref="P94:Q94"/>
+    <mergeCell ref="P95:Q95"/>
+    <mergeCell ref="P106:Q106"/>
+    <mergeCell ref="P107:Q107"/>
+    <mergeCell ref="P108:Q108"/>
+    <mergeCell ref="P109:Q109"/>
+    <mergeCell ref="P110:Q110"/>
+    <mergeCell ref="P101:Q101"/>
+    <mergeCell ref="P102:Q102"/>
+    <mergeCell ref="P103:Q103"/>
+    <mergeCell ref="P104:Q104"/>
+    <mergeCell ref="P105:Q105"/>
+    <mergeCell ref="P116:Q116"/>
+    <mergeCell ref="P117:Q117"/>
+    <mergeCell ref="P118:Q118"/>
+    <mergeCell ref="P119:Q119"/>
+    <mergeCell ref="P120:Q120"/>
+    <mergeCell ref="P111:Q111"/>
+    <mergeCell ref="P112:Q112"/>
+    <mergeCell ref="P113:Q113"/>
+    <mergeCell ref="P114:Q114"/>
+    <mergeCell ref="P115:Q115"/>
+    <mergeCell ref="P126:Q126"/>
+    <mergeCell ref="P127:Q127"/>
+    <mergeCell ref="P128:Q128"/>
+    <mergeCell ref="P129:Q129"/>
+    <mergeCell ref="P130:Q130"/>
+    <mergeCell ref="P121:Q121"/>
+    <mergeCell ref="P122:Q122"/>
+    <mergeCell ref="P123:Q123"/>
+    <mergeCell ref="P124:Q124"/>
+    <mergeCell ref="P125:Q125"/>
+    <mergeCell ref="P136:Q136"/>
+    <mergeCell ref="P137:Q137"/>
+    <mergeCell ref="P138:Q138"/>
+    <mergeCell ref="P139:Q139"/>
+    <mergeCell ref="P140:Q140"/>
+    <mergeCell ref="P131:Q131"/>
+    <mergeCell ref="P132:Q132"/>
+    <mergeCell ref="P133:Q133"/>
+    <mergeCell ref="P134:Q134"/>
+    <mergeCell ref="P135:Q135"/>
+    <mergeCell ref="B162:T163"/>
+    <mergeCell ref="B164:T167"/>
+    <mergeCell ref="P157:Q157"/>
+    <mergeCell ref="P158:Q158"/>
+    <mergeCell ref="P161:Q161"/>
+    <mergeCell ref="P159:Q159"/>
+    <mergeCell ref="P160:Q160"/>
+    <mergeCell ref="P152:Q152"/>
+    <mergeCell ref="P153:Q153"/>
+    <mergeCell ref="P154:Q154"/>
+    <mergeCell ref="P155:Q155"/>
+    <mergeCell ref="P156:Q156"/>
+    <mergeCell ref="S161:T161"/>
+    <mergeCell ref="P146:Q146"/>
+    <mergeCell ref="P147:Q147"/>
+    <mergeCell ref="P148:Q148"/>
+    <mergeCell ref="P149:Q149"/>
+    <mergeCell ref="P151:Q151"/>
+    <mergeCell ref="P141:Q141"/>
+    <mergeCell ref="P142:Q142"/>
+    <mergeCell ref="P143:Q143"/>
+    <mergeCell ref="P144:Q144"/>
+    <mergeCell ref="P145:Q145"/>
+    <mergeCell ref="P150:Q150"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="U66" r:id="rId1" xr:uid="{60CCA824-04D7-4098-BB5B-CC4EC0E5DE92}"/>
@@ -17536,11 +17536,11 @@
       <c r="G4" s="33" t="s">
         <v>164</v>
       </c>
-      <c r="H4" s="410">
+      <c r="H4" s="411">
         <v>93</v>
       </c>
-      <c r="I4" s="410"/>
-      <c r="J4" s="411"/>
+      <c r="I4" s="411"/>
+      <c r="J4" s="412"/>
       <c r="K4" s="324"/>
       <c r="L4" s="324"/>
     </row>
@@ -17559,40 +17559,40 @@
       <c r="L5" s="324"/>
     </row>
     <row r="6" spans="3:12" x14ac:dyDescent="0.25">
-      <c r="C6" s="412" t="s">
+      <c r="C6" s="413" t="s">
         <v>343</v>
       </c>
-      <c r="D6" s="413"/>
-      <c r="E6" s="413"/>
-      <c r="F6" s="413"/>
-      <c r="G6" s="413"/>
-      <c r="H6" s="413"/>
-      <c r="I6" s="413"/>
-      <c r="J6" s="414"/>
+      <c r="D6" s="414"/>
+      <c r="E6" s="414"/>
+      <c r="F6" s="414"/>
+      <c r="G6" s="414"/>
+      <c r="H6" s="414"/>
+      <c r="I6" s="414"/>
+      <c r="J6" s="415"/>
       <c r="K6" s="324"/>
       <c r="L6" s="324"/>
     </row>
     <row r="7" spans="3:12" x14ac:dyDescent="0.25">
-      <c r="C7" s="415"/>
-      <c r="D7" s="416"/>
-      <c r="E7" s="416"/>
-      <c r="F7" s="416"/>
-      <c r="G7" s="416"/>
-      <c r="H7" s="416"/>
-      <c r="I7" s="416"/>
-      <c r="J7" s="417"/>
+      <c r="C7" s="416"/>
+      <c r="D7" s="417"/>
+      <c r="E7" s="417"/>
+      <c r="F7" s="417"/>
+      <c r="G7" s="417"/>
+      <c r="H7" s="417"/>
+      <c r="I7" s="417"/>
+      <c r="J7" s="418"/>
       <c r="K7" s="33"/>
       <c r="L7" s="33"/>
     </row>
     <row r="8" spans="3:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C8" s="418"/>
-      <c r="D8" s="419"/>
-      <c r="E8" s="419"/>
-      <c r="F8" s="419"/>
-      <c r="G8" s="419"/>
-      <c r="H8" s="419"/>
-      <c r="I8" s="419"/>
-      <c r="J8" s="420"/>
+      <c r="C8" s="419"/>
+      <c r="D8" s="420"/>
+      <c r="E8" s="420"/>
+      <c r="F8" s="420"/>
+      <c r="G8" s="420"/>
+      <c r="H8" s="420"/>
+      <c r="I8" s="420"/>
+      <c r="J8" s="421"/>
     </row>
     <row r="10" spans="3:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="11" spans="3:12" x14ac:dyDescent="0.25">
@@ -17640,11 +17640,11 @@
       <c r="G13" s="33" t="s">
         <v>164</v>
       </c>
-      <c r="H13" s="410">
+      <c r="H13" s="411">
         <v>44</v>
       </c>
-      <c r="I13" s="410"/>
-      <c r="J13" s="411"/>
+      <c r="I13" s="411"/>
+      <c r="J13" s="412"/>
       <c r="K13" s="324"/>
       <c r="L13" s="324"/>
     </row>
@@ -17663,40 +17663,40 @@
       <c r="L14" s="324"/>
     </row>
     <row r="15" spans="3:12" x14ac:dyDescent="0.25">
-      <c r="C15" s="412" t="s">
+      <c r="C15" s="413" t="s">
         <v>344</v>
       </c>
-      <c r="D15" s="413"/>
-      <c r="E15" s="413"/>
-      <c r="F15" s="413"/>
-      <c r="G15" s="413"/>
-      <c r="H15" s="413"/>
-      <c r="I15" s="413"/>
-      <c r="J15" s="414"/>
+      <c r="D15" s="414"/>
+      <c r="E15" s="414"/>
+      <c r="F15" s="414"/>
+      <c r="G15" s="414"/>
+      <c r="H15" s="414"/>
+      <c r="I15" s="414"/>
+      <c r="J15" s="415"/>
       <c r="K15" s="324"/>
       <c r="L15" s="324"/>
     </row>
     <row r="16" spans="3:12" x14ac:dyDescent="0.25">
-      <c r="C16" s="415"/>
-      <c r="D16" s="416"/>
-      <c r="E16" s="416"/>
-      <c r="F16" s="416"/>
-      <c r="G16" s="416"/>
-      <c r="H16" s="416"/>
-      <c r="I16" s="416"/>
-      <c r="J16" s="417"/>
+      <c r="C16" s="416"/>
+      <c r="D16" s="417"/>
+      <c r="E16" s="417"/>
+      <c r="F16" s="417"/>
+      <c r="G16" s="417"/>
+      <c r="H16" s="417"/>
+      <c r="I16" s="417"/>
+      <c r="J16" s="418"/>
       <c r="K16" s="324"/>
       <c r="L16" s="324"/>
     </row>
     <row r="17" spans="3:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C17" s="418"/>
-      <c r="D17" s="419"/>
-      <c r="E17" s="419"/>
-      <c r="F17" s="419"/>
-      <c r="G17" s="419"/>
-      <c r="H17" s="419"/>
-      <c r="I17" s="419"/>
-      <c r="J17" s="420"/>
+      <c r="C17" s="419"/>
+      <c r="D17" s="420"/>
+      <c r="E17" s="420"/>
+      <c r="F17" s="420"/>
+      <c r="G17" s="420"/>
+      <c r="H17" s="420"/>
+      <c r="I17" s="420"/>
+      <c r="J17" s="421"/>
     </row>
     <row r="19" spans="3:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="20" spans="3:13" x14ac:dyDescent="0.25">
@@ -17745,11 +17745,11 @@
       <c r="G22" s="33" t="s">
         <v>164</v>
       </c>
-      <c r="H22" s="410">
+      <c r="H22" s="411">
         <v>90</v>
       </c>
-      <c r="I22" s="410"/>
-      <c r="J22" s="411"/>
+      <c r="I22" s="411"/>
+      <c r="J22" s="412"/>
       <c r="K22" s="324"/>
       <c r="L22" s="324"/>
       <c r="M22" s="324"/>
@@ -17770,42 +17770,42 @@
       <c r="M23" s="324"/>
     </row>
     <row r="24" spans="3:13" x14ac:dyDescent="0.25">
-      <c r="C24" s="412" t="s">
+      <c r="C24" s="413" t="s">
         <v>345</v>
       </c>
-      <c r="D24" s="413"/>
-      <c r="E24" s="413"/>
-      <c r="F24" s="413"/>
-      <c r="G24" s="413"/>
-      <c r="H24" s="413"/>
-      <c r="I24" s="413"/>
-      <c r="J24" s="414"/>
+      <c r="D24" s="414"/>
+      <c r="E24" s="414"/>
+      <c r="F24" s="414"/>
+      <c r="G24" s="414"/>
+      <c r="H24" s="414"/>
+      <c r="I24" s="414"/>
+      <c r="J24" s="415"/>
       <c r="K24" s="324"/>
       <c r="L24" s="324"/>
       <c r="M24" s="324"/>
     </row>
     <row r="25" spans="3:13" x14ac:dyDescent="0.25">
-      <c r="C25" s="415"/>
-      <c r="D25" s="416"/>
-      <c r="E25" s="416"/>
-      <c r="F25" s="416"/>
-      <c r="G25" s="416"/>
-      <c r="H25" s="416"/>
-      <c r="I25" s="416"/>
-      <c r="J25" s="417"/>
+      <c r="C25" s="416"/>
+      <c r="D25" s="417"/>
+      <c r="E25" s="417"/>
+      <c r="F25" s="417"/>
+      <c r="G25" s="417"/>
+      <c r="H25" s="417"/>
+      <c r="I25" s="417"/>
+      <c r="J25" s="418"/>
       <c r="K25" s="324"/>
       <c r="L25" s="324"/>
       <c r="M25" s="324"/>
     </row>
     <row r="26" spans="3:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C26" s="418"/>
-      <c r="D26" s="419"/>
-      <c r="E26" s="419"/>
-      <c r="F26" s="419"/>
-      <c r="G26" s="419"/>
-      <c r="H26" s="419"/>
-      <c r="I26" s="419"/>
-      <c r="J26" s="420"/>
+      <c r="C26" s="419"/>
+      <c r="D26" s="420"/>
+      <c r="E26" s="420"/>
+      <c r="F26" s="420"/>
+      <c r="G26" s="420"/>
+      <c r="H26" s="420"/>
+      <c r="I26" s="420"/>
+      <c r="J26" s="421"/>
       <c r="K26" s="324"/>
       <c r="L26" s="324"/>
       <c r="M26" s="324"/>
@@ -17856,11 +17856,11 @@
       <c r="G31" s="33" t="s">
         <v>164</v>
       </c>
-      <c r="H31" s="410">
+      <c r="H31" s="411">
         <v>78</v>
       </c>
-      <c r="I31" s="410"/>
-      <c r="J31" s="411"/>
+      <c r="I31" s="411"/>
+      <c r="J31" s="412"/>
       <c r="K31" s="324"/>
       <c r="L31" s="324"/>
     </row>
@@ -17879,40 +17879,40 @@
       <c r="L32" s="324"/>
     </row>
     <row r="33" spans="3:12" x14ac:dyDescent="0.25">
-      <c r="C33" s="412" t="s">
+      <c r="C33" s="413" t="s">
         <v>346</v>
       </c>
-      <c r="D33" s="413"/>
-      <c r="E33" s="413"/>
-      <c r="F33" s="413"/>
-      <c r="G33" s="413"/>
-      <c r="H33" s="413"/>
-      <c r="I33" s="413"/>
-      <c r="J33" s="414"/>
+      <c r="D33" s="414"/>
+      <c r="E33" s="414"/>
+      <c r="F33" s="414"/>
+      <c r="G33" s="414"/>
+      <c r="H33" s="414"/>
+      <c r="I33" s="414"/>
+      <c r="J33" s="415"/>
       <c r="K33" s="324"/>
       <c r="L33" s="324"/>
     </row>
     <row r="34" spans="3:12" x14ac:dyDescent="0.25">
-      <c r="C34" s="415"/>
-      <c r="D34" s="416"/>
-      <c r="E34" s="416"/>
-      <c r="F34" s="416"/>
-      <c r="G34" s="416"/>
-      <c r="H34" s="416"/>
-      <c r="I34" s="416"/>
-      <c r="J34" s="417"/>
+      <c r="C34" s="416"/>
+      <c r="D34" s="417"/>
+      <c r="E34" s="417"/>
+      <c r="F34" s="417"/>
+      <c r="G34" s="417"/>
+      <c r="H34" s="417"/>
+      <c r="I34" s="417"/>
+      <c r="J34" s="418"/>
       <c r="K34" s="324"/>
       <c r="L34" s="324"/>
     </row>
     <row r="35" spans="3:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C35" s="418"/>
-      <c r="D35" s="419"/>
-      <c r="E35" s="419"/>
-      <c r="F35" s="419"/>
-      <c r="G35" s="419"/>
-      <c r="H35" s="419"/>
-      <c r="I35" s="419"/>
-      <c r="J35" s="420"/>
+      <c r="C35" s="419"/>
+      <c r="D35" s="420"/>
+      <c r="E35" s="420"/>
+      <c r="F35" s="420"/>
+      <c r="G35" s="420"/>
+      <c r="H35" s="420"/>
+      <c r="I35" s="420"/>
+      <c r="J35" s="421"/>
     </row>
     <row r="37" spans="3:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="38" spans="3:12" x14ac:dyDescent="0.25">
@@ -17958,11 +17958,11 @@
       <c r="G40" s="33" t="s">
         <v>164</v>
       </c>
-      <c r="H40" s="410">
+      <c r="H40" s="411">
         <v>2</v>
       </c>
-      <c r="I40" s="410"/>
-      <c r="J40" s="411"/>
+      <c r="I40" s="411"/>
+      <c r="J40" s="412"/>
     </row>
     <row r="41" spans="3:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C41" s="291" t="s">
@@ -17977,36 +17977,36 @@
       <c r="J41" s="61"/>
     </row>
     <row r="42" spans="3:12" x14ac:dyDescent="0.25">
-      <c r="C42" s="412" t="s">
+      <c r="C42" s="413" t="s">
         <v>347</v>
       </c>
-      <c r="D42" s="413"/>
-      <c r="E42" s="413"/>
-      <c r="F42" s="413"/>
-      <c r="G42" s="413"/>
-      <c r="H42" s="413"/>
-      <c r="I42" s="413"/>
-      <c r="J42" s="414"/>
+      <c r="D42" s="414"/>
+      <c r="E42" s="414"/>
+      <c r="F42" s="414"/>
+      <c r="G42" s="414"/>
+      <c r="H42" s="414"/>
+      <c r="I42" s="414"/>
+      <c r="J42" s="415"/>
     </row>
     <row r="43" spans="3:12" x14ac:dyDescent="0.25">
-      <c r="C43" s="415"/>
-      <c r="D43" s="416"/>
-      <c r="E43" s="416"/>
-      <c r="F43" s="416"/>
-      <c r="G43" s="416"/>
-      <c r="H43" s="416"/>
-      <c r="I43" s="416"/>
-      <c r="J43" s="417"/>
+      <c r="C43" s="416"/>
+      <c r="D43" s="417"/>
+      <c r="E43" s="417"/>
+      <c r="F43" s="417"/>
+      <c r="G43" s="417"/>
+      <c r="H43" s="417"/>
+      <c r="I43" s="417"/>
+      <c r="J43" s="418"/>
     </row>
     <row r="44" spans="3:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C44" s="418"/>
-      <c r="D44" s="419"/>
-      <c r="E44" s="419"/>
-      <c r="F44" s="419"/>
-      <c r="G44" s="419"/>
-      <c r="H44" s="419"/>
-      <c r="I44" s="419"/>
-      <c r="J44" s="420"/>
+      <c r="C44" s="419"/>
+      <c r="D44" s="420"/>
+      <c r="E44" s="420"/>
+      <c r="F44" s="420"/>
+      <c r="G44" s="420"/>
+      <c r="H44" s="420"/>
+      <c r="I44" s="420"/>
+      <c r="J44" s="421"/>
     </row>
     <row r="46" spans="3:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="47" spans="3:12" x14ac:dyDescent="0.25">
@@ -18054,11 +18054,11 @@
       <c r="G49" s="33" t="s">
         <v>164</v>
       </c>
-      <c r="H49" s="410">
+      <c r="H49" s="411">
         <v>59</v>
       </c>
-      <c r="I49" s="410"/>
-      <c r="J49" s="411"/>
+      <c r="I49" s="411"/>
+      <c r="J49" s="412"/>
       <c r="K49" s="324"/>
       <c r="L49" s="324"/>
     </row>
@@ -18077,38 +18077,38 @@
       <c r="L50" s="324"/>
     </row>
     <row r="51" spans="3:12" x14ac:dyDescent="0.25">
-      <c r="C51" s="412" t="s">
-        <v>438</v>
-      </c>
-      <c r="D51" s="413"/>
-      <c r="E51" s="413"/>
-      <c r="F51" s="413"/>
-      <c r="G51" s="413"/>
-      <c r="H51" s="413"/>
-      <c r="I51" s="413"/>
-      <c r="J51" s="414"/>
+      <c r="C51" s="413" t="s">
+        <v>433</v>
+      </c>
+      <c r="D51" s="414"/>
+      <c r="E51" s="414"/>
+      <c r="F51" s="414"/>
+      <c r="G51" s="414"/>
+      <c r="H51" s="414"/>
+      <c r="I51" s="414"/>
+      <c r="J51" s="415"/>
       <c r="K51" s="324"/>
       <c r="L51" s="324"/>
     </row>
     <row r="52" spans="3:12" x14ac:dyDescent="0.25">
-      <c r="C52" s="415"/>
-      <c r="D52" s="416"/>
-      <c r="E52" s="416"/>
-      <c r="F52" s="416"/>
-      <c r="G52" s="416"/>
-      <c r="H52" s="416"/>
-      <c r="I52" s="416"/>
-      <c r="J52" s="417"/>
+      <c r="C52" s="416"/>
+      <c r="D52" s="417"/>
+      <c r="E52" s="417"/>
+      <c r="F52" s="417"/>
+      <c r="G52" s="417"/>
+      <c r="H52" s="417"/>
+      <c r="I52" s="417"/>
+      <c r="J52" s="418"/>
     </row>
     <row r="53" spans="3:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C53" s="418"/>
-      <c r="D53" s="419"/>
-      <c r="E53" s="419"/>
-      <c r="F53" s="419"/>
-      <c r="G53" s="419"/>
-      <c r="H53" s="419"/>
-      <c r="I53" s="419"/>
-      <c r="J53" s="420"/>
+      <c r="C53" s="419"/>
+      <c r="D53" s="420"/>
+      <c r="E53" s="420"/>
+      <c r="F53" s="420"/>
+      <c r="G53" s="420"/>
+      <c r="H53" s="420"/>
+      <c r="I53" s="420"/>
+      <c r="J53" s="421"/>
     </row>
     <row r="55" spans="3:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="56" spans="3:12" x14ac:dyDescent="0.25">
@@ -18154,11 +18154,11 @@
       <c r="G58" s="33" t="s">
         <v>164</v>
       </c>
-      <c r="H58" s="410">
+      <c r="H58" s="411">
         <v>39</v>
       </c>
-      <c r="I58" s="410"/>
-      <c r="J58" s="411"/>
+      <c r="I58" s="411"/>
+      <c r="J58" s="412"/>
       <c r="K58" s="324"/>
       <c r="L58" s="324"/>
     </row>
@@ -18177,40 +18177,40 @@
       <c r="L59" s="324"/>
     </row>
     <row r="60" spans="3:12" x14ac:dyDescent="0.25">
-      <c r="C60" s="412" t="s">
+      <c r="C60" s="413" t="s">
         <v>348</v>
       </c>
-      <c r="D60" s="413"/>
-      <c r="E60" s="413"/>
-      <c r="F60" s="413"/>
-      <c r="G60" s="413"/>
-      <c r="H60" s="413"/>
-      <c r="I60" s="413"/>
-      <c r="J60" s="414"/>
+      <c r="D60" s="414"/>
+      <c r="E60" s="414"/>
+      <c r="F60" s="414"/>
+      <c r="G60" s="414"/>
+      <c r="H60" s="414"/>
+      <c r="I60" s="414"/>
+      <c r="J60" s="415"/>
       <c r="K60" s="324"/>
       <c r="L60" s="324"/>
     </row>
     <row r="61" spans="3:12" x14ac:dyDescent="0.25">
-      <c r="C61" s="415"/>
-      <c r="D61" s="416"/>
-      <c r="E61" s="416"/>
-      <c r="F61" s="416"/>
-      <c r="G61" s="416"/>
-      <c r="H61" s="416"/>
-      <c r="I61" s="416"/>
-      <c r="J61" s="417"/>
+      <c r="C61" s="416"/>
+      <c r="D61" s="417"/>
+      <c r="E61" s="417"/>
+      <c r="F61" s="417"/>
+      <c r="G61" s="417"/>
+      <c r="H61" s="417"/>
+      <c r="I61" s="417"/>
+      <c r="J61" s="418"/>
       <c r="K61" s="324"/>
       <c r="L61" s="324"/>
     </row>
     <row r="62" spans="3:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C62" s="418"/>
-      <c r="D62" s="419"/>
-      <c r="E62" s="419"/>
-      <c r="F62" s="419"/>
-      <c r="G62" s="419"/>
-      <c r="H62" s="419"/>
-      <c r="I62" s="419"/>
-      <c r="J62" s="420"/>
+      <c r="C62" s="419"/>
+      <c r="D62" s="420"/>
+      <c r="E62" s="420"/>
+      <c r="F62" s="420"/>
+      <c r="G62" s="420"/>
+      <c r="H62" s="420"/>
+      <c r="I62" s="420"/>
+      <c r="J62" s="421"/>
     </row>
     <row r="64" spans="3:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="65" spans="3:13" x14ac:dyDescent="0.25">
@@ -18226,11 +18226,11 @@
       <c r="H65" s="236"/>
       <c r="I65" s="237"/>
       <c r="J65" s="238"/>
-      <c r="K65" s="421" t="s">
+      <c r="K65" s="422" t="s">
         <v>349</v>
       </c>
-      <c r="L65" s="422"/>
-      <c r="M65" s="422"/>
+      <c r="L65" s="423"/>
+      <c r="M65" s="423"/>
     </row>
     <row r="66" spans="3:13" x14ac:dyDescent="0.25">
       <c r="C66" s="303"/>
@@ -18246,9 +18246,9 @@
         <v>8</v>
       </c>
       <c r="J66" s="60"/>
-      <c r="K66" s="421"/>
-      <c r="L66" s="422"/>
-      <c r="M66" s="422"/>
+      <c r="K66" s="422"/>
+      <c r="L66" s="423"/>
+      <c r="M66" s="423"/>
     </row>
     <row r="67" spans="3:13" x14ac:dyDescent="0.25">
       <c r="C67" s="303" t="s">
@@ -18264,14 +18264,14 @@
       <c r="G67" s="33" t="s">
         <v>164</v>
       </c>
-      <c r="H67" s="410">
+      <c r="H67" s="411">
         <v>104</v>
       </c>
-      <c r="I67" s="410"/>
-      <c r="J67" s="411"/>
-      <c r="K67" s="421"/>
-      <c r="L67" s="422"/>
-      <c r="M67" s="422"/>
+      <c r="I67" s="411"/>
+      <c r="J67" s="412"/>
+      <c r="K67" s="422"/>
+      <c r="L67" s="423"/>
+      <c r="M67" s="423"/>
     </row>
     <row r="68" spans="3:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C68" s="303" t="s">
@@ -18284,50 +18284,50 @@
       <c r="H68" s="33"/>
       <c r="I68" s="33"/>
       <c r="J68" s="61"/>
-      <c r="K68" s="421"/>
-      <c r="L68" s="422"/>
-      <c r="M68" s="422"/>
+      <c r="K68" s="422"/>
+      <c r="L68" s="423"/>
+      <c r="M68" s="423"/>
     </row>
     <row r="69" spans="3:13" x14ac:dyDescent="0.25">
-      <c r="C69" s="412" t="s">
+      <c r="C69" s="413" t="s">
         <v>350</v>
       </c>
-      <c r="D69" s="413"/>
-      <c r="E69" s="413"/>
-      <c r="F69" s="413"/>
-      <c r="G69" s="413"/>
-      <c r="H69" s="413"/>
-      <c r="I69" s="413"/>
-      <c r="J69" s="414"/>
-      <c r="K69" s="421"/>
-      <c r="L69" s="422"/>
-      <c r="M69" s="422"/>
+      <c r="D69" s="414"/>
+      <c r="E69" s="414"/>
+      <c r="F69" s="414"/>
+      <c r="G69" s="414"/>
+      <c r="H69" s="414"/>
+      <c r="I69" s="414"/>
+      <c r="J69" s="415"/>
+      <c r="K69" s="422"/>
+      <c r="L69" s="423"/>
+      <c r="M69" s="423"/>
     </row>
     <row r="70" spans="3:13" x14ac:dyDescent="0.25">
-      <c r="C70" s="415"/>
-      <c r="D70" s="416"/>
-      <c r="E70" s="416"/>
-      <c r="F70" s="416"/>
-      <c r="G70" s="416"/>
-      <c r="H70" s="416"/>
-      <c r="I70" s="416"/>
-      <c r="J70" s="417"/>
-      <c r="K70" s="421"/>
-      <c r="L70" s="422"/>
-      <c r="M70" s="422"/>
+      <c r="C70" s="416"/>
+      <c r="D70" s="417"/>
+      <c r="E70" s="417"/>
+      <c r="F70" s="417"/>
+      <c r="G70" s="417"/>
+      <c r="H70" s="417"/>
+      <c r="I70" s="417"/>
+      <c r="J70" s="418"/>
+      <c r="K70" s="422"/>
+      <c r="L70" s="423"/>
+      <c r="M70" s="423"/>
     </row>
     <row r="71" spans="3:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C71" s="418"/>
-      <c r="D71" s="419"/>
-      <c r="E71" s="419"/>
-      <c r="F71" s="419"/>
-      <c r="G71" s="419"/>
-      <c r="H71" s="419"/>
-      <c r="I71" s="419"/>
-      <c r="J71" s="420"/>
-      <c r="K71" s="421"/>
-      <c r="L71" s="422"/>
-      <c r="M71" s="422"/>
+      <c r="C71" s="419"/>
+      <c r="D71" s="420"/>
+      <c r="E71" s="420"/>
+      <c r="F71" s="420"/>
+      <c r="G71" s="420"/>
+      <c r="H71" s="420"/>
+      <c r="I71" s="420"/>
+      <c r="J71" s="421"/>
+      <c r="K71" s="422"/>
+      <c r="L71" s="423"/>
+      <c r="M71" s="423"/>
     </row>
     <row r="73" spans="3:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="74" spans="3:13" x14ac:dyDescent="0.25">
@@ -18375,11 +18375,11 @@
       <c r="G76" s="33" t="s">
         <v>164</v>
       </c>
-      <c r="H76" s="410">
+      <c r="H76" s="411">
         <v>119</v>
       </c>
-      <c r="I76" s="410"/>
-      <c r="J76" s="411"/>
+      <c r="I76" s="411"/>
+      <c r="J76" s="412"/>
       <c r="K76" s="324"/>
       <c r="L76" s="324"/>
     </row>
@@ -18398,40 +18398,40 @@
       <c r="L77" s="324"/>
     </row>
     <row r="78" spans="3:13" x14ac:dyDescent="0.25">
-      <c r="C78" s="412" t="s">
+      <c r="C78" s="413" t="s">
         <v>351</v>
       </c>
-      <c r="D78" s="413"/>
-      <c r="E78" s="413"/>
-      <c r="F78" s="413"/>
-      <c r="G78" s="413"/>
-      <c r="H78" s="413"/>
-      <c r="I78" s="413"/>
-      <c r="J78" s="414"/>
+      <c r="D78" s="414"/>
+      <c r="E78" s="414"/>
+      <c r="F78" s="414"/>
+      <c r="G78" s="414"/>
+      <c r="H78" s="414"/>
+      <c r="I78" s="414"/>
+      <c r="J78" s="415"/>
       <c r="K78" s="324"/>
       <c r="L78" s="324"/>
     </row>
     <row r="79" spans="3:13" x14ac:dyDescent="0.25">
-      <c r="C79" s="415"/>
-      <c r="D79" s="416"/>
-      <c r="E79" s="416"/>
-      <c r="F79" s="416"/>
-      <c r="G79" s="416"/>
-      <c r="H79" s="416"/>
-      <c r="I79" s="416"/>
-      <c r="J79" s="417"/>
+      <c r="C79" s="416"/>
+      <c r="D79" s="417"/>
+      <c r="E79" s="417"/>
+      <c r="F79" s="417"/>
+      <c r="G79" s="417"/>
+      <c r="H79" s="417"/>
+      <c r="I79" s="417"/>
+      <c r="J79" s="418"/>
       <c r="K79" s="324"/>
       <c r="L79" s="324"/>
     </row>
     <row r="80" spans="3:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C80" s="418"/>
-      <c r="D80" s="419"/>
-      <c r="E80" s="419"/>
-      <c r="F80" s="419"/>
-      <c r="G80" s="419"/>
-      <c r="H80" s="419"/>
-      <c r="I80" s="419"/>
-      <c r="J80" s="420"/>
+      <c r="C80" s="419"/>
+      <c r="D80" s="420"/>
+      <c r="E80" s="420"/>
+      <c r="F80" s="420"/>
+      <c r="G80" s="420"/>
+      <c r="H80" s="420"/>
+      <c r="I80" s="420"/>
+      <c r="J80" s="421"/>
       <c r="K80" s="324"/>
       <c r="L80" s="324"/>
     </row>
@@ -18481,11 +18481,11 @@
       <c r="G85" s="33" t="s">
         <v>164</v>
       </c>
-      <c r="H85" s="410">
+      <c r="H85" s="411">
         <v>60</v>
       </c>
-      <c r="I85" s="410"/>
-      <c r="J85" s="411"/>
+      <c r="I85" s="411"/>
+      <c r="J85" s="412"/>
       <c r="K85" s="324"/>
       <c r="L85" s="324"/>
     </row>
@@ -18504,40 +18504,40 @@
       <c r="L86" s="324"/>
     </row>
     <row r="87" spans="3:12" x14ac:dyDescent="0.25">
-      <c r="C87" s="412" t="s">
+      <c r="C87" s="413" t="s">
         <v>352</v>
       </c>
-      <c r="D87" s="413"/>
-      <c r="E87" s="413"/>
-      <c r="F87" s="413"/>
-      <c r="G87" s="413"/>
-      <c r="H87" s="413"/>
-      <c r="I87" s="413"/>
-      <c r="J87" s="414"/>
+      <c r="D87" s="414"/>
+      <c r="E87" s="414"/>
+      <c r="F87" s="414"/>
+      <c r="G87" s="414"/>
+      <c r="H87" s="414"/>
+      <c r="I87" s="414"/>
+      <c r="J87" s="415"/>
       <c r="K87" s="324"/>
       <c r="L87" s="324"/>
     </row>
     <row r="88" spans="3:12" x14ac:dyDescent="0.25">
-      <c r="C88" s="415"/>
-      <c r="D88" s="416"/>
-      <c r="E88" s="416"/>
-      <c r="F88" s="416"/>
-      <c r="G88" s="416"/>
-      <c r="H88" s="416"/>
-      <c r="I88" s="416"/>
-      <c r="J88" s="417"/>
+      <c r="C88" s="416"/>
+      <c r="D88" s="417"/>
+      <c r="E88" s="417"/>
+      <c r="F88" s="417"/>
+      <c r="G88" s="417"/>
+      <c r="H88" s="417"/>
+      <c r="I88" s="417"/>
+      <c r="J88" s="418"/>
       <c r="K88" s="324"/>
       <c r="L88" s="324"/>
     </row>
     <row r="89" spans="3:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C89" s="418"/>
-      <c r="D89" s="419"/>
-      <c r="E89" s="419"/>
-      <c r="F89" s="419"/>
-      <c r="G89" s="419"/>
-      <c r="H89" s="419"/>
-      <c r="I89" s="419"/>
-      <c r="J89" s="420"/>
+      <c r="C89" s="419"/>
+      <c r="D89" s="420"/>
+      <c r="E89" s="420"/>
+      <c r="F89" s="420"/>
+      <c r="G89" s="420"/>
+      <c r="H89" s="420"/>
+      <c r="I89" s="420"/>
+      <c r="J89" s="421"/>
     </row>
     <row r="91" spans="3:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="92" spans="3:12" x14ac:dyDescent="0.25">
@@ -18585,11 +18585,11 @@
       <c r="G94" s="33" t="s">
         <v>164</v>
       </c>
-      <c r="H94" s="410">
+      <c r="H94" s="411">
         <v>105</v>
       </c>
-      <c r="I94" s="410"/>
-      <c r="J94" s="411"/>
+      <c r="I94" s="411"/>
+      <c r="J94" s="412"/>
       <c r="K94" s="324"/>
       <c r="L94" s="324"/>
     </row>
@@ -18608,40 +18608,40 @@
       <c r="L95" s="324"/>
     </row>
     <row r="96" spans="3:12" x14ac:dyDescent="0.25">
-      <c r="C96" s="412" t="s">
+      <c r="C96" s="413" t="s">
         <v>368</v>
       </c>
-      <c r="D96" s="413"/>
-      <c r="E96" s="413"/>
-      <c r="F96" s="413"/>
-      <c r="G96" s="413"/>
-      <c r="H96" s="413"/>
-      <c r="I96" s="413"/>
-      <c r="J96" s="414"/>
+      <c r="D96" s="414"/>
+      <c r="E96" s="414"/>
+      <c r="F96" s="414"/>
+      <c r="G96" s="414"/>
+      <c r="H96" s="414"/>
+      <c r="I96" s="414"/>
+      <c r="J96" s="415"/>
       <c r="K96" s="324"/>
       <c r="L96" s="324"/>
     </row>
     <row r="97" spans="3:13" x14ac:dyDescent="0.25">
-      <c r="C97" s="415"/>
-      <c r="D97" s="416"/>
-      <c r="E97" s="416"/>
-      <c r="F97" s="416"/>
-      <c r="G97" s="416"/>
-      <c r="H97" s="416"/>
-      <c r="I97" s="416"/>
-      <c r="J97" s="417"/>
+      <c r="C97" s="416"/>
+      <c r="D97" s="417"/>
+      <c r="E97" s="417"/>
+      <c r="F97" s="417"/>
+      <c r="G97" s="417"/>
+      <c r="H97" s="417"/>
+      <c r="I97" s="417"/>
+      <c r="J97" s="418"/>
       <c r="K97" s="324"/>
       <c r="L97" s="324"/>
     </row>
     <row r="98" spans="3:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C98" s="418"/>
-      <c r="D98" s="419"/>
-      <c r="E98" s="419"/>
-      <c r="F98" s="419"/>
-      <c r="G98" s="419"/>
-      <c r="H98" s="419"/>
-      <c r="I98" s="419"/>
-      <c r="J98" s="420"/>
+      <c r="C98" s="419"/>
+      <c r="D98" s="420"/>
+      <c r="E98" s="420"/>
+      <c r="F98" s="420"/>
+      <c r="G98" s="420"/>
+      <c r="H98" s="420"/>
+      <c r="I98" s="420"/>
+      <c r="J98" s="421"/>
     </row>
     <row r="101" spans="3:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="102" spans="3:13" x14ac:dyDescent="0.25">
@@ -18691,11 +18691,11 @@
       <c r="G104" s="33" t="s">
         <v>164</v>
       </c>
-      <c r="H104" s="410" t="s">
+      <c r="H104" s="411" t="s">
         <v>353</v>
       </c>
-      <c r="I104" s="410"/>
-      <c r="J104" s="411"/>
+      <c r="I104" s="411"/>
+      <c r="J104" s="412"/>
       <c r="L104" s="324"/>
       <c r="M104" s="324"/>
     </row>
@@ -18714,40 +18714,40 @@
       <c r="M105" s="324"/>
     </row>
     <row r="106" spans="3:13" x14ac:dyDescent="0.25">
-      <c r="C106" s="412" t="s">
+      <c r="C106" s="413" t="s">
         <v>354</v>
       </c>
-      <c r="D106" s="413"/>
-      <c r="E106" s="413"/>
-      <c r="F106" s="413"/>
-      <c r="G106" s="413"/>
-      <c r="H106" s="413"/>
-      <c r="I106" s="413"/>
-      <c r="J106" s="414"/>
+      <c r="D106" s="414"/>
+      <c r="E106" s="414"/>
+      <c r="F106" s="414"/>
+      <c r="G106" s="414"/>
+      <c r="H106" s="414"/>
+      <c r="I106" s="414"/>
+      <c r="J106" s="415"/>
       <c r="L106" s="324"/>
       <c r="M106" s="324"/>
     </row>
     <row r="107" spans="3:13" x14ac:dyDescent="0.25">
-      <c r="C107" s="415"/>
-      <c r="D107" s="416"/>
-      <c r="E107" s="416"/>
-      <c r="F107" s="416"/>
-      <c r="G107" s="416"/>
-      <c r="H107" s="416"/>
-      <c r="I107" s="416"/>
-      <c r="J107" s="417"/>
+      <c r="C107" s="416"/>
+      <c r="D107" s="417"/>
+      <c r="E107" s="417"/>
+      <c r="F107" s="417"/>
+      <c r="G107" s="417"/>
+      <c r="H107" s="417"/>
+      <c r="I107" s="417"/>
+      <c r="J107" s="418"/>
       <c r="L107" s="324"/>
       <c r="M107" s="324"/>
     </row>
     <row r="108" spans="3:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C108" s="418"/>
-      <c r="D108" s="419"/>
-      <c r="E108" s="419"/>
-      <c r="F108" s="419"/>
-      <c r="G108" s="419"/>
-      <c r="H108" s="419"/>
-      <c r="I108" s="419"/>
-      <c r="J108" s="420"/>
+      <c r="C108" s="419"/>
+      <c r="D108" s="420"/>
+      <c r="E108" s="420"/>
+      <c r="F108" s="420"/>
+      <c r="G108" s="420"/>
+      <c r="H108" s="420"/>
+      <c r="I108" s="420"/>
+      <c r="J108" s="421"/>
       <c r="L108" s="324"/>
       <c r="M108" s="324"/>
     </row>
@@ -18801,11 +18801,11 @@
       <c r="G113" s="33" t="s">
         <v>164</v>
       </c>
-      <c r="H113" s="410">
+      <c r="H113" s="411">
         <v>36</v>
       </c>
-      <c r="I113" s="410"/>
-      <c r="J113" s="411"/>
+      <c r="I113" s="411"/>
+      <c r="J113" s="412"/>
       <c r="K113" s="324"/>
       <c r="L113" s="324"/>
       <c r="M113" s="324"/>
@@ -18826,42 +18826,42 @@
       <c r="M114" s="324"/>
     </row>
     <row r="115" spans="3:13" x14ac:dyDescent="0.25">
-      <c r="C115" s="412" t="s">
+      <c r="C115" s="413" t="s">
         <v>355</v>
       </c>
-      <c r="D115" s="413"/>
-      <c r="E115" s="413"/>
-      <c r="F115" s="413"/>
-      <c r="G115" s="413"/>
-      <c r="H115" s="413"/>
-      <c r="I115" s="413"/>
-      <c r="J115" s="414"/>
+      <c r="D115" s="414"/>
+      <c r="E115" s="414"/>
+      <c r="F115" s="414"/>
+      <c r="G115" s="414"/>
+      <c r="H115" s="414"/>
+      <c r="I115" s="414"/>
+      <c r="J115" s="415"/>
       <c r="K115" s="324"/>
       <c r="L115" s="324"/>
       <c r="M115" s="324"/>
     </row>
     <row r="116" spans="3:13" x14ac:dyDescent="0.25">
-      <c r="C116" s="415"/>
-      <c r="D116" s="416"/>
-      <c r="E116" s="416"/>
-      <c r="F116" s="416"/>
-      <c r="G116" s="416"/>
-      <c r="H116" s="416"/>
-      <c r="I116" s="416"/>
-      <c r="J116" s="417"/>
+      <c r="C116" s="416"/>
+      <c r="D116" s="417"/>
+      <c r="E116" s="417"/>
+      <c r="F116" s="417"/>
+      <c r="G116" s="417"/>
+      <c r="H116" s="417"/>
+      <c r="I116" s="417"/>
+      <c r="J116" s="418"/>
       <c r="K116" s="324"/>
       <c r="L116" s="324"/>
       <c r="M116" s="324"/>
     </row>
     <row r="117" spans="3:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C117" s="418"/>
-      <c r="D117" s="419"/>
-      <c r="E117" s="419"/>
-      <c r="F117" s="419"/>
-      <c r="G117" s="419"/>
-      <c r="H117" s="419"/>
-      <c r="I117" s="419"/>
-      <c r="J117" s="420"/>
+      <c r="C117" s="419"/>
+      <c r="D117" s="420"/>
+      <c r="E117" s="420"/>
+      <c r="F117" s="420"/>
+      <c r="G117" s="420"/>
+      <c r="H117" s="420"/>
+      <c r="I117" s="420"/>
+      <c r="J117" s="421"/>
       <c r="K117" s="324"/>
       <c r="L117" s="324"/>
       <c r="M117" s="324"/>
@@ -18919,11 +18919,11 @@
       <c r="G122" s="33" t="s">
         <v>164</v>
       </c>
-      <c r="H122" s="410">
+      <c r="H122" s="411">
         <v>73</v>
       </c>
-      <c r="I122" s="410"/>
-      <c r="J122" s="411"/>
+      <c r="I122" s="411"/>
+      <c r="J122" s="412"/>
       <c r="K122" s="324"/>
       <c r="L122" s="324"/>
     </row>
@@ -18942,40 +18942,40 @@
       <c r="L123" s="324"/>
     </row>
     <row r="124" spans="3:13" x14ac:dyDescent="0.25">
-      <c r="C124" s="412" t="s">
+      <c r="C124" s="413" t="s">
         <v>356</v>
       </c>
-      <c r="D124" s="413"/>
-      <c r="E124" s="413"/>
-      <c r="F124" s="413"/>
-      <c r="G124" s="413"/>
-      <c r="H124" s="413"/>
-      <c r="I124" s="413"/>
-      <c r="J124" s="414"/>
+      <c r="D124" s="414"/>
+      <c r="E124" s="414"/>
+      <c r="F124" s="414"/>
+      <c r="G124" s="414"/>
+      <c r="H124" s="414"/>
+      <c r="I124" s="414"/>
+      <c r="J124" s="415"/>
       <c r="K124" s="324"/>
       <c r="L124" s="324"/>
     </row>
     <row r="125" spans="3:13" x14ac:dyDescent="0.25">
-      <c r="C125" s="415"/>
-      <c r="D125" s="416"/>
-      <c r="E125" s="416"/>
-      <c r="F125" s="416"/>
-      <c r="G125" s="416"/>
-      <c r="H125" s="416"/>
-      <c r="I125" s="416"/>
-      <c r="J125" s="417"/>
+      <c r="C125" s="416"/>
+      <c r="D125" s="417"/>
+      <c r="E125" s="417"/>
+      <c r="F125" s="417"/>
+      <c r="G125" s="417"/>
+      <c r="H125" s="417"/>
+      <c r="I125" s="417"/>
+      <c r="J125" s="418"/>
       <c r="K125" s="324"/>
       <c r="L125" s="324"/>
     </row>
     <row r="126" spans="3:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C126" s="418"/>
-      <c r="D126" s="419"/>
-      <c r="E126" s="419"/>
-      <c r="F126" s="419"/>
-      <c r="G126" s="419"/>
-      <c r="H126" s="419"/>
-      <c r="I126" s="419"/>
-      <c r="J126" s="420"/>
+      <c r="C126" s="419"/>
+      <c r="D126" s="420"/>
+      <c r="E126" s="420"/>
+      <c r="F126" s="420"/>
+      <c r="G126" s="420"/>
+      <c r="H126" s="420"/>
+      <c r="I126" s="420"/>
+      <c r="J126" s="421"/>
     </row>
     <row r="128" spans="3:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="129" spans="3:12" x14ac:dyDescent="0.25">
@@ -19021,11 +19021,11 @@
       <c r="G131" s="33" t="s">
         <v>164</v>
       </c>
-      <c r="H131" s="410">
+      <c r="H131" s="411">
         <v>77</v>
       </c>
-      <c r="I131" s="410"/>
-      <c r="J131" s="411"/>
+      <c r="I131" s="411"/>
+      <c r="J131" s="412"/>
       <c r="K131" s="324"/>
       <c r="L131" s="324"/>
     </row>
@@ -19044,40 +19044,40 @@
       <c r="L132" s="324"/>
     </row>
     <row r="133" spans="3:12" x14ac:dyDescent="0.25">
-      <c r="C133" s="412" t="s">
+      <c r="C133" s="413" t="s">
         <v>357</v>
       </c>
-      <c r="D133" s="413"/>
-      <c r="E133" s="413"/>
-      <c r="F133" s="413"/>
-      <c r="G133" s="413"/>
-      <c r="H133" s="413"/>
-      <c r="I133" s="413"/>
-      <c r="J133" s="414"/>
+      <c r="D133" s="414"/>
+      <c r="E133" s="414"/>
+      <c r="F133" s="414"/>
+      <c r="G133" s="414"/>
+      <c r="H133" s="414"/>
+      <c r="I133" s="414"/>
+      <c r="J133" s="415"/>
       <c r="K133" s="324"/>
       <c r="L133" s="324"/>
     </row>
     <row r="134" spans="3:12" x14ac:dyDescent="0.25">
-      <c r="C134" s="415"/>
-      <c r="D134" s="416"/>
-      <c r="E134" s="416"/>
-      <c r="F134" s="416"/>
-      <c r="G134" s="416"/>
-      <c r="H134" s="416"/>
-      <c r="I134" s="416"/>
-      <c r="J134" s="417"/>
+      <c r="C134" s="416"/>
+      <c r="D134" s="417"/>
+      <c r="E134" s="417"/>
+      <c r="F134" s="417"/>
+      <c r="G134" s="417"/>
+      <c r="H134" s="417"/>
+      <c r="I134" s="417"/>
+      <c r="J134" s="418"/>
       <c r="K134" s="324"/>
       <c r="L134" s="324"/>
     </row>
     <row r="135" spans="3:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C135" s="418"/>
-      <c r="D135" s="419"/>
-      <c r="E135" s="419"/>
-      <c r="F135" s="419"/>
-      <c r="G135" s="419"/>
-      <c r="H135" s="419"/>
-      <c r="I135" s="419"/>
-      <c r="J135" s="420"/>
+      <c r="C135" s="419"/>
+      <c r="D135" s="420"/>
+      <c r="E135" s="420"/>
+      <c r="F135" s="420"/>
+      <c r="G135" s="420"/>
+      <c r="H135" s="420"/>
+      <c r="I135" s="420"/>
+      <c r="J135" s="421"/>
     </row>
     <row r="137" spans="3:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="138" spans="3:12" x14ac:dyDescent="0.25">
@@ -19125,11 +19125,11 @@
       <c r="G140" s="33" t="s">
         <v>164</v>
       </c>
-      <c r="H140" s="410">
+      <c r="H140" s="411">
         <v>61</v>
       </c>
-      <c r="I140" s="410"/>
-      <c r="J140" s="411"/>
+      <c r="I140" s="411"/>
+      <c r="J140" s="412"/>
       <c r="K140" s="324"/>
       <c r="L140" s="324"/>
     </row>
@@ -19148,40 +19148,40 @@
       <c r="L141" s="324"/>
     </row>
     <row r="142" spans="3:12" x14ac:dyDescent="0.25">
-      <c r="C142" s="412" t="s">
+      <c r="C142" s="413" t="s">
         <v>358</v>
       </c>
-      <c r="D142" s="413"/>
-      <c r="E142" s="413"/>
-      <c r="F142" s="413"/>
-      <c r="G142" s="413"/>
-      <c r="H142" s="413"/>
-      <c r="I142" s="413"/>
-      <c r="J142" s="414"/>
+      <c r="D142" s="414"/>
+      <c r="E142" s="414"/>
+      <c r="F142" s="414"/>
+      <c r="G142" s="414"/>
+      <c r="H142" s="414"/>
+      <c r="I142" s="414"/>
+      <c r="J142" s="415"/>
       <c r="K142" s="324"/>
       <c r="L142" s="324"/>
     </row>
     <row r="143" spans="3:12" x14ac:dyDescent="0.25">
-      <c r="C143" s="415"/>
-      <c r="D143" s="416"/>
-      <c r="E143" s="416"/>
-      <c r="F143" s="416"/>
-      <c r="G143" s="416"/>
-      <c r="H143" s="416"/>
-      <c r="I143" s="416"/>
-      <c r="J143" s="417"/>
+      <c r="C143" s="416"/>
+      <c r="D143" s="417"/>
+      <c r="E143" s="417"/>
+      <c r="F143" s="417"/>
+      <c r="G143" s="417"/>
+      <c r="H143" s="417"/>
+      <c r="I143" s="417"/>
+      <c r="J143" s="418"/>
       <c r="K143" s="324"/>
       <c r="L143" s="324"/>
     </row>
     <row r="144" spans="3:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C144" s="418"/>
-      <c r="D144" s="419"/>
-      <c r="E144" s="419"/>
-      <c r="F144" s="419"/>
-      <c r="G144" s="419"/>
-      <c r="H144" s="419"/>
-      <c r="I144" s="419"/>
-      <c r="J144" s="420"/>
+      <c r="C144" s="419"/>
+      <c r="D144" s="420"/>
+      <c r="E144" s="420"/>
+      <c r="F144" s="420"/>
+      <c r="G144" s="420"/>
+      <c r="H144" s="420"/>
+      <c r="I144" s="420"/>
+      <c r="J144" s="421"/>
     </row>
     <row r="146" spans="3:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="147" spans="3:12" x14ac:dyDescent="0.25">
@@ -19229,11 +19229,11 @@
       <c r="G149" s="33" t="s">
         <v>164</v>
       </c>
-      <c r="H149" s="410">
+      <c r="H149" s="411">
         <v>88</v>
       </c>
-      <c r="I149" s="410"/>
-      <c r="J149" s="411"/>
+      <c r="I149" s="411"/>
+      <c r="J149" s="412"/>
       <c r="K149" s="324"/>
       <c r="L149" s="324"/>
     </row>
@@ -19252,40 +19252,40 @@
       <c r="L150" s="324"/>
     </row>
     <row r="151" spans="3:12" x14ac:dyDescent="0.25">
-      <c r="C151" s="412" t="s">
+      <c r="C151" s="413" t="s">
         <v>359</v>
       </c>
-      <c r="D151" s="413"/>
-      <c r="E151" s="413"/>
-      <c r="F151" s="413"/>
-      <c r="G151" s="413"/>
-      <c r="H151" s="413"/>
-      <c r="I151" s="413"/>
-      <c r="J151" s="414"/>
+      <c r="D151" s="414"/>
+      <c r="E151" s="414"/>
+      <c r="F151" s="414"/>
+      <c r="G151" s="414"/>
+      <c r="H151" s="414"/>
+      <c r="I151" s="414"/>
+      <c r="J151" s="415"/>
       <c r="K151" s="324"/>
       <c r="L151" s="324"/>
     </row>
     <row r="152" spans="3:12" x14ac:dyDescent="0.25">
-      <c r="C152" s="415"/>
-      <c r="D152" s="416"/>
-      <c r="E152" s="416"/>
-      <c r="F152" s="416"/>
-      <c r="G152" s="416"/>
-      <c r="H152" s="416"/>
-      <c r="I152" s="416"/>
-      <c r="J152" s="417"/>
+      <c r="C152" s="416"/>
+      <c r="D152" s="417"/>
+      <c r="E152" s="417"/>
+      <c r="F152" s="417"/>
+      <c r="G152" s="417"/>
+      <c r="H152" s="417"/>
+      <c r="I152" s="417"/>
+      <c r="J152" s="418"/>
       <c r="K152" s="324"/>
       <c r="L152" s="324"/>
     </row>
     <row r="153" spans="3:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C153" s="418"/>
-      <c r="D153" s="419"/>
-      <c r="E153" s="419"/>
-      <c r="F153" s="419"/>
-      <c r="G153" s="419"/>
-      <c r="H153" s="419"/>
-      <c r="I153" s="419"/>
-      <c r="J153" s="420"/>
+      <c r="C153" s="419"/>
+      <c r="D153" s="420"/>
+      <c r="E153" s="420"/>
+      <c r="F153" s="420"/>
+      <c r="G153" s="420"/>
+      <c r="H153" s="420"/>
+      <c r="I153" s="420"/>
+      <c r="J153" s="421"/>
       <c r="K153" s="324"/>
       <c r="L153" s="324"/>
     </row>
@@ -19335,11 +19335,11 @@
       <c r="G158" s="33" t="s">
         <v>164</v>
       </c>
-      <c r="H158" s="410">
+      <c r="H158" s="411">
         <v>86</v>
       </c>
-      <c r="I158" s="410"/>
-      <c r="J158" s="411"/>
+      <c r="I158" s="411"/>
+      <c r="J158" s="412"/>
       <c r="K158" s="324"/>
       <c r="L158" s="324"/>
     </row>
@@ -19358,40 +19358,40 @@
       <c r="L159" s="324"/>
     </row>
     <row r="160" spans="3:12" x14ac:dyDescent="0.25">
-      <c r="C160" s="412" t="s">
+      <c r="C160" s="413" t="s">
         <v>360</v>
       </c>
-      <c r="D160" s="413"/>
-      <c r="E160" s="413"/>
-      <c r="F160" s="413"/>
-      <c r="G160" s="413"/>
-      <c r="H160" s="413"/>
-      <c r="I160" s="413"/>
-      <c r="J160" s="414"/>
+      <c r="D160" s="414"/>
+      <c r="E160" s="414"/>
+      <c r="F160" s="414"/>
+      <c r="G160" s="414"/>
+      <c r="H160" s="414"/>
+      <c r="I160" s="414"/>
+      <c r="J160" s="415"/>
       <c r="K160" s="324"/>
       <c r="L160" s="324"/>
     </row>
     <row r="161" spans="3:13" x14ac:dyDescent="0.25">
-      <c r="C161" s="415"/>
-      <c r="D161" s="416"/>
-      <c r="E161" s="416"/>
-      <c r="F161" s="416"/>
-      <c r="G161" s="416"/>
-      <c r="H161" s="416"/>
-      <c r="I161" s="416"/>
-      <c r="J161" s="417"/>
+      <c r="C161" s="416"/>
+      <c r="D161" s="417"/>
+      <c r="E161" s="417"/>
+      <c r="F161" s="417"/>
+      <c r="G161" s="417"/>
+      <c r="H161" s="417"/>
+      <c r="I161" s="417"/>
+      <c r="J161" s="418"/>
       <c r="K161" s="324"/>
       <c r="L161" s="324"/>
     </row>
     <row r="162" spans="3:13" ht="56.45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C162" s="418"/>
-      <c r="D162" s="419"/>
-      <c r="E162" s="419"/>
-      <c r="F162" s="419"/>
-      <c r="G162" s="419"/>
-      <c r="H162" s="419"/>
-      <c r="I162" s="419"/>
-      <c r="J162" s="420"/>
+      <c r="C162" s="419"/>
+      <c r="D162" s="420"/>
+      <c r="E162" s="420"/>
+      <c r="F162" s="420"/>
+      <c r="G162" s="420"/>
+      <c r="H162" s="420"/>
+      <c r="I162" s="420"/>
+      <c r="J162" s="421"/>
       <c r="K162" s="324"/>
       <c r="L162" s="324"/>
     </row>
@@ -19442,11 +19442,11 @@
       <c r="G167" s="33" t="s">
         <v>164</v>
       </c>
-      <c r="H167" s="410" t="s">
+      <c r="H167" s="411" t="s">
         <v>361</v>
       </c>
-      <c r="I167" s="410"/>
-      <c r="J167" s="411"/>
+      <c r="I167" s="411"/>
+      <c r="J167" s="412"/>
       <c r="K167" s="324"/>
       <c r="L167" s="324"/>
       <c r="M167" s="324"/>
@@ -19467,42 +19467,42 @@
       <c r="M168" s="324"/>
     </row>
     <row r="169" spans="3:13" x14ac:dyDescent="0.25">
-      <c r="C169" s="412" t="s">
+      <c r="C169" s="413" t="s">
         <v>362</v>
       </c>
-      <c r="D169" s="413"/>
-      <c r="E169" s="413"/>
-      <c r="F169" s="413"/>
-      <c r="G169" s="413"/>
-      <c r="H169" s="413"/>
-      <c r="I169" s="413"/>
-      <c r="J169" s="414"/>
+      <c r="D169" s="414"/>
+      <c r="E169" s="414"/>
+      <c r="F169" s="414"/>
+      <c r="G169" s="414"/>
+      <c r="H169" s="414"/>
+      <c r="I169" s="414"/>
+      <c r="J169" s="415"/>
       <c r="K169" s="324"/>
       <c r="L169" s="324"/>
       <c r="M169" s="324"/>
     </row>
     <row r="170" spans="3:13" x14ac:dyDescent="0.25">
-      <c r="C170" s="415"/>
-      <c r="D170" s="416"/>
-      <c r="E170" s="416"/>
-      <c r="F170" s="416"/>
-      <c r="G170" s="416"/>
-      <c r="H170" s="416"/>
-      <c r="I170" s="416"/>
-      <c r="J170" s="417"/>
+      <c r="C170" s="416"/>
+      <c r="D170" s="417"/>
+      <c r="E170" s="417"/>
+      <c r="F170" s="417"/>
+      <c r="G170" s="417"/>
+      <c r="H170" s="417"/>
+      <c r="I170" s="417"/>
+      <c r="J170" s="418"/>
       <c r="K170" s="324"/>
       <c r="L170" s="324"/>
       <c r="M170" s="324"/>
     </row>
     <row r="171" spans="3:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C171" s="418"/>
-      <c r="D171" s="419"/>
-      <c r="E171" s="419"/>
-      <c r="F171" s="419"/>
-      <c r="G171" s="419"/>
-      <c r="H171" s="419"/>
-      <c r="I171" s="419"/>
-      <c r="J171" s="420"/>
+      <c r="C171" s="419"/>
+      <c r="D171" s="420"/>
+      <c r="E171" s="420"/>
+      <c r="F171" s="420"/>
+      <c r="G171" s="420"/>
+      <c r="H171" s="420"/>
+      <c r="I171" s="420"/>
+      <c r="J171" s="421"/>
       <c r="K171" s="324"/>
       <c r="L171" s="324"/>
       <c r="M171" s="324"/>
@@ -19553,11 +19553,11 @@
       <c r="G176" s="33" t="s">
         <v>164</v>
       </c>
-      <c r="H176" s="410">
+      <c r="H176" s="411">
         <v>102</v>
       </c>
-      <c r="I176" s="410"/>
-      <c r="J176" s="411"/>
+      <c r="I176" s="411"/>
+      <c r="J176" s="412"/>
       <c r="K176" s="324"/>
       <c r="L176" s="324"/>
     </row>
@@ -19576,40 +19576,40 @@
       <c r="L177" s="324"/>
     </row>
     <row r="178" spans="3:13" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C178" s="412" t="s">
+      <c r="C178" s="413" t="s">
         <v>363</v>
       </c>
-      <c r="D178" s="413"/>
-      <c r="E178" s="413"/>
-      <c r="F178" s="413"/>
-      <c r="G178" s="413"/>
-      <c r="H178" s="413"/>
-      <c r="I178" s="413"/>
-      <c r="J178" s="414"/>
+      <c r="D178" s="414"/>
+      <c r="E178" s="414"/>
+      <c r="F178" s="414"/>
+      <c r="G178" s="414"/>
+      <c r="H178" s="414"/>
+      <c r="I178" s="414"/>
+      <c r="J178" s="415"/>
       <c r="K178" s="324"/>
       <c r="L178" s="324"/>
     </row>
     <row r="179" spans="3:13" x14ac:dyDescent="0.25">
-      <c r="C179" s="415"/>
-      <c r="D179" s="416"/>
-      <c r="E179" s="416"/>
-      <c r="F179" s="416"/>
-      <c r="G179" s="416"/>
-      <c r="H179" s="416"/>
-      <c r="I179" s="416"/>
-      <c r="J179" s="417"/>
+      <c r="C179" s="416"/>
+      <c r="D179" s="417"/>
+      <c r="E179" s="417"/>
+      <c r="F179" s="417"/>
+      <c r="G179" s="417"/>
+      <c r="H179" s="417"/>
+      <c r="I179" s="417"/>
+      <c r="J179" s="418"/>
       <c r="K179" s="324"/>
       <c r="L179" s="324"/>
     </row>
     <row r="180" spans="3:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C180" s="418"/>
-      <c r="D180" s="419"/>
-      <c r="E180" s="419"/>
-      <c r="F180" s="419"/>
-      <c r="G180" s="419"/>
-      <c r="H180" s="419"/>
-      <c r="I180" s="419"/>
-      <c r="J180" s="420"/>
+      <c r="C180" s="419"/>
+      <c r="D180" s="420"/>
+      <c r="E180" s="420"/>
+      <c r="F180" s="420"/>
+      <c r="G180" s="420"/>
+      <c r="H180" s="420"/>
+      <c r="I180" s="420"/>
+      <c r="J180" s="421"/>
     </row>
     <row r="182" spans="3:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="183" spans="3:13" x14ac:dyDescent="0.25">
@@ -19658,11 +19658,11 @@
       <c r="G185" s="33" t="s">
         <v>164</v>
       </c>
-      <c r="H185" s="410">
+      <c r="H185" s="411">
         <v>130</v>
       </c>
-      <c r="I185" s="410"/>
-      <c r="J185" s="411"/>
+      <c r="I185" s="411"/>
+      <c r="J185" s="412"/>
       <c r="K185" s="324"/>
       <c r="L185" s="324"/>
       <c r="M185" s="324"/>
@@ -19683,39 +19683,39 @@
       <c r="M186" s="324"/>
     </row>
     <row r="187" spans="3:13" x14ac:dyDescent="0.25">
-      <c r="C187" s="412" t="s">
+      <c r="C187" s="413" t="s">
         <v>364</v>
       </c>
-      <c r="D187" s="413"/>
-      <c r="E187" s="413"/>
-      <c r="F187" s="413"/>
-      <c r="G187" s="413"/>
-      <c r="H187" s="413"/>
-      <c r="I187" s="413"/>
-      <c r="J187" s="414"/>
+      <c r="D187" s="414"/>
+      <c r="E187" s="414"/>
+      <c r="F187" s="414"/>
+      <c r="G187" s="414"/>
+      <c r="H187" s="414"/>
+      <c r="I187" s="414"/>
+      <c r="J187" s="415"/>
       <c r="K187" s="324"/>
       <c r="L187" s="324"/>
       <c r="M187" s="324"/>
     </row>
     <row r="188" spans="3:13" x14ac:dyDescent="0.25">
-      <c r="C188" s="415"/>
-      <c r="D188" s="416"/>
-      <c r="E188" s="416"/>
-      <c r="F188" s="416"/>
-      <c r="G188" s="416"/>
-      <c r="H188" s="416"/>
-      <c r="I188" s="416"/>
-      <c r="J188" s="417"/>
+      <c r="C188" s="416"/>
+      <c r="D188" s="417"/>
+      <c r="E188" s="417"/>
+      <c r="F188" s="417"/>
+      <c r="G188" s="417"/>
+      <c r="H188" s="417"/>
+      <c r="I188" s="417"/>
+      <c r="J188" s="418"/>
     </row>
     <row r="189" spans="3:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C189" s="418"/>
-      <c r="D189" s="419"/>
-      <c r="E189" s="419"/>
-      <c r="F189" s="419"/>
-      <c r="G189" s="419"/>
-      <c r="H189" s="419"/>
-      <c r="I189" s="419"/>
-      <c r="J189" s="420"/>
+      <c r="C189" s="419"/>
+      <c r="D189" s="420"/>
+      <c r="E189" s="420"/>
+      <c r="F189" s="420"/>
+      <c r="G189" s="420"/>
+      <c r="H189" s="420"/>
+      <c r="I189" s="420"/>
+      <c r="J189" s="421"/>
     </row>
     <row r="191" spans="3:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="192" spans="3:13" x14ac:dyDescent="0.25">
@@ -19763,11 +19763,11 @@
       <c r="G194" s="33" t="s">
         <v>164</v>
       </c>
-      <c r="H194" s="410">
+      <c r="H194" s="411">
         <v>8</v>
       </c>
-      <c r="I194" s="410"/>
-      <c r="J194" s="411"/>
+      <c r="I194" s="411"/>
+      <c r="J194" s="412"/>
       <c r="K194" s="324"/>
       <c r="L194" s="324"/>
     </row>
@@ -19786,40 +19786,40 @@
       <c r="L195" s="324"/>
     </row>
     <row r="196" spans="3:12" x14ac:dyDescent="0.25">
-      <c r="C196" s="412" t="s">
+      <c r="C196" s="413" t="s">
         <v>366</v>
       </c>
-      <c r="D196" s="413"/>
-      <c r="E196" s="413"/>
-      <c r="F196" s="413"/>
-      <c r="G196" s="413"/>
-      <c r="H196" s="413"/>
-      <c r="I196" s="413"/>
-      <c r="J196" s="414"/>
+      <c r="D196" s="414"/>
+      <c r="E196" s="414"/>
+      <c r="F196" s="414"/>
+      <c r="G196" s="414"/>
+      <c r="H196" s="414"/>
+      <c r="I196" s="414"/>
+      <c r="J196" s="415"/>
       <c r="K196" s="324"/>
       <c r="L196" s="324"/>
     </row>
     <row r="197" spans="3:12" x14ac:dyDescent="0.25">
-      <c r="C197" s="415"/>
-      <c r="D197" s="416"/>
-      <c r="E197" s="416"/>
-      <c r="F197" s="416"/>
-      <c r="G197" s="416"/>
-      <c r="H197" s="416"/>
-      <c r="I197" s="416"/>
-      <c r="J197" s="417"/>
+      <c r="C197" s="416"/>
+      <c r="D197" s="417"/>
+      <c r="E197" s="417"/>
+      <c r="F197" s="417"/>
+      <c r="G197" s="417"/>
+      <c r="H197" s="417"/>
+      <c r="I197" s="417"/>
+      <c r="J197" s="418"/>
       <c r="K197" s="324"/>
       <c r="L197" s="324"/>
     </row>
     <row r="198" spans="3:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C198" s="418"/>
-      <c r="D198" s="419"/>
-      <c r="E198" s="419"/>
-      <c r="F198" s="419"/>
-      <c r="G198" s="419"/>
-      <c r="H198" s="419"/>
-      <c r="I198" s="419"/>
-      <c r="J198" s="420"/>
+      <c r="C198" s="419"/>
+      <c r="D198" s="420"/>
+      <c r="E198" s="420"/>
+      <c r="F198" s="420"/>
+      <c r="G198" s="420"/>
+      <c r="H198" s="420"/>
+      <c r="I198" s="420"/>
+      <c r="J198" s="421"/>
     </row>
     <row r="200" spans="3:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="201" spans="3:12" x14ac:dyDescent="0.25">
@@ -19865,11 +19865,11 @@
       <c r="G203" s="33" t="s">
         <v>164</v>
       </c>
-      <c r="H203" s="410">
+      <c r="H203" s="411">
         <v>96</v>
       </c>
-      <c r="I203" s="410"/>
-      <c r="J203" s="411"/>
+      <c r="I203" s="411"/>
+      <c r="J203" s="412"/>
       <c r="K203" s="324"/>
       <c r="L203" s="324"/>
     </row>
@@ -19888,38 +19888,38 @@
       <c r="L204" s="324"/>
     </row>
     <row r="205" spans="3:12" x14ac:dyDescent="0.25">
-      <c r="C205" s="412" t="s">
+      <c r="C205" s="413" t="s">
         <v>365</v>
       </c>
-      <c r="D205" s="413"/>
-      <c r="E205" s="413"/>
-      <c r="F205" s="413"/>
-      <c r="G205" s="413"/>
-      <c r="H205" s="413"/>
-      <c r="I205" s="413"/>
-      <c r="J205" s="414"/>
+      <c r="D205" s="414"/>
+      <c r="E205" s="414"/>
+      <c r="F205" s="414"/>
+      <c r="G205" s="414"/>
+      <c r="H205" s="414"/>
+      <c r="I205" s="414"/>
+      <c r="J205" s="415"/>
       <c r="K205" s="324"/>
       <c r="L205" s="324"/>
     </row>
     <row r="206" spans="3:12" x14ac:dyDescent="0.25">
-      <c r="C206" s="415"/>
-      <c r="D206" s="416"/>
-      <c r="E206" s="416"/>
-      <c r="F206" s="416"/>
-      <c r="G206" s="416"/>
-      <c r="H206" s="416"/>
-      <c r="I206" s="416"/>
-      <c r="J206" s="417"/>
+      <c r="C206" s="416"/>
+      <c r="D206" s="417"/>
+      <c r="E206" s="417"/>
+      <c r="F206" s="417"/>
+      <c r="G206" s="417"/>
+      <c r="H206" s="417"/>
+      <c r="I206" s="417"/>
+      <c r="J206" s="418"/>
     </row>
     <row r="207" spans="3:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C207" s="418"/>
-      <c r="D207" s="419"/>
-      <c r="E207" s="419"/>
-      <c r="F207" s="419"/>
-      <c r="G207" s="419"/>
-      <c r="H207" s="419"/>
-      <c r="I207" s="419"/>
-      <c r="J207" s="420"/>
+      <c r="C207" s="419"/>
+      <c r="D207" s="420"/>
+      <c r="E207" s="420"/>
+      <c r="F207" s="420"/>
+      <c r="G207" s="420"/>
+      <c r="H207" s="420"/>
+      <c r="I207" s="420"/>
+      <c r="J207" s="421"/>
     </row>
     <row r="209" spans="3:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="210" spans="3:12" x14ac:dyDescent="0.25">
@@ -19967,11 +19967,11 @@
       <c r="G212" s="33" t="s">
         <v>164</v>
       </c>
-      <c r="H212" s="410">
+      <c r="H212" s="411">
         <v>138</v>
       </c>
-      <c r="I212" s="410"/>
-      <c r="J212" s="411"/>
+      <c r="I212" s="411"/>
+      <c r="J212" s="412"/>
       <c r="K212" s="324"/>
       <c r="L212" s="324"/>
     </row>
@@ -19990,38 +19990,38 @@
       <c r="L213" s="324"/>
     </row>
     <row r="214" spans="3:12" x14ac:dyDescent="0.25">
-      <c r="C214" s="412" t="s">
-        <v>439</v>
-      </c>
-      <c r="D214" s="413"/>
-      <c r="E214" s="413"/>
-      <c r="F214" s="413"/>
-      <c r="G214" s="413"/>
-      <c r="H214" s="413"/>
-      <c r="I214" s="413"/>
-      <c r="J214" s="414"/>
+      <c r="C214" s="413" t="s">
+        <v>434</v>
+      </c>
+      <c r="D214" s="414"/>
+      <c r="E214" s="414"/>
+      <c r="F214" s="414"/>
+      <c r="G214" s="414"/>
+      <c r="H214" s="414"/>
+      <c r="I214" s="414"/>
+      <c r="J214" s="415"/>
       <c r="K214" s="324"/>
       <c r="L214" s="324"/>
     </row>
     <row r="215" spans="3:12" x14ac:dyDescent="0.25">
-      <c r="C215" s="415"/>
-      <c r="D215" s="416"/>
-      <c r="E215" s="416"/>
-      <c r="F215" s="416"/>
-      <c r="G215" s="416"/>
-      <c r="H215" s="416"/>
-      <c r="I215" s="416"/>
-      <c r="J215" s="417"/>
+      <c r="C215" s="416"/>
+      <c r="D215" s="417"/>
+      <c r="E215" s="417"/>
+      <c r="F215" s="417"/>
+      <c r="G215" s="417"/>
+      <c r="H215" s="417"/>
+      <c r="I215" s="417"/>
+      <c r="J215" s="418"/>
     </row>
     <row r="216" spans="3:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C216" s="418"/>
-      <c r="D216" s="419"/>
-      <c r="E216" s="419"/>
-      <c r="F216" s="419"/>
-      <c r="G216" s="419"/>
-      <c r="H216" s="419"/>
-      <c r="I216" s="419"/>
-      <c r="J216" s="420"/>
+      <c r="C216" s="419"/>
+      <c r="D216" s="420"/>
+      <c r="E216" s="420"/>
+      <c r="F216" s="420"/>
+      <c r="G216" s="420"/>
+      <c r="H216" s="420"/>
+      <c r="I216" s="420"/>
+      <c r="J216" s="421"/>
     </row>
     <row r="218" spans="3:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="219" spans="3:12" x14ac:dyDescent="0.25">
@@ -20069,11 +20069,11 @@
       <c r="G221" s="33" t="s">
         <v>164</v>
       </c>
-      <c r="H221" s="410">
+      <c r="H221" s="411">
         <v>7</v>
       </c>
-      <c r="I221" s="410"/>
-      <c r="J221" s="411"/>
+      <c r="I221" s="411"/>
+      <c r="J221" s="412"/>
       <c r="K221" s="324"/>
       <c r="L221" s="324"/>
     </row>
@@ -20092,40 +20092,40 @@
       <c r="L222" s="324"/>
     </row>
     <row r="223" spans="3:12" x14ac:dyDescent="0.25">
-      <c r="C223" s="412" t="s">
+      <c r="C223" s="413" t="s">
         <v>367</v>
       </c>
-      <c r="D223" s="413"/>
-      <c r="E223" s="413"/>
-      <c r="F223" s="413"/>
-      <c r="G223" s="413"/>
-      <c r="H223" s="413"/>
-      <c r="I223" s="413"/>
-      <c r="J223" s="414"/>
+      <c r="D223" s="414"/>
+      <c r="E223" s="414"/>
+      <c r="F223" s="414"/>
+      <c r="G223" s="414"/>
+      <c r="H223" s="414"/>
+      <c r="I223" s="414"/>
+      <c r="J223" s="415"/>
       <c r="K223" s="324"/>
       <c r="L223" s="324"/>
     </row>
     <row r="224" spans="3:12" x14ac:dyDescent="0.25">
-      <c r="C224" s="415"/>
-      <c r="D224" s="416"/>
-      <c r="E224" s="416"/>
-      <c r="F224" s="416"/>
-      <c r="G224" s="416"/>
-      <c r="H224" s="416"/>
-      <c r="I224" s="416"/>
-      <c r="J224" s="417"/>
+      <c r="C224" s="416"/>
+      <c r="D224" s="417"/>
+      <c r="E224" s="417"/>
+      <c r="F224" s="417"/>
+      <c r="G224" s="417"/>
+      <c r="H224" s="417"/>
+      <c r="I224" s="417"/>
+      <c r="J224" s="418"/>
       <c r="K224" s="324"/>
       <c r="L224" s="324"/>
     </row>
     <row r="225" spans="3:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C225" s="418"/>
-      <c r="D225" s="419"/>
-      <c r="E225" s="419"/>
-      <c r="F225" s="419"/>
-      <c r="G225" s="419"/>
-      <c r="H225" s="419"/>
-      <c r="I225" s="419"/>
-      <c r="J225" s="420"/>
+      <c r="C225" s="419"/>
+      <c r="D225" s="420"/>
+      <c r="E225" s="420"/>
+      <c r="F225" s="420"/>
+      <c r="G225" s="420"/>
+      <c r="H225" s="420"/>
+      <c r="I225" s="420"/>
+      <c r="J225" s="421"/>
       <c r="K225" s="324"/>
       <c r="L225" s="324"/>
     </row>
@@ -20175,11 +20175,11 @@
       <c r="G230" s="33" t="s">
         <v>164</v>
       </c>
-      <c r="H230" s="410">
+      <c r="H230" s="411">
         <v>70</v>
       </c>
-      <c r="I230" s="410"/>
-      <c r="J230" s="411"/>
+      <c r="I230" s="411"/>
+      <c r="J230" s="412"/>
       <c r="K230" s="324"/>
       <c r="L230" s="324"/>
     </row>
@@ -20198,40 +20198,40 @@
       <c r="L231" s="324"/>
     </row>
     <row r="232" spans="3:13" x14ac:dyDescent="0.25">
-      <c r="C232" s="412" t="s">
+      <c r="C232" s="413" t="s">
         <v>369</v>
       </c>
-      <c r="D232" s="413"/>
-      <c r="E232" s="413"/>
-      <c r="F232" s="413"/>
-      <c r="G232" s="413"/>
-      <c r="H232" s="413"/>
-      <c r="I232" s="413"/>
-      <c r="J232" s="414"/>
+      <c r="D232" s="414"/>
+      <c r="E232" s="414"/>
+      <c r="F232" s="414"/>
+      <c r="G232" s="414"/>
+      <c r="H232" s="414"/>
+      <c r="I232" s="414"/>
+      <c r="J232" s="415"/>
       <c r="K232" s="324"/>
       <c r="L232" s="324"/>
     </row>
     <row r="233" spans="3:13" x14ac:dyDescent="0.25">
-      <c r="C233" s="415"/>
-      <c r="D233" s="416"/>
-      <c r="E233" s="416"/>
-      <c r="F233" s="416"/>
-      <c r="G233" s="416"/>
-      <c r="H233" s="416"/>
-      <c r="I233" s="416"/>
-      <c r="J233" s="417"/>
+      <c r="C233" s="416"/>
+      <c r="D233" s="417"/>
+      <c r="E233" s="417"/>
+      <c r="F233" s="417"/>
+      <c r="G233" s="417"/>
+      <c r="H233" s="417"/>
+      <c r="I233" s="417"/>
+      <c r="J233" s="418"/>
       <c r="K233" s="324"/>
       <c r="L233" s="324"/>
     </row>
     <row r="234" spans="3:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C234" s="418"/>
-      <c r="D234" s="419"/>
-      <c r="E234" s="419"/>
-      <c r="F234" s="419"/>
-      <c r="G234" s="419"/>
-      <c r="H234" s="419"/>
-      <c r="I234" s="419"/>
-      <c r="J234" s="420"/>
+      <c r="C234" s="419"/>
+      <c r="D234" s="420"/>
+      <c r="E234" s="420"/>
+      <c r="F234" s="420"/>
+      <c r="G234" s="420"/>
+      <c r="H234" s="420"/>
+      <c r="I234" s="420"/>
+      <c r="J234" s="421"/>
       <c r="K234" s="324"/>
       <c r="L234" s="324"/>
     </row>
@@ -20284,11 +20284,11 @@
       <c r="G239" s="33" t="s">
         <v>164</v>
       </c>
-      <c r="H239" s="410">
+      <c r="H239" s="411">
         <v>109</v>
       </c>
-      <c r="I239" s="410"/>
-      <c r="J239" s="411"/>
+      <c r="I239" s="411"/>
+      <c r="J239" s="412"/>
       <c r="K239" s="327"/>
       <c r="L239" s="327"/>
       <c r="M239" s="57"/>
@@ -20309,83 +20309,44 @@
       <c r="M240" s="57"/>
     </row>
     <row r="241" spans="3:13" x14ac:dyDescent="0.25">
-      <c r="C241" s="412" t="s">
+      <c r="C241" s="413" t="s">
         <v>370</v>
       </c>
-      <c r="D241" s="413"/>
-      <c r="E241" s="413"/>
-      <c r="F241" s="413"/>
-      <c r="G241" s="413"/>
-      <c r="H241" s="413"/>
-      <c r="I241" s="413"/>
-      <c r="J241" s="414"/>
+      <c r="D241" s="414"/>
+      <c r="E241" s="414"/>
+      <c r="F241" s="414"/>
+      <c r="G241" s="414"/>
+      <c r="H241" s="414"/>
+      <c r="I241" s="414"/>
+      <c r="J241" s="415"/>
       <c r="K241" s="327"/>
       <c r="L241" s="327"/>
       <c r="M241" s="57"/>
     </row>
     <row r="242" spans="3:13" x14ac:dyDescent="0.25">
-      <c r="C242" s="415"/>
-      <c r="D242" s="416"/>
-      <c r="E242" s="416"/>
-      <c r="F242" s="416"/>
-      <c r="G242" s="416"/>
-      <c r="H242" s="416"/>
-      <c r="I242" s="416"/>
-      <c r="J242" s="417"/>
+      <c r="C242" s="416"/>
+      <c r="D242" s="417"/>
+      <c r="E242" s="417"/>
+      <c r="F242" s="417"/>
+      <c r="G242" s="417"/>
+      <c r="H242" s="417"/>
+      <c r="I242" s="417"/>
+      <c r="J242" s="418"/>
       <c r="K242" s="324"/>
       <c r="L242" s="324"/>
     </row>
     <row r="243" spans="3:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C243" s="418"/>
-      <c r="D243" s="419"/>
-      <c r="E243" s="419"/>
-      <c r="F243" s="419"/>
-      <c r="G243" s="419"/>
-      <c r="H243" s="419"/>
-      <c r="I243" s="419"/>
-      <c r="J243" s="420"/>
+      <c r="C243" s="419"/>
+      <c r="D243" s="420"/>
+      <c r="E243" s="420"/>
+      <c r="F243" s="420"/>
+      <c r="G243" s="420"/>
+      <c r="H243" s="420"/>
+      <c r="I243" s="420"/>
+      <c r="J243" s="421"/>
     </row>
   </sheetData>
   <mergeCells count="55">
-    <mergeCell ref="H203:J203"/>
-    <mergeCell ref="C205:J207"/>
-    <mergeCell ref="H230:J230"/>
-    <mergeCell ref="C232:J234"/>
-    <mergeCell ref="H221:J221"/>
-    <mergeCell ref="C223:J225"/>
-    <mergeCell ref="H212:J212"/>
-    <mergeCell ref="C214:J216"/>
-    <mergeCell ref="C178:J180"/>
-    <mergeCell ref="H185:J185"/>
-    <mergeCell ref="C187:J189"/>
-    <mergeCell ref="H194:J194"/>
-    <mergeCell ref="C196:J198"/>
-    <mergeCell ref="K65:M71"/>
-    <mergeCell ref="H49:J49"/>
-    <mergeCell ref="C51:J53"/>
-    <mergeCell ref="H58:J58"/>
-    <mergeCell ref="C60:J62"/>
-    <mergeCell ref="H67:J67"/>
-    <mergeCell ref="C69:J71"/>
-    <mergeCell ref="C24:J26"/>
-    <mergeCell ref="H31:J31"/>
-    <mergeCell ref="C33:J35"/>
-    <mergeCell ref="H4:J4"/>
-    <mergeCell ref="C6:J8"/>
-    <mergeCell ref="H13:J13"/>
-    <mergeCell ref="C15:J17"/>
-    <mergeCell ref="H22:J22"/>
-    <mergeCell ref="H40:J40"/>
-    <mergeCell ref="C42:J44"/>
-    <mergeCell ref="H131:J131"/>
-    <mergeCell ref="C133:J135"/>
-    <mergeCell ref="H122:J122"/>
-    <mergeCell ref="C124:J126"/>
-    <mergeCell ref="H113:J113"/>
-    <mergeCell ref="C115:J117"/>
-    <mergeCell ref="H104:J104"/>
-    <mergeCell ref="C106:J108"/>
-    <mergeCell ref="H85:J85"/>
     <mergeCell ref="H239:J239"/>
     <mergeCell ref="C241:J243"/>
     <mergeCell ref="C160:J162"/>
@@ -20402,6 +20363,45 @@
     <mergeCell ref="H167:J167"/>
     <mergeCell ref="C169:J171"/>
     <mergeCell ref="H176:J176"/>
+    <mergeCell ref="H40:J40"/>
+    <mergeCell ref="C42:J44"/>
+    <mergeCell ref="H131:J131"/>
+    <mergeCell ref="C133:J135"/>
+    <mergeCell ref="H122:J122"/>
+    <mergeCell ref="C124:J126"/>
+    <mergeCell ref="H113:J113"/>
+    <mergeCell ref="C115:J117"/>
+    <mergeCell ref="H104:J104"/>
+    <mergeCell ref="C106:J108"/>
+    <mergeCell ref="H85:J85"/>
+    <mergeCell ref="C24:J26"/>
+    <mergeCell ref="H31:J31"/>
+    <mergeCell ref="C33:J35"/>
+    <mergeCell ref="H4:J4"/>
+    <mergeCell ref="C6:J8"/>
+    <mergeCell ref="H13:J13"/>
+    <mergeCell ref="C15:J17"/>
+    <mergeCell ref="H22:J22"/>
+    <mergeCell ref="K65:M71"/>
+    <mergeCell ref="H49:J49"/>
+    <mergeCell ref="C51:J53"/>
+    <mergeCell ref="H58:J58"/>
+    <mergeCell ref="C60:J62"/>
+    <mergeCell ref="H67:J67"/>
+    <mergeCell ref="C69:J71"/>
+    <mergeCell ref="C178:J180"/>
+    <mergeCell ref="H185:J185"/>
+    <mergeCell ref="C187:J189"/>
+    <mergeCell ref="H194:J194"/>
+    <mergeCell ref="C196:J198"/>
+    <mergeCell ref="H203:J203"/>
+    <mergeCell ref="C205:J207"/>
+    <mergeCell ref="H230:J230"/>
+    <mergeCell ref="C232:J234"/>
+    <mergeCell ref="H221:J221"/>
+    <mergeCell ref="C223:J225"/>
+    <mergeCell ref="H212:J212"/>
+    <mergeCell ref="C214:J216"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/BRISAS/EXPENSAS/2026/JULIO/BRISAS-JULIO.xlsx
+++ b/BRISAS/EXPENSAS/2026/JULIO/BRISAS-JULIO.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistemax\Desktop\rc-consorcio2025\BRISAS\EXPENSAS\2026\JULIO\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{05C91EBF-EA56-4C3F-80C4-73862639885A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F429DE1F-BC21-43DE-81DE-36503A7E1E16}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="850" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="850" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RESUMEN" sheetId="1" r:id="rId1"/>
@@ -2792,73 +2792,11 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="17" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="17" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="30" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="30" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="8" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="8" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="8" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="8" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="8" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="8" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="8" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="8" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -2893,33 +2831,81 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="44" fontId="9" fillId="5" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="8" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="24" fillId="8" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="8" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="8" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="8" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="8" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="8" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="8" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="8" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="44" fontId="13" fillId="4" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="44" fontId="13" fillId="4" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="17" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="44" fontId="17" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="2" fillId="17" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="169" fontId="22" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="2" fillId="17" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="30" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="30" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="44" fontId="9" fillId="5" borderId="32" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="9" fillId="5" borderId="33" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="9" fillId="5" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="9" fillId="5" borderId="7" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="9" fillId="5" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="169" fontId="22" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="169" fontId="22" fillId="3" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -2978,10 +2964,24 @@
     <xf numFmtId="0" fontId="13" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="44" fontId="9" fillId="5" borderId="32" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="9" fillId="5" borderId="33" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="9" fillId="5" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="9" fillId="5" borderId="7" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="8" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="44" fontId="13" fillId="4" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="13" fillId="4" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="17" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="17" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -3448,34 +3448,34 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="375"/>
-      <c r="B1" s="370" t="s">
+      <c r="A1" s="353"/>
+      <c r="B1" s="348" t="s">
         <v>155</v>
       </c>
-      <c r="C1" s="371"/>
-      <c r="D1" s="371"/>
-      <c r="E1" s="372"/>
+      <c r="C1" s="349"/>
+      <c r="D1" s="349"/>
+      <c r="E1" s="350"/>
     </row>
     <row r="2" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="376"/>
-      <c r="B2" s="370" t="s">
+      <c r="A2" s="354"/>
+      <c r="B2" s="348" t="s">
         <v>157</v>
       </c>
-      <c r="C2" s="371"/>
-      <c r="D2" s="371"/>
-      <c r="E2" s="372"/>
+      <c r="C2" s="349"/>
+      <c r="D2" s="349"/>
+      <c r="E2" s="350"/>
     </row>
     <row r="3" spans="1:5" ht="32.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="376"/>
-      <c r="B3" s="367" t="s">
+      <c r="A3" s="354"/>
+      <c r="B3" s="345" t="s">
         <v>153</v>
       </c>
-      <c r="C3" s="368"/>
-      <c r="D3" s="368"/>
-      <c r="E3" s="369"/>
+      <c r="C3" s="346"/>
+      <c r="D3" s="346"/>
+      <c r="E3" s="347"/>
     </row>
     <row r="4" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="376"/>
+      <c r="A4" s="354"/>
       <c r="B4" s="43" t="s">
         <v>154</v>
       </c>
@@ -3484,7 +3484,7 @@
       <c r="E4" s="42"/>
     </row>
     <row r="5" spans="1:5" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="376"/>
+      <c r="A5" s="354"/>
       <c r="B5" s="46" t="s">
         <v>372</v>
       </c>
@@ -3493,7 +3493,7 @@
       <c r="E5" s="45"/>
     </row>
     <row r="6" spans="1:5" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="376"/>
+      <c r="A6" s="354"/>
       <c r="B6" s="47" t="s">
         <v>282</v>
       </c>
@@ -3502,7 +3502,7 @@
       <c r="E6" s="45"/>
     </row>
     <row r="7" spans="1:5" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="376"/>
+      <c r="A7" s="354"/>
       <c r="B7" s="47" t="s">
         <v>281</v>
       </c>
@@ -3511,13 +3511,13 @@
       <c r="E7" s="45"/>
     </row>
     <row r="8" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="377"/>
-      <c r="B8" s="373" t="s">
+      <c r="A8" s="355"/>
+      <c r="B8" s="351" t="s">
         <v>156</v>
       </c>
-      <c r="C8" s="373"/>
-      <c r="D8" s="373"/>
-      <c r="E8" s="374"/>
+      <c r="C8" s="351"/>
+      <c r="D8" s="351"/>
+      <c r="E8" s="352"/>
     </row>
     <row r="9" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="30"/>
@@ -3527,27 +3527,27 @@
       <c r="E9" s="30"/>
     </row>
     <row r="10" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="352" t="s">
+      <c r="A10" s="356" t="s">
         <v>371</v>
       </c>
-      <c r="B10" s="353"/>
-      <c r="C10" s="353"/>
-      <c r="D10" s="353"/>
-      <c r="E10" s="354"/>
+      <c r="B10" s="357"/>
+      <c r="C10" s="357"/>
+      <c r="D10" s="357"/>
+      <c r="E10" s="358"/>
     </row>
     <row r="11" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="355"/>
-      <c r="B11" s="356"/>
-      <c r="C11" s="356"/>
-      <c r="D11" s="356"/>
-      <c r="E11" s="357"/>
+      <c r="A11" s="359"/>
+      <c r="B11" s="360"/>
+      <c r="C11" s="360"/>
+      <c r="D11" s="360"/>
+      <c r="E11" s="361"/>
     </row>
     <row r="12" spans="1:5" ht="14.45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="358"/>
-      <c r="B12" s="359"/>
-      <c r="C12" s="359"/>
-      <c r="D12" s="359"/>
-      <c r="E12" s="360"/>
+      <c r="A12" s="362"/>
+      <c r="B12" s="363"/>
+      <c r="C12" s="363"/>
+      <c r="D12" s="363"/>
+      <c r="E12" s="364"/>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" s="30"/>
@@ -3564,34 +3564,34 @@
       <c r="E14" s="30"/>
     </row>
     <row r="15" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="361" t="s">
+      <c r="A15" s="365" t="s">
         <v>240</v>
       </c>
-      <c r="B15" s="361"/>
-      <c r="C15" s="361"/>
-      <c r="D15" s="361"/>
-      <c r="E15" s="361"/>
+      <c r="B15" s="365"/>
+      <c r="C15" s="365"/>
+      <c r="D15" s="365"/>
+      <c r="E15" s="365"/>
     </row>
     <row r="16" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="361"/>
-      <c r="B16" s="361"/>
-      <c r="C16" s="361"/>
-      <c r="D16" s="361"/>
-      <c r="E16" s="361"/>
+      <c r="A16" s="365"/>
+      <c r="B16" s="365"/>
+      <c r="C16" s="365"/>
+      <c r="D16" s="365"/>
+      <c r="E16" s="365"/>
     </row>
     <row r="17" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="361"/>
-      <c r="B17" s="361"/>
-      <c r="C17" s="361"/>
-      <c r="D17" s="361"/>
-      <c r="E17" s="361"/>
+      <c r="A17" s="365"/>
+      <c r="B17" s="365"/>
+      <c r="C17" s="365"/>
+      <c r="D17" s="365"/>
+      <c r="E17" s="365"/>
     </row>
     <row r="18" spans="1:8" ht="243" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="361"/>
-      <c r="B18" s="361"/>
-      <c r="C18" s="361"/>
-      <c r="D18" s="361"/>
-      <c r="E18" s="361"/>
+      <c r="A18" s="365"/>
+      <c r="B18" s="365"/>
+      <c r="C18" s="365"/>
+      <c r="D18" s="365"/>
+      <c r="E18" s="365"/>
     </row>
     <row r="19" spans="1:8" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A19" s="30"/>
@@ -3650,10 +3650,10 @@
       <c r="G24" s="252"/>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A25" s="363" t="s">
+      <c r="A25" s="366" t="s">
         <v>374</v>
       </c>
-      <c r="B25" s="364"/>
+      <c r="B25" s="367"/>
       <c r="C25" s="22"/>
       <c r="D25" s="266">
         <v>-491806.35</v>
@@ -3663,10 +3663,10 @@
       <c r="G25" s="253"/>
     </row>
     <row r="26" spans="1:8" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="365" t="s">
+      <c r="A26" s="368" t="s">
         <v>375</v>
       </c>
-      <c r="B26" s="366"/>
+      <c r="B26" s="369"/>
       <c r="C26" s="22"/>
       <c r="D26" s="266">
         <v>0</v>
@@ -3694,7 +3694,7 @@
       <c r="A28" s="342" t="s">
         <v>335</v>
       </c>
-      <c r="B28" s="343"/>
+      <c r="B28" s="344"/>
       <c r="C28" s="22"/>
       <c r="D28" s="333">
         <v>1520000</v>
@@ -3847,7 +3847,7 @@
       <c r="A38" s="342" t="s">
         <v>268</v>
       </c>
-      <c r="B38" s="343"/>
+      <c r="B38" s="344"/>
       <c r="C38" s="22"/>
       <c r="D38" s="198">
         <v>148518.18</v>
@@ -3862,7 +3862,7 @@
       <c r="A39" s="342" t="s">
         <v>269</v>
       </c>
-      <c r="B39" s="343"/>
+      <c r="B39" s="344"/>
       <c r="C39" s="22"/>
       <c r="D39" s="198">
         <v>7805</v>
@@ -3877,7 +3877,7 @@
       <c r="A40" s="342" t="s">
         <v>308</v>
       </c>
-      <c r="B40" s="343"/>
+      <c r="B40" s="344"/>
       <c r="C40" s="329"/>
       <c r="D40" s="198">
         <v>23573.47</v>
@@ -3892,7 +3892,7 @@
       <c r="A41" s="342" t="s">
         <v>308</v>
       </c>
-      <c r="B41" s="343"/>
+      <c r="B41" s="344"/>
       <c r="C41" s="22"/>
       <c r="D41" s="198">
         <v>26214.080000000002</v>
@@ -3932,7 +3932,7 @@
       <c r="A44" s="342" t="s">
         <v>439</v>
       </c>
-      <c r="B44" s="362"/>
+      <c r="B44" s="343"/>
       <c r="C44" s="101"/>
       <c r="D44" s="198">
         <v>46102546.960000001</v>
@@ -3951,7 +3951,7 @@
       <c r="A45" s="342" t="s">
         <v>413</v>
       </c>
-      <c r="B45" s="362"/>
+      <c r="B45" s="343"/>
       <c r="C45" s="101"/>
       <c r="D45" s="198">
         <v>5702320.7999999998</v>
@@ -3993,7 +3993,7 @@
       <c r="A48" s="342" t="s">
         <v>395</v>
       </c>
-      <c r="B48" s="362"/>
+      <c r="B48" s="343"/>
       <c r="C48" s="101"/>
       <c r="D48" s="198">
         <v>1472058.6</v>
@@ -4008,7 +4008,7 @@
       <c r="A49" s="342" t="s">
         <v>381</v>
       </c>
-      <c r="B49" s="362"/>
+      <c r="B49" s="343"/>
       <c r="C49" s="101"/>
       <c r="D49" s="198">
         <v>756250</v>
@@ -4023,7 +4023,7 @@
       <c r="A50" s="342" t="s">
         <v>396</v>
       </c>
-      <c r="B50" s="362"/>
+      <c r="B50" s="343"/>
       <c r="C50" s="101"/>
       <c r="D50" s="198">
         <v>97574.399999999994</v>
@@ -4038,7 +4038,7 @@
       <c r="A51" s="342" t="s">
         <v>407</v>
       </c>
-      <c r="B51" s="343"/>
+      <c r="B51" s="344"/>
       <c r="C51" s="102"/>
       <c r="D51" s="198">
         <v>6300000</v>
@@ -4053,7 +4053,7 @@
       <c r="A52" s="342" t="s">
         <v>378</v>
       </c>
-      <c r="B52" s="343"/>
+      <c r="B52" s="344"/>
       <c r="C52" s="102"/>
       <c r="D52" s="198">
         <v>228690</v>
@@ -4068,7 +4068,7 @@
       <c r="A53" s="342" t="s">
         <v>338</v>
       </c>
-      <c r="B53" s="343"/>
+      <c r="B53" s="344"/>
       <c r="C53" s="102"/>
       <c r="D53" s="198">
         <v>118400</v>
@@ -4083,7 +4083,7 @@
       <c r="A54" s="342" t="s">
         <v>436</v>
       </c>
-      <c r="B54" s="343"/>
+      <c r="B54" s="344"/>
       <c r="C54" s="102"/>
       <c r="D54" s="198">
         <v>0</v>
@@ -4096,7 +4096,7 @@
       <c r="A55" s="342" t="s">
         <v>431</v>
       </c>
-      <c r="B55" s="343"/>
+      <c r="B55" s="344"/>
       <c r="C55" s="102"/>
       <c r="D55" s="198">
         <v>820380</v>
@@ -4111,7 +4111,7 @@
       <c r="A56" s="342" t="s">
         <v>392</v>
       </c>
-      <c r="B56" s="343"/>
+      <c r="B56" s="344"/>
       <c r="C56" s="102"/>
       <c r="D56" s="198">
         <v>220000</v>
@@ -4126,7 +4126,7 @@
       <c r="A57" s="342" t="s">
         <v>398</v>
       </c>
-      <c r="B57" s="343"/>
+      <c r="B57" s="344"/>
       <c r="C57" s="102"/>
       <c r="D57" s="198">
         <v>110000</v>
@@ -4141,7 +4141,7 @@
       <c r="A58" s="342" t="s">
         <v>415</v>
       </c>
-      <c r="B58" s="343"/>
+      <c r="B58" s="344"/>
       <c r="C58" s="102"/>
       <c r="D58" s="198">
         <v>110000</v>
@@ -4156,7 +4156,7 @@
       <c r="A59" s="342" t="s">
         <v>416</v>
       </c>
-      <c r="B59" s="343"/>
+      <c r="B59" s="344"/>
       <c r="C59" s="102"/>
       <c r="D59" s="198">
         <v>110000</v>
@@ -4171,7 +4171,7 @@
       <c r="A60" s="342" t="s">
         <v>421</v>
       </c>
-      <c r="B60" s="343"/>
+      <c r="B60" s="344"/>
       <c r="C60" s="102"/>
       <c r="D60" s="198">
         <v>150000</v>
@@ -4186,7 +4186,7 @@
       <c r="A61" s="342" t="s">
         <v>379</v>
       </c>
-      <c r="B61" s="343"/>
+      <c r="B61" s="344"/>
       <c r="C61" s="102"/>
       <c r="D61" s="198">
         <v>1300000</v>
@@ -4201,7 +4201,7 @@
       <c r="A62" s="342" t="s">
         <v>408</v>
       </c>
-      <c r="B62" s="343"/>
+      <c r="B62" s="344"/>
       <c r="C62" s="22"/>
       <c r="D62" s="198">
         <v>2459883</v>
@@ -4242,7 +4242,7 @@
       <c r="A65" s="342" t="s">
         <v>397</v>
       </c>
-      <c r="B65" s="343"/>
+      <c r="B65" s="344"/>
       <c r="C65" s="22"/>
       <c r="D65" s="336">
         <v>120000</v>
@@ -4257,8 +4257,8 @@
       <c r="A66" s="342" t="s">
         <v>402</v>
       </c>
-      <c r="B66" s="362"/>
-      <c r="C66" s="343"/>
+      <c r="B66" s="343"/>
+      <c r="C66" s="344"/>
       <c r="D66" s="336">
         <v>350000</v>
       </c>
@@ -4272,8 +4272,8 @@
       <c r="A67" s="342" t="s">
         <v>435</v>
       </c>
-      <c r="B67" s="362"/>
-      <c r="C67" s="343"/>
+      <c r="B67" s="343"/>
+      <c r="C67" s="344"/>
       <c r="D67" s="336">
         <v>2120000</v>
       </c>
@@ -4287,7 +4287,7 @@
       <c r="A68" s="342" t="s">
         <v>410</v>
       </c>
-      <c r="B68" s="343"/>
+      <c r="B68" s="344"/>
       <c r="C68" s="22"/>
       <c r="D68" s="336">
         <v>1250000</v>
@@ -4302,7 +4302,7 @@
       <c r="A69" s="342" t="s">
         <v>437</v>
       </c>
-      <c r="B69" s="343"/>
+      <c r="B69" s="344"/>
       <c r="C69" s="98"/>
       <c r="D69" s="336">
         <v>75000</v>
@@ -4377,7 +4377,7 @@
       <c r="A74" s="342" t="s">
         <v>453</v>
       </c>
-      <c r="B74" s="343"/>
+      <c r="B74" s="344"/>
       <c r="C74" s="98"/>
       <c r="D74" s="336">
         <v>1465520</v>
@@ -4392,7 +4392,7 @@
       <c r="A75" s="342" t="s">
         <v>399</v>
       </c>
-      <c r="B75" s="343"/>
+      <c r="B75" s="344"/>
       <c r="C75" s="22"/>
       <c r="D75" s="337">
         <v>3179880</v>
@@ -4407,7 +4407,7 @@
       <c r="A76" s="342" t="s">
         <v>430</v>
       </c>
-      <c r="B76" s="343"/>
+      <c r="B76" s="344"/>
       <c r="C76" s="98"/>
       <c r="D76" s="337">
         <v>946220</v>
@@ -4422,7 +4422,7 @@
       <c r="A77" s="342" t="s">
         <v>417</v>
       </c>
-      <c r="B77" s="343"/>
+      <c r="B77" s="344"/>
       <c r="C77" s="98"/>
       <c r="D77" s="336">
         <v>1113200</v>
@@ -4437,7 +4437,7 @@
       <c r="A78" s="342" t="s">
         <v>418</v>
       </c>
-      <c r="B78" s="343"/>
+      <c r="B78" s="344"/>
       <c r="C78" s="98"/>
       <c r="D78" s="336">
         <v>749938.04</v>
@@ -4452,7 +4452,7 @@
       <c r="A79" s="342" t="s">
         <v>414</v>
       </c>
-      <c r="B79" s="343"/>
+      <c r="B79" s="344"/>
       <c r="C79" s="98"/>
       <c r="D79" s="336">
         <v>1113200</v>
@@ -4467,7 +4467,7 @@
       <c r="A80" s="342" t="s">
         <v>455</v>
       </c>
-      <c r="B80" s="343"/>
+      <c r="B80" s="344"/>
       <c r="C80" s="98"/>
       <c r="D80" s="336">
         <v>1669800</v>
@@ -4482,7 +4482,7 @@
       <c r="A81" s="342" t="s">
         <v>409</v>
       </c>
-      <c r="B81" s="343"/>
+      <c r="B81" s="344"/>
       <c r="C81" s="98"/>
       <c r="D81" s="336">
         <v>46300</v>
@@ -4497,7 +4497,7 @@
       <c r="A82" s="342" t="s">
         <v>393</v>
       </c>
-      <c r="B82" s="343"/>
+      <c r="B82" s="344"/>
       <c r="C82" s="98"/>
       <c r="D82" s="336">
         <v>95648.4</v>
@@ -4512,7 +4512,7 @@
       <c r="A83" s="342" t="s">
         <v>411</v>
       </c>
-      <c r="B83" s="343"/>
+      <c r="B83" s="344"/>
       <c r="C83" s="98"/>
       <c r="D83" s="336">
         <v>139099</v>
@@ -4527,7 +4527,7 @@
       <c r="A84" s="342" t="s">
         <v>465</v>
       </c>
-      <c r="B84" s="343"/>
+      <c r="B84" s="344"/>
       <c r="C84" s="98"/>
       <c r="D84" s="336">
         <v>1250000</v>
@@ -4542,7 +4542,7 @@
       <c r="A85" s="342" t="s">
         <v>466</v>
       </c>
-      <c r="B85" s="343"/>
+      <c r="B85" s="344"/>
       <c r="C85" s="98"/>
       <c r="D85" s="336">
         <v>1775000</v>
@@ -4557,7 +4557,7 @@
       <c r="A86" s="342" t="s">
         <v>467</v>
       </c>
-      <c r="B86" s="343"/>
+      <c r="B86" s="344"/>
       <c r="C86" s="98"/>
       <c r="D86" s="336">
         <v>1000000</v>
@@ -4572,7 +4572,7 @@
       <c r="A87" s="342" t="s">
         <v>468</v>
       </c>
-      <c r="B87" s="343"/>
+      <c r="B87" s="344"/>
       <c r="C87" s="98"/>
       <c r="D87" s="336">
         <v>1000000</v>
@@ -4587,7 +4587,7 @@
       <c r="A88" s="342" t="s">
         <v>469</v>
       </c>
-      <c r="B88" s="343"/>
+      <c r="B88" s="344"/>
       <c r="C88" s="98"/>
       <c r="D88" s="336">
         <v>1250000</v>
@@ -4602,7 +4602,7 @@
       <c r="A89" s="342" t="s">
         <v>387</v>
       </c>
-      <c r="B89" s="343"/>
+      <c r="B89" s="344"/>
       <c r="C89" s="98"/>
       <c r="D89" s="336">
         <v>20500</v>
@@ -4617,7 +4617,7 @@
       <c r="A90" s="342" t="s">
         <v>388</v>
       </c>
-      <c r="B90" s="343"/>
+      <c r="B90" s="344"/>
       <c r="C90" s="98"/>
       <c r="D90" s="336">
         <v>48500</v>
@@ -4632,7 +4632,7 @@
       <c r="A91" s="342" t="s">
         <v>427</v>
       </c>
-      <c r="B91" s="343"/>
+      <c r="B91" s="344"/>
       <c r="C91" s="98"/>
       <c r="D91" s="336">
         <v>315000</v>
@@ -4672,7 +4672,7 @@
       <c r="A94" s="342" t="s">
         <v>380</v>
       </c>
-      <c r="B94" s="343"/>
+      <c r="B94" s="344"/>
       <c r="C94" s="22"/>
       <c r="D94" s="338">
         <v>3218160</v>
@@ -4687,7 +4687,7 @@
       <c r="A95" s="342" t="s">
         <v>441</v>
       </c>
-      <c r="B95" s="343"/>
+      <c r="B95" s="344"/>
       <c r="C95" s="22"/>
       <c r="D95" s="339">
         <v>250000</v>
@@ -4829,7 +4829,7 @@
       <c r="A107" s="342" t="s">
         <v>337</v>
       </c>
-      <c r="B107" s="343"/>
+      <c r="B107" s="344"/>
       <c r="C107" s="22"/>
       <c r="D107" s="198">
         <v>397708.95</v>
@@ -4844,7 +4844,7 @@
       <c r="A108" s="342" t="s">
         <v>331</v>
       </c>
-      <c r="B108" s="343"/>
+      <c r="B108" s="344"/>
       <c r="C108" s="22"/>
       <c r="D108" s="198">
         <v>64376.63</v>
@@ -4859,7 +4859,7 @@
       <c r="A109" s="342" t="s">
         <v>332</v>
       </c>
-      <c r="B109" s="343"/>
+      <c r="B109" s="344"/>
       <c r="C109" s="22"/>
       <c r="D109" s="198">
         <v>64376.63</v>
@@ -4875,7 +4875,7 @@
       <c r="A110" s="342" t="s">
         <v>333</v>
       </c>
-      <c r="B110" s="343"/>
+      <c r="B110" s="344"/>
       <c r="C110" s="22"/>
       <c r="D110" s="198">
         <v>64581.58</v>
@@ -4888,10 +4888,10 @@
       <c r="G110" s="30"/>
     </row>
     <row r="111" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A111" s="344" t="s">
+      <c r="A111" s="370" t="s">
         <v>403</v>
       </c>
-      <c r="B111" s="345"/>
+      <c r="B111" s="371"/>
       <c r="C111" s="22"/>
       <c r="D111" s="198">
         <v>1314489.94</v>
@@ -4903,10 +4903,10 @@
       <c r="G111" s="30"/>
     </row>
     <row r="112" spans="1:7" ht="36.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A112" s="344" t="s">
+      <c r="A112" s="370" t="s">
         <v>404</v>
       </c>
-      <c r="B112" s="345"/>
+      <c r="B112" s="371"/>
       <c r="C112" s="22"/>
       <c r="D112" s="198">
         <v>458163.6</v>
@@ -4919,10 +4919,10 @@
       <c r="G112" s="30"/>
     </row>
     <row r="113" spans="1:7" ht="31.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A113" s="344" t="s">
+      <c r="A113" s="370" t="s">
         <v>405</v>
       </c>
-      <c r="B113" s="345"/>
+      <c r="B113" s="371"/>
       <c r="C113" s="22"/>
       <c r="D113" s="198">
         <v>124681.3</v>
@@ -4935,10 +4935,10 @@
       <c r="G113" s="30"/>
     </row>
     <row r="114" spans="1:7" ht="33.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A114" s="344" t="s">
+      <c r="A114" s="370" t="s">
         <v>406</v>
       </c>
-      <c r="B114" s="345"/>
+      <c r="B114" s="371"/>
       <c r="C114" s="22"/>
       <c r="D114" s="198">
         <v>92816.68</v>
@@ -4954,10 +4954,10 @@
       <c r="G114" s="30"/>
     </row>
     <row r="115" spans="1:7" ht="33.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A115" s="344" t="s">
+      <c r="A115" s="370" t="s">
         <v>401</v>
       </c>
-      <c r="B115" s="345"/>
+      <c r="B115" s="371"/>
       <c r="C115" s="22"/>
       <c r="D115" s="198">
         <v>646140</v>
@@ -4969,10 +4969,10 @@
       <c r="G115" s="30"/>
     </row>
     <row r="116" spans="1:7" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A116" s="344" t="s">
+      <c r="A116" s="370" t="s">
         <v>189</v>
       </c>
-      <c r="B116" s="345"/>
+      <c r="B116" s="371"/>
       <c r="C116" s="22"/>
       <c r="D116" s="198">
         <v>117933.22</v>
@@ -4985,10 +4985,10 @@
       <c r="G116" s="30"/>
     </row>
     <row r="117" spans="1:7" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A117" s="344" t="s">
+      <c r="A117" s="370" t="s">
         <v>300</v>
       </c>
-      <c r="B117" s="345"/>
+      <c r="B117" s="371"/>
       <c r="C117" s="22"/>
       <c r="D117" s="198">
         <v>8811.25</v>
@@ -5036,10 +5036,10 @@
       <c r="G120" s="30"/>
     </row>
     <row r="121" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A121" s="344" t="s">
+      <c r="A121" s="370" t="s">
         <v>428</v>
       </c>
-      <c r="B121" s="345"/>
+      <c r="B121" s="371"/>
       <c r="C121" s="22"/>
       <c r="D121" s="337">
         <v>9914839.9499999993</v>
@@ -5051,10 +5051,10 @@
       <c r="G121" s="30"/>
     </row>
     <row r="122" spans="1:7" ht="114" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A122" s="344" t="s">
+      <c r="A122" s="370" t="s">
         <v>386</v>
       </c>
-      <c r="B122" s="345"/>
+      <c r="B122" s="371"/>
       <c r="C122" s="22"/>
       <c r="D122" s="337">
         <v>15917020</v>
@@ -5069,7 +5069,7 @@
       <c r="A123" s="342" t="s">
         <v>425</v>
       </c>
-      <c r="B123" s="343"/>
+      <c r="B123" s="344"/>
       <c r="C123" s="22"/>
       <c r="D123" s="337">
         <v>8064666.6699999999</v>
@@ -5084,7 +5084,7 @@
       <c r="A124" s="342" t="s">
         <v>429</v>
       </c>
-      <c r="B124" s="343"/>
+      <c r="B124" s="344"/>
       <c r="C124" s="22"/>
       <c r="D124" s="337">
         <v>1071600</v>
@@ -5171,10 +5171,10 @@
       <c r="G131" s="30"/>
     </row>
     <row r="132" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A132" s="347" t="s">
+      <c r="A132" s="373" t="s">
         <v>440</v>
       </c>
-      <c r="B132" s="347"/>
+      <c r="B132" s="373"/>
       <c r="C132" s="22"/>
       <c r="D132" s="198">
         <f>2038428-1520000</f>
@@ -5189,7 +5189,7 @@
     </row>
     <row r="133" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A133" s="342"/>
-      <c r="B133" s="343"/>
+      <c r="B133" s="344"/>
       <c r="C133" s="98"/>
       <c r="D133" s="198"/>
       <c r="E133" s="26"/>
@@ -5493,10 +5493,10 @@
       <c r="F163" s="74"/>
     </row>
     <row r="164" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A164" s="350" t="s">
+      <c r="A164" s="376" t="s">
         <v>326</v>
       </c>
-      <c r="B164" s="351"/>
+      <c r="B164" s="377"/>
       <c r="C164" s="6"/>
       <c r="D164" s="13"/>
       <c r="E164" s="34"/>
@@ -5565,10 +5565,10 @@
       <c r="F170" s="74"/>
     </row>
     <row r="171" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A171" s="348" t="s">
+      <c r="A171" s="374" t="s">
         <v>292</v>
       </c>
-      <c r="B171" s="349"/>
+      <c r="B171" s="375"/>
       <c r="C171" s="6"/>
       <c r="D171" s="13"/>
       <c r="E171" s="34"/>
@@ -5875,16 +5875,16 @@
       <c r="F194" s="35"/>
     </row>
     <row r="195" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A195" s="346" t="s">
+      <c r="A195" s="372" t="s">
         <v>17</v>
       </c>
-      <c r="B195" s="346"/>
-      <c r="C195" s="346"/>
+      <c r="B195" s="372"/>
+      <c r="C195" s="372"/>
     </row>
     <row r="196" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A196" s="346"/>
-      <c r="B196" s="346"/>
-      <c r="C196" s="346"/>
+      <c r="A196" s="372"/>
+      <c r="B196" s="372"/>
+      <c r="C196" s="372"/>
     </row>
     <row r="197" spans="1:13" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A197" s="63"/>
@@ -5911,6 +5911,66 @@
     </row>
   </sheetData>
   <mergeCells count="76">
+    <mergeCell ref="A75:B75"/>
+    <mergeCell ref="A80:B80"/>
+    <mergeCell ref="A59:B59"/>
+    <mergeCell ref="A60:B60"/>
+    <mergeCell ref="A95:B95"/>
+    <mergeCell ref="A84:B84"/>
+    <mergeCell ref="A86:B86"/>
+    <mergeCell ref="A87:B87"/>
+    <mergeCell ref="A90:B90"/>
+    <mergeCell ref="A94:B94"/>
+    <mergeCell ref="A68:B68"/>
+    <mergeCell ref="A61:B61"/>
+    <mergeCell ref="A69:B69"/>
+    <mergeCell ref="A57:B57"/>
+    <mergeCell ref="A52:B52"/>
+    <mergeCell ref="A65:B65"/>
+    <mergeCell ref="A54:B54"/>
+    <mergeCell ref="A53:B53"/>
+    <mergeCell ref="A55:B55"/>
+    <mergeCell ref="A58:B58"/>
+    <mergeCell ref="A62:B62"/>
+    <mergeCell ref="A56:B56"/>
+    <mergeCell ref="A108:B108"/>
+    <mergeCell ref="A109:B109"/>
+    <mergeCell ref="A110:B110"/>
+    <mergeCell ref="A107:B107"/>
+    <mergeCell ref="A113:B113"/>
+    <mergeCell ref="A112:B112"/>
+    <mergeCell ref="A111:B111"/>
+    <mergeCell ref="A114:B114"/>
+    <mergeCell ref="A195:C196"/>
+    <mergeCell ref="A132:B132"/>
+    <mergeCell ref="A171:B171"/>
+    <mergeCell ref="A133:B133"/>
+    <mergeCell ref="A164:B164"/>
+    <mergeCell ref="A123:B123"/>
+    <mergeCell ref="A124:B124"/>
+    <mergeCell ref="A122:B122"/>
+    <mergeCell ref="A121:B121"/>
+    <mergeCell ref="A115:B115"/>
+    <mergeCell ref="A117:B117"/>
+    <mergeCell ref="A116:B116"/>
+    <mergeCell ref="A10:E12"/>
+    <mergeCell ref="A15:E18"/>
+    <mergeCell ref="A44:B44"/>
+    <mergeCell ref="A25:B25"/>
+    <mergeCell ref="A26:B26"/>
+    <mergeCell ref="A28:B28"/>
+    <mergeCell ref="A40:B40"/>
+    <mergeCell ref="B3:E3"/>
+    <mergeCell ref="B1:E1"/>
+    <mergeCell ref="B2:E2"/>
+    <mergeCell ref="B8:E8"/>
+    <mergeCell ref="A1:A8"/>
+    <mergeCell ref="A48:B48"/>
+    <mergeCell ref="A38:B38"/>
+    <mergeCell ref="A45:B45"/>
+    <mergeCell ref="A49:B49"/>
+    <mergeCell ref="A41:B41"/>
+    <mergeCell ref="A39:B39"/>
     <mergeCell ref="A50:B50"/>
     <mergeCell ref="A91:B91"/>
     <mergeCell ref="A83:B83"/>
@@ -5927,66 +5987,6 @@
     <mergeCell ref="A66:C66"/>
     <mergeCell ref="A67:C67"/>
     <mergeCell ref="A51:B51"/>
-    <mergeCell ref="A48:B48"/>
-    <mergeCell ref="A38:B38"/>
-    <mergeCell ref="A45:B45"/>
-    <mergeCell ref="A49:B49"/>
-    <mergeCell ref="A41:B41"/>
-    <mergeCell ref="A39:B39"/>
-    <mergeCell ref="B3:E3"/>
-    <mergeCell ref="B1:E1"/>
-    <mergeCell ref="B2:E2"/>
-    <mergeCell ref="B8:E8"/>
-    <mergeCell ref="A1:A8"/>
-    <mergeCell ref="A10:E12"/>
-    <mergeCell ref="A15:E18"/>
-    <mergeCell ref="A44:B44"/>
-    <mergeCell ref="A25:B25"/>
-    <mergeCell ref="A26:B26"/>
-    <mergeCell ref="A28:B28"/>
-    <mergeCell ref="A40:B40"/>
-    <mergeCell ref="A114:B114"/>
-    <mergeCell ref="A195:C196"/>
-    <mergeCell ref="A132:B132"/>
-    <mergeCell ref="A171:B171"/>
-    <mergeCell ref="A133:B133"/>
-    <mergeCell ref="A164:B164"/>
-    <mergeCell ref="A123:B123"/>
-    <mergeCell ref="A124:B124"/>
-    <mergeCell ref="A122:B122"/>
-    <mergeCell ref="A121:B121"/>
-    <mergeCell ref="A115:B115"/>
-    <mergeCell ref="A117:B117"/>
-    <mergeCell ref="A116:B116"/>
-    <mergeCell ref="A108:B108"/>
-    <mergeCell ref="A109:B109"/>
-    <mergeCell ref="A110:B110"/>
-    <mergeCell ref="A107:B107"/>
-    <mergeCell ref="A113:B113"/>
-    <mergeCell ref="A112:B112"/>
-    <mergeCell ref="A111:B111"/>
-    <mergeCell ref="A57:B57"/>
-    <mergeCell ref="A52:B52"/>
-    <mergeCell ref="A65:B65"/>
-    <mergeCell ref="A54:B54"/>
-    <mergeCell ref="A53:B53"/>
-    <mergeCell ref="A55:B55"/>
-    <mergeCell ref="A58:B58"/>
-    <mergeCell ref="A62:B62"/>
-    <mergeCell ref="A56:B56"/>
-    <mergeCell ref="A75:B75"/>
-    <mergeCell ref="A80:B80"/>
-    <mergeCell ref="A59:B59"/>
-    <mergeCell ref="A60:B60"/>
-    <mergeCell ref="A95:B95"/>
-    <mergeCell ref="A84:B84"/>
-    <mergeCell ref="A86:B86"/>
-    <mergeCell ref="A87:B87"/>
-    <mergeCell ref="A90:B90"/>
-    <mergeCell ref="A94:B94"/>
-    <mergeCell ref="A68:B68"/>
-    <mergeCell ref="A61:B61"/>
-    <mergeCell ref="A69:B69"/>
   </mergeCells>
   <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup paperSize="3" scale="115" orientation="portrait" r:id="rId1"/>
@@ -6026,27 +6026,27 @@
     <row r="1" spans="1:24" ht="251.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="2"/>
       <c r="B1" s="2"/>
-      <c r="C1" s="391" t="s">
+      <c r="C1" s="389" t="s">
         <v>463</v>
       </c>
-      <c r="D1" s="392"/>
-      <c r="E1" s="392"/>
-      <c r="F1" s="392"/>
-      <c r="G1" s="392"/>
-      <c r="H1" s="392"/>
-      <c r="I1" s="392"/>
-      <c r="J1" s="392"/>
-      <c r="K1" s="392"/>
-      <c r="L1" s="392"/>
+      <c r="D1" s="390"/>
+      <c r="E1" s="390"/>
+      <c r="F1" s="390"/>
+      <c r="G1" s="390"/>
+      <c r="H1" s="390"/>
+      <c r="I1" s="390"/>
+      <c r="J1" s="390"/>
+      <c r="K1" s="390"/>
+      <c r="L1" s="390"/>
       <c r="M1" s="142"/>
-      <c r="N1" s="393" t="s">
+      <c r="N1" s="391" t="s">
         <v>310</v>
       </c>
-      <c r="O1" s="393"/>
-      <c r="P1" s="388">
+      <c r="O1" s="391"/>
+      <c r="P1" s="386">
         <v>30000000</v>
       </c>
-      <c r="Q1" s="388"/>
+      <c r="Q1" s="386"/>
       <c r="R1" s="164"/>
       <c r="S1" s="4"/>
       <c r="T1" s="2"/>
@@ -6060,11 +6060,11 @@
     <row r="2" spans="1:24" ht="34.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="2"/>
       <c r="B2" s="2"/>
-      <c r="C2" s="390" t="s">
+      <c r="C2" s="388" t="s">
         <v>226</v>
       </c>
-      <c r="D2" s="390"/>
-      <c r="E2" s="390"/>
+      <c r="D2" s="388"/>
+      <c r="E2" s="388"/>
       <c r="F2" s="142"/>
       <c r="G2" s="385">
         <f>X2</f>
@@ -6085,10 +6085,10 @@
         <v>260</v>
       </c>
       <c r="O2" s="224"/>
-      <c r="P2" s="389">
-        <v>0</v>
-      </c>
-      <c r="Q2" s="389"/>
+      <c r="P2" s="387">
+        <v>0</v>
+      </c>
+      <c r="Q2" s="387"/>
       <c r="R2" s="165"/>
       <c r="T2" s="2"/>
       <c r="U2" t="s">
@@ -6100,112 +6100,112 @@
       </c>
     </row>
     <row r="3" spans="1:24" ht="91.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="398" t="str">
+      <c r="A3" s="396" t="str">
         <f>"ATENCIÓN: Si usted abona antes del " &amp; TEXT(RESUMEN!A10,"dd/mm/yyyy") &amp; ", deberá abonar el importe indicado en la columna de color naranja. En caso de abonar con posterioridad a dicha fecha, deberá abonar el monto indicado en la columna de color celeste."</f>
         <v>ATENCIÓN: Si usted abona antes del Primer Vencimiento:  17/08, deberá abonar el importe indicado en la columna de color naranja. En caso de abonar con posterioridad a dicha fecha, deberá abonar el monto indicado en la columna de color celeste.</v>
       </c>
-      <c r="B3" s="399"/>
-      <c r="C3" s="399"/>
-      <c r="D3" s="399"/>
-      <c r="E3" s="399"/>
-      <c r="F3" s="399"/>
-      <c r="G3" s="399"/>
-      <c r="H3" s="399"/>
-      <c r="I3" s="399"/>
-      <c r="J3" s="399"/>
-      <c r="K3" s="399"/>
-      <c r="L3" s="399"/>
-      <c r="M3" s="399"/>
-      <c r="N3" s="399"/>
-      <c r="O3" s="399"/>
-      <c r="P3" s="399"/>
-      <c r="Q3" s="399"/>
-      <c r="R3" s="399"/>
-      <c r="S3" s="399"/>
-      <c r="T3" s="400"/>
+      <c r="B3" s="397"/>
+      <c r="C3" s="397"/>
+      <c r="D3" s="397"/>
+      <c r="E3" s="397"/>
+      <c r="F3" s="397"/>
+      <c r="G3" s="397"/>
+      <c r="H3" s="397"/>
+      <c r="I3" s="397"/>
+      <c r="J3" s="397"/>
+      <c r="K3" s="397"/>
+      <c r="L3" s="397"/>
+      <c r="M3" s="397"/>
+      <c r="N3" s="397"/>
+      <c r="O3" s="397"/>
+      <c r="P3" s="397"/>
+      <c r="Q3" s="397"/>
+      <c r="R3" s="397"/>
+      <c r="S3" s="397"/>
+      <c r="T3" s="398"/>
       <c r="X3" s="37"/>
     </row>
     <row r="4" spans="1:24" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="401" t="s">
-        <v>0</v>
-      </c>
-      <c r="B4" s="403" t="s">
+      <c r="A4" s="399" t="s">
+        <v>0</v>
+      </c>
+      <c r="B4" s="401" t="s">
         <v>1</v>
       </c>
-      <c r="C4" s="403" t="s">
+      <c r="C4" s="401" t="s">
         <v>2</v>
       </c>
-      <c r="D4" s="403" t="s">
+      <c r="D4" s="401" t="s">
         <v>6</v>
       </c>
-      <c r="E4" s="386" t="s">
+      <c r="E4" s="378" t="s">
         <v>181</v>
       </c>
-      <c r="F4" s="403" t="s">
+      <c r="F4" s="401" t="s">
         <v>3</v>
       </c>
-      <c r="G4" s="405" t="s">
+      <c r="G4" s="403" t="s">
         <v>16</v>
       </c>
-      <c r="H4" s="386" t="s">
+      <c r="H4" s="378" t="s">
         <v>232</v>
       </c>
-      <c r="I4" s="386" t="s">
+      <c r="I4" s="378" t="s">
         <v>15</v>
       </c>
-      <c r="J4" s="386"/>
-      <c r="K4" s="386" t="s">
+      <c r="J4" s="378"/>
+      <c r="K4" s="378" t="s">
         <v>182</v>
       </c>
-      <c r="L4" s="386" t="s">
+      <c r="L4" s="378" t="s">
         <v>146</v>
       </c>
-      <c r="M4" s="386" t="s">
+      <c r="M4" s="378" t="s">
         <v>184</v>
       </c>
-      <c r="N4" s="386" t="s">
+      <c r="N4" s="378" t="s">
         <v>183</v>
       </c>
-      <c r="O4" s="386" t="s">
+      <c r="O4" s="378" t="s">
         <v>320</v>
       </c>
-      <c r="P4" s="394" t="s">
+      <c r="P4" s="392" t="s">
         <v>318</v>
       </c>
-      <c r="Q4" s="395"/>
-      <c r="R4" s="394" t="s">
+      <c r="Q4" s="393"/>
+      <c r="R4" s="392" t="s">
         <v>313</v>
       </c>
-      <c r="S4" s="395"/>
-      <c r="T4" s="386" t="s">
+      <c r="S4" s="393"/>
+      <c r="T4" s="378" t="s">
         <v>258</v>
       </c>
       <c r="U4" s="13"/>
     </row>
     <row r="5" spans="1:24" ht="25.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="402"/>
-      <c r="B5" s="404"/>
-      <c r="C5" s="404"/>
-      <c r="D5" s="404"/>
-      <c r="E5" s="387"/>
-      <c r="F5" s="404"/>
-      <c r="G5" s="406"/>
-      <c r="H5" s="387"/>
-      <c r="I5" s="387"/>
-      <c r="J5" s="387"/>
-      <c r="K5" s="387"/>
-      <c r="L5" s="387"/>
-      <c r="M5" s="387"/>
-      <c r="N5" s="387"/>
-      <c r="O5" s="387"/>
-      <c r="P5" s="396" t="str">
+      <c r="A5" s="400"/>
+      <c r="B5" s="402"/>
+      <c r="C5" s="402"/>
+      <c r="D5" s="402"/>
+      <c r="E5" s="379"/>
+      <c r="F5" s="402"/>
+      <c r="G5" s="404"/>
+      <c r="H5" s="379"/>
+      <c r="I5" s="379"/>
+      <c r="J5" s="379"/>
+      <c r="K5" s="379"/>
+      <c r="L5" s="379"/>
+      <c r="M5" s="379"/>
+      <c r="N5" s="379"/>
+      <c r="O5" s="379"/>
+      <c r="P5" s="394" t="str">
         <f>RESUMEN!A10</f>
         <v>Primer Vencimiento:  17/08</v>
       </c>
-      <c r="Q5" s="397"/>
-      <c r="R5" s="396"/>
-      <c r="S5" s="397"/>
-      <c r="T5" s="387"/>
+      <c r="Q5" s="395"/>
+      <c r="R5" s="394"/>
+      <c r="S5" s="395"/>
+      <c r="T5" s="379"/>
     </row>
     <row r="6" spans="1:24" ht="26.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="184"/>
@@ -6258,11 +6258,11 @@
       <c r="O6" s="185">
         <v>0</v>
       </c>
-      <c r="P6" s="407">
+      <c r="P6" s="380">
         <f t="shared" ref="P6:P37" si="2">ROUND(SUM(G6:O6),0) + S6</f>
         <v>759748.01</v>
       </c>
-      <c r="Q6" s="408"/>
+      <c r="Q6" s="381"/>
       <c r="R6" s="226">
         <f t="shared" ref="R6:R37" si="3">ROUND(P6+P6*3.033%,0) + S6</f>
         <v>782791.01</v>
@@ -6328,11 +6328,11 @@
       <c r="O7" s="185">
         <v>0</v>
       </c>
-      <c r="P7" s="409">
+      <c r="P7" s="382">
         <f t="shared" si="2"/>
         <v>3658299.02</v>
       </c>
-      <c r="Q7" s="410"/>
+      <c r="Q7" s="383"/>
       <c r="R7" s="226">
         <f t="shared" si="3"/>
         <v>3769255.02</v>
@@ -6397,11 +6397,11 @@
       <c r="O8" s="185">
         <v>0</v>
       </c>
-      <c r="P8" s="378">
+      <c r="P8" s="384">
         <f t="shared" si="2"/>
         <v>737362.03</v>
       </c>
-      <c r="Q8" s="378"/>
+      <c r="Q8" s="384"/>
       <c r="R8" s="226">
         <f t="shared" si="3"/>
         <v>759726.03</v>
@@ -6470,11 +6470,11 @@
       <c r="O9" s="185">
         <v>0</v>
       </c>
-      <c r="P9" s="378">
+      <c r="P9" s="384">
         <f t="shared" si="2"/>
         <v>3191997.04</v>
       </c>
-      <c r="Q9" s="378"/>
+      <c r="Q9" s="384"/>
       <c r="R9" s="226">
         <f t="shared" si="3"/>
         <v>3288810.04</v>
@@ -6544,11 +6544,11 @@
       <c r="O10" s="185">
         <v>0</v>
       </c>
-      <c r="P10" s="378">
+      <c r="P10" s="384">
         <f t="shared" si="2"/>
         <v>767816.05</v>
       </c>
-      <c r="Q10" s="378"/>
+      <c r="Q10" s="384"/>
       <c r="R10" s="226">
         <f t="shared" si="3"/>
         <v>791104.05</v>
@@ -6615,11 +6615,11 @@
       <c r="O11" s="185">
         <v>0</v>
       </c>
-      <c r="P11" s="378">
+      <c r="P11" s="384">
         <f t="shared" si="2"/>
         <v>751681.06</v>
       </c>
-      <c r="Q11" s="378"/>
+      <c r="Q11" s="384"/>
       <c r="R11" s="226">
         <f t="shared" si="3"/>
         <v>774480.06</v>
@@ -6687,11 +6687,11 @@
       <c r="O12" s="185">
         <v>0</v>
       </c>
-      <c r="P12" s="378">
+      <c r="P12" s="384">
         <f t="shared" si="2"/>
         <v>625812.06999999995</v>
       </c>
-      <c r="Q12" s="378"/>
+      <c r="Q12" s="384"/>
       <c r="R12" s="226">
         <f t="shared" si="3"/>
         <v>644793.06999999995</v>
@@ -6759,11 +6759,11 @@
       <c r="O13" s="185">
         <v>0</v>
       </c>
-      <c r="P13" s="378">
+      <c r="P13" s="384">
         <f t="shared" si="2"/>
         <v>763050.08</v>
       </c>
-      <c r="Q13" s="378"/>
+      <c r="Q13" s="384"/>
       <c r="R13" s="226">
         <f t="shared" si="3"/>
         <v>786193.08</v>
@@ -6831,11 +6831,11 @@
       <c r="O14" s="185">
         <v>0</v>
       </c>
-      <c r="P14" s="378">
+      <c r="P14" s="384">
         <f t="shared" si="2"/>
         <v>759482.09</v>
       </c>
-      <c r="Q14" s="378"/>
+      <c r="Q14" s="384"/>
       <c r="R14" s="226">
         <f t="shared" si="3"/>
         <v>782517.09</v>
@@ -6900,11 +6900,11 @@
       <c r="O15" s="185">
         <v>0</v>
       </c>
-      <c r="P15" s="378">
+      <c r="P15" s="384">
         <f t="shared" si="2"/>
         <v>744528.1</v>
       </c>
-      <c r="Q15" s="378"/>
+      <c r="Q15" s="384"/>
       <c r="R15" s="226">
         <f t="shared" si="3"/>
         <v>767110.1</v>
@@ -6972,11 +6972,11 @@
       <c r="O16" s="185">
         <v>0</v>
       </c>
-      <c r="P16" s="378">
+      <c r="P16" s="384">
         <f t="shared" si="2"/>
         <v>745214.11</v>
       </c>
-      <c r="Q16" s="378"/>
+      <c r="Q16" s="384"/>
       <c r="R16" s="226">
         <f t="shared" si="3"/>
         <v>767816.11</v>
@@ -7045,11 +7045,11 @@
       <c r="O17" s="185">
         <v>0</v>
       </c>
-      <c r="P17" s="378">
+      <c r="P17" s="384">
         <f t="shared" si="2"/>
         <v>4564903.12</v>
       </c>
-      <c r="Q17" s="378"/>
+      <c r="Q17" s="384"/>
       <c r="R17" s="226">
         <f t="shared" si="3"/>
         <v>4703357.12</v>
@@ -7118,11 +7118,11 @@
       <c r="O18" s="185">
         <v>0</v>
       </c>
-      <c r="P18" s="378">
+      <c r="P18" s="384">
         <f t="shared" si="2"/>
         <v>759748.13</v>
       </c>
-      <c r="Q18" s="378"/>
+      <c r="Q18" s="384"/>
       <c r="R18" s="226">
         <f t="shared" si="3"/>
         <v>782791.13</v>
@@ -7188,11 +7188,11 @@
       <c r="O19" s="341">
         <v>223900</v>
       </c>
-      <c r="P19" s="378">
+      <c r="P19" s="384">
         <f t="shared" si="2"/>
         <v>991716.14</v>
       </c>
-      <c r="Q19" s="378"/>
+      <c r="Q19" s="384"/>
       <c r="R19" s="226">
         <f t="shared" si="3"/>
         <v>1021795.14</v>
@@ -7261,11 +7261,11 @@
       <c r="O20" s="185">
         <v>0</v>
       </c>
-      <c r="P20" s="378">
+      <c r="P20" s="384">
         <f t="shared" si="2"/>
         <v>743613.15</v>
       </c>
-      <c r="Q20" s="378"/>
+      <c r="Q20" s="384"/>
       <c r="R20" s="226">
         <f t="shared" si="3"/>
         <v>766167.15</v>
@@ -7334,11 +7334,11 @@
       <c r="O21" s="185">
         <v>0</v>
       </c>
-      <c r="P21" s="378">
+      <c r="P21" s="384">
         <f t="shared" si="2"/>
         <v>759748.16</v>
       </c>
-      <c r="Q21" s="378"/>
+      <c r="Q21" s="384"/>
       <c r="R21" s="226">
         <f t="shared" si="3"/>
         <v>782791.16</v>
@@ -7403,11 +7403,11 @@
       <c r="O22" s="185">
         <v>0</v>
       </c>
-      <c r="P22" s="378">
+      <c r="P22" s="384">
         <f t="shared" si="2"/>
         <v>629697.17000000004</v>
       </c>
-      <c r="Q22" s="378"/>
+      <c r="Q22" s="384"/>
       <c r="R22" s="226">
         <f t="shared" si="3"/>
         <v>648796.17000000004</v>
@@ -7476,11 +7476,11 @@
       <c r="O23" s="185">
         <v>0</v>
       </c>
-      <c r="P23" s="378">
+      <c r="P23" s="384">
         <f t="shared" si="2"/>
         <v>759748.18</v>
       </c>
-      <c r="Q23" s="378"/>
+      <c r="Q23" s="384"/>
       <c r="R23" s="226">
         <f t="shared" si="3"/>
         <v>782791.18</v>
@@ -7549,11 +7549,11 @@
       <c r="O24" s="185">
         <v>0</v>
       </c>
-      <c r="P24" s="378">
+      <c r="P24" s="384">
         <f t="shared" si="2"/>
         <v>767816.19</v>
       </c>
-      <c r="Q24" s="378"/>
+      <c r="Q24" s="384"/>
       <c r="R24" s="226">
         <f t="shared" si="3"/>
         <v>791104.19</v>
@@ -7619,11 +7619,11 @@
       <c r="O25" s="185">
         <v>0</v>
       </c>
-      <c r="P25" s="378">
+      <c r="P25" s="384">
         <f t="shared" si="2"/>
         <v>767816.2</v>
       </c>
-      <c r="Q25" s="378"/>
+      <c r="Q25" s="384"/>
       <c r="R25" s="226">
         <f t="shared" si="3"/>
         <v>791104.2</v>
@@ -7689,11 +7689,11 @@
       <c r="O26" s="185">
         <v>0</v>
       </c>
-      <c r="P26" s="378">
+      <c r="P26" s="384">
         <f t="shared" si="2"/>
         <v>767816.21</v>
       </c>
-      <c r="Q26" s="378"/>
+      <c r="Q26" s="384"/>
       <c r="R26" s="226">
         <f t="shared" si="3"/>
         <v>791104.21</v>
@@ -7764,11 +7764,11 @@
       <c r="O27" s="185">
         <v>0</v>
       </c>
-      <c r="P27" s="378">
+      <c r="P27" s="384">
         <f t="shared" si="2"/>
         <v>745213.22</v>
       </c>
-      <c r="Q27" s="378"/>
+      <c r="Q27" s="384"/>
       <c r="R27" s="226">
         <f t="shared" si="3"/>
         <v>767816.22</v>
@@ -7836,11 +7836,11 @@
       <c r="O28" s="185">
         <v>0</v>
       </c>
-      <c r="P28" s="378">
+      <c r="P28" s="384">
         <f t="shared" si="2"/>
         <v>745264.23</v>
       </c>
-      <c r="Q28" s="378"/>
+      <c r="Q28" s="384"/>
       <c r="R28" s="226">
         <f t="shared" si="3"/>
         <v>767868.23</v>
@@ -7908,11 +7908,11 @@
       <c r="O29" s="185">
         <v>0</v>
       </c>
-      <c r="P29" s="378">
+      <c r="P29" s="384">
         <f t="shared" si="2"/>
         <v>745213.24</v>
       </c>
-      <c r="Q29" s="378"/>
+      <c r="Q29" s="384"/>
       <c r="R29" s="226">
         <f t="shared" si="3"/>
         <v>767816.24</v>
@@ -7981,11 +7981,11 @@
       <c r="O30" s="185">
         <v>0</v>
       </c>
-      <c r="P30" s="378">
+      <c r="P30" s="384">
         <f t="shared" si="2"/>
         <v>775884.25</v>
       </c>
-      <c r="Q30" s="378"/>
+      <c r="Q30" s="384"/>
       <c r="R30" s="226">
         <f t="shared" si="3"/>
         <v>799417.25</v>
@@ -8053,11 +8053,11 @@
       <c r="O31" s="185">
         <v>0</v>
       </c>
-      <c r="P31" s="378">
+      <c r="P31" s="384">
         <f t="shared" si="2"/>
         <v>775884.26</v>
       </c>
-      <c r="Q31" s="378"/>
+      <c r="Q31" s="384"/>
       <c r="R31" s="226">
         <f t="shared" si="3"/>
         <v>799417.26</v>
@@ -8126,11 +8126,11 @@
       <c r="O32" s="185">
         <v>0</v>
       </c>
-      <c r="P32" s="378">
+      <c r="P32" s="384">
         <f t="shared" si="2"/>
         <v>775884.27</v>
       </c>
-      <c r="Q32" s="378"/>
+      <c r="Q32" s="384"/>
       <c r="R32" s="226">
         <f t="shared" si="3"/>
         <v>799417.27</v>
@@ -8195,11 +8195,11 @@
       <c r="O33" s="185">
         <v>0</v>
       </c>
-      <c r="P33" s="378">
+      <c r="P33" s="384">
         <f t="shared" si="2"/>
         <v>728196.28</v>
       </c>
-      <c r="Q33" s="378"/>
+      <c r="Q33" s="384"/>
       <c r="R33" s="226">
         <f t="shared" si="3"/>
         <v>750282.28</v>
@@ -8267,11 +8267,11 @@
       <c r="O34" s="185">
         <v>0</v>
       </c>
-      <c r="P34" s="378">
+      <c r="P34" s="384">
         <f t="shared" si="2"/>
         <v>753043.29</v>
       </c>
-      <c r="Q34" s="378"/>
+      <c r="Q34" s="384"/>
       <c r="R34" s="226">
         <f t="shared" si="3"/>
         <v>775883.29</v>
@@ -8339,11 +8339,11 @@
       <c r="O35" s="185">
         <v>0</v>
       </c>
-      <c r="P35" s="378">
+      <c r="P35" s="384">
         <f t="shared" si="2"/>
         <v>729553.3</v>
       </c>
-      <c r="Q35" s="378"/>
+      <c r="Q35" s="384"/>
       <c r="R35" s="226">
         <f t="shared" si="3"/>
         <v>751681.3</v>
@@ -8409,11 +8409,11 @@
       <c r="O36" s="185">
         <v>0</v>
       </c>
-      <c r="P36" s="378">
+      <c r="P36" s="384">
         <f t="shared" si="2"/>
         <v>2403472.31</v>
       </c>
-      <c r="Q36" s="378"/>
+      <c r="Q36" s="384"/>
       <c r="R36" s="226">
         <f t="shared" si="3"/>
         <v>2476370.31</v>
@@ -8482,11 +8482,11 @@
       <c r="O37" s="185">
         <v>0</v>
       </c>
-      <c r="P37" s="378">
+      <c r="P37" s="384">
         <f t="shared" si="2"/>
         <v>618525.31999999995</v>
       </c>
-      <c r="Q37" s="378"/>
+      <c r="Q37" s="384"/>
       <c r="R37" s="226">
         <f t="shared" si="3"/>
         <v>637285.31999999995</v>
@@ -8551,11 +8551,11 @@
       <c r="O38" s="185">
         <v>0</v>
       </c>
-      <c r="P38" s="378">
+      <c r="P38" s="384">
         <f t="shared" ref="P38:P69" si="13">ROUND(SUM(G38:O38),0) + S38</f>
         <v>751681.33</v>
       </c>
-      <c r="Q38" s="378"/>
+      <c r="Q38" s="384"/>
       <c r="R38" s="226">
         <f t="shared" ref="R38:R69" si="14">ROUND(P38+P38*3.033%,0) + S38</f>
         <v>774480.33</v>
@@ -8619,11 +8619,11 @@
       <c r="O39" s="185">
         <v>0</v>
       </c>
-      <c r="P39" s="378">
+      <c r="P39" s="384">
         <f t="shared" si="13"/>
         <v>2448435.34</v>
       </c>
-      <c r="Q39" s="378"/>
+      <c r="Q39" s="384"/>
       <c r="R39" s="226">
         <f t="shared" si="14"/>
         <v>2522696.34</v>
@@ -8693,11 +8693,11 @@
       <c r="O40" s="185">
         <v>0</v>
       </c>
-      <c r="P40" s="378">
+      <c r="P40" s="384">
         <f t="shared" si="13"/>
         <v>759748.35</v>
       </c>
-      <c r="Q40" s="378"/>
+      <c r="Q40" s="384"/>
       <c r="R40" s="226">
         <f t="shared" si="14"/>
         <v>782792.35</v>
@@ -8766,11 +8766,11 @@
       <c r="O41" s="185">
         <v>0</v>
       </c>
-      <c r="P41" s="378">
+      <c r="P41" s="384">
         <f t="shared" si="13"/>
         <v>720580.36</v>
       </c>
-      <c r="Q41" s="378"/>
+      <c r="Q41" s="384"/>
       <c r="R41" s="226">
         <f t="shared" si="14"/>
         <v>742436.36</v>
@@ -8838,11 +8838,11 @@
       <c r="O42" s="185">
         <v>0</v>
       </c>
-      <c r="P42" s="378">
+      <c r="P42" s="384">
         <f t="shared" si="13"/>
         <v>751681.37</v>
       </c>
-      <c r="Q42" s="378"/>
+      <c r="Q42" s="384"/>
       <c r="R42" s="226">
         <f t="shared" si="14"/>
         <v>774480.37</v>
@@ -8910,11 +8910,11 @@
       <c r="O43" s="185">
         <v>0</v>
       </c>
-      <c r="P43" s="378">
+      <c r="P43" s="384">
         <f t="shared" si="13"/>
         <v>751681.38</v>
       </c>
-      <c r="Q43" s="378"/>
+      <c r="Q43" s="384"/>
       <c r="R43" s="226">
         <f t="shared" si="14"/>
         <v>774480.38</v>
@@ -8983,11 +8983,11 @@
       <c r="O44" s="185">
         <v>0</v>
       </c>
-      <c r="P44" s="378">
+      <c r="P44" s="384">
         <f t="shared" si="13"/>
         <v>751543.39</v>
       </c>
-      <c r="Q44" s="378"/>
+      <c r="Q44" s="384"/>
       <c r="R44" s="226">
         <f t="shared" si="14"/>
         <v>774338.39</v>
@@ -9056,11 +9056,11 @@
       <c r="O45" s="185">
         <v>0</v>
       </c>
-      <c r="P45" s="378">
+      <c r="P45" s="384">
         <f t="shared" si="13"/>
         <v>751681.4</v>
       </c>
-      <c r="Q45" s="378"/>
+      <c r="Q45" s="384"/>
       <c r="R45" s="226">
         <f t="shared" si="14"/>
         <v>774480.4</v>
@@ -9126,11 +9126,11 @@
       <c r="O46" s="185">
         <v>0</v>
       </c>
-      <c r="P46" s="378">
+      <c r="P46" s="384">
         <f t="shared" si="13"/>
         <v>729553.41</v>
       </c>
-      <c r="Q46" s="378"/>
+      <c r="Q46" s="384"/>
       <c r="R46" s="226">
         <f t="shared" si="14"/>
         <v>751681.41</v>
@@ -9200,11 +9200,11 @@
       <c r="O47" s="185">
         <v>0</v>
       </c>
-      <c r="P47" s="378">
+      <c r="P47" s="384">
         <f t="shared" si="13"/>
         <v>751681.42</v>
       </c>
-      <c r="Q47" s="378"/>
+      <c r="Q47" s="384"/>
       <c r="R47" s="226">
         <f t="shared" si="14"/>
         <v>774480.42</v>
@@ -9274,11 +9274,11 @@
       <c r="O48" s="185">
         <v>0</v>
       </c>
-      <c r="P48" s="378">
+      <c r="P48" s="384">
         <f t="shared" si="13"/>
         <v>679072.43</v>
       </c>
-      <c r="Q48" s="378"/>
+      <c r="Q48" s="384"/>
       <c r="R48" s="226">
         <f t="shared" si="14"/>
         <v>699669.43</v>
@@ -9344,11 +9344,11 @@
       <c r="O49" s="185">
         <v>0</v>
       </c>
-      <c r="P49" s="378">
+      <c r="P49" s="384">
         <f t="shared" si="13"/>
         <v>692960.44</v>
       </c>
-      <c r="Q49" s="378"/>
+      <c r="Q49" s="384"/>
       <c r="R49" s="226">
         <f t="shared" si="14"/>
         <v>713978.44</v>
@@ -9417,11 +9417,11 @@
       <c r="O50" s="185">
         <v>0</v>
       </c>
-      <c r="P50" s="378">
+      <c r="P50" s="384">
         <f t="shared" si="13"/>
         <v>1654405.45</v>
       </c>
-      <c r="Q50" s="378"/>
+      <c r="Q50" s="384"/>
       <c r="R50" s="226">
         <f t="shared" si="14"/>
         <v>1704584.45</v>
@@ -9487,11 +9487,11 @@
       <c r="O51" s="185">
         <v>0</v>
       </c>
-      <c r="P51" s="378">
+      <c r="P51" s="384">
         <f t="shared" si="13"/>
         <v>1451354.46</v>
       </c>
-      <c r="Q51" s="378"/>
+      <c r="Q51" s="384"/>
       <c r="R51" s="226">
         <f t="shared" si="14"/>
         <v>1495374.46</v>
@@ -9558,11 +9558,11 @@
       <c r="O52" s="185">
         <v>0</v>
       </c>
-      <c r="P52" s="378">
+      <c r="P52" s="384">
         <f t="shared" si="13"/>
         <v>3148838.47</v>
       </c>
-      <c r="Q52" s="378"/>
+      <c r="Q52" s="384"/>
       <c r="R52" s="226">
         <f t="shared" si="14"/>
         <v>3244343.47</v>
@@ -9633,11 +9633,11 @@
       <c r="O53" s="185">
         <v>0</v>
       </c>
-      <c r="P53" s="378">
+      <c r="P53" s="384">
         <f t="shared" si="13"/>
         <v>1187332.48</v>
       </c>
-      <c r="Q53" s="378"/>
+      <c r="Q53" s="384"/>
       <c r="R53" s="226">
         <f t="shared" si="14"/>
         <v>1223344.48</v>
@@ -9705,11 +9705,11 @@
       <c r="O54" s="185">
         <v>0</v>
       </c>
-      <c r="P54" s="378">
+      <c r="P54" s="384">
         <f t="shared" si="13"/>
         <v>751681.49</v>
       </c>
-      <c r="Q54" s="378"/>
+      <c r="Q54" s="384"/>
       <c r="R54" s="226">
         <f t="shared" si="14"/>
         <v>774480.49</v>
@@ -9779,11 +9779,11 @@
       <c r="O55" s="185">
         <v>0</v>
       </c>
-      <c r="P55" s="378">
+      <c r="P55" s="384">
         <f t="shared" si="13"/>
         <v>751681.5</v>
       </c>
-      <c r="Q55" s="378"/>
+      <c r="Q55" s="384"/>
       <c r="R55" s="226">
         <f t="shared" si="14"/>
         <v>774480.5</v>
@@ -9853,11 +9853,11 @@
       <c r="O56" s="185">
         <v>0</v>
       </c>
-      <c r="P56" s="378">
+      <c r="P56" s="384">
         <f t="shared" si="13"/>
         <v>751681.51</v>
       </c>
-      <c r="Q56" s="378"/>
+      <c r="Q56" s="384"/>
       <c r="R56" s="226">
         <f t="shared" si="14"/>
         <v>774480.51</v>
@@ -9927,11 +9927,11 @@
       <c r="O57" s="185">
         <v>0</v>
       </c>
-      <c r="P57" s="378">
+      <c r="P57" s="384">
         <f t="shared" si="13"/>
         <v>759748.52</v>
       </c>
-      <c r="Q57" s="378"/>
+      <c r="Q57" s="384"/>
       <c r="R57" s="226">
         <f t="shared" si="14"/>
         <v>782792.52</v>
@@ -9998,11 +9998,11 @@
       <c r="O58" s="185">
         <v>0</v>
       </c>
-      <c r="P58" s="378">
+      <c r="P58" s="384">
         <f t="shared" si="13"/>
         <v>4746223.53</v>
       </c>
-      <c r="Q58" s="378"/>
+      <c r="Q58" s="384"/>
       <c r="R58" s="226">
         <f t="shared" si="14"/>
         <v>4890176.53</v>
@@ -10069,11 +10069,11 @@
       <c r="O59" s="185">
         <v>0</v>
       </c>
-      <c r="P59" s="378">
+      <c r="P59" s="384">
         <f t="shared" si="13"/>
         <v>751681.54</v>
       </c>
-      <c r="Q59" s="378"/>
+      <c r="Q59" s="384"/>
       <c r="R59" s="226">
         <f t="shared" si="14"/>
         <v>774480.54</v>
@@ -10142,11 +10142,11 @@
       <c r="O60" s="185">
         <v>0</v>
       </c>
-      <c r="P60" s="378">
+      <c r="P60" s="384">
         <f t="shared" si="13"/>
         <v>729553.55</v>
       </c>
-      <c r="Q60" s="378"/>
+      <c r="Q60" s="384"/>
       <c r="R60" s="226">
         <f t="shared" si="14"/>
         <v>751681.55</v>
@@ -10216,11 +10216,11 @@
       <c r="O61" s="185">
         <v>0</v>
       </c>
-      <c r="P61" s="378">
+      <c r="P61" s="384">
         <f t="shared" si="13"/>
         <v>751681.56</v>
       </c>
-      <c r="Q61" s="378"/>
+      <c r="Q61" s="384"/>
       <c r="R61" s="226">
         <f t="shared" si="14"/>
         <v>774480.56</v>
@@ -10290,11 +10290,11 @@
       <c r="O62" s="185">
         <v>0</v>
       </c>
-      <c r="P62" s="378">
+      <c r="P62" s="384">
         <f t="shared" si="13"/>
         <v>751681.57</v>
       </c>
-      <c r="Q62" s="378"/>
+      <c r="Q62" s="384"/>
       <c r="R62" s="226">
         <f t="shared" si="14"/>
         <v>774480.57</v>
@@ -10360,11 +10360,11 @@
       <c r="O63" s="185">
         <v>0</v>
       </c>
-      <c r="P63" s="378">
+      <c r="P63" s="384">
         <f t="shared" si="13"/>
         <v>729553.58</v>
       </c>
-      <c r="Q63" s="378"/>
+      <c r="Q63" s="384"/>
       <c r="R63" s="226">
         <f t="shared" si="14"/>
         <v>751681.58</v>
@@ -10430,11 +10430,11 @@
       <c r="O64" s="185">
         <v>0</v>
       </c>
-      <c r="P64" s="378">
+      <c r="P64" s="384">
         <f t="shared" si="13"/>
         <v>718232.59</v>
       </c>
-      <c r="Q64" s="378"/>
+      <c r="Q64" s="384"/>
       <c r="R64" s="226">
         <f t="shared" si="14"/>
         <v>740017.59</v>
@@ -10503,11 +10503,11 @@
       <c r="O65" s="185">
         <v>0</v>
       </c>
-      <c r="P65" s="378">
+      <c r="P65" s="384">
         <f t="shared" si="13"/>
         <v>751232.6</v>
       </c>
-      <c r="Q65" s="378"/>
+      <c r="Q65" s="384"/>
       <c r="R65" s="226">
         <f t="shared" si="14"/>
         <v>774017.6</v>
@@ -10576,11 +10576,11 @@
       <c r="O66" s="185">
         <v>0</v>
       </c>
-      <c r="P66" s="378">
+      <c r="P66" s="384">
         <f t="shared" si="13"/>
         <v>751624.61</v>
       </c>
-      <c r="Q66" s="378"/>
+      <c r="Q66" s="384"/>
       <c r="R66" s="226">
         <f t="shared" si="14"/>
         <v>774421.61</v>
@@ -10649,11 +10649,11 @@
       <c r="O67" s="185">
         <v>0</v>
       </c>
-      <c r="P67" s="378">
+      <c r="P67" s="384">
         <f t="shared" si="13"/>
         <v>1529226.62</v>
       </c>
-      <c r="Q67" s="378"/>
+      <c r="Q67" s="384"/>
       <c r="R67" s="226">
         <f t="shared" si="14"/>
         <v>1575608.62</v>
@@ -10719,11 +10719,11 @@
       <c r="O68" s="185">
         <v>0</v>
       </c>
-      <c r="P68" s="378">
+      <c r="P68" s="384">
         <f t="shared" si="13"/>
         <v>728882.63</v>
       </c>
-      <c r="Q68" s="378"/>
+      <c r="Q68" s="384"/>
       <c r="R68" s="226">
         <f t="shared" si="14"/>
         <v>750990.63</v>
@@ -10793,11 +10793,11 @@
       <c r="O69" s="185">
         <v>0</v>
       </c>
-      <c r="P69" s="378">
+      <c r="P69" s="384">
         <f t="shared" si="13"/>
         <v>751681.64</v>
       </c>
-      <c r="Q69" s="378"/>
+      <c r="Q69" s="384"/>
       <c r="R69" s="226">
         <f t="shared" si="14"/>
         <v>774480.64</v>
@@ -10867,11 +10867,11 @@
       <c r="O70" s="185">
         <v>0</v>
       </c>
-      <c r="P70" s="378">
+      <c r="P70" s="384">
         <f t="shared" ref="P70:P101" si="21">ROUND(SUM(G70:O70),0) + S70</f>
         <v>751681.65</v>
       </c>
-      <c r="Q70" s="378"/>
+      <c r="Q70" s="384"/>
       <c r="R70" s="226">
         <f t="shared" ref="R70:R101" si="22">ROUND(P70+P70*3.033%,0) + S70</f>
         <v>774480.65</v>
@@ -10938,11 +10938,11 @@
       <c r="O71" s="185">
         <v>0</v>
       </c>
-      <c r="P71" s="378">
+      <c r="P71" s="384">
         <f t="shared" si="21"/>
         <v>751681.66</v>
       </c>
-      <c r="Q71" s="378"/>
+      <c r="Q71" s="384"/>
       <c r="R71" s="226">
         <f t="shared" si="22"/>
         <v>774480.66</v>
@@ -11011,11 +11011,11 @@
       <c r="O72" s="185">
         <v>0</v>
       </c>
-      <c r="P72" s="378">
+      <c r="P72" s="384">
         <f t="shared" si="21"/>
         <v>1527073.67</v>
       </c>
-      <c r="Q72" s="378"/>
+      <c r="Q72" s="384"/>
       <c r="R72" s="226">
         <f t="shared" si="22"/>
         <v>1573390.67</v>
@@ -11082,11 +11082,11 @@
       <c r="O73" s="185">
         <v>0</v>
       </c>
-      <c r="P73" s="378">
+      <c r="P73" s="384">
         <f t="shared" si="21"/>
         <v>4973793.68</v>
       </c>
-      <c r="Q73" s="378"/>
+      <c r="Q73" s="384"/>
       <c r="R73" s="226">
         <f t="shared" si="22"/>
         <v>5124649.68</v>
@@ -11152,11 +11152,11 @@
       <c r="O74" s="185">
         <v>0</v>
       </c>
-      <c r="P74" s="378">
+      <c r="P74" s="384">
         <f t="shared" si="21"/>
         <v>679072.69</v>
       </c>
-      <c r="Q74" s="378"/>
+      <c r="Q74" s="384"/>
       <c r="R74" s="226">
         <f t="shared" si="22"/>
         <v>699669.69</v>
@@ -11224,11 +11224,11 @@
       <c r="O75" s="185">
         <v>0</v>
       </c>
-      <c r="P75" s="378">
+      <c r="P75" s="384">
         <f t="shared" si="21"/>
         <v>1759862.7</v>
       </c>
-      <c r="Q75" s="378"/>
+      <c r="Q75" s="384"/>
       <c r="R75" s="226">
         <f t="shared" si="22"/>
         <v>1813239.7</v>
@@ -11296,11 +11296,11 @@
       <c r="O76" s="185">
         <v>0</v>
       </c>
-      <c r="P76" s="378">
+      <c r="P76" s="384">
         <f t="shared" si="21"/>
         <v>1469187.71</v>
       </c>
-      <c r="Q76" s="378"/>
+      <c r="Q76" s="384"/>
       <c r="R76" s="226">
         <f t="shared" si="22"/>
         <v>1513748.71</v>
@@ -11368,11 +11368,11 @@
       <c r="O77" s="185">
         <v>0</v>
       </c>
-      <c r="P77" s="378">
+      <c r="P77" s="384">
         <f t="shared" si="21"/>
         <v>689767.72</v>
       </c>
-      <c r="Q77" s="378"/>
+      <c r="Q77" s="384"/>
       <c r="R77" s="226">
         <f t="shared" si="22"/>
         <v>710688.72</v>
@@ -11440,11 +11440,11 @@
       <c r="O78" s="185">
         <v>0</v>
       </c>
-      <c r="P78" s="378">
+      <c r="P78" s="384">
         <f t="shared" si="21"/>
         <v>711063.73</v>
       </c>
-      <c r="Q78" s="378"/>
+      <c r="Q78" s="384"/>
       <c r="R78" s="226">
         <f t="shared" si="22"/>
         <v>732630.73</v>
@@ -11510,11 +11510,11 @@
       <c r="O79" s="185">
         <v>0</v>
       </c>
-      <c r="P79" s="378">
+      <c r="P79" s="384">
         <f t="shared" si="21"/>
         <v>743613.74</v>
       </c>
-      <c r="Q79" s="378"/>
+      <c r="Q79" s="384"/>
       <c r="R79" s="226">
         <f t="shared" si="22"/>
         <v>766168.74</v>
@@ -11579,11 +11579,11 @@
       <c r="O80" s="185">
         <v>0</v>
       </c>
-      <c r="P80" s="378">
+      <c r="P80" s="384">
         <f t="shared" si="21"/>
         <v>719410.75</v>
       </c>
-      <c r="Q80" s="378"/>
+      <c r="Q80" s="384"/>
       <c r="R80" s="226">
         <f t="shared" si="22"/>
         <v>741230.75</v>
@@ -11652,11 +11652,11 @@
       <c r="O81" s="185">
         <v>0</v>
       </c>
-      <c r="P81" s="378">
+      <c r="P81" s="384">
         <f t="shared" si="21"/>
         <v>751681.76</v>
       </c>
-      <c r="Q81" s="378"/>
+      <c r="Q81" s="384"/>
       <c r="R81" s="226">
         <f t="shared" si="22"/>
         <v>774480.76</v>
@@ -11721,11 +11721,11 @@
       <c r="O82" s="185">
         <v>0</v>
       </c>
-      <c r="P82" s="378">
+      <c r="P82" s="384">
         <f t="shared" si="21"/>
         <v>880410.77</v>
       </c>
-      <c r="Q82" s="378"/>
+      <c r="Q82" s="384"/>
       <c r="R82" s="226">
         <f t="shared" si="22"/>
         <v>907114.77</v>
@@ -11793,11 +11793,11 @@
       <c r="O83" s="185">
         <v>0</v>
       </c>
-      <c r="P83" s="378">
+      <c r="P83" s="384">
         <f t="shared" si="21"/>
         <v>752933.78</v>
       </c>
-      <c r="Q83" s="378"/>
+      <c r="Q83" s="384"/>
       <c r="R83" s="226">
         <f t="shared" si="22"/>
         <v>775770.78</v>
@@ -11866,11 +11866,11 @@
       <c r="O84" s="185">
         <v>0</v>
       </c>
-      <c r="P84" s="378">
+      <c r="P84" s="384">
         <f t="shared" si="21"/>
         <v>1526975.79</v>
       </c>
-      <c r="Q84" s="378"/>
+      <c r="Q84" s="384"/>
       <c r="R84" s="226">
         <f t="shared" si="22"/>
         <v>1573289.79</v>
@@ -11942,11 +11942,11 @@
       <c r="O85" s="185">
         <v>0</v>
       </c>
-      <c r="P85" s="378">
+      <c r="P85" s="384">
         <f t="shared" si="21"/>
         <v>751681.8</v>
       </c>
-      <c r="Q85" s="378"/>
+      <c r="Q85" s="384"/>
       <c r="R85" s="226">
         <f t="shared" si="22"/>
         <v>774480.8</v>
@@ -12015,11 +12015,11 @@
       <c r="O86" s="185">
         <v>0</v>
       </c>
-      <c r="P86" s="378">
+      <c r="P86" s="384">
         <f t="shared" si="21"/>
         <v>751681.81</v>
       </c>
-      <c r="Q86" s="378"/>
+      <c r="Q86" s="384"/>
       <c r="R86" s="226">
         <f t="shared" si="22"/>
         <v>774480.81</v>
@@ -12088,11 +12088,11 @@
         <f>I87/2</f>
         <v>169419.524232</v>
       </c>
-      <c r="P87" s="378">
+      <c r="P87" s="384">
         <f t="shared" si="21"/>
         <v>1626958.82</v>
       </c>
-      <c r="Q87" s="378"/>
+      <c r="Q87" s="384"/>
       <c r="R87" s="226">
         <f t="shared" si="22"/>
         <v>1676304.82</v>
@@ -12161,11 +12161,11 @@
       <c r="O88" s="185">
         <v>0</v>
       </c>
-      <c r="P88" s="378">
+      <c r="P88" s="384">
         <f t="shared" si="21"/>
         <v>775884.83</v>
       </c>
-      <c r="Q88" s="378"/>
+      <c r="Q88" s="384"/>
       <c r="R88" s="226">
         <f t="shared" si="22"/>
         <v>799417.83</v>
@@ -12230,11 +12230,11 @@
       <c r="O89" s="185">
         <v>0</v>
       </c>
-      <c r="P89" s="378">
+      <c r="P89" s="384">
         <f t="shared" si="21"/>
         <v>775884.84</v>
       </c>
-      <c r="Q89" s="378"/>
+      <c r="Q89" s="384"/>
       <c r="R89" s="226">
         <f t="shared" si="22"/>
         <v>799417.84</v>
@@ -12300,11 +12300,11 @@
       <c r="O90" s="185">
         <v>0</v>
       </c>
-      <c r="P90" s="378">
+      <c r="P90" s="384">
         <f t="shared" si="21"/>
         <v>775884.85</v>
       </c>
-      <c r="Q90" s="378"/>
+      <c r="Q90" s="384"/>
       <c r="R90" s="226">
         <f t="shared" si="22"/>
         <v>799417.85</v>
@@ -12375,11 +12375,11 @@
         <f>2239*100</f>
         <v>223900</v>
       </c>
-      <c r="P91" s="378">
+      <c r="P91" s="384">
         <f t="shared" si="21"/>
         <v>1394226.86</v>
       </c>
-      <c r="Q91" s="378"/>
+      <c r="Q91" s="384"/>
       <c r="R91" s="226">
         <f t="shared" si="22"/>
         <v>1436514.86</v>
@@ -12448,11 +12448,11 @@
       <c r="O92" s="185">
         <v>0</v>
       </c>
-      <c r="P92" s="378">
+      <c r="P92" s="384">
         <f t="shared" si="21"/>
         <v>775884.87</v>
       </c>
-      <c r="Q92" s="378"/>
+      <c r="Q92" s="384"/>
       <c r="R92" s="226">
         <f t="shared" si="22"/>
         <v>799417.87</v>
@@ -12517,11 +12517,11 @@
       <c r="O93" s="185">
         <v>0</v>
       </c>
-      <c r="P93" s="378">
+      <c r="P93" s="384">
         <f t="shared" si="21"/>
         <v>767654.88</v>
       </c>
-      <c r="Q93" s="378"/>
+      <c r="Q93" s="384"/>
       <c r="R93" s="226">
         <f t="shared" si="22"/>
         <v>790938.88</v>
@@ -12587,11 +12587,11 @@
       <c r="O94" s="185">
         <v>0</v>
       </c>
-      <c r="P94" s="378">
+      <c r="P94" s="384">
         <f t="shared" si="21"/>
         <v>775884.89</v>
       </c>
-      <c r="Q94" s="378"/>
+      <c r="Q94" s="384"/>
       <c r="R94" s="226">
         <f t="shared" si="22"/>
         <v>799417.89</v>
@@ -12660,11 +12660,11 @@
       <c r="O95" s="185">
         <v>0</v>
       </c>
-      <c r="P95" s="378">
+      <c r="P95" s="384">
         <f t="shared" si="21"/>
         <v>2097847.9</v>
       </c>
-      <c r="Q95" s="378"/>
+      <c r="Q95" s="384"/>
       <c r="R95" s="226">
         <f t="shared" si="22"/>
         <v>2161476.9</v>
@@ -12733,11 +12733,11 @@
       <c r="O96" s="185">
         <v>0</v>
       </c>
-      <c r="P96" s="378">
+      <c r="P96" s="384">
         <f t="shared" si="21"/>
         <v>775884.91</v>
       </c>
-      <c r="Q96" s="378"/>
+      <c r="Q96" s="384"/>
       <c r="R96" s="226">
         <f t="shared" si="22"/>
         <v>799417.91</v>
@@ -12806,11 +12806,11 @@
       <c r="O97" s="185">
         <v>0</v>
       </c>
-      <c r="P97" s="378">
+      <c r="P97" s="384">
         <f t="shared" si="21"/>
         <v>775884.92</v>
       </c>
-      <c r="Q97" s="378"/>
+      <c r="Q97" s="384"/>
       <c r="R97" s="226">
         <f t="shared" si="22"/>
         <v>799418.92</v>
@@ -12878,11 +12878,11 @@
       <c r="O98" s="185">
         <v>0</v>
       </c>
-      <c r="P98" s="378">
+      <c r="P98" s="384">
         <f t="shared" si="21"/>
         <v>1558282.93</v>
       </c>
-      <c r="Q98" s="378"/>
+      <c r="Q98" s="384"/>
       <c r="R98" s="226">
         <f t="shared" si="22"/>
         <v>1605546.93</v>
@@ -12951,11 +12951,11 @@
       <c r="O99" s="185">
         <v>0</v>
       </c>
-      <c r="P99" s="378">
+      <c r="P99" s="384">
         <f t="shared" si="21"/>
         <v>775884.94</v>
       </c>
-      <c r="Q99" s="378"/>
+      <c r="Q99" s="384"/>
       <c r="R99" s="226">
         <f t="shared" si="22"/>
         <v>799418.94</v>
@@ -13023,11 +13023,11 @@
       <c r="O100" s="185">
         <v>0</v>
       </c>
-      <c r="P100" s="378">
+      <c r="P100" s="384">
         <f t="shared" si="21"/>
         <v>5461803.9500000002</v>
       </c>
-      <c r="Q100" s="378"/>
+      <c r="Q100" s="384"/>
       <c r="R100" s="226">
         <f t="shared" si="22"/>
         <v>5627460.9500000002</v>
@@ -13092,11 +13092,11 @@
       <c r="O101" s="185">
         <v>0</v>
       </c>
-      <c r="P101" s="378">
+      <c r="P101" s="384">
         <f t="shared" si="21"/>
         <v>751813.96</v>
       </c>
-      <c r="Q101" s="378"/>
+      <c r="Q101" s="384"/>
       <c r="R101" s="226">
         <f t="shared" si="22"/>
         <v>774616.96</v>
@@ -13165,11 +13165,11 @@
       <c r="O102" s="185">
         <v>0</v>
       </c>
-      <c r="P102" s="378">
+      <c r="P102" s="384">
         <f t="shared" ref="P102:P133" si="30">ROUND(SUM(G102:O102),0) + S102</f>
         <v>775884.97</v>
       </c>
-      <c r="Q102" s="378"/>
+      <c r="Q102" s="384"/>
       <c r="R102" s="226">
         <f t="shared" ref="R102:R133" si="31">ROUND(P102+P102*3.033%,0) + S102</f>
         <v>799418.97</v>
@@ -13238,11 +13238,11 @@
       <c r="O103" s="185">
         <v>0</v>
       </c>
-      <c r="P103" s="378">
+      <c r="P103" s="384">
         <f t="shared" si="30"/>
         <v>775884.98</v>
       </c>
-      <c r="Q103" s="378"/>
+      <c r="Q103" s="384"/>
       <c r="R103" s="226">
         <f t="shared" si="31"/>
         <v>799418.98</v>
@@ -13308,11 +13308,11 @@
       <c r="O104" s="185">
         <v>0</v>
       </c>
-      <c r="P104" s="378">
+      <c r="P104" s="384">
         <f t="shared" si="30"/>
         <v>775884.99</v>
       </c>
-      <c r="Q104" s="378"/>
+      <c r="Q104" s="384"/>
       <c r="R104" s="226">
         <f t="shared" si="31"/>
         <v>799418.99</v>
@@ -13381,11 +13381,11 @@
       <c r="O105" s="185">
         <v>0</v>
       </c>
-      <c r="P105" s="378">
+      <c r="P105" s="384">
         <f t="shared" si="30"/>
         <v>775885</v>
       </c>
-      <c r="Q105" s="378"/>
+      <c r="Q105" s="384"/>
       <c r="R105" s="226">
         <f t="shared" si="31"/>
         <v>799419</v>
@@ -13451,11 +13451,11 @@
       <c r="O106" s="185">
         <v>0</v>
       </c>
-      <c r="P106" s="378">
+      <c r="P106" s="384">
         <f t="shared" si="30"/>
         <v>775885.01</v>
       </c>
-      <c r="Q106" s="378"/>
+      <c r="Q106" s="384"/>
       <c r="R106" s="226">
         <f t="shared" si="31"/>
         <v>799419.01</v>
@@ -13520,11 +13520,11 @@
       <c r="O107" s="185">
         <v>0</v>
       </c>
-      <c r="P107" s="378">
+      <c r="P107" s="384">
         <f t="shared" si="30"/>
         <v>764543.02</v>
       </c>
-      <c r="Q107" s="378"/>
+      <c r="Q107" s="384"/>
       <c r="R107" s="226">
         <f t="shared" si="31"/>
         <v>787733.02</v>
@@ -13590,11 +13590,11 @@
       <c r="O108" s="185">
         <v>0</v>
       </c>
-      <c r="P108" s="378">
+      <c r="P108" s="384">
         <f t="shared" si="30"/>
         <v>3224447.03</v>
       </c>
-      <c r="Q108" s="378"/>
+      <c r="Q108" s="384"/>
       <c r="R108" s="226">
         <f t="shared" si="31"/>
         <v>3322246.03</v>
@@ -13660,11 +13660,11 @@
       <c r="O109" s="185">
         <v>0</v>
       </c>
-      <c r="P109" s="378">
+      <c r="P109" s="384">
         <f t="shared" si="30"/>
         <v>767817.04</v>
       </c>
-      <c r="Q109" s="378"/>
+      <c r="Q109" s="384"/>
       <c r="R109" s="226">
         <f t="shared" si="31"/>
         <v>791106.04</v>
@@ -13733,11 +13733,11 @@
       <c r="O110" s="185">
         <v>0</v>
       </c>
-      <c r="P110" s="378">
+      <c r="P110" s="384">
         <f t="shared" si="30"/>
         <v>727479.05</v>
       </c>
-      <c r="Q110" s="378"/>
+      <c r="Q110" s="384"/>
       <c r="R110" s="226">
         <f t="shared" si="31"/>
         <v>749544.05</v>
@@ -13805,11 +13805,11 @@
       <c r="O111" s="185">
         <v>0</v>
       </c>
-      <c r="P111" s="378">
+      <c r="P111" s="384">
         <f t="shared" si="30"/>
         <v>3618180.06</v>
       </c>
-      <c r="Q111" s="378"/>
+      <c r="Q111" s="384"/>
       <c r="R111" s="226">
         <f t="shared" si="31"/>
         <v>3727920.06</v>
@@ -13878,11 +13878,11 @@
       <c r="O112" s="185">
         <v>0</v>
       </c>
-      <c r="P112" s="378">
+      <c r="P112" s="384">
         <f t="shared" si="30"/>
         <v>743614.07</v>
       </c>
-      <c r="Q112" s="378"/>
+      <c r="Q112" s="384"/>
       <c r="R112" s="226">
         <f t="shared" si="31"/>
         <v>766169.07</v>
@@ -13951,11 +13951,11 @@
       <c r="O113" s="185">
         <v>0</v>
       </c>
-      <c r="P113" s="378">
+      <c r="P113" s="384">
         <f t="shared" si="30"/>
         <v>743614.08</v>
       </c>
-      <c r="Q113" s="378"/>
+      <c r="Q113" s="384"/>
       <c r="R113" s="226">
         <f t="shared" si="31"/>
         <v>766169.08</v>
@@ -14020,11 +14020,11 @@
       <c r="O114" s="185">
         <v>0</v>
       </c>
-      <c r="P114" s="378">
+      <c r="P114" s="384">
         <f t="shared" si="30"/>
         <v>1469510.09</v>
       </c>
-      <c r="Q114" s="378"/>
+      <c r="Q114" s="384"/>
       <c r="R114" s="226">
         <f t="shared" si="31"/>
         <v>1514081.09</v>
@@ -14092,11 +14092,11 @@
       <c r="O115" s="185">
         <v>0</v>
       </c>
-      <c r="P115" s="378">
+      <c r="P115" s="384">
         <f t="shared" si="30"/>
         <v>1540074.1</v>
       </c>
-      <c r="Q115" s="378"/>
+      <c r="Q115" s="384"/>
       <c r="R115" s="226">
         <f t="shared" si="31"/>
         <v>1586786.1</v>
@@ -14166,11 +14166,11 @@
       <c r="O116" s="185">
         <v>0</v>
       </c>
-      <c r="P116" s="378">
+      <c r="P116" s="384">
         <f t="shared" si="30"/>
         <v>751682.11</v>
       </c>
-      <c r="Q116" s="378"/>
+      <c r="Q116" s="384"/>
       <c r="R116" s="226">
         <f t="shared" si="31"/>
         <v>774482.11</v>
@@ -14235,11 +14235,11 @@
       <c r="O117" s="185">
         <v>0</v>
       </c>
-      <c r="P117" s="378">
+      <c r="P117" s="384">
         <f t="shared" si="30"/>
         <v>1525913.12</v>
       </c>
-      <c r="Q117" s="378"/>
+      <c r="Q117" s="384"/>
       <c r="R117" s="226">
         <f t="shared" si="31"/>
         <v>1572195.12</v>
@@ -14307,11 +14307,11 @@
       <c r="O118" s="185">
         <v>0</v>
       </c>
-      <c r="P118" s="378">
+      <c r="P118" s="384">
         <f t="shared" si="30"/>
         <v>745213.13</v>
       </c>
-      <c r="Q118" s="378"/>
+      <c r="Q118" s="384"/>
       <c r="R118" s="226">
         <f t="shared" si="31"/>
         <v>767816.13</v>
@@ -14377,11 +14377,11 @@
       <c r="O119" s="185">
         <v>0</v>
       </c>
-      <c r="P119" s="378">
+      <c r="P119" s="384">
         <f t="shared" si="30"/>
         <v>751682.14</v>
       </c>
-      <c r="Q119" s="378"/>
+      <c r="Q119" s="384"/>
       <c r="R119" s="226">
         <f t="shared" si="31"/>
         <v>774482.14</v>
@@ -14447,11 +14447,11 @@
       <c r="O120" s="185">
         <v>0</v>
       </c>
-      <c r="P120" s="378">
+      <c r="P120" s="384">
         <f t="shared" si="30"/>
         <v>904966.15</v>
       </c>
-      <c r="Q120" s="378"/>
+      <c r="Q120" s="384"/>
       <c r="R120" s="226">
         <f t="shared" si="31"/>
         <v>932415.15</v>
@@ -14520,11 +14520,11 @@
       <c r="O121" s="185">
         <v>0</v>
       </c>
-      <c r="P121" s="378">
+      <c r="P121" s="384">
         <f t="shared" si="30"/>
         <v>831345.16</v>
       </c>
-      <c r="Q121" s="378"/>
+      <c r="Q121" s="384"/>
       <c r="R121" s="226">
         <f t="shared" si="31"/>
         <v>856561.16</v>
@@ -14590,11 +14590,11 @@
       <c r="O122" s="185">
         <v>0</v>
       </c>
-      <c r="P122" s="378">
+      <c r="P122" s="384">
         <f t="shared" si="30"/>
         <v>880763.17</v>
       </c>
-      <c r="Q122" s="378"/>
+      <c r="Q122" s="384"/>
       <c r="R122" s="226">
         <f t="shared" si="31"/>
         <v>907478.17</v>
@@ -14663,11 +14663,11 @@
       <c r="O123" s="185">
         <v>0</v>
       </c>
-      <c r="P123" s="378">
+      <c r="P123" s="384">
         <f t="shared" si="30"/>
         <v>855800.18</v>
       </c>
-      <c r="Q123" s="378"/>
+      <c r="Q123" s="384"/>
       <c r="R123" s="226">
         <f t="shared" si="31"/>
         <v>881758.18</v>
@@ -14735,11 +14735,11 @@
       <c r="O124" s="185">
         <v>0</v>
       </c>
-      <c r="P124" s="378">
+      <c r="P124" s="384">
         <f t="shared" si="30"/>
         <v>824214.19</v>
       </c>
-      <c r="Q124" s="378"/>
+      <c r="Q124" s="384"/>
       <c r="R124" s="226">
         <f t="shared" si="31"/>
         <v>849214.19</v>
@@ -14808,11 +14808,11 @@
       <c r="O125" s="185">
         <v>0</v>
       </c>
-      <c r="P125" s="378">
+      <c r="P125" s="384">
         <f t="shared" si="30"/>
         <v>759749.2</v>
       </c>
-      <c r="Q125" s="378"/>
+      <c r="Q125" s="384"/>
       <c r="R125" s="226">
         <f t="shared" si="31"/>
         <v>782793.2</v>
@@ -14881,11 +14881,11 @@
       <c r="O126" s="185">
         <v>0</v>
       </c>
-      <c r="P126" s="378">
+      <c r="P126" s="384">
         <f t="shared" si="30"/>
         <v>759749.21</v>
       </c>
-      <c r="Q126" s="378"/>
+      <c r="Q126" s="384"/>
       <c r="R126" s="226">
         <f t="shared" si="31"/>
         <v>782793.21</v>
@@ -14954,11 +14954,11 @@
       <c r="O127" s="185">
         <v>0</v>
       </c>
-      <c r="P127" s="378">
+      <c r="P127" s="384">
         <f t="shared" si="30"/>
         <v>759749.22</v>
       </c>
-      <c r="Q127" s="378"/>
+      <c r="Q127" s="384"/>
       <c r="R127" s="226">
         <f t="shared" si="31"/>
         <v>782793.22</v>
@@ -15024,11 +15024,11 @@
       <c r="O128" s="185">
         <v>0</v>
       </c>
-      <c r="P128" s="378">
+      <c r="P128" s="384">
         <f t="shared" si="30"/>
         <v>759749.23</v>
       </c>
-      <c r="Q128" s="378"/>
+      <c r="Q128" s="384"/>
       <c r="R128" s="226">
         <f t="shared" si="31"/>
         <v>782793.23</v>
@@ -15096,11 +15096,11 @@
       <c r="O129" s="185">
         <v>0</v>
       </c>
-      <c r="P129" s="378">
+      <c r="P129" s="384">
         <f t="shared" si="30"/>
         <v>737383.24</v>
       </c>
-      <c r="Q129" s="378"/>
+      <c r="Q129" s="384"/>
       <c r="R129" s="226">
         <f t="shared" si="31"/>
         <v>759749.24</v>
@@ -15166,11 +15166,11 @@
       <c r="O130" s="185">
         <v>0</v>
       </c>
-      <c r="P130" s="378">
+      <c r="P130" s="384">
         <f t="shared" si="30"/>
         <v>759749.25</v>
       </c>
-      <c r="Q130" s="378"/>
+      <c r="Q130" s="384"/>
       <c r="R130" s="226">
         <f t="shared" si="31"/>
         <v>782793.25</v>
@@ -15239,11 +15239,11 @@
       <c r="O131" s="185">
         <v>0</v>
       </c>
-      <c r="P131" s="378">
+      <c r="P131" s="384">
         <f t="shared" si="30"/>
         <v>759749.26</v>
       </c>
-      <c r="Q131" s="378"/>
+      <c r="Q131" s="384"/>
       <c r="R131" s="226">
         <f t="shared" si="31"/>
         <v>782793.26</v>
@@ -15309,11 +15309,11 @@
       <c r="O132" s="185">
         <v>0</v>
       </c>
-      <c r="P132" s="378">
+      <c r="P132" s="384">
         <f t="shared" si="30"/>
         <v>840425.27</v>
       </c>
-      <c r="Q132" s="378"/>
+      <c r="Q132" s="384"/>
       <c r="R132" s="226">
         <f t="shared" si="31"/>
         <v>865916.27</v>
@@ -15382,11 +15382,11 @@
       <c r="O133" s="185">
         <v>0</v>
       </c>
-      <c r="P133" s="378">
+      <c r="P133" s="384">
         <f t="shared" si="30"/>
         <v>880763.28</v>
       </c>
-      <c r="Q133" s="378"/>
+      <c r="Q133" s="384"/>
       <c r="R133" s="226">
         <f t="shared" si="31"/>
         <v>907478.28</v>
@@ -15452,11 +15452,11 @@
       <c r="O134" s="185">
         <v>0</v>
       </c>
-      <c r="P134" s="378">
+      <c r="P134" s="384">
         <f t="shared" ref="P134:P144" si="37">ROUND(SUM(G134:O134),0) + S134</f>
         <v>880763.29</v>
       </c>
-      <c r="Q134" s="378"/>
+      <c r="Q134" s="384"/>
       <c r="R134" s="226">
         <f t="shared" ref="R134:R144" si="38">ROUND(P134+P134*3.033%,0) + S134</f>
         <v>907478.29</v>
@@ -15524,11 +15524,11 @@
       <c r="O135" s="185">
         <v>0</v>
       </c>
-      <c r="P135" s="378">
+      <c r="P135" s="384">
         <f t="shared" si="37"/>
         <v>848330.3</v>
       </c>
-      <c r="Q135" s="378"/>
+      <c r="Q135" s="384"/>
       <c r="R135" s="226">
         <f t="shared" si="38"/>
         <v>874061.3</v>
@@ -15597,11 +15597,11 @@
       <c r="O136" s="185">
         <v>0</v>
       </c>
-      <c r="P136" s="378">
+      <c r="P136" s="384">
         <f t="shared" si="37"/>
         <v>880763.31</v>
       </c>
-      <c r="Q136" s="378"/>
+      <c r="Q136" s="384"/>
       <c r="R136" s="226">
         <f t="shared" si="38"/>
         <v>907478.31</v>
@@ -15670,11 +15670,11 @@
       <c r="O137" s="185">
         <v>0</v>
       </c>
-      <c r="P137" s="378">
+      <c r="P137" s="384">
         <f t="shared" si="37"/>
         <v>872696.31999999995</v>
       </c>
-      <c r="Q137" s="378"/>
+      <c r="Q137" s="384"/>
       <c r="R137" s="226">
         <f t="shared" si="38"/>
         <v>899166.32</v>
@@ -15743,11 +15743,11 @@
       <c r="O138" s="185">
         <v>0</v>
       </c>
-      <c r="P138" s="378">
+      <c r="P138" s="384">
         <f t="shared" si="37"/>
         <v>904966.33</v>
       </c>
-      <c r="Q138" s="378"/>
+      <c r="Q138" s="384"/>
       <c r="R138" s="226">
         <f t="shared" si="38"/>
         <v>932415.33</v>
@@ -15815,11 +15815,11 @@
       <c r="O139" s="185">
         <v>0</v>
       </c>
-      <c r="P139" s="378">
+      <c r="P139" s="384">
         <f t="shared" si="37"/>
         <v>792194.34</v>
       </c>
-      <c r="Q139" s="378"/>
+      <c r="Q139" s="384"/>
       <c r="R139" s="226">
         <f t="shared" si="38"/>
         <v>816223.34</v>
@@ -15887,11 +15887,11 @@
       <c r="O140" s="185">
         <v>0</v>
       </c>
-      <c r="P140" s="378">
+      <c r="P140" s="384">
         <f t="shared" si="37"/>
         <v>854834.35</v>
       </c>
-      <c r="Q140" s="378"/>
+      <c r="Q140" s="384"/>
       <c r="R140" s="226">
         <f t="shared" si="38"/>
         <v>880762.35</v>
@@ -15960,11 +15960,11 @@
       <c r="O141" s="185">
         <v>0</v>
       </c>
-      <c r="P141" s="378">
+      <c r="P141" s="384">
         <f t="shared" si="37"/>
         <v>888831.36</v>
       </c>
-      <c r="Q141" s="378"/>
+      <c r="Q141" s="384"/>
       <c r="R141" s="226">
         <f t="shared" si="38"/>
         <v>915791.35999999999</v>
@@ -16033,11 +16033,11 @@
       <c r="O142" s="185">
         <v>0</v>
       </c>
-      <c r="P142" s="378">
+      <c r="P142" s="384">
         <f t="shared" si="37"/>
         <v>824290.37</v>
       </c>
-      <c r="Q142" s="378"/>
+      <c r="Q142" s="384"/>
       <c r="R142" s="226">
         <f t="shared" si="38"/>
         <v>849292.37</v>
@@ -16102,11 +16102,11 @@
       <c r="O143" s="185">
         <v>0</v>
       </c>
-      <c r="P143" s="378">
+      <c r="P143" s="384">
         <f t="shared" si="37"/>
         <v>879189.38</v>
       </c>
-      <c r="Q143" s="378"/>
+      <c r="Q143" s="384"/>
       <c r="R143" s="226">
         <f t="shared" si="38"/>
         <v>905856.38</v>
@@ -16174,11 +16174,11 @@
       <c r="O144" s="185">
         <v>0</v>
       </c>
-      <c r="P144" s="378">
+      <c r="P144" s="384">
         <f t="shared" si="37"/>
         <v>2193265.39</v>
       </c>
-      <c r="Q144" s="378"/>
+      <c r="Q144" s="384"/>
       <c r="R144" s="226">
         <f t="shared" si="38"/>
         <v>2259788.39</v>
@@ -16224,8 +16224,8 @@
       <c r="O145" s="185">
         <v>0</v>
       </c>
-      <c r="P145" s="378"/>
-      <c r="Q145" s="378"/>
+      <c r="P145" s="384"/>
+      <c r="Q145" s="384"/>
       <c r="R145" s="227"/>
       <c r="S145" s="13">
         <f t="shared" si="39"/>
@@ -16265,8 +16265,8 @@
       <c r="O146" s="185">
         <v>0</v>
       </c>
-      <c r="P146" s="378"/>
-      <c r="Q146" s="378"/>
+      <c r="P146" s="384"/>
+      <c r="Q146" s="384"/>
       <c r="R146" s="227"/>
       <c r="S146" s="13">
         <f t="shared" si="39"/>
@@ -16299,8 +16299,8 @@
       <c r="O147" s="185">
         <v>0</v>
       </c>
-      <c r="P147" s="378"/>
-      <c r="Q147" s="378"/>
+      <c r="P147" s="384"/>
+      <c r="Q147" s="384"/>
       <c r="R147" s="227"/>
       <c r="S147" s="13">
         <f t="shared" si="39"/>
@@ -16333,8 +16333,8 @@
       <c r="O148" s="185">
         <v>0</v>
       </c>
-      <c r="P148" s="378"/>
-      <c r="Q148" s="378"/>
+      <c r="P148" s="384"/>
+      <c r="Q148" s="384"/>
       <c r="R148" s="227"/>
       <c r="S148" s="13">
         <f t="shared" si="39"/>
@@ -16396,11 +16396,11 @@
       <c r="O149" s="185">
         <v>0</v>
       </c>
-      <c r="P149" s="378">
+      <c r="P149" s="384">
         <f t="shared" ref="P149:P158" si="47">ROUND(SUM(G149:O149),0) + S149</f>
         <v>695209.46</v>
       </c>
-      <c r="Q149" s="378"/>
+      <c r="Q149" s="384"/>
       <c r="R149" s="226">
         <f t="shared" ref="R149:R158" si="48">ROUND(P149+P149*3.033%,0) + S149</f>
         <v>716296.46</v>
@@ -16463,11 +16463,11 @@
       <c r="O150" s="185">
         <v>0</v>
       </c>
-      <c r="P150" s="378">
+      <c r="P150" s="384">
         <f t="shared" si="47"/>
         <v>1139411.55</v>
       </c>
-      <c r="Q150" s="378"/>
+      <c r="Q150" s="384"/>
       <c r="R150" s="226">
         <f t="shared" si="48"/>
         <v>1173971.55</v>
@@ -16535,11 +16535,11 @@
       <c r="O151" s="185">
         <v>0</v>
       </c>
-      <c r="P151" s="378">
+      <c r="P151" s="384">
         <f t="shared" si="47"/>
         <v>759749.58</v>
       </c>
-      <c r="Q151" s="378"/>
+      <c r="Q151" s="384"/>
       <c r="R151" s="226">
         <f t="shared" si="48"/>
         <v>782794.58</v>
@@ -16604,11 +16604,11 @@
       <c r="O152" s="185">
         <v>0</v>
       </c>
-      <c r="P152" s="378">
+      <c r="P152" s="384">
         <f t="shared" si="47"/>
         <v>759749.59</v>
       </c>
-      <c r="Q152" s="378"/>
+      <c r="Q152" s="384"/>
       <c r="R152" s="226">
         <f t="shared" si="48"/>
         <v>782794.59</v>
@@ -16673,11 +16673,11 @@
       <c r="O153" s="185">
         <v>0</v>
       </c>
-      <c r="P153" s="378">
+      <c r="P153" s="384">
         <f t="shared" si="47"/>
         <v>759749.63</v>
       </c>
-      <c r="Q153" s="378"/>
+      <c r="Q153" s="384"/>
       <c r="R153" s="226">
         <f t="shared" si="48"/>
         <v>782794.63</v>
@@ -16742,11 +16742,11 @@
       <c r="O154" s="185">
         <v>0</v>
       </c>
-      <c r="P154" s="378">
+      <c r="P154" s="384">
         <f t="shared" si="47"/>
         <v>743614.68</v>
       </c>
-      <c r="Q154" s="378"/>
+      <c r="Q154" s="384"/>
       <c r="R154" s="226">
         <f t="shared" si="48"/>
         <v>766170.68</v>
@@ -16810,11 +16810,11 @@
       <c r="O155" s="185">
         <v>0</v>
       </c>
-      <c r="P155" s="378">
+      <c r="P155" s="384">
         <f t="shared" si="47"/>
         <v>737382.73</v>
       </c>
-      <c r="Q155" s="378"/>
+      <c r="Q155" s="384"/>
       <c r="R155" s="226">
         <f t="shared" si="48"/>
         <v>759749.73</v>
@@ -16881,11 +16881,11 @@
       <c r="O156" s="185">
         <v>0</v>
       </c>
-      <c r="P156" s="378">
+      <c r="P156" s="384">
         <f t="shared" si="47"/>
         <v>737382.75</v>
       </c>
-      <c r="Q156" s="378"/>
+      <c r="Q156" s="384"/>
       <c r="R156" s="226">
         <f t="shared" si="48"/>
         <v>759749.75</v>
@@ -16953,11 +16953,11 @@
       <c r="O157" s="185">
         <v>0</v>
       </c>
-      <c r="P157" s="378">
+      <c r="P157" s="384">
         <f t="shared" si="47"/>
         <v>759749.76</v>
       </c>
-      <c r="Q157" s="378"/>
+      <c r="Q157" s="384"/>
       <c r="R157" s="226">
         <f t="shared" si="48"/>
         <v>782794.76</v>
@@ -17021,11 +17021,11 @@
       <c r="O158" s="185">
         <v>0</v>
       </c>
-      <c r="P158" s="378">
+      <c r="P158" s="384">
         <f t="shared" si="47"/>
         <v>760897.04</v>
       </c>
-      <c r="Q158" s="378"/>
+      <c r="Q158" s="384"/>
       <c r="R158" s="226">
         <f t="shared" si="48"/>
         <v>783977.04</v>
@@ -17058,8 +17058,8 @@
       <c r="M159" s="20"/>
       <c r="N159" s="20"/>
       <c r="O159" s="66"/>
-      <c r="P159" s="383"/>
-      <c r="Q159" s="383"/>
+      <c r="P159" s="409"/>
+      <c r="Q159" s="409"/>
       <c r="R159" s="163"/>
       <c r="S159" s="13"/>
       <c r="T159" s="1"/>
@@ -17080,8 +17080,8 @@
       <c r="M160" s="174"/>
       <c r="N160" s="174"/>
       <c r="O160" s="223"/>
-      <c r="P160" s="384"/>
-      <c r="Q160" s="384"/>
+      <c r="P160" s="410"/>
+      <c r="Q160" s="410"/>
       <c r="R160" s="166"/>
       <c r="S160" s="13"/>
       <c r="T160" s="175"/>
@@ -17135,150 +17135,312 @@
         <f t="shared" si="51"/>
         <v>617219.524232</v>
       </c>
-      <c r="P161" s="381">
+      <c r="P161" s="407">
         <f>SUM(P6:P160)</f>
         <v>160799642.07000002</v>
       </c>
-      <c r="Q161" s="382"/>
+      <c r="Q161" s="408"/>
       <c r="R161" s="167">
         <f>SUM(R6:R160)</f>
         <v>165676810.06999999</v>
       </c>
-      <c r="S161" s="381"/>
-      <c r="T161" s="382"/>
+      <c r="S161" s="407"/>
+      <c r="T161" s="408"/>
     </row>
     <row r="162" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B162" s="379" t="s">
+      <c r="B162" s="405" t="s">
         <v>314</v>
       </c>
-      <c r="C162" s="379"/>
-      <c r="D162" s="379"/>
-      <c r="E162" s="379"/>
-      <c r="F162" s="379"/>
-      <c r="G162" s="379"/>
-      <c r="H162" s="379"/>
-      <c r="I162" s="379"/>
-      <c r="J162" s="379"/>
-      <c r="K162" s="379"/>
-      <c r="L162" s="379"/>
-      <c r="M162" s="379"/>
-      <c r="N162" s="379"/>
-      <c r="O162" s="379"/>
-      <c r="P162" s="379"/>
-      <c r="Q162" s="379"/>
-      <c r="R162" s="379"/>
-      <c r="S162" s="379"/>
-      <c r="T162" s="379"/>
+      <c r="C162" s="405"/>
+      <c r="D162" s="405"/>
+      <c r="E162" s="405"/>
+      <c r="F162" s="405"/>
+      <c r="G162" s="405"/>
+      <c r="H162" s="405"/>
+      <c r="I162" s="405"/>
+      <c r="J162" s="405"/>
+      <c r="K162" s="405"/>
+      <c r="L162" s="405"/>
+      <c r="M162" s="405"/>
+      <c r="N162" s="405"/>
+      <c r="O162" s="405"/>
+      <c r="P162" s="405"/>
+      <c r="Q162" s="405"/>
+      <c r="R162" s="405"/>
+      <c r="S162" s="405"/>
+      <c r="T162" s="405"/>
     </row>
     <row r="163" spans="1:20" ht="49.7" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B163" s="380"/>
-      <c r="C163" s="380"/>
-      <c r="D163" s="380"/>
-      <c r="E163" s="380"/>
-      <c r="F163" s="380"/>
-      <c r="G163" s="380"/>
-      <c r="H163" s="380"/>
-      <c r="I163" s="380"/>
-      <c r="J163" s="380"/>
-      <c r="K163" s="380"/>
-      <c r="L163" s="380"/>
-      <c r="M163" s="380"/>
-      <c r="N163" s="380"/>
-      <c r="O163" s="380"/>
-      <c r="P163" s="380"/>
-      <c r="Q163" s="380"/>
-      <c r="R163" s="380"/>
-      <c r="S163" s="380"/>
-      <c r="T163" s="380"/>
+      <c r="B163" s="406"/>
+      <c r="C163" s="406"/>
+      <c r="D163" s="406"/>
+      <c r="E163" s="406"/>
+      <c r="F163" s="406"/>
+      <c r="G163" s="406"/>
+      <c r="H163" s="406"/>
+      <c r="I163" s="406"/>
+      <c r="J163" s="406"/>
+      <c r="K163" s="406"/>
+      <c r="L163" s="406"/>
+      <c r="M163" s="406"/>
+      <c r="N163" s="406"/>
+      <c r="O163" s="406"/>
+      <c r="P163" s="406"/>
+      <c r="Q163" s="406"/>
+      <c r="R163" s="406"/>
+      <c r="S163" s="406"/>
+      <c r="T163" s="406"/>
     </row>
     <row r="164" spans="1:20" ht="13.7" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B164" s="380" t="s">
+      <c r="B164" s="406" t="s">
         <v>259</v>
       </c>
-      <c r="C164" s="380"/>
-      <c r="D164" s="380"/>
-      <c r="E164" s="380"/>
-      <c r="F164" s="380"/>
-      <c r="G164" s="380"/>
-      <c r="H164" s="380"/>
-      <c r="I164" s="380"/>
-      <c r="J164" s="380"/>
-      <c r="K164" s="380"/>
-      <c r="L164" s="380"/>
-      <c r="M164" s="380"/>
-      <c r="N164" s="380"/>
-      <c r="O164" s="380"/>
-      <c r="P164" s="380"/>
-      <c r="Q164" s="380"/>
-      <c r="R164" s="380"/>
-      <c r="S164" s="380"/>
-      <c r="T164" s="380"/>
+      <c r="C164" s="406"/>
+      <c r="D164" s="406"/>
+      <c r="E164" s="406"/>
+      <c r="F164" s="406"/>
+      <c r="G164" s="406"/>
+      <c r="H164" s="406"/>
+      <c r="I164" s="406"/>
+      <c r="J164" s="406"/>
+      <c r="K164" s="406"/>
+      <c r="L164" s="406"/>
+      <c r="M164" s="406"/>
+      <c r="N164" s="406"/>
+      <c r="O164" s="406"/>
+      <c r="P164" s="406"/>
+      <c r="Q164" s="406"/>
+      <c r="R164" s="406"/>
+      <c r="S164" s="406"/>
+      <c r="T164" s="406"/>
     </row>
     <row r="165" spans="1:20" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B165" s="380"/>
-      <c r="C165" s="380"/>
-      <c r="D165" s="380"/>
-      <c r="E165" s="380"/>
-      <c r="F165" s="380"/>
-      <c r="G165" s="380"/>
-      <c r="H165" s="380"/>
-      <c r="I165" s="380"/>
-      <c r="J165" s="380"/>
-      <c r="K165" s="380"/>
-      <c r="L165" s="380"/>
-      <c r="M165" s="380"/>
-      <c r="N165" s="380"/>
-      <c r="O165" s="380"/>
-      <c r="P165" s="380"/>
-      <c r="Q165" s="380"/>
-      <c r="R165" s="380"/>
-      <c r="S165" s="380"/>
-      <c r="T165" s="380"/>
+      <c r="B165" s="406"/>
+      <c r="C165" s="406"/>
+      <c r="D165" s="406"/>
+      <c r="E165" s="406"/>
+      <c r="F165" s="406"/>
+      <c r="G165" s="406"/>
+      <c r="H165" s="406"/>
+      <c r="I165" s="406"/>
+      <c r="J165" s="406"/>
+      <c r="K165" s="406"/>
+      <c r="L165" s="406"/>
+      <c r="M165" s="406"/>
+      <c r="N165" s="406"/>
+      <c r="O165" s="406"/>
+      <c r="P165" s="406"/>
+      <c r="Q165" s="406"/>
+      <c r="R165" s="406"/>
+      <c r="S165" s="406"/>
+      <c r="T165" s="406"/>
     </row>
     <row r="166" spans="1:20" ht="3.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B166" s="380"/>
-      <c r="C166" s="380"/>
-      <c r="D166" s="380"/>
-      <c r="E166" s="380"/>
-      <c r="F166" s="380"/>
-      <c r="G166" s="380"/>
-      <c r="H166" s="380"/>
-      <c r="I166" s="380"/>
-      <c r="J166" s="380"/>
-      <c r="K166" s="380"/>
-      <c r="L166" s="380"/>
-      <c r="M166" s="380"/>
-      <c r="N166" s="380"/>
-      <c r="O166" s="380"/>
-      <c r="P166" s="380"/>
-      <c r="Q166" s="380"/>
-      <c r="R166" s="380"/>
-      <c r="S166" s="380"/>
-      <c r="T166" s="380"/>
+      <c r="B166" s="406"/>
+      <c r="C166" s="406"/>
+      <c r="D166" s="406"/>
+      <c r="E166" s="406"/>
+      <c r="F166" s="406"/>
+      <c r="G166" s="406"/>
+      <c r="H166" s="406"/>
+      <c r="I166" s="406"/>
+      <c r="J166" s="406"/>
+      <c r="K166" s="406"/>
+      <c r="L166" s="406"/>
+      <c r="M166" s="406"/>
+      <c r="N166" s="406"/>
+      <c r="O166" s="406"/>
+      <c r="P166" s="406"/>
+      <c r="Q166" s="406"/>
+      <c r="R166" s="406"/>
+      <c r="S166" s="406"/>
+      <c r="T166" s="406"/>
     </row>
     <row r="167" spans="1:20" ht="128.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B167" s="380"/>
-      <c r="C167" s="380"/>
-      <c r="D167" s="380"/>
-      <c r="E167" s="380"/>
-      <c r="F167" s="380"/>
-      <c r="G167" s="380"/>
-      <c r="H167" s="380"/>
-      <c r="I167" s="380"/>
-      <c r="J167" s="380"/>
-      <c r="K167" s="380"/>
-      <c r="L167" s="380"/>
-      <c r="M167" s="380"/>
-      <c r="N167" s="380"/>
-      <c r="O167" s="380"/>
-      <c r="P167" s="380"/>
-      <c r="Q167" s="380"/>
-      <c r="R167" s="380"/>
-      <c r="S167" s="380"/>
-      <c r="T167" s="380"/>
+      <c r="B167" s="406"/>
+      <c r="C167" s="406"/>
+      <c r="D167" s="406"/>
+      <c r="E167" s="406"/>
+      <c r="F167" s="406"/>
+      <c r="G167" s="406"/>
+      <c r="H167" s="406"/>
+      <c r="I167" s="406"/>
+      <c r="J167" s="406"/>
+      <c r="K167" s="406"/>
+      <c r="L167" s="406"/>
+      <c r="M167" s="406"/>
+      <c r="N167" s="406"/>
+      <c r="O167" s="406"/>
+      <c r="P167" s="406"/>
+      <c r="Q167" s="406"/>
+      <c r="R167" s="406"/>
+      <c r="S167" s="406"/>
+      <c r="T167" s="406"/>
     </row>
   </sheetData>
   <mergeCells count="186">
+    <mergeCell ref="P146:Q146"/>
+    <mergeCell ref="P147:Q147"/>
+    <mergeCell ref="P148:Q148"/>
+    <mergeCell ref="P149:Q149"/>
+    <mergeCell ref="P151:Q151"/>
+    <mergeCell ref="P141:Q141"/>
+    <mergeCell ref="P142:Q142"/>
+    <mergeCell ref="P143:Q143"/>
+    <mergeCell ref="P144:Q144"/>
+    <mergeCell ref="P145:Q145"/>
+    <mergeCell ref="P150:Q150"/>
+    <mergeCell ref="B162:T163"/>
+    <mergeCell ref="B164:T167"/>
+    <mergeCell ref="P157:Q157"/>
+    <mergeCell ref="P158:Q158"/>
+    <mergeCell ref="P161:Q161"/>
+    <mergeCell ref="P159:Q159"/>
+    <mergeCell ref="P160:Q160"/>
+    <mergeCell ref="P152:Q152"/>
+    <mergeCell ref="P153:Q153"/>
+    <mergeCell ref="P154:Q154"/>
+    <mergeCell ref="P155:Q155"/>
+    <mergeCell ref="P156:Q156"/>
+    <mergeCell ref="S161:T161"/>
+    <mergeCell ref="P136:Q136"/>
+    <mergeCell ref="P137:Q137"/>
+    <mergeCell ref="P138:Q138"/>
+    <mergeCell ref="P139:Q139"/>
+    <mergeCell ref="P140:Q140"/>
+    <mergeCell ref="P131:Q131"/>
+    <mergeCell ref="P132:Q132"/>
+    <mergeCell ref="P133:Q133"/>
+    <mergeCell ref="P134:Q134"/>
+    <mergeCell ref="P135:Q135"/>
+    <mergeCell ref="P126:Q126"/>
+    <mergeCell ref="P127:Q127"/>
+    <mergeCell ref="P128:Q128"/>
+    <mergeCell ref="P129:Q129"/>
+    <mergeCell ref="P130:Q130"/>
+    <mergeCell ref="P121:Q121"/>
+    <mergeCell ref="P122:Q122"/>
+    <mergeCell ref="P123:Q123"/>
+    <mergeCell ref="P124:Q124"/>
+    <mergeCell ref="P125:Q125"/>
+    <mergeCell ref="P116:Q116"/>
+    <mergeCell ref="P117:Q117"/>
+    <mergeCell ref="P118:Q118"/>
+    <mergeCell ref="P119:Q119"/>
+    <mergeCell ref="P120:Q120"/>
+    <mergeCell ref="P111:Q111"/>
+    <mergeCell ref="P112:Q112"/>
+    <mergeCell ref="P113:Q113"/>
+    <mergeCell ref="P114:Q114"/>
+    <mergeCell ref="P115:Q115"/>
+    <mergeCell ref="P106:Q106"/>
+    <mergeCell ref="P107:Q107"/>
+    <mergeCell ref="P108:Q108"/>
+    <mergeCell ref="P109:Q109"/>
+    <mergeCell ref="P110:Q110"/>
+    <mergeCell ref="P101:Q101"/>
+    <mergeCell ref="P102:Q102"/>
+    <mergeCell ref="P103:Q103"/>
+    <mergeCell ref="P104:Q104"/>
+    <mergeCell ref="P105:Q105"/>
+    <mergeCell ref="P96:Q96"/>
+    <mergeCell ref="P97:Q97"/>
+    <mergeCell ref="P98:Q98"/>
+    <mergeCell ref="P99:Q99"/>
+    <mergeCell ref="P100:Q100"/>
+    <mergeCell ref="P91:Q91"/>
+    <mergeCell ref="P92:Q92"/>
+    <mergeCell ref="P93:Q93"/>
+    <mergeCell ref="P94:Q94"/>
+    <mergeCell ref="P95:Q95"/>
+    <mergeCell ref="P86:Q86"/>
+    <mergeCell ref="P87:Q87"/>
+    <mergeCell ref="P88:Q88"/>
+    <mergeCell ref="P89:Q89"/>
+    <mergeCell ref="P90:Q90"/>
+    <mergeCell ref="P81:Q81"/>
+    <mergeCell ref="P82:Q82"/>
+    <mergeCell ref="P83:Q83"/>
+    <mergeCell ref="P84:Q84"/>
+    <mergeCell ref="P85:Q85"/>
+    <mergeCell ref="P76:Q76"/>
+    <mergeCell ref="P77:Q77"/>
+    <mergeCell ref="P78:Q78"/>
+    <mergeCell ref="P79:Q79"/>
+    <mergeCell ref="P80:Q80"/>
+    <mergeCell ref="P71:Q71"/>
+    <mergeCell ref="P72:Q72"/>
+    <mergeCell ref="P73:Q73"/>
+    <mergeCell ref="P74:Q74"/>
+    <mergeCell ref="P75:Q75"/>
+    <mergeCell ref="P66:Q66"/>
+    <mergeCell ref="P67:Q67"/>
+    <mergeCell ref="P68:Q68"/>
+    <mergeCell ref="P69:Q69"/>
+    <mergeCell ref="P70:Q70"/>
+    <mergeCell ref="P61:Q61"/>
+    <mergeCell ref="P62:Q62"/>
+    <mergeCell ref="P63:Q63"/>
+    <mergeCell ref="P64:Q64"/>
+    <mergeCell ref="P65:Q65"/>
+    <mergeCell ref="P56:Q56"/>
+    <mergeCell ref="P57:Q57"/>
+    <mergeCell ref="P58:Q58"/>
+    <mergeCell ref="P59:Q59"/>
+    <mergeCell ref="P60:Q60"/>
+    <mergeCell ref="P51:Q51"/>
+    <mergeCell ref="P52:Q52"/>
+    <mergeCell ref="P53:Q53"/>
+    <mergeCell ref="P54:Q54"/>
+    <mergeCell ref="P55:Q55"/>
+    <mergeCell ref="P27:Q27"/>
+    <mergeCell ref="P28:Q28"/>
+    <mergeCell ref="P29:Q29"/>
+    <mergeCell ref="P30:Q30"/>
+    <mergeCell ref="P46:Q46"/>
+    <mergeCell ref="P47:Q47"/>
+    <mergeCell ref="P48:Q48"/>
+    <mergeCell ref="P49:Q49"/>
+    <mergeCell ref="P50:Q50"/>
+    <mergeCell ref="P41:Q41"/>
+    <mergeCell ref="P42:Q42"/>
+    <mergeCell ref="P43:Q43"/>
+    <mergeCell ref="P44:Q44"/>
+    <mergeCell ref="P45:Q45"/>
+    <mergeCell ref="P36:Q36"/>
+    <mergeCell ref="P37:Q37"/>
+    <mergeCell ref="P38:Q38"/>
+    <mergeCell ref="P39:Q39"/>
+    <mergeCell ref="P40:Q40"/>
+    <mergeCell ref="P31:Q31"/>
+    <mergeCell ref="P32:Q32"/>
+    <mergeCell ref="P33:Q33"/>
+    <mergeCell ref="P34:Q34"/>
+    <mergeCell ref="P35:Q35"/>
+    <mergeCell ref="K2:L2"/>
+    <mergeCell ref="M4:M5"/>
+    <mergeCell ref="P1:Q1"/>
+    <mergeCell ref="P2:Q2"/>
+    <mergeCell ref="G2:H2"/>
+    <mergeCell ref="N4:N5"/>
+    <mergeCell ref="O4:O5"/>
+    <mergeCell ref="C2:E2"/>
+    <mergeCell ref="C1:L1"/>
+    <mergeCell ref="N1:O1"/>
+    <mergeCell ref="P4:Q4"/>
+    <mergeCell ref="P5:Q5"/>
+    <mergeCell ref="A3:T3"/>
+    <mergeCell ref="R4:S5"/>
+    <mergeCell ref="T4:T5"/>
+    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="B4:B5"/>
+    <mergeCell ref="C4:C5"/>
+    <mergeCell ref="D4:D5"/>
+    <mergeCell ref="K4:K5"/>
+    <mergeCell ref="H4:H5"/>
+    <mergeCell ref="E4:E5"/>
+    <mergeCell ref="F4:F5"/>
+    <mergeCell ref="G4:G5"/>
     <mergeCell ref="I4:I5"/>
     <mergeCell ref="J4:J5"/>
     <mergeCell ref="P6:Q6"/>
@@ -17303,168 +17465,6 @@
     <mergeCell ref="P23:Q23"/>
     <mergeCell ref="P24:Q24"/>
     <mergeCell ref="P25:Q25"/>
-    <mergeCell ref="K2:L2"/>
-    <mergeCell ref="M4:M5"/>
-    <mergeCell ref="P1:Q1"/>
-    <mergeCell ref="P2:Q2"/>
-    <mergeCell ref="G2:H2"/>
-    <mergeCell ref="N4:N5"/>
-    <mergeCell ref="O4:O5"/>
-    <mergeCell ref="C2:E2"/>
-    <mergeCell ref="C1:L1"/>
-    <mergeCell ref="N1:O1"/>
-    <mergeCell ref="P4:Q4"/>
-    <mergeCell ref="P5:Q5"/>
-    <mergeCell ref="A3:T3"/>
-    <mergeCell ref="R4:S5"/>
-    <mergeCell ref="T4:T5"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="B4:B5"/>
-    <mergeCell ref="C4:C5"/>
-    <mergeCell ref="D4:D5"/>
-    <mergeCell ref="K4:K5"/>
-    <mergeCell ref="H4:H5"/>
-    <mergeCell ref="E4:E5"/>
-    <mergeCell ref="F4:F5"/>
-    <mergeCell ref="G4:G5"/>
-    <mergeCell ref="P27:Q27"/>
-    <mergeCell ref="P28:Q28"/>
-    <mergeCell ref="P29:Q29"/>
-    <mergeCell ref="P30:Q30"/>
-    <mergeCell ref="P46:Q46"/>
-    <mergeCell ref="P47:Q47"/>
-    <mergeCell ref="P48:Q48"/>
-    <mergeCell ref="P49:Q49"/>
-    <mergeCell ref="P50:Q50"/>
-    <mergeCell ref="P41:Q41"/>
-    <mergeCell ref="P42:Q42"/>
-    <mergeCell ref="P43:Q43"/>
-    <mergeCell ref="P44:Q44"/>
-    <mergeCell ref="P45:Q45"/>
-    <mergeCell ref="P36:Q36"/>
-    <mergeCell ref="P37:Q37"/>
-    <mergeCell ref="P38:Q38"/>
-    <mergeCell ref="P39:Q39"/>
-    <mergeCell ref="P40:Q40"/>
-    <mergeCell ref="P31:Q31"/>
-    <mergeCell ref="P32:Q32"/>
-    <mergeCell ref="P33:Q33"/>
-    <mergeCell ref="P34:Q34"/>
-    <mergeCell ref="P35:Q35"/>
-    <mergeCell ref="P56:Q56"/>
-    <mergeCell ref="P57:Q57"/>
-    <mergeCell ref="P58:Q58"/>
-    <mergeCell ref="P59:Q59"/>
-    <mergeCell ref="P60:Q60"/>
-    <mergeCell ref="P51:Q51"/>
-    <mergeCell ref="P52:Q52"/>
-    <mergeCell ref="P53:Q53"/>
-    <mergeCell ref="P54:Q54"/>
-    <mergeCell ref="P55:Q55"/>
-    <mergeCell ref="P66:Q66"/>
-    <mergeCell ref="P67:Q67"/>
-    <mergeCell ref="P68:Q68"/>
-    <mergeCell ref="P69:Q69"/>
-    <mergeCell ref="P70:Q70"/>
-    <mergeCell ref="P61:Q61"/>
-    <mergeCell ref="P62:Q62"/>
-    <mergeCell ref="P63:Q63"/>
-    <mergeCell ref="P64:Q64"/>
-    <mergeCell ref="P65:Q65"/>
-    <mergeCell ref="P76:Q76"/>
-    <mergeCell ref="P77:Q77"/>
-    <mergeCell ref="P78:Q78"/>
-    <mergeCell ref="P79:Q79"/>
-    <mergeCell ref="P80:Q80"/>
-    <mergeCell ref="P71:Q71"/>
-    <mergeCell ref="P72:Q72"/>
-    <mergeCell ref="P73:Q73"/>
-    <mergeCell ref="P74:Q74"/>
-    <mergeCell ref="P75:Q75"/>
-    <mergeCell ref="P86:Q86"/>
-    <mergeCell ref="P87:Q87"/>
-    <mergeCell ref="P88:Q88"/>
-    <mergeCell ref="P89:Q89"/>
-    <mergeCell ref="P90:Q90"/>
-    <mergeCell ref="P81:Q81"/>
-    <mergeCell ref="P82:Q82"/>
-    <mergeCell ref="P83:Q83"/>
-    <mergeCell ref="P84:Q84"/>
-    <mergeCell ref="P85:Q85"/>
-    <mergeCell ref="P96:Q96"/>
-    <mergeCell ref="P97:Q97"/>
-    <mergeCell ref="P98:Q98"/>
-    <mergeCell ref="P99:Q99"/>
-    <mergeCell ref="P100:Q100"/>
-    <mergeCell ref="P91:Q91"/>
-    <mergeCell ref="P92:Q92"/>
-    <mergeCell ref="P93:Q93"/>
-    <mergeCell ref="P94:Q94"/>
-    <mergeCell ref="P95:Q95"/>
-    <mergeCell ref="P106:Q106"/>
-    <mergeCell ref="P107:Q107"/>
-    <mergeCell ref="P108:Q108"/>
-    <mergeCell ref="P109:Q109"/>
-    <mergeCell ref="P110:Q110"/>
-    <mergeCell ref="P101:Q101"/>
-    <mergeCell ref="P102:Q102"/>
-    <mergeCell ref="P103:Q103"/>
-    <mergeCell ref="P104:Q104"/>
-    <mergeCell ref="P105:Q105"/>
-    <mergeCell ref="P116:Q116"/>
-    <mergeCell ref="P117:Q117"/>
-    <mergeCell ref="P118:Q118"/>
-    <mergeCell ref="P119:Q119"/>
-    <mergeCell ref="P120:Q120"/>
-    <mergeCell ref="P111:Q111"/>
-    <mergeCell ref="P112:Q112"/>
-    <mergeCell ref="P113:Q113"/>
-    <mergeCell ref="P114:Q114"/>
-    <mergeCell ref="P115:Q115"/>
-    <mergeCell ref="P126:Q126"/>
-    <mergeCell ref="P127:Q127"/>
-    <mergeCell ref="P128:Q128"/>
-    <mergeCell ref="P129:Q129"/>
-    <mergeCell ref="P130:Q130"/>
-    <mergeCell ref="P121:Q121"/>
-    <mergeCell ref="P122:Q122"/>
-    <mergeCell ref="P123:Q123"/>
-    <mergeCell ref="P124:Q124"/>
-    <mergeCell ref="P125:Q125"/>
-    <mergeCell ref="P136:Q136"/>
-    <mergeCell ref="P137:Q137"/>
-    <mergeCell ref="P138:Q138"/>
-    <mergeCell ref="P139:Q139"/>
-    <mergeCell ref="P140:Q140"/>
-    <mergeCell ref="P131:Q131"/>
-    <mergeCell ref="P132:Q132"/>
-    <mergeCell ref="P133:Q133"/>
-    <mergeCell ref="P134:Q134"/>
-    <mergeCell ref="P135:Q135"/>
-    <mergeCell ref="B162:T163"/>
-    <mergeCell ref="B164:T167"/>
-    <mergeCell ref="P157:Q157"/>
-    <mergeCell ref="P158:Q158"/>
-    <mergeCell ref="P161:Q161"/>
-    <mergeCell ref="P159:Q159"/>
-    <mergeCell ref="P160:Q160"/>
-    <mergeCell ref="P152:Q152"/>
-    <mergeCell ref="P153:Q153"/>
-    <mergeCell ref="P154:Q154"/>
-    <mergeCell ref="P155:Q155"/>
-    <mergeCell ref="P156:Q156"/>
-    <mergeCell ref="S161:T161"/>
-    <mergeCell ref="P146:Q146"/>
-    <mergeCell ref="P147:Q147"/>
-    <mergeCell ref="P148:Q148"/>
-    <mergeCell ref="P149:Q149"/>
-    <mergeCell ref="P151:Q151"/>
-    <mergeCell ref="P141:Q141"/>
-    <mergeCell ref="P142:Q142"/>
-    <mergeCell ref="P143:Q143"/>
-    <mergeCell ref="P144:Q144"/>
-    <mergeCell ref="P145:Q145"/>
-    <mergeCell ref="P150:Q150"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="U66" r:id="rId1" xr:uid="{60CCA824-04D7-4098-BB5B-CC4EC0E5DE92}"/>
@@ -20347,6 +20347,45 @@
     </row>
   </sheetData>
   <mergeCells count="55">
+    <mergeCell ref="H203:J203"/>
+    <mergeCell ref="C205:J207"/>
+    <mergeCell ref="H230:J230"/>
+    <mergeCell ref="C232:J234"/>
+    <mergeCell ref="H221:J221"/>
+    <mergeCell ref="C223:J225"/>
+    <mergeCell ref="H212:J212"/>
+    <mergeCell ref="C214:J216"/>
+    <mergeCell ref="C178:J180"/>
+    <mergeCell ref="H185:J185"/>
+    <mergeCell ref="C187:J189"/>
+    <mergeCell ref="H194:J194"/>
+    <mergeCell ref="C196:J198"/>
+    <mergeCell ref="K65:M71"/>
+    <mergeCell ref="H49:J49"/>
+    <mergeCell ref="C51:J53"/>
+    <mergeCell ref="H58:J58"/>
+    <mergeCell ref="C60:J62"/>
+    <mergeCell ref="H67:J67"/>
+    <mergeCell ref="C69:J71"/>
+    <mergeCell ref="C24:J26"/>
+    <mergeCell ref="H31:J31"/>
+    <mergeCell ref="C33:J35"/>
+    <mergeCell ref="H4:J4"/>
+    <mergeCell ref="C6:J8"/>
+    <mergeCell ref="H13:J13"/>
+    <mergeCell ref="C15:J17"/>
+    <mergeCell ref="H22:J22"/>
+    <mergeCell ref="H40:J40"/>
+    <mergeCell ref="C42:J44"/>
+    <mergeCell ref="H131:J131"/>
+    <mergeCell ref="C133:J135"/>
+    <mergeCell ref="H122:J122"/>
+    <mergeCell ref="C124:J126"/>
+    <mergeCell ref="H113:J113"/>
+    <mergeCell ref="C115:J117"/>
+    <mergeCell ref="H104:J104"/>
+    <mergeCell ref="C106:J108"/>
+    <mergeCell ref="H85:J85"/>
     <mergeCell ref="H239:J239"/>
     <mergeCell ref="C241:J243"/>
     <mergeCell ref="C160:J162"/>
@@ -20363,45 +20402,6 @@
     <mergeCell ref="H167:J167"/>
     <mergeCell ref="C169:J171"/>
     <mergeCell ref="H176:J176"/>
-    <mergeCell ref="H40:J40"/>
-    <mergeCell ref="C42:J44"/>
-    <mergeCell ref="H131:J131"/>
-    <mergeCell ref="C133:J135"/>
-    <mergeCell ref="H122:J122"/>
-    <mergeCell ref="C124:J126"/>
-    <mergeCell ref="H113:J113"/>
-    <mergeCell ref="C115:J117"/>
-    <mergeCell ref="H104:J104"/>
-    <mergeCell ref="C106:J108"/>
-    <mergeCell ref="H85:J85"/>
-    <mergeCell ref="C24:J26"/>
-    <mergeCell ref="H31:J31"/>
-    <mergeCell ref="C33:J35"/>
-    <mergeCell ref="H4:J4"/>
-    <mergeCell ref="C6:J8"/>
-    <mergeCell ref="H13:J13"/>
-    <mergeCell ref="C15:J17"/>
-    <mergeCell ref="H22:J22"/>
-    <mergeCell ref="K65:M71"/>
-    <mergeCell ref="H49:J49"/>
-    <mergeCell ref="C51:J53"/>
-    <mergeCell ref="H58:J58"/>
-    <mergeCell ref="C60:J62"/>
-    <mergeCell ref="H67:J67"/>
-    <mergeCell ref="C69:J71"/>
-    <mergeCell ref="C178:J180"/>
-    <mergeCell ref="H185:J185"/>
-    <mergeCell ref="C187:J189"/>
-    <mergeCell ref="H194:J194"/>
-    <mergeCell ref="C196:J198"/>
-    <mergeCell ref="H203:J203"/>
-    <mergeCell ref="C205:J207"/>
-    <mergeCell ref="H230:J230"/>
-    <mergeCell ref="C232:J234"/>
-    <mergeCell ref="H221:J221"/>
-    <mergeCell ref="C223:J225"/>
-    <mergeCell ref="H212:J212"/>
-    <mergeCell ref="C214:J216"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
